--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -858,7 +858,7 @@
         <v>9.16</v>
       </c>
       <c r="L7" t="n">
-        <v>3738670000000</v>
+        <v>3738850000000</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>7.14</v>
       </c>
       <c r="L14" t="n">
-        <v>1076990000000</v>
+        <v>1077430000000</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>12.03</v>
       </c>
       <c r="L19" t="n">
-        <v>541570000000</v>
+        <v>545810000000</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
         <v>6.05</v>
       </c>
       <c r="L111" t="n">
-        <v>86170000000</v>
+        <v>86140000000</v>
       </c>
       <c r="M111" t="inlineStr">
         <is>
@@ -10560,7 +10560,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="L154" t="n">
-        <v>35910000000</v>
+        <v>35970000000</v>
       </c>
       <c r="M154" t="inlineStr">
         <is>
@@ -13926,7 +13926,7 @@
         <v>1</v>
       </c>
       <c r="L205" t="n">
-        <v>369500000</v>
+        <v>369490000</v>
       </c>
       <c r="M205" t="inlineStr">
         <is>

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -457,7 +457,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
@@ -858,7 +858,7 @@
         <v>8.82</v>
       </c>
       <c r="L7" t="n">
-        <v>3715270000000</v>
+        <v>3714340000000</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>17.69</v>
       </c>
       <c r="L11" t="n">
-        <v>1607300000000</v>
+        <v>1613740000000</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>7.11</v>
       </c>
       <c r="L14" t="n">
-        <v>1067180000000</v>
+        <v>1068860000000</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>20.47</v>
       </c>
       <c r="L74" t="n">
-        <v>172950000000</v>
+        <v>172960000000</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>11.17</v>
       </c>
       <c r="L93" t="n">
-        <v>127210000000</v>
+        <v>127260000000</v>
       </c>
       <c r="M93" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>1.1</v>
       </c>
       <c r="L148" t="n">
-        <v>40580000000</v>
+        <v>40830000000</v>
       </c>
       <c r="M148" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
         <v>2.83</v>
       </c>
       <c r="L173" t="n">
-        <v>16650000000</v>
+        <v>16640000000</v>
       </c>
       <c r="M173" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>0.64</v>
       </c>
       <c r="L204" t="n">
-        <v>673900000</v>
+        <v>673910000</v>
       </c>
       <c r="M204" t="inlineStr">
         <is>
@@ -13926,7 +13926,7 @@
         <v>1.01</v>
       </c>
       <c r="L205" t="n">
-        <v>363230000</v>
+        <v>363220000</v>
       </c>
       <c r="M205" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>iShares Bitcoin Trust Beneficial Interest</t>
+          <t>iShares Bitcoin Trust</t>
         </is>
       </c>
       <c r="H206" s="3" t="inlineStr">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -858,7 +858,7 @@
         <v>7.96</v>
       </c>
       <c r="L7" t="n">
-        <v>3800330000000</v>
+        <v>3798670000000</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>6.49</v>
       </c>
       <c r="L14" t="n">
-        <v>1081450000000</v>
+        <v>1081160000000</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -858,7 +858,7 @@
         <v>7.59</v>
       </c>
       <c r="L7" t="n">
-        <v>3790120000000</v>
+        <v>3790970000000</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>6.36</v>
       </c>
       <c r="L14" t="n">
-        <v>1074600000000</v>
+        <v>1074760000000</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>1.09</v>
       </c>
       <c r="L147" t="n">
-        <v>40310000000</v>
+        <v>40390000000</v>
       </c>
       <c r="M147" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
         <v>2.45</v>
       </c>
       <c r="L172" t="n">
-        <v>16880000000</v>
+        <v>16890000000</v>
       </c>
       <c r="M172" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>iShares Bitcoin Trust</t>
+          <t>iShares Bitcoin Trust ETF</t>
         </is>
       </c>
       <c r="H206" s="3" t="inlineStr">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -858,7 +858,7 @@
         <v>6.79</v>
       </c>
       <c r="L7" t="n">
-        <v>3781970000000</v>
+        <v>3781300000000</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>5.92</v>
       </c>
       <c r="L14" t="n">
-        <v>1084300000000</v>
+        <v>1084820000000</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>0.53</v>
       </c>
       <c r="L76" t="n">
-        <v>171730000000</v>
+        <v>171740000000</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>1.97</v>
       </c>
       <c r="L107" t="n">
-        <v>94180000000</v>
+        <v>94320000000</v>
       </c>
       <c r="M107" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>0.95</v>
       </c>
       <c r="L148" t="n">
-        <v>40110000000</v>
+        <v>40100000000</v>
       </c>
       <c r="M148" t="inlineStr">
         <is>
@@ -13926,7 +13926,7 @@
         <v>1.09</v>
       </c>
       <c r="L205" t="n">
-        <v>469800000</v>
+        <v>469790000</v>
       </c>
       <c r="M205" t="inlineStr">
         <is>

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -858,7 +858,7 @@
         <v>7.18</v>
       </c>
       <c r="L7" t="n">
-        <v>3799610000000</v>
+        <v>3803830000000</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>6.19</v>
       </c>
       <c r="L14" t="n">
-        <v>1072300000000</v>
+        <v>1071270000000</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10114,132 +10114,132 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Carnival Corp</t>
+          <t>Rocket Lab Corp</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>30.92</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>8.93%</t>
         </is>
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>6.98%</t>
+          <t>19.66%</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>11.58%</t>
+          <t>35.53%</t>
         </is>
       </c>
       <c r="G148" s="4" t="inlineStr">
         <is>
-          <t>17.53%</t>
+          <t>82.31%</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>8.93%</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>23.43%</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>63.76%</t>
+          <t>188.72%</t>
+        </is>
+      </c>
+      <c r="J148" s="5" t="inlineStr">
+        <is>
+          <t>67.55%</t>
         </is>
       </c>
       <c r="K148" t="n">
-        <v>0.9399999999999999</v>
+        <v>5.38</v>
       </c>
       <c r="L148" t="n">
-        <v>40600000000</v>
+        <v>40590000000</v>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>32.89 -5.99</t>
+          <t>79.83 -4.81</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>15.07 105.18</t>
+          <t>14.71 416.59</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Rocket Lab Corp</t>
+          <t>Carnival Corp</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>75.98999999999999</v>
+        <v>30.92</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>8.93%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>19.66%</t>
+          <t>6.98%</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>35.53%</t>
+          <t>11.58%</t>
         </is>
       </c>
       <c r="G149" s="4" t="inlineStr">
         <is>
-          <t>82.31%</t>
+          <t>17.53%</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>8.93%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>188.72%</t>
-        </is>
-      </c>
-      <c r="J149" s="5" t="inlineStr">
-        <is>
-          <t>67.55%</t>
+          <t>23.43%</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>63.76%</t>
         </is>
       </c>
       <c r="K149" t="n">
-        <v>5.38</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L149" t="n">
-        <v>40590000000</v>
+        <v>40570000000</v>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>79.83 -4.81</t>
+          <t>32.89 -5.99</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>14.71 416.59</t>
+          <t>15.07 105.18</t>
         </is>
       </c>
     </row>
@@ -11880,7 +11880,7 @@
         <v>2.27</v>
       </c>
       <c r="L174" t="n">
-        <v>15960000000</v>
+        <v>15940000000</v>
       </c>
       <c r="M174" t="inlineStr">
         <is>

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -726,7 +726,7 @@
         <v>4.41</v>
       </c>
       <c r="L5" t="n">
-        <v>3832540000000</v>
+        <v>3827670000000</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         <v>7.39</v>
       </c>
       <c r="L7" t="n">
-        <v>3967900000000</v>
+        <v>3967940000000</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>7.92</v>
       </c>
       <c r="L8" t="n">
-        <v>3562190000000</v>
+        <v>3553490000000</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>5.29</v>
       </c>
       <c r="L9" t="n">
-        <v>2644550000000</v>
+        <v>2632890000000</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>13.57</v>
       </c>
       <c r="L12" t="n">
-        <v>1635600000000</v>
+        <v>1576380000000</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>16.5</v>
       </c>
       <c r="L13" t="n">
-        <v>1480020000000</v>
+        <v>1449390000000</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>6.32</v>
       </c>
       <c r="L14" t="n">
-        <v>1077060000000</v>
+        <v>1078510000000</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>31.37</v>
       </c>
       <c r="L15" t="n">
-        <v>1005470000000</v>
+        <v>1025920000000</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>2.1</v>
       </c>
       <c r="L16" t="n">
-        <v>912820000000</v>
+        <v>901190000000</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1798,132 +1798,132 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ASML Holding NV</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1273.88</v>
+        <v>204.39</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>6.66%</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>14.40%</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>18.41%</t>
+          <t>-0.66%</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>-1.60%</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>1.34%</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>48.45%</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>19.07%</t>
+          <t>16.66%</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-1.24%</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>68.15%</t>
-        </is>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>71.67%</t>
+          <t>39.77%</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>47.61%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>37.26</v>
+        <v>3.25</v>
       </c>
       <c r="L22" t="n">
-        <v>493760000000</v>
+        <v>495710000000</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1246.38 2.21</t>
+          <t>215.18 -5.02</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>578.51 120.20</t>
+          <t>140.68 45.29</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>ASML Holding NV</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>204.39</v>
+        <v>1273.88</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-0.66%</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>-1.60%</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>1.34%</t>
+          <t>6.66%</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>14.40%</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>18.41%</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>16.66%</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>-1.24%</t>
+          <t>48.45%</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>19.07%</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>39.77%</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>47.61%</t>
+          <t>68.15%</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>71.67%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>3.25</v>
+        <v>37.26</v>
       </c>
       <c r="L23" t="n">
-        <v>492440000000</v>
+        <v>493760000000</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>215.18 -5.02</t>
+          <t>1246.38 2.21</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>140.68 45.29</t>
+          <t>578.51 120.20</t>
         </is>
       </c>
     </row>
@@ -1996,198 +1996,198 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Costco Wholesale Corp</t>
+          <t>Netflix Inc</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>924.88</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.05%</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>5.98%</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>3.39%</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>-2.67%</t>
+          <t>-1.18%</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>-3.87%</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>-12.14%</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>-20.99%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>7.25%</t>
+          <t>-4.59%</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.38%</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>66.16%</t>
+          <t>1.75%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>27.27%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>17.04</v>
+        <v>2.34</v>
       </c>
       <c r="L25" t="n">
-        <v>410530000000</v>
+        <v>413680000000</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1078.23 -14.22</t>
+          <t>134.12 -33.30</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>844.06 9.58</t>
+          <t>82.11 8.95</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Netflix Inc</t>
+          <t>Bank Of America Corp</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>89.45999999999999</v>
+        <v>55.85</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-1.18%</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>-3.87%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-12.14%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-20.99%</t>
+          <t>-0.59%</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>0.49%</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>3.34%</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>16.11%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-4.59%</t>
+          <t>1.55%</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.75%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>27.27%</t>
+          <t>21.20%</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>55.11%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>2.34</v>
+        <v>0.96</v>
       </c>
       <c r="L26" t="n">
-        <v>408790000000</v>
+        <v>410250000000</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>134.12 -33.30</t>
+          <t>57.55 -2.95</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>82.11 8.95</t>
+          <t>33.06 68.91</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Bank Of America Corp</t>
+          <t>Costco Wholesale Corp</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>55.85</v>
+        <v>924.88</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-0.59%</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>0.49%</t>
+          <t>1.05%</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>5.98%</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>3.34%</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>16.11%</t>
+          <t>3.39%</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>-2.67%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>7.25%</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>21.20%</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>55.11%</t>
+          <t>0.38%</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>66.16%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>0.96</v>
+        <v>17.04</v>
       </c>
       <c r="L27" t="n">
-        <v>407840000000</v>
+        <v>406280000000</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>57.55 -2.95</t>
+          <t>1078.23 -14.22</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>33.06 68.91</t>
+          <t>844.06 9.58</t>
         </is>
       </c>
     </row>
@@ -2244,7 +2244,7 @@
         <v>5.56</v>
       </c>
       <c r="L28" t="n">
-        <v>388970000000</v>
+        <v>396120000000</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>8.74</v>
       </c>
       <c r="L30" t="n">
-        <v>372960000000</v>
+        <v>357950000000</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -2392,264 +2392,264 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Alibaba Group Holding Ltd ADR</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>321.59</v>
+        <v>150.96</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>-2.27%</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>3.49%</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>5.96%</t>
+          <t>0.03%</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>-3.95%</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>21.09%</t>
+          <t>9.61%</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>4.40%</t>
+          <t>2.99%</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>86.63%</t>
+          <t>80.12%</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>59.61%</t>
+          <t>47.41%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>8.24</v>
+        <v>4.93</v>
       </c>
       <c r="L31" t="n">
-        <v>339220000000</v>
+        <v>339190000000</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>332.79 -3.37</t>
+          <t>192.67 -21.65</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>159.36 101.80</t>
+          <t>79.43 90.06</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Alibaba Group Holding Ltd ADR</t>
+          <t>Advanced Micro Devices Inc</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>150.96</v>
+        <v>203.17</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-2.27%</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>0.03%</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>-3.95%</t>
+          <t>-0.74%</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>-4.24%</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>-9.29%</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>9.61%</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>2.99%</t>
+          <t>22.57%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>-5.13%</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>80.12%</t>
+          <t>59.56%</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>47.41%</t>
+          <t>38.99%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>4.93</v>
+        <v>8.51</v>
       </c>
       <c r="L32" t="n">
-        <v>339190000000</v>
+        <v>333230000000</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>192.67 -21.65</t>
+          <t>267.08 -23.93</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>79.43 90.06</t>
+          <t>76.48 165.65</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble Co</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>141.87</v>
+        <v>321.59</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.24%</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>-0.87%</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>-2.30%</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>-8.68%</t>
+          <t>2.27%</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>3.49%</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>5.96%</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>21.09%</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-1.00%</t>
+          <t>4.40%</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-12.05%</t>
+          <t>86.63%</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>45.68%</t>
+          <t>59.61%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>2.15</v>
+        <v>8.24</v>
       </c>
       <c r="L33" t="n">
-        <v>331510000000</v>
+        <v>331680000000</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>179.99 -21.18</t>
+          <t>332.79 -3.37</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>137.62 3.09</t>
+          <t>159.36 101.80</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices Inc</t>
+          <t>Procter &amp; Gamble Co</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>203.17</v>
+        <v>141.87</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-0.74%</t>
+          <t>0.24%</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>-4.24%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-9.29%</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>22.57%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>-5.13%</t>
+          <t>-0.87%</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>-2.30%</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>-8.68%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-1.00%</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>59.56%</t>
+          <t>-12.05%</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>38.99%</t>
+          <t>45.68%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>8.51</v>
+        <v>2.15</v>
       </c>
       <c r="L34" t="n">
-        <v>330770000000</v>
+        <v>331510000000</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>267.08 -23.93</t>
+          <t>179.99 -21.18</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>76.48 165.65</t>
+          <t>137.62 3.09</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
         <v>3.39</v>
       </c>
       <c r="L35" t="n">
-        <v>326410000000</v>
+        <v>320650000000</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -2788,132 +2788,132 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Coca-Cola Co</t>
+          <t>Wells Fargo &amp; Co</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>70.51000000000001</v>
+        <v>95.95</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.64%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>1.12%</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>0.32%</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t>0.89%</t>
+          <t>1.93%</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>7.27%</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>19.35%</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>2.95%</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>15.89%</t>
+          <t>34.03%</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>54.94%</t>
+          <t>63.34%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>0.93</v>
+        <v>1.78</v>
       </c>
       <c r="L37" t="n">
-        <v>303310000000</v>
+        <v>300100000000</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>74.38 -5.20</t>
+          <t>97.76 -1.85</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>60.71 16.14</t>
+          <t>58.42 64.24</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Co</t>
+          <t>Coca-Cola Co</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>95.95</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>1.64%</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>1.93%</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>7.27%</t>
-        </is>
-      </c>
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t>19.35%</t>
+          <t>1.12%</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>0.32%</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>0.89%</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2.95%</t>
+          <t>0.86%</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>34.03%</t>
+          <t>15.89%</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>63.34%</t>
+          <t>54.94%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>1.78</v>
+        <v>0.93</v>
       </c>
       <c r="L38" t="n">
-        <v>301200000000</v>
+        <v>298400000000</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>97.76 -1.85</t>
+          <t>74.38 -5.20</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>58.42 64.24</t>
+          <t>60.71 16.14</t>
         </is>
       </c>
     </row>
@@ -2970,7 +2970,7 @@
         <v>3.32</v>
       </c>
       <c r="L39" t="n">
-        <v>296120000000</v>
+        <v>293510000000</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>1.25</v>
       </c>
       <c r="L41" t="n">
-        <v>291910000000</v>
+        <v>292220000000</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -3118,132 +3118,132 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Caterpillar Inc</t>
+          <t>Toyota Motor Corporation ADR</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>617.62</v>
+        <v>221.52</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>3.16%</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>4.45%</t>
+          <t>2.80%</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>6.53%</t>
+          <t>7.23%</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>39.48%</t>
+          <t>15.70%</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>7.81%</t>
+          <t>3.49%</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>70.14%</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>60.73%</t>
+          <t>14.71%</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>65.33%</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>15.82</v>
+        <v>3.46</v>
       </c>
       <c r="L42" t="n">
-        <v>289030000000</v>
+        <v>288720000000</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>627.50 -1.57</t>
+          <t>220.56 0.44</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>267.30 131.06</t>
+          <t>155.00 42.92</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Toyota Motor Corporation ADR</t>
+          <t>Caterpillar Inc</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>221.52</v>
+        <v>617.62</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3.16%</t>
+          <t>1.56%</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>2.80%</t>
+          <t>4.45%</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>7.23%</t>
+          <t>6.53%</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>15.70%</t>
+          <t>39.48%</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>3.49%</t>
+          <t>7.81%</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>14.71%</t>
-        </is>
-      </c>
-      <c r="J43" s="5" t="inlineStr">
-        <is>
-          <t>65.33%</t>
+          <t>70.14%</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>60.73%</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>3.46</v>
+        <v>15.82</v>
       </c>
       <c r="L43" t="n">
-        <v>288720000000</v>
+        <v>284590000000</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>220.56 0.44</t>
+          <t>627.50 -1.57</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>155.00 42.92</t>
+          <t>267.30 131.06</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
         <v>6.7</v>
       </c>
       <c r="L44" t="n">
-        <v>284370000000</v>
+        <v>282960000000</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -3514,264 +3514,264 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>NVS</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Lam Research Corp</t>
+          <t>Novartis AG ADR</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>218.36</v>
+        <v>141.54</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>8.66%</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>21.83%</t>
+          <t>0.06%</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>2.75%</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>31.92%</t>
+          <t>7.04%</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>88.62%</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="inlineStr">
-        <is>
-          <t>27.56%</t>
+          <t>15.69%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2.66%</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>181.68%</t>
-        </is>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>76.72%</t>
+          <t>43.00%</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>69.28%</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>8.41</v>
+        <v>2.07</v>
       </c>
       <c r="L48" t="n">
-        <v>274270000000</v>
+        <v>268580000000</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>210.45 3.76</t>
+          <t>143.49 -1.36</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>56.32 287.71</t>
+          <t>97.39 45.33</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>NVS</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Novartis AG ADR</t>
+          <t>American Express Co</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>141.54</v>
+        <v>375.61</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>0.06%</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>2.75%</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>7.04%</t>
+          <t>-1.92%</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>-0.86%</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>1.99%</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>15.69%</t>
+          <t>17.26%</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2.66%</t>
+          <t>1.53%</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>43.00%</t>
-        </is>
-      </c>
-      <c r="J49" s="5" t="inlineStr">
-        <is>
-          <t>69.28%</t>
+          <t>24.37%</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>51.22%</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>2.07</v>
+        <v>7.45</v>
       </c>
       <c r="L49" t="n">
-        <v>268580000000</v>
+        <v>263820000000</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>143.49 -1.36</t>
+          <t>387.49 -3.07</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>97.39 45.33</t>
+          <t>220.43 70.40</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>American Express Co</t>
+          <t>Philip Morris International Inc</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>375.61</v>
+        <v>162.61</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-1.92%</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>-0.86%</t>
-        </is>
-      </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>1.99%</t>
-        </is>
-      </c>
-      <c r="G50" s="4" t="inlineStr">
-        <is>
-          <t>17.26%</t>
+          <t>2.39%</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>2.42%</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>5.06%</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>-1.17%</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.38%</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>24.37%</t>
+          <t>33.95%</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>51.22%</t>
+          <t>60.44%</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>7.45</v>
+        <v>3.27</v>
       </c>
       <c r="L50" t="n">
-        <v>258740000000</v>
+        <v>253130000000</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>387.49 -3.07</t>
+          <t>186.69 -12.90</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>220.43 70.40</t>
+          <t>116.12 40.04</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Philip Morris International Inc</t>
+          <t>Lam Research Corp</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>162.61</v>
+        <v>218.36</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2.39%</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>2.42%</t>
+          <t>8.66%</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>21.83%</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>5.06%</t>
-        </is>
-      </c>
-      <c r="G51" s="3" t="inlineStr">
-        <is>
-          <t>-1.17%</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>1.38%</t>
+          <t>31.92%</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>88.62%</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>27.56%</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>33.95%</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>60.44%</t>
+          <t>181.68%</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>76.72%</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>3.27</v>
+        <v>8.41</v>
       </c>
       <c r="L51" t="n">
-        <v>253130000000</v>
+        <v>252410000000</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>186.69 -12.90</t>
+          <t>210.45 3.76</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>116.12 40.04</t>
+          <t>56.32 287.71</t>
         </is>
       </c>
     </row>
@@ -3828,7 +3828,7 @@
         <v>4.2</v>
       </c>
       <c r="L52" t="n">
-        <v>252740000000</v>
+        <v>250950000000</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -3910,198 +3910,198 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Applied Materials Inc</t>
+          <t>Thermo Fisher Scientific Inc</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>301.18</v>
+        <v>618.86</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>6.94%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>12.51%</t>
+          <t>5.60%</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>19.36%</t>
+          <t>6.73%</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>54.09%</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="inlineStr">
-        <is>
-          <t>17.20%</t>
+          <t>26.82%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>6.80%</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>69.37%</t>
+          <t>13.42%</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>69.30%</t>
+          <t>67.25%</t>
         </is>
       </c>
       <c r="K54" t="n">
-        <v>9.94</v>
+        <v>12.6</v>
       </c>
       <c r="L54" t="n">
-        <v>238820000000</v>
+        <v>227870000000</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>298.22 0.99</t>
+          <t>628.08 -1.47</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>123.74 143.40</t>
+          <t>385.46 60.55</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc</t>
+          <t>T-Mobile US Inc</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>618.86</v>
+        <v>200.56</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2.04%</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>5.60%</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>6.73%</t>
-        </is>
-      </c>
-      <c r="G55" s="4" t="inlineStr">
-        <is>
-          <t>26.82%</t>
+          <t>1.34%</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>0.80%</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>-2.00%</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>-13.65%</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>6.80%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>13.42%</t>
-        </is>
-      </c>
-      <c r="J55" s="5" t="inlineStr">
-        <is>
-          <t>67.25%</t>
+          <t>-5.55%</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>47.61%</t>
         </is>
       </c>
       <c r="K55" t="n">
-        <v>12.6</v>
+        <v>3.85</v>
       </c>
       <c r="L55" t="n">
-        <v>232510000000</v>
+        <v>224330000000</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>628.08 -1.47</t>
+          <t>276.49 -27.46</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>385.46 60.55</t>
+          <t>194.01 3.38</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>T-Mobile US Inc</t>
+          <t>Applied Materials Inc</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>200.56</v>
+        <v>301.18</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>1.34%</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>0.80%</t>
-        </is>
-      </c>
-      <c r="F56" s="3" t="inlineStr">
-        <is>
-          <t>-2.00%</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>-13.65%</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>-1.22%</t>
+          <t>6.94%</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>12.51%</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>19.36%</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>54.09%</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>17.20%</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>-5.55%</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>47.61%</t>
+          <t>69.37%</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>69.30%</t>
         </is>
       </c>
       <c r="K56" t="n">
-        <v>3.85</v>
+        <v>9.94</v>
       </c>
       <c r="L56" t="n">
-        <v>224330000000</v>
+        <v>223320000000</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>276.49 -27.46</t>
+          <t>298.22 0.99</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>194.01 3.38</t>
+          <t>123.74 143.40</t>
         </is>
       </c>
     </row>
@@ -4174,264 +4174,264 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>McDonald's Corp</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>647.72</v>
+        <v>307.32</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>5.06%</t>
+          <t>-0.51%</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>-4.39%</t>
-        </is>
-      </c>
-      <c r="F58" s="5" t="inlineStr">
-        <is>
-          <t>1.68%</t>
-        </is>
-      </c>
-      <c r="G58" s="4" t="inlineStr">
-        <is>
-          <t>36.60%</t>
+          <t>-1.08%</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>-0.04%</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-3.87%</t>
+          <t>0.55%</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>96.28%</t>
+          <t>6.21%</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>48.03%</t>
+          <t>48.45%</t>
         </is>
       </c>
       <c r="K58" t="n">
-        <v>33.42</v>
+        <v>4.57</v>
       </c>
       <c r="L58" t="n">
-        <v>218900000000</v>
+        <v>218860000000</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>745.61 -13.13</t>
+          <t>326.32 -5.82</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>200.50 223.05</t>
+          <t>276.53 11.13</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>McDonald's Corp</t>
+          <t>Citigroup Inc</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>307.32</v>
+        <v>121.32</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>-0.51%</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="inlineStr">
-        <is>
-          <t>-1.08%</t>
-        </is>
-      </c>
-      <c r="F59" s="3" t="inlineStr">
-        <is>
-          <t>-0.04%</t>
-        </is>
-      </c>
-      <c r="G59" s="5" t="inlineStr">
-        <is>
-          <t>0.32%</t>
+          <t>0.60%</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>3.42%</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>11.98%</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>33.21%</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>3.97%</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>6.21%</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>48.45%</t>
+          <t>64.66%</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>66.77%</t>
         </is>
       </c>
       <c r="K59" t="n">
-        <v>4.57</v>
+        <v>2.45</v>
       </c>
       <c r="L59" t="n">
-        <v>218860000000</v>
+        <v>217070000000</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>326.32 -5.82</t>
+          <t>124.17 -2.30</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>276.53 11.13</t>
+          <t>55.51 118.56</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Citigroup Inc</t>
+          <t>Shopify Inc</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>121.32</v>
+        <v>164.48</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>0.60%</t>
-        </is>
-      </c>
-      <c r="E60" s="5" t="inlineStr">
-        <is>
-          <t>3.42%</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>11.98%</t>
+          <t>-2.26%</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>-0.72%</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>2.32%</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>33.21%</t>
+          <t>23.93%</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>3.97%</t>
+          <t>2.18%</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>64.66%</t>
-        </is>
-      </c>
-      <c r="J60" s="5" t="inlineStr">
-        <is>
-          <t>66.77%</t>
+          <t>54.04%</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>50.71%</t>
         </is>
       </c>
       <c r="K60" t="n">
-        <v>2.45</v>
+        <v>6.16</v>
       </c>
       <c r="L60" t="n">
-        <v>217070000000</v>
+        <v>214130000000</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>124.17 -2.30</t>
+          <t>182.19 -9.72</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>55.51 118.56</t>
+          <t>69.84 135.51</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Shopify Inc</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>164.48</v>
+        <v>647.72</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>-2.26%</t>
+          <t>5.06%</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>-0.72%</t>
+          <t>-4.39%</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>1.68%</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>23.93%</t>
+          <t>36.60%</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2.18%</t>
+          <t>-3.87%</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>54.04%</t>
+          <t>96.28%</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>50.71%</t>
+          <t>48.03%</t>
         </is>
       </c>
       <c r="K61" t="n">
-        <v>6.16</v>
+        <v>33.42</v>
       </c>
       <c r="L61" t="n">
-        <v>214130000000</v>
+        <v>208360000000</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>182.19 -9.72</t>
+          <t>745.61 -13.13</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>69.84 135.51</t>
+          <t>200.50 223.05</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4488,7 @@
         <v>11.33</v>
       </c>
       <c r="L62" t="n">
-        <v>207820000000</v>
+        <v>207410000000</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -4504,132 +4504,132 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Linde Plc</t>
+          <t>Walt Disney Co</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>444.08</v>
+        <v>115.88</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.50%</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>4.25%</t>
+          <t>2.61%</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>6.17%</t>
-        </is>
-      </c>
-      <c r="G63" s="3" t="inlineStr">
-        <is>
-          <t>-1.84%</t>
+          <t>5.44%</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>4.82%</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>4.15%</t>
+          <t>1.85%</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>7.02%</t>
-        </is>
-      </c>
-      <c r="J63" s="4" t="inlineStr">
-        <is>
-          <t>71.25%</t>
+          <t>4.03%</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>61.73%</t>
         </is>
       </c>
       <c r="K63" t="n">
-        <v>6.71</v>
+        <v>2.17</v>
       </c>
       <c r="L63" t="n">
-        <v>207360000000</v>
+        <v>206880000000</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>486.38 -8.70</t>
+          <t>124.69 -7.07</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>387.78 14.52</t>
+          <t>80.10 44.67</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Walt Disney Co</t>
+          <t>Linde Plc</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>115.88</v>
+        <v>444.08</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>2.61%</t>
+          <t>4.25%</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>5.44%</t>
-        </is>
-      </c>
-      <c r="G64" s="5" t="inlineStr">
-        <is>
-          <t>4.82%</t>
+          <t>6.17%</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>-1.84%</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>4.15%</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>4.03%</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>61.73%</t>
+          <t>7.02%</t>
+        </is>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>71.25%</t>
         </is>
       </c>
       <c r="K64" t="n">
-        <v>2.17</v>
+        <v>6.71</v>
       </c>
       <c r="L64" t="n">
-        <v>206880000000</v>
+        <v>205310000000</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>124.69 -7.07</t>
+          <t>486.38 -8.70</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>80.10 44.67</t>
+          <t>387.78 14.52</t>
         </is>
       </c>
     </row>
@@ -4768,330 +4768,330 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Blackstone Inc</t>
+          <t>Qualcomm, Inc</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>157.62</v>
+        <v>177.78</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>-2.25%</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>1.61%</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>5.57%</t>
-        </is>
-      </c>
-      <c r="G67" s="5" t="inlineStr">
-        <is>
-          <t>2.59%</t>
+          <t>0.87%</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>2.30%</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>11.31%</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>3.93%</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>-7.70%</t>
+          <t>10.75%</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>55.74%</t>
+          <t>53.85%</t>
         </is>
       </c>
       <c r="K67" t="n">
-        <v>4.25</v>
+        <v>4.75</v>
       </c>
       <c r="L67" t="n">
-        <v>192270000000</v>
+        <v>194780000000</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>190.09 -17.08</t>
+          <t>205.95 -13.68</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>115.66 36.28</t>
+          <t>120.80 47.17</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PepsiCo Inc</t>
+          <t>Blackstone Inc</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>139.91</v>
+        <v>157.62</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>0.39%</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="inlineStr">
-        <is>
-          <t>-3.39%</t>
-        </is>
-      </c>
-      <c r="F68" s="3" t="inlineStr">
-        <is>
-          <t>-3.85%</t>
-        </is>
-      </c>
-      <c r="G68" s="3" t="inlineStr">
-        <is>
-          <t>-1.23%</t>
+          <t>1.49%</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>1.61%</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>5.57%</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>2.59%</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-2.52%</t>
+          <t>2.26%</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>-3.78%</t>
+          <t>-7.70%</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>36.98%</t>
+          <t>55.74%</t>
         </is>
       </c>
       <c r="K68" t="n">
-        <v>2.17</v>
+        <v>4.25</v>
       </c>
       <c r="L68" t="n">
-        <v>191300000000</v>
+        <v>192270000000</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>160.15 -12.64</t>
+          <t>190.09 -17.08</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>127.60 9.65</t>
+          <t>115.66 36.28</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Qualcomm, Inc</t>
+          <t>PepsiCo Inc</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>177.78</v>
+        <v>139.91</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>-2.25%</t>
-        </is>
-      </c>
-      <c r="E69" s="5" t="inlineStr">
-        <is>
-          <t>0.87%</t>
-        </is>
-      </c>
-      <c r="F69" s="5" t="inlineStr">
-        <is>
-          <t>2.30%</t>
-        </is>
-      </c>
-      <c r="G69" s="4" t="inlineStr">
-        <is>
-          <t>11.31%</t>
+          <t>0.39%</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>-3.39%</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>-3.85%</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>3.93%</t>
+          <t>-2.52%</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>10.75%</t>
+          <t>-3.78%</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>53.85%</t>
+          <t>36.98%</t>
         </is>
       </c>
       <c r="K69" t="n">
-        <v>4.75</v>
+        <v>2.17</v>
       </c>
       <c r="L69" t="n">
-        <v>190400000000</v>
+        <v>191300000000</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>205.95 -13.68</t>
+          <t>160.15 -12.64</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>120.80 47.17</t>
+          <t>127.60 9.65</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>KLA Corp</t>
+          <t>Boeing Co</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1400</v>
+        <v>234.53</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>5.69%</t>
+          <t>3.14%</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>10.04%</t>
+          <t>8.01%</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>14.83%</t>
+          <t>15.07%</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>45.62%</t>
-        </is>
-      </c>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>15.22%</t>
+          <t>13.35%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>8.02%</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>103.10%</t>
-        </is>
-      </c>
-      <c r="J70" s="5" t="inlineStr">
-        <is>
-          <t>65.79%</t>
+          <t>35.95%</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>76.14%</t>
         </is>
       </c>
       <c r="K70" t="n">
-        <v>46.44</v>
+        <v>5.31</v>
       </c>
       <c r="L70" t="n">
-        <v>183950000000</v>
+        <v>183650000000</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>1406.97 -0.50</t>
+          <t>242.69 -3.36</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>551.33 153.93</t>
+          <t>128.88 81.98</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Boeing Co</t>
+          <t>Uber Technologies Inc</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>234.53</v>
+        <v>85.44</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>3.14%</t>
-        </is>
-      </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>8.01%</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>15.07%</t>
-        </is>
-      </c>
-      <c r="G71" s="4" t="inlineStr">
-        <is>
-          <t>13.35%</t>
+          <t>-2.45%</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>3.58%</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>-2.19%</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>-3.21%</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>8.02%</t>
+          <t>4.56%</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>35.95%</t>
-        </is>
-      </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>76.14%</t>
+          <t>29.16%</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>52.31%</t>
         </is>
       </c>
       <c r="K71" t="n">
-        <v>5.31</v>
+        <v>2.44</v>
       </c>
       <c r="L71" t="n">
-        <v>183650000000</v>
+        <v>182000000000</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>242.69 -3.36</t>
+          <t>101.99 -16.23</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>128.88 81.98</t>
+          <t>60.63 40.92</t>
         </is>
       </c>
     </row>
@@ -5148,7 +5148,7 @@
         <v>15.62</v>
       </c>
       <c r="L72" t="n">
-        <v>180020000000</v>
+        <v>181640000000</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
@@ -5230,396 +5230,396 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Uber Technologies Inc</t>
+          <t>AMGEN Inc</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>85.44</v>
+        <v>326.1</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>-2.45%</t>
-        </is>
-      </c>
-      <c r="E74" s="5" t="inlineStr">
-        <is>
-          <t>3.58%</t>
+          <t>-1.21%</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>-0.53%</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>-2.19%</t>
-        </is>
-      </c>
-      <c r="G74" s="3" t="inlineStr">
-        <is>
-          <t>-3.21%</t>
+          <t>-0.38%</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>9.37%</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>4.56%</t>
+          <t>-0.37%</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>29.16%</t>
+          <t>24.44%</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>52.31%</t>
+          <t>48.21%</t>
         </is>
       </c>
       <c r="K74" t="n">
-        <v>2.44</v>
+        <v>7.41</v>
       </c>
       <c r="L74" t="n">
-        <v>177530000000</v>
+        <v>177760000000</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>101.99 -16.23</t>
+          <t>346.38 -5.85</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>60.63 40.92</t>
+          <t>260.55 25.16</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>Blackrock Inc</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>5492.11</v>
+        <v>1085.1</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>1.77%</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>6.67%</t>
+          <t>0.05%</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>1.53%</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>4.11%</t>
+          <t>3.08%</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2.55%</t>
+          <t>1.38%</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>14.51%</t>
+          <t>10.64%</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>64.36%</t>
+          <t>51.08%</t>
         </is>
       </c>
       <c r="K75" t="n">
-        <v>112.85</v>
+        <v>20.98</v>
       </c>
       <c r="L75" t="n">
-        <v>177030000000</v>
+        <v>177480000000</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>5839.41 -5.95</t>
+          <t>1219.94 -11.05</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>4096.23 34.08</t>
+          <t>773.74 40.24</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Blackrock Inc</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1085.1</v>
+        <v>5492.11</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>0.87%</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>0.05%</t>
-        </is>
-      </c>
-      <c r="F76" s="5" t="inlineStr">
-        <is>
-          <t>1.53%</t>
+          <t>1.77%</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>6.67%</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>3.08%</t>
+          <t>4.11%</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>2.55%</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>10.64%</t>
+          <t>14.51%</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>51.08%</t>
+          <t>64.36%</t>
         </is>
       </c>
       <c r="K76" t="n">
-        <v>20.98</v>
+        <v>112.85</v>
       </c>
       <c r="L76" t="n">
-        <v>177020000000</v>
+        <v>177030000000</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>1219.94 -11.05</t>
+          <t>5839.41 -5.95</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>773.74 40.24</t>
+          <t>4096.23 34.08</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>AMGEN Inc</t>
+          <t>KLA Corp</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>326.1</v>
+        <v>1400</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>-1.21%</t>
-        </is>
-      </c>
-      <c r="E77" s="3" t="inlineStr">
-        <is>
-          <t>-0.53%</t>
-        </is>
-      </c>
-      <c r="F77" s="3" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>5.69%</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>10.04%</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>14.83%</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>9.37%</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>-0.37%</t>
+          <t>45.62%</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>15.22%</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>24.44%</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>48.21%</t>
+          <t>103.10%</t>
+        </is>
+      </c>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>65.79%</t>
         </is>
       </c>
       <c r="K77" t="n">
-        <v>7.41</v>
+        <v>46.44</v>
       </c>
       <c r="L77" t="n">
-        <v>175600000000</v>
+        <v>174040000000</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>346.38 -5.85</t>
+          <t>1406.97 -0.50</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>260.55 25.16</t>
+          <t>551.33 153.93</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>190.31</v>
+        <v>280.67</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0.99%</t>
-        </is>
-      </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>6.04%</t>
+          <t>-0.41%</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>3.32%</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>11.26%</t>
+          <t>8.17%</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>4.82%</t>
+          <t>2.62%</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>9.70%</t>
+          <t>4.61%</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>-0.99%</t>
-        </is>
-      </c>
-      <c r="J78" s="5" t="inlineStr">
-        <is>
-          <t>65.69%</t>
+          <t>-21.25%</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>63.39%</t>
         </is>
       </c>
       <c r="K78" t="n">
-        <v>4.99</v>
+        <v>7.35</v>
       </c>
       <c r="L78" t="n">
-        <v>172920000000</v>
+        <v>172700000000</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>221.69 -14.15</t>
+          <t>398.35 -29.54</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>139.95 35.98</t>
+          <t>229.40 22.35</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>280.67</v>
+        <v>190.31</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>-0.41%</t>
-        </is>
-      </c>
-      <c r="E79" s="5" t="inlineStr">
-        <is>
-          <t>3.32%</t>
+          <t>0.99%</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>6.04%</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>8.17%</t>
+          <t>11.26%</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>2.62%</t>
+          <t>4.82%</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>4.61%</t>
+          <t>9.70%</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>-21.25%</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>63.39%</t>
+          <t>-0.99%</t>
+        </is>
+      </c>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>65.69%</t>
         </is>
       </c>
       <c r="K79" t="n">
-        <v>7.35</v>
+        <v>4.99</v>
       </c>
       <c r="L79" t="n">
-        <v>172700000000</v>
+        <v>171230000000</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>398.35 -29.54</t>
+          <t>221.69 -14.15</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>229.40 22.35</t>
+          <t>139.95 35.98</t>
         </is>
       </c>
     </row>
@@ -5676,7 +5676,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="L80" t="n">
-        <v>170600000000</v>
+        <v>171060000000</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -5824,132 +5824,132 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Danaher Corp</t>
+          <t>PDD Holdings Inc ADR</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>238.37</v>
+        <v>120.55</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>1.43%</t>
-        </is>
-      </c>
-      <c r="E83" s="5" t="inlineStr">
-        <is>
-          <t>3.51%</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="inlineStr">
-        <is>
-          <t>6.02%</t>
-        </is>
-      </c>
-      <c r="G83" s="4" t="inlineStr">
-        <is>
-          <t>16.08%</t>
+          <t>-0.86%</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>5.83%</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>-0.08%</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>3.77%</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>4.13%</t>
+          <t>6.31%</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>-0.31%</t>
-        </is>
-      </c>
-      <c r="J83" s="5" t="inlineStr">
-        <is>
-          <t>66.50%</t>
+          <t>19.81%</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>58.24%</t>
         </is>
       </c>
       <c r="K83" t="n">
-        <v>4.35</v>
+        <v>3.42</v>
       </c>
       <c r="L83" t="n">
-        <v>168370000000</v>
+        <v>167820000000</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>258.23 -7.69</t>
+          <t>139.41 -13.53</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>171.00 39.40</t>
+          <t>87.11 38.39</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>PDD Holdings Inc ADR</t>
+          <t>Danaher Corp</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>120.55</v>
+        <v>238.37</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>-0.86%</t>
-        </is>
-      </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>5.83%</t>
-        </is>
-      </c>
-      <c r="F84" s="3" t="inlineStr">
-        <is>
-          <t>-0.08%</t>
-        </is>
-      </c>
-      <c r="G84" s="5" t="inlineStr">
-        <is>
-          <t>3.77%</t>
+          <t>1.43%</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>3.51%</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>6.02%</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>16.08%</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>6.31%</t>
+          <t>4.13%</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>19.81%</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>58.24%</t>
+          <t>-0.31%</t>
+        </is>
+      </c>
+      <c r="J84" s="5" t="inlineStr">
+        <is>
+          <t>66.50%</t>
         </is>
       </c>
       <c r="K84" t="n">
-        <v>3.42</v>
+        <v>4.35</v>
       </c>
       <c r="L84" t="n">
-        <v>167820000000</v>
+        <v>165990000000</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>139.41 -13.53</t>
+          <t>258.23 -7.69</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>87.11 38.39</t>
+          <t>171.00 39.40</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
         <v>1.46</v>
       </c>
       <c r="L85" t="n">
-        <v>166380000000</v>
+        <v>165550000000</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>8.67</v>
       </c>
       <c r="L86" t="n">
-        <v>164100000000</v>
+        <v>163980000000</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>2.97</v>
       </c>
       <c r="L87" t="n">
-        <v>150250000000</v>
+        <v>149710000000</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
@@ -6204,7 +6204,7 @@
         <v>6.2</v>
       </c>
       <c r="L88" t="n">
-        <v>149890000000</v>
+        <v>143720000000</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
@@ -6270,7 +6270,7 @@
         <v>8.630000000000001</v>
       </c>
       <c r="L89" t="n">
-        <v>139790000000</v>
+        <v>141920000000</v>
       </c>
       <c r="M89" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>12.22</v>
       </c>
       <c r="L91" t="n">
-        <v>132000000000</v>
+        <v>135440000000</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>4.83</v>
       </c>
       <c r="L92" t="n">
-        <v>131750000000</v>
+        <v>132990000000</v>
       </c>
       <c r="M92" t="inlineStr">
         <is>
@@ -6484,66 +6484,66 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Progressive Corp</t>
+          <t>Medtronic Plc</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>215.16</v>
+        <v>97.53</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>-3.97%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>-3.08%</t>
-        </is>
-      </c>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t>-13.26%</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>-5.52%</t>
+          <t>-0.29%</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="inlineStr">
+        <is>
+          <t>6.58%</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>1.53%</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>-9.52%</t>
+          <t>22.11%</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>40.70%</t>
+          <t>46.80%</t>
         </is>
       </c>
       <c r="K93" t="n">
-        <v>4.96</v>
+        <v>1.63</v>
       </c>
       <c r="L93" t="n">
-        <v>126170000000</v>
+        <v>126520000000</v>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>292.99 -26.56</t>
+          <t>106.33 -8.28</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>199.90 7.63</t>
+          <t>79.55 22.60</t>
         </is>
       </c>
     </row>
@@ -6616,462 +6616,462 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Medtronic Plc</t>
+          <t>Progressive Corp</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>97.53</v>
+        <v>215.16</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>-1.18%</t>
+          <t>0.94%</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-3.97%</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>-0.29%</t>
-        </is>
-      </c>
-      <c r="G95" s="4" t="inlineStr">
-        <is>
-          <t>6.58%</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>1.53%</t>
+          <t>-3.08%</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>-13.26%</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>-5.52%</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>22.11%</t>
+          <t>-9.52%</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>46.80%</t>
+          <t>40.70%</t>
         </is>
       </c>
       <c r="K95" t="n">
-        <v>1.63</v>
+        <v>4.96</v>
       </c>
       <c r="L95" t="n">
-        <v>125030000000</v>
+        <v>124990000000</v>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>106.33 -8.28</t>
+          <t>292.99 -26.56</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>79.55 22.60</t>
+          <t>199.90 7.63</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Chubb Limited</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>129.4</v>
+        <v>306.81</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>0.79%</t>
-        </is>
-      </c>
-      <c r="E96" s="5" t="inlineStr">
-        <is>
-          <t>0.65%</t>
+          <t>-1.98%</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>-1.43%</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>2.41%</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>13.85%</t>
+          <t>7.23%</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>-1.70%</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>21.41%</t>
+          <t>14.16%</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>55.94%</t>
+          <t>49.71%</t>
         </is>
       </c>
       <c r="K96" t="n">
-        <v>2.13</v>
+        <v>4.67</v>
       </c>
       <c r="L96" t="n">
-        <v>123050000000</v>
+        <v>123180000000</v>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>131.70 -1.75</t>
+          <t>316.94 -3.20</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>85.35 51.61</t>
+          <t>252.16 21.67</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Chubb Limited</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>306.81</v>
+        <v>129.4</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>-1.98%</t>
-        </is>
-      </c>
-      <c r="E97" s="3" t="inlineStr">
-        <is>
-          <t>-1.43%</t>
+          <t>0.79%</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>0.65%</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>2.41%</t>
+          <t>1.99%</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>7.23%</t>
+          <t>13.85%</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>-1.70%</t>
+          <t>1.36%</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>14.16%</t>
+          <t>21.41%</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>49.71%</t>
+          <t>55.94%</t>
         </is>
       </c>
       <c r="K97" t="n">
-        <v>4.67</v>
+        <v>2.13</v>
       </c>
       <c r="L97" t="n">
-        <v>120750000000</v>
+        <v>122090000000</v>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>316.94 -3.20</t>
+          <t>131.70 -1.75</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>252.16 21.67</t>
+          <t>85.35 51.61</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>Arm Holdings plc. ADR</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>470.61</v>
+        <v>111.79</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>-1.44%</t>
+          <t>-3.60%</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>-7.01%</t>
-        </is>
-      </c>
-      <c r="G98" s="5" t="inlineStr">
-        <is>
-          <t>1.42%</t>
+          <t>-16.40%</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>-18.55%</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>2.27%</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>30.75%</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>43.90%</t>
+          <t>-22.57%</t>
+        </is>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>32.18%</t>
         </is>
       </c>
       <c r="K98" t="n">
-        <v>15.04</v>
+        <v>4.67</v>
       </c>
       <c r="L98" t="n">
-        <v>118640000000</v>
+        <v>118610000000</v>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>566.90 -16.99</t>
+          <t>183.16 -38.97</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>298.00 57.92</t>
+          <t>80.00 39.74</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Arm Holdings plc. ADR</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>111.79</v>
+        <v>470.61</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>1.45%</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>-3.60%</t>
+          <t>-1.44%</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>-16.40%</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>-18.55%</t>
+          <t>-7.01%</t>
+        </is>
+      </c>
+      <c r="G99" s="5" t="inlineStr">
+        <is>
+          <t>1.42%</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>-22.57%</t>
-        </is>
-      </c>
-      <c r="J99" s="3" t="inlineStr">
-        <is>
-          <t>32.18%</t>
+          <t>30.75%</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>43.90%</t>
         </is>
       </c>
       <c r="K99" t="n">
-        <v>4.67</v>
+        <v>15.04</v>
       </c>
       <c r="L99" t="n">
-        <v>118610000000</v>
+        <v>116940000000</v>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>183.16 -38.97</t>
+          <t>566.90 -16.99</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>80.00 39.74</t>
+          <t>298.00 57.92</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Co</t>
+          <t>Spotify Technology S.A</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>55.86</v>
+        <v>539.37</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>-0.07%</t>
-        </is>
-      </c>
-      <c r="E100" s="5" t="inlineStr">
-        <is>
-          <t>3.14%</t>
-        </is>
-      </c>
-      <c r="F100" s="4" t="inlineStr">
-        <is>
-          <t>10.73%</t>
-        </is>
-      </c>
-      <c r="G100" s="4" t="inlineStr">
-        <is>
-          <t>15.42%</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>3.56%</t>
+          <t>-2.58%</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>-6.48%</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>-9.73%</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>-17.16%</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>-7.12%</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>-2.24%</t>
-        </is>
-      </c>
-      <c r="J100" s="5" t="inlineStr">
-        <is>
-          <t>65.49%</t>
+          <t>16.26%</t>
+        </is>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>33.18%</t>
         </is>
       </c>
       <c r="K100" t="n">
-        <v>1.16</v>
+        <v>17.82</v>
       </c>
       <c r="L100" t="n">
-        <v>113720000000</v>
+        <v>114000000000</v>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>63.33 -11.80</t>
+          <t>785.00 -31.29</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>42.52 31.37</t>
+          <t>451.43 19.48</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Spotify Technology S.A</t>
+          <t>Bristol-Myers Squibb Co</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>539.37</v>
+        <v>55.86</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>-2.58%</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>-6.48%</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>-9.73%</t>
-        </is>
-      </c>
-      <c r="G101" s="2" t="inlineStr">
-        <is>
-          <t>-17.16%</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>-7.12%</t>
+          <t>-0.07%</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>3.14%</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>10.73%</t>
+        </is>
+      </c>
+      <c r="G101" s="4" t="inlineStr">
+        <is>
+          <t>15.42%</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>3.56%</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>16.26%</t>
-        </is>
-      </c>
-      <c r="J101" s="3" t="inlineStr">
-        <is>
-          <t>33.18%</t>
+          <t>-2.24%</t>
+        </is>
+      </c>
+      <c r="J101" s="5" t="inlineStr">
+        <is>
+          <t>65.49%</t>
         </is>
       </c>
       <c r="K101" t="n">
-        <v>17.82</v>
+        <v>1.16</v>
       </c>
       <c r="L101" t="n">
-        <v>111050000000</v>
+        <v>113800000000</v>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>785.00 -31.29</t>
+          <t>63.33 -11.80</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>451.43 19.48</t>
+          <t>42.52 31.37</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
         <v>65.77</v>
       </c>
       <c r="L102" t="n">
-        <v>110440000000</v>
+        <v>110510000000</v>
       </c>
       <c r="M102" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>11.09</v>
       </c>
       <c r="L103" t="n">
-        <v>107720000000</v>
+        <v>109310000000</v>
       </c>
       <c r="M103" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>4.37</v>
       </c>
       <c r="L104" t="n">
-        <v>107590000000</v>
+        <v>107450000000</v>
       </c>
       <c r="M104" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>0.95</v>
       </c>
       <c r="L107" t="n">
-        <v>96570000000</v>
+        <v>93840000000</v>
       </c>
       <c r="M107" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         <v>2.74</v>
       </c>
       <c r="L108" t="n">
-        <v>94640000000</v>
+        <v>92360000000</v>
       </c>
       <c r="M108" t="inlineStr">
         <is>
@@ -7656,7 +7656,7 @@
         <v>2.96</v>
       </c>
       <c r="L110" t="n">
-        <v>91130000000</v>
+        <v>91560000000</v>
       </c>
       <c r="M110" t="inlineStr">
         <is>
@@ -7672,396 +7672,396 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp</t>
+          <t>3M Co</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>618.8200000000001</v>
+        <v>165.24</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>4.74%</t>
-        </is>
-      </c>
-      <c r="E111" s="4" t="inlineStr">
-        <is>
-          <t>6.62%</t>
-        </is>
-      </c>
-      <c r="F111" s="4" t="inlineStr">
-        <is>
-          <t>8.44%</t>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>1.29%</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>12.97%</t>
+          <t>7.40%</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>8.52%</t>
+          <t>3.21%</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>36.79%</t>
+          <t>24.46%</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>64.03%</t>
+          <t>53.15%</t>
         </is>
       </c>
       <c r="K111" t="n">
-        <v>18.15</v>
+        <v>3.16</v>
       </c>
       <c r="L111" t="n">
-        <v>88320000000</v>
+        <v>87780000000</v>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>640.90 -3.45</t>
+          <t>174.69 -5.41</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>426.24 45.18</t>
+          <t>121.98 35.47</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>3M Co</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>165.24</v>
+        <v>55.21</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.58%</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>1.29%</t>
-        </is>
-      </c>
-      <c r="F112" s="3" t="inlineStr">
-        <is>
-          <t>-0.25%</t>
+          <t>1.44%</t>
+        </is>
+      </c>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>8.83%</t>
         </is>
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>7.40%</t>
+          <t>18.93%</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>3.47%</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>24.46%</t>
+          <t>13.37%</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>53.15%</t>
+          <t>62.24%</t>
         </is>
       </c>
       <c r="K112" t="n">
-        <v>3.16</v>
+        <v>0.95</v>
       </c>
       <c r="L112" t="n">
-        <v>87780000000</v>
+        <v>86320000000</v>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>174.69 -5.41</t>
+          <t>56.19 -1.75</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>121.98 35.47</t>
+          <t>35.18 56.94</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>Airbnb Inc</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>55.21</v>
+        <v>139.27</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>-0.58%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>3.11%</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>8.83%</t>
+          <t>10.20%</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr">
         <is>
-          <t>18.93%</t>
+          <t>9.58%</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>3.47%</t>
+          <t>2.62%</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>13.37%</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>62.24%</t>
+          <t>6.08%</t>
+        </is>
+      </c>
+      <c r="J113" s="5" t="inlineStr">
+        <is>
+          <t>68.98%</t>
         </is>
       </c>
       <c r="K113" t="n">
-        <v>0.95</v>
+        <v>3.01</v>
       </c>
       <c r="L113" t="n">
-        <v>85820000000</v>
+        <v>85350000000</v>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>56.19 -1.75</t>
+          <t>163.93 -15.04</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>35.18 56.94</t>
+          <t>99.88 39.44</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Airbnb Inc</t>
+          <t>Apollo Global Management Inc</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>139.27</v>
+        <v>145.82</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>0.44%</t>
-        </is>
-      </c>
-      <c r="E114" s="5" t="inlineStr">
-        <is>
-          <t>3.11%</t>
+          <t>-0.25%</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>10.20%</t>
+          <t>5.87%</t>
         </is>
       </c>
       <c r="G114" s="4" t="inlineStr">
         <is>
-          <t>9.58%</t>
+          <t>7.11%</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2.62%</t>
+          <t>0.73%</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>6.08%</t>
-        </is>
-      </c>
-      <c r="J114" s="5" t="inlineStr">
-        <is>
-          <t>68.98%</t>
+          <t>-10.24%</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>53.15%</t>
         </is>
       </c>
       <c r="K114" t="n">
-        <v>3.01</v>
+        <v>4.02</v>
       </c>
       <c r="L114" t="n">
-        <v>85730000000</v>
+        <v>84850000000</v>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>163.93 -15.04</t>
+          <t>174.91 -16.63</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>99.88 39.44</t>
+          <t>102.58 42.15</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Nu Holdings Ltd</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>311.5</v>
+        <v>17.46</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2.36%</t>
-        </is>
-      </c>
-      <c r="E115" s="4" t="inlineStr">
-        <is>
-          <t>7.64%</t>
+          <t>-0.85%</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>3.44%</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>14.17%</t>
+          <t>5.49%</t>
         </is>
       </c>
       <c r="G115" s="4" t="inlineStr">
         <is>
-          <t>9.58%</t>
+          <t>24.19%</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>11.68%</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>38.24%</t>
-        </is>
-      </c>
-      <c r="J115" s="5" t="inlineStr">
-        <is>
-          <t>67.77%</t>
+          <t>56.45%</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>58.65%</t>
         </is>
       </c>
       <c r="K115" t="n">
-        <v>9.58</v>
+        <v>0.46</v>
       </c>
       <c r="L115" t="n">
-        <v>84950000000</v>
+        <v>84360000000</v>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>366.50 -15.01</t>
+          <t>18.37 -4.95</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>164.01 89.93</t>
+          <t>9.01 93.78</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Apollo Global Management Inc</t>
+          <t>Northrop Grumman Corp</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>145.82</v>
+        <v>618.8200000000001</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>-0.25%</t>
-        </is>
-      </c>
-      <c r="E116" s="3" t="inlineStr">
-        <is>
-          <t>-1.12%</t>
+          <t>4.74%</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>6.62%</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>5.87%</t>
+          <t>8.44%</t>
         </is>
       </c>
       <c r="G116" s="4" t="inlineStr">
         <is>
-          <t>7.11%</t>
+          <t>12.97%</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>8.52%</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>-10.24%</t>
+          <t>36.79%</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>53.15%</t>
+          <t>64.03%</t>
         </is>
       </c>
       <c r="K116" t="n">
-        <v>4.02</v>
+        <v>18.15</v>
       </c>
       <c r="L116" t="n">
-        <v>84640000000</v>
+        <v>84320000000</v>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>174.91 -16.63</t>
+          <t>640.90 -3.45</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>102.58 42.15</t>
+          <t>426.24 45.18</t>
         </is>
       </c>
     </row>
@@ -8134,330 +8134,330 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>NU</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Nu Holdings Ltd</t>
+          <t>Elevance Health Inc</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>17.46</v>
+        <v>372.83</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>-0.85%</t>
-        </is>
-      </c>
-      <c r="E118" s="5" t="inlineStr">
-        <is>
-          <t>3.44%</t>
+          <t>-0.52%</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>5.10%</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>5.49%</t>
+          <t>10.58%</t>
         </is>
       </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
-          <t>24.19%</t>
+          <t>5.91%</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>6.36%</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>56.45%</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>58.65%</t>
+          <t>-2.08%</t>
+        </is>
+      </c>
+      <c r="J118" s="5" t="inlineStr">
+        <is>
+          <t>68.43%</t>
         </is>
       </c>
       <c r="K118" t="n">
-        <v>0.46</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L118" t="n">
-        <v>83640000000</v>
+        <v>83290000000</v>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>18.37 -4.95</t>
+          <t>458.75 -18.73</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>9.01 93.78</t>
+          <t>273.71 36.21</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Elevance Health Inc</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>372.83</v>
+        <v>311.5</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>-0.52%</t>
+          <t>2.36%</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>5.10%</t>
+          <t>7.64%</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>10.58%</t>
+          <t>14.17%</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr">
         <is>
-          <t>5.91%</t>
+          <t>9.58%</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>6.36%</t>
+          <t>11.68%</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>-2.08%</t>
+          <t>38.24%</t>
         </is>
       </c>
       <c r="J119" s="5" t="inlineStr">
         <is>
-          <t>68.43%</t>
+          <t>67.77%</t>
         </is>
       </c>
       <c r="K119" t="n">
-        <v>8.800000000000001</v>
+        <v>9.58</v>
       </c>
       <c r="L119" t="n">
-        <v>82860000000</v>
+        <v>82990000000</v>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>458.75 -18.73</t>
+          <t>366.50 -15.01</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>273.71 36.21</t>
+          <t>164.01 89.93</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>General Motors Company</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>120.62</v>
+        <v>82.87</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>1.79%</t>
-        </is>
-      </c>
-      <c r="E120" s="3" t="inlineStr">
-        <is>
-          <t>-4.95%</t>
-        </is>
-      </c>
-      <c r="F120" s="2" t="inlineStr">
-        <is>
-          <t>-9.99%</t>
-        </is>
-      </c>
-      <c r="G120" s="3" t="inlineStr">
-        <is>
-          <t>-2.60%</t>
+          <t>-2.65%</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>0.81%</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>9.33%</t>
+        </is>
+      </c>
+      <c r="G120" s="4" t="inlineStr">
+        <is>
+          <t>41.58%</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>-4.18%</t>
+          <t>1.91%</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>59.43%</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>37.90%</t>
+          <t>60.25%</t>
         </is>
       </c>
       <c r="K120" t="n">
-        <v>4.68</v>
+        <v>1.82</v>
       </c>
       <c r="L120" t="n">
-        <v>79930000000</v>
+        <v>79410000000</v>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>168.08 -28.24</t>
+          <t>85.18 -2.71</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>66.25 82.08</t>
+          <t>41.60 99.21</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Equinix Inc</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>800.35</v>
+        <v>120.62</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2.36%</t>
-        </is>
-      </c>
-      <c r="E121" s="5" t="inlineStr">
-        <is>
-          <t>4.63%</t>
-        </is>
-      </c>
-      <c r="F121" s="5" t="inlineStr">
-        <is>
-          <t>3.52%</t>
+          <t>1.79%</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>-4.95%</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>-9.99%</t>
         </is>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-2.60%</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>4.46%</t>
+          <t>-4.18%</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>-14.86%</t>
-        </is>
-      </c>
-      <c r="J121" s="5" t="inlineStr">
-        <is>
-          <t>65.83%</t>
+          <t>-0.54%</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>37.90%</t>
         </is>
       </c>
       <c r="K121" t="n">
-        <v>15.68</v>
+        <v>4.68</v>
       </c>
       <c r="L121" t="n">
-        <v>78580000000</v>
+        <v>78530000000</v>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>953.41 -16.05</t>
+          <t>168.08 -28.24</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>701.41 14.11</t>
+          <t>66.25 82.08</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>General Motors Company</t>
+          <t>Equinix Inc</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>82.87</v>
+        <v>800.35</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>-2.65%</t>
+          <t>2.36%</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>0.81%</t>
-        </is>
-      </c>
-      <c r="F122" s="4" t="inlineStr">
-        <is>
-          <t>9.33%</t>
-        </is>
-      </c>
-      <c r="G122" s="4" t="inlineStr">
-        <is>
-          <t>41.58%</t>
+          <t>4.63%</t>
+        </is>
+      </c>
+      <c r="F122" s="5" t="inlineStr">
+        <is>
+          <t>3.52%</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="inlineStr">
+        <is>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>4.46%</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>59.43%</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>60.25%</t>
+          <t>-14.86%</t>
+        </is>
+      </c>
+      <c r="J122" s="5" t="inlineStr">
+        <is>
+          <t>65.83%</t>
         </is>
       </c>
       <c r="K122" t="n">
-        <v>1.82</v>
+        <v>15.68</v>
       </c>
       <c r="L122" t="n">
-        <v>77310000000</v>
+        <v>76770000000</v>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>85.18 -2.71</t>
+          <t>953.41 -16.05</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>41.60 99.21</t>
+          <t>701.41 14.11</t>
         </is>
       </c>
     </row>
@@ -8514,7 +8514,7 @@
         <v>8.02</v>
       </c>
       <c r="L123" t="n">
-        <v>74970000000</v>
+        <v>76580000000</v>
       </c>
       <c r="M123" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         <v>6.06</v>
       </c>
       <c r="L124" t="n">
-        <v>74510000000</v>
+        <v>75840000000</v>
       </c>
       <c r="M124" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
         <v>3.03</v>
       </c>
       <c r="L125" t="n">
-        <v>73070000000</v>
+        <v>73160000000</v>
       </c>
       <c r="M125" t="inlineStr">
         <is>
@@ -8728,66 +8728,66 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>Ferrari N.V</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>200.46</v>
+        <v>376.19</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>6.81%</t>
-        </is>
-      </c>
-      <c r="E127" s="4" t="inlineStr">
-        <is>
-          <t>9.55%</t>
-        </is>
-      </c>
-      <c r="F127" s="4" t="inlineStr">
-        <is>
-          <t>19.07%</t>
-        </is>
-      </c>
-      <c r="G127" s="4" t="inlineStr">
-        <is>
-          <t>108.43%</t>
-        </is>
-      </c>
-      <c r="H127" s="4" t="inlineStr">
-        <is>
-          <t>16.36%</t>
+          <t>1.44%</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="inlineStr">
+        <is>
+          <t>0.98%</t>
+        </is>
+      </c>
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t>-2.70%</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>-15.48%</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>1.79%</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>308.96%</t>
+          <t>-12.10%</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>59.55%</t>
+          <t>48.63%</t>
         </is>
       </c>
       <c r="K127" t="n">
-        <v>13.16</v>
+        <v>7.27</v>
       </c>
       <c r="L127" t="n">
-        <v>68540000000</v>
+        <v>66930000000</v>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>221.23 -9.39</t>
+          <t>519.10 -27.53</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>28.83 595.32</t>
+          <t>356.93 5.40</t>
         </is>
       </c>
     </row>
@@ -8844,7 +8844,7 @@
         <v>1.33</v>
       </c>
       <c r="L128" t="n">
-        <v>67530000000</v>
+        <v>66380000000</v>
       </c>
       <c r="M128" t="inlineStr">
         <is>
@@ -8860,264 +8860,264 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Ferrari N.V</t>
+          <t>Coinbase Global Inc</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>376.19</v>
+        <v>240.78</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>1.44%</t>
-        </is>
-      </c>
-      <c r="E129" s="5" t="inlineStr">
-        <is>
-          <t>0.98%</t>
-        </is>
-      </c>
-      <c r="F129" s="3" t="inlineStr">
-        <is>
-          <t>-2.70%</t>
+          <t>-1.96%</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>-1.74%</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>-10.53%</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>-15.48%</t>
+          <t>-16.21%</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>6.47%</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>-12.10%</t>
+          <t>-8.91%</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>48.63%</t>
+          <t>42.83%</t>
         </is>
       </c>
       <c r="K129" t="n">
-        <v>7.27</v>
+        <v>11.94</v>
       </c>
       <c r="L129" t="n">
-        <v>66930000000</v>
+        <v>66230000000</v>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>519.10 -27.53</t>
+          <t>444.64 -45.85</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>356.93 5.40</t>
+          <t>142.58 68.87</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive Co</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>81.48</v>
+        <v>182.78</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>0.75%</t>
-        </is>
-      </c>
-      <c r="E130" s="5" t="inlineStr">
-        <is>
-          <t>3.26%</t>
-        </is>
-      </c>
-      <c r="F130" s="5" t="inlineStr">
-        <is>
-          <t>3.81%</t>
+          <t>-2.24%</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>-7.60%</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>-11.71%</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>-4.03%</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>3.11%</t>
+          <t>-1.83%</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>-7.29%</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>-6.76%</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>61.57%</t>
+          <t>60.80%</t>
+        </is>
+      </c>
+      <c r="J130" s="3" t="inlineStr">
+        <is>
+          <t>33.53%</t>
         </is>
       </c>
       <c r="K130" t="n">
-        <v>1.46</v>
+        <v>7.37</v>
       </c>
       <c r="L130" t="n">
-        <v>65680000000</v>
+        <v>65490000000</v>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>100.18 -18.67</t>
+          <t>260.00 -29.70</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>74.54 9.30</t>
+          <t>89.42 104.41</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Coinbase Global Inc</t>
+          <t>Colgate-Palmolive Co</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>240.78</v>
+        <v>81.48</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>-1.96%</t>
-        </is>
-      </c>
-      <c r="E131" s="3" t="inlineStr">
-        <is>
-          <t>-1.74%</t>
-        </is>
-      </c>
-      <c r="F131" s="2" t="inlineStr">
-        <is>
-          <t>-10.53%</t>
-        </is>
-      </c>
-      <c r="G131" s="2" t="inlineStr">
-        <is>
-          <t>-16.21%</t>
+          <t>0.75%</t>
+        </is>
+      </c>
+      <c r="E131" s="5" t="inlineStr">
+        <is>
+          <t>3.26%</t>
+        </is>
+      </c>
+      <c r="F131" s="5" t="inlineStr">
+        <is>
+          <t>3.81%</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t>-4.03%</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>6.47%</t>
+          <t>3.11%</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>-8.91%</t>
+          <t>-6.76%</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>42.83%</t>
+          <t>61.57%</t>
         </is>
       </c>
       <c r="K131" t="n">
-        <v>11.94</v>
+        <v>1.46</v>
       </c>
       <c r="L131" t="n">
-        <v>64930000000</v>
+        <v>65190000000</v>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>444.64 -45.85</t>
+          <t>100.18 -18.67</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>142.58 68.87</t>
+          <t>74.54 9.30</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>182.78</v>
+        <v>200.46</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>-2.24%</t>
-        </is>
-      </c>
-      <c r="E132" s="2" t="inlineStr">
-        <is>
-          <t>-7.60%</t>
-        </is>
-      </c>
-      <c r="F132" s="2" t="inlineStr">
-        <is>
-          <t>-11.71%</t>
-        </is>
-      </c>
-      <c r="G132" s="3" t="inlineStr">
-        <is>
-          <t>-1.83%</t>
-        </is>
-      </c>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t>-7.29%</t>
+          <t>6.81%</t>
+        </is>
+      </c>
+      <c r="E132" s="4" t="inlineStr">
+        <is>
+          <t>9.55%</t>
+        </is>
+      </c>
+      <c r="F132" s="4" t="inlineStr">
+        <is>
+          <t>19.07%</t>
+        </is>
+      </c>
+      <c r="G132" s="4" t="inlineStr">
+        <is>
+          <t>108.43%</t>
+        </is>
+      </c>
+      <c r="H132" s="4" t="inlineStr">
+        <is>
+          <t>16.36%</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>60.80%</t>
-        </is>
-      </c>
-      <c r="J132" s="3" t="inlineStr">
-        <is>
-          <t>33.53%</t>
+          <t>308.96%</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>59.55%</t>
         </is>
       </c>
       <c r="K132" t="n">
-        <v>7.37</v>
+        <v>13.16</v>
       </c>
       <c r="L132" t="n">
-        <v>64020000000</v>
+        <v>64170000000</v>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>260.00 -29.70</t>
+          <t>221.23 -9.39</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>89.42 104.41</t>
+          <t>28.83 595.32</t>
         </is>
       </c>
     </row>
@@ -9174,7 +9174,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="L133" t="n">
-        <v>62540000000</v>
+        <v>61470000000</v>
       </c>
       <c r="M133" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>6.71</v>
       </c>
       <c r="L134" t="n">
-        <v>58520000000</v>
+        <v>58630000000</v>
       </c>
       <c r="M134" t="inlineStr">
         <is>
@@ -9322,462 +9322,462 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Vistra Corp</t>
+          <t>Zoetis Inc</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>166.37</v>
+        <v>127.17</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>10.47%</t>
+          <t>0.25%</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>1.52%</t>
-        </is>
-      </c>
-      <c r="F136" s="3" t="inlineStr">
-        <is>
-          <t>-3.50%</t>
-        </is>
-      </c>
-      <c r="G136" s="3" t="inlineStr">
-        <is>
-          <t>-4.83%</t>
+          <t>2.17%</t>
+        </is>
+      </c>
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>2.27%</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>-13.11%</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>3.12%</t>
+          <t>1.07%</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>-22.22%</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>50.42%</t>
+          <t>55.48%</t>
         </is>
       </c>
       <c r="K136" t="n">
-        <v>8.98</v>
+        <v>2.92</v>
       </c>
       <c r="L136" t="n">
-        <v>56370000000</v>
+        <v>56040000000</v>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>219.82 -24.32</t>
+          <t>177.40 -28.31</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>90.51 83.81</t>
+          <t>115.25 10.34</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Zoetis Inc</t>
+          <t>Workday Inc</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>127.17</v>
+        <v>207.18</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>0.25%</t>
-        </is>
-      </c>
-      <c r="E137" s="5" t="inlineStr">
-        <is>
-          <t>2.17%</t>
-        </is>
-      </c>
-      <c r="F137" s="5" t="inlineStr">
-        <is>
-          <t>2.27%</t>
+          <t>-1.24%</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>-3.79%</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>-6.26%</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>-13.11%</t>
+          <t>-11.20%</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>-3.54%</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>-22.22%</t>
+          <t>-17.02%</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>55.48%</t>
+          <t>37.12%</t>
         </is>
       </c>
       <c r="K137" t="n">
-        <v>2.92</v>
+        <v>5.19</v>
       </c>
       <c r="L137" t="n">
-        <v>56040000000</v>
+        <v>54490000000</v>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>177.40 -28.31</t>
+          <t>283.68 -26.97</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>115.25 10.34</t>
+          <t>202.22 2.46</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>PayPal Holdings Inc</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>377.41</v>
+        <v>57.66</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>12.81%</t>
-        </is>
-      </c>
-      <c r="E138" s="4" t="inlineStr">
-        <is>
-          <t>45.29%</t>
-        </is>
-      </c>
-      <c r="F138" s="4" t="inlineStr">
-        <is>
-          <t>57.93%</t>
-        </is>
-      </c>
-      <c r="G138" s="4" t="inlineStr">
-        <is>
-          <t>257.85%</t>
-        </is>
-      </c>
-      <c r="H138" s="4" t="inlineStr">
-        <is>
-          <t>58.99%</t>
+          <t>-1.05%</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="inlineStr">
+        <is>
+          <t>-3.32%</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>-7.15%</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>-14.79%</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J138" s="4" t="inlineStr">
-        <is>
-          <t>76.31%</t>
+          <t>-34.45%</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>35.59%</t>
         </is>
       </c>
       <c r="K138" t="n">
-        <v>27.86</v>
+        <v>1.42</v>
       </c>
       <c r="L138" t="n">
-        <v>55310000000</v>
+        <v>53950000000</v>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>360.98 4.55</t>
+          <t>93.25 -38.16</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>27.89 1253.45</t>
+          <t>55.85 3.24</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Workday Inc</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>207.18</v>
+        <v>40.11</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>-1.24%</t>
-        </is>
-      </c>
-      <c r="E139" s="3" t="inlineStr">
-        <is>
-          <t>-3.79%</t>
-        </is>
-      </c>
-      <c r="F139" s="2" t="inlineStr">
-        <is>
-          <t>-6.26%</t>
+          <t>2.37%</t>
+        </is>
+      </c>
+      <c r="E139" s="4" t="inlineStr">
+        <is>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="F139" s="4" t="inlineStr">
+        <is>
+          <t>16.33%</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>-11.20%</t>
+          <t>-8.68%</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>-3.54%</t>
+          <t>8.41%</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>-17.02%</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>37.12%</t>
+          <t>-30.83%</t>
+        </is>
+      </c>
+      <c r="J139" s="4" t="inlineStr">
+        <is>
+          <t>76.30%</t>
         </is>
       </c>
       <c r="K139" t="n">
-        <v>5.19</v>
+        <v>0.99</v>
       </c>
       <c r="L139" t="n">
-        <v>54490000000</v>
+        <v>51810000000</v>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>283.68 -26.97</t>
+          <t>59.57 -32.67</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>202.22 2.46</t>
+          <t>29.75 34.82</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>PayPal Holdings Inc</t>
+          <t>Vistra Corp</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>57.66</v>
+        <v>166.37</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>-1.05%</t>
-        </is>
-      </c>
-      <c r="E140" s="3" t="inlineStr">
-        <is>
-          <t>-3.32%</t>
-        </is>
-      </c>
-      <c r="F140" s="2" t="inlineStr">
-        <is>
-          <t>-7.15%</t>
-        </is>
-      </c>
-      <c r="G140" s="2" t="inlineStr">
-        <is>
-          <t>-14.79%</t>
+          <t>10.47%</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="inlineStr">
+        <is>
+          <t>1.52%</t>
+        </is>
+      </c>
+      <c r="F140" s="3" t="inlineStr">
+        <is>
+          <t>-3.50%</t>
+        </is>
+      </c>
+      <c r="G140" s="3" t="inlineStr">
+        <is>
+          <t>-4.83%</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>-1.23%</t>
+          <t>3.12%</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>-34.45%</t>
+          <t>1.84%</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>35.59%</t>
+          <t>50.42%</t>
         </is>
       </c>
       <c r="K140" t="n">
-        <v>1.42</v>
+        <v>8.98</v>
       </c>
       <c r="L140" t="n">
-        <v>53950000000</v>
+        <v>51030000000</v>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>93.25 -38.16</t>
+          <t>219.82 -24.32</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>55.85 3.24</t>
+          <t>90.51 83.81</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>Edwards Lifesciences Corp</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>40.11</v>
+        <v>85.13</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2.37%</t>
-        </is>
-      </c>
-      <c r="E141" s="4" t="inlineStr">
-        <is>
-          <t>6.96%</t>
-        </is>
-      </c>
-      <c r="F141" s="4" t="inlineStr">
-        <is>
-          <t>16.33%</t>
-        </is>
-      </c>
-      <c r="G141" s="2" t="inlineStr">
-        <is>
-          <t>-8.68%</t>
+          <t>0.65%</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>-0.17%</t>
+        </is>
+      </c>
+      <c r="F141" s="5" t="inlineStr">
+        <is>
+          <t>0.30%</t>
+        </is>
+      </c>
+      <c r="G141" s="4" t="inlineStr">
+        <is>
+          <t>8.64%</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>8.41%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>-30.83%</t>
-        </is>
-      </c>
-      <c r="J141" s="4" t="inlineStr">
-        <is>
-          <t>76.30%</t>
+          <t>15.60%</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>50.56%</t>
         </is>
       </c>
       <c r="K141" t="n">
-        <v>0.99</v>
+        <v>1.61</v>
       </c>
       <c r="L141" t="n">
-        <v>53040000000</v>
+        <v>49080000000</v>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>59.57 -32.67</t>
+          <t>87.89 -3.14</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>29.75 34.82</t>
+          <t>65.94 29.10</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences Corp</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>85.13</v>
+        <v>377.41</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>0.65%</t>
-        </is>
-      </c>
-      <c r="E142" s="3" t="inlineStr">
-        <is>
-          <t>-0.17%</t>
-        </is>
-      </c>
-      <c r="F142" s="5" t="inlineStr">
-        <is>
-          <t>0.30%</t>
+          <t>12.81%</t>
+        </is>
+      </c>
+      <c r="E142" s="4" t="inlineStr">
+        <is>
+          <t>45.29%</t>
+        </is>
+      </c>
+      <c r="F142" s="4" t="inlineStr">
+        <is>
+          <t>57.93%</t>
         </is>
       </c>
       <c r="G142" s="4" t="inlineStr">
         <is>
-          <t>8.64%</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>-0.14%</t>
+          <t>257.85%</t>
+        </is>
+      </c>
+      <c r="H142" s="4" t="inlineStr">
+        <is>
+          <t>58.99%</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>15.60%</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>50.56%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J142" s="4" t="inlineStr">
+        <is>
+          <t>76.31%</t>
         </is>
       </c>
       <c r="K142" t="n">
-        <v>1.61</v>
+        <v>27.86</v>
       </c>
       <c r="L142" t="n">
-        <v>49400000000</v>
+        <v>49030000000</v>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>87.89 -3.14</t>
+          <t>360.98 4.55</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>65.94 29.10</t>
+          <t>27.89 1253.45</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
         <v>2.96</v>
       </c>
       <c r="L143" t="n">
-        <v>47780000000</v>
+        <v>48150000000</v>
       </c>
       <c r="M143" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>12.17</v>
       </c>
       <c r="L144" t="n">
-        <v>46340000000</v>
+        <v>48120000000</v>
       </c>
       <c r="M144" t="inlineStr">
         <is>
@@ -9916,66 +9916,66 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Rocket Lab Corp</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>84.84999999999999</v>
+        <v>125.49</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2.13%</t>
-        </is>
-      </c>
-      <c r="E145" s="4" t="inlineStr">
-        <is>
-          <t>19.06%</t>
-        </is>
-      </c>
-      <c r="F145" s="4" t="inlineStr">
-        <is>
-          <t>46.22%</t>
-        </is>
-      </c>
-      <c r="G145" s="4" t="inlineStr">
-        <is>
-          <t>96.05%</t>
-        </is>
-      </c>
-      <c r="H145" s="4" t="inlineStr">
-        <is>
-          <t>21.63%</t>
+          <t>-3.97%</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>-9.27%</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>-19.32%</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>-7.06%</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>-7.72%</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>203.58%</t>
-        </is>
-      </c>
-      <c r="J145" s="4" t="inlineStr">
-        <is>
-          <t>70.92%</t>
+          <t>-11.25%</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>28.74%</t>
         </is>
       </c>
       <c r="K145" t="n">
-        <v>5.97</v>
+        <v>5.08</v>
       </c>
       <c r="L145" t="n">
-        <v>45320000000</v>
+        <v>45830000000</v>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>89.87 -5.59</t>
+          <t>201.69 -37.78</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>14.71 476.82</t>
+          <t>81.63 53.73</t>
         </is>
       </c>
     </row>
@@ -10048,66 +10048,66 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>Rocket Lab Corp</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>125.49</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>-3.97%</t>
-        </is>
-      </c>
-      <c r="E147" s="2" t="inlineStr">
-        <is>
-          <t>-9.27%</t>
-        </is>
-      </c>
-      <c r="F147" s="2" t="inlineStr">
-        <is>
-          <t>-19.32%</t>
-        </is>
-      </c>
-      <c r="G147" s="2" t="inlineStr">
-        <is>
-          <t>-7.06%</t>
-        </is>
-      </c>
-      <c r="H147" s="2" t="inlineStr">
-        <is>
-          <t>-7.72%</t>
+          <t>2.13%</t>
+        </is>
+      </c>
+      <c r="E147" s="4" t="inlineStr">
+        <is>
+          <t>19.06%</t>
+        </is>
+      </c>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t>46.22%</t>
+        </is>
+      </c>
+      <c r="G147" s="4" t="inlineStr">
+        <is>
+          <t>96.05%</t>
+        </is>
+      </c>
+      <c r="H147" s="4" t="inlineStr">
+        <is>
+          <t>21.63%</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>-11.25%</t>
-        </is>
-      </c>
-      <c r="J147" s="2" t="inlineStr">
-        <is>
-          <t>28.74%</t>
+          <t>203.58%</t>
+        </is>
+      </c>
+      <c r="J147" s="4" t="inlineStr">
+        <is>
+          <t>70.92%</t>
         </is>
       </c>
       <c r="K147" t="n">
-        <v>5.08</v>
+        <v>5.97</v>
       </c>
       <c r="L147" t="n">
-        <v>44010000000</v>
+        <v>44380000000</v>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>201.69 -37.78</t>
+          <t>89.87 -5.59</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>81.63 53.73</t>
+          <t>14.71 476.82</t>
         </is>
       </c>
     </row>
@@ -10164,7 +10164,7 @@
         <v>11.47</v>
       </c>
       <c r="L148" t="n">
-        <v>43670000000</v>
+        <v>43680000000</v>
       </c>
       <c r="M148" t="inlineStr">
         <is>
@@ -10230,7 +10230,7 @@
         <v>2.14</v>
       </c>
       <c r="L149" t="n">
-        <v>42260000000</v>
+        <v>42630000000</v>
       </c>
       <c r="M149" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>0.97</v>
       </c>
       <c r="L151" t="n">
-        <v>42220000000</v>
+        <v>41610000000</v>
       </c>
       <c r="M151" t="inlineStr">
         <is>
@@ -10560,7 +10560,7 @@
         <v>6.06</v>
       </c>
       <c r="L154" t="n">
-        <v>39940000000</v>
+        <v>38420000000</v>
       </c>
       <c r="M154" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>1.94</v>
       </c>
       <c r="L155" t="n">
-        <v>37570000000</v>
+        <v>37380000000</v>
       </c>
       <c r="M155" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>6.94</v>
       </c>
       <c r="L156" t="n">
-        <v>34560000000</v>
+        <v>35130000000</v>
       </c>
       <c r="M156" t="inlineStr">
         <is>
@@ -10758,7 +10758,7 @@
         <v>1.36</v>
       </c>
       <c r="L157" t="n">
-        <v>34540000000</v>
+        <v>34940000000</v>
       </c>
       <c r="M157" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         <v>1.39</v>
       </c>
       <c r="L158" t="n">
-        <v>31330000000</v>
+        <v>32050000000</v>
       </c>
       <c r="M158" t="inlineStr">
         <is>
@@ -10906,132 +10906,132 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>AFRM</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Astera Labs Inc</t>
+          <t>Affirm Holdings Inc</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>162.61</v>
+        <v>81.8</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>3.75%</t>
-        </is>
-      </c>
-      <c r="E160" s="5" t="inlineStr">
-        <is>
-          <t>0.36%</t>
-        </is>
-      </c>
-      <c r="F160" s="5" t="inlineStr">
-        <is>
-          <t>1.26%</t>
+          <t>0.23%</t>
+        </is>
+      </c>
+      <c r="E160" s="4" t="inlineStr">
+        <is>
+          <t>7.96%</t>
+        </is>
+      </c>
+      <c r="F160" s="4" t="inlineStr">
+        <is>
+          <t>13.34%</t>
         </is>
       </c>
       <c r="G160" s="4" t="inlineStr">
         <is>
-          <t>18.81%</t>
+          <t>22.44%</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>-2.25%</t>
+          <t>9.90%</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>21.71%</t>
+          <t>33.46%</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>49.85%</t>
+          <t>63.68%</t>
         </is>
       </c>
       <c r="K160" t="n">
-        <v>12.74</v>
+        <v>3.4</v>
       </c>
       <c r="L160" t="n">
-        <v>27470000000</v>
+        <v>26940000000</v>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>262.90 -38.15</t>
+          <t>100.00 -18.20</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>47.12 245.06</t>
+          <t>30.90 164.72</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>AFRM</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Affirm Holdings Inc</t>
+          <t>Astera Labs Inc</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>81.8</v>
+        <v>162.61</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>0.23%</t>
-        </is>
-      </c>
-      <c r="E161" s="4" t="inlineStr">
-        <is>
-          <t>7.96%</t>
-        </is>
-      </c>
-      <c r="F161" s="4" t="inlineStr">
-        <is>
-          <t>13.34%</t>
+          <t>3.75%</t>
+        </is>
+      </c>
+      <c r="E161" s="5" t="inlineStr">
+        <is>
+          <t>0.36%</t>
+        </is>
+      </c>
+      <c r="F161" s="5" t="inlineStr">
+        <is>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="G161" s="4" t="inlineStr">
         <is>
-          <t>22.44%</t>
+          <t>18.81%</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>9.90%</t>
+          <t>-2.25%</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>33.46%</t>
+          <t>21.71%</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>63.68%</t>
+          <t>49.85%</t>
         </is>
       </c>
       <c r="K161" t="n">
-        <v>3.4</v>
+        <v>12.74</v>
       </c>
       <c r="L161" t="n">
-        <v>27000000000</v>
+        <v>26470000000</v>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>100.00 -18.20</t>
+          <t>262.90 -38.15</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>30.90 164.72</t>
+          <t>47.12 245.06</t>
         </is>
       </c>
     </row>
@@ -11088,7 +11088,7 @@
         <v>12.63</v>
       </c>
       <c r="L162" t="n">
-        <v>25610000000</v>
+        <v>26430000000</v>
       </c>
       <c r="M162" t="inlineStr">
         <is>
@@ -11154,7 +11154,7 @@
         <v>2.23</v>
       </c>
       <c r="L163" t="n">
-        <v>25220000000</v>
+        <v>25360000000</v>
       </c>
       <c r="M163" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>4.31</v>
       </c>
       <c r="L165" t="n">
-        <v>21560000000</v>
+        <v>22280000000</v>
       </c>
       <c r="M165" t="inlineStr">
         <is>
@@ -11352,7 +11352,7 @@
         <v>4.98</v>
       </c>
       <c r="L166" t="n">
-        <v>19920000000</v>
+        <v>20840000000</v>
       </c>
       <c r="M166" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>0.18</v>
       </c>
       <c r="L167" t="n">
-        <v>19820000000</v>
+        <v>19940000000</v>
       </c>
       <c r="M167" t="inlineStr">
         <is>
@@ -11484,7 +11484,7 @@
         <v>0.18</v>
       </c>
       <c r="L168" t="n">
-        <v>19820000000</v>
+        <v>19940000000</v>
       </c>
       <c r="M168" t="inlineStr">
         <is>
@@ -11550,7 +11550,7 @@
         <v>5.15</v>
       </c>
       <c r="L169" t="n">
-        <v>19520000000</v>
+        <v>19260000000</v>
       </c>
       <c r="M169" t="inlineStr">
         <is>
@@ -11616,7 +11616,7 @@
         <v>0.76</v>
       </c>
       <c r="L170" t="n">
-        <v>18330000000</v>
+        <v>18100000000</v>
       </c>
       <c r="M170" t="inlineStr">
         <is>
@@ -11632,66 +11632,66 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>AeroVironment Inc</t>
+          <t>IonQ Inc</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>364.99</v>
+        <v>49.45</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>5.81%</t>
-        </is>
-      </c>
-      <c r="E171" s="4" t="inlineStr">
-        <is>
-          <t>37.01%</t>
-        </is>
-      </c>
-      <c r="F171" s="4" t="inlineStr">
-        <is>
-          <t>26.44%</t>
+          <t>-1.98%</t>
+        </is>
+      </c>
+      <c r="E171" s="5" t="inlineStr">
+        <is>
+          <t>1.77%</t>
+        </is>
+      </c>
+      <c r="F171" s="3" t="inlineStr">
+        <is>
+          <t>-1.91%</t>
         </is>
       </c>
       <c r="G171" s="4" t="inlineStr">
         <is>
-          <t>47.29%</t>
-        </is>
-      </c>
-      <c r="H171" s="4" t="inlineStr">
-        <is>
-          <t>50.89%</t>
+          <t>9.13%</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>10.21%</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>123.87%</t>
-        </is>
-      </c>
-      <c r="J171" s="4" t="inlineStr">
-        <is>
-          <t>77.05%</t>
+          <t>-0.28%</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>50.16%</t>
         </is>
       </c>
       <c r="K171" t="n">
-        <v>18.81</v>
+        <v>3.66</v>
       </c>
       <c r="L171" t="n">
-        <v>18220000000</v>
+        <v>17870000000</v>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>417.86 -12.65</t>
+          <t>84.64 -41.58</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>102.25 256.96</t>
+          <t>17.88 176.57</t>
         </is>
       </c>
     </row>
@@ -11748,7 +11748,7 @@
         <v>1.41</v>
       </c>
       <c r="L172" t="n">
-        <v>18000000000</v>
+        <v>17850000000</v>
       </c>
       <c r="M172" t="inlineStr">
         <is>
@@ -11764,66 +11764,66 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>IonQ Inc</t>
+          <t>AeroVironment Inc</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>49.45</v>
+        <v>364.99</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>-1.98%</t>
-        </is>
-      </c>
-      <c r="E173" s="5" t="inlineStr">
-        <is>
-          <t>1.77%</t>
-        </is>
-      </c>
-      <c r="F173" s="3" t="inlineStr">
-        <is>
-          <t>-1.91%</t>
+          <t>5.81%</t>
+        </is>
+      </c>
+      <c r="E173" s="4" t="inlineStr">
+        <is>
+          <t>37.01%</t>
+        </is>
+      </c>
+      <c r="F173" s="4" t="inlineStr">
+        <is>
+          <t>26.44%</t>
         </is>
       </c>
       <c r="G173" s="4" t="inlineStr">
         <is>
-          <t>9.13%</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>10.21%</t>
+          <t>47.29%</t>
+        </is>
+      </c>
+      <c r="H173" s="4" t="inlineStr">
+        <is>
+          <t>50.89%</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>-0.28%</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>50.16%</t>
+          <t>123.87%</t>
+        </is>
+      </c>
+      <c r="J173" s="4" t="inlineStr">
+        <is>
+          <t>77.05%</t>
         </is>
       </c>
       <c r="K173" t="n">
-        <v>3.66</v>
+        <v>18.81</v>
       </c>
       <c r="L173" t="n">
-        <v>17520000000</v>
+        <v>17220000000</v>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>84.64 -41.58</t>
+          <t>417.86 -12.65</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>17.88 176.57</t>
+          <t>102.25 256.96</t>
         </is>
       </c>
     </row>
@@ -11880,7 +11880,7 @@
         <v>2.69</v>
       </c>
       <c r="L174" t="n">
-        <v>16570000000</v>
+        <v>16560000000</v>
       </c>
       <c r="M174" t="inlineStr">
         <is>
@@ -11896,132 +11896,132 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>OKLO</t>
+          <t>ROKU</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Oklo Inc</t>
+          <t>Roku Inc</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>105.31</v>
+        <v>111.17</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>7.90%</t>
-        </is>
-      </c>
-      <c r="E175" s="4" t="inlineStr">
-        <is>
-          <t>24.08%</t>
+          <t>2.12%</t>
+        </is>
+      </c>
+      <c r="E175" s="5" t="inlineStr">
+        <is>
+          <t>0.98%</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>8.69%</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="G175" s="4" t="inlineStr">
         <is>
-          <t>38.59%</t>
-        </is>
-      </c>
-      <c r="H175" s="4" t="inlineStr">
-        <is>
-          <t>46.75%</t>
+          <t>25.66%</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>2.47%</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>256.98%</t>
+          <t>42.54%</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>62.85%</t>
+          <t>56.66%</t>
         </is>
       </c>
       <c r="K175" t="n">
-        <v>8.35</v>
+        <v>4.33</v>
       </c>
       <c r="L175" t="n">
-        <v>16450000000</v>
+        <v>16080000000</v>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>193.84 -45.67</t>
+          <t>116.66 -4.71</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>17.42 504.54</t>
+          <t>52.43 112.04</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ROKU</t>
+          <t>OKLO</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Roku Inc</t>
+          <t>Oklo Inc</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>111.17</v>
+        <v>105.31</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2.12%</t>
-        </is>
-      </c>
-      <c r="E176" s="5" t="inlineStr">
-        <is>
-          <t>0.98%</t>
+          <t>7.90%</t>
+        </is>
+      </c>
+      <c r="E176" s="4" t="inlineStr">
+        <is>
+          <t>24.08%</t>
         </is>
       </c>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>8.69%</t>
         </is>
       </c>
       <c r="G176" s="4" t="inlineStr">
         <is>
-          <t>25.66%</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>2.47%</t>
+          <t>38.59%</t>
+        </is>
+      </c>
+      <c r="H176" s="4" t="inlineStr">
+        <is>
+          <t>46.75%</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>42.54%</t>
+          <t>256.98%</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>56.66%</t>
+          <t>62.85%</t>
         </is>
       </c>
       <c r="K176" t="n">
-        <v>4.33</v>
+        <v>8.35</v>
       </c>
       <c r="L176" t="n">
-        <v>16430000000</v>
+        <v>15250000000</v>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>116.66 -4.71</t>
+          <t>193.84 -45.67</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>52.43 112.04</t>
+          <t>17.42 504.54</t>
         </is>
       </c>
     </row>
@@ -12078,7 +12078,7 @@
         <v>4.12</v>
       </c>
       <c r="L177" t="n">
-        <v>15070000000</v>
+        <v>14960000000</v>
       </c>
       <c r="M177" t="inlineStr">
         <is>
@@ -12094,132 +12094,132 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Celsius Holdings Inc</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>52.9</v>
+        <v>34.3</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>3.16%</t>
+          <t>1.30%</t>
         </is>
       </c>
       <c r="E178" s="4" t="inlineStr">
         <is>
-          <t>15.29%</t>
+          <t>7.34%</t>
         </is>
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>15.66%</t>
+          <t>22.55%</t>
         </is>
       </c>
       <c r="G178" s="4" t="inlineStr">
         <is>
-          <t>12.58%</t>
+          <t>25.12%</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr">
         <is>
-          <t>15.65%</t>
+          <t>16.31%</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>81.16%</t>
-        </is>
-      </c>
-      <c r="J178" s="4" t="inlineStr">
-        <is>
-          <t>73.21%</t>
+          <t>-27.84%</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>61.70%</t>
         </is>
       </c>
       <c r="K178" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="L178" t="n">
-        <v>13640000000</v>
+        <v>13230000000</v>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>66.74 -20.74</t>
+          <t>45.40 -24.45</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>21.10 150.71</t>
+          <t>22.28 53.95</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>Celsius Holdings Inc</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>34.3</v>
+        <v>52.9</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>3.16%</t>
         </is>
       </c>
       <c r="E179" s="4" t="inlineStr">
         <is>
-          <t>7.34%</t>
+          <t>15.29%</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>22.55%</t>
+          <t>15.66%</t>
         </is>
       </c>
       <c r="G179" s="4" t="inlineStr">
         <is>
-          <t>25.12%</t>
+          <t>12.58%</t>
         </is>
       </c>
       <c r="H179" s="4" t="inlineStr">
         <is>
-          <t>16.31%</t>
+          <t>15.65%</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>-27.84%</t>
-        </is>
-      </c>
-      <c r="J179" t="inlineStr">
-        <is>
-          <t>61.70%</t>
+          <t>81.16%</t>
+        </is>
+      </c>
+      <c r="J179" s="4" t="inlineStr">
+        <is>
+          <t>73.21%</t>
         </is>
       </c>
       <c r="K179" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="L179" t="n">
-        <v>13400000000</v>
+        <v>13220000000</v>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>45.40 -24.45</t>
+          <t>66.74 -20.74</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>22.28 53.95</t>
+          <t>21.10 150.71</t>
         </is>
       </c>
     </row>
@@ -12276,7 +12276,7 @@
         <v>3.95</v>
       </c>
       <c r="L180" t="n">
-        <v>12110000000</v>
+        <v>11940000000</v>
       </c>
       <c r="M180" t="inlineStr">
         <is>
@@ -12342,7 +12342,7 @@
         <v>2.99</v>
       </c>
       <c r="L181" t="n">
-        <v>10520000000</v>
+        <v>10530000000</v>
       </c>
       <c r="M181" t="inlineStr">
         <is>
@@ -12408,7 +12408,7 @@
         <v>2.3</v>
       </c>
       <c r="L182" t="n">
-        <v>10260000000</v>
+        <v>10370000000</v>
       </c>
       <c r="M182" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
         <v>0.63</v>
       </c>
       <c r="L183" t="n">
-        <v>9400000000</v>
+        <v>9150000000</v>
       </c>
       <c r="M183" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
         <v>2.07</v>
       </c>
       <c r="L184" t="n">
-        <v>8160000000</v>
+        <v>8330000000</v>
       </c>
       <c r="M184" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         <v>1.87</v>
       </c>
       <c r="L185" t="n">
-        <v>7210000000</v>
+        <v>7710000000</v>
       </c>
       <c r="M185" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         <v>0.66</v>
       </c>
       <c r="L186" t="n">
-        <v>6580000000</v>
+        <v>6440000000</v>
       </c>
       <c r="M186" t="inlineStr">
         <is>
@@ -12688,198 +12688,198 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>LMND</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>NuScale Power Corporation</t>
+          <t>Lemonade Inc</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>20.51</v>
+        <v>79.65000000000001</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>4.27%</t>
-        </is>
-      </c>
-      <c r="E187" s="4" t="inlineStr">
-        <is>
-          <t>19.84%</t>
-        </is>
-      </c>
-      <c r="F187" s="2" t="inlineStr">
-        <is>
-          <t>-8.42%</t>
-        </is>
-      </c>
-      <c r="G187" s="2" t="inlineStr">
-        <is>
-          <t>-32.90%</t>
-        </is>
-      </c>
-      <c r="H187" s="4" t="inlineStr">
-        <is>
-          <t>44.74%</t>
+          <t>-1.37%</t>
+        </is>
+      </c>
+      <c r="E187" s="5" t="inlineStr">
+        <is>
+          <t>1.77%</t>
+        </is>
+      </c>
+      <c r="F187" s="4" t="inlineStr">
+        <is>
+          <t>6.88%</t>
+        </is>
+      </c>
+      <c r="G187" s="4" t="inlineStr">
+        <is>
+          <t>57.82%</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>11.90%</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>-5.57%</t>
+          <t>120.39%</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>56.24%</t>
+          <t>55.26%</t>
         </is>
       </c>
       <c r="K187" t="n">
-        <v>1.8</v>
+        <v>4.68</v>
       </c>
       <c r="L187" t="n">
-        <v>6210000000</v>
+        <v>6040000000</v>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>57.42 -64.28</t>
+          <t>85.20 -6.51</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>11.08 85.11</t>
+          <t>24.31 227.64</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>LMND</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Lemonade Inc</t>
+          <t>NuScale Power Corporation</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>79.65000000000001</v>
+        <v>20.51</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>-1.37%</t>
-        </is>
-      </c>
-      <c r="E188" s="5" t="inlineStr">
-        <is>
-          <t>1.77%</t>
-        </is>
-      </c>
-      <c r="F188" s="4" t="inlineStr">
-        <is>
-          <t>6.88%</t>
-        </is>
-      </c>
-      <c r="G188" s="4" t="inlineStr">
-        <is>
-          <t>57.82%</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>11.90%</t>
+          <t>4.27%</t>
+        </is>
+      </c>
+      <c r="E188" s="4" t="inlineStr">
+        <is>
+          <t>19.84%</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>-8.42%</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>-32.90%</t>
+        </is>
+      </c>
+      <c r="H188" s="4" t="inlineStr">
+        <is>
+          <t>44.74%</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>120.39%</t>
+          <t>-5.57%</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>55.26%</t>
+          <t>56.24%</t>
         </is>
       </c>
       <c r="K188" t="n">
-        <v>4.68</v>
+        <v>1.8</v>
       </c>
       <c r="L188" t="n">
         <v>5950000000</v>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>85.20 -6.51</t>
+          <t>57.42 -64.28</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>24.31 227.64</t>
+          <t>11.08 85.11</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>LEU</t>
+          <t>CRSP</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Centrus Energy Corp</t>
+          <t>CRISPR Therapeutics AG</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>306.19</v>
+        <v>53.84</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>6.97%</t>
-        </is>
-      </c>
-      <c r="E189" s="4" t="inlineStr">
-        <is>
-          <t>16.15%</t>
-        </is>
-      </c>
-      <c r="F189" s="4" t="inlineStr">
-        <is>
-          <t>11.70%</t>
-        </is>
-      </c>
-      <c r="G189" s="4" t="inlineStr">
-        <is>
-          <t>45.22%</t>
-        </is>
-      </c>
-      <c r="H189" s="4" t="inlineStr">
-        <is>
-          <t>26.13%</t>
+          <t>-4.54%</t>
+        </is>
+      </c>
+      <c r="E189" s="3" t="inlineStr">
+        <is>
+          <t>-3.30%</t>
+        </is>
+      </c>
+      <c r="F189" s="3" t="inlineStr">
+        <is>
+          <t>-2.86%</t>
+        </is>
+      </c>
+      <c r="G189" s="5" t="inlineStr">
+        <is>
+          <t>3.64%</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>2.67%</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>315.74%</t>
+          <t>28.44%</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>59.07%</t>
+          <t>44.66%</t>
         </is>
       </c>
       <c r="K189" t="n">
-        <v>23.07</v>
+        <v>2.78</v>
       </c>
       <c r="L189" t="n">
-        <v>5580000000</v>
+        <v>5370000000</v>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>464.25 -34.05</t>
+          <t>78.48 -31.40</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>49.40 519.82</t>
+          <t>30.04 79.23</t>
         </is>
       </c>
     </row>
@@ -12936,7 +12936,7 @@
         <v>1.18</v>
       </c>
       <c r="L190" t="n">
-        <v>5210000000</v>
+        <v>5260000000</v>
       </c>
       <c r="M190" t="inlineStr">
         <is>
@@ -13002,7 +13002,7 @@
         <v>0.46</v>
       </c>
       <c r="L191" t="n">
-        <v>5140000000</v>
+        <v>5210000000</v>
       </c>
       <c r="M191" t="inlineStr">
         <is>
@@ -13018,66 +13018,66 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>CRSP</t>
+          <t>LEU</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>CRISPR Therapeutics AG</t>
+          <t>Centrus Energy Corp</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>53.84</v>
+        <v>306.19</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>-4.54%</t>
-        </is>
-      </c>
-      <c r="E192" s="3" t="inlineStr">
-        <is>
-          <t>-3.30%</t>
-        </is>
-      </c>
-      <c r="F192" s="3" t="inlineStr">
-        <is>
-          <t>-2.86%</t>
-        </is>
-      </c>
-      <c r="G192" s="5" t="inlineStr">
-        <is>
-          <t>3.64%</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>2.67%</t>
+          <t>6.97%</t>
+        </is>
+      </c>
+      <c r="E192" s="4" t="inlineStr">
+        <is>
+          <t>16.15%</t>
+        </is>
+      </c>
+      <c r="F192" s="4" t="inlineStr">
+        <is>
+          <t>11.70%</t>
+        </is>
+      </c>
+      <c r="G192" s="4" t="inlineStr">
+        <is>
+          <t>45.22%</t>
+        </is>
+      </c>
+      <c r="H192" s="4" t="inlineStr">
+        <is>
+          <t>26.13%</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>28.44%</t>
+          <t>315.74%</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>44.66%</t>
+          <t>59.07%</t>
         </is>
       </c>
       <c r="K192" t="n">
-        <v>2.78</v>
+        <v>23.07</v>
       </c>
       <c r="L192" t="n">
-        <v>5130000000</v>
+        <v>5210000000</v>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>78.48 -31.40</t>
+          <t>464.25 -34.05</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>30.04 79.23</t>
+          <t>49.40 519.82</t>
         </is>
       </c>
     </row>
@@ -13134,7 +13134,7 @@
         <v>2.48</v>
       </c>
       <c r="L193" t="n">
-        <v>4780000000</v>
+        <v>4920000000</v>
       </c>
       <c r="M193" t="inlineStr">
         <is>
@@ -13150,264 +13150,264 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>OSCR</t>
+          <t>TMDX</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Oscar Health Inc</t>
+          <t>Transmedics Group Inc</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>17.73</v>
+        <v>137.07</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>4.91%</t>
+          <t>-0.36%</t>
         </is>
       </c>
       <c r="E194" s="4" t="inlineStr">
         <is>
-          <t>13.75%</t>
+          <t>7.84%</t>
         </is>
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>11.09%</t>
+          <t>6.08%</t>
         </is>
       </c>
       <c r="G194" s="4" t="inlineStr">
         <is>
-          <t>9.57%</t>
-        </is>
-      </c>
-      <c r="H194" s="4" t="inlineStr">
-        <is>
-          <t>23.38%</t>
+          <t>17.15%</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>12.68%</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>23.21%</t>
+          <t>74.23%</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>64.87%</t>
+          <t>61.58%</t>
         </is>
       </c>
       <c r="K194" t="n">
-        <v>0.9</v>
+        <v>5.85</v>
       </c>
       <c r="L194" t="n">
-        <v>4690000000</v>
+        <v>4700000000</v>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>23.80 -25.50</t>
+          <t>156.00 -12.13</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>11.20 58.30</t>
+          <t>55.00 149.22</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>TMDX</t>
+          <t>OSCR</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Transmedics Group Inc</t>
+          <t>Oscar Health Inc</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>137.07</v>
+        <v>17.73</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>-0.36%</t>
+          <t>4.91%</t>
         </is>
       </c>
       <c r="E195" s="4" t="inlineStr">
         <is>
-          <t>7.84%</t>
+          <t>13.75%</t>
         </is>
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>6.08%</t>
+          <t>11.09%</t>
         </is>
       </c>
       <c r="G195" s="4" t="inlineStr">
         <is>
-          <t>17.15%</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>12.68%</t>
+          <t>9.57%</t>
+        </is>
+      </c>
+      <c r="H195" s="4" t="inlineStr">
+        <is>
+          <t>23.38%</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>74.23%</t>
+          <t>23.21%</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>61.58%</t>
+          <t>64.87%</t>
         </is>
       </c>
       <c r="K195" t="n">
-        <v>5.85</v>
+        <v>0.9</v>
       </c>
       <c r="L195" t="n">
-        <v>4680000000</v>
+        <v>4470000000</v>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>156.00 -12.13</t>
+          <t>23.80 -25.50</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>55.00 149.22</t>
+          <t>11.20 58.30</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>FLNC</t>
+          <t>MARA</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Fluence Energy Inc</t>
+          <t>MARA Holdings Inc</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>23.2</v>
+        <v>10.22</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>9.54%</t>
-        </is>
-      </c>
-      <c r="E196" s="4" t="inlineStr">
-        <is>
-          <t>10.36%</t>
-        </is>
-      </c>
-      <c r="F196" s="4" t="inlineStr">
-        <is>
-          <t>14.89%</t>
-        </is>
-      </c>
-      <c r="G196" s="4" t="inlineStr">
-        <is>
-          <t>112.03%</t>
-        </is>
-      </c>
-      <c r="H196" s="4" t="inlineStr">
-        <is>
-          <t>17.29%</t>
+          <t>-2.11%</t>
+        </is>
+      </c>
+      <c r="E196" s="5" t="inlineStr">
+        <is>
+          <t>0.48%</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>-15.89%</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>-32.40%</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>13.81%</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>31.37%</t>
+          <t>-46.41%</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>59.15%</t>
+          <t>44.23%</t>
         </is>
       </c>
       <c r="K196" t="n">
-        <v>1.9</v>
+        <v>0.71</v>
       </c>
       <c r="L196" t="n">
-        <v>4240000000</v>
+        <v>3950000000</v>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>25.85 -10.25</t>
+          <t>23.45 -56.42</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>3.46 570.52</t>
+          <t>8.95 14.19</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>MARA</t>
+          <t>FLNC</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>MARA Holdings Inc</t>
+          <t>Fluence Energy Inc</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>10.22</v>
+        <v>23.2</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>-2.11%</t>
-        </is>
-      </c>
-      <c r="E197" s="5" t="inlineStr">
-        <is>
-          <t>0.48%</t>
-        </is>
-      </c>
-      <c r="F197" s="2" t="inlineStr">
-        <is>
-          <t>-15.89%</t>
-        </is>
-      </c>
-      <c r="G197" s="2" t="inlineStr">
-        <is>
-          <t>-32.40%</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>13.81%</t>
+          <t>9.54%</t>
+        </is>
+      </c>
+      <c r="E197" s="4" t="inlineStr">
+        <is>
+          <t>10.36%</t>
+        </is>
+      </c>
+      <c r="F197" s="4" t="inlineStr">
+        <is>
+          <t>14.89%</t>
+        </is>
+      </c>
+      <c r="G197" s="4" t="inlineStr">
+        <is>
+          <t>112.03%</t>
+        </is>
+      </c>
+      <c r="H197" s="4" t="inlineStr">
+        <is>
+          <t>17.29%</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>-46.41%</t>
+          <t>31.37%</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>44.23%</t>
+          <t>59.15%</t>
         </is>
       </c>
       <c r="K197" t="n">
-        <v>0.71</v>
+        <v>1.9</v>
       </c>
       <c r="L197" t="n">
         <v>3870000000</v>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>23.45 -56.42</t>
+          <t>25.85 -10.25</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>8.95 14.19</t>
+          <t>3.46 570.52</t>
         </is>
       </c>
     </row>
@@ -13464,7 +13464,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="L198" t="n">
-        <v>2630000000</v>
+        <v>2680000000</v>
       </c>
       <c r="M198" t="inlineStr">
         <is>
@@ -13530,7 +13530,7 @@
         <v>0.6</v>
       </c>
       <c r="L199" t="n">
-        <v>1970000000</v>
+        <v>1950000000</v>
       </c>
       <c r="M199" t="inlineStr">
         <is>
@@ -13662,7 +13662,7 @@
         <v>2.87</v>
       </c>
       <c r="L201" t="n">
-        <v>1620000000</v>
+        <v>1670000000</v>
       </c>
       <c r="M201" t="inlineStr">
         <is>
@@ -13728,7 +13728,7 @@
         <v>0.51</v>
       </c>
       <c r="L202" t="n">
-        <v>1390000000</v>
+        <v>1490000000</v>
       </c>
       <c r="M202" t="inlineStr">
         <is>
@@ -13794,7 +13794,7 @@
         <v>0.32</v>
       </c>
       <c r="L203" t="n">
-        <v>1320000000</v>
+        <v>1350000000</v>
       </c>
       <c r="M203" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>0.59</v>
       </c>
       <c r="L204" t="n">
-        <v>939580000</v>
+        <v>805710000</v>
       </c>
       <c r="M204" t="inlineStr">
         <is>
@@ -13926,7 +13926,7 @@
         <v>1.4</v>
       </c>
       <c r="L205" t="n">
-        <v>522520000</v>
+        <v>556450000</v>
       </c>
       <c r="M205" t="inlineStr">
         <is>

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -858,7 +858,7 @@
         <v>7.38</v>
       </c>
       <c r="L7" t="n">
-        <v>3983700000000</v>
+        <v>3983950000000</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>5.9</v>
       </c>
       <c r="L14" t="n">
-        <v>1064070000000</v>
+        <v>1064620000000</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -6666,7 +6666,7 @@
         <v>9.07</v>
       </c>
       <c r="L95" t="n">
-        <v>123960000000</v>
+        <v>121560000000</v>
       </c>
       <c r="M95" t="inlineStr">
         <is>
@@ -10560,7 +10560,7 @@
         <v>1</v>
       </c>
       <c r="L154" t="n">
-        <v>38010000000</v>
+        <v>37980000000</v>
       </c>
       <c r="M154" t="inlineStr">
         <is>
@@ -11946,7 +11946,7 @@
         <v>2.5</v>
       </c>
       <c r="L175" t="n">
-        <v>16550000000</v>
+        <v>16540000000</v>
       </c>
       <c r="M175" t="inlineStr">
         <is>

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -846,7 +846,7 @@
         <v>10.13</v>
       </c>
       <c r="L7" t="n">
-        <v>3896710000000</v>
+        <v>3906940000000</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>7.72</v>
       </c>
       <c r="L14" t="n">
-        <v>1096700000000</v>
+        <v>1096350000000</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
         <v>0.63</v>
       </c>
       <c r="L118" t="n">
-        <v>83360000000</v>
+        <v>84310000000</v>
       </c>
       <c r="M118" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
         <v>1.29</v>
       </c>
       <c r="L140" t="n">
-        <v>46990000000</v>
+        <v>46820000000</v>
       </c>
       <c r="M140" t="inlineStr">
         <is>
@@ -10416,7 +10416,7 @@
         <v>5.5</v>
       </c>
       <c r="L152" t="n">
-        <v>35850000000</v>
+        <v>35980000000</v>
       </c>
       <c r="M152" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>5.84</v>
       </c>
       <c r="L171" t="n">
-        <v>13700000000</v>
+        <v>13860000000</v>
       </c>
       <c r="M171" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>2.95</v>
       </c>
       <c r="L173" t="n">
-        <v>13290000000</v>
+        <v>13280000000</v>
       </c>
       <c r="M173" t="inlineStr">
         <is>
@@ -12412,132 +12412,132 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>PRMB</t>
+          <t>MBLY</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Primo Brands Corp</t>
+          <t>Mobileye Global Inc</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>19.63</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2.08%</t>
-        </is>
-      </c>
-      <c r="E183" s="3" t="inlineStr">
-        <is>
-          <t>4.09%</t>
-        </is>
-      </c>
-      <c r="F183" s="2" t="inlineStr">
-        <is>
-          <t>13.40%</t>
+          <t>3.69%</t>
+        </is>
+      </c>
+      <c r="E183" s="1" t="inlineStr">
+        <is>
+          <t>-12.77%</t>
+        </is>
+      </c>
+      <c r="F183" s="1" t="inlineStr">
+        <is>
+          <t>-18.20%</t>
         </is>
       </c>
       <c r="G183" s="1" t="inlineStr">
         <is>
-          <t>-17.80%</t>
-        </is>
-      </c>
-      <c r="H183" s="2" t="inlineStr">
-        <is>
-          <t>20.06%</t>
+          <t>-36.85%</t>
+        </is>
+      </c>
+      <c r="H183" s="1" t="inlineStr">
+        <is>
+          <t>-16.57%</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>-41.44%</t>
-        </is>
-      </c>
-      <c r="J183" s="3" t="inlineStr">
-        <is>
-          <t>67.58%</t>
+          <t>-46.07%</t>
+        </is>
+      </c>
+      <c r="J183" s="4" t="inlineStr">
+        <is>
+          <t>34.42%</t>
         </is>
       </c>
       <c r="K183" t="n">
-        <v>0.63</v>
+        <v>0.54</v>
       </c>
       <c r="L183" t="n">
-        <v>7180000000</v>
+        <v>7320000000</v>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>35.85 -45.24</t>
+          <t>20.18 -56.84</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>14.36 36.70</t>
+          <t>8.32 4.69</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>MBLY</t>
+          <t>PRMB</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Mobileye Global Inc</t>
+          <t>Primo Brands Corp</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>8.710000000000001</v>
+        <v>19.63</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>3.69%</t>
-        </is>
-      </c>
-      <c r="E184" s="1" t="inlineStr">
-        <is>
-          <t>-12.77%</t>
-        </is>
-      </c>
-      <c r="F184" s="1" t="inlineStr">
-        <is>
-          <t>-18.20%</t>
+          <t>2.08%</t>
+        </is>
+      </c>
+      <c r="E184" s="3" t="inlineStr">
+        <is>
+          <t>4.09%</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>13.40%</t>
         </is>
       </c>
       <c r="G184" s="1" t="inlineStr">
         <is>
-          <t>-36.85%</t>
-        </is>
-      </c>
-      <c r="H184" s="1" t="inlineStr">
-        <is>
-          <t>-16.57%</t>
+          <t>-17.80%</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>20.06%</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>-46.07%</t>
-        </is>
-      </c>
-      <c r="J184" s="4" t="inlineStr">
-        <is>
-          <t>34.42%</t>
+          <t>-41.44%</t>
+        </is>
+      </c>
+      <c r="J184" s="3" t="inlineStr">
+        <is>
+          <t>67.58%</t>
         </is>
       </c>
       <c r="K184" t="n">
-        <v>0.54</v>
+        <v>0.63</v>
       </c>
       <c r="L184" t="n">
-        <v>7090000000</v>
+        <v>7180000000</v>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>20.18 -56.84</t>
+          <t>35.85 -45.24</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>8.32 4.69</t>
+          <t>14.36 36.70</t>
         </is>
       </c>
     </row>

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -846,7 +846,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>3699490000000</v>
+        <v>3699930000000</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>7.52</v>
       </c>
       <c r="L14" t="n">
-        <v>1073130000000</v>
+        <v>1076050000000</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>40.48</v>
       </c>
       <c r="L16" t="n">
-        <v>983200000000</v>
+        <v>981090000000</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>12.79</v>
       </c>
       <c r="L23" t="n">
-        <v>462490000000</v>
+        <v>462280000000</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -6137,726 +6137,726 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>4140.6</v>
+        <v>166.95</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>-0.44%</t>
-        </is>
-      </c>
-      <c r="E88" s="1" t="inlineStr">
-        <is>
-          <t>-13.21%</t>
+          <t>2.54%</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>-3.76%</t>
         </is>
       </c>
       <c r="F88" s="1" t="inlineStr">
         <is>
-          <t>-18.93%</t>
+          <t>-8.70%</t>
         </is>
       </c>
       <c r="G88" s="1" t="inlineStr">
         <is>
-          <t>-21.95%</t>
+          <t>-13.61%</t>
         </is>
       </c>
       <c r="H88" s="1" t="inlineStr">
         <is>
-          <t>-22.68%</t>
+          <t>-9.36%</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>-17.33%</t>
-        </is>
-      </c>
-      <c r="J88" s="1" t="inlineStr">
-        <is>
-          <t>22.33%</t>
+          <t>-17.30%</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>40.87%</t>
         </is>
       </c>
       <c r="K88" t="n">
-        <v>175.84</v>
+        <v>6.83</v>
       </c>
       <c r="L88" t="n">
-        <v>133470000000</v>
+        <v>134910000000</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>5839.41 -29.09</t>
+          <t>223.61 -25.34</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>4096.23 1.08</t>
+          <t>144.15 15.82</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Arm Holdings plc. ADR</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>125.28</v>
+        <v>4140.6</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2.53%</t>
-        </is>
-      </c>
-      <c r="E89" s="3" t="inlineStr">
-        <is>
-          <t>9.43%</t>
-        </is>
-      </c>
-      <c r="F89" s="3" t="inlineStr">
-        <is>
-          <t>6.49%</t>
+          <t>-0.44%</t>
+        </is>
+      </c>
+      <c r="E89" s="1" t="inlineStr">
+        <is>
+          <t>-13.21%</t>
+        </is>
+      </c>
+      <c r="F89" s="1" t="inlineStr">
+        <is>
+          <t>-18.93%</t>
         </is>
       </c>
       <c r="G89" s="1" t="inlineStr">
         <is>
-          <t>-9.48%</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>14.61%</t>
+          <t>-21.95%</t>
+        </is>
+      </c>
+      <c r="H89" s="1" t="inlineStr">
+        <is>
+          <t>-22.68%</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>-23.99%</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>61.73%</t>
+          <t>-17.33%</t>
+        </is>
+      </c>
+      <c r="J89" s="1" t="inlineStr">
+        <is>
+          <t>22.33%</t>
         </is>
       </c>
       <c r="K89" t="n">
-        <v>6.56</v>
+        <v>175.84</v>
       </c>
       <c r="L89" t="n">
-        <v>133050000000</v>
+        <v>133470000000</v>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>183.16 -31.60</t>
+          <t>5839.41 -29.09</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>80.00 56.60</t>
+          <t>4096.23 1.08</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Arm Holdings plc. ADR</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>138.97</v>
+        <v>125.28</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>1.90%</t>
-        </is>
-      </c>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t>4.70%</t>
+          <t>2.53%</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>9.43%</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>6.58%</t>
-        </is>
-      </c>
-      <c r="G90" s="3" t="inlineStr">
-        <is>
-          <t>18.49%</t>
+          <t>6.49%</t>
+        </is>
+      </c>
+      <c r="G90" s="1" t="inlineStr">
+        <is>
+          <t>-9.48%</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>8.86%</t>
+          <t>14.61%</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>14.95%</t>
+          <t>-23.99%</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>64.03%</t>
+          <t>61.73%</t>
         </is>
       </c>
       <c r="K90" t="n">
-        <v>2.99</v>
+        <v>6.56</v>
       </c>
       <c r="L90" t="n">
-        <v>132150000000</v>
+        <v>133050000000</v>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>141.95 -2.10</t>
+          <t>183.16 -31.60</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>85.35 62.82</t>
+          <t>80.00 56.60</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>390.55</v>
+        <v>138.97</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>6.44%</t>
-        </is>
-      </c>
-      <c r="E91" s="1" t="inlineStr">
-        <is>
-          <t>-18.96%</t>
-        </is>
-      </c>
-      <c r="F91" s="1" t="inlineStr">
-        <is>
-          <t>-34.68%</t>
-        </is>
-      </c>
-      <c r="G91" s="1" t="inlineStr">
-        <is>
-          <t>-22.51%</t>
-        </is>
-      </c>
-      <c r="H91" s="1" t="inlineStr">
-        <is>
-          <t>-42.04%</t>
+          <t>1.90%</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>4.70%</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>6.58%</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>18.49%</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>8.86%</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>-17.20%</t>
+          <t>14.95%</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>35.30%</t>
+          <t>64.03%</t>
         </is>
       </c>
       <c r="K91" t="n">
-        <v>43.02</v>
+        <v>2.99</v>
       </c>
       <c r="L91" t="n">
-        <v>131990000000</v>
+        <v>132150000000</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>745.61 -47.62</t>
+          <t>141.95 -2.10</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>200.50 94.79</t>
+          <t>85.35 62.82</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Chubb Limited</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>324.95</v>
+        <v>390.55</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>-2.27%</t>
-        </is>
-      </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>3.43%</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>4.84%</t>
-        </is>
-      </c>
-      <c r="G92" s="3" t="inlineStr">
-        <is>
-          <t>12.42%</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>4.11%</t>
+          <t>6.44%</t>
+        </is>
+      </c>
+      <c r="E92" s="1" t="inlineStr">
+        <is>
+          <t>-18.96%</t>
+        </is>
+      </c>
+      <c r="F92" s="1" t="inlineStr">
+        <is>
+          <t>-34.68%</t>
+        </is>
+      </c>
+      <c r="G92" s="1" t="inlineStr">
+        <is>
+          <t>-22.51%</t>
+        </is>
+      </c>
+      <c r="H92" s="1" t="inlineStr">
+        <is>
+          <t>-42.04%</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>21.37%</t>
+          <t>-17.20%</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>61.06%</t>
+          <t>35.30%</t>
         </is>
       </c>
       <c r="K92" t="n">
-        <v>7.06</v>
+        <v>43.02</v>
       </c>
       <c r="L92" t="n">
-        <v>127880000000</v>
+        <v>131990000000</v>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>335.60 -3.17</t>
+          <t>745.61 -47.62</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>263.14 23.49</t>
+          <t>200.50 94.79</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Medtronic Plc</t>
+          <t>Chubb Limited</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>99.48999999999999</v>
+        <v>324.95</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>-1.38%</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>-1.60%</t>
-        </is>
-      </c>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t>-0.09%</t>
+          <t>-2.27%</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>3.43%</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>4.84%</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>6.53%</t>
+          <t>12.42%</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>4.11%</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>7.91%</t>
+          <t>21.37%</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>44.58%</t>
+          <t>61.06%</t>
         </is>
       </c>
       <c r="K93" t="n">
-        <v>2.18</v>
+        <v>7.06</v>
       </c>
       <c r="L93" t="n">
-        <v>127550000000</v>
+        <v>127880000000</v>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>106.33 -6.43</t>
+          <t>335.60 -3.17</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>79.55 25.07</t>
+          <t>263.14 23.49</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Co</t>
+          <t>Medtronic Plc</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>60.74</v>
+        <v>99.48999999999999</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>1.47%</t>
-        </is>
-      </c>
-      <c r="E94" s="3" t="inlineStr">
-        <is>
-          <t>6.48%</t>
-        </is>
-      </c>
-      <c r="F94" s="3" t="inlineStr">
-        <is>
-          <t>10.12%</t>
+          <t>-1.38%</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>-1.60%</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>24.34%</t>
+          <t>6.53%</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>12.61%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>8.52%</t>
-        </is>
-      </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t>67.28%</t>
+          <t>7.91%</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>44.58%</t>
         </is>
       </c>
       <c r="K94" t="n">
-        <v>1.42</v>
+        <v>2.18</v>
       </c>
       <c r="L94" t="n">
-        <v>123700000000</v>
+        <v>127550000000</v>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>63.33 -4.09</t>
+          <t>106.33 -6.43</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>42.52 42.85</t>
+          <t>79.55 25.07</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>S&amp;P Global Inc</t>
+          <t>Bristol-Myers Squibb Co</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>409.54</v>
+        <v>60.74</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>3.11%</t>
-        </is>
-      </c>
-      <c r="E95" s="1" t="inlineStr">
-        <is>
-          <t>-15.66%</t>
-        </is>
-      </c>
-      <c r="F95" s="1" t="inlineStr">
-        <is>
-          <t>-18.98%</t>
-        </is>
-      </c>
-      <c r="G95" s="1" t="inlineStr">
-        <is>
-          <t>-20.12%</t>
-        </is>
-      </c>
-      <c r="H95" s="1" t="inlineStr">
-        <is>
-          <t>-21.63%</t>
+          <t>1.47%</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>6.48%</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>10.12%</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>24.34%</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>12.61%</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>-24.48%</t>
-        </is>
-      </c>
-      <c r="J95" s="1" t="inlineStr">
-        <is>
-          <t>25.62%</t>
+          <t>8.52%</t>
+        </is>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>67.28%</t>
         </is>
       </c>
       <c r="K95" t="n">
-        <v>18.19</v>
+        <v>1.42</v>
       </c>
       <c r="L95" t="n">
-        <v>122370000000</v>
+        <v>123700000000</v>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>579.05 -29.27</t>
+          <t>63.33 -4.09</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>381.61 7.32</t>
+          <t>42.52 42.85</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>HCA Healthcare Inc</t>
+          <t>S&amp;P Global Inc</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>540.29</v>
+        <v>409.54</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>0.95%</t>
-        </is>
-      </c>
-      <c r="E96" s="3" t="inlineStr">
-        <is>
-          <t>9.28%</t>
-        </is>
-      </c>
-      <c r="F96" s="3" t="inlineStr">
-        <is>
-          <t>11.64%</t>
-        </is>
-      </c>
-      <c r="G96" s="3" t="inlineStr">
-        <is>
-          <t>27.41%</t>
-        </is>
-      </c>
-      <c r="H96" s="3" t="inlineStr">
-        <is>
-          <t>15.73%</t>
+          <t>3.11%</t>
+        </is>
+      </c>
+      <c r="E96" s="1" t="inlineStr">
+        <is>
+          <t>-15.66%</t>
+        </is>
+      </c>
+      <c r="F96" s="1" t="inlineStr">
+        <is>
+          <t>-18.98%</t>
+        </is>
+      </c>
+      <c r="G96" s="1" t="inlineStr">
+        <is>
+          <t>-20.12%</t>
+        </is>
+      </c>
+      <c r="H96" s="1" t="inlineStr">
+        <is>
+          <t>-21.63%</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>67.83%</t>
-        </is>
-      </c>
-      <c r="J96" s="4" t="inlineStr">
-        <is>
-          <t>69.42%</t>
+          <t>-24.48%</t>
+        </is>
+      </c>
+      <c r="J96" s="1" t="inlineStr">
+        <is>
+          <t>25.62%</t>
         </is>
       </c>
       <c r="K96" t="n">
-        <v>15.57</v>
+        <v>18.19</v>
       </c>
       <c r="L96" t="n">
-        <v>120820000000</v>
+        <v>122370000000</v>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>552.90 -2.28</t>
+          <t>579.05 -29.27</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>295.00 83.15</t>
+          <t>381.61 7.32</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Progressive Corp</t>
+          <t>HCA Healthcare Inc</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>204.53</v>
+        <v>540.29</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>-0.45%</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>-0.45%</t>
-        </is>
-      </c>
-      <c r="F97" s="1" t="inlineStr">
-        <is>
-          <t>-5.05%</t>
-        </is>
-      </c>
-      <c r="G97" s="1" t="inlineStr">
-        <is>
-          <t>-14.84%</t>
-        </is>
-      </c>
-      <c r="H97" s="1" t="inlineStr">
-        <is>
-          <t>-10.18%</t>
+          <t>0.95%</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>9.28%</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>11.64%</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>27.41%</t>
+        </is>
+      </c>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>15.73%</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>-21.97%</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>44.81%</t>
+          <t>67.83%</t>
+        </is>
+      </c>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>69.42%</t>
         </is>
       </c>
       <c r="K97" t="n">
-        <v>5.72</v>
+        <v>15.57</v>
       </c>
       <c r="L97" t="n">
-        <v>119940000000</v>
+        <v>120820000000</v>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>292.99 -30.19</t>
+          <t>552.90 -2.28</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>197.92 3.34</t>
+          <t>295.00 83.15</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>Progressive Corp</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>166.95</v>
+        <v>204.53</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2.54%</t>
+          <t>-0.45%</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>-3.76%</t>
+          <t>-0.45%</t>
         </is>
       </c>
       <c r="F98" s="1" t="inlineStr">
         <is>
-          <t>-8.70%</t>
+          <t>-5.05%</t>
         </is>
       </c>
       <c r="G98" s="1" t="inlineStr">
         <is>
-          <t>-13.61%</t>
+          <t>-14.84%</t>
         </is>
       </c>
       <c r="H98" s="1" t="inlineStr">
         <is>
-          <t>-9.36%</t>
+          <t>-10.18%</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>-17.30%</t>
+          <t>-21.97%</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>40.87%</t>
+          <t>44.81%</t>
         </is>
       </c>
       <c r="K98" t="n">
-        <v>6.83</v>
+        <v>5.72</v>
       </c>
       <c r="L98" t="n">
-        <v>116360000000</v>
+        <v>119940000000</v>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>223.61 -25.34</t>
+          <t>292.99 -30.19</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>144.15 15.82</t>
+          <t>197.92 3.34</t>
         </is>
       </c>
     </row>
@@ -6913,7 +6913,7 @@
         <v>6.32</v>
       </c>
       <c r="L99" t="n">
-        <v>114420000000</v>
+        <v>114500000000</v>
       </c>
       <c r="M99" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>4.47</v>
       </c>
       <c r="L127" t="n">
-        <v>74700000000</v>
+        <v>74490000000</v>
       </c>
       <c r="M127" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>3.77</v>
       </c>
       <c r="L136" t="n">
-        <v>55810000000</v>
+        <v>53460000000</v>
       </c>
       <c r="M136" t="inlineStr">
         <is>
@@ -9701,264 +9701,264 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Coinbase Global Inc</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>164.32</v>
+        <v>125.2</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>16.46%</t>
-        </is>
-      </c>
-      <c r="E142" s="1" t="inlineStr">
-        <is>
-          <t>-13.50%</t>
+          <t>-0.74%</t>
+        </is>
+      </c>
+      <c r="E142" s="4" t="inlineStr">
+        <is>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="F142" s="1" t="inlineStr">
         <is>
-          <t>-27.54%</t>
+          <t>-6.27%</t>
         </is>
       </c>
       <c r="G142" s="1" t="inlineStr">
         <is>
-          <t>-43.27%</t>
+          <t>-9.59%</t>
         </is>
       </c>
       <c r="H142" s="1" t="inlineStr">
         <is>
-          <t>-27.34%</t>
+          <t>-7.93%</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>-44.88%</t>
+          <t>-7.87%</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>37.11%</t>
+          <t>48.25%</t>
         </is>
       </c>
       <c r="K142" t="n">
-        <v>13.08</v>
+        <v>7.67</v>
       </c>
       <c r="L142" t="n">
-        <v>44310000000</v>
+        <v>44260000000</v>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>444.64 -63.04</t>
+          <t>201.69 -37.92</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>139.36 17.91</t>
+          <t>81.63 53.37</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>Edwards Lifesciences Corp</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>125.2</v>
+        <v>75.87</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>-0.74%</t>
-        </is>
-      </c>
-      <c r="E143" s="4" t="inlineStr">
-        <is>
-          <t>0.20%</t>
+          <t>-0.75%</t>
+        </is>
+      </c>
+      <c r="E143" s="1" t="inlineStr">
+        <is>
+          <t>-6.36%</t>
         </is>
       </c>
       <c r="F143" s="1" t="inlineStr">
         <is>
-          <t>-6.27%</t>
-        </is>
-      </c>
-      <c r="G143" s="1" t="inlineStr">
-        <is>
-          <t>-9.59%</t>
+          <t>-8.98%</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>-4.66%</t>
         </is>
       </c>
       <c r="H143" s="1" t="inlineStr">
         <is>
-          <t>-7.93%</t>
+          <t>-11.00%</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>-7.87%</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>48.25%</t>
+          <t>-0.17%</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>33.01%</t>
         </is>
       </c>
       <c r="K143" t="n">
-        <v>7.67</v>
+        <v>2.26</v>
       </c>
       <c r="L143" t="n">
-        <v>44260000000</v>
+        <v>44030000000</v>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>201.69 -37.92</t>
+          <t>87.89 -13.68</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>81.63 53.37</t>
+          <t>65.94 15.06</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences Corp</t>
+          <t>Carnival Corp</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>75.87</v>
+        <v>31.77</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>-0.75%</t>
-        </is>
-      </c>
-      <c r="E144" s="1" t="inlineStr">
-        <is>
-          <t>-6.36%</t>
-        </is>
-      </c>
-      <c r="F144" s="1" t="inlineStr">
-        <is>
-          <t>-8.98%</t>
-        </is>
-      </c>
-      <c r="G144" s="2" t="inlineStr">
-        <is>
-          <t>-4.66%</t>
-        </is>
-      </c>
-      <c r="H144" s="1" t="inlineStr">
-        <is>
-          <t>-11.00%</t>
+          <t>-2.55%</t>
+        </is>
+      </c>
+      <c r="E144" s="4" t="inlineStr">
+        <is>
+          <t>3.31%</t>
+        </is>
+      </c>
+      <c r="F144" s="3" t="inlineStr">
+        <is>
+          <t>5.83%</t>
+        </is>
+      </c>
+      <c r="G144" s="3" t="inlineStr">
+        <is>
+          <t>13.25%</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>4.03%</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>-0.17%</t>
-        </is>
-      </c>
-      <c r="J144" s="2" t="inlineStr">
-        <is>
-          <t>33.01%</t>
+          <t>22.85%</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>53.25%</t>
         </is>
       </c>
       <c r="K144" t="n">
-        <v>2.26</v>
+        <v>1.28</v>
       </c>
       <c r="L144" t="n">
-        <v>44030000000</v>
+        <v>43930000000</v>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>87.89 -13.68</t>
+          <t>34.03 -6.64</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>65.94 15.06</t>
+          <t>15.07 110.82</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Carnival Corp</t>
+          <t>Coinbase Global Inc</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>31.77</v>
+        <v>164.32</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>-2.55%</t>
-        </is>
-      </c>
-      <c r="E145" s="4" t="inlineStr">
-        <is>
-          <t>3.31%</t>
-        </is>
-      </c>
-      <c r="F145" s="3" t="inlineStr">
-        <is>
-          <t>5.83%</t>
-        </is>
-      </c>
-      <c r="G145" s="3" t="inlineStr">
-        <is>
-          <t>13.25%</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>4.03%</t>
+          <t>16.46%</t>
+        </is>
+      </c>
+      <c r="E145" s="1" t="inlineStr">
+        <is>
+          <t>-13.50%</t>
+        </is>
+      </c>
+      <c r="F145" s="1" t="inlineStr">
+        <is>
+          <t>-27.54%</t>
+        </is>
+      </c>
+      <c r="G145" s="1" t="inlineStr">
+        <is>
+          <t>-43.27%</t>
+        </is>
+      </c>
+      <c r="H145" s="1" t="inlineStr">
+        <is>
+          <t>-27.34%</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>22.85%</t>
+          <t>-44.88%</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>53.25%</t>
+          <t>37.11%</t>
         </is>
       </c>
       <c r="K145" t="n">
-        <v>1.28</v>
+        <v>13.08</v>
       </c>
       <c r="L145" t="n">
-        <v>43880000000</v>
+        <v>43390000000</v>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>34.03 -6.64</t>
+          <t>444.64 -63.04</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>15.07 110.82</t>
+          <t>139.36 17.91</t>
         </is>
       </c>
     </row>
@@ -11269,7 +11269,7 @@
         <v>5.39</v>
       </c>
       <c r="L165" t="n">
-        <v>17850000000</v>
+        <v>17860000000</v>
       </c>
       <c r="M165" t="inlineStr">
         <is>
@@ -12655,7 +12655,7 @@
         <v>3.02</v>
       </c>
       <c r="L186" t="n">
-        <v>5060000000</v>
+        <v>5090000000</v>
       </c>
       <c r="M186" t="inlineStr">
         <is>
@@ -12985,7 +12985,7 @@
         <v>1.21</v>
       </c>
       <c r="L191" t="n">
-        <v>3930000000</v>
+        <v>4190000000</v>
       </c>
       <c r="M191" t="inlineStr">
         <is>
@@ -13777,7 +13777,7 @@
         <v>0.31</v>
       </c>
       <c r="L203" t="n">
-        <v>825260000</v>
+        <v>825250000</v>
       </c>
       <c r="M203" t="inlineStr">
         <is>
@@ -13909,7 +13909,7 @@
         <v>1.68</v>
       </c>
       <c r="L205" t="n">
-        <v>439550000</v>
+        <v>439560000</v>
       </c>
       <c r="M205" t="inlineStr">
         <is>

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -714,7 +714,7 @@
         <v>6.54</v>
       </c>
       <c r="L5" t="n">
-        <v>3755140000000</v>
+        <v>3755130000000</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>3699930000000</v>
+        <v>3701920000000</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>21.95</v>
       </c>
       <c r="L11" t="n">
-        <v>1618330000000</v>
+        <v>1618340000000</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1126,132 +1126,132 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tesla Inc</t>
+          <t>Broadcom Inc</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>417.44</v>
+        <v>325.17</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>-1.81%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-1.72%</t>
+          <t>-1.43%</t>
         </is>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
-          <t>-5.97%</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>8.38%</t>
+          <t>-6.01%</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>3.96%</t>
         </is>
       </c>
       <c r="H12" s="1" t="inlineStr">
         <is>
-          <t>-7.18%</t>
+          <t>-6.05%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>17.28%</t>
+          <t>37.90%</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>44.92%</t>
+          <t>44.78%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>16.07</v>
+        <v>15.15</v>
       </c>
       <c r="L12" t="n">
-        <v>1566420000000</v>
+        <v>1541720000000</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>498.83 -16.32</t>
+          <t>414.61 -21.57</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>214.25 94.84</t>
+          <t>138.10 135.46</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Broadcom Inc</t>
+          <t>Tesla Inc</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>325.17</v>
+        <v>417.44</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-1.81%</t>
+          <t>0.09%</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1.43%</t>
+          <t>-1.72%</t>
         </is>
       </c>
       <c r="F13" s="1" t="inlineStr">
         <is>
-          <t>-6.01%</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>3.96%</t>
+          <t>-5.97%</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>8.38%</t>
         </is>
       </c>
       <c r="H13" s="1" t="inlineStr">
         <is>
-          <t>-6.05%</t>
+          <t>-7.18%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>37.90%</t>
+          <t>17.28%</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>44.78%</t>
+          <t>44.92%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>15.15</v>
+        <v>16.07</v>
       </c>
       <c r="L13" t="n">
-        <v>1541720000000</v>
+        <v>1388330000000</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>414.61 -21.57</t>
+          <t>498.83 -16.32</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>138.10 135.46</t>
+          <t>214.25 94.84</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
         <v>7.52</v>
       </c>
       <c r="L14" t="n">
-        <v>1076050000000</v>
+        <v>1073380000000</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>40.48</v>
       </c>
       <c r="L16" t="n">
-        <v>981090000000</v>
+        <v>983200000000</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>70.56999999999999</v>
       </c>
       <c r="L68" t="n">
-        <v>191910000000</v>
+        <v>191920000000</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>16.74</v>
       </c>
       <c r="L70" t="n">
-        <v>189660000000</v>
+        <v>189670000000</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>32.69</v>
       </c>
       <c r="L73" t="n">
-        <v>174800000000</v>
+        <v>174810000000</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>14.99</v>
       </c>
       <c r="L78" t="n">
-        <v>163440000000</v>
+        <v>163430000000</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -6137,726 +6137,726 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>166.95</v>
+        <v>4140.6</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2.54%</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>-3.76%</t>
+          <t>-0.44%</t>
+        </is>
+      </c>
+      <c r="E88" s="1" t="inlineStr">
+        <is>
+          <t>-13.21%</t>
         </is>
       </c>
       <c r="F88" s="1" t="inlineStr">
         <is>
-          <t>-8.70%</t>
+          <t>-18.93%</t>
         </is>
       </c>
       <c r="G88" s="1" t="inlineStr">
         <is>
-          <t>-13.61%</t>
+          <t>-21.95%</t>
         </is>
       </c>
       <c r="H88" s="1" t="inlineStr">
         <is>
-          <t>-9.36%</t>
+          <t>-22.68%</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>-17.30%</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>40.87%</t>
+          <t>-17.33%</t>
+        </is>
+      </c>
+      <c r="J88" s="1" t="inlineStr">
+        <is>
+          <t>22.33%</t>
         </is>
       </c>
       <c r="K88" t="n">
-        <v>6.83</v>
+        <v>175.84</v>
       </c>
       <c r="L88" t="n">
-        <v>134910000000</v>
+        <v>133450000000</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>223.61 -25.34</t>
+          <t>5839.41 -29.09</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>144.15 15.82</t>
+          <t>4096.23 1.08</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>Arm Holdings plc. ADR</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>4140.6</v>
+        <v>125.28</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>-0.44%</t>
-        </is>
-      </c>
-      <c r="E89" s="1" t="inlineStr">
-        <is>
-          <t>-13.21%</t>
-        </is>
-      </c>
-      <c r="F89" s="1" t="inlineStr">
-        <is>
-          <t>-18.93%</t>
+          <t>2.53%</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>9.43%</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>6.49%</t>
         </is>
       </c>
       <c r="G89" s="1" t="inlineStr">
         <is>
-          <t>-21.95%</t>
-        </is>
-      </c>
-      <c r="H89" s="1" t="inlineStr">
-        <is>
-          <t>-22.68%</t>
+          <t>-9.48%</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>14.61%</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>-17.33%</t>
-        </is>
-      </c>
-      <c r="J89" s="1" t="inlineStr">
-        <is>
-          <t>22.33%</t>
+          <t>-23.99%</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>61.73%</t>
         </is>
       </c>
       <c r="K89" t="n">
-        <v>175.84</v>
+        <v>6.56</v>
       </c>
       <c r="L89" t="n">
-        <v>133470000000</v>
+        <v>133050000000</v>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>5839.41 -29.09</t>
+          <t>183.16 -31.60</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>4096.23 1.08</t>
+          <t>80.00 56.60</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Arm Holdings plc. ADR</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>125.28</v>
+        <v>138.97</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2.53%</t>
-        </is>
-      </c>
-      <c r="E90" s="3" t="inlineStr">
-        <is>
-          <t>9.43%</t>
+          <t>1.90%</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>4.70%</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>6.49%</t>
-        </is>
-      </c>
-      <c r="G90" s="1" t="inlineStr">
-        <is>
-          <t>-9.48%</t>
+          <t>6.58%</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>18.49%</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>14.61%</t>
+          <t>8.86%</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>-23.99%</t>
+          <t>14.95%</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>61.73%</t>
+          <t>64.03%</t>
         </is>
       </c>
       <c r="K90" t="n">
-        <v>6.56</v>
+        <v>2.99</v>
       </c>
       <c r="L90" t="n">
-        <v>133050000000</v>
+        <v>132110000000</v>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>183.16 -31.60</t>
+          <t>141.95 -2.10</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>80.00 56.60</t>
+          <t>85.35 62.82</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>138.97</v>
+        <v>390.55</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>1.90%</t>
-        </is>
-      </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>4.70%</t>
-        </is>
-      </c>
-      <c r="F91" s="3" t="inlineStr">
-        <is>
-          <t>6.58%</t>
-        </is>
-      </c>
-      <c r="G91" s="3" t="inlineStr">
-        <is>
-          <t>18.49%</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>8.86%</t>
+          <t>6.44%</t>
+        </is>
+      </c>
+      <c r="E91" s="1" t="inlineStr">
+        <is>
+          <t>-18.96%</t>
+        </is>
+      </c>
+      <c r="F91" s="1" t="inlineStr">
+        <is>
+          <t>-34.68%</t>
+        </is>
+      </c>
+      <c r="G91" s="1" t="inlineStr">
+        <is>
+          <t>-22.51%</t>
+        </is>
+      </c>
+      <c r="H91" s="1" t="inlineStr">
+        <is>
+          <t>-42.04%</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>14.95%</t>
+          <t>-17.20%</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>64.03%</t>
+          <t>35.30%</t>
         </is>
       </c>
       <c r="K91" t="n">
-        <v>2.99</v>
+        <v>43.02</v>
       </c>
       <c r="L91" t="n">
-        <v>132150000000</v>
+        <v>131990000000</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>141.95 -2.10</t>
+          <t>745.61 -47.62</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>85.35 62.82</t>
+          <t>200.50 94.79</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>Chubb Limited</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>390.55</v>
+        <v>324.95</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>6.44%</t>
-        </is>
-      </c>
-      <c r="E92" s="1" t="inlineStr">
-        <is>
-          <t>-18.96%</t>
-        </is>
-      </c>
-      <c r="F92" s="1" t="inlineStr">
-        <is>
-          <t>-34.68%</t>
-        </is>
-      </c>
-      <c r="G92" s="1" t="inlineStr">
-        <is>
-          <t>-22.51%</t>
-        </is>
-      </c>
-      <c r="H92" s="1" t="inlineStr">
-        <is>
-          <t>-42.04%</t>
+          <t>-2.27%</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>3.43%</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>4.84%</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>12.42%</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>4.11%</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>-17.20%</t>
+          <t>21.37%</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>35.30%</t>
+          <t>61.06%</t>
         </is>
       </c>
       <c r="K92" t="n">
-        <v>43.02</v>
+        <v>7.06</v>
       </c>
       <c r="L92" t="n">
-        <v>131990000000</v>
+        <v>127880000000</v>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>745.61 -47.62</t>
+          <t>335.60 -3.17</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>200.50 94.79</t>
+          <t>263.14 23.49</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Chubb Limited</t>
+          <t>Medtronic Plc</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>324.95</v>
+        <v>99.48999999999999</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>-2.27%</t>
-        </is>
-      </c>
-      <c r="E93" s="4" t="inlineStr">
-        <is>
-          <t>3.43%</t>
-        </is>
-      </c>
-      <c r="F93" s="4" t="inlineStr">
-        <is>
-          <t>4.84%</t>
+          <t>-1.38%</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>-1.60%</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>12.42%</t>
+          <t>6.53%</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>4.11%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>21.37%</t>
+          <t>7.91%</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>61.06%</t>
+          <t>44.58%</t>
         </is>
       </c>
       <c r="K93" t="n">
-        <v>7.06</v>
+        <v>2.18</v>
       </c>
       <c r="L93" t="n">
-        <v>127880000000</v>
+        <v>127550000000</v>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>335.60 -3.17</t>
+          <t>106.33 -6.43</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>263.14 23.49</t>
+          <t>79.55 25.07</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Medtronic Plc</t>
+          <t>Bristol-Myers Squibb Co</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>99.48999999999999</v>
+        <v>60.74</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>-1.38%</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>-1.60%</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>-0.09%</t>
+          <t>1.47%</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>6.48%</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>10.12%</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>6.53%</t>
+          <t>24.34%</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>12.61%</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>7.91%</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>44.58%</t>
+          <t>8.52%</t>
+        </is>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>67.28%</t>
         </is>
       </c>
       <c r="K94" t="n">
-        <v>2.18</v>
+        <v>1.42</v>
       </c>
       <c r="L94" t="n">
-        <v>127550000000</v>
+        <v>123700000000</v>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>106.33 -6.43</t>
+          <t>63.33 -4.09</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>79.55 25.07</t>
+          <t>42.52 42.85</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Co</t>
+          <t>S&amp;P Global Inc</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>60.74</v>
+        <v>409.54</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>1.47%</t>
-        </is>
-      </c>
-      <c r="E95" s="3" t="inlineStr">
-        <is>
-          <t>6.48%</t>
-        </is>
-      </c>
-      <c r="F95" s="3" t="inlineStr">
-        <is>
-          <t>10.12%</t>
-        </is>
-      </c>
-      <c r="G95" s="3" t="inlineStr">
-        <is>
-          <t>24.34%</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>12.61%</t>
+          <t>3.11%</t>
+        </is>
+      </c>
+      <c r="E95" s="1" t="inlineStr">
+        <is>
+          <t>-15.66%</t>
+        </is>
+      </c>
+      <c r="F95" s="1" t="inlineStr">
+        <is>
+          <t>-18.98%</t>
+        </is>
+      </c>
+      <c r="G95" s="1" t="inlineStr">
+        <is>
+          <t>-20.12%</t>
+        </is>
+      </c>
+      <c r="H95" s="1" t="inlineStr">
+        <is>
+          <t>-21.63%</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>8.52%</t>
-        </is>
-      </c>
-      <c r="J95" s="4" t="inlineStr">
-        <is>
-          <t>67.28%</t>
+          <t>-24.48%</t>
+        </is>
+      </c>
+      <c r="J95" s="1" t="inlineStr">
+        <is>
+          <t>25.62%</t>
         </is>
       </c>
       <c r="K95" t="n">
-        <v>1.42</v>
+        <v>18.19</v>
       </c>
       <c r="L95" t="n">
-        <v>123700000000</v>
+        <v>122370000000</v>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>63.33 -4.09</t>
+          <t>579.05 -29.27</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>42.52 42.85</t>
+          <t>381.61 7.32</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>S&amp;P Global Inc</t>
+          <t>HCA Healthcare Inc</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>409.54</v>
+        <v>540.29</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>3.11%</t>
-        </is>
-      </c>
-      <c r="E96" s="1" t="inlineStr">
-        <is>
-          <t>-15.66%</t>
-        </is>
-      </c>
-      <c r="F96" s="1" t="inlineStr">
-        <is>
-          <t>-18.98%</t>
-        </is>
-      </c>
-      <c r="G96" s="1" t="inlineStr">
-        <is>
-          <t>-20.12%</t>
-        </is>
-      </c>
-      <c r="H96" s="1" t="inlineStr">
-        <is>
-          <t>-21.63%</t>
+          <t>0.95%</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>9.28%</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>11.64%</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>27.41%</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>15.73%</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>-24.48%</t>
-        </is>
-      </c>
-      <c r="J96" s="1" t="inlineStr">
-        <is>
-          <t>25.62%</t>
+          <t>67.83%</t>
+        </is>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>69.42%</t>
         </is>
       </c>
       <c r="K96" t="n">
-        <v>18.19</v>
+        <v>15.57</v>
       </c>
       <c r="L96" t="n">
-        <v>122370000000</v>
+        <v>120820000000</v>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>579.05 -29.27</t>
+          <t>552.90 -2.28</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>381.61 7.32</t>
+          <t>295.00 83.15</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>HCA Healthcare Inc</t>
+          <t>Progressive Corp</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>540.29</v>
+        <v>204.53</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>0.95%</t>
-        </is>
-      </c>
-      <c r="E97" s="3" t="inlineStr">
-        <is>
-          <t>9.28%</t>
-        </is>
-      </c>
-      <c r="F97" s="3" t="inlineStr">
-        <is>
-          <t>11.64%</t>
-        </is>
-      </c>
-      <c r="G97" s="3" t="inlineStr">
-        <is>
-          <t>27.41%</t>
-        </is>
-      </c>
-      <c r="H97" s="3" t="inlineStr">
-        <is>
-          <t>15.73%</t>
+          <t>-0.45%</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>-0.45%</t>
+        </is>
+      </c>
+      <c r="F97" s="1" t="inlineStr">
+        <is>
+          <t>-5.05%</t>
+        </is>
+      </c>
+      <c r="G97" s="1" t="inlineStr">
+        <is>
+          <t>-14.84%</t>
+        </is>
+      </c>
+      <c r="H97" s="1" t="inlineStr">
+        <is>
+          <t>-10.18%</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>67.83%</t>
-        </is>
-      </c>
-      <c r="J97" s="4" t="inlineStr">
-        <is>
-          <t>69.42%</t>
+          <t>-21.97%</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>44.81%</t>
         </is>
       </c>
       <c r="K97" t="n">
-        <v>15.57</v>
+        <v>5.72</v>
       </c>
       <c r="L97" t="n">
-        <v>120820000000</v>
+        <v>119940000000</v>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>552.90 -2.28</t>
+          <t>292.99 -30.19</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>295.00 83.15</t>
+          <t>197.92 3.34</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Progressive Corp</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>204.53</v>
+        <v>166.95</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>-0.45%</t>
+          <t>2.54%</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>-0.45%</t>
+          <t>-3.76%</t>
         </is>
       </c>
       <c r="F98" s="1" t="inlineStr">
         <is>
-          <t>-5.05%</t>
+          <t>-8.70%</t>
         </is>
       </c>
       <c r="G98" s="1" t="inlineStr">
         <is>
-          <t>-14.84%</t>
+          <t>-13.61%</t>
         </is>
       </c>
       <c r="H98" s="1" t="inlineStr">
         <is>
-          <t>-10.18%</t>
+          <t>-9.36%</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>-21.97%</t>
+          <t>-17.30%</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>44.81%</t>
+          <t>40.87%</t>
         </is>
       </c>
       <c r="K98" t="n">
-        <v>5.72</v>
+        <v>6.83</v>
       </c>
       <c r="L98" t="n">
-        <v>119940000000</v>
+        <v>116360000000</v>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>292.99 -30.19</t>
+          <t>223.61 -25.34</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>197.92 3.34</t>
+          <t>144.15 15.82</t>
         </is>
       </c>
     </row>
@@ -6913,7 +6913,7 @@
         <v>6.32</v>
       </c>
       <c r="L99" t="n">
-        <v>114500000000</v>
+        <v>114420000000</v>
       </c>
       <c r="M99" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>26.31</v>
       </c>
       <c r="L109" t="n">
-        <v>94340000000</v>
+        <v>94370000000</v>
       </c>
       <c r="M109" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>4.47</v>
       </c>
       <c r="L127" t="n">
-        <v>74490000000</v>
+        <v>73870000000</v>
       </c>
       <c r="M127" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>3.77</v>
       </c>
       <c r="L136" t="n">
-        <v>53460000000</v>
+        <v>55810000000</v>
       </c>
       <c r="M136" t="inlineStr">
         <is>
@@ -9437,132 +9437,132 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Autodesk Inc</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>96.04000000000001</v>
+        <v>231.22</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>0.36%</t>
-        </is>
-      </c>
-      <c r="E138" s="4" t="inlineStr">
-        <is>
-          <t>1.84%</t>
-        </is>
-      </c>
-      <c r="F138" s="3" t="inlineStr">
-        <is>
-          <t>11.70%</t>
+          <t>3.46%</t>
+        </is>
+      </c>
+      <c r="E138" s="1" t="inlineStr">
+        <is>
+          <t>-7.99%</t>
+        </is>
+      </c>
+      <c r="F138" s="1" t="inlineStr">
+        <is>
+          <t>-16.27%</t>
         </is>
       </c>
       <c r="G138" s="1" t="inlineStr">
         <is>
-          <t>-11.08%</t>
-        </is>
-      </c>
-      <c r="H138" s="3" t="inlineStr">
-        <is>
-          <t>34.12%</t>
+          <t>-21.70%</t>
+        </is>
+      </c>
+      <c r="H138" s="1" t="inlineStr">
+        <is>
+          <t>-21.89%</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>54.48%</t>
+          <t>-23.81%</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>32.60%</t>
         </is>
       </c>
       <c r="K138" t="n">
-        <v>8.68</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="L138" t="n">
-        <v>50060000000</v>
+        <v>49020000000</v>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>187.00 -48.64</t>
+          <t>329.09 -29.74</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>33.51 186.56</t>
+          <t>216.01 7.04</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Autodesk Inc</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>231.22</v>
+        <v>96.04000000000001</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>3.46%</t>
-        </is>
-      </c>
-      <c r="E139" s="1" t="inlineStr">
-        <is>
-          <t>-7.99%</t>
-        </is>
-      </c>
-      <c r="F139" s="1" t="inlineStr">
-        <is>
-          <t>-16.27%</t>
+          <t>0.36%</t>
+        </is>
+      </c>
+      <c r="E139" s="4" t="inlineStr">
+        <is>
+          <t>1.84%</t>
+        </is>
+      </c>
+      <c r="F139" s="3" t="inlineStr">
+        <is>
+          <t>11.70%</t>
         </is>
       </c>
       <c r="G139" s="1" t="inlineStr">
         <is>
-          <t>-21.70%</t>
-        </is>
-      </c>
-      <c r="H139" s="1" t="inlineStr">
-        <is>
-          <t>-21.89%</t>
+          <t>-11.08%</t>
+        </is>
+      </c>
+      <c r="H139" s="3" t="inlineStr">
+        <is>
+          <t>34.12%</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>-23.81%</t>
-        </is>
-      </c>
-      <c r="J139" s="2" t="inlineStr">
-        <is>
-          <t>32.60%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>54.48%</t>
         </is>
       </c>
       <c r="K139" t="n">
-        <v>9.710000000000001</v>
+        <v>8.68</v>
       </c>
       <c r="L139" t="n">
-        <v>49020000000</v>
+        <v>47860000000</v>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>329.09 -29.74</t>
+          <t>187.00 -48.64</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>216.01 7.04</t>
+          <t>33.51 186.56</t>
         </is>
       </c>
     </row>
@@ -9767,198 +9767,198 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences Corp</t>
+          <t>Coinbase Global Inc</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>75.87</v>
+        <v>164.32</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>-0.75%</t>
+          <t>16.46%</t>
         </is>
       </c>
       <c r="E143" s="1" t="inlineStr">
         <is>
-          <t>-6.36%</t>
+          <t>-13.50%</t>
         </is>
       </c>
       <c r="F143" s="1" t="inlineStr">
         <is>
-          <t>-8.98%</t>
-        </is>
-      </c>
-      <c r="G143" s="2" t="inlineStr">
-        <is>
-          <t>-4.66%</t>
+          <t>-27.54%</t>
+        </is>
+      </c>
+      <c r="G143" s="1" t="inlineStr">
+        <is>
+          <t>-43.27%</t>
         </is>
       </c>
       <c r="H143" s="1" t="inlineStr">
         <is>
-          <t>-11.00%</t>
+          <t>-27.34%</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>-0.17%</t>
-        </is>
-      </c>
-      <c r="J143" s="2" t="inlineStr">
-        <is>
-          <t>33.01%</t>
+          <t>-44.88%</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>37.11%</t>
         </is>
       </c>
       <c r="K143" t="n">
-        <v>2.26</v>
+        <v>13.08</v>
       </c>
       <c r="L143" t="n">
-        <v>44030000000</v>
+        <v>44240000000</v>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>87.89 -13.68</t>
+          <t>444.64 -63.04</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>65.94 15.06</t>
+          <t>139.36 17.91</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Carnival Corp</t>
+          <t>Edwards Lifesciences Corp</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>31.77</v>
+        <v>75.87</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>-2.55%</t>
-        </is>
-      </c>
-      <c r="E144" s="4" t="inlineStr">
-        <is>
-          <t>3.31%</t>
-        </is>
-      </c>
-      <c r="F144" s="3" t="inlineStr">
-        <is>
-          <t>5.83%</t>
-        </is>
-      </c>
-      <c r="G144" s="3" t="inlineStr">
-        <is>
-          <t>13.25%</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>4.03%</t>
+          <t>-0.75%</t>
+        </is>
+      </c>
+      <c r="E144" s="1" t="inlineStr">
+        <is>
+          <t>-6.36%</t>
+        </is>
+      </c>
+      <c r="F144" s="1" t="inlineStr">
+        <is>
+          <t>-8.98%</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>-4.66%</t>
+        </is>
+      </c>
+      <c r="H144" s="1" t="inlineStr">
+        <is>
+          <t>-11.00%</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>22.85%</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>53.25%</t>
+          <t>-0.17%</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>33.01%</t>
         </is>
       </c>
       <c r="K144" t="n">
-        <v>1.28</v>
+        <v>2.26</v>
       </c>
       <c r="L144" t="n">
-        <v>43930000000</v>
+        <v>44030000000</v>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>34.03 -6.64</t>
+          <t>87.89 -13.68</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>15.07 110.82</t>
+          <t>65.94 15.06</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Coinbase Global Inc</t>
+          <t>Carnival Corp</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>164.32</v>
+        <v>31.77</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>16.46%</t>
-        </is>
-      </c>
-      <c r="E145" s="1" t="inlineStr">
-        <is>
-          <t>-13.50%</t>
-        </is>
-      </c>
-      <c r="F145" s="1" t="inlineStr">
-        <is>
-          <t>-27.54%</t>
-        </is>
-      </c>
-      <c r="G145" s="1" t="inlineStr">
-        <is>
-          <t>-43.27%</t>
-        </is>
-      </c>
-      <c r="H145" s="1" t="inlineStr">
-        <is>
-          <t>-27.34%</t>
+          <t>-2.55%</t>
+        </is>
+      </c>
+      <c r="E145" s="4" t="inlineStr">
+        <is>
+          <t>3.31%</t>
+        </is>
+      </c>
+      <c r="F145" s="3" t="inlineStr">
+        <is>
+          <t>5.83%</t>
+        </is>
+      </c>
+      <c r="G145" s="3" t="inlineStr">
+        <is>
+          <t>13.25%</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>4.03%</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>-44.88%</t>
+          <t>22.85%</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>37.11%</t>
+          <t>53.25%</t>
         </is>
       </c>
       <c r="K145" t="n">
-        <v>13.08</v>
+        <v>1.28</v>
       </c>
       <c r="L145" t="n">
-        <v>43390000000</v>
+        <v>43920000000</v>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>444.64 -63.04</t>
+          <t>34.03 -6.64</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>139.36 17.91</t>
+          <t>15.07 110.82</t>
         </is>
       </c>
     </row>
@@ -10427,132 +10427,132 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Charter Communications Inc</t>
+          <t>Fiserv, Inc</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>239.09</v>
+        <v>59.36</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>0.42%</t>
-        </is>
-      </c>
-      <c r="E153" s="3" t="inlineStr">
-        <is>
-          <t>13.51%</t>
-        </is>
-      </c>
-      <c r="F153" s="3" t="inlineStr">
-        <is>
-          <t>14.79%</t>
+          <t>0.92%</t>
+        </is>
+      </c>
+      <c r="E153" s="1" t="inlineStr">
+        <is>
+          <t>-5.72%</t>
+        </is>
+      </c>
+      <c r="F153" s="1" t="inlineStr">
+        <is>
+          <t>-9.71%</t>
         </is>
       </c>
       <c r="G153" s="1" t="inlineStr">
         <is>
-          <t>-15.80%</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>14.53%</t>
+          <t>-49.76%</t>
+        </is>
+      </c>
+      <c r="H153" s="1" t="inlineStr">
+        <is>
+          <t>-11.63%</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>-33.73%</t>
-        </is>
-      </c>
-      <c r="J153" s="4" t="inlineStr">
-        <is>
-          <t>67.01%</t>
+          <t>-74.18%</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>38.12%</t>
         </is>
       </c>
       <c r="K153" t="n">
-        <v>8.81</v>
+        <v>2.26</v>
       </c>
       <c r="L153" t="n">
-        <v>33980000000</v>
+        <v>31930000000</v>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>437.06 -45.30</t>
+          <t>238.59 -75.12</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>180.38 32.55</t>
+          <t>57.79 2.72</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Fiserv, Inc</t>
+          <t>Charter Communications Inc</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>59.36</v>
+        <v>239.09</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>0.92%</t>
-        </is>
-      </c>
-      <c r="E154" s="1" t="inlineStr">
-        <is>
-          <t>-5.72%</t>
-        </is>
-      </c>
-      <c r="F154" s="1" t="inlineStr">
-        <is>
-          <t>-9.71%</t>
+          <t>0.42%</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="inlineStr">
+        <is>
+          <t>13.51%</t>
+        </is>
+      </c>
+      <c r="F154" s="3" t="inlineStr">
+        <is>
+          <t>14.79%</t>
         </is>
       </c>
       <c r="G154" s="1" t="inlineStr">
         <is>
-          <t>-49.76%</t>
-        </is>
-      </c>
-      <c r="H154" s="1" t="inlineStr">
-        <is>
-          <t>-11.63%</t>
+          <t>-15.80%</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>14.53%</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>-74.18%</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>38.12%</t>
+          <t>-33.73%</t>
+        </is>
+      </c>
+      <c r="J154" s="4" t="inlineStr">
+        <is>
+          <t>67.01%</t>
         </is>
       </c>
       <c r="K154" t="n">
-        <v>2.26</v>
+        <v>8.81</v>
       </c>
       <c r="L154" t="n">
-        <v>31930000000</v>
+        <v>30280000000</v>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>238.59 -75.12</t>
+          <t>437.06 -45.30</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>57.79 2.72</t>
+          <t>180.38 32.55</t>
         </is>
       </c>
     </row>
@@ -10939,7 +10939,7 @@
         <v>8.449999999999999</v>
       </c>
       <c r="L160" t="n">
-        <v>24680000000</v>
+        <v>24670000000</v>
       </c>
       <c r="M160" t="inlineStr">
         <is>
@@ -11087,264 +11087,264 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>DKNG</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>DraftKings Inc</t>
+          <t>Super Micro Computer Inc</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>21.76</v>
+        <v>30.54</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>-13.51%</t>
-        </is>
-      </c>
-      <c r="E163" s="1" t="inlineStr">
-        <is>
-          <t>-23.30%</t>
-        </is>
-      </c>
-      <c r="F163" s="1" t="inlineStr">
-        <is>
-          <t>-32.56%</t>
+          <t>0.36%</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>-3.22%</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>-2.66%</t>
         </is>
       </c>
       <c r="G163" s="1" t="inlineStr">
         <is>
-          <t>-41.30%</t>
-        </is>
-      </c>
-      <c r="H163" s="1" t="inlineStr">
-        <is>
-          <t>-36.85%</t>
+          <t>-26.77%</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>4.34%</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>-53.15%</t>
-        </is>
-      </c>
-      <c r="J163" s="1" t="inlineStr">
-        <is>
-          <t>21.26%</t>
+          <t>-27.77%</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>46.72%</t>
         </is>
       </c>
       <c r="K163" t="n">
-        <v>1.66</v>
+        <v>2.02</v>
       </c>
       <c r="L163" t="n">
-        <v>19380000000</v>
+        <v>18290000000</v>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>53.61 -59.41</t>
+          <t>66.44 -54.03</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>25.01 -12.99</t>
+          <t>27.60 10.65</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Super Micro Computer Inc</t>
+          <t>Illumina Inc</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>30.54</v>
+        <v>116.81</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>0.36%</t>
-        </is>
-      </c>
-      <c r="E164" s="2" t="inlineStr">
-        <is>
-          <t>-3.22%</t>
-        </is>
-      </c>
-      <c r="F164" s="2" t="inlineStr">
-        <is>
-          <t>-2.66%</t>
-        </is>
-      </c>
-      <c r="G164" s="1" t="inlineStr">
-        <is>
-          <t>-26.77%</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>4.34%</t>
+          <t>2.07%</t>
+        </is>
+      </c>
+      <c r="E164" s="1" t="inlineStr">
+        <is>
+          <t>-14.84%</t>
+        </is>
+      </c>
+      <c r="F164" s="1" t="inlineStr">
+        <is>
+          <t>-14.60%</t>
+        </is>
+      </c>
+      <c r="G164" s="3" t="inlineStr">
+        <is>
+          <t>8.29%</t>
+        </is>
+      </c>
+      <c r="H164" s="1" t="inlineStr">
+        <is>
+          <t>-10.94%</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>-27.77%</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>46.72%</t>
+          <t>14.77%</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>30.57%</t>
         </is>
       </c>
       <c r="K164" t="n">
-        <v>2.02</v>
+        <v>5.39</v>
       </c>
       <c r="L164" t="n">
-        <v>18290000000</v>
+        <v>17850000000</v>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>66.44 -54.03</t>
+          <t>155.53 -24.90</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>27.60 10.65</t>
+          <t>68.70 70.03</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Illumina Inc</t>
+          <t>Twilio Inc</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>116.81</v>
+        <v>113</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>2.35%</t>
         </is>
       </c>
       <c r="E165" s="1" t="inlineStr">
         <is>
-          <t>-14.84%</t>
+          <t>-5.70%</t>
         </is>
       </c>
       <c r="F165" s="1" t="inlineStr">
         <is>
-          <t>-14.60%</t>
-        </is>
-      </c>
-      <c r="G165" s="3" t="inlineStr">
-        <is>
-          <t>8.29%</t>
+          <t>-12.44%</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>-4.53%</t>
         </is>
       </c>
       <c r="H165" s="1" t="inlineStr">
         <is>
-          <t>-10.94%</t>
+          <t>-20.56%</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>14.77%</t>
-        </is>
-      </c>
-      <c r="J165" s="2" t="inlineStr">
-        <is>
-          <t>30.57%</t>
+          <t>-23.28%</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>40.78%</t>
         </is>
       </c>
       <c r="K165" t="n">
-        <v>5.39</v>
+        <v>6.79</v>
       </c>
       <c r="L165" t="n">
-        <v>17860000000</v>
+        <v>17130000000</v>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>155.53 -24.90</t>
+          <t>147.42 -23.35</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>68.70 70.03</t>
+          <t>77.51 45.78</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>GRAB</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Twilio Inc</t>
+          <t>Grab Holdings Limited</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>113</v>
+        <v>4.13</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>-3.28%</t>
         </is>
       </c>
       <c r="E166" s="1" t="inlineStr">
         <is>
-          <t>-5.70%</t>
+          <t>-5.56%</t>
         </is>
       </c>
       <c r="F166" s="1" t="inlineStr">
         <is>
-          <t>-12.44%</t>
-        </is>
-      </c>
-      <c r="G166" s="2" t="inlineStr">
-        <is>
-          <t>-4.53%</t>
+          <t>-13.37%</t>
+        </is>
+      </c>
+      <c r="G166" s="1" t="inlineStr">
+        <is>
+          <t>-20.15%</t>
         </is>
       </c>
       <c r="H166" s="1" t="inlineStr">
         <is>
-          <t>-20.56%</t>
+          <t>-17.23%</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>-23.28%</t>
+          <t>-16.73%</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>40.78%</t>
+          <t>35.21%</t>
         </is>
       </c>
       <c r="K166" t="n">
-        <v>6.79</v>
+        <v>0.2</v>
       </c>
       <c r="L166" t="n">
-        <v>17130000000</v>
+        <v>16870000000</v>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>147.42 -23.35</t>
+          <t>6.62 -37.61</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>77.51 45.78</t>
+          <t>3.36 22.92</t>
         </is>
       </c>
     </row>
@@ -11417,660 +11417,660 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>GRAB</t>
+          <t>AFRM</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Grab Holdings Limited</t>
+          <t>Affirm Holdings Inc</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>4.13</v>
+        <v>49.81</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>-3.28%</t>
+          <t>0.10%</t>
         </is>
       </c>
       <c r="E168" s="1" t="inlineStr">
         <is>
-          <t>-5.56%</t>
+          <t>-21.18%</t>
         </is>
       </c>
       <c r="F168" s="1" t="inlineStr">
         <is>
-          <t>-13.37%</t>
+          <t>-28.63%</t>
         </is>
       </c>
       <c r="G168" s="1" t="inlineStr">
         <is>
-          <t>-20.15%</t>
+          <t>-28.20%</t>
         </is>
       </c>
       <c r="H168" s="1" t="inlineStr">
         <is>
-          <t>-17.23%</t>
+          <t>-33.08%</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>-16.73%</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>35.21%</t>
+          <t>-37.17%</t>
+        </is>
+      </c>
+      <c r="J168" s="1" t="inlineStr">
+        <is>
+          <t>24.36%</t>
         </is>
       </c>
       <c r="K168" t="n">
-        <v>0.2</v>
+        <v>4.14</v>
       </c>
       <c r="L168" t="n">
-        <v>16870000000</v>
+        <v>16590000000</v>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>6.62 -37.61</t>
+          <t>100.00 -50.19</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>3.36 22.92</t>
+          <t>30.90 61.19</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>AFRM</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Affirm Holdings Inc</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>49.81</v>
+        <v>42.23</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>0.10%</t>
-        </is>
-      </c>
-      <c r="E169" s="1" t="inlineStr">
-        <is>
-          <t>-21.18%</t>
-        </is>
-      </c>
-      <c r="F169" s="1" t="inlineStr">
-        <is>
-          <t>-28.63%</t>
-        </is>
-      </c>
-      <c r="G169" s="1" t="inlineStr">
-        <is>
-          <t>-28.20%</t>
-        </is>
-      </c>
-      <c r="H169" s="1" t="inlineStr">
-        <is>
-          <t>-33.08%</t>
+          <t>5.29%</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>-4.14%</t>
+        </is>
+      </c>
+      <c r="F169" s="3" t="inlineStr">
+        <is>
+          <t>14.93%</t>
+        </is>
+      </c>
+      <c r="G169" s="3" t="inlineStr">
+        <is>
+          <t>43.87%</t>
+        </is>
+      </c>
+      <c r="H169" s="3" t="inlineStr">
+        <is>
+          <t>43.20%</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>-37.17%</t>
-        </is>
-      </c>
-      <c r="J169" s="1" t="inlineStr">
-        <is>
-          <t>24.36%</t>
+          <t>32.30%</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>53.99%</t>
         </is>
       </c>
       <c r="K169" t="n">
-        <v>4.14</v>
+        <v>3.23</v>
       </c>
       <c r="L169" t="n">
-        <v>16590000000</v>
+        <v>16500000000</v>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>100.00 -50.19</t>
+          <t>55.20 -23.50</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>30.90 61.19</t>
+          <t>22.28 89.54</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>Circle Internet Group Inc</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>42.23</v>
+        <v>60.04</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>5.29%</t>
-        </is>
-      </c>
-      <c r="E170" s="2" t="inlineStr">
-        <is>
-          <t>-4.14%</t>
-        </is>
-      </c>
-      <c r="F170" s="3" t="inlineStr">
-        <is>
-          <t>14.93%</t>
-        </is>
-      </c>
-      <c r="G170" s="3" t="inlineStr">
-        <is>
-          <t>43.87%</t>
-        </is>
-      </c>
-      <c r="H170" s="3" t="inlineStr">
-        <is>
-          <t>43.20%</t>
+          <t>6.02%</t>
+        </is>
+      </c>
+      <c r="E170" s="1" t="inlineStr">
+        <is>
+          <t>-6.45%</t>
+        </is>
+      </c>
+      <c r="F170" s="1" t="inlineStr">
+        <is>
+          <t>-20.59%</t>
+        </is>
+      </c>
+      <c r="G170" s="1" t="inlineStr">
+        <is>
+          <t>-51.40%</t>
+        </is>
+      </c>
+      <c r="H170" s="1" t="inlineStr">
+        <is>
+          <t>-24.29%</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>32.30%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>53.99%</t>
+          <t>40.63%</t>
         </is>
       </c>
       <c r="K170" t="n">
-        <v>3.23</v>
+        <v>5.01</v>
       </c>
       <c r="L170" t="n">
-        <v>16500000000</v>
+        <v>14140000000</v>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>55.20 -23.50</t>
+          <t>298.99 -79.92</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>22.28 89.54</t>
+          <t>49.90 20.32</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>CRCL</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Circle Internet Group Inc</t>
+          <t>IREN Ltd</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>60.04</v>
+        <v>42.22</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>6.02%</t>
+          <t>5.47%</t>
         </is>
       </c>
       <c r="E171" s="1" t="inlineStr">
         <is>
-          <t>-6.45%</t>
+          <t>-16.51%</t>
         </is>
       </c>
       <c r="F171" s="1" t="inlineStr">
         <is>
-          <t>-20.59%</t>
-        </is>
-      </c>
-      <c r="G171" s="1" t="inlineStr">
-        <is>
-          <t>-51.40%</t>
-        </is>
-      </c>
-      <c r="H171" s="1" t="inlineStr">
-        <is>
-          <t>-24.29%</t>
+          <t>-8.67%</t>
+        </is>
+      </c>
+      <c r="G171" s="3" t="inlineStr">
+        <is>
+          <t>25.43%</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>11.78%</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>222.78%</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>40.63%</t>
+          <t>43.28%</t>
         </is>
       </c>
       <c r="K171" t="n">
-        <v>5.01</v>
+        <v>5.36</v>
       </c>
       <c r="L171" t="n">
-        <v>14140000000</v>
+        <v>14010000000</v>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>298.99 -79.92</t>
+          <t>76.87 -45.08</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>49.90 20.32</t>
+          <t>5.12 723.80</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>ROKU</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>IREN Ltd</t>
+          <t>Roku Inc</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>42.22</v>
+        <v>90.06</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>5.47%</t>
+          <t>8.60%</t>
         </is>
       </c>
       <c r="E172" s="1" t="inlineStr">
         <is>
-          <t>-16.51%</t>
+          <t>-6.51%</t>
         </is>
       </c>
       <c r="F172" s="1" t="inlineStr">
         <is>
-          <t>-8.67%</t>
-        </is>
-      </c>
-      <c r="G172" s="3" t="inlineStr">
-        <is>
-          <t>25.43%</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>11.78%</t>
+          <t>-12.77%</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>-2.74%</t>
+        </is>
+      </c>
+      <c r="H172" s="1" t="inlineStr">
+        <is>
+          <t>-16.99%</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>222.78%</t>
+          <t>3.76%</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>43.28%</t>
+          <t>40.72%</t>
         </is>
       </c>
       <c r="K172" t="n">
-        <v>5.36</v>
+        <v>5.54</v>
       </c>
       <c r="L172" t="n">
-        <v>14010000000</v>
+        <v>13310000000</v>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>76.87 -45.08</t>
+          <t>116.66 -22.80</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>5.12 723.80</t>
+          <t>52.43 71.77</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ROKU</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Roku Inc</t>
+          <t>AeroVironment Inc</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>90.06</v>
+        <v>243.87</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>8.60%</t>
+          <t>3.72%</t>
         </is>
       </c>
       <c r="E173" s="1" t="inlineStr">
         <is>
-          <t>-6.51%</t>
+          <t>-14.74%</t>
         </is>
       </c>
       <c r="F173" s="1" t="inlineStr">
         <is>
-          <t>-12.77%</t>
-        </is>
-      </c>
-      <c r="G173" s="2" t="inlineStr">
-        <is>
-          <t>-2.74%</t>
-        </is>
-      </c>
-      <c r="H173" s="1" t="inlineStr">
-        <is>
-          <t>-16.99%</t>
+          <t>-14.07%</t>
+        </is>
+      </c>
+      <c r="G173" s="1" t="inlineStr">
+        <is>
+          <t>-8.89%</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>0.82%</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>3.76%</t>
+          <t>51.15%</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>40.72%</t>
+          <t>39.73%</t>
         </is>
       </c>
       <c r="K173" t="n">
-        <v>5.54</v>
+        <v>21.64</v>
       </c>
       <c r="L173" t="n">
-        <v>13310000000</v>
+        <v>12180000000</v>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>116.66 -22.80</t>
+          <t>417.86 -41.64</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>52.43 71.77</t>
+          <t>102.25 138.50</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>AeroVironment Inc</t>
+          <t>IonQ Inc</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>243.87</v>
+        <v>34.11</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>3.72%</t>
+          <t>8.98%</t>
         </is>
       </c>
       <c r="E174" s="1" t="inlineStr">
         <is>
-          <t>-14.74%</t>
+          <t>-15.96%</t>
         </is>
       </c>
       <c r="F174" s="1" t="inlineStr">
         <is>
-          <t>-14.07%</t>
+          <t>-25.80%</t>
         </is>
       </c>
       <c r="G174" s="1" t="inlineStr">
         <is>
-          <t>-8.89%</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>0.82%</t>
+          <t>-27.99%</t>
+        </is>
+      </c>
+      <c r="H174" s="1" t="inlineStr">
+        <is>
+          <t>-23.98%</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>51.15%</t>
+          <t>-11.75%</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>39.73%</t>
+          <t>38.08%</t>
         </is>
       </c>
       <c r="K174" t="n">
-        <v>21.64</v>
+        <v>3.72</v>
       </c>
       <c r="L174" t="n">
-        <v>12180000000</v>
+        <v>12080000000</v>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>417.86 -41.64</t>
+          <t>84.64 -59.70</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>102.25 138.50</t>
+          <t>17.88 90.77</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>TXRH</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>IonQ Inc</t>
+          <t>Texas Roadhouse Inc</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>34.11</v>
+        <v>180.9</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
+          <t>-0.56%</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>-2.87%</t>
+        </is>
+      </c>
+      <c r="F175" s="4" t="inlineStr">
+        <is>
+          <t>1.30%</t>
+        </is>
+      </c>
+      <c r="G175" s="4" t="inlineStr">
+        <is>
+          <t>1.83%</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
           <t>8.98%</t>
         </is>
       </c>
-      <c r="E175" s="1" t="inlineStr">
-        <is>
-          <t>-15.96%</t>
-        </is>
-      </c>
-      <c r="F175" s="1" t="inlineStr">
-        <is>
-          <t>-25.80%</t>
-        </is>
-      </c>
-      <c r="G175" s="1" t="inlineStr">
-        <is>
-          <t>-27.99%</t>
-        </is>
-      </c>
-      <c r="H175" s="1" t="inlineStr">
-        <is>
-          <t>-23.98%</t>
-        </is>
-      </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>-11.75%</t>
+          <t>5.52%</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>38.08%</t>
+          <t>45.93%</t>
         </is>
       </c>
       <c r="K175" t="n">
-        <v>3.72</v>
+        <v>4.94</v>
       </c>
       <c r="L175" t="n">
-        <v>12080000000</v>
+        <v>11970000000</v>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>84.64 -59.70</t>
+          <t>199.99 -9.55</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>17.88 90.77</t>
+          <t>148.73 21.63</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>TXRH</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Texas Roadhouse Inc</t>
+          <t>Celsius Holdings Inc</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>180.9</v>
+        <v>44.68</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>-0.56%</t>
-        </is>
-      </c>
-      <c r="E176" s="2" t="inlineStr">
-        <is>
-          <t>-2.87%</t>
-        </is>
-      </c>
-      <c r="F176" s="4" t="inlineStr">
-        <is>
-          <t>1.30%</t>
-        </is>
-      </c>
-      <c r="G176" s="4" t="inlineStr">
-        <is>
-          <t>1.83%</t>
+          <t>0.65%</t>
+        </is>
+      </c>
+      <c r="E176" s="1" t="inlineStr">
+        <is>
+          <t>-12.87%</t>
+        </is>
+      </c>
+      <c r="F176" s="1" t="inlineStr">
+        <is>
+          <t>-7.46%</t>
+        </is>
+      </c>
+      <c r="G176" s="1" t="inlineStr">
+        <is>
+          <t>-8.51%</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>8.98%</t>
+          <t>-2.32%</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>5.52%</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>45.93%</t>
+          <t>97.18%</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>34.48%</t>
         </is>
       </c>
       <c r="K176" t="n">
-        <v>4.94</v>
+        <v>2.17</v>
       </c>
       <c r="L176" t="n">
-        <v>11970000000</v>
+        <v>11520000000</v>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>199.99 -9.55</t>
+          <t>66.74 -33.05</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>148.73 21.63</t>
+          <t>21.31 109.67</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>DKNG</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Celsius Holdings Inc</t>
+          <t>DraftKings Inc</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>44.68</v>
+        <v>21.76</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>0.65%</t>
+          <t>-13.51%</t>
         </is>
       </c>
       <c r="E177" s="1" t="inlineStr">
         <is>
-          <t>-12.87%</t>
+          <t>-23.30%</t>
         </is>
       </c>
       <c r="F177" s="1" t="inlineStr">
         <is>
-          <t>-7.46%</t>
+          <t>-32.56%</t>
         </is>
       </c>
       <c r="G177" s="1" t="inlineStr">
         <is>
-          <t>-8.51%</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>-2.32%</t>
+          <t>-41.30%</t>
+        </is>
+      </c>
+      <c r="H177" s="1" t="inlineStr">
+        <is>
+          <t>-36.85%</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>97.18%</t>
-        </is>
-      </c>
-      <c r="J177" s="2" t="inlineStr">
-        <is>
-          <t>34.48%</t>
+          <t>-53.15%</t>
+        </is>
+      </c>
+      <c r="J177" s="1" t="inlineStr">
+        <is>
+          <t>21.26%</t>
         </is>
       </c>
       <c r="K177" t="n">
-        <v>2.17</v>
+        <v>1.66</v>
       </c>
       <c r="L177" t="n">
-        <v>11520000000</v>
+        <v>10830000000</v>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>66.74 -33.05</t>
+          <t>53.61 -59.41</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>21.31 109.67</t>
+          <t>25.01 -12.99</t>
         </is>
       </c>
     </row>
@@ -12127,7 +12127,7 @@
         <v>3.3</v>
       </c>
       <c r="L178" t="n">
-        <v>10510000000</v>
+        <v>10520000000</v>
       </c>
       <c r="M178" t="inlineStr">
         <is>
@@ -12341,198 +12341,198 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>BROS</t>
+          <t>MBLY</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Dutch Bros Inc</t>
+          <t>Mobileye Global Inc</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>53.2</v>
+        <v>9.19</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>4.68%</t>
-        </is>
-      </c>
-      <c r="E182" s="1" t="inlineStr">
-        <is>
-          <t>-6.25%</t>
+          <t>-2.23%</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>-3.59%</t>
         </is>
       </c>
       <c r="F182" s="1" t="inlineStr">
         <is>
-          <t>-11.20%</t>
+          <t>-11.85%</t>
         </is>
       </c>
       <c r="G182" s="1" t="inlineStr">
         <is>
-          <t>-13.59%</t>
+          <t>-32.73%</t>
         </is>
       </c>
       <c r="H182" s="1" t="inlineStr">
         <is>
-          <t>-13.10%</t>
+          <t>-11.97%</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>-36.32%</t>
+          <t>-47.31%</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>40.73%</t>
+          <t>42.44%</t>
         </is>
       </c>
       <c r="K182" t="n">
-        <v>3.28</v>
+        <v>0.53</v>
       </c>
       <c r="L182" t="n">
-        <v>8750000000</v>
+        <v>7730000000</v>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>86.88 -38.77</t>
+          <t>20.18 -54.46</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>47.16 12.81</t>
+          <t>8.32 10.46</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>MBLY</t>
+          <t>PRMB</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Mobileye Global Inc</t>
+          <t>Primo Brands Corp</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>9.19</v>
+        <v>18.76</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>-2.23%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>-3.59%</t>
-        </is>
-      </c>
-      <c r="F183" s="1" t="inlineStr">
-        <is>
-          <t>-11.85%</t>
+          <t>-1.43%</t>
+        </is>
+      </c>
+      <c r="F183" s="3" t="inlineStr">
+        <is>
+          <t>6.52%</t>
         </is>
       </c>
       <c r="G183" s="1" t="inlineStr">
         <is>
-          <t>-32.73%</t>
-        </is>
-      </c>
-      <c r="H183" s="1" t="inlineStr">
-        <is>
-          <t>-11.97%</t>
+          <t>-20.30%</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>14.74%</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>-47.31%</t>
+          <t>-44.08%</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>42.44%</t>
+          <t>52.19%</t>
         </is>
       </c>
       <c r="K183" t="n">
-        <v>0.53</v>
+        <v>0.61</v>
       </c>
       <c r="L183" t="n">
-        <v>7720000000</v>
+        <v>6860000000</v>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>20.18 -54.46</t>
+          <t>35.85 -47.66</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>8.32 10.46</t>
+          <t>14.36 30.64</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>PRMB</t>
+          <t>BROS</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Primo Brands Corp</t>
+          <t>Dutch Bros Inc</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>18.76</v>
+        <v>53.2</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>-0.79%</t>
-        </is>
-      </c>
-      <c r="E184" s="2" t="inlineStr">
-        <is>
-          <t>-1.43%</t>
-        </is>
-      </c>
-      <c r="F184" s="3" t="inlineStr">
-        <is>
-          <t>6.52%</t>
+          <t>4.68%</t>
+        </is>
+      </c>
+      <c r="E184" s="1" t="inlineStr">
+        <is>
+          <t>-6.25%</t>
+        </is>
+      </c>
+      <c r="F184" s="1" t="inlineStr">
+        <is>
+          <t>-11.20%</t>
         </is>
       </c>
       <c r="G184" s="1" t="inlineStr">
         <is>
-          <t>-20.30%</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>14.74%</t>
+          <t>-13.59%</t>
+        </is>
+      </c>
+      <c r="H184" s="1" t="inlineStr">
+        <is>
+          <t>-13.10%</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>-44.08%</t>
+          <t>-36.32%</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>52.19%</t>
+          <t>40.73%</t>
         </is>
       </c>
       <c r="K184" t="n">
-        <v>0.61</v>
+        <v>3.28</v>
       </c>
       <c r="L184" t="n">
-        <v>6860000000</v>
+        <v>6760000000</v>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>35.85 -47.66</t>
+          <t>86.88 -38.77</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>14.36 30.64</t>
+          <t>47.16 12.81</t>
         </is>
       </c>
     </row>
@@ -12655,7 +12655,7 @@
         <v>3.02</v>
       </c>
       <c r="L186" t="n">
-        <v>5090000000</v>
+        <v>5060000000</v>
       </c>
       <c r="M186" t="inlineStr">
         <is>
@@ -12919,7 +12919,7 @@
         <v>1.76</v>
       </c>
       <c r="L190" t="n">
-        <v>4330000000</v>
+        <v>4050000000</v>
       </c>
       <c r="M190" t="inlineStr">
         <is>
@@ -12985,7 +12985,7 @@
         <v>1.21</v>
       </c>
       <c r="L191" t="n">
-        <v>4190000000</v>
+        <v>3930000000</v>
       </c>
       <c r="M191" t="inlineStr">
         <is>
@@ -13199,264 +13199,264 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>FLNC</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Fluence Energy Inc</t>
+          <t>Upstart Holdings Inc</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>18.46</v>
+        <v>30.68</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>5.85%</t>
+          <t>1.62%</t>
         </is>
       </c>
       <c r="E195" s="1" t="inlineStr">
         <is>
-          <t>-26.80%</t>
+          <t>-23.90%</t>
         </is>
       </c>
       <c r="F195" s="1" t="inlineStr">
         <is>
-          <t>-20.28%</t>
-        </is>
-      </c>
-      <c r="G195" s="3" t="inlineStr">
-        <is>
-          <t>37.43%</t>
+          <t>-31.25%</t>
+        </is>
+      </c>
+      <c r="G195" s="1" t="inlineStr">
+        <is>
+          <t>-43.91%</t>
         </is>
       </c>
       <c r="H195" s="1" t="inlineStr">
         <is>
-          <t>-6.67%</t>
+          <t>-29.84%</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>198.71%</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>36.87%</t>
+          <t>-63.55%</t>
+        </is>
+      </c>
+      <c r="J195" s="1" t="inlineStr">
+        <is>
+          <t>28.59%</t>
         </is>
       </c>
       <c r="K195" t="n">
-        <v>2.91</v>
+        <v>2.78</v>
       </c>
       <c r="L195" t="n">
-        <v>3400000000</v>
+        <v>3010000000</v>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>33.51 -44.91</t>
+          <t>96.43 -68.18</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>3.46 433.53</t>
+          <t>29.91 2.57</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>MARA</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Upstart Holdings Inc</t>
+          <t>MARA Holdings Inc</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>30.68</v>
+        <v>7.92</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>9.24%</t>
         </is>
       </c>
       <c r="E196" s="1" t="inlineStr">
         <is>
-          <t>-23.90%</t>
+          <t>-13.53%</t>
         </is>
       </c>
       <c r="F196" s="1" t="inlineStr">
         <is>
-          <t>-31.25%</t>
+          <t>-21.25%</t>
         </is>
       </c>
       <c r="G196" s="1" t="inlineStr">
         <is>
-          <t>-43.91%</t>
+          <t>-46.24%</t>
         </is>
       </c>
       <c r="H196" s="1" t="inlineStr">
         <is>
-          <t>-29.84%</t>
+          <t>-11.80%</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>-63.55%</t>
-        </is>
-      </c>
-      <c r="J196" s="1" t="inlineStr">
-        <is>
-          <t>28.59%</t>
+          <t>-53.16%</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>40.39%</t>
         </is>
       </c>
       <c r="K196" t="n">
-        <v>2.78</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L196" t="n">
-        <v>3010000000</v>
+        <v>3000000000</v>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>96.43 -68.18</t>
+          <t>23.45 -66.23</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>29.91 2.57</t>
+          <t>6.66 18.92</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>MARA</t>
+          <t>FSLY</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>MARA Holdings Inc</t>
+          <t>Fastly Inc</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>7.92</v>
+        <v>18.26</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>9.24%</t>
-        </is>
-      </c>
-      <c r="E197" s="1" t="inlineStr">
-        <is>
-          <t>-13.53%</t>
-        </is>
-      </c>
-      <c r="F197" s="1" t="inlineStr">
-        <is>
-          <t>-21.25%</t>
-        </is>
-      </c>
-      <c r="G197" s="1" t="inlineStr">
-        <is>
-          <t>-46.24%</t>
-        </is>
-      </c>
-      <c r="H197" s="1" t="inlineStr">
-        <is>
-          <t>-11.80%</t>
+          <t>13.84%</t>
+        </is>
+      </c>
+      <c r="E197" s="3" t="inlineStr">
+        <is>
+          <t>83.95%</t>
+        </is>
+      </c>
+      <c r="F197" s="3" t="inlineStr">
+        <is>
+          <t>80.44%</t>
+        </is>
+      </c>
+      <c r="G197" s="3" t="inlineStr">
+        <is>
+          <t>114.27%</t>
+        </is>
+      </c>
+      <c r="H197" s="3" t="inlineStr">
+        <is>
+          <t>79.37%</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>-53.16%</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>40.39%</t>
+          <t>129.11%</t>
+        </is>
+      </c>
+      <c r="J197" s="3" t="inlineStr">
+        <is>
+          <t>85.08%</t>
         </is>
       </c>
       <c r="K197" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.25</v>
       </c>
       <c r="L197" t="n">
-        <v>3000000000</v>
+        <v>2730000000</v>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>23.45 -66.23</t>
+          <t>17.86 2.24</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>6.66 18.92</t>
+          <t>4.65 292.69</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>FSLY</t>
+          <t>FLNC</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Fastly Inc</t>
+          <t>Fluence Energy Inc</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>18.26</v>
+        <v>18.46</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>13.84%</t>
-        </is>
-      </c>
-      <c r="E198" s="3" t="inlineStr">
-        <is>
-          <t>83.95%</t>
-        </is>
-      </c>
-      <c r="F198" s="3" t="inlineStr">
-        <is>
-          <t>80.44%</t>
+          <t>5.85%</t>
+        </is>
+      </c>
+      <c r="E198" s="1" t="inlineStr">
+        <is>
+          <t>-26.80%</t>
+        </is>
+      </c>
+      <c r="F198" s="1" t="inlineStr">
+        <is>
+          <t>-20.28%</t>
         </is>
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>114.27%</t>
-        </is>
-      </c>
-      <c r="H198" s="3" t="inlineStr">
-        <is>
-          <t>79.37%</t>
+          <t>37.43%</t>
+        </is>
+      </c>
+      <c r="H198" s="1" t="inlineStr">
+        <is>
+          <t>-6.67%</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>129.11%</t>
-        </is>
-      </c>
-      <c r="J198" s="3" t="inlineStr">
-        <is>
-          <t>85.08%</t>
+          <t>198.71%</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>36.87%</t>
         </is>
       </c>
       <c r="K198" t="n">
-        <v>1.25</v>
+        <v>2.91</v>
       </c>
       <c r="L198" t="n">
-        <v>2730000000</v>
+        <v>2440000000</v>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>17.86 2.24</t>
+          <t>33.51 -44.91</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>4.65 292.69</t>
+          <t>3.46 433.53</t>
         </is>
       </c>
     </row>
@@ -13777,7 +13777,7 @@
         <v>0.31</v>
       </c>
       <c r="L203" t="n">
-        <v>825250000</v>
+        <v>825240000</v>
       </c>
       <c r="M203" t="inlineStr">
         <is>
@@ -13909,7 +13909,7 @@
         <v>1.68</v>
       </c>
       <c r="L205" t="n">
-        <v>439560000</v>
+        <v>439610000</v>
       </c>
       <c r="M205" t="inlineStr">
         <is>

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -846,7 +846,7 @@
         <v>9.27</v>
       </c>
       <c r="L7" t="n">
-        <v>3804440000000</v>
+        <v>3809880000000</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>7.33</v>
       </c>
       <c r="L14" t="n">
-        <v>1075150000000</v>
+        <v>1074370000000</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>16.16</v>
       </c>
       <c r="L44" t="n">
-        <v>297950000000</v>
+        <v>297910000000</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>38.33</v>
       </c>
       <c r="L87" t="n">
-        <v>141490000000</v>
+        <v>141270000000</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>1.27</v>
       </c>
       <c r="L144" t="n">
-        <v>44300000000</v>
+        <v>44180000000</v>
       </c>
       <c r="M144" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>2.33</v>
       </c>
       <c r="L153" t="n">
-        <v>33060000000</v>
+        <v>32870000000</v>
       </c>
       <c r="M153" t="inlineStr">
         <is>

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -846,7 +846,7 @@
         <v>8.84</v>
       </c>
       <c r="L7" t="n">
-        <v>3768920000000</v>
+        <v>3769570000000</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>7.4</v>
       </c>
       <c r="L14" t="n">
-        <v>1088950000000</v>
+        <v>1089120000000</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -3505,6 +3505,11 @@
           <t>MS</t>
         </is>
       </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Morgan Stanley</t>
+        </is>
+      </c>
       <c r="C48" t="n">
         <v>166.51</v>
       </c>
@@ -4619,132 +4624,132 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc</t>
+          <t>NextEra Energy Inc</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>521.11</v>
+        <v>93.77</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0.19%</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>-2.02%</t>
-        </is>
-      </c>
-      <c r="F65" s="1" t="inlineStr">
-        <is>
-          <t>-9.18%</t>
-        </is>
-      </c>
-      <c r="G65" s="4" t="inlineStr">
-        <is>
-          <t>2.47%</t>
-        </is>
-      </c>
-      <c r="H65" s="1" t="inlineStr">
-        <is>
-          <t>-10.07%</t>
+          <t>1.93%</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>2.62%</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>9.33%</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>19.16%</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>16.80%</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>35.15%</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>36.50%</t>
+          <t>61.90%</t>
         </is>
       </c>
       <c r="K65" t="n">
-        <v>13.77</v>
+        <v>2.2</v>
       </c>
       <c r="L65" t="n">
-        <v>195790000000</v>
+        <v>195370000000</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>643.99 -19.08</t>
+          <t>95.91 -2.23</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>385.46 35.19</t>
+          <t>61.72 51.93</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NextEra Energy Inc</t>
+          <t>Thermo Fisher Scientific Inc</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>93.77</v>
+        <v>521.11</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>1.93%</t>
-        </is>
-      </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>2.62%</t>
-        </is>
-      </c>
-      <c r="F66" s="3" t="inlineStr">
-        <is>
-          <t>9.33%</t>
-        </is>
-      </c>
-      <c r="G66" s="3" t="inlineStr">
-        <is>
-          <t>19.16%</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>16.80%</t>
+          <t>0.19%</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>-2.02%</t>
+        </is>
+      </c>
+      <c r="F66" s="1" t="inlineStr">
+        <is>
+          <t>-9.18%</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>2.47%</t>
+        </is>
+      </c>
+      <c r="H66" s="1" t="inlineStr">
+        <is>
+          <t>-10.07%</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>35.15%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>61.90%</t>
+          <t>36.50%</t>
         </is>
       </c>
       <c r="K66" t="n">
-        <v>2.2</v>
+        <v>13.77</v>
       </c>
       <c r="L66" t="n">
-        <v>195370000000</v>
+        <v>193580000000</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>95.91 -2.23</t>
+          <t>643.99 -19.08</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>61.72 51.93</t>
+          <t>385.46 35.19</t>
         </is>
       </c>
     </row>
@@ -5395,7 +5400,7 @@
         <v>19.16</v>
       </c>
       <c r="L76" t="n">
-        <v>170700000000</v>
+        <v>170090000000</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
@@ -7045,7 +7050,7 @@
         <v>22.67</v>
       </c>
       <c r="L101" t="n">
-        <v>113820000000</v>
+        <v>113120000000</v>
       </c>
       <c r="M101" t="inlineStr">
         <is>
@@ -8513,132 +8518,132 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Cigna Group</t>
+          <t>SLB Ltd</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>289.82</v>
+        <v>51.34</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>1.70%</t>
-        </is>
-      </c>
-      <c r="F124" s="4" t="inlineStr">
-        <is>
-          <t>3.64%</t>
-        </is>
-      </c>
-      <c r="G124" s="2" t="inlineStr">
-        <is>
-          <t>-0.47%</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>5.30%</t>
+          <t>1.40%</t>
+        </is>
+      </c>
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t>10.93%</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="inlineStr">
+        <is>
+          <t>35.44%</t>
+        </is>
+      </c>
+      <c r="H124" s="3" t="inlineStr">
+        <is>
+          <t>33.77%</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>-4.32%</t>
+          <t>25.49%</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>56.48%</t>
+          <t>60.46%</t>
         </is>
       </c>
       <c r="K124" t="n">
-        <v>7.28</v>
+        <v>1.49</v>
       </c>
       <c r="L124" t="n">
-        <v>77420000000</v>
+        <v>76770000000</v>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>350.00 -17.19</t>
+          <t>52.40 -2.01</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>239.51 21.01</t>
+          <t>31.11 65.03</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>SLB Ltd</t>
+          <t>Cigna Group</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>51.34</v>
+        <v>289.82</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>1.40%</t>
-        </is>
-      </c>
-      <c r="F125" s="3" t="inlineStr">
-        <is>
-          <t>10.93%</t>
-        </is>
-      </c>
-      <c r="G125" s="3" t="inlineStr">
-        <is>
-          <t>35.44%</t>
-        </is>
-      </c>
-      <c r="H125" s="3" t="inlineStr">
-        <is>
-          <t>33.77%</t>
+          <t>1.70%</t>
+        </is>
+      </c>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t>3.64%</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>-0.47%</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>5.30%</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>25.49%</t>
+          <t>-4.32%</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>60.46%</t>
+          <t>56.48%</t>
         </is>
       </c>
       <c r="K125" t="n">
-        <v>1.49</v>
+        <v>7.28</v>
       </c>
       <c r="L125" t="n">
-        <v>76770000000</v>
+        <v>76380000000</v>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>52.40 -2.01</t>
+          <t>350.00 -17.19</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>31.11 65.03</t>
+          <t>239.51 21.01</t>
         </is>
       </c>
     </row>
@@ -8909,132 +8914,132 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Apollo Global Management Inc</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>104.6</v>
+        <v>172.19</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>-8.57%</t>
-        </is>
-      </c>
-      <c r="E130" s="1" t="inlineStr">
-        <is>
-          <t>-15.74%</t>
+          <t>-1.41%</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>-3.13%</t>
         </is>
       </c>
       <c r="F130" s="1" t="inlineStr">
         <is>
-          <t>-22.99%</t>
+          <t>-7.33%</t>
         </is>
       </c>
       <c r="G130" s="1" t="inlineStr">
         <is>
-          <t>-23.13%</t>
+          <t>-12.54%</t>
         </is>
       </c>
       <c r="H130" s="1" t="inlineStr">
         <is>
-          <t>-27.74%</t>
+          <t>-12.66%</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>-29.06%</t>
-        </is>
-      </c>
-      <c r="J130" s="1" t="inlineStr">
-        <is>
-          <t>24.76%</t>
+          <t>22.36%</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>45.13%</t>
         </is>
       </c>
       <c r="K130" t="n">
-        <v>5.78</v>
+        <v>11.81</v>
       </c>
       <c r="L130" t="n">
-        <v>60480000000</v>
+        <v>60640000000</v>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>157.28 -33.49</t>
+          <t>260.00 -33.77</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>102.58 1.97</t>
+          <t>89.42 92.56</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>Apollo Global Management Inc</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>172.19</v>
+        <v>104.6</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>-1.41%</t>
-        </is>
-      </c>
-      <c r="E131" s="2" t="inlineStr">
-        <is>
-          <t>-3.13%</t>
+          <t>-8.57%</t>
+        </is>
+      </c>
+      <c r="E131" s="1" t="inlineStr">
+        <is>
+          <t>-15.74%</t>
         </is>
       </c>
       <c r="F131" s="1" t="inlineStr">
         <is>
-          <t>-7.33%</t>
+          <t>-22.99%</t>
         </is>
       </c>
       <c r="G131" s="1" t="inlineStr">
         <is>
-          <t>-12.54%</t>
+          <t>-23.13%</t>
         </is>
       </c>
       <c r="H131" s="1" t="inlineStr">
         <is>
-          <t>-12.66%</t>
+          <t>-27.74%</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>22.36%</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>45.13%</t>
+          <t>-29.06%</t>
+        </is>
+      </c>
+      <c r="J131" s="1" t="inlineStr">
+        <is>
+          <t>24.76%</t>
         </is>
       </c>
       <c r="K131" t="n">
-        <v>11.81</v>
+        <v>5.78</v>
       </c>
       <c r="L131" t="n">
-        <v>60240000000</v>
+        <v>60480000000</v>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>260.00 -33.77</t>
+          <t>157.28 -33.49</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>89.42 92.56</t>
+          <t>102.58 1.97</t>
         </is>
       </c>
     </row>
@@ -9817,7 +9822,7 @@
         <v>1.33</v>
       </c>
       <c r="L143" t="n">
-        <v>43540000000</v>
+        <v>43620000000</v>
       </c>
       <c r="M143" t="inlineStr">
         <is>
@@ -10229,132 +10234,132 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Block Inc</t>
+          <t>Rocket Lab Corp</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>63.7</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>16.82%</t>
-        </is>
-      </c>
-      <c r="E150" s="3" t="inlineStr">
-        <is>
-          <t>16.49%</t>
-        </is>
-      </c>
-      <c r="F150" s="4" t="inlineStr">
-        <is>
-          <t>3.58%</t>
-        </is>
-      </c>
-      <c r="G150" s="1" t="inlineStr">
-        <is>
-          <t>-6.43%</t>
+          <t>-4.89%</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>-4.16%</t>
+        </is>
+      </c>
+      <c r="F150" s="1" t="inlineStr">
+        <is>
+          <t>-9.93%</t>
+        </is>
+      </c>
+      <c r="G150" s="3" t="inlineStr">
+        <is>
+          <t>30.62%</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>-2.14%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>-0.90%</t>
+          <t>248.46%</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>62.19%</t>
+          <t>44.60%</t>
         </is>
       </c>
       <c r="K150" t="n">
-        <v>3.23</v>
+        <v>5.99</v>
       </c>
       <c r="L150" t="n">
-        <v>38710000000</v>
+        <v>39210000000</v>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>82.50 -22.79</t>
+          <t>99.58 -30.61</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>44.27 43.89</t>
+          <t>14.71 369.75</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Rocket Lab Corp</t>
+          <t>Block Inc</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>69.09999999999999</v>
+        <v>63.7</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>-4.89%</t>
-        </is>
-      </c>
-      <c r="E151" s="2" t="inlineStr">
-        <is>
-          <t>-4.16%</t>
-        </is>
-      </c>
-      <c r="F151" s="1" t="inlineStr">
-        <is>
-          <t>-9.93%</t>
-        </is>
-      </c>
-      <c r="G151" s="3" t="inlineStr">
-        <is>
-          <t>30.62%</t>
+          <t>16.82%</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>16.49%</t>
+        </is>
+      </c>
+      <c r="F151" s="4" t="inlineStr">
+        <is>
+          <t>3.58%</t>
+        </is>
+      </c>
+      <c r="G151" s="1" t="inlineStr">
+        <is>
+          <t>-6.43%</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>-2.14%</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>248.46%</t>
+          <t>-0.90%</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>44.60%</t>
+          <t>62.19%</t>
         </is>
       </c>
       <c r="K151" t="n">
-        <v>5.99</v>
+        <v>3.23</v>
       </c>
       <c r="L151" t="n">
-        <v>36910000000</v>
+        <v>38160000000</v>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>99.58 -30.61</t>
+          <t>82.50 -22.79</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>14.71 369.75</t>
+          <t>44.27 43.89</t>
         </is>
       </c>
     </row>
@@ -10741,7 +10746,7 @@
         <v>11.04</v>
       </c>
       <c r="L157" t="n">
-        <v>23440000000</v>
+        <v>23630000000</v>
       </c>
       <c r="M157" t="inlineStr">
         <is>
@@ -12193,7 +12198,7 @@
         <v>2.78</v>
       </c>
       <c r="L179" t="n">
-        <v>10700000000</v>
+        <v>10710000000</v>
       </c>
       <c r="M179" t="inlineStr">
         <is>
@@ -13777,7 +13782,7 @@
         <v>0.31</v>
       </c>
       <c r="L203" t="n">
-        <v>933510000</v>
+        <v>938370000</v>
       </c>
       <c r="M203" t="inlineStr">
         <is>
@@ -13843,7 +13848,7 @@
         <v>0.54</v>
       </c>
       <c r="L204" t="n">
-        <v>668080000</v>
+        <v>668090000</v>
       </c>
       <c r="M204" t="inlineStr">
         <is>

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -846,7 +846,7 @@
         <v>8.25</v>
       </c>
       <c r="L7" t="n">
-        <v>3608340000000</v>
+        <v>3610000000000</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>9.26</v>
       </c>
       <c r="L14" t="n">
-        <v>1076540000000</v>
+        <v>1076120000000</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10416,7 +10416,7 @@
         <v>1.53</v>
       </c>
       <c r="L152" t="n">
-        <v>34640000000</v>
+        <v>34600000000</v>
       </c>
       <c r="M152" t="inlineStr">
         <is>
@@ -12198,7 +12198,7 @@
         <v>2.72</v>
       </c>
       <c r="L179" t="n">
-        <v>11030000000</v>
+        <v>11020000000</v>
       </c>
       <c r="M179" t="inlineStr">
         <is>

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -780,7 +780,7 @@
         <v>5.97</v>
       </c>
       <c r="L6" t="n">
-        <v>4380080000000</v>
+        <v>4380070000000</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>7.96</v>
       </c>
       <c r="L7" t="n">
-        <v>3649010000000</v>
+        <v>3652220000000</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>8.16</v>
       </c>
       <c r="L14" t="n">
-        <v>1056540000000</v>
+        <v>1057050000000</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>30.48</v>
       </c>
       <c r="L16" t="n">
-        <v>929280000000</v>
+        <v>930720000000</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         <v>6.25</v>
       </c>
       <c r="L71" t="n">
-        <v>173140000000</v>
+        <v>173700000000</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         <v>1.59</v>
       </c>
       <c r="L152" t="n">
-        <v>33290000000</v>
+        <v>33230000000</v>
       </c>
       <c r="M152" t="inlineStr">
         <is>
@@ -12193,7 +12193,7 @@
         <v>2.71</v>
       </c>
       <c r="L179" t="n">
-        <v>10270000000</v>
+        <v>10260000000</v>
       </c>
       <c r="M179" t="inlineStr">
         <is>
@@ -13772,7 +13772,7 @@
         <v>0.3</v>
       </c>
       <c r="L203" t="n">
-        <v>957980000</v>
+        <v>957990000</v>
       </c>
       <c r="M203" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
         <v>2.04</v>
       </c>
       <c r="L204" t="n">
-        <v>752260000</v>
+        <v>793350000</v>
       </c>
       <c r="M204" t="inlineStr">
         <is>

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -846,7 +846,7 @@
         <v>7.38</v>
       </c>
       <c r="L7" t="n">
-        <v>3623570000000</v>
+        <v>3629180000000</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>7.61</v>
       </c>
       <c r="L14" t="n">
-        <v>1037830000000</v>
+        <v>1037190000000</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>25.87</v>
       </c>
       <c r="L22" t="n">
-        <v>475980000000</v>
+        <v>476920000000</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>9.359999999999999</v>
       </c>
       <c r="L94" t="n">
-        <v>123060000000</v>
+        <v>122780000000</v>
       </c>
       <c r="M94" t="inlineStr">
         <is>
@@ -10416,7 +10416,7 @@
         <v>1.4</v>
       </c>
       <c r="L152" t="n">
-        <v>33310000000</v>
+        <v>33440000000</v>
       </c>
       <c r="M152" t="inlineStr">
         <is>
@@ -12132,7 +12132,7 @@
         <v>2.51</v>
       </c>
       <c r="L178" t="n">
-        <v>10520000000</v>
+        <v>10530000000</v>
       </c>
       <c r="M178" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
         <v>0.65</v>
       </c>
       <c r="L188" t="n">
-        <v>4820000000</v>
+        <v>4810000000</v>
       </c>
       <c r="M188" t="inlineStr">
         <is>

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -445,7 +445,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
@@ -583,7 +583,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P 500 ETF Trust</t>
+          <t>Units of undivided interest in SPDR Trust Series 1</t>
         </is>
       </c>
       <c r="H3" s="1" t="inlineStr">
@@ -846,7 +846,7 @@
         <v>7.62</v>
       </c>
       <c r="L7" t="n">
-        <v>3312840000000</v>
+        <v>3315540000000</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>7.26</v>
       </c>
       <c r="L14" t="n">
-        <v>1010490000000</v>
+        <v>1011180000000</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10350,7 +10350,7 @@
         <v>1.36</v>
       </c>
       <c r="L151" t="n">
-        <v>33510000000</v>
+        <v>33530000000</v>
       </c>
       <c r="M151" t="inlineStr">
         <is>
@@ -12066,7 +12066,7 @@
         <v>2.52</v>
       </c>
       <c r="L177" t="n">
-        <v>9710000000</v>
+        <v>9700000000</v>
       </c>
       <c r="M177" t="inlineStr">
         <is>

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -846,7 +846,7 @@
         <v>8.130000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>3578640000000</v>
+        <v>3570810000000</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>6.79</v>
       </c>
       <c r="L14" t="n">
-        <v>1028290000000</v>
+        <v>1029190000000</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -3505,11 +3505,6 @@
           <t>GS</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Goldman Sachs Group, Inc</t>
-        </is>
-      </c>
       <c r="C48" t="n">
         <v>863.04</v>
       </c>
@@ -10350,7 +10345,7 @@
         <v>1.37</v>
       </c>
       <c r="L151" t="n">
-        <v>35490000000</v>
+        <v>35520000000</v>
       </c>
       <c r="M151" t="inlineStr">
         <is>

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SPDR S&amp;P 500 ETF TRUST</t>
+          <t>SPDR S&amp;P 500 ETF Trust</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -846,7 +846,7 @@
         <v>8.19</v>
       </c>
       <c r="L7" t="n">
-        <v>3833350000000</v>
+        <v>3829390000000</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>6.75</v>
       </c>
       <c r="L14" t="n">
-        <v>1034590000000</v>
+        <v>1034620000000</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>1.34</v>
       </c>
       <c r="L34" t="n">
-        <v>333180000000</v>
+        <v>333440000000</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>26.87</v>
       </c>
       <c r="L48" t="n">
-        <v>269390000000</v>
+        <v>267800000000</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>12.02</v>
       </c>
       <c r="L76" t="n">
-        <v>160030000000</v>
+        <v>160050000000</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>16.63</v>
       </c>
       <c r="L82" t="n">
-        <v>141200000000</v>
+        <v>141440000000</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         <v>3.08</v>
       </c>
       <c r="L90" t="n">
-        <v>130510000000</v>
+        <v>130880000000</v>
       </c>
       <c r="M90" t="inlineStr">
         <is>
@@ -6913,7 +6913,7 @@
         <v>4.73</v>
       </c>
       <c r="L99" t="n">
-        <v>113740000000</v>
+        <v>113560000000</v>
       </c>
       <c r="M99" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>13.6</v>
       </c>
       <c r="L103" t="n">
-        <v>110800000000</v>
+        <v>110770000000</v>
       </c>
       <c r="M103" t="inlineStr">
         <is>
@@ -7655,132 +7655,132 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange Inc</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>160.6</v>
+        <v>225.35</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>-0.85%</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t>0.61%</t>
-        </is>
-      </c>
-      <c r="F111" s="3" t="inlineStr">
-        <is>
-          <t>-0.24%</t>
-        </is>
-      </c>
-      <c r="G111" s="3" t="inlineStr">
-        <is>
-          <t>-3.48%</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>-0.84%</t>
+          <t>-2.00%</t>
+        </is>
+      </c>
+      <c r="E111" s="1" t="inlineStr">
+        <is>
+          <t>-6.93%</t>
+        </is>
+      </c>
+      <c r="F111" s="1" t="inlineStr">
+        <is>
+          <t>-12.79%</t>
+        </is>
+      </c>
+      <c r="G111" s="1" t="inlineStr">
+        <is>
+          <t>-30.48%</t>
+        </is>
+      </c>
+      <c r="H111" s="1" t="inlineStr">
+        <is>
+          <t>-35.61%</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>3.49%</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>49.63%</t>
+          <t>-35.62%</t>
+        </is>
+      </c>
+      <c r="J111" s="1" t="inlineStr">
+        <is>
+          <t>29.19%</t>
         </is>
       </c>
       <c r="K111" t="n">
-        <v>4.01</v>
+        <v>8.66</v>
       </c>
       <c r="L111" t="n">
-        <v>91200000000</v>
+        <v>91090000000</v>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>189.35 -15.18</t>
+          <t>422.95 -46.72</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>143.17 12.17</t>
+          <t>227.70 -1.03</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>Intercontinental Exchange Inc</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>225.35</v>
+        <v>160.6</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>-2.00%</t>
-        </is>
-      </c>
-      <c r="E112" s="1" t="inlineStr">
-        <is>
-          <t>-6.93%</t>
-        </is>
-      </c>
-      <c r="F112" s="1" t="inlineStr">
-        <is>
-          <t>-12.79%</t>
-        </is>
-      </c>
-      <c r="G112" s="1" t="inlineStr">
-        <is>
-          <t>-30.48%</t>
-        </is>
-      </c>
-      <c r="H112" s="1" t="inlineStr">
-        <is>
-          <t>-35.61%</t>
+          <t>-0.85%</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>0.61%</t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t>-0.24%</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="inlineStr">
+        <is>
+          <t>-3.48%</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>-35.62%</t>
-        </is>
-      </c>
-      <c r="J112" s="1" t="inlineStr">
-        <is>
-          <t>29.19%</t>
+          <t>3.49%</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>49.63%</t>
         </is>
       </c>
       <c r="K112" t="n">
-        <v>8.66</v>
+        <v>4.01</v>
       </c>
       <c r="L112" t="n">
-        <v>91090000000</v>
+        <v>90970000000</v>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>422.95 -46.72</t>
+          <t>189.35 -15.18</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>227.70 -1.03</t>
+          <t>143.17 12.17</t>
         </is>
       </c>
     </row>
@@ -7903,7 +7903,7 @@
         <v>1.27</v>
       </c>
       <c r="L114" t="n">
-        <v>86480000000</v>
+        <v>86400000000</v>
       </c>
       <c r="M114" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         <v>1.92</v>
       </c>
       <c r="L120" t="n">
-        <v>77640000000</v>
+        <v>77940000000</v>
       </c>
       <c r="M120" t="inlineStr">
         <is>
@@ -10213,7 +10213,7 @@
         <v>1.44</v>
       </c>
       <c r="L149" t="n">
-        <v>38680000000</v>
+        <v>38720000000</v>
       </c>
       <c r="M149" t="inlineStr">
         <is>

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -846,7 +846,7 @@
         <v>7.9</v>
       </c>
       <c r="L7" t="n">
-        <v>4127790000000</v>
+        <v>4120900000000</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>Microsoft Corp</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -978,7 +978,7 @@
         <v>6.59</v>
       </c>
       <c r="L9" t="n">
-        <v>2689740000000</v>
+        <v>2694590000000</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>6.63</v>
       </c>
       <c r="L14" t="n">
-        <v>1023090000000</v>
+        <v>1022920000000</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Home Depot, Inc</t>
+          <t>Home Depot Inc</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cisco Systems, Inc</t>
+          <t>Cisco Systems Inc</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -3309,7 +3309,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Toyota Motor Corporation ADR</t>
+          <t>Toyota Motor Corp ADR</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Goldman Sachs Group, Inc</t>
+          <t>Goldman Sachs Group Inc</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -3750,7 +3750,7 @@
         <v>2.18</v>
       </c>
       <c r="L51" t="n">
-        <v>246080000000</v>
+        <v>245980000000</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>3.19</v>
       </c>
       <c r="L60" t="n">
-        <v>215530000000</v>
+        <v>215500000000</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>AT&amp;T, Inc</t>
+          <t>AT&amp;T Inc</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Arm Holdings plc. ADR</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Gilead Sciences, Inc</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Qualcomm, Inc</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -6010,7 +6010,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Corning, Inc</t>
+          <t>Corning Inc</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Lowe's Cos., Inc</t>
+          <t>Lowe's Cos. Inc</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Spotify Technology S.A</t>
+          <t>Spotify Technology SA</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -7573,7 +7573,7 @@
         <v>1.41</v>
       </c>
       <c r="L109" t="n">
-        <v>107290000000</v>
+        <v>107250000000</v>
       </c>
       <c r="M109" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>United Parcel Service, Inc</t>
+          <t>United Parcel Service Inc</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -8101,7 +8101,7 @@
         <v>4.72</v>
       </c>
       <c r="L117" t="n">
-        <v>85110000000</v>
+        <v>84700000000</v>
       </c>
       <c r="M117" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals, Inc</t>
+          <t>Regeneron Pharmaceuticals Inc</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Nike, Inc</t>
+          <t>Nike Inc</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Ferrari N.V</t>
+          <t>Ferrari NV</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -9817,7 +9817,7 @@
         <v>5.56</v>
       </c>
       <c r="L143" t="n">
-        <v>48290000000</v>
+        <v>48830000000</v>
       </c>
       <c r="M143" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         <v>1.51</v>
       </c>
       <c r="L151" t="n">
-        <v>40500000000</v>
+        <v>40520000000</v>
       </c>
       <c r="M151" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Nebius Group N.V</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -10432,7 +10432,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Fiserv, Inc</t>
+          <t>Fiserv Inc</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Estee Lauder Cos., Inc</t>
+          <t>Estee Lauder Cos. Inc</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -11401,7 +11401,7 @@
         <v>8.75</v>
       </c>
       <c r="L167" t="n">
-        <v>20440000000</v>
+        <v>20460000000</v>
       </c>
       <c r="M167" t="inlineStr">
         <is>
@@ -12011,132 +12011,132 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>TXRH</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Zillow Group Inc</t>
+          <t>Texas Roadhouse Inc</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>46.86</v>
+        <v>165.08</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>6.31%</t>
-        </is>
-      </c>
-      <c r="E177" s="2" t="inlineStr">
-        <is>
-          <t>11.12%</t>
-        </is>
-      </c>
-      <c r="F177" s="2" t="inlineStr">
-        <is>
-          <t>5.43%</t>
+          <t>3.21%</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="inlineStr">
+        <is>
+          <t>0.44%</t>
+        </is>
+      </c>
+      <c r="F177" s="4" t="inlineStr">
+        <is>
+          <t>-4.57%</t>
         </is>
       </c>
       <c r="G177" s="1" t="inlineStr">
         <is>
-          <t>-30.78%</t>
-        </is>
-      </c>
-      <c r="H177" s="1" t="inlineStr">
-        <is>
-          <t>-31.31%</t>
+          <t>-5.20%</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>-25.11%</t>
+          <t>1.97%</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>61.33%</t>
+          <t>47.62%</t>
         </is>
       </c>
       <c r="K177" t="n">
-        <v>2.24</v>
+        <v>4.56</v>
       </c>
       <c r="L177" t="n">
-        <v>11240000000</v>
+        <v>10880000000</v>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>93.88 -50.09</t>
+          <t>199.99 -17.46</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>39.05 20.00</t>
+          <t>156.00 5.82</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>TXRH</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Texas Roadhouse Inc</t>
+          <t>Zillow Group Inc</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>165.08</v>
+        <v>46.86</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>3.21%</t>
-        </is>
-      </c>
-      <c r="E178" s="3" t="inlineStr">
-        <is>
-          <t>0.44%</t>
-        </is>
-      </c>
-      <c r="F178" s="4" t="inlineStr">
-        <is>
-          <t>-4.57%</t>
+          <t>6.31%</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>11.12%</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>5.43%</t>
         </is>
       </c>
       <c r="G178" s="1" t="inlineStr">
         <is>
-          <t>-5.20%</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>-0.55%</t>
+          <t>-30.78%</t>
+        </is>
+      </c>
+      <c r="H178" s="1" t="inlineStr">
+        <is>
+          <t>-31.31%</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>-25.11%</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>47.62%</t>
+          <t>61.33%</t>
         </is>
       </c>
       <c r="K178" t="n">
-        <v>4.56</v>
+        <v>2.24</v>
       </c>
       <c r="L178" t="n">
-        <v>10880000000</v>
+        <v>10740000000</v>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>199.99 -17.46</t>
+          <t>93.88 -50.09</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>156.00 5.82</t>
+          <t>39.05 20.00</t>
         </is>
       </c>
     </row>
@@ -13067,7 +13067,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>NuScale Power Corporation</t>
+          <t>NuScale Power Corp</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -13112,7 +13112,7 @@
         <v>1.03</v>
       </c>
       <c r="L193" t="n">
-        <v>4280000000</v>
+        <v>4340000000</v>
       </c>
       <c r="M193" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
         <v>0.52</v>
       </c>
       <c r="L204" t="n">
-        <v>676110000</v>
+        <v>676100000</v>
       </c>
       <c r="M204" t="inlineStr">
         <is>

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -846,7 +846,7 @@
         <v>7.63</v>
       </c>
       <c r="L7" t="n">
-        <v>4148740000000</v>
+        <v>4154900000000</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>19.42</v>
       </c>
       <c r="L12" t="n">
-        <v>1707530000000</v>
+        <v>1713510000000</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>14.94</v>
       </c>
       <c r="L13" t="n">
-        <v>1412040000000</v>
+        <v>1413280000000</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>6.35</v>
       </c>
       <c r="L15" t="n">
-        <v>1011910000000</v>
+        <v>1012140000000</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -2644,132 +2644,132 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Home Depot Inc</t>
+          <t>Lam Research Corp</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>335.89</v>
+        <v>267.78</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-1.26%</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>0.21%</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>-3.80%</t>
-        </is>
-      </c>
-      <c r="G35" s="1" t="inlineStr">
-        <is>
-          <t>-9.64%</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>-2.39%</t>
+          <t>3.57%</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>8.72%</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>13.83%</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>57.15%</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>56.43%</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>-6.60%</t>
+          <t>277.69%</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>46.35%</t>
+          <t>61.20%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>8.449999999999999</v>
+        <v>11.83</v>
       </c>
       <c r="L35" t="n">
-        <v>334560000000</v>
+        <v>334880000000</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>426.75 -21.29</t>
+          <t>273.50 -2.09</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>315.31 6.53</t>
+          <t>67.55 296.42</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Lam Research Corp</t>
+          <t>Home Depot Inc</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>267.78</v>
+        <v>335.89</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3.57%</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>8.72%</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>13.83%</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>57.15%</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>56.43%</t>
+          <t>-1.26%</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>0.21%</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>-3.80%</t>
+        </is>
+      </c>
+      <c r="G36" s="1" t="inlineStr">
+        <is>
+          <t>-9.64%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-2.39%</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>277.69%</t>
+          <t>-6.60%</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>61.20%</t>
+          <t>46.35%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>11.83</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>334400000000</v>
+        <v>334560000000</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>273.50 -2.09</t>
+          <t>426.75 -21.29</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>67.55 296.42</t>
+          <t>315.31 6.53</t>
         </is>
       </c>
     </row>
@@ -4207,7 +4207,7 @@
         <v>8.68</v>
       </c>
       <c r="L58" t="n">
-        <v>217610000000</v>
+        <v>218030000000</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>8.77</v>
       </c>
       <c r="L59" t="n">
-        <v>215390000000</v>
+        <v>214310000000</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -5213,792 +5213,792 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Salesforce Inc</t>
+          <t>Shopify Inc</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>178.16</v>
+        <v>125.83</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2.80%</t>
-        </is>
-      </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>-1.14%</t>
-        </is>
-      </c>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>-4.84%</t>
+          <t>1.29%</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>3.80%</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>3.14%</t>
         </is>
       </c>
       <c r="G74" s="1" t="inlineStr">
         <is>
-          <t>-22.72%</t>
+          <t>-11.27%</t>
         </is>
       </c>
       <c r="H74" s="1" t="inlineStr">
         <is>
-          <t>-32.75%</t>
+          <t>-21.83%</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>-32.69%</t>
+          <t>32.29%</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>45.49%</t>
+          <t>52.41%</t>
         </is>
       </c>
       <c r="K74" t="n">
-        <v>7.99</v>
+        <v>6.34</v>
       </c>
       <c r="L74" t="n">
-        <v>164440000000</v>
+        <v>164100000000</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>296.05 -39.82</t>
+          <t>182.19 -30.93</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>163.52 8.95</t>
+          <t>88.14 42.76</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Shopify Inc</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>125.83</v>
+        <v>130.4</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>1.29%</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>3.80%</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>3.14%</t>
-        </is>
-      </c>
-      <c r="G75" s="1" t="inlineStr">
-        <is>
-          <t>-11.27%</t>
-        </is>
-      </c>
-      <c r="H75" s="1" t="inlineStr">
-        <is>
-          <t>-21.83%</t>
+          <t>-2.42%</t>
+        </is>
+      </c>
+      <c r="E75" s="1" t="inlineStr">
+        <is>
+          <t>-5.27%</t>
+        </is>
+      </c>
+      <c r="F75" s="1" t="inlineStr">
+        <is>
+          <t>-8.61%</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>3.22%</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>6.24%</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>32.29%</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>52.41%</t>
+          <t>22.85%</t>
+        </is>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>30.58%</t>
         </is>
       </c>
       <c r="K75" t="n">
-        <v>6.34</v>
+        <v>3.17</v>
       </c>
       <c r="L75" t="n">
-        <v>164100000000</v>
+        <v>161860000000</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>182.19 -30.93</t>
+          <t>157.29 -17.10</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>88.14 42.76</t>
+          <t>93.37 39.66</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>130.4</v>
+        <v>148.85</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>-2.42%</t>
-        </is>
-      </c>
-      <c r="E76" s="1" t="inlineStr">
-        <is>
-          <t>-5.27%</t>
-        </is>
-      </c>
-      <c r="F76" s="1" t="inlineStr">
-        <is>
-          <t>-8.61%</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>3.22%</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>6.24%</t>
+          <t>11.12%</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>13.20%</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>10.61%</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>-4.92%</t>
+        </is>
+      </c>
+      <c r="H76" s="1" t="inlineStr">
+        <is>
+          <t>-12.98%</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>22.85%</t>
-        </is>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>30.58%</t>
+          <t>1.11%</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>73.20%</t>
         </is>
       </c>
       <c r="K76" t="n">
-        <v>3.17</v>
+        <v>4.4</v>
       </c>
       <c r="L76" t="n">
-        <v>161860000000</v>
+        <v>158820000000</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>157.29 -17.10</t>
+          <t>205.95 -27.73</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>93.37 39.66</t>
+          <t>121.99 22.02</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>148.85</v>
+        <v>91.13</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>11.12%</t>
-        </is>
-      </c>
-      <c r="E77" s="3" t="inlineStr">
-        <is>
-          <t>13.20%</t>
-        </is>
-      </c>
-      <c r="F77" s="3" t="inlineStr">
-        <is>
-          <t>10.61%</t>
-        </is>
-      </c>
-      <c r="G77" s="4" t="inlineStr">
-        <is>
-          <t>-4.92%</t>
+          <t>-1.46%</t>
+        </is>
+      </c>
+      <c r="E77" s="1" t="inlineStr">
+        <is>
+          <t>-8.14%</t>
+        </is>
+      </c>
+      <c r="F77" s="1" t="inlineStr">
+        <is>
+          <t>-14.14%</t>
+        </is>
+      </c>
+      <c r="G77" s="1" t="inlineStr">
+        <is>
+          <t>-25.04%</t>
         </is>
       </c>
       <c r="H77" s="1" t="inlineStr">
         <is>
-          <t>-12.98%</t>
+          <t>-27.26%</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>1.11%</t>
-        </is>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>73.20%</t>
+          <t>-29.56%</t>
+        </is>
+      </c>
+      <c r="J77" s="1" t="inlineStr">
+        <is>
+          <t>24.54%</t>
         </is>
       </c>
       <c r="K77" t="n">
-        <v>4.4</v>
+        <v>2.43</v>
       </c>
       <c r="L77" t="n">
-        <v>158820000000</v>
+        <v>158720000000</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>205.95 -27.73</t>
+          <t>139.06 -34.47</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>121.99 22.02</t>
+          <t>90.72 0.45</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Charles Schwab Corp</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>91.13</v>
+        <v>88.5</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>-1.46%</t>
+          <t>-0.47%</t>
         </is>
       </c>
       <c r="E78" s="1" t="inlineStr">
         <is>
-          <t>-8.14%</t>
+          <t>-5.61%</t>
         </is>
       </c>
       <c r="F78" s="1" t="inlineStr">
         <is>
-          <t>-14.14%</t>
+          <t>-5.97%</t>
         </is>
       </c>
       <c r="G78" s="1" t="inlineStr">
         <is>
-          <t>-25.04%</t>
+          <t>-7.69%</t>
         </is>
       </c>
       <c r="H78" s="1" t="inlineStr">
         <is>
-          <t>-27.26%</t>
+          <t>-11.42%</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>-29.56%</t>
-        </is>
-      </c>
-      <c r="J78" s="1" t="inlineStr">
-        <is>
-          <t>24.54%</t>
+          <t>11.49%</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>36.67%</t>
         </is>
       </c>
       <c r="K78" t="n">
-        <v>2.43</v>
+        <v>2.76</v>
       </c>
       <c r="L78" t="n">
-        <v>158720000000</v>
+        <v>153820000000</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>139.06 -34.47</t>
+          <t>107.50 -17.67</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>90.72 0.45</t>
+          <t>77.51 14.17</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Charles Schwab Corp</t>
+          <t>Uber Technologies Inc</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>88.5</v>
+        <v>74.64</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>-0.47%</t>
-        </is>
-      </c>
-      <c r="E79" s="1" t="inlineStr">
-        <is>
-          <t>-5.61%</t>
-        </is>
-      </c>
-      <c r="F79" s="1" t="inlineStr">
-        <is>
-          <t>-5.97%</t>
+          <t>-0.08%</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>1.62%</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>1.36%</t>
         </is>
       </c>
       <c r="G79" s="1" t="inlineStr">
         <is>
-          <t>-7.69%</t>
+          <t>-12.87%</t>
         </is>
       </c>
       <c r="H79" s="1" t="inlineStr">
         <is>
-          <t>-11.42%</t>
+          <t>-8.65%</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>11.49%</t>
+          <t>-4.43%</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>36.67%</t>
+          <t>51.08%</t>
         </is>
       </c>
       <c r="K79" t="n">
-        <v>2.76</v>
+        <v>2.41</v>
       </c>
       <c r="L79" t="n">
-        <v>153820000000</v>
+        <v>152030000000</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>107.50 -17.67</t>
+          <t>101.99 -26.82</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>77.51 14.17</t>
+          <t>68.46 9.03</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Uber Technologies Inc</t>
+          <t>Deere &amp; Co</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>74.64</v>
+        <v>562.64</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>-0.08%</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>1.62%</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>1.36%</t>
-        </is>
-      </c>
-      <c r="G80" s="1" t="inlineStr">
-        <is>
-          <t>-12.87%</t>
-        </is>
-      </c>
-      <c r="H80" s="1" t="inlineStr">
-        <is>
-          <t>-8.65%</t>
+          <t>-4.95%</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>-3.67%</t>
+        </is>
+      </c>
+      <c r="F80" s="1" t="inlineStr">
+        <is>
+          <t>-5.33%</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>9.34%</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>20.85%</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>-4.43%</t>
+          <t>21.13%</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>51.08%</t>
+          <t>41.62%</t>
         </is>
       </c>
       <c r="K80" t="n">
-        <v>2.41</v>
+        <v>16.4</v>
       </c>
       <c r="L80" t="n">
-        <v>152030000000</v>
+        <v>151970000000</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>101.99 -26.82</t>
+          <t>674.19 -16.55</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>68.46 9.03</t>
+          <t>433.00 29.94</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Deere &amp; Co</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>562.64</v>
+        <v>448.29</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>-4.95%</t>
-        </is>
-      </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>-3.67%</t>
-        </is>
-      </c>
-      <c r="F81" s="1" t="inlineStr">
-        <is>
-          <t>-5.33%</t>
-        </is>
-      </c>
-      <c r="G81" s="3" t="inlineStr">
-        <is>
-          <t>9.34%</t>
-        </is>
-      </c>
-      <c r="H81" s="3" t="inlineStr">
-        <is>
-          <t>20.85%</t>
+          <t>-1.29%</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>5.24%</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>3.52%</t>
+        </is>
+      </c>
+      <c r="G81" s="1" t="inlineStr">
+        <is>
+          <t>-14.31%</t>
+        </is>
+      </c>
+      <c r="H81" s="1" t="inlineStr">
+        <is>
+          <t>-33.47%</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>21.13%</t>
+          <t>67.35%</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>41.62%</t>
+          <t>51.42%</t>
         </is>
       </c>
       <c r="K81" t="n">
-        <v>16.4</v>
+        <v>27.72</v>
       </c>
       <c r="L81" t="n">
-        <v>151970000000</v>
+        <v>151200000000</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>674.19 -16.55</t>
+          <t>745.61 -39.88</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>433.00 29.94</t>
+          <t>246.00 82.23</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>Corning Inc</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>448.29</v>
+        <v>175.89</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>3.77%</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>5.24%</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>3.52%</t>
-        </is>
-      </c>
-      <c r="G82" s="1" t="inlineStr">
-        <is>
-          <t>-14.31%</t>
-        </is>
-      </c>
-      <c r="H82" s="1" t="inlineStr">
-        <is>
-          <t>-33.47%</t>
+          <t>10.47%</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>20.34%</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>80.23%</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>100.88%</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>67.35%</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>51.42%</t>
+          <t>300.84%</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>68.41%</t>
         </is>
       </c>
       <c r="K82" t="n">
-        <v>27.72</v>
+        <v>8.67</v>
       </c>
       <c r="L82" t="n">
-        <v>151200000000</v>
+        <v>151090000000</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>745.61 -39.88</t>
+          <t>176.75 -0.49</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>246.00 82.23</t>
+          <t>42.00 318.79</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Corning Inc</t>
+          <t>Blackstone Inc</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>175.89</v>
+        <v>121.65</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>3.77%</t>
-        </is>
-      </c>
-      <c r="E83" s="3" t="inlineStr">
-        <is>
-          <t>10.47%</t>
-        </is>
-      </c>
-      <c r="F83" s="3" t="inlineStr">
-        <is>
-          <t>20.34%</t>
-        </is>
-      </c>
-      <c r="G83" s="3" t="inlineStr">
-        <is>
-          <t>80.23%</t>
-        </is>
-      </c>
-      <c r="H83" s="3" t="inlineStr">
-        <is>
-          <t>100.88%</t>
+          <t>-0.56%</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>1.24%</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>4.00%</t>
+        </is>
+      </c>
+      <c r="G83" s="1" t="inlineStr">
+        <is>
+          <t>-18.26%</t>
+        </is>
+      </c>
+      <c r="H83" s="1" t="inlineStr">
+        <is>
+          <t>-21.08%</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>300.84%</t>
-        </is>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>68.41%</t>
+          <t>-9.59%</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>51.37%</t>
         </is>
       </c>
       <c r="K83" t="n">
-        <v>8.67</v>
+        <v>4.87</v>
       </c>
       <c r="L83" t="n">
-        <v>151090000000</v>
+        <v>148510000000</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>176.75 -0.49</t>
+          <t>190.09 -36.00</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>42.00 318.79</t>
+          <t>101.73 19.58</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Blackstone Inc</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>121.65</v>
+        <v>989.9</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>-0.56%</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>1.24%</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>4.00%</t>
-        </is>
-      </c>
-      <c r="G84" s="1" t="inlineStr">
-        <is>
-          <t>-18.26%</t>
-        </is>
-      </c>
-      <c r="H84" s="1" t="inlineStr">
-        <is>
-          <t>-21.08%</t>
+          <t>6.16%</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>20.10%</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>38.28%</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>202.73%</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>317.01%</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>-9.59%</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>51.37%</t>
+          <t>2965.65%</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>67.89%</t>
         </is>
       </c>
       <c r="K84" t="n">
-        <v>4.87</v>
+        <v>60.07</v>
       </c>
       <c r="L84" t="n">
-        <v>148510000000</v>
+        <v>146110000000</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>190.09 -36.00</t>
+          <t>981.06 0.90</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>101.73 19.58</t>
+          <t>30.31 3165.92</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>Salesforce Inc</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>989.9</v>
+        <v>178.16</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>6.16%</t>
-        </is>
-      </c>
-      <c r="E85" s="3" t="inlineStr">
-        <is>
-          <t>20.10%</t>
-        </is>
-      </c>
-      <c r="F85" s="3" t="inlineStr">
-        <is>
-          <t>38.28%</t>
-        </is>
-      </c>
-      <c r="G85" s="3" t="inlineStr">
-        <is>
-          <t>202.73%</t>
-        </is>
-      </c>
-      <c r="H85" s="3" t="inlineStr">
-        <is>
-          <t>317.01%</t>
+          <t>2.80%</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>-1.14%</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>-4.84%</t>
+        </is>
+      </c>
+      <c r="G85" s="1" t="inlineStr">
+        <is>
+          <t>-22.72%</t>
+        </is>
+      </c>
+      <c r="H85" s="1" t="inlineStr">
+        <is>
+          <t>-32.75%</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2965.65%</t>
-        </is>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>67.89%</t>
+          <t>-32.69%</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>45.49%</t>
         </is>
       </c>
       <c r="K85" t="n">
-        <v>60.07</v>
+        <v>7.99</v>
       </c>
       <c r="L85" t="n">
-        <v>146110000000</v>
+        <v>145740000000</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>981.06 0.90</t>
+          <t>296.05 -39.82</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>30.31 3165.92</t>
+          <t>163.52 8.95</t>
         </is>
       </c>
     </row>
@@ -6913,7 +6913,7 @@
         <v>18.01</v>
       </c>
       <c r="L99" t="n">
-        <v>118330000000</v>
+        <v>118380000000</v>
       </c>
       <c r="M99" t="inlineStr">
         <is>
@@ -8579,132 +8579,132 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Apollo Global Management Inc</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>265.84</v>
+        <v>124.26</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2.08%</t>
-        </is>
-      </c>
-      <c r="E125" s="4" t="inlineStr">
-        <is>
-          <t>-2.85%</t>
-        </is>
-      </c>
-      <c r="F125" s="1" t="inlineStr">
-        <is>
-          <t>-6.89%</t>
+          <t>-0.41%</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>8.04%</t>
+        </is>
+      </c>
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t>9.73%</t>
         </is>
       </c>
       <c r="G125" s="1" t="inlineStr">
         <is>
-          <t>-11.88%</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>-4.69%</t>
+          <t>-5.26%</t>
+        </is>
+      </c>
+      <c r="H125" s="1" t="inlineStr">
+        <is>
+          <t>-14.16%</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>25.81%</t>
+          <t>-6.80%</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>44.42%</t>
+          <t>62.45%</t>
         </is>
       </c>
       <c r="K125" t="n">
-        <v>13.27</v>
+        <v>4.64</v>
       </c>
       <c r="L125" t="n">
-        <v>71920000000</v>
+        <v>71850000000</v>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>366.50 -27.47</t>
+          <t>157.28 -20.99</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>203.85 30.41</t>
+          <t>99.56 24.81</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Apollo Global Management Inc</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>124.26</v>
+        <v>265.84</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>-0.41%</t>
-        </is>
-      </c>
-      <c r="E126" s="3" t="inlineStr">
-        <is>
-          <t>8.04%</t>
-        </is>
-      </c>
-      <c r="F126" s="3" t="inlineStr">
-        <is>
-          <t>9.73%</t>
+          <t>2.08%</t>
+        </is>
+      </c>
+      <c r="E126" s="4" t="inlineStr">
+        <is>
+          <t>-2.85%</t>
+        </is>
+      </c>
+      <c r="F126" s="1" t="inlineStr">
+        <is>
+          <t>-6.89%</t>
         </is>
       </c>
       <c r="G126" s="1" t="inlineStr">
         <is>
-          <t>-5.26%</t>
-        </is>
-      </c>
-      <c r="H126" s="1" t="inlineStr">
-        <is>
-          <t>-14.16%</t>
+          <t>-11.88%</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>-4.69%</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>-6.80%</t>
+          <t>25.81%</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>62.45%</t>
+          <t>44.42%</t>
         </is>
       </c>
       <c r="K126" t="n">
-        <v>4.64</v>
+        <v>13.27</v>
       </c>
       <c r="L126" t="n">
-        <v>71850000000</v>
+        <v>71300000000</v>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>157.28 -20.99</t>
+          <t>366.50 -27.47</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>99.56 24.81</t>
+          <t>203.85 30.41</t>
         </is>
       </c>
     </row>
@@ -9091,7 +9091,7 @@
         <v>9.92</v>
       </c>
       <c r="L132" t="n">
-        <v>59100000000</v>
+        <v>59210000000</v>
       </c>
       <c r="M132" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         <v>1.38</v>
       </c>
       <c r="L150" t="n">
-        <v>37690000000</v>
+        <v>37550000000</v>
       </c>
       <c r="M150" t="inlineStr">
         <is>
@@ -12127,7 +12127,7 @@
         <v>2.14</v>
       </c>
       <c r="L178" t="n">
-        <v>10400000000</v>
+        <v>10410000000</v>
       </c>
       <c r="M178" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>1.91</v>
       </c>
       <c r="L197" t="n">
-        <v>3280000000</v>
+        <v>3210000000</v>
       </c>
       <c r="M197" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
         <v>0.51</v>
       </c>
       <c r="L204" t="n">
-        <v>673590000</v>
+        <v>673580000</v>
       </c>
       <c r="M204" t="inlineStr">
         <is>

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>iShares Russell 2000 ETF</t>
+          <t>iShares Russell 2000 Index Fund</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -846,7 +846,7 @@
         <v>9.720000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>4662120000000</v>
+        <v>4659460000000</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>6.22</v>
       </c>
       <c r="L15" t="n">
-        <v>1020990000000</v>
+        <v>1020620000000</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>12.92</v>
       </c>
       <c r="L26" t="n">
-        <v>441860000000</v>
+        <v>442060000000</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
         <v>3.01</v>
       </c>
       <c r="L91" t="n">
-        <v>134900000000</v>
+        <v>134940000000</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -846,7 +846,7 @@
         <v>9.19</v>
       </c>
       <c r="L7" t="n">
-        <v>4828700000000</v>
+        <v>4835680000000</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>6.52</v>
       </c>
       <c r="L15" t="n">
-        <v>1028400000000</v>
+        <v>1028320000000</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>5.08</v>
       </c>
       <c r="L32" t="n">
-        <v>362400000000</v>
+        <v>361710000000</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>5.99</v>
       </c>
       <c r="L67" t="n">
-        <v>196010000000</v>
+        <v>195920000000</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
         <v>3.21</v>
       </c>
       <c r="L78" t="n">
-        <v>163010000000</v>
+        <v>163060000000</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>2.98</v>
       </c>
       <c r="L113" t="n">
-        <v>85720000000</v>
+        <v>85660000000</v>
       </c>
       <c r="M113" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>16.02</v>
       </c>
       <c r="L129" t="n">
-        <v>69030000000</v>
+        <v>68970000000</v>
       </c>
       <c r="M129" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         <v>7.42</v>
       </c>
       <c r="L134" t="n">
-        <v>60730000000</v>
+        <v>61040000000</v>
       </c>
       <c r="M134" t="inlineStr">
         <is>
@@ -10416,7 +10416,7 @@
         <v>4.72</v>
       </c>
       <c r="L152" t="n">
-        <v>34830000000</v>
+        <v>34720000000</v>
       </c>
       <c r="M152" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>0.83</v>
       </c>
       <c r="L170" t="n">
-        <v>20090000000</v>
+        <v>20200000000</v>
       </c>
       <c r="M170" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
         <v>3.59</v>
       </c>
       <c r="L172" t="n">
-        <v>18050000000</v>
+        <v>18380000000</v>
       </c>
       <c r="M172" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
         <v>1.01</v>
       </c>
       <c r="L181" t="n">
-        <v>8440000000</v>
+        <v>8430000000</v>
       </c>
       <c r="M181" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         <v>1.91</v>
       </c>
       <c r="L183" t="n">
-        <v>8300000000</v>
+        <v>8250000000</v>
       </c>
       <c r="M183" t="inlineStr">
         <is>
@@ -13843,7 +13843,7 @@
         <v>0.43</v>
       </c>
       <c r="L204" t="n">
-        <v>677370000</v>
+        <v>677360000</v>
       </c>
       <c r="M204" t="inlineStr">
         <is>
@@ -13909,7 +13909,7 @@
         <v>1.28</v>
       </c>
       <c r="L205" t="n">
-        <v>522850000</v>
+        <v>522860000</v>
       </c>
       <c r="M205" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>iShares Ethereum Trust</t>
+          <t>iShares Ethereum Trust ETF</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -846,7 +846,7 @@
         <v>9.4</v>
       </c>
       <c r="L7" t="n">
-        <v>4791230000000</v>
+        <v>4788550000000</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>6.57</v>
       </c>
       <c r="L15" t="n">
-        <v>1041680000000</v>
+        <v>1041000000000</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -5020,264 +5020,264 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>AMGEN Inc</t>
+          <t>Blackrock Inc</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>326.31</v>
+        <v>1081.9</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>-2.95%</t>
-        </is>
-      </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>-6.22%</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>0.00%</t>
+          <t>-2.00%</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>1.56%</t>
+        </is>
+      </c>
+      <c r="F71" s="1" t="inlineStr">
+        <is>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>0.16%</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>1.08%</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>20.10%</t>
+          <t>10.05%</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>38.21%</t>
+          <t>58.15%</t>
         </is>
       </c>
       <c r="K71" t="n">
-        <v>7.81</v>
+        <v>24.05</v>
       </c>
       <c r="L71" t="n">
-        <v>176110000000</v>
+        <v>176180000000</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>391.29 -16.61</t>
+          <t>1219.94 -11.32</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>264.15 23.53</t>
+          <t>917.39 17.93</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Boeing Co</t>
+          <t>AMGEN Inc</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>220.49</v>
+        <v>326.31</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>-3.80%</t>
+          <t>-2.95%</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>-4.01%</t>
-        </is>
-      </c>
-      <c r="F72" s="3" t="inlineStr">
-        <is>
-          <t>1.18%</t>
-        </is>
-      </c>
-      <c r="G72" s="3" t="inlineStr">
-        <is>
-          <t>0.37%</t>
+          <t>-3.15%</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>-6.22%</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>6.91%</t>
+          <t>20.10%</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>44.58%</t>
+          <t>38.21%</t>
         </is>
       </c>
       <c r="K72" t="n">
-        <v>7.54</v>
+        <v>7.81</v>
       </c>
       <c r="L72" t="n">
-        <v>173810000000</v>
+        <v>176110000000</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>254.35 -13.31</t>
+          <t>391.29 -16.61</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>176.77 24.73</t>
+          <t>264.15 23.53</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>Boeing Co</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>501</v>
+        <v>220.49</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>3.26%</t>
-        </is>
-      </c>
-      <c r="E73" s="1" t="inlineStr">
-        <is>
-          <t>6.51%</t>
-        </is>
-      </c>
-      <c r="F73" s="1" t="inlineStr">
-        <is>
-          <t>11.82%</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>-5.76%</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>-25.65%</t>
+          <t>-3.80%</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>-4.01%</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>1.18%</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>0.37%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>1.55%</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>36.66%</t>
+          <t>6.91%</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>58.35%</t>
+          <t>44.58%</t>
         </is>
       </c>
       <c r="K73" t="n">
-        <v>29.91</v>
+        <v>7.54</v>
       </c>
       <c r="L73" t="n">
-        <v>168310000000</v>
+        <v>173810000000</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>745.61 -32.81</t>
+          <t>254.35 -13.31</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>320.00 56.56</t>
+          <t>176.77 24.73</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Blackrock Inc</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1081.9</v>
+        <v>501</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>-2.00%</t>
-        </is>
-      </c>
-      <c r="E74" s="3" t="inlineStr">
-        <is>
-          <t>1.56%</t>
+          <t>3.26%</t>
+        </is>
+      </c>
+      <c r="E74" s="1" t="inlineStr">
+        <is>
+          <t>6.51%</t>
         </is>
       </c>
       <c r="F74" s="1" t="inlineStr">
         <is>
-          <t>6.96%</t>
-        </is>
-      </c>
-      <c r="G74" s="3" t="inlineStr">
-        <is>
-          <t>0.16%</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>1.08%</t>
+          <t>11.82%</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>-5.76%</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>-25.65%</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>10.05%</t>
+          <t>36.66%</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>58.15%</t>
+          <t>58.35%</t>
         </is>
       </c>
       <c r="K74" t="n">
-        <v>24.05</v>
+        <v>29.91</v>
       </c>
       <c r="L74" t="n">
-        <v>167950000000</v>
+        <v>168310000000</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>1219.94 -11.32</t>
+          <t>745.61 -32.81</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>917.39 17.93</t>
+          <t>320.00 56.56</t>
         </is>
       </c>
     </row>
@@ -5928,7 +5928,7 @@
         <v>23.05</v>
       </c>
       <c r="L84" t="n">
-        <v>151240000000</v>
+        <v>151220000000</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>4.13</v>
       </c>
       <c r="L157" t="n">
-        <v>29510000000</v>
+        <v>29520000000</v>
       </c>
       <c r="M157" t="inlineStr">
         <is>
@@ -12193,7 +12193,7 @@
         <v>1.94</v>
       </c>
       <c r="L179" t="n">
-        <v>8640000000</v>
+        <v>8630000000</v>
       </c>
       <c r="M179" t="inlineStr">
         <is>
@@ -12589,7 +12589,7 @@
         <v>1.13</v>
       </c>
       <c r="L185" t="n">
-        <v>7020000000</v>
+        <v>7030000000</v>
       </c>
       <c r="M185" t="inlineStr">
         <is>
@@ -13793,132 +13793,132 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>ASPI</t>
+          <t>UMAC</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>ASP Isotopes Inc</t>
+          <t>Unusual Machines Inc</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>5.8</v>
+        <v>16.2</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>-4.76%</t>
+          <t>-4.31%</t>
         </is>
       </c>
       <c r="E204" s="1" t="inlineStr">
         <is>
-          <t>5.36%</t>
+          <t>9.46%</t>
         </is>
       </c>
       <c r="F204" s="1" t="inlineStr">
         <is>
-          <t>13.23%</t>
-        </is>
-      </c>
-      <c r="G204" s="2" t="inlineStr">
-        <is>
-          <t>-19.81%</t>
-        </is>
-      </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>8.41%</t>
+          <t>6.08%</t>
+        </is>
+      </c>
+      <c r="G204" s="1" t="inlineStr">
+        <is>
+          <t>24.38%</t>
+        </is>
+      </c>
+      <c r="H204" s="1" t="inlineStr">
+        <is>
+          <t>27.16%</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>-8.81%</t>
+          <t>195.62%</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>54.90%</t>
+          <t>56.37%</t>
         </is>
       </c>
       <c r="K204" t="n">
-        <v>0.48</v>
+        <v>1.48</v>
       </c>
       <c r="L204" t="n">
-        <v>730240000</v>
+        <v>774260000</v>
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>14.49 -59.97</t>
+          <t>23.38 -30.71</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>3.92 47.96</t>
+          <t>4.67 246.90</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>UMAC</t>
+          <t>ASPI</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Unusual Machines Inc</t>
+          <t>ASP Isotopes Inc</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>16.2</v>
+        <v>5.8</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>-4.31%</t>
+          <t>-4.76%</t>
         </is>
       </c>
       <c r="E205" s="1" t="inlineStr">
         <is>
-          <t>9.46%</t>
+          <t>5.36%</t>
         </is>
       </c>
       <c r="F205" s="1" t="inlineStr">
         <is>
-          <t>6.08%</t>
-        </is>
-      </c>
-      <c r="G205" s="1" t="inlineStr">
-        <is>
-          <t>24.38%</t>
-        </is>
-      </c>
-      <c r="H205" s="1" t="inlineStr">
-        <is>
-          <t>27.16%</t>
+          <t>13.23%</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>-19.81%</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>8.41%</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>195.62%</t>
+          <t>-8.81%</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>56.37%</t>
+          <t>54.90%</t>
         </is>
       </c>
       <c r="K205" t="n">
-        <v>1.48</v>
+        <v>0.48</v>
       </c>
       <c r="L205" t="n">
-        <v>631170000</v>
+        <v>730240000</v>
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>23.38 -30.71</t>
+          <t>14.49 -59.97</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>4.67 246.90</t>
+          <t>3.92 47.96</t>
         </is>
       </c>
     </row>

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -846,7 +846,7 @@
         <v>9.550000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>4624220000000</v>
+        <v>4620520000000</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>6.67</v>
       </c>
       <c r="L14" t="n">
-        <v>1048240000000</v>
+        <v>1048580000000</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>17.64</v>
       </c>
       <c r="L36" t="n">
-        <v>342970000000</v>
+        <v>343120000000</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         <v>9.710000000000001</v>
       </c>
       <c r="L120" t="n">
-        <v>79170000000</v>
+        <v>79140000000</v>
       </c>
       <c r="M120" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>10.18</v>
       </c>
       <c r="L123" t="n">
-        <v>78570000000</v>
+        <v>78590000000</v>
       </c>
       <c r="M123" t="inlineStr">
         <is>
@@ -10213,7 +10213,7 @@
         <v>2.67</v>
       </c>
       <c r="L149" t="n">
-        <v>40550000000</v>
+        <v>40520000000</v>
       </c>
       <c r="M149" t="inlineStr">
         <is>
@@ -11335,7 +11335,7 @@
         <v>3.77</v>
       </c>
       <c r="L166" t="n">
-        <v>21720000000</v>
+        <v>21850000000</v>
       </c>
       <c r="M166" t="inlineStr">
         <is>

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -10543,7 +10543,7 @@
         <v>7.26</v>
       </c>
       <c r="L154" t="n">
-        <v>32130000000</v>
+        <v>32000000000</v>
       </c>
       <c r="M154" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>4.93</v>
       </c>
       <c r="L156" t="n">
-        <v>31140000000</v>
+        <v>31130000000</v>
       </c>
       <c r="M156" t="inlineStr">
         <is>

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -846,7 +846,7 @@
         <v>9.359999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>4586900000000</v>
+        <v>4586910000000</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>6.36</v>
       </c>
       <c r="L16" t="n">
-        <v>1023150000000</v>
+        <v>1022970000000</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>8.27</v>
       </c>
       <c r="L81" t="n">
-        <v>156330000000</v>
+        <v>156510000000</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -6192,7 +6192,7 @@
         <v>15.31</v>
       </c>
       <c r="L88" t="n">
-        <v>146450000000</v>
+        <v>146350000000</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>6.25</v>
       </c>
       <c r="L99" t="n">
-        <v>120060000000</v>
+        <v>120190000000</v>
       </c>
       <c r="M99" t="inlineStr">
         <is>

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -846,7 +846,7 @@
         <v>9.869999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>4450850000000</v>
+        <v>4450040000000</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>7.12</v>
       </c>
       <c r="L15" t="n">
-        <v>1053070000000</v>
+        <v>1053510000000</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>35.1</v>
       </c>
       <c r="L76" t="n">
-        <v>170800000000</v>
+        <v>170820000000</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>1.77</v>
       </c>
       <c r="L182" t="n">
-        <v>8020000000</v>
+        <v>8040000000</v>
       </c>
       <c r="M182" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>1.23</v>
       </c>
       <c r="L189" t="n">
-        <v>5170000000</v>
+        <v>5290000000</v>
       </c>
       <c r="M189" t="inlineStr">
         <is>

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -846,7 +846,7 @@
         <v>10.69</v>
       </c>
       <c r="L7" t="n">
-        <v>4347600000000</v>
+        <v>4349630000000</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>6.77</v>
       </c>
       <c r="L16" t="n">
-        <v>1054170000000</v>
+        <v>1054340000000</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -846,7 +846,7 @@
         <v>10.78</v>
       </c>
       <c r="L7" t="n">
-        <v>4463610000000</v>
+        <v>4455980000000</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>7.06</v>
       </c>
       <c r="L15" t="n">
-        <v>1055890000000</v>
+        <v>1055400000000</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         <v>27.56</v>
       </c>
       <c r="L52" t="n">
-        <v>265400000000</v>
+        <v>265470000000</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>6.01</v>
       </c>
       <c r="L168" t="n">
-        <v>20500000000</v>
+        <v>20480000000</v>
       </c>
       <c r="M168" t="inlineStr">
         <is>
@@ -13914,7 +13914,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="L205" t="n">
-        <v>903980000</v>
+        <v>903990000</v>
       </c>
       <c r="M205" t="inlineStr">
         <is>

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -714,7 +714,7 @@
         <v>7.09</v>
       </c>
       <c r="L5" t="n">
-        <v>4376980000000</v>
+        <v>4376990000000</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>10.78</v>
       </c>
       <c r="L7" t="n">
-        <v>4455980000000</v>
+        <v>4452180000000</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>79.81</v>
       </c>
       <c r="L14" t="n">
-        <v>1278840000000</v>
+        <v>1278830000000</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>7.06</v>
       </c>
       <c r="L15" t="n">
-        <v>1055400000000</v>
+        <v>1055700000000</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>32.6</v>
       </c>
       <c r="L44" t="n">
-        <v>323490000000</v>
+        <v>323500000000</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         <v>27.56</v>
       </c>
       <c r="L52" t="n">
-        <v>265470000000</v>
+        <v>265400000000</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>3.66</v>
       </c>
       <c r="L57" t="n">
-        <v>245330000000</v>
+        <v>245340000000</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>12.57</v>
       </c>
       <c r="L61" t="n">
-        <v>234130000000</v>
+        <v>234120000000</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>5.17</v>
       </c>
       <c r="L65" t="n">
-        <v>197950000000</v>
+        <v>197960000000</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>13.51</v>
       </c>
       <c r="L99" t="n">
-        <v>117810000000</v>
+        <v>117800000000</v>
       </c>
       <c r="M99" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>24.14</v>
       </c>
       <c r="L104" t="n">
-        <v>107720000000</v>
+        <v>107710000000</v>
       </c>
       <c r="M104" t="inlineStr">
         <is>
@@ -7380,7 +7380,7 @@
         <v>20.62</v>
       </c>
       <c r="L106" t="n">
-        <v>96350000000</v>
+        <v>96340000000</v>
       </c>
       <c r="M106" t="inlineStr">
         <is>
@@ -7644,7 +7644,7 @@
         <v>4.38</v>
       </c>
       <c r="L110" t="n">
-        <v>85830000000</v>
+        <v>84520000000</v>
       </c>
       <c r="M110" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v>17.16</v>
       </c>
       <c r="L126" t="n">
-        <v>73030000000</v>
+        <v>73040000000</v>
       </c>
       <c r="M126" t="inlineStr">
         <is>
@@ -9970,330 +9970,330 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Carnival Corp Ltd</t>
+          <t>MSCI Inc</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>30.87</v>
+        <v>581.1900000000001</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>3.21%</t>
-        </is>
-      </c>
-      <c r="E146" s="1" t="inlineStr">
-        <is>
-          <t>10.20%</t>
-        </is>
-      </c>
-      <c r="F146" s="1" t="inlineStr">
-        <is>
-          <t>13.56%</t>
-        </is>
-      </c>
-      <c r="G146" s="1" t="inlineStr">
-        <is>
-          <t>8.82%</t>
+          <t>-2.63%</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="inlineStr">
+        <is>
+          <t>-4.35%</t>
+        </is>
+      </c>
+      <c r="F146" s="3" t="inlineStr">
+        <is>
+          <t>-1.44%</t>
+        </is>
+      </c>
+      <c r="G146" s="4" t="inlineStr">
+        <is>
+          <t>2.09%</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.30%</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>30.75%</t>
+          <t>6.89%</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>63.75%</t>
+          <t>41.99%</t>
         </is>
       </c>
       <c r="K146" t="n">
-        <v>1.31</v>
+        <v>16.32</v>
       </c>
       <c r="L146" t="n">
-        <v>42700000000</v>
+        <v>42310000000</v>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>34.03 -9.29</t>
+          <t>644.68 -9.85</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>22.58 36.70</t>
+          <t>501.08 15.99</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MSCI Inc</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>581.1900000000001</v>
+        <v>32.49</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>-2.63%</t>
-        </is>
-      </c>
-      <c r="E147" s="3" t="inlineStr">
-        <is>
-          <t>-4.35%</t>
+          <t>1.98%</t>
+        </is>
+      </c>
+      <c r="E147" s="4" t="inlineStr">
+        <is>
+          <t>4.17%</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>-1.44%</t>
-        </is>
-      </c>
-      <c r="G147" s="4" t="inlineStr">
-        <is>
-          <t>2.09%</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>1.30%</t>
+          <t>-0.54%</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>-9.30%</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>-12.19%</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>6.89%</t>
+          <t>-37.31%</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>41.99%</t>
+          <t>55.06%</t>
         </is>
       </c>
       <c r="K147" t="n">
-        <v>16.32</v>
+        <v>1.14</v>
       </c>
       <c r="L147" t="n">
-        <v>42310000000</v>
+        <v>41680000000</v>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>644.68 -9.85</t>
+          <t>58.42 -44.39</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>501.08 15.99</t>
+          <t>28.03 15.89</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>Autodesk Inc</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>32.49</v>
+        <v>193.82</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>1.98%</t>
-        </is>
-      </c>
-      <c r="E148" s="4" t="inlineStr">
-        <is>
-          <t>4.17%</t>
-        </is>
-      </c>
-      <c r="F148" s="3" t="inlineStr">
-        <is>
-          <t>-0.54%</t>
+          <t>0.39%</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>-13.24%</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>-16.64%</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>-9.30%</t>
+          <t>-28.15%</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>-12.19%</t>
+          <t>-34.52%</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>-37.31%</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>55.06%</t>
+          <t>-34.34%</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>28.45%</t>
         </is>
       </c>
       <c r="K148" t="n">
-        <v>1.14</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="L148" t="n">
-        <v>41680000000</v>
+        <v>40900000000</v>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>58.42 -44.39</t>
+          <t>329.09 -41.10</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>28.03 15.89</t>
+          <t>192.30 0.79</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Autodesk Inc</t>
+          <t>Strategy Inc</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>193.82</v>
+        <v>112.53</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>-3.46%</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>-13.24%</t>
+          <t>-16.60%</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>-16.64%</t>
+          <t>-27.15%</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>-28.15%</t>
+          <t>-41.34%</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>-34.52%</t>
+          <t>-25.94%</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>-34.34%</t>
-        </is>
-      </c>
-      <c r="J149" s="2" t="inlineStr">
-        <is>
-          <t>28.45%</t>
+          <t>-69.51%</t>
+        </is>
+      </c>
+      <c r="J149" s="3" t="inlineStr">
+        <is>
+          <t>34.04%</t>
         </is>
       </c>
       <c r="K149" t="n">
-        <v>9.619999999999999</v>
+        <v>10.32</v>
       </c>
       <c r="L149" t="n">
-        <v>40900000000</v>
+        <v>39440000000</v>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>329.09 -41.10</t>
+          <t>457.22 -75.39</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>192.30 0.79</t>
+          <t>104.17 8.03</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Strategy Inc</t>
+          <t>Carnival Corp Ltd</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>112.53</v>
+        <v>30.87</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>-3.46%</t>
-        </is>
-      </c>
-      <c r="E150" s="2" t="inlineStr">
-        <is>
-          <t>-16.60%</t>
-        </is>
-      </c>
-      <c r="F150" s="2" t="inlineStr">
-        <is>
-          <t>-27.15%</t>
-        </is>
-      </c>
-      <c r="G150" s="2" t="inlineStr">
-        <is>
-          <t>-41.34%</t>
-        </is>
-      </c>
-      <c r="H150" s="2" t="inlineStr">
-        <is>
-          <t>-25.94%</t>
+          <t>3.21%</t>
+        </is>
+      </c>
+      <c r="E150" s="1" t="inlineStr">
+        <is>
+          <t>10.20%</t>
+        </is>
+      </c>
+      <c r="F150" s="1" t="inlineStr">
+        <is>
+          <t>13.56%</t>
+        </is>
+      </c>
+      <c r="G150" s="1" t="inlineStr">
+        <is>
+          <t>8.82%</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>1.08%</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>-69.51%</t>
-        </is>
-      </c>
-      <c r="J150" s="3" t="inlineStr">
-        <is>
-          <t>34.04%</t>
+          <t>30.75%</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>63.75%</t>
         </is>
       </c>
       <c r="K150" t="n">
-        <v>10.32</v>
+        <v>1.31</v>
       </c>
       <c r="L150" t="n">
-        <v>39440000000</v>
+        <v>38250000000</v>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>457.22 -75.39</t>
+          <t>34.03 -9.29</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>104.17 8.03</t>
+          <t>22.58 36.70</t>
         </is>
       </c>
     </row>
@@ -11158,594 +11158,594 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>DKNG</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>DraftKings Inc</t>
+          <t>SoFi Technologies Inc</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>26.39</v>
+        <v>17.91</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>0.27%</t>
-        </is>
-      </c>
-      <c r="E164" s="4" t="inlineStr">
-        <is>
-          <t>0.41%</t>
+          <t>2.81%</t>
+        </is>
+      </c>
+      <c r="E164" s="1" t="inlineStr">
+        <is>
+          <t>6.28%</t>
         </is>
       </c>
       <c r="F164" s="1" t="inlineStr">
         <is>
-          <t>6.50%</t>
+          <t>5.72%</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>-11.90%</t>
+          <t>-21.09%</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>-23.42%</t>
+          <t>-31.59%</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>-33.36%</t>
+          <t>16.60%</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>50.88%</t>
+          <t>58.00%</t>
         </is>
       </c>
       <c r="K164" t="n">
-        <v>1.44</v>
+        <v>0.95</v>
       </c>
       <c r="L164" t="n">
-        <v>23460000000</v>
+        <v>22970000000</v>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>48.78 -45.90</t>
+          <t>32.73 -45.28</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>20.46 28.98</t>
+          <t>14.36 24.72</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>SoFi Technologies Inc</t>
+          <t>IREN Ltd</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>17.91</v>
+        <v>59.96</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2.81%</t>
-        </is>
-      </c>
-      <c r="E165" s="1" t="inlineStr">
-        <is>
-          <t>6.28%</t>
+          <t>3.18%</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="inlineStr">
+        <is>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="F165" s="1" t="inlineStr">
         <is>
-          <t>5.72%</t>
-        </is>
-      </c>
-      <c r="G165" s="2" t="inlineStr">
-        <is>
-          <t>-21.09%</t>
-        </is>
-      </c>
-      <c r="H165" s="2" t="inlineStr">
-        <is>
-          <t>-31.59%</t>
+          <t>11.09%</t>
+        </is>
+      </c>
+      <c r="G165" s="1" t="inlineStr">
+        <is>
+          <t>24.06%</t>
+        </is>
+      </c>
+      <c r="H165" s="1" t="inlineStr">
+        <is>
+          <t>58.75%</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>16.60%</t>
+          <t>511.84%</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>58.00%</t>
+          <t>53.18%</t>
         </is>
       </c>
       <c r="K165" t="n">
-        <v>0.95</v>
+        <v>5.24</v>
       </c>
       <c r="L165" t="n">
-        <v>22970000000</v>
+        <v>21400000000</v>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>32.73 -45.28</t>
+          <t>76.87 -22.00</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>14.36 24.72</t>
+          <t>9.63 522.42</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>IREN Ltd</t>
+          <t>IonQ Inc</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>59.96</v>
+        <v>56.55</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>3.18%</t>
-        </is>
-      </c>
-      <c r="E166" s="3" t="inlineStr">
-        <is>
-          <t>-0.32%</t>
+          <t>3.40%</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>-9.20%</t>
         </is>
       </c>
       <c r="F166" s="1" t="inlineStr">
         <is>
-          <t>11.09%</t>
+          <t>7.86%</t>
         </is>
       </c>
       <c r="G166" s="1" t="inlineStr">
         <is>
-          <t>24.06%</t>
+          <t>14.74%</t>
         </is>
       </c>
       <c r="H166" s="1" t="inlineStr">
         <is>
-          <t>58.75%</t>
+          <t>26.03%</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>511.84%</t>
+          <t>42.69%</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>53.18%</t>
+          <t>48.58%</t>
         </is>
       </c>
       <c r="K166" t="n">
-        <v>5.24</v>
+        <v>5.38</v>
       </c>
       <c r="L166" t="n">
-        <v>21400000000</v>
+        <v>21110000000</v>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>76.87 -22.00</t>
+          <t>84.64 -33.19</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>9.63 522.42</t>
+          <t>25.89 118.42</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>ROKU</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>IonQ Inc</t>
+          <t>Roku Inc</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>56.55</v>
+        <v>138.07</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>3.40%</t>
-        </is>
-      </c>
-      <c r="E167" s="2" t="inlineStr">
-        <is>
-          <t>-9.20%</t>
+          <t>0.57%</t>
+        </is>
+      </c>
+      <c r="E167" s="1" t="inlineStr">
+        <is>
+          <t>7.17%</t>
         </is>
       </c>
       <c r="F167" s="1" t="inlineStr">
         <is>
-          <t>7.86%</t>
+          <t>12.77%</t>
         </is>
       </c>
       <c r="G167" s="1" t="inlineStr">
         <is>
-          <t>14.74%</t>
+          <t>31.45%</t>
         </is>
       </c>
       <c r="H167" s="1" t="inlineStr">
         <is>
-          <t>26.03%</t>
+          <t>27.27%</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>42.69%</t>
+          <t>69.56%</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>48.58%</t>
+          <t>61.77%</t>
         </is>
       </c>
       <c r="K167" t="n">
-        <v>5.38</v>
+        <v>6.01</v>
       </c>
       <c r="L167" t="n">
-        <v>21110000000</v>
+        <v>20480000000</v>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>84.64 -33.19</t>
+          <t>148.88 -7.26</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>25.89 118.42</t>
+          <t>77.64 77.83</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ROKU</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Roku Inc</t>
+          <t>Zscaler Inc</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>138.07</v>
+        <v>124.85</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>0.57%</t>
-        </is>
-      </c>
-      <c r="E168" s="1" t="inlineStr">
-        <is>
-          <t>7.17%</t>
-        </is>
-      </c>
-      <c r="F168" s="1" t="inlineStr">
-        <is>
-          <t>12.77%</t>
-        </is>
-      </c>
-      <c r="G168" s="1" t="inlineStr">
-        <is>
-          <t>31.45%</t>
-        </is>
-      </c>
-      <c r="H168" s="1" t="inlineStr">
-        <is>
-          <t>27.27%</t>
+          <t>0.38%</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>-10.08%</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>-11.29%</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>-40.99%</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>-44.49%</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>69.56%</t>
+          <t>-59.12%</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>61.77%</t>
+          <t>40.52%</t>
         </is>
       </c>
       <c r="K168" t="n">
-        <v>6.01</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="L168" t="n">
-        <v>20480000000</v>
+        <v>20190000000</v>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>148.88 -7.26</t>
+          <t>336.99 -62.95</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>77.64 77.83</t>
+          <t>114.62 8.92</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Zscaler Inc</t>
+          <t>Circle Internet Group Inc</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>124.85</v>
+        <v>80.23</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>-0.45%</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>-10.08%</t>
+          <t>-13.25%</t>
         </is>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>-11.29%</t>
+          <t>-20.79%</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>-40.99%</t>
-        </is>
-      </c>
-      <c r="H169" s="2" t="inlineStr">
-        <is>
-          <t>-44.49%</t>
+          <t>-19.24%</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>1.17%</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>-59.12%</t>
+          <t>-59.80%</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>40.52%</t>
+          <t>38.15%</t>
         </is>
       </c>
       <c r="K169" t="n">
-        <v>9.210000000000001</v>
+        <v>7.67</v>
       </c>
       <c r="L169" t="n">
-        <v>20190000000</v>
+        <v>19940000000</v>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>336.99 -62.95</t>
+          <t>298.99 -73.17</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>114.62 8.92</t>
+          <t>49.90 60.78</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>CRCL</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Circle Internet Group Inc</t>
+          <t>Super Micro Computer Inc</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>80.23</v>
+        <v>30.66</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>-0.45%</t>
+          <t>10.37%</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>-13.25%</t>
+          <t>-19.27%</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>-20.79%</t>
+          <t>-6.54%</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>-19.24%</t>
+          <t>-13.76%</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>4.75%</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>-59.80%</t>
+          <t>-31.05%</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>38.15%</t>
+          <t>43.36%</t>
         </is>
       </c>
       <c r="K170" t="n">
-        <v>7.67</v>
+        <v>3.44</v>
       </c>
       <c r="L170" t="n">
-        <v>19940000000</v>
+        <v>19830000000</v>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>298.99 -73.17</t>
+          <t>62.36 -50.83</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>49.90 60.78</t>
+          <t>19.48 57.39</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Super Micro Computer Inc</t>
+          <t>Charter Communications Inc</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>30.66</v>
+        <v>126.23</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>10.37%</t>
+          <t>-4.37%</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>-19.27%</t>
+          <t>-9.31%</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>-6.54%</t>
+          <t>-24.01%</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>-13.76%</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>4.75%</t>
+          <t>-40.35%</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>-39.53%</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>-31.05%</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>43.36%</t>
+          <t>-66.56%</t>
+        </is>
+      </c>
+      <c r="J171" s="3" t="inlineStr">
+        <is>
+          <t>32.07%</t>
         </is>
       </c>
       <c r="K171" t="n">
-        <v>3.44</v>
+        <v>7.28</v>
       </c>
       <c r="L171" t="n">
-        <v>19830000000</v>
+        <v>15520000000</v>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>62.36 -50.83</t>
+          <t>422.29 -70.11</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>19.48 57.39</t>
+          <t>126.70 -0.37</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>GRAB</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Charter Communications Inc</t>
+          <t>Grab Holdings Limited</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>126.23</v>
+        <v>3.57</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>-4.37%</t>
-        </is>
-      </c>
-      <c r="E172" s="2" t="inlineStr">
-        <is>
-          <t>-9.31%</t>
-        </is>
-      </c>
-      <c r="F172" s="2" t="inlineStr">
-        <is>
-          <t>-24.01%</t>
+          <t>3.48%</t>
+        </is>
+      </c>
+      <c r="E172" s="4" t="inlineStr">
+        <is>
+          <t>3.00%</t>
+        </is>
+      </c>
+      <c r="F172" s="3" t="inlineStr">
+        <is>
+          <t>-2.36%</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>-40.35%</t>
+          <t>-23.26%</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>-39.53%</t>
+          <t>-28.46%</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>-66.56%</t>
-        </is>
-      </c>
-      <c r="J172" s="3" t="inlineStr">
-        <is>
-          <t>32.07%</t>
+          <t>-23.39%</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>53.88%</t>
         </is>
       </c>
       <c r="K172" t="n">
-        <v>7.28</v>
+        <v>0.16</v>
       </c>
       <c r="L172" t="n">
-        <v>17480000000</v>
+        <v>14630000000</v>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>422.29 -70.11</t>
+          <t>6.62 -46.07</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>126.70 -0.37</t>
+          <t>3.18 12.26</t>
         </is>
       </c>
     </row>
@@ -11818,132 +11818,132 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>GRAB</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Grab Holdings Limited</t>
+          <t>Applied Digital Corp</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>3.57</v>
+        <v>46.59</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>3.48%</t>
+          <t>2.24%</t>
         </is>
       </c>
       <c r="E174" s="4" t="inlineStr">
         <is>
-          <t>3.00%</t>
-        </is>
-      </c>
-      <c r="F174" s="3" t="inlineStr">
-        <is>
-          <t>-2.36%</t>
-        </is>
-      </c>
-      <c r="G174" s="2" t="inlineStr">
-        <is>
-          <t>-23.26%</t>
-        </is>
-      </c>
-      <c r="H174" s="2" t="inlineStr">
-        <is>
-          <t>-28.46%</t>
+          <t>3.53%</t>
+        </is>
+      </c>
+      <c r="F174" s="1" t="inlineStr">
+        <is>
+          <t>17.77%</t>
+        </is>
+      </c>
+      <c r="G174" s="1" t="inlineStr">
+        <is>
+          <t>49.24%</t>
+        </is>
+      </c>
+      <c r="H174" s="1" t="inlineStr">
+        <is>
+          <t>90.01%</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>-23.39%</t>
+          <t>339.11%</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>53.88%</t>
+          <t>57.24%</t>
         </is>
       </c>
       <c r="K174" t="n">
-        <v>0.16</v>
+        <v>3.99</v>
       </c>
       <c r="L174" t="n">
-        <v>14630000000</v>
+        <v>13310000000</v>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>6.62 -46.07</t>
+          <t>50.72 -8.15</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>3.18 12.26</t>
+          <t>9.02 416.52</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>DKNG</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Applied Digital Corp</t>
+          <t>DraftKings Inc</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>46.59</v>
+        <v>26.39</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t>3.53%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="F175" s="1" t="inlineStr">
         <is>
-          <t>17.77%</t>
-        </is>
-      </c>
-      <c r="G175" s="1" t="inlineStr">
-        <is>
-          <t>49.24%</t>
-        </is>
-      </c>
-      <c r="H175" s="1" t="inlineStr">
-        <is>
-          <t>90.01%</t>
+          <t>6.50%</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>-11.90%</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>-23.42%</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>339.11%</t>
+          <t>-33.36%</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>57.24%</t>
+          <t>50.88%</t>
         </is>
       </c>
       <c r="K175" t="n">
-        <v>3.99</v>
+        <v>1.44</v>
       </c>
       <c r="L175" t="n">
-        <v>13310000000</v>
+        <v>13090000000</v>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>50.72 -8.15</t>
+          <t>48.78 -45.90</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>9.02 416.52</t>
+          <t>20.46 28.98</t>
         </is>
       </c>
     </row>
@@ -12016,198 +12016,198 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>BROS</t>
+          <t>PINS</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Dutch Bros Inc</t>
+          <t>Pinterest Inc</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>70.72</v>
+        <v>20.27</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>7.61%</t>
-        </is>
-      </c>
-      <c r="E177" s="1" t="inlineStr">
-        <is>
-          <t>18.99%</t>
-        </is>
-      </c>
-      <c r="F177" s="1" t="inlineStr">
-        <is>
-          <t>25.79%</t>
-        </is>
-      </c>
-      <c r="G177" s="1" t="inlineStr">
-        <is>
-          <t>25.69%</t>
-        </is>
-      </c>
-      <c r="H177" s="1" t="inlineStr">
-        <is>
-          <t>15.52%</t>
+          <t>-0.44%</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="inlineStr">
+        <is>
+          <t>-2.22%</t>
+        </is>
+      </c>
+      <c r="F177" s="4" t="inlineStr">
+        <is>
+          <t>0.08%</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>-17.74%</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>-21.71%</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>1.27%</t>
-        </is>
-      </c>
-      <c r="J177" s="1" t="inlineStr">
-        <is>
-          <t>77.12%</t>
+          <t>-41.72%</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>47.23%</t>
         </is>
       </c>
       <c r="K177" t="n">
-        <v>3.07</v>
+        <v>1.08</v>
       </c>
       <c r="L177" t="n">
-        <v>11650000000</v>
+        <v>11350000000</v>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>74.65 -5.26</t>
+          <t>39.93 -49.24</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>44.58 58.64</t>
+          <t>13.84 46.46</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>PINS</t>
+          <t>OKLO</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Pinterest Inc</t>
+          <t>Oklo Inc</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>20.27</v>
+        <v>61.17</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>4.00%</t>
         </is>
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>-2.22%</t>
-        </is>
-      </c>
-      <c r="F178" s="4" t="inlineStr">
-        <is>
-          <t>0.08%</t>
+          <t>-2.48%</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>-5.94%</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>-17.74%</t>
+          <t>-28.07%</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>-21.71%</t>
+          <t>-14.76%</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>-41.72%</t>
+          <t>-1.37%</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>47.23%</t>
+          <t>48.55%</t>
         </is>
       </c>
       <c r="K178" t="n">
-        <v>1.08</v>
+        <v>5.38</v>
       </c>
       <c r="L178" t="n">
-        <v>11350000000</v>
+        <v>10640000000</v>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>39.93 -49.24</t>
+          <t>193.84 -68.44</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>13.84 46.46</t>
+          <t>44.88 36.30</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>OKLO</t>
+          <t>BROS</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Oklo Inc</t>
+          <t>Dutch Bros Inc</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>61.17</v>
+        <v>70.72</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>4.00%</t>
-        </is>
-      </c>
-      <c r="E179" s="3" t="inlineStr">
-        <is>
-          <t>-2.48%</t>
-        </is>
-      </c>
-      <c r="F179" s="2" t="inlineStr">
-        <is>
-          <t>-5.94%</t>
-        </is>
-      </c>
-      <c r="G179" s="2" t="inlineStr">
-        <is>
-          <t>-28.07%</t>
-        </is>
-      </c>
-      <c r="H179" s="2" t="inlineStr">
-        <is>
-          <t>-14.76%</t>
+          <t>7.61%</t>
+        </is>
+      </c>
+      <c r="E179" s="1" t="inlineStr">
+        <is>
+          <t>18.99%</t>
+        </is>
+      </c>
+      <c r="F179" s="1" t="inlineStr">
+        <is>
+          <t>25.79%</t>
+        </is>
+      </c>
+      <c r="G179" s="1" t="inlineStr">
+        <is>
+          <t>25.69%</t>
+        </is>
+      </c>
+      <c r="H179" s="1" t="inlineStr">
+        <is>
+          <t>15.52%</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>-1.37%</t>
-        </is>
-      </c>
-      <c r="J179" t="inlineStr">
-        <is>
-          <t>48.55%</t>
+          <t>1.27%</t>
+        </is>
+      </c>
+      <c r="J179" s="1" t="inlineStr">
+        <is>
+          <t>77.12%</t>
         </is>
       </c>
       <c r="K179" t="n">
-        <v>5.38</v>
+        <v>3.07</v>
       </c>
       <c r="L179" t="n">
-        <v>10640000000</v>
+        <v>9000000000</v>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>193.84 -68.44</t>
+          <t>74.65 -5.26</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>44.88 36.30</t>
+          <t>44.58 58.64</t>
         </is>
       </c>
     </row>
@@ -12594,7 +12594,7 @@
         <v>1.76</v>
       </c>
       <c r="L185" t="n">
-        <v>7360000000</v>
+        <v>7350000000</v>
       </c>
       <c r="M185" t="inlineStr">
         <is>
@@ -13006,86 +13006,86 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>FLNC</t>
+          <t>LMND</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Fluence Energy Inc</t>
+          <t>Lemonade Inc</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>24.8</v>
+        <v>58.84</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>5.89%</t>
-        </is>
-      </c>
-      <c r="E192" s="1" t="inlineStr">
-        <is>
-          <t>6.01%</t>
-        </is>
-      </c>
-      <c r="F192" s="1" t="inlineStr">
-        <is>
-          <t>31.42%</t>
-        </is>
-      </c>
-      <c r="G192" s="1" t="inlineStr">
-        <is>
-          <t>37.31%</t>
-        </is>
-      </c>
-      <c r="H192" s="1" t="inlineStr">
-        <is>
-          <t>25.38%</t>
+          <t>2.72%</t>
+        </is>
+      </c>
+      <c r="E192" s="4" t="inlineStr">
+        <is>
+          <t>4.07%</t>
+        </is>
+      </c>
+      <c r="F192" s="4" t="inlineStr">
+        <is>
+          <t>1.11%</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>-8.15%</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>-17.34%</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>345.24%</t>
+          <t>45.28%</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>56.71%</t>
+          <t>54.57%</t>
         </is>
       </c>
       <c r="K192" t="n">
-        <v>3.14</v>
+        <v>3.52</v>
       </c>
       <c r="L192" t="n">
-        <v>4570000000</v>
+        <v>4520000000</v>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>33.51 -25.99</t>
+          <t>99.90 -41.10</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>5.42 357.56</t>
+          <t>35.70 64.82</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>LMND</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Lemonade Inc</t>
+          <t>NuScale Power Corp</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>58.84</v>
+        <v>11.74</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2.72%</t>
+          <t>13.54%</t>
         </is>
       </c>
       <c r="E193" s="4" t="inlineStr">
@@ -13095,175 +13095,175 @@
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.73%</t>
         </is>
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>-8.15%</t>
+          <t>-43.35%</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>-17.34%</t>
+          <t>-17.15%</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>45.28%</t>
+          <t>-70.02%</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>54.57%</t>
+          <t>53.44%</t>
         </is>
       </c>
       <c r="K193" t="n">
-        <v>3.52</v>
+        <v>1.13</v>
       </c>
       <c r="L193" t="n">
-        <v>4520000000</v>
+        <v>4060000000</v>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>99.90 -41.10</t>
+          <t>57.42 -79.55</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>35.70 64.82</t>
+          <t>8.85 32.66</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>LEU</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>NuScale Power Corp</t>
+          <t>Centrus Energy Corp</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>11.74</v>
+        <v>191.39</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>13.54%</t>
-        </is>
-      </c>
-      <c r="E194" s="4" t="inlineStr">
-        <is>
-          <t>4.07%</t>
+          <t>12.38%</t>
+        </is>
+      </c>
+      <c r="E194" s="1" t="inlineStr">
+        <is>
+          <t>9.44%</t>
         </is>
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>0.99%</t>
         </is>
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>-43.35%</t>
+          <t>-22.69%</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>-17.15%</t>
+          <t>-21.16%</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>-70.02%</t>
+          <t>5.76%</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>53.44%</t>
+          <t>55.41%</t>
         </is>
       </c>
       <c r="K194" t="n">
-        <v>1.13</v>
+        <v>14.57</v>
       </c>
       <c r="L194" t="n">
-        <v>4290000000</v>
+        <v>3760000000</v>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>57.42 -79.55</t>
+          <t>464.25 -58.77</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>8.85 32.66</t>
+          <t>144.65 32.31</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>LEU</t>
+          <t>FLNC</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Centrus Energy Corp</t>
+          <t>Fluence Energy Inc</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>191.39</v>
+        <v>24.8</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>12.38%</t>
+          <t>5.89%</t>
         </is>
       </c>
       <c r="E195" s="1" t="inlineStr">
         <is>
-          <t>9.44%</t>
-        </is>
-      </c>
-      <c r="F195" s="4" t="inlineStr">
-        <is>
-          <t>0.99%</t>
-        </is>
-      </c>
-      <c r="G195" s="2" t="inlineStr">
-        <is>
-          <t>-22.69%</t>
-        </is>
-      </c>
-      <c r="H195" s="2" t="inlineStr">
-        <is>
-          <t>-21.16%</t>
+          <t>6.01%</t>
+        </is>
+      </c>
+      <c r="F195" s="1" t="inlineStr">
+        <is>
+          <t>31.42%</t>
+        </is>
+      </c>
+      <c r="G195" s="1" t="inlineStr">
+        <is>
+          <t>37.31%</t>
+        </is>
+      </c>
+      <c r="H195" s="1" t="inlineStr">
+        <is>
+          <t>25.38%</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>5.76%</t>
+          <t>345.24%</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>55.41%</t>
+          <t>56.71%</t>
         </is>
       </c>
       <c r="K195" t="n">
-        <v>14.57</v>
+        <v>3.14</v>
       </c>
       <c r="L195" t="n">
-        <v>3770000000</v>
+        <v>3290000000</v>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>464.25 -58.77</t>
+          <t>33.51 -25.99</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>144.65 32.31</t>
+          <t>5.42 357.56</t>
         </is>
       </c>
     </row>
@@ -13914,7 +13914,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="L205" t="n">
-        <v>903990000</v>
+        <v>903960000</v>
       </c>
       <c r="M205" t="inlineStr">
         <is>

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -846,7 +846,7 @@
         <v>11.41</v>
       </c>
       <c r="L7" t="n">
-        <v>4065040000000</v>
+        <v>4073120000000</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>95.17</v>
       </c>
       <c r="L14" t="n">
-        <v>1276970000000</v>
+        <v>1278850000000</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>7.3</v>
       </c>
       <c r="L16" t="n">
-        <v>1076410000000</v>
+        <v>1074100000000</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -12528,7 +12528,7 @@
         <v>1.71</v>
       </c>
       <c r="L184" t="n">
-        <v>7120000000</v>
+        <v>7130000000</v>
       </c>
       <c r="M184" t="inlineStr">
         <is>
@@ -13716,7 +13716,7 @@
         <v>0.66</v>
       </c>
       <c r="L202" t="n">
-        <v>1290000000</v>
+        <v>1380000000</v>
       </c>
       <c r="M202" t="inlineStr">
         <is>
@@ -13914,7 +13914,7 @@
         <v>0.72</v>
       </c>
       <c r="L205" t="n">
-        <v>776830000</v>
+        <v>776820000</v>
       </c>
       <c r="M205" t="inlineStr">
         <is>

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -4344,7 +4344,7 @@
         <v>3.84</v>
       </c>
       <c r="L60" t="n">
-        <v>227460000000</v>
+        <v>227620000000</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4138020000000</v>
+        <v>4249930000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4718270000000</v>
+        <v>4842180000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4275020000000</v>
+        <v>4296860000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2737900000000</v>
+        <v>2770950000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2583210000000</v>
+        <v>2563850000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2360370000000</v>
+        <v>2476910000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1771960000000</v>
+        <v>1797180000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1546760000000</v>
+        <v>1579660000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1428120000000</v>
+        <v>1429870000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1293470000000</v>
+        <v>1303650000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1158280000000</v>
+        <v>1129550000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,52 +726,52 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1068370000000</v>
+        <v>1079020000000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Walmart Inc</t>
+          <t>Advanced Micro Devices Inc</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>912000000000</v>
+        <v>947230000000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co</t>
+          <t>Walmart Inc</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>882600000000</v>
+        <v>901330000000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices Inc</t>
+          <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>879690000000</v>
+        <v>877080000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>725790000000</v>
+        <v>766770000000</v>
       </c>
     </row>
     <row r="21">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>643710000000</v>
+        <v>646420000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,37 +816,37 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>622290000000</v>
+        <v>611360000000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Exxon Mobil Corp</t>
+          <t>Applied Materials Inc</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>563960000000</v>
+        <v>574030000000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Applied Materials Inc</t>
+          <t>Exxon Mobil Corp</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>551520000000</v>
+        <v>566700000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>513870000000</v>
+        <v>541910000000</v>
       </c>
     </row>
     <row r="26">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>475930000000</v>
+        <v>490530000000</v>
       </c>
     </row>
     <row r="27">
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>463910000000</v>
+        <v>462960000000</v>
       </c>
     </row>
     <row r="28">
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>450310000000</v>
+        <v>453810000000</v>
       </c>
     </row>
     <row r="29">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>449310000000</v>
+        <v>444600000000</v>
       </c>
     </row>
     <row r="30">
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>425620000000</v>
+        <v>422130000000</v>
       </c>
     </row>
     <row r="31">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>419830000000</v>
+        <v>414860000000</v>
       </c>
     </row>
     <row r="32">
@@ -966,97 +966,97 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>410750000000</v>
+        <v>404360000000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>KLA Corp</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>389910000000</v>
+        <v>394120000000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Unitedhealth Group Inc</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>381260000000</v>
+        <v>389930000000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>Unitedhealth Group Inc</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>365570000000</v>
+        <v>377450000000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>KLA Corp</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>363650000000</v>
+        <v>377260000000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Coca-Cola Co</t>
+          <t>Home Depot Inc</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>355600000000</v>
+        <v>351660000000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Home Depot Inc</t>
+          <t>Coca-Cola Co</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>349800000000</v>
+        <v>349660000000</v>
       </c>
     </row>
     <row r="39">
@@ -1071,112 +1071,112 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>345680000000</v>
+        <v>341470000000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Chevron Corp</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>335520000000</v>
+        <v>336720000000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Chevron Corp</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>333940000000</v>
+        <v>330130000000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Merck &amp; Co Inc</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>319550000000</v>
+        <v>329720000000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Netflix Inc</t>
+          <t>Merck &amp; Co Inc</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>310670000000</v>
+        <v>317370000000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>303640000000</v>
+        <v>315710000000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Goldman Sachs Group Inc</t>
+          <t>Netflix Inc</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>300970000000</v>
+        <v>300650000000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>Goldman Sachs Group Inc</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>296270000000</v>
+        <v>298360000000</v>
       </c>
     </row>
     <row r="47">
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>296140000000</v>
+        <v>294070000000</v>
       </c>
     </row>
     <row r="48">
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>288480000000</v>
+        <v>286880000000</v>
       </c>
     </row>
     <row r="49">
@@ -1221,142 +1221,142 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>285010000000</v>
+        <v>281960000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>277370000000</v>
+        <v>279710000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>Palantir Technologies Inc</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>270580000000</v>
+        <v>279690000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>268780000000</v>
+        <v>277930000000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>International Business Machines Corp</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>261290000000</v>
+        <v>271270000000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>International Business Machines Corp</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>259810000000</v>
+        <v>264310000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Co</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>255560000000</v>
+        <v>255510000000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Wells Fargo &amp; Co</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>252270000000</v>
+        <v>252890000000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Citigroup Inc</t>
+          <t>Linde Plc</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>244360000000</v>
+        <v>240060000000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Linde Plc</t>
+          <t>Citigroup Inc</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>236420000000</v>
+        <v>240020000000</v>
       </c>
     </row>
     <row r="59">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>232590000000</v>
+        <v>230800000000</v>
       </c>
     </row>
     <row r="60">
@@ -1386,7 +1386,7 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>229300000000</v>
+        <v>230420000000</v>
       </c>
     </row>
     <row r="61">
@@ -1401,7 +1401,7 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>224690000000</v>
+        <v>220160000000</v>
       </c>
     </row>
     <row r="62">
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>220060000000</v>
+        <v>219830000000</v>
       </c>
     </row>
     <row r="63">
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>214380000000</v>
+        <v>216190000000</v>
       </c>
     </row>
     <row r="64">
@@ -1446,232 +1446,232 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>202910000000</v>
+        <v>199430000000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>AMGEN Inc</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>198910000000</v>
+        <v>195440000000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>AMGEN Inc</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>194590000000</v>
+        <v>194770000000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>McDonald's Corp</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>189830000000</v>
+        <v>194270000000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PepsiCo Inc</t>
+          <t>McDonald's Corp</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>189540000000</v>
+        <v>192060000000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>Thermo Fisher Scientific Inc</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>189120000000</v>
+        <v>186320000000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>T-Mobile US Inc</t>
+          <t>PepsiCo Inc</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>188270000000</v>
+        <v>185060000000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc</t>
+          <t>NextEra Energy Inc</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>188200000000</v>
+        <v>183050000000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NextEra Energy Inc</t>
+          <t>T-Mobile US Inc</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>184910000000</v>
+        <v>181520000000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc</t>
+          <t>Sap SE ADR</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>184140000000</v>
+        <v>179930000000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Sap SE ADR</t>
+          <t>Verizon Communications Inc</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>180850000000</v>
+        <v>176790000000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>172520000000</v>
+        <v>173090000000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Walt Disney Co</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>171270000000</v>
+        <v>172720000000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Boeing Co</t>
+          <t>Deere &amp; Co</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>169240000000</v>
+        <v>171230000000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Deere &amp; Co</t>
+          <t>Boeing Co</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>169150000000</v>
+        <v>170640000000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>Walt Disney Co</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>167550000000</v>
+        <v>167140000000</v>
       </c>
     </row>
     <row r="80">
@@ -1686,37 +1686,37 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>162320000000</v>
+        <v>160980000000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Charles Schwab Corp</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>161480000000</v>
+        <v>160470000000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Charles Schwab Corp</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>157480000000</v>
+        <v>158050000000</v>
       </c>
     </row>
     <row r="83">
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>156850000000</v>
+        <v>156860000000</v>
       </c>
     </row>
     <row r="84">
@@ -1746,97 +1746,97 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>154730000000</v>
+        <v>156580000000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Uber Technologies Inc</t>
+          <t>Shopify Inc</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>153690000000</v>
+        <v>148170000000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc</t>
+          <t>Uber Technologies Inc</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>151610000000</v>
+        <v>146890000000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Shopify Inc</t>
+          <t>AT&amp;T Inc</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>148200000000</v>
+        <v>143830000000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Intuitive Surgical Inc</t>
+          <t>Blackstone Inc</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>143780000000</v>
+        <v>143740000000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>Intuitive Surgical Inc</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>141350000000</v>
+        <v>140840000000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Blackstone Inc</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>140330000000</v>
+        <v>138110000000</v>
       </c>
     </row>
     <row r="91">
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>136440000000</v>
+        <v>134820000000</v>
       </c>
     </row>
     <row r="92">
@@ -1866,22 +1866,22 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>133150000000</v>
+        <v>132160000000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>129490000000</v>
+        <v>128610000000</v>
       </c>
     </row>
     <row r="94">
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>129340000000</v>
+        <v>128300000000</v>
       </c>
     </row>
     <row r="95">
@@ -1911,22 +1911,22 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>128470000000</v>
+        <v>127650000000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Altria Group Inc</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>123660000000</v>
+        <v>126300000000</v>
       </c>
     </row>
     <row r="97">
@@ -1941,7 +1941,7 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>123160000000</v>
+        <v>123630000000</v>
       </c>
     </row>
     <row r="98">
@@ -1956,67 +1956,67 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>120930000000</v>
+        <v>120550000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Co</t>
+          <t>Altria Group Inc</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>119580000000</v>
+        <v>120150000000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Starbucks Corp</t>
+          <t>Bristol-Myers Squibb Co</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>118600000000</v>
+        <v>117660000000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>Lockheed Martin Corp</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>117910000000</v>
+        <v>117460000000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corp</t>
+          <t>Starbucks Corp</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>115760000000</v>
+        <v>116470000000</v>
       </c>
     </row>
     <row r="103">
@@ -2031,7 +2031,7 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>108950000000</v>
+        <v>108580000000</v>
       </c>
     </row>
     <row r="104">
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>107020000000</v>
+        <v>102800000000</v>
       </c>
     </row>
     <row r="105">
@@ -2061,7 +2061,7 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>103590000000</v>
+        <v>100140000000</v>
       </c>
     </row>
     <row r="106">
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>95150000000</v>
+        <v>94500000000</v>
       </c>
     </row>
     <row r="107">
@@ -2091,82 +2091,82 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>95120000000</v>
+        <v>93760000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>United Parcel Service Inc</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>91810000000</v>
+        <v>92680000000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc</t>
+          <t>United Parcel Service Inc</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>89930000000</v>
+        <v>91380000000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Airbnb Inc</t>
+          <t>Automatic Data Processing Inc</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>88700000000</v>
+        <v>89520000000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>Snowflake Inc</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>88480000000</v>
+        <v>88210000000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Snowflake Inc</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>87220000000</v>
+        <v>87100000000</v>
       </c>
     </row>
     <row r="113">
@@ -2181,52 +2181,52 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>87030000000</v>
+        <v>86490000000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>Airbnb Inc</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>86560000000</v>
+        <v>86250000000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>MercadoLibre Inc</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>86210000000</v>
+        <v>86050000000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>MercadoLibre Inc</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>85330000000</v>
+        <v>85160000000</v>
       </c>
     </row>
     <row r="117">
@@ -2241,7 +2241,7 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>84720000000</v>
+        <v>84450000000</v>
       </c>
     </row>
     <row r="118">
@@ -2256,52 +2256,52 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>84270000000</v>
+        <v>83980000000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>Astera Labs Inc</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>82060000000</v>
+        <v>82790000000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>MMC</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Marsh</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>80320000000</v>
+        <v>81500000000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>MMC</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Astera Labs Inc</t>
+          <t>Marsh</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>78160000000</v>
+        <v>80300000000</v>
       </c>
     </row>
     <row r="122">
@@ -2316,7 +2316,7 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>76330000000</v>
+        <v>76150000000</v>
       </c>
     </row>
     <row r="123">
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>73940000000</v>
+        <v>73360000000</v>
       </c>
     </row>
     <row r="124">
@@ -2346,63 +2346,63 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>73740000000</v>
+        <v>72930000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Intuit Inc</t>
+          <t>Northrop Grumman Corp</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>72870000000</v>
+        <v>72340000000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp</t>
+          <t>Intuit Inc</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>70450000000</v>
+        <v>71390000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>General Motors Company</t>
+          <t>Intercontinental Exchange Inc</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>69730000000</v>
+        <v>69620000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange Inc</t>
+          <t>SLB Ltd</t>
         </is>
       </c>
       <c r="L128" t="n">
@@ -2412,31 +2412,31 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SLB Ltd</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>69340000000</v>
+        <v>69500000000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals Inc</t>
+          <t>General Motors Company</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>66240000000</v>
+        <v>69500000000</v>
       </c>
     </row>
     <row r="131">
@@ -2451,37 +2451,37 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>66200000000</v>
+        <v>68210000000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Ferrari NV</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>65720000000</v>
+        <v>65710000000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Ferrari NV</t>
+          <t>Regeneron Pharmaceuticals Inc</t>
         </is>
       </c>
       <c r="L133" t="n">
-        <v>65020000000</v>
+        <v>65370000000</v>
       </c>
     </row>
     <row r="134">
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>63820000000</v>
+        <v>64940000000</v>
       </c>
     </row>
     <row r="135">
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>61430000000</v>
+        <v>60790000000</v>
       </c>
     </row>
     <row r="136">
@@ -2526,7 +2526,7 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>60830000000</v>
+        <v>59320000000</v>
       </c>
     </row>
     <row r="137">
@@ -2541,7 +2541,7 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>56730000000</v>
+        <v>58840000000</v>
       </c>
     </row>
     <row r="138">
@@ -2556,67 +2556,67 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>55870000000</v>
+        <v>55390000000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Vistra Corp</t>
+          <t>Sea Ltd ADR</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>54750000000</v>
+        <v>54330000000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Sea Ltd ADR</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>52700000000</v>
+        <v>54310000000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences Corp</t>
+          <t>Vistra Corp</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>52500000000</v>
+        <v>53490000000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Edwards Lifesciences Corp</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>52110000000</v>
+        <v>52090000000</v>
       </c>
     </row>
     <row r="143">
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>48830000000</v>
+        <v>48310000000</v>
       </c>
     </row>
     <row r="144">
@@ -2646,7 +2646,7 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>46440000000</v>
+        <v>45230000000</v>
       </c>
     </row>
     <row r="145">
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>42290000000</v>
+        <v>43610000000</v>
       </c>
     </row>
     <row r="146">
@@ -2676,7 +2676,7 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>41200000000</v>
+        <v>41020000000</v>
       </c>
     </row>
     <row r="147">
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>40620000000</v>
+        <v>40770000000</v>
       </c>
     </row>
     <row r="148">
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>40380000000</v>
+        <v>39130000000</v>
       </c>
     </row>
     <row r="149">
@@ -2721,7 +2721,7 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>39950000000</v>
+        <v>38520000000</v>
       </c>
     </row>
     <row r="150">
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>39150000000</v>
+        <v>38090000000</v>
       </c>
     </row>
     <row r="151">
@@ -2751,52 +2751,52 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>33570000000</v>
+        <v>33420000000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Strategy Inc</t>
+          <t>Twilio Inc</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>32480000000</v>
+        <v>31320000000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Zoetis Inc</t>
+          <t>JD.com Inc ADR</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>30710000000</v>
+        <v>30910000000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>JD</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>JD.com Inc ADR</t>
+          <t>Strategy Inc</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>30630000000</v>
+        <v>30460000000</v>
       </c>
     </row>
     <row r="155">
@@ -2811,22 +2811,22 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>30520000000</v>
+        <v>30240000000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Twilio Inc</t>
+          <t>Zoetis Inc</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>30170000000</v>
+        <v>30130000000</v>
       </c>
     </row>
     <row r="157">
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>28720000000</v>
+        <v>28560000000</v>
       </c>
     </row>
     <row r="158">
@@ -2856,37 +2856,37 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>27660000000</v>
+        <v>27790000000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>AFRM</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Illumina Inc</t>
+          <t>Affirm Holdings Inc</t>
         </is>
       </c>
       <c r="L159" t="n">
-        <v>27400000000</v>
+        <v>27310000000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>AFRM</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Affirm Holdings Inc</t>
+          <t>Illumina Inc</t>
         </is>
       </c>
       <c r="L160" t="n">
-        <v>27390000000</v>
+        <v>26600000000</v>
       </c>
     </row>
     <row r="161">
@@ -2901,37 +2901,37 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>26040000000</v>
+        <v>26160000000</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ZM</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Zoom Communications Inc</t>
+          <t>First Solar Inc</t>
         </is>
       </c>
       <c r="L162" t="n">
-        <v>25260000000</v>
+        <v>25350000000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>ZM</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>First Solar Inc</t>
+          <t>Zoom Communications Inc</t>
         </is>
       </c>
       <c r="L163" t="n">
-        <v>25020000000</v>
+        <v>25310000000</v>
       </c>
     </row>
     <row r="164">
@@ -2946,37 +2946,37 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>23330000000</v>
+        <v>23000000000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>DKNG</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>DraftKings Inc</t>
+          <t>Zscaler Inc</t>
         </is>
       </c>
       <c r="L165" t="n">
-        <v>22940000000</v>
+        <v>22830000000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>DKNG</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Zscaler Inc</t>
+          <t>DraftKings Inc</t>
         </is>
       </c>
       <c r="L166" t="n">
-        <v>22250000000</v>
+        <v>22460000000</v>
       </c>
     </row>
     <row r="167">
@@ -2991,82 +2991,82 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>20250000000</v>
+        <v>20490000000</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Charter Communications Inc</t>
+          <t>IonQ Inc</t>
         </is>
       </c>
       <c r="L168" t="n">
-        <v>20240000000</v>
+        <v>19880000000</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>IonQ Inc</t>
+          <t>Charter Communications Inc</t>
         </is>
       </c>
       <c r="L169" t="n">
-        <v>20110000000</v>
+        <v>19700000000</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>CRCL</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Circle Internet Group Inc</t>
+          <t>Super Micro Computer Inc</t>
         </is>
       </c>
       <c r="L170" t="n">
-        <v>18880000000</v>
+        <v>18970000000</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Super Micro Computer Inc</t>
+          <t>IREN Ltd</t>
         </is>
       </c>
       <c r="L171" t="n">
-        <v>18210000000</v>
+        <v>16320000000</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>IREN Ltd</t>
+          <t>Circle Internet Group Inc</t>
         </is>
       </c>
       <c r="L172" t="n">
-        <v>16380000000</v>
+        <v>15570000000</v>
       </c>
     </row>
     <row r="173">
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>15330000000</v>
+        <v>15450000000</v>
       </c>
     </row>
     <row r="174">
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>15330000000</v>
+        <v>15450000000</v>
       </c>
     </row>
     <row r="175">
@@ -3111,37 +3111,37 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>12740000000</v>
+        <v>12700000000</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>PINS</t>
+          <t>BROS</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Pinterest Inc</t>
+          <t>Dutch Bros Inc</t>
         </is>
       </c>
       <c r="L176" t="n">
-        <v>12260000000</v>
+        <v>11830000000</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>BROS</t>
+          <t>PINS</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Dutch Bros Inc</t>
+          <t>Pinterest Inc</t>
         </is>
       </c>
       <c r="L177" t="n">
-        <v>11810000000</v>
+        <v>11780000000</v>
       </c>
     </row>
     <row r="178">
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>10790000000</v>
+        <v>10660000000</v>
       </c>
     </row>
     <row r="179">
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>9180000000</v>
+        <v>9100000000</v>
       </c>
     </row>
     <row r="180">
@@ -3186,7 +3186,7 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>8980000000</v>
+        <v>8870000000</v>
       </c>
     </row>
     <row r="181">
@@ -3201,82 +3201,82 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>8880000000</v>
+        <v>8600000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>HIMS</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Hims &amp; Hers Health Inc</t>
+          <t>AeroVironment Inc</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>7730000000</v>
+        <v>8240000000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>MBLY</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Celsius Holdings Inc</t>
+          <t>Mobileye Global Inc</t>
         </is>
       </c>
       <c r="L183" t="n">
-        <v>7620000000</v>
+        <v>8150000000</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>HIMS</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Zillow Group Inc</t>
+          <t>Hims &amp; Hers Health Inc</t>
         </is>
       </c>
       <c r="L184" t="n">
-        <v>7180000000</v>
+        <v>8020000000</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>MBLY</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Mobileye Global Inc</t>
+          <t>Celsius Holdings Inc</t>
         </is>
       </c>
       <c r="L185" t="n">
-        <v>6990000000</v>
+        <v>7490000000</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>AeroVironment Inc</t>
+          <t>Zillow Group Inc</t>
         </is>
       </c>
       <c r="L186" t="n">
-        <v>6940000000</v>
+        <v>7210000000</v>
       </c>
     </row>
     <row r="187">
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>6460000000</v>
+        <v>6420000000</v>
       </c>
     </row>
     <row r="188">
@@ -3306,37 +3306,37 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>5740000000</v>
+        <v>5820000000</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>CRSP</t>
+          <t>MARA</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>CRISPR Therapeutics AG</t>
+          <t>MARA Holdings Inc</t>
         </is>
       </c>
       <c r="L189" t="n">
-        <v>5430000000</v>
+        <v>5300000000</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>MARA</t>
+          <t>CRSP</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>MARA Holdings Inc</t>
+          <t>CRISPR Therapeutics AG</t>
         </is>
       </c>
       <c r="L190" t="n">
-        <v>5350000000</v>
+        <v>5260000000</v>
       </c>
     </row>
     <row r="191">
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>4780000000</v>
+        <v>5000000000</v>
       </c>
     </row>
     <row r="192">
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>4170000000</v>
+        <v>4290000000</v>
       </c>
     </row>
     <row r="193">
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3750000000</v>
+        <v>3670000000</v>
       </c>
     </row>
     <row r="194">
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3530000000</v>
+        <v>3660000000</v>
       </c>
     </row>
     <row r="195">
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>3350000000</v>
+        <v>3390000000</v>
       </c>
     </row>
     <row r="196">
@@ -3426,37 +3426,37 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>3150000000</v>
+        <v>3300000000</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>PENN</t>
+          <t>FSLY</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>PENN Entertainment Inc</t>
+          <t>Fastly Inc</t>
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2950000000</v>
+        <v>2870000000</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>FSLY</t>
+          <t>PENN</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Fastly Inc</t>
+          <t>PENN Entertainment Inc</t>
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2820000000</v>
+        <v>2860000000</v>
       </c>
     </row>
     <row r="199">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>2330000000</v>
+        <v>2300000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>2240000000</v>
+        <v>2190000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1570000000</v>
+        <v>1530000000</v>
       </c>
     </row>
     <row r="202">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1380000000</v>
+        <v>1410000000</v>
       </c>
     </row>
     <row r="203">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>1110000000</v>
+        <v>1100000000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>919070000</v>
+        <v>1070000000</v>
       </c>
     </row>
     <row r="205">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4249930000000</v>
+        <v>4323660000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4842180000000</v>
+        <v>4781440000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4296860000000</v>
+        <v>4363490000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2770950000000</v>
+        <v>2854600000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2563850000000</v>
+        <v>2599990000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2476910000000</v>
+        <v>2303990000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1797180000000</v>
+        <v>1757160000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1579660000000</v>
+        <v>1597310000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1429870000000</v>
+        <v>1555820000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1303650000000</v>
+        <v>1165850000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1129550000000</v>
+        <v>1122310000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,52 +726,52 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1079020000000</v>
+        <v>1076990000000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices Inc</t>
+          <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>947230000000</v>
+        <v>895140000000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Walmart Inc</t>
+          <t>Advanced Micro Devices Inc</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>901330000000</v>
+        <v>881960000000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co</t>
+          <t>Walmart Inc</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>877080000000</v>
+        <v>866000000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>766770000000</v>
+        <v>710340000000</v>
       </c>
     </row>
     <row r="21">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>646420000000</v>
+        <v>661480000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,37 +816,37 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>611360000000</v>
+        <v>611380000000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Applied Materials Inc</t>
+          <t>Exxon Mobil Corp</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>574030000000</v>
+        <v>564870000000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Exxon Mobil Corp</t>
+          <t>Applied Materials Inc</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>566700000000</v>
+        <v>516800000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,22 +861,22 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>541910000000</v>
+        <v>489300000000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Caterpillar Inc</t>
+          <t>Mastercard Incorporated</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>490530000000</v>
+        <v>461620000000</v>
       </c>
     </row>
     <row r="27">
@@ -891,22 +891,22 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>462960000000</v>
+        <v>461190000000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated</t>
+          <t>Caterpillar Inc</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>453810000000</v>
+        <v>456680000000</v>
       </c>
     </row>
     <row r="29">
@@ -921,142 +921,142 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>444600000000</v>
+        <v>443570000000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Oracle Corp</t>
+          <t>Bank Of America Corp</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>422130000000</v>
+        <v>414160000000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Costco Wholesale Corp</t>
+          <t>Oracle Corp</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>414860000000</v>
+        <v>410470000000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Bank Of America Corp</t>
+          <t>Costco Wholesale Corp</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>404360000000</v>
+        <v>410070000000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>KLA Corp</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>394120000000</v>
+        <v>391190000000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Unitedhealth Group Inc</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>389930000000</v>
+        <v>387360000000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Unitedhealth Group Inc</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>377450000000</v>
+        <v>359070000000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>Home Depot Inc</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>377260000000</v>
+        <v>349830000000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Home Depot Inc</t>
+          <t>Coca-Cola Co</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>351660000000</v>
+        <v>349750000000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Coca-Cola Co</t>
+          <t>KLA Corp</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>349660000000</v>
+        <v>347720000000</v>
       </c>
     </row>
     <row r="39">
@@ -1071,22 +1071,22 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>341470000000</v>
+        <v>343310000000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>336720000000</v>
+        <v>334160000000</v>
       </c>
     </row>
     <row r="41">
@@ -1101,22 +1101,22 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>330130000000</v>
+        <v>329990000000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Netflix Inc</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>329720000000</v>
+        <v>312400000000</v>
       </c>
     </row>
     <row r="43">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>317370000000</v>
+        <v>309640000000</v>
       </c>
     </row>
     <row r="44">
@@ -1146,127 +1146,127 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>315710000000</v>
+        <v>304820000000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Netflix Inc</t>
+          <t>Palantir Technologies Inc</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>300650000000</v>
+        <v>301410000000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Goldman Sachs Group Inc</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>298360000000</v>
+        <v>300950000000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Astrazeneca plc</t>
+          <t>Goldman Sachs Group Inc</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>294070000000</v>
+        <v>300790000000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>NVS</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Novartis AG ADR</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>286880000000</v>
+        <v>286910000000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Philip Morris International Inc</t>
+          <t>Astrazeneca plc</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>281960000000</v>
+        <v>285140000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>NVS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>Novartis AG ADR</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>279710000000</v>
+        <v>282160000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc</t>
+          <t>Philip Morris International Inc</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>279690000000</v>
+        <v>276940000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>277930000000</v>
+        <v>275680000000</v>
       </c>
     </row>
     <row r="53">
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>271270000000</v>
+        <v>271580000000</v>
       </c>
     </row>
     <row r="54">
@@ -1296,37 +1296,37 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>264310000000</v>
+        <v>269040000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Wells Fargo &amp; Co</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>255510000000</v>
+        <v>262990000000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Co</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>252890000000</v>
+        <v>258270000000</v>
       </c>
     </row>
     <row r="57">
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>240060000000</v>
+        <v>246820000000</v>
       </c>
     </row>
     <row r="58">
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>240020000000</v>
+        <v>240310000000</v>
       </c>
     </row>
     <row r="59">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>230800000000</v>
+        <v>237450000000</v>
       </c>
     </row>
     <row r="60">
@@ -1386,67 +1386,67 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>230420000000</v>
+        <v>235250000000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>Shell Plc ADR</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>220160000000</v>
+        <v>213480000000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Corning Inc</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>219830000000</v>
+        <v>206250000000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Shell Plc ADR</t>
+          <t>Toyota Motor Corp ADR</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>216190000000</v>
+        <v>200900000000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Toyota Motor Corp ADR</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>199430000000</v>
+        <v>196710000000</v>
       </c>
     </row>
     <row r="65">
@@ -1461,37 +1461,37 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>195440000000</v>
+        <v>195010000000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>PepsiCo Inc</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>194770000000</v>
+        <v>192930000000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>194270000000</v>
+        <v>191740000000</v>
       </c>
     </row>
     <row r="68">
@@ -1506,7 +1506,7 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>192060000000</v>
+        <v>191430000000</v>
       </c>
     </row>
     <row r="69">
@@ -1521,37 +1521,37 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>186320000000</v>
+        <v>190760000000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PepsiCo Inc</t>
+          <t>Corning Inc</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>185060000000</v>
+        <v>189880000000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NextEra Energy Inc</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>183050000000</v>
+        <v>189680000000</v>
       </c>
     </row>
     <row r="72">
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>181520000000</v>
+        <v>187290000000</v>
       </c>
     </row>
     <row r="73">
@@ -1581,52 +1581,52 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>179930000000</v>
+        <v>185820000000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc</t>
+          <t>NextEra Energy Inc</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>176790000000</v>
+        <v>180130000000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>Verizon Communications Inc</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>173090000000</v>
+        <v>175330000000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Boeing Co</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>172720000000</v>
+        <v>172310000000</v>
       </c>
     </row>
     <row r="77">
@@ -1641,67 +1641,67 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>171230000000</v>
+        <v>169420000000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Boeing Co</t>
+          <t>Charles Schwab Corp</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>170640000000</v>
+        <v>166570000000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Walt Disney Co</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>167140000000</v>
+        <v>166560000000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Novo Nordisk ADR</t>
+          <t>Walt Disney Co</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>160980000000</v>
+        <v>166200000000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Charles Schwab Corp</t>
+          <t>Novo Nordisk ADR</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>160470000000</v>
+        <v>163770000000</v>
       </c>
     </row>
     <row r="82">
@@ -1716,52 +1716,52 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>158050000000</v>
+        <v>160560000000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>Blackrock Inc</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>156860000000</v>
+        <v>159650000000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Blackrock Inc</t>
+          <t>Shopify Inc</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>156580000000</v>
+        <v>157830000000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Shopify Inc</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>148170000000</v>
+        <v>156400000000</v>
       </c>
     </row>
     <row r="86">
@@ -1776,52 +1776,52 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>146890000000</v>
+        <v>147910000000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc</t>
+          <t>Blackstone Inc</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>143830000000</v>
+        <v>146030000000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Blackstone Inc</t>
+          <t>Intuitive Surgical Inc</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>143740000000</v>
+        <v>142510000000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Intuitive Surgical Inc</t>
+          <t>AT&amp;T Inc</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>140840000000</v>
+        <v>142300000000</v>
       </c>
     </row>
     <row r="90">
@@ -1836,7 +1836,7 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>138110000000</v>
+        <v>141520000000</v>
       </c>
     </row>
     <row r="91">
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>134820000000</v>
+        <v>137110000000</v>
       </c>
     </row>
     <row r="92">
@@ -1866,52 +1866,52 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>132160000000</v>
+        <v>136420000000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>Salesforce Inc</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>128610000000</v>
+        <v>133690000000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Salesforce Inc</t>
+          <t>Progressive Corp</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>128300000000</v>
+        <v>131650000000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Progressive Corp</t>
+          <t>S&amp;P Global Inc</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>127650000000</v>
+        <v>129860000000</v>
       </c>
     </row>
     <row r="96">
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>126300000000</v>
+        <v>127540000000</v>
       </c>
     </row>
     <row r="97">
@@ -1941,127 +1941,127 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>123630000000</v>
+        <v>124430000000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>S&amp;P Global Inc</t>
+          <t>Lockheed Martin Corp</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>120550000000</v>
+        <v>120310000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Altria Group Inc</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>120150000000</v>
+        <v>119620000000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Co</t>
+          <t>Altria Group Inc</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>117660000000</v>
+        <v>119460000000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corp</t>
+          <t>Starbucks Corp</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>117460000000</v>
+        <v>117830000000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Starbucks Corp</t>
+          <t>PDD Holdings Inc ADR</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>116470000000</v>
+        <v>117460000000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PDD Holdings Inc ADR</t>
+          <t>Bristol-Myers Squibb Co</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>108580000000</v>
+        <v>115250000000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Equinix Inc</t>
+          <t>Medtronic Plc</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>102800000000</v>
+        <v>101380000000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Medtronic Plc</t>
+          <t>Equinix Inc</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>100140000000</v>
+        <v>99970000000</v>
       </c>
     </row>
     <row r="106">
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>94500000000</v>
+        <v>97250000000</v>
       </c>
     </row>
     <row r="107">
@@ -2091,52 +2091,52 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>93760000000</v>
+        <v>96180000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>Automatic Data Processing Inc</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>92680000000</v>
+        <v>94230000000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>United Parcel Service Inc</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>91380000000</v>
+        <v>94140000000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc</t>
+          <t>United Parcel Service Inc</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>89520000000</v>
+        <v>93110000000</v>
       </c>
     </row>
     <row r="111">
@@ -2151,217 +2151,217 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>88210000000</v>
+        <v>90530000000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>Elevance Health Inc</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>87100000000</v>
+        <v>90380000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>HCA Healthcare Inc</t>
+          <t>Airbnb Inc</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>86490000000</v>
+        <v>88780000000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Airbnb Inc</t>
+          <t>MercadoLibre Inc</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>86250000000</v>
+        <v>88320000000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>MercadoLibre Inc</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>86050000000</v>
+        <v>87470000000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>HCA Healthcare Inc</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>85160000000</v>
+        <v>87240000000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>3M Co</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>84450000000</v>
+        <v>83860000000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Elevance Health Inc</t>
+          <t>3M Co</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>83980000000</v>
+        <v>83430000000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>MMC</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Astera Labs Inc</t>
+          <t>Marsh</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>82790000000</v>
+        <v>82940000000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>81500000000</v>
+        <v>82150000000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>MMC</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Marsh</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>80300000000</v>
+        <v>80240000000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>Colgate-Palmolive Co</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>76150000000</v>
+        <v>74230000000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive Co</t>
+          <t>Astera Labs Inc</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>73360000000</v>
+        <v>73850000000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Cigna Group</t>
+          <t>Northrop Grumman Corp</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>72930000000</v>
+        <v>73850000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp</t>
+          <t>Cigna Group</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>72340000000</v>
+        <v>73290000000</v>
       </c>
     </row>
     <row r="126">
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>71390000000</v>
+        <v>73060000000</v>
       </c>
     </row>
     <row r="127">
@@ -2391,142 +2391,142 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>69620000000</v>
+        <v>71670000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SLB Ltd</t>
+          <t>Apollo Global Management Inc</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>69510000000</v>
+        <v>68280000000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>General Motors Company</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>69500000000</v>
+        <v>68090000000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>General Motors Company</t>
+          <t>SLB Ltd</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>69500000000</v>
+        <v>67410000000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Apollo Global Management Inc</t>
+          <t>Ferrari NV</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>68210000000</v>
+        <v>66130000000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Ferrari NV</t>
+          <t>Regeneron Pharmaceuticals Inc</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>65710000000</v>
+        <v>65500000000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals Inc</t>
+          <t>Nu Holdings Ltd</t>
         </is>
       </c>
       <c r="L133" t="n">
-        <v>65370000000</v>
+        <v>65080000000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>NU</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Nu Holdings Ltd</t>
+          <t>Nike Inc</t>
         </is>
       </c>
       <c r="L134" t="n">
-        <v>64940000000</v>
+        <v>63770000000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Nike Inc</t>
+          <t>Target Corp</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>60790000000</v>
+        <v>59180000000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Target Corp</t>
+          <t>Sea Ltd ADR</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>59320000000</v>
+        <v>58020000000</v>
       </c>
     </row>
     <row r="137">
@@ -2541,52 +2541,52 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>58840000000</v>
+        <v>57930000000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Ford Motor Co</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L138" t="n">
-        <v>55390000000</v>
+        <v>57670000000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Sea Ltd ADR</t>
+          <t>Ford Motor Co</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>54330000000</v>
+        <v>54350000000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Edwards Lifesciences Corp</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>54310000000</v>
+        <v>52970000000</v>
       </c>
     </row>
     <row r="141">
@@ -2601,37 +2601,37 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>53490000000</v>
+        <v>51640000000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences Corp</t>
+          <t>Occidental Petroleum Corp</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>52090000000</v>
+        <v>47680000000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Occidental Petroleum Corp</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>48310000000</v>
+        <v>46750000000</v>
       </c>
     </row>
     <row r="144">
@@ -2646,7 +2646,7 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>45230000000</v>
+        <v>45910000000</v>
       </c>
     </row>
     <row r="145">
@@ -2661,67 +2661,67 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>43610000000</v>
+        <v>44900000000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Autodesk Inc</t>
+          <t>MSCI Inc</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>41020000000</v>
+        <v>42370000000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MSCI Inc</t>
+          <t>Autodesk Inc</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>40770000000</v>
+        <v>42150000000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Carnival Corp Ltd</t>
+          <t>Coinbase Global Inc</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>39130000000</v>
+        <v>41950000000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Coinbase Global Inc</t>
+          <t>Carnival Corp Ltd</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>38520000000</v>
+        <v>39060000000</v>
       </c>
     </row>
     <row r="150">
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>38090000000</v>
+        <v>38870000000</v>
       </c>
     </row>
     <row r="151">
@@ -2751,67 +2751,67 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>33420000000</v>
+        <v>38070000000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Twilio Inc</t>
+          <t>Strategy Inc</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>31320000000</v>
+        <v>32730000000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>JD</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>JD.com Inc ADR</t>
+          <t>Workday Inc</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>30910000000</v>
+        <v>32180000000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Strategy Inc</t>
+          <t>JD.com Inc ADR</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>30460000000</v>
+        <v>31920000000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Workday Inc</t>
+          <t>Twilio Inc</t>
         </is>
       </c>
       <c r="L155" t="n">
-        <v>30240000000</v>
+        <v>31760000000</v>
       </c>
     </row>
     <row r="156">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>30130000000</v>
+        <v>30370000000</v>
       </c>
     </row>
     <row r="157">
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>28560000000</v>
+        <v>29840000000</v>
       </c>
     </row>
     <row r="158">
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>27790000000</v>
+        <v>28770000000</v>
       </c>
     </row>
     <row r="159">
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>27310000000</v>
+        <v>28080000000</v>
       </c>
     </row>
     <row r="160">
@@ -2886,7 +2886,7 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>26600000000</v>
+        <v>27820000000</v>
       </c>
     </row>
     <row r="161">
@@ -2901,67 +2901,67 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>26160000000</v>
+        <v>27050000000</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>ZM</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>First Solar Inc</t>
+          <t>Zoom Communications Inc</t>
         </is>
       </c>
       <c r="L162" t="n">
-        <v>25350000000</v>
+        <v>26430000000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ZM</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Zoom Communications Inc</t>
+          <t>First Solar Inc</t>
         </is>
       </c>
       <c r="L163" t="n">
-        <v>25310000000</v>
+        <v>24940000000</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>SoFi Technologies Inc</t>
+          <t>Zscaler Inc</t>
         </is>
       </c>
       <c r="L164" t="n">
-        <v>23000000000</v>
+        <v>23680000000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Zscaler Inc</t>
+          <t>SoFi Technologies Inc</t>
         </is>
       </c>
       <c r="L165" t="n">
-        <v>22830000000</v>
+        <v>23650000000</v>
       </c>
     </row>
     <row r="166">
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>22460000000</v>
+        <v>22910000000</v>
       </c>
     </row>
     <row r="167">
@@ -2991,37 +2991,37 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>20490000000</v>
+        <v>20840000000</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>IonQ Inc</t>
+          <t>Charter Communications Inc</t>
         </is>
       </c>
       <c r="L168" t="n">
-        <v>19880000000</v>
+        <v>19370000000</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Charter Communications Inc</t>
+          <t>IonQ Inc</t>
         </is>
       </c>
       <c r="L169" t="n">
-        <v>19700000000</v>
+        <v>19190000000</v>
       </c>
     </row>
     <row r="170">
@@ -3036,67 +3036,67 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>18970000000</v>
+        <v>17890000000</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>GRAB</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>IREN Ltd</t>
+          <t>Grab Holdings Limited</t>
         </is>
       </c>
       <c r="L171" t="n">
-        <v>16320000000</v>
+        <v>15940000000</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>CRCL</t>
+          <t>GRAB</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Circle Internet Group Inc</t>
+          <t>Grab Holdings Limited</t>
         </is>
       </c>
       <c r="L172" t="n">
-        <v>15570000000</v>
+        <v>15940000000</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>GRAB</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Grab Holdings Limited</t>
+          <t>IREN Ltd</t>
         </is>
       </c>
       <c r="L173" t="n">
-        <v>15450000000</v>
+        <v>15460000000</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>GRAB</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Grab Holdings Limited</t>
+          <t>Circle Internet Group Inc</t>
         </is>
       </c>
       <c r="L174" t="n">
-        <v>15450000000</v>
+        <v>15400000000</v>
       </c>
     </row>
     <row r="175">
@@ -3111,37 +3111,37 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>12700000000</v>
+        <v>12590000000</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>BROS</t>
+          <t>PINS</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Dutch Bros Inc</t>
+          <t>Pinterest Inc</t>
         </is>
       </c>
       <c r="L176" t="n">
-        <v>11830000000</v>
+        <v>12260000000</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>PINS</t>
+          <t>BROS</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Pinterest Inc</t>
+          <t>Dutch Bros Inc</t>
         </is>
       </c>
       <c r="L177" t="n">
-        <v>11780000000</v>
+        <v>12080000000</v>
       </c>
     </row>
     <row r="178">
@@ -3156,52 +3156,52 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>10660000000</v>
+        <v>10150000000</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>OKLO</t>
+          <t>OSCR</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Oklo Inc</t>
+          <t>Oscar Health Inc</t>
         </is>
       </c>
       <c r="L179" t="n">
-        <v>9100000000</v>
+        <v>9620000000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>PRMB</t>
+          <t>OKLO</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Primo Brands Corp</t>
+          <t>Oklo Inc</t>
         </is>
       </c>
       <c r="L180" t="n">
-        <v>8870000000</v>
+        <v>9130000000</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>OSCR</t>
+          <t>PRMB</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Oscar Health Inc</t>
+          <t>Primo Brands Corp</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>8600000000</v>
+        <v>8900000000</v>
       </c>
     </row>
     <row r="182">
@@ -3216,52 +3216,52 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>8240000000</v>
+        <v>8730000000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>MBLY</t>
+          <t>HIMS</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Mobileye Global Inc</t>
+          <t>Hims &amp; Hers Health Inc</t>
         </is>
       </c>
       <c r="L183" t="n">
-        <v>8150000000</v>
+        <v>8700000000</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>HIMS</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Hims &amp; Hers Health Inc</t>
+          <t>Celsius Holdings Inc</t>
         </is>
       </c>
       <c r="L184" t="n">
-        <v>8020000000</v>
+        <v>8150000000</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>MBLY</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Celsius Holdings Inc</t>
+          <t>Mobileye Global Inc</t>
         </is>
       </c>
       <c r="L185" t="n">
-        <v>7490000000</v>
+        <v>8140000000</v>
       </c>
     </row>
     <row r="186">
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>7210000000</v>
+        <v>7550000000</v>
       </c>
     </row>
     <row r="187">
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>6420000000</v>
+        <v>6210000000</v>
       </c>
     </row>
     <row r="188">
@@ -3306,52 +3306,52 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>5820000000</v>
+        <v>6030000000</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>MARA</t>
+          <t>CRSP</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>MARA Holdings Inc</t>
+          <t>CRISPR Therapeutics AG</t>
         </is>
       </c>
       <c r="L189" t="n">
-        <v>5300000000</v>
+        <v>5360000000</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>CRSP</t>
+          <t>LMND</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>CRISPR Therapeutics AG</t>
+          <t>Lemonade Inc</t>
         </is>
       </c>
       <c r="L190" t="n">
-        <v>5260000000</v>
+        <v>5330000000</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>LMND</t>
+          <t>MARA</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Lemonade Inc</t>
+          <t>MARA Holdings Inc</t>
         </is>
       </c>
       <c r="L191" t="n">
-        <v>5000000000</v>
+        <v>5100000000</v>
       </c>
     </row>
     <row r="192">
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>4290000000</v>
+        <v>4140000000</v>
       </c>
     </row>
     <row r="193">
@@ -3381,37 +3381,37 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3670000000</v>
+        <v>3710000000</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>FLNC</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Fluence Energy Inc</t>
+          <t>Upstart Holdings Inc</t>
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3660000000</v>
+        <v>3420000000</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>FLNC</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Upstart Holdings Inc</t>
+          <t>Fluence Energy Inc</t>
         </is>
       </c>
       <c r="L195" t="n">
-        <v>3390000000</v>
+        <v>3380000000</v>
       </c>
     </row>
     <row r="196">
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>3300000000</v>
+        <v>3270000000</v>
       </c>
     </row>
     <row r="197">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2870000000</v>
+        <v>2900000000</v>
       </c>
     </row>
     <row r="198">
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2860000000</v>
+        <v>2880000000</v>
       </c>
     </row>
     <row r="199">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>2300000000</v>
+        <v>2340000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>2190000000</v>
+        <v>2130000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1530000000</v>
+        <v>1640000000</v>
       </c>
     </row>
     <row r="202">
@@ -3516,37 +3516,37 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1410000000</v>
+        <v>1470000000</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>NNE</t>
+          <t>UMAC</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Nano Nuclear Energy Inc</t>
+          <t>Unusual Machines Inc</t>
         </is>
       </c>
       <c r="L203" t="n">
-        <v>1100000000</v>
+        <v>1110000000</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>UMAC</t>
+          <t>NNE</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Unusual Machines Inc</t>
+          <t>Nano Nuclear Energy Inc</t>
         </is>
       </c>
       <c r="L204" t="n">
-        <v>1070000000</v>
+        <v>1080000000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>783120000</v>
+        <v>776820000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4323660000000</v>
+        <v>4532960000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4781440000000</v>
+        <v>4714890000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4363490000000</v>
+        <v>4337520000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2854600000000</v>
+        <v>2900730000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2599990000000</v>
+        <v>2610430000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2303990000000</v>
+        <v>2251760000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,67 +651,67 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1757160000000</v>
+        <v>1714870000000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tesla Inc</t>
+          <t>Meta Platforms Inc</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1597310000000</v>
+        <v>1479650000000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Meta Platforms Inc</t>
+          <t>Tesla Inc</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1555820000000</v>
+        <v>1477690000000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Micron Technology Inc</t>
+          <t>Lilly(Eli) &amp; Co</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1165850000000</v>
+        <v>1143190000000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lilly(Eli) &amp; Co</t>
+          <t>Micron Technology Inc</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1122310000000</v>
+        <v>1101790000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1076990000000</v>
+        <v>1095920000000</v>
       </c>
     </row>
     <row r="17">
@@ -741,67 +741,67 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>895140000000</v>
+        <v>896220000000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices Inc</t>
+          <t>Walmart Inc</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>881960000000</v>
+        <v>890030000000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Walmart Inc</t>
+          <t>Advanced Micro Devices Inc</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>866000000000</v>
+        <v>844360000000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ASML Holding NV</t>
+          <t>Visa Inc</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>710340000000</v>
+        <v>682300000000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Visa Inc</t>
+          <t>ASML Holding NV</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>661480000000</v>
+        <v>681930000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>611380000000</v>
+        <v>633190000000</v>
       </c>
     </row>
     <row r="23">
@@ -827,11 +827,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Exxon Mobil Corp</t>
+          <t>ExxonMobil Holdings Corp</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>564870000000</v>
+        <v>568230000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,37 +846,37 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>516800000000</v>
+        <v>478790000000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lam Research Corp</t>
+          <t>Mastercard Incorporated</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>489300000000</v>
+        <v>476600000000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated</t>
+          <t>Abbvie Inc</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>461620000000</v>
+        <v>461260000000</v>
       </c>
     </row>
     <row r="27">
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>461190000000</v>
+        <v>444160000000</v>
       </c>
     </row>
     <row r="28">
@@ -906,67 +906,67 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>456680000000</v>
+        <v>443840000000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Abbvie Inc</t>
+          <t>Lam Research Corp</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>443570000000</v>
+        <v>439460000000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Bank Of America Corp</t>
+          <t>Costco Wholesale Corp</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>414160000000</v>
+        <v>422050000000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Oracle Corp</t>
+          <t>Bank Of America Corp</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>410470000000</v>
+        <v>416780000000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Costco Wholesale Corp</t>
+          <t>Oracle Corp</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>410070000000</v>
+        <v>404040000000</v>
       </c>
     </row>
     <row r="33">
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>391190000000</v>
+        <v>393880000000</v>
       </c>
     </row>
     <row r="34">
@@ -996,22 +996,22 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>387360000000</v>
+        <v>386290000000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>Coca-Cola Co</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>359070000000</v>
+        <v>362010000000</v>
       </c>
     </row>
     <row r="36">
@@ -1026,247 +1026,247 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>349830000000</v>
+        <v>356870000000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Coca-Cola Co</t>
+          <t>Procter &amp; Gamble Co</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>349750000000</v>
+        <v>352570000000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>KLA Corp</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>347720000000</v>
+        <v>337430000000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble Co</t>
+          <t>Chevron Corp</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>343310000000</v>
+        <v>336980000000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>334160000000</v>
+        <v>335460000000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Chevron Corp</t>
+          <t>Netflix Inc</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>329990000000</v>
+        <v>326970000000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Netflix Inc</t>
+          <t>Merck &amp; Co Inc</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>312400000000</v>
+        <v>319990000000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Merck &amp; Co Inc</t>
+          <t>Palantir Technologies Inc</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>309640000000</v>
+        <v>309970000000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>KLA Corp</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>304820000000</v>
+        <v>307690000000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc</t>
+          <t>Astrazeneca plc</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>301410000000</v>
+        <v>302650000000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>Goldman Sachs Group Inc</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>300950000000</v>
+        <v>301200000000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Goldman Sachs Group Inc</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>300790000000</v>
+        <v>299110000000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>NVS</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>Novartis AG ADR</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>286910000000</v>
+        <v>292700000000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Astrazeneca plc</t>
+          <t>Philip Morris International Inc</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>285140000000</v>
+        <v>284080000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NVS</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Novartis AG ADR</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>282160000000</v>
+        <v>283670000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Philip Morris International Inc</t>
+          <t>International Business Machines Corp</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>276940000000</v>
+        <v>272120000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>275680000000</v>
+        <v>268330000000</v>
       </c>
     </row>
     <row r="53">
@@ -1281,52 +1281,52 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>271580000000</v>
+        <v>266730000000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>International Business Machines Corp</t>
+          <t>Wells Fargo &amp; Co</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>269040000000</v>
+        <v>261680000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Co</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>262990000000</v>
+        <v>258420000000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>258270000000</v>
+        <v>255630000000</v>
       </c>
     </row>
     <row r="57">
@@ -1341,37 +1341,37 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>246820000000</v>
+        <v>252880000000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Citigroup Inc</t>
+          <t>American Express Co</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>240310000000</v>
+        <v>240150000000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>American Express Co</t>
+          <t>Citigroup Inc</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>237450000000</v>
+        <v>240040000000</v>
       </c>
     </row>
     <row r="60">
@@ -1386,7 +1386,7 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>235250000000</v>
+        <v>230810000000</v>
       </c>
     </row>
     <row r="61">
@@ -1401,67 +1401,67 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>213480000000</v>
+        <v>217530000000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>Toyota Motor Corp ADR</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>206250000000</v>
+        <v>206730000000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Toyota Motor Corp ADR</t>
+          <t>AMGEN Inc</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>200900000000</v>
+        <v>201930000000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>McDonald's Corp</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>196710000000</v>
+        <v>199390000000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>AMGEN Inc</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>195010000000</v>
+        <v>197520000000</v>
       </c>
     </row>
     <row r="66">
@@ -1476,232 +1476,232 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>192930000000</v>
+        <v>197120000000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>Thermo Fisher Scientific Inc</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>191740000000</v>
+        <v>194520000000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>McDonald's Corp</t>
+          <t>T-Mobile US Inc</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>191430000000</v>
+        <v>192110000000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc</t>
+          <t>Sap SE ADR</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>190760000000</v>
+        <v>189830000000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Corning Inc</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>189880000000</v>
+        <v>185780000000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>189680000000</v>
+        <v>185770000000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>T-Mobile US Inc</t>
+          <t>NextEra Energy Inc</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>187290000000</v>
+        <v>184240000000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Sap SE ADR</t>
+          <t>Boeing Co</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>185820000000</v>
+        <v>178540000000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NextEra Energy Inc</t>
+          <t>Verizon Communications Inc</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>180130000000</v>
+        <v>177710000000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>175330000000</v>
+        <v>177060000000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Boeing Co</t>
+          <t>Walt Disney Co</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>172310000000</v>
+        <v>172780000000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Deere &amp; Co</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>169420000000</v>
+        <v>170770000000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Charles Schwab Corp</t>
+          <t>Corning Inc</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>166570000000</v>
+        <v>169360000000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Novo Nordisk ADR</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>166560000000</v>
+        <v>169340000000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Walt Disney Co</t>
+          <t>Charles Schwab Corp</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>166200000000</v>
+        <v>168700000000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Novo Nordisk ADR</t>
+          <t>Deere &amp; Co</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>163770000000</v>
+        <v>167700000000</v>
       </c>
     </row>
     <row r="82">
@@ -1716,52 +1716,52 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>160560000000</v>
+        <v>166170000000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Blackrock Inc</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>159650000000</v>
+        <v>162980000000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Shopify Inc</t>
+          <t>Blackrock Inc</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>157830000000</v>
+        <v>162150000000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>Shopify Inc</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>156400000000</v>
+        <v>155020000000</v>
       </c>
     </row>
     <row r="86">
@@ -1776,67 +1776,67 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>147910000000</v>
+        <v>151510000000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Blackstone Inc</t>
+          <t>Intuitive Surgical Inc</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>146030000000</v>
+        <v>150880000000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Intuitive Surgical Inc</t>
+          <t>Blackstone Inc</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>142510000000</v>
+        <v>149980000000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>142300000000</v>
+        <v>143010000000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>AT&amp;T Inc</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>141520000000</v>
+        <v>143000000000</v>
       </c>
     </row>
     <row r="91">
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>137110000000</v>
+        <v>140090000000</v>
       </c>
     </row>
     <row r="92">
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>136420000000</v>
+        <v>140080000000</v>
       </c>
     </row>
     <row r="93">
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>133690000000</v>
+        <v>136040000000</v>
       </c>
     </row>
     <row r="94">
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>131650000000</v>
+        <v>135690000000</v>
       </c>
     </row>
     <row r="95">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>129860000000</v>
+        <v>130210000000</v>
       </c>
     </row>
     <row r="96">
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>127540000000</v>
+        <v>130000000000</v>
       </c>
     </row>
     <row r="97">
@@ -1941,7 +1941,7 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>124430000000</v>
+        <v>127560000000</v>
       </c>
     </row>
     <row r="98">
@@ -1956,52 +1956,52 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>120310000000</v>
+        <v>125870000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>Altria Group Inc</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>119620000000</v>
+        <v>121420000000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Altria Group Inc</t>
+          <t>Starbucks Corp</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>119460000000</v>
+        <v>118840000000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Starbucks Corp</t>
+          <t>Bristol-Myers Squibb Co</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>117830000000</v>
+        <v>118710000000</v>
       </c>
     </row>
     <row r="102">
@@ -2016,22 +2016,22 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>117460000000</v>
+        <v>117270000000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Co</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>115250000000</v>
+        <v>115440000000</v>
       </c>
     </row>
     <row r="104">
@@ -2046,112 +2046,112 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>101380000000</v>
+        <v>106490000000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Equinix Inc</t>
+          <t>Spotify Technology SA</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>99970000000</v>
+        <v>100030000000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Spotify Technology SA</t>
+          <t>Equinix Inc</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>97250000000</v>
+        <v>98820000000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>Automatic Data Processing Inc</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>96180000000</v>
+        <v>96840000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>94230000000</v>
+        <v>96160000000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>United Parcel Service Inc</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>94140000000</v>
+        <v>94060000000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>United Parcel Service Inc</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>93110000000</v>
+        <v>92680000000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Snowflake Inc</t>
+          <t>HCA Healthcare Inc</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>90530000000</v>
+        <v>91070000000</v>
       </c>
     </row>
     <row r="112">
@@ -2166,247 +2166,247 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>90380000000</v>
+        <v>90750000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Airbnb Inc</t>
+          <t>Snowflake Inc</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>88780000000</v>
+        <v>90170000000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>MercadoLibre Inc</t>
+          <t>Airbnb Inc</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>88320000000</v>
+        <v>89760000000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>MercadoLibre Inc</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>87470000000</v>
+        <v>89400000000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>HCA Healthcare Inc</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>87240000000</v>
+        <v>87340000000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>83860000000</v>
+        <v>86090000000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>MMC</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>3M Co</t>
+          <t>Marsh</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>83430000000</v>
+        <v>86020000000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>MMC</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Marsh</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>82940000000</v>
+        <v>84050000000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>3M Co</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>82150000000</v>
+        <v>83680000000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>80240000000</v>
+        <v>79470000000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive Co</t>
+          <t>Northrop Grumman Corp</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>74230000000</v>
+        <v>77980000000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Astera Labs Inc</t>
+          <t>Cigna Group</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>73850000000</v>
+        <v>76120000000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp</t>
+          <t>Colgate-Palmolive Co</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>73850000000</v>
+        <v>76120000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Cigna Group</t>
+          <t>Intuit Inc</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>73290000000</v>
+        <v>75320000000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Intuit Inc</t>
+          <t>Intercontinental Exchange Inc</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>73060000000</v>
+        <v>75210000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange Inc</t>
+          <t>Astera Labs Inc</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>71670000000</v>
+        <v>69660000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Apollo Global Management Inc</t>
+          <t>Regeneron Pharmaceuticals Inc</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>68280000000</v>
+        <v>68590000000</v>
       </c>
     </row>
     <row r="129">
@@ -2421,22 +2421,22 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>68090000000</v>
+        <v>68530000000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>SLB Ltd</t>
+          <t>Apollo Global Management Inc</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>67410000000</v>
+        <v>68380000000</v>
       </c>
     </row>
     <row r="131">
@@ -2451,22 +2451,22 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>66130000000</v>
+        <v>67950000000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals Inc</t>
+          <t>SLB Ltd</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>65500000000</v>
+        <v>67470000000</v>
       </c>
     </row>
     <row r="133">
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>65080000000</v>
+        <v>66150000000</v>
       </c>
     </row>
     <row r="134">
@@ -2496,97 +2496,97 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>63770000000</v>
+        <v>65290000000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Target Corp</t>
+          <t>Rocket Lab Corp</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>59180000000</v>
+        <v>60090000000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Sea Ltd ADR</t>
+          <t>Target Corp</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>58020000000</v>
+        <v>59140000000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Rocket Lab Corp</t>
+          <t>Sea Ltd ADR</t>
         </is>
       </c>
       <c r="L137" t="n">
-        <v>57930000000</v>
+        <v>58570000000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Edwards Lifesciences Corp</t>
         </is>
       </c>
       <c r="L138" t="n">
-        <v>57670000000</v>
+        <v>54340000000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Ford Motor Co</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>54350000000</v>
+        <v>54260000000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences Corp</t>
+          <t>Ford Motor Co</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>52970000000</v>
+        <v>53240000000</v>
       </c>
     </row>
     <row r="141">
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>51640000000</v>
+        <v>50930000000</v>
       </c>
     </row>
     <row r="142">
@@ -2616,52 +2616,52 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>47680000000</v>
+        <v>48650000000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Block Inc</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>46750000000</v>
+        <v>46920000000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Block Inc</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>45910000000</v>
+        <v>45400000000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>44900000000</v>
+        <v>44600000000</v>
       </c>
     </row>
     <row r="146">
@@ -2676,7 +2676,7 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>42370000000</v>
+        <v>43910000000</v>
       </c>
     </row>
     <row r="147">
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>42150000000</v>
+        <v>43780000000</v>
       </c>
     </row>
     <row r="148">
@@ -2706,37 +2706,37 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>41950000000</v>
+        <v>43600000000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Carnival Corp Ltd</t>
+          <t>PayPal Holdings Inc</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>39060000000</v>
+        <v>40110000000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>PayPal Holdings Inc</t>
+          <t>Carnival Corp Ltd</t>
         </is>
       </c>
       <c r="L150" t="n">
-        <v>38870000000</v>
+        <v>38230000000</v>
       </c>
     </row>
     <row r="151">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>38070000000</v>
+        <v>37480000000</v>
       </c>
     </row>
     <row r="152">
@@ -2766,7 +2766,7 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>32730000000</v>
+        <v>35310000000</v>
       </c>
     </row>
     <row r="153">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>32180000000</v>
+        <v>33440000000</v>
       </c>
     </row>
     <row r="154">
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>31920000000</v>
+        <v>32290000000</v>
       </c>
     </row>
     <row r="155">
@@ -2811,82 +2811,82 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>31760000000</v>
+        <v>31770000000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Zoetis Inc</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>30370000000</v>
+        <v>31650000000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Estee Lauder Cos. Inc</t>
+          <t>Zoetis Inc</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>29840000000</v>
+        <v>31360000000</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>Estee Lauder Cos. Inc</t>
         </is>
       </c>
       <c r="L158" t="n">
-        <v>28770000000</v>
+        <v>30290000000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>AFRM</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Affirm Holdings Inc</t>
+          <t>Illumina Inc</t>
         </is>
       </c>
       <c r="L159" t="n">
-        <v>28080000000</v>
+        <v>28550000000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>AFRM</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Illumina Inc</t>
+          <t>Affirm Holdings Inc</t>
         </is>
       </c>
       <c r="L160" t="n">
-        <v>27820000000</v>
+        <v>28330000000</v>
       </c>
     </row>
     <row r="161">
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>27050000000</v>
+        <v>27910000000</v>
       </c>
     </row>
     <row r="162">
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>26430000000</v>
+        <v>25550000000</v>
       </c>
     </row>
     <row r="163">
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>24940000000</v>
+        <v>24130000000</v>
       </c>
     </row>
     <row r="164">
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>23680000000</v>
+        <v>23820000000</v>
       </c>
     </row>
     <row r="165">
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>23650000000</v>
+        <v>23400000000</v>
       </c>
     </row>
     <row r="166">
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>22910000000</v>
+        <v>23020000000</v>
       </c>
     </row>
     <row r="167">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>20840000000</v>
+        <v>21130000000</v>
       </c>
     </row>
     <row r="168">
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>19370000000</v>
+        <v>19000000000</v>
       </c>
     </row>
     <row r="169">
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>19190000000</v>
+        <v>18340000000</v>
       </c>
     </row>
     <row r="170">
@@ -3036,22 +3036,22 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>17890000000</v>
+        <v>17610000000</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>GRAB</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Grab Holdings Limited</t>
+          <t>Circle Internet Group Inc</t>
         </is>
       </c>
       <c r="L171" t="n">
-        <v>15940000000</v>
+        <v>16060000000</v>
       </c>
     </row>
     <row r="172">
@@ -3066,37 +3066,37 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>15940000000</v>
+        <v>15990000000</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>GRAB</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>IREN Ltd</t>
+          <t>Grab Holdings Limited</t>
         </is>
       </c>
       <c r="L173" t="n">
-        <v>15460000000</v>
+        <v>15990000000</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>CRCL</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Circle Internet Group Inc</t>
+          <t>IREN Ltd</t>
         </is>
       </c>
       <c r="L174" t="n">
-        <v>15400000000</v>
+        <v>13850000000</v>
       </c>
     </row>
     <row r="175">
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>12590000000</v>
+        <v>12770000000</v>
       </c>
     </row>
     <row r="176">
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>12260000000</v>
+        <v>12360000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,82 +3141,82 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>12080000000</v>
+        <v>11890000000</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>OSCR</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Applied Digital Corp</t>
+          <t>Oscar Health Inc</t>
         </is>
       </c>
       <c r="L178" t="n">
-        <v>10150000000</v>
+        <v>9700000000</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>OSCR</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Oscar Health Inc</t>
+          <t>AeroVironment Inc</t>
         </is>
       </c>
       <c r="L179" t="n">
-        <v>9620000000</v>
+        <v>9660000000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>OKLO</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Oklo Inc</t>
+          <t>Applied Digital Corp</t>
         </is>
       </c>
       <c r="L180" t="n">
-        <v>9130000000</v>
+        <v>9450000000</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>PRMB</t>
+          <t>OKLO</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Primo Brands Corp</t>
+          <t>Oklo Inc</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>8900000000</v>
+        <v>9110000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>PRMB</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>AeroVironment Inc</t>
+          <t>Primo Brands Corp</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>8730000000</v>
+        <v>9080000000</v>
       </c>
     </row>
     <row r="183">
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>8700000000</v>
+        <v>8520000000</v>
       </c>
     </row>
     <row r="184">
@@ -3246,7 +3246,7 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>8150000000</v>
+        <v>8480000000</v>
       </c>
     </row>
     <row r="185">
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>8140000000</v>
+        <v>8060000000</v>
       </c>
     </row>
     <row r="186">
@@ -3276,37 +3276,37 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>7550000000</v>
+        <v>7630000000</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>RGTI</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Rigetti Computing Inc</t>
+          <t>SentinelOne Inc</t>
         </is>
       </c>
       <c r="L187" t="n">
-        <v>6210000000</v>
+        <v>6000000000</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>RGTI</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>SentinelOne Inc</t>
+          <t>Rigetti Computing Inc</t>
         </is>
       </c>
       <c r="L188" t="n">
-        <v>6030000000</v>
+        <v>5960000000</v>
       </c>
     </row>
     <row r="189">
@@ -3321,7 +3321,7 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>5360000000</v>
+        <v>5790000000</v>
       </c>
     </row>
     <row r="190">
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>5330000000</v>
+        <v>5490000000</v>
       </c>
     </row>
     <row r="191">
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>5100000000</v>
+        <v>4730000000</v>
       </c>
     </row>
     <row r="192">
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>4140000000</v>
+        <v>3880000000</v>
       </c>
     </row>
     <row r="193">
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3710000000</v>
+        <v>3570000000</v>
       </c>
     </row>
     <row r="194">
@@ -3396,67 +3396,67 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3420000000</v>
+        <v>3330000000</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>FLNC</t>
+          <t>LEU</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Fluence Energy Inc</t>
+          <t>Centrus Energy Corp</t>
         </is>
       </c>
       <c r="L195" t="n">
-        <v>3380000000</v>
+        <v>3190000000</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>LEU</t>
+          <t>FLNC</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Centrus Energy Corp</t>
+          <t>Fluence Energy Inc</t>
         </is>
       </c>
       <c r="L196" t="n">
-        <v>3270000000</v>
+        <v>3130000000</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>FSLY</t>
+          <t>PENN</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Fastly Inc</t>
+          <t>PENN Entertainment Inc</t>
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2900000000</v>
+        <v>2950000000</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>PENN</t>
+          <t>FSLY</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>PENN Entertainment Inc</t>
+          <t>Fastly Inc</t>
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2880000000</v>
+        <v>2840000000</v>
       </c>
     </row>
     <row r="199">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>2340000000</v>
+        <v>2380000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>2130000000</v>
+        <v>2040000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1640000000</v>
+        <v>1660000000</v>
       </c>
     </row>
     <row r="202">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1470000000</v>
+        <v>1410000000</v>
       </c>
     </row>
     <row r="203">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>1110000000</v>
+        <v>1060000000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>1080000000</v>
+        <v>1040000000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>776820000</v>
+        <v>708830000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4337520000000</v>
+        <v>4340360000000</v>
       </c>
     </row>
     <row r="8">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1095920000000</v>
+        <v>1095160000000</v>
       </c>
     </row>
     <row r="17">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>568230000000</v>
+        <v>568160000000</v>
       </c>
     </row>
     <row r="24">
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>162150000000</v>
+        <v>161910000000</v>
       </c>
     </row>
     <row r="85">
@@ -1902,31 +1902,31 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>S&amp;P Global Inc</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>130210000000</v>
+        <v>132740000000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>S&amp;P Global Inc</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>130000000000</v>
+        <v>130210000000</v>
       </c>
     </row>
     <row r="97">
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>7630000000</v>
+        <v>7650000000</v>
       </c>
     </row>
     <row r="187">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>708830000</v>
+        <v>708840000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4532960000000</v>
+        <v>4592150000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4714890000000</v>
+        <v>4732310000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4340360000000</v>
+        <v>4446620000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2900730000000</v>
+        <v>2872870000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2610430000000</v>
+        <v>2626460000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2251760000000</v>
+        <v>2343200000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,37 +651,37 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1714870000000</v>
+        <v>1778860000000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Meta Platforms Inc</t>
+          <t>Tesla Inc</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1479650000000</v>
+        <v>1576540000000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tesla Inc</t>
+          <t>Meta Platforms Inc</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1477690000000</v>
+        <v>1523790000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1143190000000</v>
+        <v>1130150000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1101790000000</v>
+        <v>1112170000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1095160000000</v>
+        <v>1092570000000</v>
       </c>
     </row>
     <row r="17">
@@ -741,67 +741,67 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>896220000000</v>
+        <v>904920000000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Walmart Inc</t>
+          <t>Advanced Micro Devices Inc</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>890030000000</v>
+        <v>900170000000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices Inc</t>
+          <t>Walmart Inc</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>844360000000</v>
+        <v>880560000000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Visa Inc</t>
+          <t>ASML Holding NV</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>682300000000</v>
+        <v>703420000000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ASML Holding NV</t>
+          <t>Visa Inc</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>681930000000</v>
+        <v>673100000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>633190000000</v>
+        <v>624260000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,37 +831,37 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>568160000000</v>
+        <v>565470000000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Applied Materials Inc</t>
+          <t>Mastercard Incorporated</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>478790000000</v>
+        <v>471040000000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated</t>
+          <t>Applied Materials Inc</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>476600000000</v>
+        <v>470650000000</v>
       </c>
     </row>
     <row r="26">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>461260000000</v>
+        <v>450110000000</v>
       </c>
     </row>
     <row r="27">
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>444160000000</v>
+        <v>449240000000</v>
       </c>
     </row>
     <row r="28">
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>443840000000</v>
+        <v>446780000000</v>
       </c>
     </row>
     <row r="29">
@@ -921,37 +921,37 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>439460000000</v>
+        <v>437950000000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Costco Wholesale Corp</t>
+          <t>Bank Of America Corp</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>422050000000</v>
+        <v>425090000000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Bank Of America Corp</t>
+          <t>Costco Wholesale Corp</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>416780000000</v>
+        <v>421420000000</v>
       </c>
     </row>
     <row r="32">
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>404040000000</v>
+        <v>414100000000</v>
       </c>
     </row>
     <row r="33">
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>393880000000</v>
+        <v>395090000000</v>
       </c>
     </row>
     <row r="34">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>386290000000</v>
+        <v>379600000000</v>
       </c>
     </row>
     <row r="35">
@@ -1011,82 +1011,82 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>362010000000</v>
+        <v>356930000000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Home Depot Inc</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>356870000000</v>
+        <v>350310000000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble Co</t>
+          <t>Home Depot Inc</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>352570000000</v>
+        <v>349640000000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Procter &amp; Gamble Co</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>337430000000</v>
+        <v>347680000000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Chevron Corp</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>336980000000</v>
+        <v>342860000000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>Chevron Corp</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>335460000000</v>
+        <v>334790000000</v>
       </c>
     </row>
     <row r="41">
@@ -1101,112 +1101,112 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>326970000000</v>
+        <v>320100000000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Merck &amp; Co Inc</t>
+          <t>Palantir Technologies Inc</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>319990000000</v>
+        <v>317740000000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc</t>
+          <t>Merck &amp; Co Inc</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>309970000000</v>
+        <v>313120000000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>KLA Corp</t>
+          <t>Goldman Sachs Group Inc</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>307690000000</v>
+        <v>311320000000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Astrazeneca plc</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>302650000000</v>
+        <v>309580000000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Goldman Sachs Group Inc</t>
+          <t>KLA Corp</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>301200000000</v>
+        <v>304770000000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>Astrazeneca plc</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>299110000000</v>
+        <v>294910000000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>NVS</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Novartis AG ADR</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>292700000000</v>
+        <v>291390000000</v>
       </c>
     </row>
     <row r="49">
@@ -1221,22 +1221,22 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>284080000000</v>
+        <v>287960000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>NVS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>Novartis AG ADR</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>283670000000</v>
+        <v>284630000000</v>
       </c>
     </row>
     <row r="51">
@@ -1251,37 +1251,37 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>272120000000</v>
+        <v>281510000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>268330000000</v>
+        <v>276210000000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>266730000000</v>
+        <v>271180000000</v>
       </c>
     </row>
     <row r="54">
@@ -1296,37 +1296,37 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>261680000000</v>
+        <v>267610000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>258420000000</v>
+        <v>266960000000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>255630000000</v>
+        <v>258330000000</v>
       </c>
     </row>
     <row r="57">
@@ -1341,37 +1341,37 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>252880000000</v>
+        <v>250040000000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>American Express Co</t>
+          <t>Citigroup Inc</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>240150000000</v>
+        <v>246710000000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Citigroup Inc</t>
+          <t>American Express Co</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>240040000000</v>
+        <v>242930000000</v>
       </c>
     </row>
     <row r="60">
@@ -1386,7 +1386,7 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>230810000000</v>
+        <v>235060000000</v>
       </c>
     </row>
     <row r="61">
@@ -1401,37 +1401,37 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>217530000000</v>
+        <v>217860000000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Toyota Motor Corp ADR</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>206730000000</v>
+        <v>203020000000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AMGEN Inc</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>201930000000</v>
+        <v>199040000000</v>
       </c>
     </row>
     <row r="64">
@@ -1446,307 +1446,307 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>199390000000</v>
+        <v>198590000000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>AMGEN Inc</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>197520000000</v>
+        <v>197770000000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PepsiCo Inc</t>
+          <t>T-Mobile US Inc</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>197120000000</v>
+        <v>196730000000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>194520000000</v>
+        <v>196550000000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>T-Mobile US Inc</t>
+          <t>PepsiCo Inc</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>192110000000</v>
+        <v>195840000000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Sap SE ADR</t>
+          <t>Thermo Fisher Scientific Inc</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>189830000000</v>
+        <v>192350000000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>Toyota Motor Corp ADR</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>185780000000</v>
+        <v>191320000000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>Sap SE ADR</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>185770000000</v>
+        <v>187380000000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NextEra Energy Inc</t>
+          <t>Boeing Co</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>184240000000</v>
+        <v>184890000000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Boeing Co</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>178540000000</v>
+        <v>182680000000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc</t>
+          <t>NextEra Energy Inc</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>177710000000</v>
+        <v>182370000000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>Verizon Communications Inc</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>177060000000</v>
+        <v>175670000000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Walt Disney Co</t>
+          <t>Charles Schwab Corp</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>172780000000</v>
+        <v>174990000000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Deere &amp; Co</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>170770000000</v>
+        <v>171480000000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Corning Inc</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>169360000000</v>
+        <v>169920000000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Novo Nordisk ADR</t>
+          <t>Walt Disney Co</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>169340000000</v>
+        <v>169150000000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Charles Schwab Corp</t>
+          <t>Corning Inc</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>168700000000</v>
+        <v>167650000000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Deere &amp; Co</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>167700000000</v>
+        <v>166570000000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Novo Nordisk ADR</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>166170000000</v>
+        <v>165410000000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>Blackrock Inc</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>162980000000</v>
+        <v>164430000000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Blackrock Inc</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>161910000000</v>
+        <v>160920000000</v>
       </c>
     </row>
     <row r="85">
@@ -1761,112 +1761,112 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>155020000000</v>
+        <v>155900000000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Uber Technologies Inc</t>
+          <t>Intuitive Surgical Inc</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>151510000000</v>
+        <v>153290000000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Intuitive Surgical Inc</t>
+          <t>Blackstone Inc</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>150880000000</v>
+        <v>150760000000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Blackstone Inc</t>
+          <t>Uber Technologies Inc</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>149980000000</v>
+        <v>147420000000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>AT&amp;T Inc</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>143010000000</v>
+        <v>143000000000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>143000000000</v>
+        <v>140280000000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Danaher Corp</t>
+          <t>Chubb Limited</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>140090000000</v>
+        <v>138280000000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Chubb Limited</t>
+          <t>Danaher Corp</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>140080000000</v>
+        <v>137040000000</v>
       </c>
     </row>
     <row r="93">
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>136040000000</v>
+        <v>135670000000</v>
       </c>
     </row>
     <row r="94">
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>135690000000</v>
+        <v>135370000000</v>
       </c>
     </row>
     <row r="95">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>132740000000</v>
+        <v>133470000000</v>
       </c>
     </row>
     <row r="96">
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>130210000000</v>
+        <v>132380000000</v>
       </c>
     </row>
     <row r="97">
@@ -1941,7 +1941,7 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>127560000000</v>
+        <v>125480000000</v>
       </c>
     </row>
     <row r="98">
@@ -1956,82 +1956,82 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>125870000000</v>
+        <v>124040000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Altria Group Inc</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>121420000000</v>
+        <v>122330000000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Starbucks Corp</t>
+          <t>Altria Group Inc</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>118840000000</v>
+        <v>120030000000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Co</t>
+          <t>PDD Holdings Inc ADR</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>118710000000</v>
+        <v>119200000000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PDD Holdings Inc ADR</t>
+          <t>Starbucks Corp</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>117270000000</v>
+        <v>116370000000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>Bristol-Myers Squibb Co</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>115440000000</v>
+        <v>115790000000</v>
       </c>
     </row>
     <row r="104">
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>106490000000</v>
+        <v>106320000000</v>
       </c>
     </row>
     <row r="105">
@@ -2061,7 +2061,7 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>100030000000</v>
+        <v>99420000000</v>
       </c>
     </row>
     <row r="106">
@@ -2076,37 +2076,37 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>98820000000</v>
+        <v>98510000000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>96840000000</v>
+        <v>97870000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>Automatic Data Processing Inc</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>96160000000</v>
+        <v>95730000000</v>
       </c>
     </row>
     <row r="109">
@@ -2121,52 +2121,52 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>94060000000</v>
+        <v>93520000000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>HCA Healthcare Inc</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>92680000000</v>
+        <v>92520000000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>HCA Healthcare Inc</t>
+          <t>MercadoLibre Inc</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>91070000000</v>
+        <v>91540000000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Elevance Health Inc</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>90750000000</v>
+        <v>90900000000</v>
       </c>
     </row>
     <row r="113">
@@ -2181,7 +2181,7 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>90170000000</v>
+        <v>90840000000</v>
       </c>
     </row>
     <row r="114">
@@ -2196,52 +2196,52 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>89760000000</v>
+        <v>88990000000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>MercadoLibre Inc</t>
+          <t>Elevance Health Inc</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>89400000000</v>
+        <v>88640000000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>87340000000</v>
+        <v>87910000000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>86090000000</v>
+        <v>86680000000</v>
       </c>
     </row>
     <row r="118">
@@ -2256,7 +2256,7 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>86020000000</v>
+        <v>84180000000</v>
       </c>
     </row>
     <row r="119">
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>84050000000</v>
+        <v>83810000000</v>
       </c>
     </row>
     <row r="120">
@@ -2286,52 +2286,52 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>83680000000</v>
+        <v>83010000000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Northrop Grumman Corp</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>79470000000</v>
+        <v>77800000000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>77980000000</v>
+        <v>77180000000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Cigna Group</t>
+          <t>Intercontinental Exchange Inc</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>76120000000</v>
+        <v>76290000000</v>
       </c>
     </row>
     <row r="124">
@@ -2346,37 +2346,37 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>76120000000</v>
+        <v>74730000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Intuit Inc</t>
+          <t>Cigna Group</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>75320000000</v>
+        <v>74590000000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange Inc</t>
+          <t>Intuit Inc</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>75210000000</v>
+        <v>74440000000</v>
       </c>
     </row>
     <row r="127">
@@ -2391,22 +2391,22 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>69660000000</v>
+        <v>74180000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals Inc</t>
+          <t>Apollo Global Management Inc</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>68590000000</v>
+        <v>70430000000</v>
       </c>
     </row>
     <row r="129">
@@ -2421,67 +2421,67 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>68530000000</v>
+        <v>70190000000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Apollo Global Management Inc</t>
+          <t>Ferrari NV</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>68380000000</v>
+        <v>69170000000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Ferrari NV</t>
+          <t>SLB Ltd</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>67950000000</v>
+        <v>68350000000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>SLB Ltd</t>
+          <t>Nu Holdings Ltd</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>67470000000</v>
+        <v>68340000000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>NU</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Nu Holdings Ltd</t>
+          <t>Regeneron Pharmaceuticals Inc</t>
         </is>
       </c>
       <c r="L133" t="n">
-        <v>66150000000</v>
+        <v>68130000000</v>
       </c>
     </row>
     <row r="134">
@@ -2496,22 +2496,22 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>65290000000</v>
+        <v>64180000000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Rocket Lab Corp</t>
+          <t>Sea Ltd ADR</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>60090000000</v>
+        <v>59530000000</v>
       </c>
     </row>
     <row r="136">
@@ -2526,67 +2526,67 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>59140000000</v>
+        <v>57270000000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Sea Ltd ADR</t>
+          <t>Rocket Lab Corp</t>
         </is>
       </c>
       <c r="L137" t="n">
-        <v>58570000000</v>
+        <v>55680000000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences Corp</t>
+          <t>Ford Motor Co</t>
         </is>
       </c>
       <c r="L138" t="n">
-        <v>54340000000</v>
+        <v>55110000000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Edwards Lifesciences Corp</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>54260000000</v>
+        <v>54800000000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Ford Motor Co</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>53240000000</v>
+        <v>53610000000</v>
       </c>
     </row>
     <row r="141">
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>50930000000</v>
+        <v>53010000000</v>
       </c>
     </row>
     <row r="142">
@@ -2616,67 +2616,67 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>48650000000</v>
+        <v>48550000000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Block Inc</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>46920000000</v>
+        <v>47170000000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>Block Inc</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>45400000000</v>
+        <v>46970000000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>MSCI Inc</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>44600000000</v>
+        <v>44700000000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MSCI Inc</t>
+          <t>Coinbase Global Inc</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>43910000000</v>
+        <v>44490000000</v>
       </c>
     </row>
     <row r="147">
@@ -2691,22 +2691,22 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>43780000000</v>
+        <v>43790000000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Coinbase Global Inc</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>43600000000</v>
+        <v>43590000000</v>
       </c>
     </row>
     <row r="149">
@@ -2721,37 +2721,37 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>40110000000</v>
+        <v>39770000000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>RDDT</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Carnival Corp Ltd</t>
+          <t>Reddit Inc</t>
         </is>
       </c>
       <c r="L150" t="n">
-        <v>38230000000</v>
+        <v>38670000000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>RDDT</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Reddit Inc</t>
+          <t>Carnival Corp Ltd</t>
         </is>
       </c>
       <c r="L151" t="n">
-        <v>37480000000</v>
+        <v>37680000000</v>
       </c>
     </row>
     <row r="152">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>33440000000</v>
+        <v>34080000000</v>
       </c>
     </row>
     <row r="154">
@@ -2796,37 +2796,37 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>32290000000</v>
+        <v>32490000000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Twilio Inc</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="L155" t="n">
-        <v>31770000000</v>
+        <v>32460000000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>Twilio Inc</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>31650000000</v>
+        <v>31730000000</v>
       </c>
     </row>
     <row r="157">
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>31360000000</v>
+        <v>31620000000</v>
       </c>
     </row>
     <row r="158">
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>30290000000</v>
+        <v>30720000000</v>
       </c>
     </row>
     <row r="159">
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>28550000000</v>
+        <v>29400000000</v>
       </c>
     </row>
     <row r="160">
@@ -2886,7 +2886,7 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>28330000000</v>
+        <v>28730000000</v>
       </c>
     </row>
     <row r="161">
@@ -2901,37 +2901,37 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>27910000000</v>
+        <v>27610000000</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ZM</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Zoom Communications Inc</t>
+          <t>First Solar Inc</t>
         </is>
       </c>
       <c r="L162" t="n">
-        <v>25550000000</v>
+        <v>25040000000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>ZM</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>First Solar Inc</t>
+          <t>Zoom Communications Inc</t>
         </is>
       </c>
       <c r="L163" t="n">
-        <v>24130000000</v>
+        <v>24910000000</v>
       </c>
     </row>
     <row r="164">
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>23820000000</v>
+        <v>24320000000</v>
       </c>
     </row>
     <row r="165">
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>23400000000</v>
+        <v>23870000000</v>
       </c>
     </row>
     <row r="166">
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>23020000000</v>
+        <v>23300000000</v>
       </c>
     </row>
     <row r="167">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>21130000000</v>
+        <v>21100000000</v>
       </c>
     </row>
     <row r="168">
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>19000000000</v>
+        <v>18760000000</v>
       </c>
     </row>
     <row r="169">
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>18340000000</v>
+        <v>18240000000</v>
       </c>
     </row>
     <row r="170">
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>17610000000</v>
+        <v>17590000000</v>
       </c>
     </row>
     <row r="171">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>16060000000</v>
+        <v>17060000000</v>
       </c>
     </row>
     <row r="172">
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>15990000000</v>
+        <v>15780000000</v>
       </c>
     </row>
     <row r="173">
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>15990000000</v>
+        <v>15780000000</v>
       </c>
     </row>
     <row r="174">
@@ -3096,37 +3096,37 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>13850000000</v>
+        <v>15670000000</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>TXRH</t>
+          <t>PINS</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Texas Roadhouse Inc</t>
+          <t>Pinterest Inc</t>
         </is>
       </c>
       <c r="L175" t="n">
-        <v>12770000000</v>
+        <v>12460000000</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>PINS</t>
+          <t>TXRH</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Pinterest Inc</t>
+          <t>Texas Roadhouse Inc</t>
         </is>
       </c>
       <c r="L176" t="n">
-        <v>12360000000</v>
+        <v>12230000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,52 +3141,52 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>11890000000</v>
+        <v>11220000000</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>OSCR</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Oscar Health Inc</t>
+          <t>Applied Digital Corp</t>
         </is>
       </c>
       <c r="L178" t="n">
-        <v>9700000000</v>
+        <v>9570000000</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>OSCR</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>AeroVironment Inc</t>
+          <t>Oscar Health Inc</t>
         </is>
       </c>
       <c r="L179" t="n">
-        <v>9660000000</v>
+        <v>9480000000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>PRMB</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Applied Digital Corp</t>
+          <t>Primo Brands Corp</t>
         </is>
       </c>
       <c r="L180" t="n">
-        <v>9450000000</v>
+        <v>9170000000</v>
       </c>
     </row>
     <row r="181">
@@ -3201,22 +3201,22 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>9110000000</v>
+        <v>9020000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>PRMB</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Primo Brands Corp</t>
+          <t>AeroVironment Inc</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>9080000000</v>
+        <v>8950000000</v>
       </c>
     </row>
     <row r="183">
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>8520000000</v>
+        <v>8860000000</v>
       </c>
     </row>
     <row r="184">
@@ -3246,7 +3246,7 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>8480000000</v>
+        <v>8450000000</v>
       </c>
     </row>
     <row r="185">
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>8060000000</v>
+        <v>8420000000</v>
       </c>
     </row>
     <row r="186">
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>7650000000</v>
+        <v>7540000000</v>
       </c>
     </row>
     <row r="187">
@@ -3291,52 +3291,52 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>6000000000</v>
+        <v>6220000000</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>RGTI</t>
+          <t>LMND</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Rigetti Computing Inc</t>
+          <t>Lemonade Inc</t>
         </is>
       </c>
       <c r="L188" t="n">
-        <v>5960000000</v>
+        <v>6050000000</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>CRSP</t>
+          <t>RGTI</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>CRISPR Therapeutics AG</t>
+          <t>Rigetti Computing Inc</t>
         </is>
       </c>
       <c r="L189" t="n">
-        <v>5790000000</v>
+        <v>5970000000</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>LMND</t>
+          <t>CRSP</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Lemonade Inc</t>
+          <t>CRISPR Therapeutics AG</t>
         </is>
       </c>
       <c r="L190" t="n">
-        <v>5490000000</v>
+        <v>5970000000</v>
       </c>
     </row>
     <row r="191">
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>4730000000</v>
+        <v>4940000000</v>
       </c>
     </row>
     <row r="192">
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>3880000000</v>
+        <v>4090000000</v>
       </c>
     </row>
     <row r="193">
@@ -3381,37 +3381,37 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3570000000</v>
+        <v>3510000000</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>LEU</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Upstart Holdings Inc</t>
+          <t>Centrus Energy Corp</t>
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3330000000</v>
+        <v>3430000000</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>LEU</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Centrus Energy Corp</t>
+          <t>Upstart Holdings Inc</t>
         </is>
       </c>
       <c r="L195" t="n">
-        <v>3190000000</v>
+        <v>3290000000</v>
       </c>
     </row>
     <row r="196">
@@ -3426,37 +3426,37 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>3130000000</v>
+        <v>3280000000</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>PENN</t>
+          <t>FSLY</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>PENN Entertainment Inc</t>
+          <t>Fastly Inc</t>
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2950000000</v>
+        <v>2860000000</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>FSLY</t>
+          <t>PENN</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Fastly Inc</t>
+          <t>PENN Entertainment Inc</t>
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2840000000</v>
+        <v>2830000000</v>
       </c>
     </row>
     <row r="199">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>2380000000</v>
+        <v>2460000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>2040000000</v>
+        <v>2110000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1660000000</v>
+        <v>1680000000</v>
       </c>
     </row>
     <row r="202">
@@ -3516,37 +3516,37 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1410000000</v>
+        <v>1440000000</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>UMAC</t>
+          <t>NNE</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Unusual Machines Inc</t>
+          <t>Nano Nuclear Energy Inc</t>
         </is>
       </c>
       <c r="L203" t="n">
-        <v>1060000000</v>
+        <v>1050000000</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>NNE</t>
+          <t>UMAC</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Nano Nuclear Energy Inc</t>
+          <t>Unusual Machines Inc</t>
         </is>
       </c>
       <c r="L204" t="n">
-        <v>1040000000</v>
+        <v>1030000000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>708840000</v>
+        <v>696250000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4592150000000</v>
+        <v>4562770000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4732310000000</v>
+        <v>4765710000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4446620000000</v>
+        <v>4426710000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2872870000000</v>
+        <v>2888470000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2626460000000</v>
+        <v>2646030000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2343200000000</v>
+        <v>2243520000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,37 +651,37 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1778860000000</v>
+        <v>1764020000000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tesla Inc</t>
+          <t>Meta Platforms Inc</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1576540000000</v>
+        <v>1562600000000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Meta Platforms Inc</t>
+          <t>Tesla Inc</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1523790000000</v>
+        <v>1513180000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,37 +696,37 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1130150000000</v>
+        <v>1163580000000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>BRK-B</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Micron Technology Inc</t>
+          <t>Berkshire Hathaway Inc</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1112170000000</v>
+        <v>1085610000000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BRK-B</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Inc</t>
+          <t>Micron Technology Inc</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1092570000000</v>
+        <v>1059800000000</v>
       </c>
     </row>
     <row r="17">
@@ -741,37 +741,37 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>904920000000</v>
+        <v>908940000000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices Inc</t>
+          <t>Walmart Inc</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>900170000000</v>
+        <v>887640000000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Walmart Inc</t>
+          <t>Advanced Micro Devices Inc</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>880560000000</v>
+        <v>841570000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>703420000000</v>
+        <v>673440000000</v>
       </c>
     </row>
     <row r="21">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>673100000000</v>
+        <v>663590000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>624260000000</v>
+        <v>643300000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>565470000000</v>
+        <v>587230000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,52 +846,52 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>471040000000</v>
+        <v>469730000000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Applied Materials Inc</t>
+          <t>Abbvie Inc</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>470650000000</v>
+        <v>449910000000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Abbvie Inc</t>
+          <t>Cisco Systems Inc</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>450110000000</v>
+        <v>440610000000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cisco Systems Inc</t>
+          <t>Applied Materials Inc</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>449240000000</v>
+        <v>440250000000</v>
       </c>
     </row>
     <row r="28">
@@ -906,97 +906,97 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>446780000000</v>
+        <v>433050000000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Lam Research Corp</t>
+          <t>Bank Of America Corp</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>437950000000</v>
+        <v>424800000000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Bank Of America Corp</t>
+          <t>Costco Wholesale Corp</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>425090000000</v>
+        <v>420200000000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Costco Wholesale Corp</t>
+          <t>Oracle Corp</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>421420000000</v>
+        <v>407870000000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Oracle Corp</t>
+          <t>Lam Research Corp</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>414100000000</v>
+        <v>407850000000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Unitedhealth Group Inc</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>395090000000</v>
+        <v>388860000000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Unitedhealth Group Inc</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>379600000000</v>
+        <v>382880000000</v>
       </c>
     </row>
     <row r="35">
@@ -1011,82 +1011,82 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>356930000000</v>
+        <v>361620000000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Procter &amp; Gamble Co</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>350310000000</v>
+        <v>355690000000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Home Depot Inc</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>349640000000</v>
+        <v>350220000000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble Co</t>
+          <t>Chevron Corp</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>347680000000</v>
+        <v>346560000000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>Home Depot Inc</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>342860000000</v>
+        <v>344210000000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Chevron Corp</t>
+          <t>Palantir Technologies Inc</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>334790000000</v>
+        <v>322130000000</v>
       </c>
     </row>
     <row r="41">
@@ -1101,22 +1101,22 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>320100000000</v>
+        <v>320780000000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>317740000000</v>
+        <v>319660000000</v>
       </c>
     </row>
     <row r="43">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>313120000000</v>
+        <v>318260000000</v>
       </c>
     </row>
     <row r="44">
@@ -1146,127 +1146,127 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>311320000000</v>
+        <v>307690000000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>Astrazeneca plc</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>309580000000</v>
+        <v>299500000000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>KLA Corp</t>
+          <t>Philip Morris International Inc</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>304770000000</v>
+        <v>292680000000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Astrazeneca plc</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>294910000000</v>
+        <v>289430000000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>International Business Machines Corp</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>291390000000</v>
+        <v>287730000000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>NVS</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Philip Morris International Inc</t>
+          <t>Novartis AG ADR</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>287960000000</v>
+        <v>287450000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NVS</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Novartis AG ADR</t>
+          <t>KLA Corp</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>284630000000</v>
+        <v>282770000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>International Business Machines Corp</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>281510000000</v>
+        <v>274690000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>276210000000</v>
+        <v>270510000000</v>
       </c>
     </row>
     <row r="53">
@@ -1281,82 +1281,82 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>271180000000</v>
+        <v>270480000000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Co</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>267610000000</v>
+        <v>266930000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>Wells Fargo &amp; Co</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>266960000000</v>
+        <v>266790000000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>Linde Plc</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>258330000000</v>
+        <v>248980000000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Linde Plc</t>
+          <t>Citigroup Inc</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>250040000000</v>
+        <v>241410000000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Citigroup Inc</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>246710000000</v>
+        <v>239560000000</v>
       </c>
     </row>
     <row r="59">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>242930000000</v>
+        <v>238530000000</v>
       </c>
     </row>
     <row r="60">
@@ -1386,7 +1386,7 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>235060000000</v>
+        <v>235610000000</v>
       </c>
     </row>
     <row r="61">
@@ -1401,82 +1401,82 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>217860000000</v>
+        <v>228600000000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>McDonald's Corp</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>203020000000</v>
+        <v>200510000000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>T-Mobile US Inc</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>199040000000</v>
+        <v>199920000000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>McDonald's Corp</t>
+          <t>AMGEN Inc</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>198590000000</v>
+        <v>198670000000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>AMGEN Inc</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>197770000000</v>
+        <v>198170000000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>T-Mobile US Inc</t>
+          <t>PepsiCo Inc</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>196730000000</v>
+        <v>198150000000</v>
       </c>
     </row>
     <row r="67">
@@ -1491,127 +1491,127 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>196550000000</v>
+        <v>192850000000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PepsiCo Inc</t>
+          <t>Thermo Fisher Scientific Inc</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>195840000000</v>
+        <v>191990000000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc</t>
+          <t>Toyota Motor Corp ADR</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>192350000000</v>
+        <v>190920000000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Toyota Motor Corp ADR</t>
+          <t>Sap SE ADR</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>191320000000</v>
+        <v>190040000000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Sap SE ADR</t>
+          <t>NextEra Energy Inc</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>187380000000</v>
+        <v>184510000000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Boeing Co</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>184890000000</v>
+        <v>183410000000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>Boeing Co</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>182680000000</v>
+        <v>182630000000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NextEra Energy Inc</t>
+          <t>Verizon Communications Inc</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>182370000000</v>
+        <v>177840000000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>175670000000</v>
+        <v>177370000000</v>
       </c>
     </row>
     <row r="76">
@@ -1626,37 +1626,37 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>174990000000</v>
+        <v>177270000000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Deere &amp; Co</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>171480000000</v>
+        <v>173600000000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>169920000000</v>
+        <v>169300000000</v>
       </c>
     </row>
     <row r="79">
@@ -1671,82 +1671,82 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>169150000000</v>
+        <v>169280000000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Corning Inc</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>167650000000</v>
+        <v>166940000000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Novo Nordisk ADR</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>166570000000</v>
+        <v>166690000000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Novo Nordisk ADR</t>
+          <t>Blackrock Inc</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>165410000000</v>
+        <v>164140000000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Blackrock Inc</t>
+          <t>Deere &amp; Co</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>164430000000</v>
+        <v>162940000000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>Corning Inc</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>160920000000</v>
+        <v>159550000000</v>
       </c>
     </row>
     <row r="85">
@@ -1761,7 +1761,7 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>155900000000</v>
+        <v>158160000000</v>
       </c>
     </row>
     <row r="86">
@@ -1776,37 +1776,37 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>153290000000</v>
+        <v>151330000000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Blackstone Inc</t>
+          <t>Uber Technologies Inc</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>150760000000</v>
+        <v>151310000000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Uber Technologies Inc</t>
+          <t>Blackstone Inc</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>147420000000</v>
+        <v>147670000000</v>
       </c>
     </row>
     <row r="89">
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>143000000000</v>
+        <v>146540000000</v>
       </c>
     </row>
     <row r="90">
@@ -1836,7 +1836,7 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>140280000000</v>
+        <v>140990000000</v>
       </c>
     </row>
     <row r="91">
@@ -1851,37 +1851,37 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>138280000000</v>
+        <v>139360000000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Danaher Corp</t>
+          <t>Salesforce Inc</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>137040000000</v>
+        <v>138840000000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Salesforce Inc</t>
+          <t>Danaher Corp</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>135670000000</v>
+        <v>137440000000</v>
       </c>
     </row>
     <row r="94">
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>135370000000</v>
+        <v>136970000000</v>
       </c>
     </row>
     <row r="95">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>133470000000</v>
+        <v>136720000000</v>
       </c>
     </row>
     <row r="96">
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>132380000000</v>
+        <v>131260000000</v>
       </c>
     </row>
     <row r="97">
@@ -1941,7 +1941,7 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>125480000000</v>
+        <v>123860000000</v>
       </c>
     </row>
     <row r="98">
@@ -1956,82 +1956,82 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>124040000000</v>
+        <v>123440000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>Altria Group Inc</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>122330000000</v>
+        <v>121840000000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Altria Group Inc</t>
+          <t>Bristol-Myers Squibb Co</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>120030000000</v>
+        <v>118380000000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PDD Holdings Inc ADR</t>
+          <t>Starbucks Corp</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>119200000000</v>
+        <v>118080000000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Starbucks Corp</t>
+          <t>PDD Holdings Inc ADR</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>116370000000</v>
+        <v>117470000000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Co</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>115790000000</v>
+        <v>117380000000</v>
       </c>
     </row>
     <row r="104">
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>106320000000</v>
+        <v>107310000000</v>
       </c>
     </row>
     <row r="105">
@@ -2061,7 +2061,7 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>99420000000</v>
+        <v>101670000000</v>
       </c>
     </row>
     <row r="106">
@@ -2076,127 +2076,127 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>98510000000</v>
+        <v>100890000000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>Automatic Data Processing Inc</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>97870000000</v>
+        <v>98170000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>95730000000</v>
+        <v>97970000000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>United Parcel Service Inc</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>93520000000</v>
+        <v>95470000000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>HCA Healthcare Inc</t>
+          <t>United Parcel Service Inc</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>92520000000</v>
+        <v>95170000000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>MercadoLibre Inc</t>
+          <t>HCA Healthcare Inc</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>91540000000</v>
+        <v>93860000000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>MercadoLibre Inc</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>90900000000</v>
+        <v>91940000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Snowflake Inc</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>90840000000</v>
+        <v>91410000000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Airbnb Inc</t>
+          <t>Snowflake Inc</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>88990000000</v>
+        <v>91070000000</v>
       </c>
     </row>
     <row r="115">
@@ -2211,22 +2211,22 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>88640000000</v>
+        <v>90960000000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>Airbnb Inc</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>87910000000</v>
+        <v>89680000000</v>
       </c>
     </row>
     <row r="117">
@@ -2241,37 +2241,37 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>86680000000</v>
+        <v>88060000000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>MMC</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Marsh</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>84180000000</v>
+        <v>86980000000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>MMC</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>Marsh</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>83810000000</v>
+        <v>85760000000</v>
       </c>
     </row>
     <row r="120">
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>83010000000</v>
+        <v>82410000000</v>
       </c>
     </row>
     <row r="121">
@@ -2301,37 +2301,37 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>77800000000</v>
+        <v>77980000000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Intercontinental Exchange Inc</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>77180000000</v>
+        <v>77160000000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange Inc</t>
+          <t>Intuit Inc</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>76290000000</v>
+        <v>76910000000</v>
       </c>
     </row>
     <row r="124">
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>74730000000</v>
+        <v>76040000000</v>
       </c>
     </row>
     <row r="125">
@@ -2361,97 +2361,97 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>74590000000</v>
+        <v>75820000000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Intuit Inc</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>74440000000</v>
+        <v>75700000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Astera Labs Inc</t>
+          <t>Regeneron Pharmaceuticals Inc</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>74180000000</v>
+        <v>70900000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Apollo Global Management Inc</t>
+          <t>SLB Ltd</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>70430000000</v>
+        <v>69400000000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>General Motors Company</t>
+          <t>Apollo Global Management Inc</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>70190000000</v>
+        <v>68800000000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Ferrari NV</t>
+          <t>General Motors Company</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>69170000000</v>
+        <v>68550000000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SLB Ltd</t>
+          <t>Ferrari NV</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>68350000000</v>
+        <v>68310000000</v>
       </c>
     </row>
     <row r="132">
@@ -2466,22 +2466,22 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>68340000000</v>
+        <v>66150000000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals Inc</t>
+          <t>Astera Labs Inc</t>
         </is>
       </c>
       <c r="L133" t="n">
-        <v>68130000000</v>
+        <v>65630000000</v>
       </c>
     </row>
     <row r="134">
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>64180000000</v>
+        <v>63990000000</v>
       </c>
     </row>
     <row r="135">
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>59530000000</v>
+        <v>59090000000</v>
       </c>
     </row>
     <row r="136">
@@ -2526,22 +2526,22 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>57270000000</v>
+        <v>57930000000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Rocket Lab Corp</t>
+          <t>Edwards Lifesciences Corp</t>
         </is>
       </c>
       <c r="L137" t="n">
-        <v>55680000000</v>
+        <v>54600000000</v>
       </c>
     </row>
     <row r="138">
@@ -2556,157 +2556,157 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>55110000000</v>
+        <v>54030000000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences Corp</t>
+          <t>Vistra Corp</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>54800000000</v>
+        <v>52510000000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Occidental Petroleum Corp</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>53610000000</v>
+        <v>51400000000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Vistra Corp</t>
+          <t>Rocket Lab Corp</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>53010000000</v>
+        <v>49890000000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Occidental Petroleum Corp</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>48550000000</v>
+        <v>49120000000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Block Inc</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>47170000000</v>
+        <v>46160000000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Block Inc</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>46970000000</v>
+        <v>45570000000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MSCI Inc</t>
+          <t>Autodesk Inc</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>44700000000</v>
+        <v>44810000000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Coinbase Global Inc</t>
+          <t>MSCI Inc</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>44490000000</v>
+        <v>44270000000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Autodesk Inc</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>43790000000</v>
+        <v>44060000000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>Coinbase Global Inc</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>43590000000</v>
+        <v>43080000000</v>
       </c>
     </row>
     <row r="149">
@@ -2721,7 +2721,7 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>39770000000</v>
+        <v>40270000000</v>
       </c>
     </row>
     <row r="150">
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>38670000000</v>
+        <v>38390000000</v>
       </c>
     </row>
     <row r="151">
@@ -2751,97 +2751,97 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>37680000000</v>
+        <v>36540000000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Strategy Inc</t>
+          <t>Workday Inc</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>35310000000</v>
+        <v>35480000000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Workday Inc</t>
+          <t>Strategy Inc</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>34080000000</v>
+        <v>34120000000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>JD</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>JD.com Inc ADR</t>
+          <t>Twilio Inc</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>32490000000</v>
+        <v>32170000000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>JD.com Inc ADR</t>
         </is>
       </c>
       <c r="L155" t="n">
-        <v>32460000000</v>
+        <v>32140000000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Twilio Inc</t>
+          <t>Zoetis Inc</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>31730000000</v>
+        <v>31980000000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Zoetis Inc</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>31620000000</v>
+        <v>31650000000</v>
       </c>
     </row>
     <row r="158">
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>30720000000</v>
+        <v>30550000000</v>
       </c>
     </row>
     <row r="159">
@@ -2871,67 +2871,67 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>29400000000</v>
+        <v>29010000000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>AFRM</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Affirm Holdings Inc</t>
+          <t>Fiserv Inc</t>
         </is>
       </c>
       <c r="L160" t="n">
-        <v>28730000000</v>
+        <v>28110000000</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AFRM</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Fiserv Inc</t>
+          <t>Affirm Holdings Inc</t>
         </is>
       </c>
       <c r="L161" t="n">
-        <v>27610000000</v>
+        <v>28000000000</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>ZM</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>First Solar Inc</t>
+          <t>Zoom Communications Inc</t>
         </is>
       </c>
       <c r="L162" t="n">
-        <v>25040000000</v>
+        <v>25120000000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ZM</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Zoom Communications Inc</t>
+          <t>First Solar Inc</t>
         </is>
       </c>
       <c r="L163" t="n">
-        <v>24910000000</v>
+        <v>24470000000</v>
       </c>
     </row>
     <row r="164">
@@ -2946,37 +2946,37 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>24320000000</v>
+        <v>24180000000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>DKNG</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>SoFi Technologies Inc</t>
+          <t>DraftKings Inc</t>
         </is>
       </c>
       <c r="L165" t="n">
-        <v>23870000000</v>
+        <v>23930000000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>DKNG</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>DraftKings Inc</t>
+          <t>SoFi Technologies Inc</t>
         </is>
       </c>
       <c r="L166" t="n">
-        <v>23300000000</v>
+        <v>22770000000</v>
       </c>
     </row>
     <row r="167">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>21100000000</v>
+        <v>20950000000</v>
       </c>
     </row>
     <row r="168">
@@ -3006,37 +3006,37 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>18760000000</v>
+        <v>19120000000</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>IonQ Inc</t>
+          <t>Super Micro Computer Inc</t>
         </is>
       </c>
       <c r="L169" t="n">
-        <v>18240000000</v>
+        <v>16980000000</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Super Micro Computer Inc</t>
+          <t>IonQ Inc</t>
         </is>
       </c>
       <c r="L170" t="n">
-        <v>17590000000</v>
+        <v>16930000000</v>
       </c>
     </row>
     <row r="171">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>17060000000</v>
+        <v>16190000000</v>
       </c>
     </row>
     <row r="172">
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>15780000000</v>
+        <v>16110000000</v>
       </c>
     </row>
     <row r="173">
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>15780000000</v>
+        <v>16110000000</v>
       </c>
     </row>
     <row r="174">
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>15670000000</v>
+        <v>14210000000</v>
       </c>
     </row>
     <row r="175">
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>12460000000</v>
+        <v>12560000000</v>
       </c>
     </row>
     <row r="176">
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>12230000000</v>
+        <v>12290000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,97 +3141,97 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>11220000000</v>
+        <v>10920000000</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>OSCR</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Applied Digital Corp</t>
+          <t>Oscar Health Inc</t>
         </is>
       </c>
       <c r="L178" t="n">
-        <v>9570000000</v>
+        <v>9380000000</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>OSCR</t>
+          <t>PRMB</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Oscar Health Inc</t>
+          <t>Primo Brands Corp</t>
         </is>
       </c>
       <c r="L179" t="n">
-        <v>9480000000</v>
+        <v>9040000000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>PRMB</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Primo Brands Corp</t>
+          <t>Applied Digital Corp</t>
         </is>
       </c>
       <c r="L180" t="n">
-        <v>9170000000</v>
+        <v>8780000000</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>OKLO</t>
+          <t>HIMS</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Oklo Inc</t>
+          <t>Hims &amp; Hers Health Inc</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>9020000000</v>
+        <v>8370000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>OKLO</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>AeroVironment Inc</t>
+          <t>Oklo Inc</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>8950000000</v>
+        <v>8330000000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>HIMS</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Hims &amp; Hers Health Inc</t>
+          <t>AeroVironment Inc</t>
         </is>
       </c>
       <c r="L183" t="n">
-        <v>8860000000</v>
+        <v>8230000000</v>
       </c>
     </row>
     <row r="184">
@@ -3246,7 +3246,7 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>8450000000</v>
+        <v>8100000000</v>
       </c>
     </row>
     <row r="185">
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>8420000000</v>
+        <v>8000000000</v>
       </c>
     </row>
     <row r="186">
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>7540000000</v>
+        <v>7500000000</v>
       </c>
     </row>
     <row r="187">
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>6220000000</v>
+        <v>6230000000</v>
       </c>
     </row>
     <row r="188">
@@ -3306,37 +3306,37 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>6050000000</v>
+        <v>5960000000</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>RGTI</t>
+          <t>CRSP</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Rigetti Computing Inc</t>
+          <t>CRISPR Therapeutics AG</t>
         </is>
       </c>
       <c r="L189" t="n">
-        <v>5970000000</v>
+        <v>5860000000</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>CRSP</t>
+          <t>RGTI</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>CRISPR Therapeutics AG</t>
+          <t>Rigetti Computing Inc</t>
         </is>
       </c>
       <c r="L190" t="n">
-        <v>5970000000</v>
+        <v>5500000000</v>
       </c>
     </row>
     <row r="191">
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>4940000000</v>
+        <v>4590000000</v>
       </c>
     </row>
     <row r="192">
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>4090000000</v>
+        <v>3850000000</v>
       </c>
     </row>
     <row r="193">
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3510000000</v>
+        <v>3270000000</v>
       </c>
     </row>
     <row r="194">
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3430000000</v>
+        <v>3260000000</v>
       </c>
     </row>
     <row r="195">
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>3290000000</v>
+        <v>3160000000</v>
       </c>
     </row>
     <row r="196">
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>3280000000</v>
+        <v>2990000000</v>
       </c>
     </row>
     <row r="197">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2860000000</v>
+        <v>2910000000</v>
       </c>
     </row>
     <row r="198">
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2830000000</v>
+        <v>2780000000</v>
       </c>
     </row>
     <row r="199">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>2110000000</v>
+        <v>1960000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1680000000</v>
+        <v>1720000000</v>
       </c>
     </row>
     <row r="202">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1440000000</v>
+        <v>1390000000</v>
       </c>
     </row>
     <row r="203">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>1050000000</v>
+        <v>983070000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>1030000000</v>
+        <v>958270000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>696250000</v>
+        <v>637080000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4562770000000</v>
+        <v>4602870000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4765710000000</v>
+        <v>4939700000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4426710000000</v>
+        <v>4379180000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2888470000000</v>
+        <v>2847620000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2646030000000</v>
+        <v>2620650000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2243520000000</v>
+        <v>2266390000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1764020000000</v>
+        <v>1849220000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1562600000000</v>
+        <v>1530970000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1513180000000</v>
+        <v>1479980000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,67 +696,67 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1163580000000</v>
+        <v>1145000000000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BRK-B</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Inc</t>
+          <t>Micron Technology Inc</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1085610000000</v>
+        <v>1071570000000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>BRK-B</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Micron Technology Inc</t>
+          <t>Berkshire Hathaway Inc</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1059800000000</v>
+        <v>1067190000000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co</t>
+          <t>Walmart Inc</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>908940000000</v>
+        <v>900060000000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Walmart Inc</t>
+          <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>887640000000</v>
+        <v>885900000000</v>
       </c>
     </row>
     <row r="19">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>841570000000</v>
+        <v>843680000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>673440000000</v>
+        <v>681670000000</v>
       </c>
     </row>
     <row r="21">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>663590000000</v>
+        <v>654790000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>643300000000</v>
+        <v>634060000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>587230000000</v>
+        <v>584910000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,22 +846,22 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>469730000000</v>
+        <v>459340000000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Abbvie Inc</t>
+          <t>Applied Materials Inc</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>449910000000</v>
+        <v>452950000000</v>
       </c>
     </row>
     <row r="26">
@@ -876,22 +876,22 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>440610000000</v>
+        <v>448610000000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Applied Materials Inc</t>
+          <t>Abbvie Inc</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>440250000000</v>
+        <v>446540000000</v>
       </c>
     </row>
     <row r="28">
@@ -906,67 +906,67 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>433050000000</v>
+        <v>436720000000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Bank Of America Corp</t>
+          <t>Costco Wholesale Corp</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>424800000000</v>
+        <v>422690000000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Costco Wholesale Corp</t>
+          <t>Lam Research Corp</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>420200000000</v>
+        <v>416630000000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Oracle Corp</t>
+          <t>Bank Of America Corp</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>407870000000</v>
+        <v>413730000000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Lam Research Corp</t>
+          <t>Oracle Corp</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>407850000000</v>
+        <v>404680000000</v>
       </c>
     </row>
     <row r="33">
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>388860000000</v>
+        <v>386510000000</v>
       </c>
     </row>
     <row r="34">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>382880000000</v>
+        <v>371460000000</v>
       </c>
     </row>
     <row r="35">
@@ -1011,52 +1011,52 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>361620000000</v>
+        <v>358830000000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble Co</t>
+          <t>Chevron Corp</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>355690000000</v>
+        <v>350460000000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Procter &amp; Gamble Co</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>350220000000</v>
+        <v>345560000000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Chevron Corp</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>346560000000</v>
+        <v>343960000000</v>
       </c>
     </row>
     <row r="39">
@@ -1071,22 +1071,22 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>344210000000</v>
+        <v>335240000000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>322130000000</v>
+        <v>319460000000</v>
       </c>
     </row>
     <row r="41">
@@ -1101,22 +1101,22 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>320780000000</v>
+        <v>318290000000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>Palantir Technologies Inc</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>319660000000</v>
+        <v>316970000000</v>
       </c>
     </row>
     <row r="43">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>318260000000</v>
+        <v>311170000000</v>
       </c>
     </row>
     <row r="44">
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>307690000000</v>
+        <v>303750000000</v>
       </c>
     </row>
     <row r="45">
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>299500000000</v>
+        <v>293550000000</v>
       </c>
     </row>
     <row r="46">
@@ -1176,37 +1176,37 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>292680000000</v>
+        <v>291560000000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>KLA Corp</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>289430000000</v>
+        <v>288920000000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>International Business Machines Corp</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>287730000000</v>
+        <v>287800000000</v>
       </c>
     </row>
     <row r="49">
@@ -1221,52 +1221,52 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>287450000000</v>
+        <v>284050000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>KLA Corp</t>
+          <t>International Business Machines Corp</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>282770000000</v>
+        <v>283890000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>274690000000</v>
+        <v>280040000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>270510000000</v>
+        <v>274230000000</v>
       </c>
     </row>
     <row r="53">
@@ -1281,112 +1281,112 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>270480000000</v>
+        <v>262480000000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>Wells Fargo &amp; Co</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>266930000000</v>
+        <v>261830000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Co</t>
+          <t>Alibaba Group Holding Ltd ADR</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>266790000000</v>
+        <v>261640000000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Linde Plc</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>248980000000</v>
+        <v>261280000000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Citigroup Inc</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>241410000000</v>
+        <v>255780000000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>Linde Plc</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>239560000000</v>
+        <v>244100000000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>American Express Co</t>
+          <t>Citigroup Inc</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>238530000000</v>
+        <v>235610000000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Alibaba Group Holding Ltd ADR</t>
+          <t>American Express Co</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>235610000000</v>
+        <v>229530000000</v>
       </c>
     </row>
     <row r="61">
@@ -1401,67 +1401,67 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>228600000000</v>
+        <v>229290000000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>McDonald's Corp</t>
+          <t>AMGEN Inc</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>200510000000</v>
+        <v>198610000000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>T-Mobile US Inc</t>
+          <t>McDonald's Corp</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>199920000000</v>
+        <v>197700000000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AMGEN Inc</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>198670000000</v>
+        <v>196630000000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>T-Mobile US Inc</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>198170000000</v>
+        <v>194950000000</v>
       </c>
     </row>
     <row r="66">
@@ -1476,97 +1476,97 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>198150000000</v>
+        <v>194780000000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>192850000000</v>
+        <v>194610000000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>191990000000</v>
+        <v>189680000000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Toyota Motor Corp ADR</t>
+          <t>Thermo Fisher Scientific Inc</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>190920000000</v>
+        <v>189580000000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Sap SE ADR</t>
+          <t>Toyota Motor Corp ADR</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>190040000000</v>
+        <v>188500000000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NextEra Energy Inc</t>
+          <t>Sap SE ADR</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>184510000000</v>
+        <v>183800000000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>NextEra Energy Inc</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>183410000000</v>
+        <v>182370000000</v>
       </c>
     </row>
     <row r="73">
@@ -1581,7 +1581,7 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>182630000000</v>
+        <v>177330000000</v>
       </c>
     </row>
     <row r="74">
@@ -1596,52 +1596,52 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>177840000000</v>
+        <v>177250000000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>Charles Schwab Corp</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>177370000000</v>
+        <v>176870000000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Charles Schwab Corp</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>177270000000</v>
+        <v>175620000000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>173600000000</v>
+        <v>175420000000</v>
       </c>
     </row>
     <row r="78">
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>169300000000</v>
+        <v>168630000000</v>
       </c>
     </row>
     <row r="79">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>169280000000</v>
+        <v>167920000000</v>
       </c>
     </row>
     <row r="80">
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>166940000000</v>
+        <v>165790000000</v>
       </c>
     </row>
     <row r="81">
@@ -1701,37 +1701,37 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>166690000000</v>
+        <v>164170000000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Blackrock Inc</t>
+          <t>Deere &amp; Co</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>164140000000</v>
+        <v>161080000000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Deere &amp; Co</t>
+          <t>Blackrock Inc</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>162940000000</v>
+        <v>161030000000</v>
       </c>
     </row>
     <row r="84">
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>159550000000</v>
+        <v>158380000000</v>
       </c>
     </row>
     <row r="85">
@@ -1761,142 +1761,142 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>158160000000</v>
+        <v>154710000000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Intuitive Surgical Inc</t>
+          <t>Uber Technologies Inc</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>151330000000</v>
+        <v>149820000000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Uber Technologies Inc</t>
+          <t>Intuitive Surgical Inc</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>151310000000</v>
+        <v>147010000000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Blackstone Inc</t>
+          <t>AT&amp;T Inc</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>147670000000</v>
+        <v>146750000000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc</t>
+          <t>Blackstone Inc</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>146540000000</v>
+        <v>144900000000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>Chubb Limited</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>140990000000</v>
+        <v>137730000000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Chubb Limited</t>
+          <t>Salesforce Inc</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>139360000000</v>
+        <v>136430000000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Salesforce Inc</t>
+          <t>Progressive Corp</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>138840000000</v>
+        <v>136090000000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Danaher Corp</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>137440000000</v>
+        <v>135050000000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Progressive Corp</t>
+          <t>Danaher Corp</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>136970000000</v>
+        <v>135020000000</v>
       </c>
     </row>
     <row r="95">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>136720000000</v>
+        <v>134240000000</v>
       </c>
     </row>
     <row r="96">
@@ -1926,22 +1926,22 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>131260000000</v>
+        <v>127510000000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Lowe's Cos. Inc</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>123860000000</v>
+        <v>122070000000</v>
       </c>
     </row>
     <row r="98">
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>123440000000</v>
+        <v>121730000000</v>
       </c>
     </row>
     <row r="99">
@@ -1971,67 +1971,67 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>121840000000</v>
+        <v>121580000000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Co</t>
+          <t>PDD Holdings Inc ADR</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>118380000000</v>
+        <v>120620000000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Starbucks Corp</t>
+          <t>Lowe's Cos. Inc</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>118080000000</v>
+        <v>119350000000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PDD Holdings Inc ADR</t>
+          <t>Starbucks Corp</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>117470000000</v>
+        <v>118380000000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>Bristol-Myers Squibb Co</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>117380000000</v>
+        <v>117500000000</v>
       </c>
     </row>
     <row r="104">
@@ -2046,82 +2046,82 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>107310000000</v>
+        <v>104980000000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Spotify Technology SA</t>
+          <t>Equinix Inc</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>101670000000</v>
+        <v>100200000000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Equinix Inc</t>
+          <t>Spotify Technology SA</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>100890000000</v>
+        <v>99870000000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>98170000000</v>
+        <v>97090000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>Automatic Data Processing Inc</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>97970000000</v>
+        <v>96480000000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>95470000000</v>
+        <v>95020000000</v>
       </c>
     </row>
     <row r="110">
@@ -2136,22 +2136,22 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>95170000000</v>
+        <v>93450000000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>HCA Healthcare Inc</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>93860000000</v>
+        <v>92940000000</v>
       </c>
     </row>
     <row r="112">
@@ -2166,22 +2166,22 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>91940000000</v>
+        <v>91730000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>HCA Healthcare Inc</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>91410000000</v>
+        <v>91090000000</v>
       </c>
     </row>
     <row r="114">
@@ -2196,7 +2196,7 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>91070000000</v>
+        <v>90570000000</v>
       </c>
     </row>
     <row r="115">
@@ -2211,67 +2211,67 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>90960000000</v>
+        <v>90360000000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Airbnb Inc</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>89680000000</v>
+        <v>87820000000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>MMC</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>Marsh</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>88060000000</v>
+        <v>86270000000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>Airbnb Inc</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>86980000000</v>
+        <v>86160000000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>MMC</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Marsh</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>85760000000</v>
+        <v>83950000000</v>
       </c>
     </row>
     <row r="120">
@@ -2286,202 +2286,202 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>82410000000</v>
+        <v>80690000000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp</t>
+          <t>Intercontinental Exchange Inc</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>77980000000</v>
+        <v>77570000000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange Inc</t>
+          <t>Northrop Grumman Corp</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>77160000000</v>
+        <v>77420000000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Intuit Inc</t>
+          <t>Cigna Group</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>76910000000</v>
+        <v>76640000000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive Co</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>76040000000</v>
+        <v>75350000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Cigna Group</t>
+          <t>Colgate-Palmolive Co</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>75820000000</v>
+        <v>74450000000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Intuit Inc</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>75700000000</v>
+        <v>74430000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals Inc</t>
+          <t>SLB Ltd</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>70900000000</v>
+        <v>70910000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SLB Ltd</t>
+          <t>Regeneron Pharmaceuticals Inc</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>69400000000</v>
+        <v>69500000000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Apollo Global Management Inc</t>
+          <t>General Motors Company</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>68800000000</v>
+        <v>68740000000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>General Motors Company</t>
+          <t>Apollo Global Management Inc</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>68550000000</v>
+        <v>68110000000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Ferrari NV</t>
+          <t>Astera Labs Inc</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>68310000000</v>
+        <v>67390000000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>NU</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Nu Holdings Ltd</t>
+          <t>Ferrari NV</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>66150000000</v>
+        <v>66200000000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Astera Labs Inc</t>
+          <t>Nu Holdings Ltd</t>
         </is>
       </c>
       <c r="L133" t="n">
-        <v>65630000000</v>
+        <v>64990000000</v>
       </c>
     </row>
     <row r="134">
@@ -2496,82 +2496,82 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>63990000000</v>
+        <v>63520000000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Sea Ltd ADR</t>
+          <t>Target Corp</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>59090000000</v>
+        <v>60140000000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Target Corp</t>
+          <t>Sea Ltd ADR</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>57930000000</v>
+        <v>59710000000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences Corp</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L137" t="n">
-        <v>54600000000</v>
+        <v>54480000000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Ford Motor Co</t>
+          <t>Edwards Lifesciences Corp</t>
         </is>
       </c>
       <c r="L138" t="n">
-        <v>54030000000</v>
+        <v>53920000000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Vistra Corp</t>
+          <t>Ford Motor Co</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>52510000000</v>
+        <v>53790000000</v>
       </c>
     </row>
     <row r="140">
@@ -2586,97 +2586,97 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>51400000000</v>
+        <v>53300000000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Rocket Lab Corp</t>
+          <t>Vistra Corp</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>49890000000</v>
+        <v>52200000000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Rocket Lab Corp</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>49120000000</v>
+        <v>49860000000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Block Inc</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>46160000000</v>
+        <v>49100000000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Block Inc</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>45570000000</v>
+        <v>45560000000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Autodesk Inc</t>
+          <t>MSCI Inc</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>44810000000</v>
+        <v>43990000000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MSCI Inc</t>
+          <t>Autodesk Inc</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>44270000000</v>
+        <v>43470000000</v>
       </c>
     </row>
     <row r="147">
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>44060000000</v>
+        <v>42880000000</v>
       </c>
     </row>
     <row r="148">
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>43080000000</v>
+        <v>41990000000</v>
       </c>
     </row>
     <row r="149">
@@ -2721,7 +2721,7 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>40270000000</v>
+        <v>39280000000</v>
       </c>
     </row>
     <row r="150">
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>38390000000</v>
+        <v>37600000000</v>
       </c>
     </row>
     <row r="151">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>36540000000</v>
+        <v>35120000000</v>
       </c>
     </row>
     <row r="152">
@@ -2766,52 +2766,52 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>35480000000</v>
+        <v>34060000000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Strategy Inc</t>
+          <t>JD.com Inc ADR</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>34120000000</v>
+        <v>33520000000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Twilio Inc</t>
+          <t>Strategy Inc</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>32170000000</v>
+        <v>32900000000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>JD</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>JD.com Inc ADR</t>
+          <t>Twilio Inc</t>
         </is>
       </c>
       <c r="L155" t="n">
-        <v>32140000000</v>
+        <v>32710000000</v>
       </c>
     </row>
     <row r="156">
@@ -2826,37 +2826,37 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>31980000000</v>
+        <v>31480000000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>Estee Lauder Cos. Inc</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>31650000000</v>
+        <v>29590000000</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Estee Lauder Cos. Inc</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="L158" t="n">
-        <v>30550000000</v>
+        <v>29280000000</v>
       </c>
     </row>
     <row r="159">
@@ -2871,37 +2871,37 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>29010000000</v>
+        <v>28420000000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AFRM</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Fiserv Inc</t>
+          <t>Affirm Holdings Inc</t>
         </is>
       </c>
       <c r="L160" t="n">
-        <v>28110000000</v>
+        <v>27220000000</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>AFRM</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Affirm Holdings Inc</t>
+          <t>Fiserv Inc</t>
         </is>
       </c>
       <c r="L161" t="n">
-        <v>28000000000</v>
+        <v>26980000000</v>
       </c>
     </row>
     <row r="162">
@@ -2916,52 +2916,52 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>25120000000</v>
+        <v>25630000000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>DKNG</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>First Solar Inc</t>
+          <t>DraftKings Inc</t>
         </is>
       </c>
       <c r="L163" t="n">
-        <v>24470000000</v>
+        <v>24160000000</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Zscaler Inc</t>
+          <t>First Solar Inc</t>
         </is>
       </c>
       <c r="L164" t="n">
-        <v>24180000000</v>
+        <v>24100000000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>DKNG</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>DraftKings Inc</t>
+          <t>Zscaler Inc</t>
         </is>
       </c>
       <c r="L165" t="n">
-        <v>23930000000</v>
+        <v>23210000000</v>
       </c>
     </row>
     <row r="166">
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>22770000000</v>
+        <v>22740000000</v>
       </c>
     </row>
     <row r="167">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>20950000000</v>
+        <v>20660000000</v>
       </c>
     </row>
     <row r="168">
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>19120000000</v>
+        <v>18490000000</v>
       </c>
     </row>
     <row r="169">
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>16980000000</v>
+        <v>18220000000</v>
       </c>
     </row>
     <row r="170">
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>16930000000</v>
+        <v>16830000000</v>
       </c>
     </row>
     <row r="171">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>16190000000</v>
+        <v>15930000000</v>
       </c>
     </row>
     <row r="172">
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>16110000000</v>
+        <v>15620000000</v>
       </c>
     </row>
     <row r="173">
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>16110000000</v>
+        <v>15620000000</v>
       </c>
     </row>
     <row r="174">
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>14210000000</v>
+        <v>15350000000</v>
       </c>
     </row>
     <row r="175">
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>12560000000</v>
+        <v>12620000000</v>
       </c>
     </row>
     <row r="176">
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>12290000000</v>
+        <v>11940000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>10920000000</v>
+        <v>10700000000</v>
       </c>
     </row>
     <row r="178">
@@ -3156,37 +3156,37 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>9380000000</v>
+        <v>9290000000</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>PRMB</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Primo Brands Corp</t>
+          <t>Applied Digital Corp</t>
         </is>
       </c>
       <c r="L179" t="n">
-        <v>9040000000</v>
+        <v>8980000000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>PRMB</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Applied Digital Corp</t>
+          <t>Primo Brands Corp</t>
         </is>
       </c>
       <c r="L180" t="n">
-        <v>8780000000</v>
+        <v>8590000000</v>
       </c>
     </row>
     <row r="181">
@@ -3201,7 +3201,7 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>8370000000</v>
+        <v>8350000000</v>
       </c>
     </row>
     <row r="182">
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>8330000000</v>
+        <v>8230000000</v>
       </c>
     </row>
     <row r="183">
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>8230000000</v>
+        <v>7980000000</v>
       </c>
     </row>
     <row r="184">
@@ -3246,7 +3246,7 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>8100000000</v>
+        <v>7820000000</v>
       </c>
     </row>
     <row r="185">
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>8000000000</v>
+        <v>7700000000</v>
       </c>
     </row>
     <row r="186">
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>7500000000</v>
+        <v>7380000000</v>
       </c>
     </row>
     <row r="187">
@@ -3291,52 +3291,52 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>6230000000</v>
+        <v>6110000000</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>LMND</t>
+          <t>CRSP</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Lemonade Inc</t>
+          <t>CRISPR Therapeutics AG</t>
         </is>
       </c>
       <c r="L188" t="n">
-        <v>5960000000</v>
+        <v>5710000000</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>CRSP</t>
+          <t>RGTI</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>CRISPR Therapeutics AG</t>
+          <t>Rigetti Computing Inc</t>
         </is>
       </c>
       <c r="L189" t="n">
-        <v>5860000000</v>
+        <v>5620000000</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>RGTI</t>
+          <t>LMND</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Rigetti Computing Inc</t>
+          <t>Lemonade Inc</t>
         </is>
       </c>
       <c r="L190" t="n">
-        <v>5500000000</v>
+        <v>5460000000</v>
       </c>
     </row>
     <row r="191">
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>4590000000</v>
+        <v>4580000000</v>
       </c>
     </row>
     <row r="192">
@@ -3366,18 +3366,18 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>3850000000</v>
+        <v>3930000000</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>LEU</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>NuScale Power Corp</t>
+          <t>Centrus Energy Corp</t>
         </is>
       </c>
       <c r="L193" t="n">
@@ -3387,61 +3387,61 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>LEU</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Centrus Energy Corp</t>
+          <t>NuScale Power Corp</t>
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3260000000</v>
+        <v>3200000000</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>FSLY</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Upstart Holdings Inc</t>
+          <t>Fastly Inc</t>
         </is>
       </c>
       <c r="L195" t="n">
-        <v>3160000000</v>
+        <v>3090000000</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>FLNC</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Fluence Energy Inc</t>
+          <t>Upstart Holdings Inc</t>
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2990000000</v>
+        <v>3040000000</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>FSLY</t>
+          <t>FLNC</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Fastly Inc</t>
+          <t>Fluence Energy Inc</t>
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2910000000</v>
+        <v>2830000000</v>
       </c>
     </row>
     <row r="198">
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2780000000</v>
+        <v>2690000000</v>
       </c>
     </row>
     <row r="199">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>2460000000</v>
+        <v>2430000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1960000000</v>
+        <v>1970000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1720000000</v>
+        <v>1640000000</v>
       </c>
     </row>
     <row r="202">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1390000000</v>
+        <v>1380000000</v>
       </c>
     </row>
     <row r="203">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>983070000</v>
+        <v>987500000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>958270000</v>
+        <v>985510000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>637080000</v>
+        <v>621960000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4602870000000</v>
+        <v>4644440000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4939700000000</v>
+        <v>4907280000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4379180000000</v>
+        <v>4348000000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2847620000000</v>
+        <v>2855190000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2620650000000</v>
+        <v>2657440000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2266390000000</v>
+        <v>2266280000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1849220000000</v>
+        <v>1908310000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1530970000000</v>
+        <v>1602960000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1479980000000</v>
+        <v>1526890000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1145000000000</v>
+        <v>1146050000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1071570000000</v>
+        <v>1119950000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,37 +726,37 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1067190000000</v>
+        <v>1071680000000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Walmart Inc</t>
+          <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>900060000000</v>
+        <v>898900000000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co</t>
+          <t>Walmart Inc</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>885900000000</v>
+        <v>892980000000</v>
       </c>
     </row>
     <row r="19">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>843680000000</v>
+        <v>891480000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>681670000000</v>
+        <v>695390000000</v>
       </c>
     </row>
     <row r="21">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>654790000000</v>
+        <v>656050000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>634060000000</v>
+        <v>623710000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,142 +831,142 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>584910000000</v>
+        <v>569700000000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated</t>
+          <t>Applied Materials Inc</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>459340000000</v>
+        <v>467370000000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Applied Materials Inc</t>
+          <t>Cisco Systems Inc</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>452950000000</v>
+        <v>466310000000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cisco Systems Inc</t>
+          <t>Mastercard Incorporated</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>448610000000</v>
+        <v>462290000000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Abbvie Inc</t>
+          <t>Lam Research Corp</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>446540000000</v>
+        <v>441660000000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Caterpillar Inc</t>
+          <t>Abbvie Inc</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>436720000000</v>
+        <v>441540000000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Costco Wholesale Corp</t>
+          <t>Caterpillar Inc</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>422690000000</v>
+        <v>432260000000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Lam Research Corp</t>
+          <t>Bank Of America Corp</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>416630000000</v>
+        <v>420470000000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Bank Of America Corp</t>
+          <t>Oracle Corp</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>413730000000</v>
+        <v>415420000000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Oracle Corp</t>
+          <t>Costco Wholesale Corp</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>404680000000</v>
+        <v>404880000000</v>
       </c>
     </row>
     <row r="33">
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>386510000000</v>
+        <v>392030000000</v>
       </c>
     </row>
     <row r="34">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>371460000000</v>
+        <v>374600000000</v>
       </c>
     </row>
     <row r="35">
@@ -1011,82 +1011,82 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>358830000000</v>
+        <v>355510000000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Chevron Corp</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>350460000000</v>
+        <v>350360000000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble Co</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>345560000000</v>
+        <v>348850000000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Chevron Corp</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>343960000000</v>
+        <v>346640000000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Home Depot Inc</t>
+          <t>Procter &amp; Gamble Co</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>335240000000</v>
+        <v>341950000000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>Home Depot Inc</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>319460000000</v>
+        <v>337750000000</v>
       </c>
     </row>
     <row r="41">
@@ -1101,202 +1101,202 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>318290000000</v>
+        <v>317790000000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc</t>
+          <t>Goldman Sachs Group Inc</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>316970000000</v>
+        <v>311520000000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Merck &amp; Co Inc</t>
+          <t>Palantir Technologies Inc</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>311170000000</v>
+        <v>309350000000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Goldman Sachs Group Inc</t>
+          <t>Merck &amp; Co Inc</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>303750000000</v>
+        <v>308900000000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Astrazeneca plc</t>
+          <t>KLA Corp</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>293550000000</v>
+        <v>299820000000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Philip Morris International Inc</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>291560000000</v>
+        <v>291870000000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>KLA Corp</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>288920000000</v>
+        <v>288940000000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>NVS</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>Novartis AG ADR</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>287800000000</v>
+        <v>283040000000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>NVS</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Novartis AG ADR</t>
+          <t>Philip Morris International Inc</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>284050000000</v>
+        <v>282360000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>International Business Machines Corp</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>283890000000</v>
+        <v>280790000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>International Business Machines Corp</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>280040000000</v>
+        <v>277550000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>Astrazeneca plc</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>274230000000</v>
+        <v>276810000000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>262480000000</v>
+        <v>275720000000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Co</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>261830000000</v>
+        <v>275190000000</v>
       </c>
     </row>
     <row r="55">
@@ -1311,37 +1311,37 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>261640000000</v>
+        <v>266820000000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>Wells Fargo &amp; Co</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>261280000000</v>
+        <v>265960000000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>255780000000</v>
+        <v>262870000000</v>
       </c>
     </row>
     <row r="58">
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>244100000000</v>
+        <v>243120000000</v>
       </c>
     </row>
     <row r="59">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>235610000000</v>
+        <v>239350000000</v>
       </c>
     </row>
     <row r="60">
@@ -1386,7 +1386,7 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>229530000000</v>
+        <v>236580000000</v>
       </c>
     </row>
     <row r="61">
@@ -1401,127 +1401,127 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>229290000000</v>
+        <v>226950000000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AMGEN Inc</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>198610000000</v>
+        <v>202020000000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>McDonald's Corp</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>197700000000</v>
+        <v>201430000000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>196630000000</v>
+        <v>199240000000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>T-Mobile US Inc</t>
+          <t>McDonald's Corp</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>194950000000</v>
+        <v>196450000000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PepsiCo Inc</t>
+          <t>T-Mobile US Inc</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>194780000000</v>
+        <v>196400000000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>AMGEN Inc</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>194610000000</v>
+        <v>196250000000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>Thermo Fisher Scientific Inc</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>189680000000</v>
+        <v>194990000000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc</t>
+          <t>PepsiCo Inc</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>189580000000</v>
+        <v>188420000000</v>
       </c>
     </row>
     <row r="70">
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>188500000000</v>
+        <v>185490000000</v>
       </c>
     </row>
     <row r="71">
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>183800000000</v>
+        <v>185010000000</v>
       </c>
     </row>
     <row r="72">
@@ -1566,22 +1566,22 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>182370000000</v>
+        <v>181660000000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Boeing Co</t>
+          <t>Charles Schwab Corp</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>177330000000</v>
+        <v>177240000000</v>
       </c>
     </row>
     <row r="74">
@@ -1596,52 +1596,52 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>177250000000</v>
+        <v>176380000000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Charles Schwab Corp</t>
+          <t>Boeing Co</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>176870000000</v>
+        <v>175880000000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>175620000000</v>
+        <v>174830000000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>175420000000</v>
+        <v>174200000000</v>
       </c>
     </row>
     <row r="78">
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>168630000000</v>
+        <v>167410000000</v>
       </c>
     </row>
     <row r="79">
@@ -1671,82 +1671,82 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>167920000000</v>
+        <v>167000000000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Blackrock Inc</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>165790000000</v>
+        <v>165800000000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Novo Nordisk ADR</t>
+          <t>Corning Inc</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>164170000000</v>
+        <v>165570000000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Deere &amp; Co</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>161080000000</v>
+        <v>164430000000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Blackrock Inc</t>
+          <t>Novo Nordisk ADR</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>161030000000</v>
+        <v>164140000000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Corning Inc</t>
+          <t>Deere &amp; Co</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>158380000000</v>
+        <v>160050000000</v>
       </c>
     </row>
     <row r="85">
@@ -1761,7 +1761,7 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>154710000000</v>
+        <v>159830000000</v>
       </c>
     </row>
     <row r="86">
@@ -1776,22 +1776,22 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>149820000000</v>
+        <v>151350000000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Intuitive Surgical Inc</t>
+          <t>Blackstone Inc</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>147010000000</v>
+        <v>149210000000</v>
       </c>
     </row>
     <row r="88">
@@ -1806,112 +1806,112 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>146750000000</v>
+        <v>146190000000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Blackstone Inc</t>
+          <t>Intuitive Surgical Inc</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>144900000000</v>
+        <v>145760000000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Chubb Limited</t>
+          <t>Danaher Corp</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>137730000000</v>
+        <v>138710000000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Salesforce Inc</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>136430000000</v>
+        <v>136010000000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Progressive Corp</t>
+          <t>Chubb Limited</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>136090000000</v>
+        <v>134900000000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>135050000000</v>
+        <v>134580000000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Danaher Corp</t>
+          <t>Progressive Corp</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>135020000000</v>
+        <v>134120000000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Salesforce Inc</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>134240000000</v>
+        <v>133090000000</v>
       </c>
     </row>
     <row r="96">
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>127510000000</v>
+        <v>128160000000</v>
       </c>
     </row>
     <row r="97">
@@ -1941,82 +1941,82 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>122070000000</v>
+        <v>124420000000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corp</t>
+          <t>PDD Holdings Inc ADR</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>121730000000</v>
+        <v>122240000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Altria Group Inc</t>
+          <t>Starbucks Corp</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>121580000000</v>
+        <v>121280000000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PDD Holdings Inc ADR</t>
+          <t>Altria Group Inc</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>120620000000</v>
+        <v>119550000000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Lowe's Cos. Inc</t>
+          <t>Lockheed Martin Corp</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>119350000000</v>
+        <v>119490000000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Starbucks Corp</t>
+          <t>Lowe's Cos. Inc</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>118380000000</v>
+        <v>119430000000</v>
       </c>
     </row>
     <row r="103">
@@ -2031,7 +2031,7 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>117500000000</v>
+        <v>118320000000</v>
       </c>
     </row>
     <row r="104">
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>104980000000</v>
+        <v>105460000000</v>
       </c>
     </row>
     <row r="105">
@@ -2061,7 +2061,7 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>100200000000</v>
+        <v>102060000000</v>
       </c>
     </row>
     <row r="106">
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>99870000000</v>
+        <v>100010000000</v>
       </c>
     </row>
     <row r="107">
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>97090000000</v>
+        <v>97940000000</v>
       </c>
     </row>
     <row r="108">
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>96480000000</v>
+        <v>96450000000</v>
       </c>
     </row>
     <row r="109">
@@ -2121,142 +2121,142 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>95020000000</v>
+        <v>96420000000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>United Parcel Service Inc</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>93450000000</v>
+        <v>95750000000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>United Parcel Service Inc</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>92940000000</v>
+        <v>94130000000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>MercadoLibre Inc</t>
+          <t>Snowflake Inc</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>91730000000</v>
+        <v>92710000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>HCA Healthcare Inc</t>
+          <t>MercadoLibre Inc</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>91090000000</v>
+        <v>91650000000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Snowflake Inc</t>
+          <t>Elevance Health Inc</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>90570000000</v>
+        <v>91290000000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Elevance Health Inc</t>
+          <t>HCA Healthcare Inc</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>90360000000</v>
+        <v>90730000000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>Airbnb Inc</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>87820000000</v>
+        <v>88530000000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>MMC</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Marsh</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>86270000000</v>
+        <v>88500000000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>MMC</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Airbnb Inc</t>
+          <t>Marsh</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>86160000000</v>
+        <v>86240000000</v>
       </c>
     </row>
     <row r="119">
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>83950000000</v>
+        <v>85100000000</v>
       </c>
     </row>
     <row r="120">
@@ -2286,202 +2286,202 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>80690000000</v>
+        <v>81020000000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange Inc</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>77570000000</v>
+        <v>77260000000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp</t>
+          <t>Cigna Group</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>77420000000</v>
+        <v>77190000000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Cigna Group</t>
+          <t>Intercontinental Exchange Inc</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>76640000000</v>
+        <v>76410000000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Northrop Grumman Corp</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>75350000000</v>
+        <v>75590000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive Co</t>
+          <t>Intuit Inc</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>74450000000</v>
+        <v>74780000000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Intuit Inc</t>
+          <t>Colgate-Palmolive Co</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>74430000000</v>
+        <v>72830000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>SLB Ltd</t>
+          <t>Astera Labs Inc</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>70910000000</v>
+        <v>71550000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals Inc</t>
+          <t>SLB Ltd</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>69500000000</v>
+        <v>70630000000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>General Motors Company</t>
+          <t>Regeneron Pharmaceuticals Inc</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>68740000000</v>
+        <v>70030000000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Apollo Global Management Inc</t>
+          <t>General Motors Company</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>68110000000</v>
+        <v>69110000000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Astera Labs Inc</t>
+          <t>Apollo Global Management Inc</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>67390000000</v>
+        <v>69090000000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Ferrari NV</t>
+          <t>Nu Holdings Ltd</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>66200000000</v>
+        <v>66440000000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>NU</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Nu Holdings Ltd</t>
+          <t>Ferrari NV</t>
         </is>
       </c>
       <c r="L133" t="n">
-        <v>64990000000</v>
+        <v>66130000000</v>
       </c>
     </row>
     <row r="134">
@@ -2496,37 +2496,37 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>63520000000</v>
+        <v>63350000000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Target Corp</t>
+          <t>Sea Ltd ADR</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>60140000000</v>
+        <v>61860000000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Sea Ltd ADR</t>
+          <t>Target Corp</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>59710000000</v>
+        <v>60080000000</v>
       </c>
     </row>
     <row r="137">
@@ -2541,67 +2541,67 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>54480000000</v>
+        <v>54410000000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences Corp</t>
+          <t>Ford Motor Co</t>
         </is>
       </c>
       <c r="L138" t="n">
-        <v>53920000000</v>
+        <v>54230000000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Ford Motor Co</t>
+          <t>Vistra Corp</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>53790000000</v>
+        <v>53270000000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Occidental Petroleum Corp</t>
+          <t>Edwards Lifesciences Corp</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>53300000000</v>
+        <v>52590000000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Vistra Corp</t>
+          <t>Occidental Petroleum Corp</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>52200000000</v>
+        <v>52020000000</v>
       </c>
     </row>
     <row r="142">
@@ -2616,7 +2616,7 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>49860000000</v>
+        <v>49380000000</v>
       </c>
     </row>
     <row r="143">
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>49100000000</v>
+        <v>48940000000</v>
       </c>
     </row>
     <row r="144">
@@ -2646,22 +2646,22 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>45560000000</v>
+        <v>46080000000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MSCI Inc</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>43990000000</v>
+        <v>44380000000</v>
       </c>
     </row>
     <row r="146">
@@ -2676,22 +2676,22 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>43470000000</v>
+        <v>44010000000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>MSCI Inc</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>42880000000</v>
+        <v>43920000000</v>
       </c>
     </row>
     <row r="148">
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>41990000000</v>
+        <v>41740000000</v>
       </c>
     </row>
     <row r="149">
@@ -2721,7 +2721,7 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>39280000000</v>
+        <v>39980000000</v>
       </c>
     </row>
     <row r="150">
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>37600000000</v>
+        <v>38560000000</v>
       </c>
     </row>
     <row r="151">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>35120000000</v>
+        <v>36600000000</v>
       </c>
     </row>
     <row r="152">
@@ -2766,7 +2766,7 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>34060000000</v>
+        <v>34170000000</v>
       </c>
     </row>
     <row r="153">
@@ -2781,37 +2781,37 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>33520000000</v>
+        <v>33650000000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Strategy Inc</t>
+          <t>Twilio Inc</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>32900000000</v>
+        <v>33180000000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Twilio Inc</t>
+          <t>Strategy Inc</t>
         </is>
       </c>
       <c r="L155" t="n">
-        <v>32710000000</v>
+        <v>32900000000</v>
       </c>
     </row>
     <row r="156">
@@ -2832,31 +2832,31 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Estee Lauder Cos. Inc</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>29590000000</v>
+        <v>30380000000</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>Estee Lauder Cos. Inc</t>
         </is>
       </c>
       <c r="L158" t="n">
-        <v>29280000000</v>
+        <v>29660000000</v>
       </c>
     </row>
     <row r="159">
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>28420000000</v>
+        <v>29320000000</v>
       </c>
     </row>
     <row r="160">
@@ -2886,7 +2886,7 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>27220000000</v>
+        <v>28060000000</v>
       </c>
     </row>
     <row r="161">
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>26980000000</v>
+        <v>27540000000</v>
       </c>
     </row>
     <row r="162">
@@ -2916,37 +2916,37 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>25630000000</v>
+        <v>26360000000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>DKNG</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>DraftKings Inc</t>
+          <t>First Solar Inc</t>
         </is>
       </c>
       <c r="L163" t="n">
-        <v>24160000000</v>
+        <v>24550000000</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>First Solar Inc</t>
+          <t>SoFi Technologies Inc</t>
         </is>
       </c>
       <c r="L164" t="n">
-        <v>24100000000</v>
+        <v>23880000000</v>
       </c>
     </row>
     <row r="165">
@@ -2961,22 +2961,22 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>23210000000</v>
+        <v>23790000000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>DKNG</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>SoFi Technologies Inc</t>
+          <t>DraftKings Inc</t>
         </is>
       </c>
       <c r="L166" t="n">
-        <v>22740000000</v>
+        <v>23380000000</v>
       </c>
     </row>
     <row r="167">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>20660000000</v>
+        <v>20810000000</v>
       </c>
     </row>
     <row r="168">
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>18490000000</v>
+        <v>18610000000</v>
       </c>
     </row>
     <row r="169">
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>18220000000</v>
+        <v>18270000000</v>
       </c>
     </row>
     <row r="170">
@@ -3036,22 +3036,22 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>16830000000</v>
+        <v>16710000000</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>CRCL</t>
+          <t>GRAB</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Circle Internet Group Inc</t>
+          <t>Grab Holdings Limited</t>
         </is>
       </c>
       <c r="L171" t="n">
-        <v>15930000000</v>
+        <v>15900000000</v>
       </c>
     </row>
     <row r="172">
@@ -3066,22 +3066,22 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>15620000000</v>
+        <v>15900000000</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>GRAB</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Grab Holdings Limited</t>
+          <t>Circle Internet Group Inc</t>
         </is>
       </c>
       <c r="L173" t="n">
-        <v>15620000000</v>
+        <v>15660000000</v>
       </c>
     </row>
     <row r="174">
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>15350000000</v>
+        <v>14890000000</v>
       </c>
     </row>
     <row r="175">
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>12620000000</v>
+        <v>12720000000</v>
       </c>
     </row>
     <row r="176">
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>11940000000</v>
+        <v>12290000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>10700000000</v>
+        <v>10820000000</v>
       </c>
     </row>
     <row r="178">
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>9290000000</v>
+        <v>9410000000</v>
       </c>
     </row>
     <row r="179">
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>8980000000</v>
+        <v>9230000000</v>
       </c>
     </row>
     <row r="180">
@@ -3186,52 +3186,52 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>8590000000</v>
+        <v>8580000000</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>HIMS</t>
+          <t>OKLO</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Hims &amp; Hers Health Inc</t>
+          <t>Oklo Inc</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>8350000000</v>
+        <v>8570000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>OKLO</t>
+          <t>HIMS</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Oklo Inc</t>
+          <t>Hims &amp; Hers Health Inc</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>8230000000</v>
+        <v>8210000000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>MBLY</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>AeroVironment Inc</t>
+          <t>Mobileye Global Inc</t>
         </is>
       </c>
       <c r="L183" t="n">
-        <v>7980000000</v>
+        <v>8030000000</v>
       </c>
     </row>
     <row r="184">
@@ -3246,37 +3246,37 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>7820000000</v>
+        <v>7800000000</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>MBLY</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Mobileye Global Inc</t>
+          <t>Zillow Group Inc</t>
         </is>
       </c>
       <c r="L185" t="n">
-        <v>7700000000</v>
+        <v>7640000000</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Zillow Group Inc</t>
+          <t>AeroVironment Inc</t>
         </is>
       </c>
       <c r="L186" t="n">
-        <v>7380000000</v>
+        <v>7510000000</v>
       </c>
     </row>
     <row r="187">
@@ -3291,37 +3291,37 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>6110000000</v>
+        <v>6470000000</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>CRSP</t>
+          <t>RGTI</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>CRISPR Therapeutics AG</t>
+          <t>Rigetti Computing Inc</t>
         </is>
       </c>
       <c r="L188" t="n">
-        <v>5710000000</v>
+        <v>5650000000</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>RGTI</t>
+          <t>CRSP</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Rigetti Computing Inc</t>
+          <t>CRISPR Therapeutics AG</t>
         </is>
       </c>
       <c r="L189" t="n">
-        <v>5620000000</v>
+        <v>5430000000</v>
       </c>
     </row>
     <row r="190">
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>5460000000</v>
+        <v>5400000000</v>
       </c>
     </row>
     <row r="191">
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>4580000000</v>
+        <v>5040000000</v>
       </c>
     </row>
     <row r="192">
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>3930000000</v>
+        <v>4000000000</v>
       </c>
     </row>
     <row r="193">
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3270000000</v>
+        <v>3410000000</v>
       </c>
     </row>
     <row r="194">
@@ -3396,37 +3396,37 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3200000000</v>
+        <v>3300000000</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>FSLY</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Fastly Inc</t>
+          <t>Upstart Holdings Inc</t>
         </is>
       </c>
       <c r="L195" t="n">
-        <v>3090000000</v>
+        <v>3180000000</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>FSLY</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Upstart Holdings Inc</t>
+          <t>Fastly Inc</t>
         </is>
       </c>
       <c r="L196" t="n">
-        <v>3040000000</v>
+        <v>3180000000</v>
       </c>
     </row>
     <row r="197">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2830000000</v>
+        <v>3090000000</v>
       </c>
     </row>
     <row r="198">
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2690000000</v>
+        <v>2770000000</v>
       </c>
     </row>
     <row r="199">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>2430000000</v>
+        <v>2490000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1970000000</v>
+        <v>2060000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1640000000</v>
+        <v>1660000000</v>
       </c>
     </row>
     <row r="202">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1380000000</v>
+        <v>1400000000</v>
       </c>
     </row>
     <row r="203">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>987500000</v>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>985510000</v>
+        <v>990770000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>621960000</v>
+        <v>647770000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4644440000000</v>
+        <v>4631220000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4907280000000</v>
+        <v>5105230000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4348000000000</v>
+        <v>4329650000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2855190000000</v>
+        <v>2860690000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2657440000000</v>
+        <v>2639150000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2266280000000</v>
+        <v>2251500000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1908310000000</v>
+        <v>1902890000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1602960000000</v>
+        <v>1698740000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1526890000000</v>
+        <v>1531430000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1146050000000</v>
+        <v>1119330000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1119950000000</v>
+        <v>1106010000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,22 +726,22 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1071680000000</v>
+        <v>1063780000000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co</t>
+          <t>Advanced Micro Devices Inc</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>898900000000</v>
+        <v>909700000000</v>
       </c>
     </row>
     <row r="18">
@@ -756,22 +756,22 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>892980000000</v>
+        <v>906430000000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices Inc</t>
+          <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>891480000000</v>
+        <v>901580000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>695390000000</v>
+        <v>692720000000</v>
       </c>
     </row>
     <row r="21">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>656050000000</v>
+        <v>657500000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>623710000000</v>
+        <v>618610000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>569700000000</v>
+        <v>575580000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>467370000000</v>
+        <v>478360000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>466310000000</v>
+        <v>478140000000</v>
       </c>
     </row>
     <row r="26">
@@ -876,22 +876,22 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>462290000000</v>
+        <v>465420000000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Lam Research Corp</t>
+          <t>Caterpillar Inc</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>441660000000</v>
+        <v>438720000000</v>
       </c>
     </row>
     <row r="28">
@@ -906,22 +906,22 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>441540000000</v>
+        <v>438310000000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Caterpillar Inc</t>
+          <t>Lam Research Corp</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>432260000000</v>
+        <v>438110000000</v>
       </c>
     </row>
     <row r="30">
@@ -936,37 +936,37 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>420470000000</v>
+        <v>423450000000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Oracle Corp</t>
+          <t>Costco Wholesale Corp</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>415420000000</v>
+        <v>406340000000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Costco Wholesale Corp</t>
+          <t>Oracle Corp</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>404880000000</v>
+        <v>405110000000</v>
       </c>
     </row>
     <row r="33">
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>392030000000</v>
+        <v>385620000000</v>
       </c>
     </row>
     <row r="34">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>374600000000</v>
+        <v>374840000000</v>
       </c>
     </row>
     <row r="35">
@@ -1011,52 +1011,52 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>355510000000</v>
+        <v>359210000000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Chevron Corp</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>350360000000</v>
+        <v>351320000000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>348850000000</v>
+        <v>350600000000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Chevron Corp</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>346640000000</v>
+        <v>344090000000</v>
       </c>
     </row>
     <row r="39">
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>341950000000</v>
+        <v>342400000000</v>
       </c>
     </row>
     <row r="40">
@@ -1086,67 +1086,67 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>337750000000</v>
+        <v>342310000000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Netflix Inc</t>
+          <t>Goldman Sachs Group Inc</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>317790000000</v>
+        <v>311290000000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Goldman Sachs Group Inc</t>
+          <t>Netflix Inc</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>311520000000</v>
+        <v>308950000000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc</t>
+          <t>Merck &amp; Co Inc</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>309350000000</v>
+        <v>305120000000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Merck &amp; Co Inc</t>
+          <t>Palantir Technologies Inc</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>308900000000</v>
+        <v>303960000000</v>
       </c>
     </row>
     <row r="45">
@@ -1161,52 +1161,52 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>299820000000</v>
+        <v>302430000000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>291870000000</v>
+        <v>293330000000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>288940000000</v>
+        <v>283730000000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>NVS</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Novartis AG ADR</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>283040000000</v>
+        <v>283460000000</v>
       </c>
     </row>
     <row r="49">
@@ -1221,112 +1221,112 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>282360000000</v>
+        <v>283070000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>NVS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>Novartis AG ADR</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>280790000000</v>
+        <v>282000000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>International Business Machines Corp</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>277550000000</v>
+        <v>281980000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Astrazeneca plc</t>
+          <t>International Business Machines Corp</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>276810000000</v>
+        <v>270270000000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>Alibaba Group Holding Ltd ADR</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>275720000000</v>
+        <v>269680000000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>Wells Fargo &amp; Co</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>275190000000</v>
+        <v>266730000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Alibaba Group Holding Ltd ADR</t>
+          <t>Astrazeneca plc</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>266820000000</v>
+        <v>266140000000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Co</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>265960000000</v>
+        <v>265620000000</v>
       </c>
     </row>
     <row r="57">
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>262870000000</v>
+        <v>263860000000</v>
       </c>
     </row>
     <row r="58">
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>243120000000</v>
+        <v>245080000000</v>
       </c>
     </row>
     <row r="59">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>239350000000</v>
+        <v>241440000000</v>
       </c>
     </row>
     <row r="60">
@@ -1386,7 +1386,7 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>236580000000</v>
+        <v>239210000000</v>
       </c>
     </row>
     <row r="61">
@@ -1401,112 +1401,112 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>226950000000</v>
+        <v>229260000000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>T-Mobile US Inc</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>202020000000</v>
+        <v>203030000000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>201430000000</v>
+        <v>200810000000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>199240000000</v>
+        <v>199370000000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>McDonald's Corp</t>
+          <t>AMGEN Inc</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>196450000000</v>
+        <v>196120000000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>T-Mobile US Inc</t>
+          <t>Thermo Fisher Scientific Inc</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>196400000000</v>
+        <v>195860000000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>AMGEN Inc</t>
+          <t>McDonald's Corp</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>196250000000</v>
+        <v>195100000000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>194990000000</v>
+        <v>190600000000</v>
       </c>
     </row>
     <row r="69">
@@ -1521,7 +1521,7 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>188420000000</v>
+        <v>187770000000</v>
       </c>
     </row>
     <row r="70">
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>185490000000</v>
+        <v>187750000000</v>
       </c>
     </row>
     <row r="71">
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>185010000000</v>
+        <v>184310000000</v>
       </c>
     </row>
     <row r="72">
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>181660000000</v>
+        <v>183450000000</v>
       </c>
     </row>
     <row r="73">
@@ -1581,7 +1581,7 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>177240000000</v>
+        <v>179340000000</v>
       </c>
     </row>
     <row r="74">
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>176380000000</v>
+        <v>175870000000</v>
       </c>
     </row>
     <row r="75">
@@ -1611,82 +1611,82 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>175880000000</v>
+        <v>175220000000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>174830000000</v>
+        <v>174800000000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>174200000000</v>
+        <v>170310000000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>Blackrock Inc</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>167410000000</v>
+        <v>168470000000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Walt Disney Co</t>
+          <t>Novo Nordisk ADR</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>167000000000</v>
+        <v>166150000000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Blackrock Inc</t>
+          <t>Walt Disney Co</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>165800000000</v>
+        <v>166050000000</v>
       </c>
     </row>
     <row r="81">
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>165570000000</v>
+        <v>164290000000</v>
       </c>
     </row>
     <row r="82">
@@ -1716,52 +1716,52 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>164430000000</v>
+        <v>163610000000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Novo Nordisk ADR</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>164140000000</v>
+        <v>161190000000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Deere &amp; Co</t>
+          <t>Shopify Inc</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>160050000000</v>
+        <v>159010000000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Shopify Inc</t>
+          <t>Deere &amp; Co</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>159830000000</v>
+        <v>158420000000</v>
       </c>
     </row>
     <row r="86">
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>151350000000</v>
+        <v>151730000000</v>
       </c>
     </row>
     <row r="87">
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>149210000000</v>
+        <v>150360000000</v>
       </c>
     </row>
     <row r="88">
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>146190000000</v>
+        <v>146820000000</v>
       </c>
     </row>
     <row r="89">
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>145760000000</v>
+        <v>144070000000</v>
       </c>
     </row>
     <row r="90">
@@ -1836,7 +1836,7 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>138710000000</v>
+        <v>140880000000</v>
       </c>
     </row>
     <row r="91">
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>136010000000</v>
+        <v>138230000000</v>
       </c>
     </row>
     <row r="92">
@@ -1866,37 +1866,37 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>134900000000</v>
+        <v>134910000000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Progressive Corp</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>134580000000</v>
+        <v>134820000000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Progressive Corp</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>134120000000</v>
+        <v>134110000000</v>
       </c>
     </row>
     <row r="95">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>133090000000</v>
+        <v>133760000000</v>
       </c>
     </row>
     <row r="96">
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>128160000000</v>
+        <v>127430000000</v>
       </c>
     </row>
     <row r="97">
@@ -1941,7 +1941,7 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>124420000000</v>
+        <v>122480000000</v>
       </c>
     </row>
     <row r="98">
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>122240000000</v>
+        <v>121170000000</v>
       </c>
     </row>
     <row r="99">
@@ -1971,37 +1971,37 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>121280000000</v>
+        <v>120820000000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Altria Group Inc</t>
+          <t>Lockheed Martin Corp</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>119550000000</v>
+        <v>120640000000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corp</t>
+          <t>Altria Group Inc</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>119490000000</v>
+        <v>119880000000</v>
       </c>
     </row>
     <row r="102">
@@ -2016,7 +2016,7 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>119430000000</v>
+        <v>118660000000</v>
       </c>
     </row>
     <row r="103">
@@ -2031,7 +2031,7 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>118320000000</v>
+        <v>117580000000</v>
       </c>
     </row>
     <row r="104">
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>105460000000</v>
+        <v>107360000000</v>
       </c>
     </row>
     <row r="105">
@@ -2061,7 +2061,7 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>102060000000</v>
+        <v>103670000000</v>
       </c>
     </row>
     <row r="106">
@@ -2076,22 +2076,22 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>100010000000</v>
+        <v>98750000000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>97940000000</v>
+        <v>97220000000</v>
       </c>
     </row>
     <row r="108">
@@ -2106,82 +2106,82 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>96450000000</v>
+        <v>96700000000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>United Parcel Service Inc</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>96420000000</v>
+        <v>95600000000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>95750000000</v>
+        <v>95310000000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>United Parcel Service Inc</t>
+          <t>MercadoLibre Inc</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>94130000000</v>
+        <v>93900000000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Snowflake Inc</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>92710000000</v>
+        <v>91670000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>MercadoLibre Inc</t>
+          <t>Snowflake Inc</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>91650000000</v>
+        <v>90620000000</v>
       </c>
     </row>
     <row r="114">
@@ -2196,7 +2196,7 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>91290000000</v>
+        <v>90390000000</v>
       </c>
     </row>
     <row r="115">
@@ -2211,7 +2211,7 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>90730000000</v>
+        <v>90200000000</v>
       </c>
     </row>
     <row r="116">
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>88530000000</v>
+        <v>89570000000</v>
       </c>
     </row>
     <row r="117">
@@ -2241,7 +2241,7 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>88500000000</v>
+        <v>88900000000</v>
       </c>
     </row>
     <row r="118">
@@ -2256,7 +2256,7 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>86240000000</v>
+        <v>85910000000</v>
       </c>
     </row>
     <row r="119">
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>85100000000</v>
+        <v>82750000000</v>
       </c>
     </row>
     <row r="120">
@@ -2286,67 +2286,67 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>81020000000</v>
+        <v>82160000000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Cigna Group</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>77260000000</v>
+        <v>77630000000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Cigna Group</t>
+          <t>Northrop Grumman Corp</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>77190000000</v>
+        <v>76650000000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange Inc</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>76410000000</v>
+        <v>76530000000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp</t>
+          <t>Intercontinental Exchange Inc</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>75590000000</v>
+        <v>76490000000</v>
       </c>
     </row>
     <row r="125">
@@ -2361,7 +2361,7 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>74780000000</v>
+        <v>75210000000</v>
       </c>
     </row>
     <row r="126">
@@ -2376,67 +2376,67 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>72830000000</v>
+        <v>73810000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Astera Labs Inc</t>
+          <t>SLB Ltd</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>71550000000</v>
+        <v>71400000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SLB Ltd</t>
+          <t>Astera Labs Inc</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>70630000000</v>
+        <v>70790000000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals Inc</t>
+          <t>General Motors Company</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>70030000000</v>
+        <v>70190000000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>General Motors Company</t>
+          <t>Regeneron Pharmaceuticals Inc</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>69110000000</v>
+        <v>69670000000</v>
       </c>
     </row>
     <row r="131">
@@ -2451,37 +2451,37 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>69090000000</v>
+        <v>69380000000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>NU</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Nu Holdings Ltd</t>
+          <t>Ferrari NV</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>66440000000</v>
+        <v>66480000000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Ferrari NV</t>
+          <t>Nu Holdings Ltd</t>
         </is>
       </c>
       <c r="L133" t="n">
-        <v>66130000000</v>
+        <v>66470000000</v>
       </c>
     </row>
     <row r="134">
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>63350000000</v>
+        <v>65710000000</v>
       </c>
     </row>
     <row r="135">
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>61860000000</v>
+        <v>63010000000</v>
       </c>
     </row>
     <row r="136">
@@ -2526,37 +2526,37 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>60080000000</v>
+        <v>61380000000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Ford Motor Co</t>
         </is>
       </c>
       <c r="L137" t="n">
-        <v>54410000000</v>
+        <v>55790000000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Ford Motor Co</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L138" t="n">
-        <v>54230000000</v>
+        <v>55280000000</v>
       </c>
     </row>
     <row r="139">
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>53270000000</v>
+        <v>53560000000</v>
       </c>
     </row>
     <row r="140">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>52590000000</v>
+        <v>53090000000</v>
       </c>
     </row>
     <row r="141">
@@ -2601,37 +2601,37 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>52020000000</v>
+        <v>52610000000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Rocket Lab Corp</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>49380000000</v>
+        <v>48490000000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Rocket Lab Corp</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>48940000000</v>
+        <v>48480000000</v>
       </c>
     </row>
     <row r="144">
@@ -2646,7 +2646,7 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>46080000000</v>
+        <v>46010000000</v>
       </c>
     </row>
     <row r="145">
@@ -2661,37 +2661,37 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>44380000000</v>
+        <v>45220000000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Autodesk Inc</t>
+          <t>MSCI Inc</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>44010000000</v>
+        <v>44020000000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MSCI Inc</t>
+          <t>Autodesk Inc</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>43920000000</v>
+        <v>43980000000</v>
       </c>
     </row>
     <row r="148">
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>41740000000</v>
+        <v>41910000000</v>
       </c>
     </row>
     <row r="149">
@@ -2721,7 +2721,7 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>39980000000</v>
+        <v>40860000000</v>
       </c>
     </row>
     <row r="150">
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>38560000000</v>
+        <v>37600000000</v>
       </c>
     </row>
     <row r="151">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>36600000000</v>
+        <v>36750000000</v>
       </c>
     </row>
     <row r="152">
@@ -2766,7 +2766,7 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>34170000000</v>
+        <v>34320000000</v>
       </c>
     </row>
     <row r="153">
@@ -2781,37 +2781,37 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>33650000000</v>
+        <v>34210000000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Twilio Inc</t>
+          <t>Strategy Inc</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>33180000000</v>
+        <v>33170000000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Strategy Inc</t>
+          <t>Twilio Inc</t>
         </is>
       </c>
       <c r="L155" t="n">
-        <v>32900000000</v>
+        <v>32560000000</v>
       </c>
     </row>
     <row r="156">
@@ -2826,67 +2826,67 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>31480000000</v>
+        <v>31680000000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>Estee Lauder Cos. Inc</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>30380000000</v>
+        <v>29910000000</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Estee Lauder Cos. Inc</t>
+          <t>Illumina Inc</t>
         </is>
       </c>
       <c r="L158" t="n">
-        <v>29660000000</v>
+        <v>28780000000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>AFRM</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Illumina Inc</t>
+          <t>Affirm Holdings Inc</t>
         </is>
       </c>
       <c r="L159" t="n">
-        <v>29320000000</v>
+        <v>27940000000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>AFRM</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Affirm Holdings Inc</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="L160" t="n">
-        <v>28060000000</v>
+        <v>27090000000</v>
       </c>
     </row>
     <row r="161">
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>27540000000</v>
+        <v>26900000000</v>
       </c>
     </row>
     <row r="162">
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>26360000000</v>
+        <v>26320000000</v>
       </c>
     </row>
     <row r="163">
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>24550000000</v>
+        <v>24480000000</v>
       </c>
     </row>
     <row r="164">
@@ -2946,37 +2946,37 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>23880000000</v>
+        <v>24090000000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>DKNG</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Zscaler Inc</t>
+          <t>DraftKings Inc</t>
         </is>
       </c>
       <c r="L165" t="n">
-        <v>23790000000</v>
+        <v>23540000000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>DKNG</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>DraftKings Inc</t>
+          <t>Zscaler Inc</t>
         </is>
       </c>
       <c r="L166" t="n">
-        <v>23380000000</v>
+        <v>22520000000</v>
       </c>
     </row>
     <row r="167">
@@ -2991,52 +2991,52 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>20810000000</v>
+        <v>20870000000</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Charter Communications Inc</t>
+          <t>Super Micro Computer Inc</t>
         </is>
       </c>
       <c r="L168" t="n">
-        <v>18610000000</v>
+        <v>18310000000</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Super Micro Computer Inc</t>
+          <t>Charter Communications Inc</t>
         </is>
       </c>
       <c r="L169" t="n">
-        <v>18270000000</v>
+        <v>18110000000</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>IonQ Inc</t>
+          <t>Circle Internet Group Inc</t>
         </is>
       </c>
       <c r="L170" t="n">
-        <v>16710000000</v>
+        <v>16440000000</v>
       </c>
     </row>
     <row r="171">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>15900000000</v>
+        <v>16110000000</v>
       </c>
     </row>
     <row r="172">
@@ -3066,22 +3066,22 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>15900000000</v>
+        <v>16110000000</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>CRCL</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Circle Internet Group Inc</t>
+          <t>IonQ Inc</t>
         </is>
       </c>
       <c r="L173" t="n">
-        <v>15660000000</v>
+        <v>16000000000</v>
       </c>
     </row>
     <row r="174">
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>14890000000</v>
+        <v>14680000000</v>
       </c>
     </row>
     <row r="175">
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>12720000000</v>
+        <v>12610000000</v>
       </c>
     </row>
     <row r="176">
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>12290000000</v>
+        <v>12460000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>10820000000</v>
+        <v>11130000000</v>
       </c>
     </row>
     <row r="178">
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>9410000000</v>
+        <v>9210000000</v>
       </c>
     </row>
     <row r="179">
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>9230000000</v>
+        <v>8900000000</v>
       </c>
     </row>
     <row r="180">
@@ -3186,7 +3186,7 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>8580000000</v>
+        <v>8710000000</v>
       </c>
     </row>
     <row r="181">
@@ -3201,37 +3201,37 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>8570000000</v>
+        <v>8500000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>HIMS</t>
+          <t>MBLY</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Hims &amp; Hers Health Inc</t>
+          <t>Mobileye Global Inc</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>8210000000</v>
+        <v>8040000000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>MBLY</t>
+          <t>HIMS</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Mobileye Global Inc</t>
+          <t>Hims &amp; Hers Health Inc</t>
         </is>
       </c>
       <c r="L183" t="n">
-        <v>8030000000</v>
+        <v>7960000000</v>
       </c>
     </row>
     <row r="184">
@@ -3246,7 +3246,7 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>7800000000</v>
+        <v>7820000000</v>
       </c>
     </row>
     <row r="185">
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>7640000000</v>
+        <v>7360000000</v>
       </c>
     </row>
     <row r="186">
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>7510000000</v>
+        <v>7320000000</v>
       </c>
     </row>
     <row r="187">
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>6470000000</v>
+        <v>6130000000</v>
       </c>
     </row>
     <row r="188">
@@ -3306,37 +3306,37 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>5650000000</v>
+        <v>5500000000</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>CRSP</t>
+          <t>LMND</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>CRISPR Therapeutics AG</t>
+          <t>Lemonade Inc</t>
         </is>
       </c>
       <c r="L189" t="n">
-        <v>5430000000</v>
+        <v>5420000000</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>LMND</t>
+          <t>CRSP</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Lemonade Inc</t>
+          <t>CRISPR Therapeutics AG</t>
         </is>
       </c>
       <c r="L190" t="n">
-        <v>5400000000</v>
+        <v>5150000000</v>
       </c>
     </row>
     <row r="191">
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>5040000000</v>
+        <v>4800000000</v>
       </c>
     </row>
     <row r="192">
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>4000000000</v>
+        <v>3800000000</v>
       </c>
     </row>
     <row r="193">
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3410000000</v>
+        <v>3370000000</v>
       </c>
     </row>
     <row r="194">
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>3180000000</v>
+        <v>3130000000</v>
       </c>
     </row>
     <row r="196">
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>3180000000</v>
+        <v>3070000000</v>
       </c>
     </row>
     <row r="197">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>3090000000</v>
+        <v>2980000000</v>
       </c>
     </row>
     <row r="198">
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2770000000</v>
+        <v>2730000000</v>
       </c>
     </row>
     <row r="199">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>2490000000</v>
+        <v>2460000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>2060000000</v>
+        <v>1950000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1660000000</v>
+        <v>1680000000</v>
       </c>
     </row>
     <row r="202">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1400000000</v>
+        <v>1390000000</v>
       </c>
     </row>
     <row r="203">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>1000000000</v>
+        <v>982290000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>990770000</v>
+        <v>899010000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>647770000</v>
+        <v>630770000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4329650000000</v>
+        <v>4326360000000</v>
       </c>
     </row>
     <row r="8">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1063780000000</v>
+        <v>1064450000000</v>
       </c>
     </row>
     <row r="17">
@@ -1512,31 +1512,31 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PepsiCo Inc</t>
+          <t>Toyota Motor Corp ADR</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>187770000000</v>
+        <v>187750000000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Toyota Motor Corp ADR</t>
+          <t>PepsiCo Inc</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>187750000000</v>
+        <v>187510000000</v>
       </c>
     </row>
     <row r="71">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>899010000</v>
+        <v>899000000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>630770000</v>
+        <v>630780000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4631220000000</v>
+        <v>4660450000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5105230000000</v>
+        <v>4925430000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4326360000000</v>
+        <v>4273230000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2860690000000</v>
+        <v>2904440000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2639150000000</v>
+        <v>2660340000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2251500000000</v>
+        <v>2186520000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1902890000000</v>
+        <v>1827150000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1698740000000</v>
+        <v>1667060000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1531430000000</v>
+        <v>1482610000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,112 +696,112 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1119330000000</v>
+        <v>1113020000000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>BRK-B</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Micron Technology Inc</t>
+          <t>Berkshire Hathaway Inc</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1106010000000</v>
+        <v>1071220000000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BRK-B</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Inc</t>
+          <t>Micron Technology Inc</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1064450000000</v>
+        <v>1058240000000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices Inc</t>
+          <t>Walmart Inc</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>909700000000</v>
+        <v>913430000000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Walmart Inc</t>
+          <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>906430000000</v>
+        <v>896380000000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co</t>
+          <t>Advanced Micro Devices Inc</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>901580000000</v>
+        <v>871380000000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ASML Holding NV</t>
+          <t>Visa Inc</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>692720000000</v>
+        <v>674050000000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Visa Inc</t>
+          <t>ASML Holding NV</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>657500000000</v>
+        <v>665250000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>618610000000</v>
+        <v>620510000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,22 +831,22 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>575580000000</v>
+        <v>598920000000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Applied Materials Inc</t>
+          <t>Mastercard Incorporated</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>478360000000</v>
+        <v>475100000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,82 +861,82 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>478140000000</v>
+        <v>470020000000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated</t>
+          <t>Applied Materials Inc</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>465420000000</v>
+        <v>456840000000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Caterpillar Inc</t>
+          <t>Abbvie Inc</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>438720000000</v>
+        <v>438160000000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Abbvie Inc</t>
+          <t>Caterpillar Inc</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>438310000000</v>
+        <v>429070000000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Lam Research Corp</t>
+          <t>Bank Of America Corp</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>438110000000</v>
+        <v>422250000000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Bank Of America Corp</t>
+          <t>Lam Research Corp</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>423450000000</v>
+        <v>412590000000</v>
       </c>
     </row>
     <row r="31">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>406340000000</v>
+        <v>410850000000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Oracle Corp</t>
+          <t>Unitedhealth Group Inc</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>405110000000</v>
+        <v>389680000000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Unitedhealth Group Inc</t>
+          <t>Oracle Corp</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>385620000000</v>
+        <v>378900000000</v>
       </c>
     </row>
     <row r="34">
@@ -996,37 +996,37 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>374840000000</v>
+        <v>368740000000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Coca-Cola Co</t>
+          <t>Chevron Corp</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>359210000000</v>
+        <v>362870000000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Chevron Corp</t>
+          <t>Coca-Cola Co</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>351320000000</v>
+        <v>362480000000</v>
       </c>
     </row>
     <row r="37">
@@ -1041,67 +1041,67 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>350600000000</v>
+        <v>348720000000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>Procter &amp; Gamble Co</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>344090000000</v>
+        <v>345490000000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble Co</t>
+          <t>Home Depot Inc</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>342400000000</v>
+        <v>336140000000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Home Depot Inc</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>342310000000</v>
+        <v>318130000000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Goldman Sachs Group Inc</t>
+          <t>Palantir Technologies Inc</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>311290000000</v>
+        <v>311750000000</v>
       </c>
     </row>
     <row r="42">
@@ -1116,37 +1116,37 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>308950000000</v>
+        <v>310880000000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Merck &amp; Co Inc</t>
+          <t>Goldman Sachs Group Inc</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>305120000000</v>
+        <v>308550000000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc</t>
+          <t>Merck &amp; Co Inc</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>303960000000</v>
+        <v>306330000000</v>
       </c>
     </row>
     <row r="45">
@@ -1161,127 +1161,127 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>302430000000</v>
+        <v>290320000000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>Philip Morris International Inc</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>293330000000</v>
+        <v>280840000000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>NVS</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>Novartis AG ADR</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>283730000000</v>
+        <v>280750000000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>283460000000</v>
+        <v>280170000000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Philip Morris International Inc</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>283070000000</v>
+        <v>276890000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NVS</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Novartis AG ADR</t>
+          <t>International Business Machines Corp</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>282000000000</v>
+        <v>272780000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>281980000000</v>
+        <v>271730000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>International Business Machines Corp</t>
+          <t>Alibaba Group Holding Ltd ADR</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>270270000000</v>
+        <v>269310000000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Alibaba Group Holding Ltd ADR</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>269680000000</v>
+        <v>269190000000</v>
       </c>
     </row>
     <row r="54">
@@ -1296,52 +1296,52 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>266730000000</v>
+        <v>268290000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Astrazeneca plc</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>266140000000</v>
+        <v>264480000000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>Astrazeneca plc</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>265620000000</v>
+        <v>262830000000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>263860000000</v>
+        <v>247900000000</v>
       </c>
     </row>
     <row r="58">
@@ -1356,37 +1356,37 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>245080000000</v>
+        <v>242430000000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Citigroup Inc</t>
+          <t>American Express Co</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>241440000000</v>
+        <v>241840000000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>American Express Co</t>
+          <t>Citigroup Inc</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>239210000000</v>
+        <v>241300000000</v>
       </c>
     </row>
     <row r="61">
@@ -1401,7 +1401,7 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>229260000000</v>
+        <v>234140000000</v>
       </c>
     </row>
     <row r="62">
@@ -1416,82 +1416,82 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>203030000000</v>
+        <v>203900000000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>Thermo Fisher Scientific Inc</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>200810000000</v>
+        <v>196410000000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>AMGEN Inc</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>199370000000</v>
+        <v>194540000000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>AMGEN Inc</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>196120000000</v>
+        <v>193910000000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc</t>
+          <t>McDonald's Corp</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>195860000000</v>
+        <v>193690000000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>McDonald's Corp</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>195100000000</v>
+        <v>191490000000</v>
       </c>
     </row>
     <row r="68">
@@ -1506,52 +1506,52 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>190600000000</v>
+        <v>191340000000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Toyota Motor Corp ADR</t>
+          <t>PepsiCo Inc</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>187750000000</v>
+        <v>189020000000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PepsiCo Inc</t>
+          <t>Sap SE ADR</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>187510000000</v>
+        <v>186770000000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Sap SE ADR</t>
+          <t>Toyota Motor Corp ADR</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>184310000000</v>
+        <v>185940000000</v>
       </c>
     </row>
     <row r="72">
@@ -1566,22 +1566,22 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>183450000000</v>
+        <v>184330000000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Charles Schwab Corp</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>179340000000</v>
+        <v>180840000000</v>
       </c>
     </row>
     <row r="74">
@@ -1596,67 +1596,67 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>175870000000</v>
+        <v>178210000000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Boeing Co</t>
+          <t>Charles Schwab Corp</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>175220000000</v>
+        <v>178050000000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Boeing Co</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>174800000000</v>
+        <v>169890000000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>Blackrock Inc</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>170310000000</v>
+        <v>167730000000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Blackrock Inc</t>
+          <t>Walt Disney Co</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>168470000000</v>
+        <v>166710000000</v>
       </c>
     </row>
     <row r="79">
@@ -1671,37 +1671,37 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>166150000000</v>
+        <v>165480000000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Walt Disney Co</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>166050000000</v>
+        <v>163140000000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Corning Inc</t>
+          <t>Shopify Inc</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>164290000000</v>
+        <v>161870000000</v>
       </c>
     </row>
     <row r="82">
@@ -1716,67 +1716,67 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>163610000000</v>
+        <v>160440000000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>Deere &amp; Co</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>161190000000</v>
+        <v>158090000000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Shopify Inc</t>
+          <t>Corning Inc</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>159010000000</v>
+        <v>157590000000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Deere &amp; Co</t>
+          <t>Uber Technologies Inc</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>158420000000</v>
+        <v>151160000000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Uber Technologies Inc</t>
+          <t>AT&amp;T Inc</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>151730000000</v>
+        <v>149740000000</v>
       </c>
     </row>
     <row r="87">
@@ -1791,22 +1791,22 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>150360000000</v>
+        <v>149070000000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>146820000000</v>
+        <v>148770000000</v>
       </c>
     </row>
     <row r="89">
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>144070000000</v>
+        <v>144190000000</v>
       </c>
     </row>
     <row r="90">
@@ -1836,22 +1836,22 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>140880000000</v>
+        <v>141670000000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>Salesforce Inc</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>138230000000</v>
+        <v>140230000000</v>
       </c>
     </row>
     <row r="92">
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>134910000000</v>
+        <v>137590000000</v>
       </c>
     </row>
     <row r="93">
@@ -1881,37 +1881,37 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>134820000000</v>
+        <v>137020000000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>134110000000</v>
+        <v>136220000000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Salesforce Inc</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>133760000000</v>
+        <v>135340000000</v>
       </c>
     </row>
     <row r="96">
@@ -1926,52 +1926,52 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>127430000000</v>
+        <v>129600000000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>Starbucks Corp</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>122480000000</v>
+        <v>122340000000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PDD Holdings Inc ADR</t>
+          <t>Bristol-Myers Squibb Co</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>121170000000</v>
+        <v>121180000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Starbucks Corp</t>
+          <t>PDD Holdings Inc ADR</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>120820000000</v>
+        <v>120360000000</v>
       </c>
     </row>
     <row r="100">
@@ -1986,7 +1986,7 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>120640000000</v>
+        <v>120050000000</v>
       </c>
     </row>
     <row r="101">
@@ -2001,37 +2001,37 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>119880000000</v>
+        <v>120020000000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Lowe's Cos. Inc</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>118660000000</v>
+        <v>117490000000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Co</t>
+          <t>Lowe's Cos. Inc</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>117580000000</v>
+        <v>116460000000</v>
       </c>
     </row>
     <row r="104">
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>107360000000</v>
+        <v>106970000000</v>
       </c>
     </row>
     <row r="105">
@@ -2061,52 +2061,52 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>103670000000</v>
+        <v>102520000000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Spotify Technology SA</t>
+          <t>Automatic Data Processing Inc</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>98750000000</v>
+        <v>100350000000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>Spotify Technology SA</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>97220000000</v>
+        <v>98770000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>96700000000</v>
+        <v>97110000000</v>
       </c>
     </row>
     <row r="109">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>95600000000</v>
+        <v>95960000000</v>
       </c>
     </row>
     <row r="110">
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>95310000000</v>
+        <v>95720000000</v>
       </c>
     </row>
     <row r="111">
@@ -2151,37 +2151,37 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>93900000000</v>
+        <v>94670000000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>Snowflake Inc</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>91670000000</v>
+        <v>93110000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Snowflake Inc</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>90620000000</v>
+        <v>92640000000</v>
       </c>
     </row>
     <row r="114">
@@ -2196,22 +2196,22 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>90390000000</v>
+        <v>92330000000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>HCA Healthcare Inc</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>90200000000</v>
+        <v>91670000000</v>
       </c>
     </row>
     <row r="116">
@@ -2226,37 +2226,37 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>89570000000</v>
+        <v>88190000000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>MMC</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>Marsh</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>88900000000</v>
+        <v>87460000000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>MMC</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Marsh</t>
+          <t>HCA Healthcare Inc</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>85910000000</v>
+        <v>86680000000</v>
       </c>
     </row>
     <row r="119">
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>82750000000</v>
+        <v>84770000000</v>
       </c>
     </row>
     <row r="120">
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>82160000000</v>
+        <v>82250000000</v>
       </c>
     </row>
     <row r="121">
@@ -2301,67 +2301,67 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>77630000000</v>
+        <v>80550000000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp</t>
+          <t>Intuit Inc</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>76650000000</v>
+        <v>79260000000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Intercontinental Exchange Inc</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>76530000000</v>
+        <v>77850000000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange Inc</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>76490000000</v>
+        <v>77400000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Intuit Inc</t>
+          <t>Northrop Grumman Corp</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>75210000000</v>
+        <v>76960000000</v>
       </c>
     </row>
     <row r="126">
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>73810000000</v>
+        <v>74590000000</v>
       </c>
     </row>
     <row r="127">
@@ -2391,22 +2391,22 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>71400000000</v>
+        <v>70810000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Astera Labs Inc</t>
+          <t>Regeneron Pharmaceuticals Inc</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>70790000000</v>
+        <v>69520000000</v>
       </c>
     </row>
     <row r="129">
@@ -2421,37 +2421,37 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>70190000000</v>
+        <v>69180000000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals Inc</t>
+          <t>Apollo Global Management Inc</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>69670000000</v>
+        <v>68510000000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Apollo Global Management Inc</t>
+          <t>Nu Holdings Ltd</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>69380000000</v>
+        <v>66030000000</v>
       </c>
     </row>
     <row r="132">
@@ -2466,52 +2466,52 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>66480000000</v>
+        <v>65830000000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>NU</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Nu Holdings Ltd</t>
+          <t>Nike Inc</t>
         </is>
       </c>
       <c r="L133" t="n">
-        <v>66470000000</v>
+        <v>64800000000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Nike Inc</t>
+          <t>Sea Ltd ADR</t>
         </is>
       </c>
       <c r="L134" t="n">
-        <v>65710000000</v>
+        <v>62740000000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Sea Ltd ADR</t>
+          <t>Astera Labs Inc</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>63010000000</v>
+        <v>62060000000</v>
       </c>
     </row>
     <row r="136">
@@ -2526,7 +2526,7 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>61380000000</v>
+        <v>61210000000</v>
       </c>
     </row>
     <row r="137">
@@ -2541,22 +2541,22 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>55790000000</v>
+        <v>55190000000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Occidental Petroleum Corp</t>
         </is>
       </c>
       <c r="L138" t="n">
-        <v>55280000000</v>
+        <v>54520000000</v>
       </c>
     </row>
     <row r="139">
@@ -2571,97 +2571,97 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>53560000000</v>
+        <v>53320000000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences Corp</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>53090000000</v>
+        <v>52970000000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Occidental Petroleum Corp</t>
+          <t>Edwards Lifesciences Corp</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>52610000000</v>
+        <v>52850000000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>48490000000</v>
+        <v>46990000000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Rocket Lab Corp</t>
+          <t>Block Inc</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>48480000000</v>
+        <v>46850000000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Block Inc</t>
+          <t>Rocket Lab Corp</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>46010000000</v>
+        <v>45900000000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>45220000000</v>
+        <v>45450000000</v>
       </c>
     </row>
     <row r="146">
@@ -2676,7 +2676,7 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>44020000000</v>
+        <v>45150000000</v>
       </c>
     </row>
     <row r="147">
@@ -2691,37 +2691,37 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>43980000000</v>
+        <v>44780000000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Coinbase Global Inc</t>
+          <t>PayPal Holdings Inc</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>41910000000</v>
+        <v>42030000000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>PayPal Holdings Inc</t>
+          <t>Coinbase Global Inc</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>40860000000</v>
+        <v>41460000000</v>
       </c>
     </row>
     <row r="150">
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>37600000000</v>
+        <v>38680000000</v>
       </c>
     </row>
     <row r="151">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>36750000000</v>
+        <v>36450000000</v>
       </c>
     </row>
     <row r="152">
@@ -2766,7 +2766,7 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>34320000000</v>
+        <v>35780000000</v>
       </c>
     </row>
     <row r="153">
@@ -2781,37 +2781,37 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>34210000000</v>
+        <v>35040000000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Strategy Inc</t>
+          <t>Twilio Inc</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>33170000000</v>
+        <v>33120000000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Twilio Inc</t>
+          <t>Strategy Inc</t>
         </is>
       </c>
       <c r="L155" t="n">
-        <v>32560000000</v>
+        <v>32280000000</v>
       </c>
     </row>
     <row r="156">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>31680000000</v>
+        <v>31610000000</v>
       </c>
     </row>
     <row r="157">
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>29910000000</v>
+        <v>29360000000</v>
       </c>
     </row>
     <row r="158">
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>28780000000</v>
+        <v>28750000000</v>
       </c>
     </row>
     <row r="159">
@@ -2871,52 +2871,52 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>27940000000</v>
+        <v>27440000000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>Fiserv Inc</t>
         </is>
       </c>
       <c r="L160" t="n">
-        <v>27090000000</v>
+        <v>27290000000</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>ZM</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Fiserv Inc</t>
+          <t>Zoom Communications Inc</t>
         </is>
       </c>
       <c r="L161" t="n">
-        <v>26900000000</v>
+        <v>26940000000</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ZM</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Zoom Communications Inc</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="L162" t="n">
-        <v>26320000000</v>
+        <v>26590000000</v>
       </c>
     </row>
     <row r="163">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>24480000000</v>
+        <v>23750000000</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>DKNG</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>SoFi Technologies Inc</t>
+          <t>DraftKings Inc</t>
         </is>
       </c>
       <c r="L164" t="n">
-        <v>24090000000</v>
+        <v>23520000000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>DKNG</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>DraftKings Inc</t>
+          <t>SoFi Technologies Inc</t>
         </is>
       </c>
       <c r="L165" t="n">
-        <v>23540000000</v>
+        <v>23260000000</v>
       </c>
     </row>
     <row r="166">
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>22520000000</v>
+        <v>22930000000</v>
       </c>
     </row>
     <row r="167">
@@ -2991,52 +2991,52 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>20870000000</v>
+        <v>21120000000</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Super Micro Computer Inc</t>
+          <t>Charter Communications Inc</t>
         </is>
       </c>
       <c r="L168" t="n">
-        <v>18310000000</v>
+        <v>18190000000</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Charter Communications Inc</t>
+          <t>Super Micro Computer Inc</t>
         </is>
       </c>
       <c r="L169" t="n">
-        <v>18110000000</v>
+        <v>17890000000</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>CRCL</t>
+          <t>GRAB</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Circle Internet Group Inc</t>
+          <t>Grab Holdings Limited</t>
         </is>
       </c>
       <c r="L170" t="n">
-        <v>16440000000</v>
+        <v>16150000000</v>
       </c>
     </row>
     <row r="171">
@@ -3051,22 +3051,22 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>16110000000</v>
+        <v>16150000000</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>GRAB</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Grab Holdings Limited</t>
+          <t>Circle Internet Group Inc</t>
         </is>
       </c>
       <c r="L172" t="n">
-        <v>16110000000</v>
+        <v>15660000000</v>
       </c>
     </row>
     <row r="173">
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>16000000000</v>
+        <v>14510000000</v>
       </c>
     </row>
     <row r="174">
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>14680000000</v>
+        <v>13910000000</v>
       </c>
     </row>
     <row r="175">
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>12610000000</v>
+        <v>12660000000</v>
       </c>
     </row>
     <row r="176">
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>12460000000</v>
+        <v>12620000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>11130000000</v>
+        <v>10950000000</v>
       </c>
     </row>
     <row r="178">
@@ -3156,67 +3156,67 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>9210000000</v>
+        <v>9530000000</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>PRMB</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Applied Digital Corp</t>
+          <t>Primo Brands Corp</t>
         </is>
       </c>
       <c r="L179" t="n">
-        <v>8900000000</v>
+        <v>8630000000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>PRMB</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Primo Brands Corp</t>
+          <t>Applied Digital Corp</t>
         </is>
       </c>
       <c r="L180" t="n">
-        <v>8710000000</v>
+        <v>8240000000</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>OKLO</t>
+          <t>MBLY</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Oklo Inc</t>
+          <t>Mobileye Global Inc</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>8500000000</v>
+        <v>8210000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>MBLY</t>
+          <t>OKLO</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Mobileye Global Inc</t>
+          <t>Oklo Inc</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>8040000000</v>
+        <v>7970000000</v>
       </c>
     </row>
     <row r="183">
@@ -3246,7 +3246,7 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>7820000000</v>
+        <v>7630000000</v>
       </c>
     </row>
     <row r="185">
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>7320000000</v>
+        <v>7180000000</v>
       </c>
     </row>
     <row r="187">
@@ -3291,37 +3291,37 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>6130000000</v>
+        <v>6360000000</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>RGTI</t>
+          <t>LMND</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Rigetti Computing Inc</t>
+          <t>Lemonade Inc</t>
         </is>
       </c>
       <c r="L188" t="n">
-        <v>5500000000</v>
+        <v>5430000000</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>LMND</t>
+          <t>RGTI</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Lemonade Inc</t>
+          <t>Rigetti Computing Inc</t>
         </is>
       </c>
       <c r="L189" t="n">
-        <v>5420000000</v>
+        <v>5110000000</v>
       </c>
     </row>
     <row r="190">
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>5150000000</v>
+        <v>4880000000</v>
       </c>
     </row>
     <row r="191">
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>4800000000</v>
+        <v>4650000000</v>
       </c>
     </row>
     <row r="192">
@@ -3366,67 +3366,67 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>3800000000</v>
+        <v>3640000000</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>LEU</t>
+          <t>FSLY</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Centrus Energy Corp</t>
+          <t>Fastly Inc</t>
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3370000000</v>
+        <v>3130000000</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>LEU</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>NuScale Power Corp</t>
+          <t>Centrus Energy Corp</t>
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3300000000</v>
+        <v>3070000000</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Upstart Holdings Inc</t>
+          <t>NuScale Power Corp</t>
         </is>
       </c>
       <c r="L195" t="n">
-        <v>3130000000</v>
+        <v>3050000000</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>FSLY</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Fastly Inc</t>
+          <t>Upstart Holdings Inc</t>
         </is>
       </c>
       <c r="L196" t="n">
-        <v>3070000000</v>
+        <v>3010000000</v>
       </c>
     </row>
     <row r="197">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2980000000</v>
+        <v>2790000000</v>
       </c>
     </row>
     <row r="198">
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2730000000</v>
+        <v>2740000000</v>
       </c>
     </row>
     <row r="199">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>2460000000</v>
+        <v>2620000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1950000000</v>
+        <v>1800000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1680000000</v>
+        <v>1740000000</v>
       </c>
     </row>
     <row r="202">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1390000000</v>
+        <v>1420000000</v>
       </c>
     </row>
     <row r="203">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>982290000</v>
+        <v>938540000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>899000000</v>
+        <v>823010000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>630780000</v>
+        <v>577900000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4660450000000</v>
+        <v>4624460000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4925430000000</v>
+        <v>5125560000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4273230000000</v>
+        <v>4362800000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2904440000000</v>
+        <v>2859430000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2660340000000</v>
+        <v>2662280000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2186520000000</v>
+        <v>2180340000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1827150000000</v>
+        <v>1851220000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1667060000000</v>
+        <v>1678000000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,82 +681,82 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1482610000000</v>
+        <v>1487940000000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lilly(Eli) &amp; Co</t>
+          <t>Micron Technology Inc</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1113020000000</v>
+        <v>1110330000000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BRK-B</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Inc</t>
+          <t>Lilly(Eli) &amp; Co</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1071220000000</v>
+        <v>1085390000000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>BRK-B</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Micron Technology Inc</t>
+          <t>Berkshire Hathaway Inc</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1058240000000</v>
+        <v>1059000000000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Walmart Inc</t>
+          <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>913430000000</v>
+        <v>918780000000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co</t>
+          <t>Walmart Inc</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>896380000000</v>
+        <v>904830000000</v>
       </c>
     </row>
     <row r="19">
@@ -771,37 +771,37 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>871380000000</v>
+        <v>893780000000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Visa Inc</t>
+          <t>ASML Holding NV</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>674050000000</v>
+        <v>684370000000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ASML Holding NV</t>
+          <t>Visa Inc</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>665250000000</v>
+        <v>670790000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>620510000000</v>
+        <v>611070000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>598920000000</v>
+        <v>601320000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,67 +846,67 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>475100000000</v>
+        <v>475390000000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cisco Systems Inc</t>
+          <t>Applied Materials Inc</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>470020000000</v>
+        <v>472960000000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Applied Materials Inc</t>
+          <t>Cisco Systems Inc</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>456840000000</v>
+        <v>461500000000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Abbvie Inc</t>
+          <t>Lam Research Corp</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>438160000000</v>
+        <v>432820000000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Caterpillar Inc</t>
+          <t>Abbvie Inc</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>429070000000</v>
+        <v>432480000000</v>
       </c>
     </row>
     <row r="29">
@@ -921,22 +921,22 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>422250000000</v>
+        <v>430200000000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Lam Research Corp</t>
+          <t>Caterpillar Inc</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>412590000000</v>
+        <v>429930000000</v>
       </c>
     </row>
     <row r="31">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>410850000000</v>
+        <v>408780000000</v>
       </c>
     </row>
     <row r="32">
@@ -966,37 +966,37 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>389680000000</v>
+        <v>386130000000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Oracle Corp</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>378900000000</v>
+        <v>369060000000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Oracle Corp</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>368740000000</v>
+        <v>368530000000</v>
       </c>
     </row>
     <row r="35">
@@ -1011,37 +1011,37 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>362870000000</v>
+        <v>361990000000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Coca-Cola Co</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>362480000000</v>
+        <v>359100000000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Coca-Cola Co</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>348720000000</v>
+        <v>357450000000</v>
       </c>
     </row>
     <row r="38">
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>345490000000</v>
+        <v>340160000000</v>
       </c>
     </row>
     <row r="39">
@@ -1071,22 +1071,22 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>336140000000</v>
+        <v>336770000000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>Goldman Sachs Group Inc</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>318130000000</v>
+        <v>336310000000</v>
       </c>
     </row>
     <row r="41">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>311750000000</v>
+        <v>320570000000</v>
       </c>
     </row>
     <row r="42">
@@ -1116,82 +1116,82 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>310880000000</v>
+        <v>309620000000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Goldman Sachs Group Inc</t>
+          <t>KLA Corp</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>308550000000</v>
+        <v>300930000000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Merck &amp; Co Inc</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>306330000000</v>
+        <v>299160000000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>KLA Corp</t>
+          <t>Merck &amp; Co Inc</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>290320000000</v>
+        <v>298310000000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Philip Morris International Inc</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>280840000000</v>
+        <v>296610000000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NVS</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Novartis AG ADR</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>280750000000</v>
+        <v>287610000000</v>
       </c>
     </row>
     <row r="48">
@@ -1206,52 +1206,52 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>280170000000</v>
+        <v>286460000000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>276890000000</v>
+        <v>278080000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>NVS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>International Business Machines Corp</t>
+          <t>Novartis AG ADR</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>272780000000</v>
+        <v>275240000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>Philip Morris International Inc</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>271730000000</v>
+        <v>274230000000</v>
       </c>
     </row>
     <row r="52">
@@ -1266,52 +1266,52 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>269310000000</v>
+        <v>269240000000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>Wells Fargo &amp; Co</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>269190000000</v>
+        <v>261000000000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Co</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>268290000000</v>
+        <v>260440000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>264480000000</v>
+        <v>260320000000</v>
       </c>
     </row>
     <row r="56">
@@ -1326,22 +1326,22 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>262830000000</v>
+        <v>255120000000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>American Express Co</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>247900000000</v>
+        <v>242270000000</v>
       </c>
     </row>
     <row r="58">
@@ -1356,22 +1356,22 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>242430000000</v>
+        <v>241730000000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>American Express Co</t>
+          <t>Shell Plc ADR</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>241840000000</v>
+        <v>235340000000</v>
       </c>
     </row>
     <row r="60">
@@ -1386,187 +1386,187 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>241300000000</v>
+        <v>228550000000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Shell Plc ADR</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>234140000000</v>
+        <v>214580000000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>T-Mobile US Inc</t>
+          <t>International Business Machines Corp</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>203900000000</v>
+        <v>204020000000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc</t>
+          <t>T-Mobile US Inc</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>196410000000</v>
+        <v>202510000000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AMGEN Inc</t>
+          <t>Thermo Fisher Scientific Inc</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>194540000000</v>
+        <v>198470000000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>193910000000</v>
+        <v>194170000000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>McDonald's Corp</t>
+          <t>AMGEN Inc</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>193690000000</v>
+        <v>191730000000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>McDonald's Corp</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>191490000000</v>
+        <v>191080000000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>191340000000</v>
+        <v>187720000000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PepsiCo Inc</t>
+          <t>Toyota Motor Corp ADR</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>189020000000</v>
+        <v>187510000000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Sap SE ADR</t>
+          <t>NextEra Energy Inc</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>186770000000</v>
+        <v>186750000000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Toyota Motor Corp ADR</t>
+          <t>PepsiCo Inc</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>185940000000</v>
+        <v>184870000000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NextEra Energy Inc</t>
+          <t>Sap SE ADR</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>184330000000</v>
+        <v>180750000000</v>
       </c>
     </row>
     <row r="73">
@@ -1581,7 +1581,7 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>180840000000</v>
+        <v>180170000000</v>
       </c>
     </row>
     <row r="74">
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>178210000000</v>
+        <v>177340000000</v>
       </c>
     </row>
     <row r="75">
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>178050000000</v>
+        <v>175830000000</v>
       </c>
     </row>
     <row r="76">
@@ -1626,7 +1626,7 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>169890000000</v>
+        <v>171150000000</v>
       </c>
     </row>
     <row r="77">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>167730000000</v>
+        <v>166740000000</v>
       </c>
     </row>
     <row r="78">
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>166710000000</v>
+        <v>166480000000</v>
       </c>
     </row>
     <row r="79">
@@ -1671,52 +1671,52 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>165480000000</v>
+        <v>164780000000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>Shopify Inc</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>163140000000</v>
+        <v>163090000000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Shopify Inc</t>
+          <t>Corning Inc</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>161870000000</v>
+        <v>161490000000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>160440000000</v>
+        <v>161450000000</v>
       </c>
     </row>
     <row r="83">
@@ -1731,187 +1731,187 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>158090000000</v>
+        <v>157750000000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Corning Inc</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>157590000000</v>
+        <v>154950000000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Uber Technologies Inc</t>
+          <t>Blackstone Inc</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>151160000000</v>
+        <v>152150000000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>149740000000</v>
+        <v>150830000000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Blackstone Inc</t>
+          <t>AT&amp;T Inc</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>149070000000</v>
+        <v>147860000000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>Uber Technologies Inc</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>148770000000</v>
+        <v>146730000000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Intuitive Surgical Inc</t>
+          <t>Danaher Corp</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>144190000000</v>
+        <v>140880000000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Danaher Corp</t>
+          <t>Salesforce Inc</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>141670000000</v>
+        <v>137230000000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Salesforce Inc</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>140230000000</v>
+        <v>135650000000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Chubb Limited</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>137590000000</v>
+        <v>135490000000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Progressive Corp</t>
+          <t>Intuitive Surgical Inc</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>137020000000</v>
+        <v>134400000000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>Chubb Limited</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>136220000000</v>
+        <v>134280000000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Progressive Corp</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>135340000000</v>
+        <v>132400000000</v>
       </c>
     </row>
     <row r="96">
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>129600000000</v>
+        <v>129910000000</v>
       </c>
     </row>
     <row r="97">
@@ -1941,97 +1941,97 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>122340000000</v>
+        <v>121000000000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Co</t>
+          <t>PDD Holdings Inc ADR</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>121180000000</v>
+        <v>119440000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PDD Holdings Inc ADR</t>
+          <t>Lockheed Martin Corp</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>120360000000</v>
+        <v>118740000000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corp</t>
+          <t>Altria Group Inc</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>120050000000</v>
+        <v>117160000000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Altria Group Inc</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>120020000000</v>
+        <v>116610000000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>Lowe's Cos. Inc</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>117490000000</v>
+        <v>116450000000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Lowe's Cos. Inc</t>
+          <t>Bristol-Myers Squibb Co</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>116460000000</v>
+        <v>116300000000</v>
       </c>
     </row>
     <row r="104">
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>106970000000</v>
+        <v>101510000000</v>
       </c>
     </row>
     <row r="105">
@@ -2061,22 +2061,22 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>102520000000</v>
+        <v>100950000000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>100350000000</v>
+        <v>100060000000</v>
       </c>
     </row>
     <row r="107">
@@ -2091,67 +2091,67 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>98770000000</v>
+        <v>98920000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>Automatic Data Processing Inc</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>97110000000</v>
+        <v>98510000000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>United Parcel Service Inc</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>95960000000</v>
+        <v>96800000000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>United Parcel Service Inc</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>95720000000</v>
+        <v>96620000000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>MercadoLibre Inc</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>94670000000</v>
+        <v>96370000000</v>
       </c>
     </row>
     <row r="112">
@@ -2166,22 +2166,22 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>93110000000</v>
+        <v>95640000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>MercadoLibre Inc</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>92640000000</v>
+        <v>95000000000</v>
       </c>
     </row>
     <row r="114">
@@ -2196,37 +2196,37 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>92330000000</v>
+        <v>92680000000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>Airbnb Inc</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>91670000000</v>
+        <v>88320000000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Airbnb Inc</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>88190000000</v>
+        <v>87760000000</v>
       </c>
     </row>
     <row r="117">
@@ -2241,52 +2241,52 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>87460000000</v>
+        <v>85780000000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>HCA Healthcare Inc</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>86680000000</v>
+        <v>82340000000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>3M Co</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>84770000000</v>
+        <v>81670000000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>3M Co</t>
+          <t>HCA Healthcare Inc</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>82250000000</v>
+        <v>80660000000</v>
       </c>
     </row>
     <row r="121">
@@ -2301,37 +2301,37 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>80550000000</v>
+        <v>80250000000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Intuit Inc</t>
+          <t>Intercontinental Exchange Inc</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>79260000000</v>
+        <v>77820000000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange Inc</t>
+          <t>Intuit Inc</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>77850000000</v>
+        <v>77260000000</v>
       </c>
     </row>
     <row r="124">
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>77400000000</v>
+        <v>75920000000</v>
       </c>
     </row>
     <row r="125">
@@ -2361,7 +2361,7 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>76960000000</v>
+        <v>75090000000</v>
       </c>
     </row>
     <row r="126">
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>74590000000</v>
+        <v>72840000000</v>
       </c>
     </row>
     <row r="127">
@@ -2391,52 +2391,52 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>70810000000</v>
+        <v>71080000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals Inc</t>
+          <t>General Motors Company</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>69520000000</v>
+        <v>69310000000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>General Motors Company</t>
+          <t>Apollo Global Management Inc</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>69180000000</v>
+        <v>69140000000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Apollo Global Management Inc</t>
+          <t>Regeneron Pharmaceuticals Inc</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>68510000000</v>
+        <v>68790000000</v>
       </c>
     </row>
     <row r="131">
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>66030000000</v>
+        <v>67580000000</v>
       </c>
     </row>
     <row r="132">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>65830000000</v>
+        <v>65160000000</v>
       </c>
     </row>
     <row r="133">
@@ -2481,37 +2481,37 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>64800000000</v>
+        <v>63470000000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Sea Ltd ADR</t>
+          <t>Astera Labs Inc</t>
         </is>
       </c>
       <c r="L134" t="n">
-        <v>62740000000</v>
+        <v>62010000000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Astera Labs Inc</t>
+          <t>Sea Ltd ADR</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>62060000000</v>
+        <v>61960000000</v>
       </c>
     </row>
     <row r="136">
@@ -2526,7 +2526,7 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>61210000000</v>
+        <v>60860000000</v>
       </c>
     </row>
     <row r="137">
@@ -2541,7 +2541,7 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>55190000000</v>
+        <v>55550000000</v>
       </c>
     </row>
     <row r="138">
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>54520000000</v>
+        <v>54280000000</v>
       </c>
     </row>
     <row r="139">
@@ -2571,112 +2571,112 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>53320000000</v>
+        <v>53420000000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Edwards Lifesciences Corp</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>52970000000</v>
+        <v>51870000000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences Corp</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>52850000000</v>
+        <v>48840000000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>Block Inc</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>46990000000</v>
+        <v>47610000000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Block Inc</t>
+          <t>Rocket Lab Corp</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>46850000000</v>
+        <v>47140000000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Rocket Lab Corp</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>45900000000</v>
+        <v>46730000000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>MSCI Inc</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>45450000000</v>
+        <v>44510000000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MSCI Inc</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>45150000000</v>
+        <v>43610000000</v>
       </c>
     </row>
     <row r="147">
@@ -2691,37 +2691,37 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>44780000000</v>
+        <v>43450000000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>PayPal Holdings Inc</t>
+          <t>Coinbase Global Inc</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>42030000000</v>
+        <v>42550000000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Coinbase Global Inc</t>
+          <t>PayPal Holdings Inc</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>41460000000</v>
+        <v>41790000000</v>
       </c>
     </row>
     <row r="150">
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>38680000000</v>
+        <v>39130000000</v>
       </c>
     </row>
     <row r="151">
@@ -2751,67 +2751,67 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>36450000000</v>
+        <v>36300000000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Workday Inc</t>
+          <t>JD.com Inc ADR</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>35780000000</v>
+        <v>34990000000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>JD</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>JD.com Inc ADR</t>
+          <t>Workday Inc</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>35040000000</v>
+        <v>34530000000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Twilio Inc</t>
+          <t>Strategy Inc</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>33120000000</v>
+        <v>34200000000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Strategy Inc</t>
+          <t>Twilio Inc</t>
         </is>
       </c>
       <c r="L155" t="n">
-        <v>32280000000</v>
+        <v>33060000000</v>
       </c>
     </row>
     <row r="156">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>31610000000</v>
+        <v>31050000000</v>
       </c>
     </row>
     <row r="157">
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>29360000000</v>
+        <v>29250000000</v>
       </c>
     </row>
     <row r="158">
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>28750000000</v>
+        <v>28930000000</v>
       </c>
     </row>
     <row r="159">
@@ -2871,22 +2871,22 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>27440000000</v>
+        <v>28280000000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Fiserv Inc</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="L160" t="n">
-        <v>27290000000</v>
+        <v>26760000000</v>
       </c>
     </row>
     <row r="161">
@@ -2901,82 +2901,82 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>26940000000</v>
+        <v>26730000000</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>Fiserv Inc</t>
         </is>
       </c>
       <c r="L162" t="n">
-        <v>26590000000</v>
+        <v>26420000000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>First Solar Inc</t>
+          <t>Zscaler Inc</t>
         </is>
       </c>
       <c r="L163" t="n">
-        <v>23750000000</v>
+        <v>24590000000</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>DKNG</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>DraftKings Inc</t>
+          <t>SoFi Technologies Inc</t>
         </is>
       </c>
       <c r="L164" t="n">
-        <v>23520000000</v>
+        <v>23790000000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>SoFi Technologies Inc</t>
+          <t>First Solar Inc</t>
         </is>
       </c>
       <c r="L165" t="n">
-        <v>23260000000</v>
+        <v>23700000000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>DKNG</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Zscaler Inc</t>
+          <t>DraftKings Inc</t>
         </is>
       </c>
       <c r="L166" t="n">
-        <v>22930000000</v>
+        <v>22420000000</v>
       </c>
     </row>
     <row r="167">
@@ -2991,52 +2991,52 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>21120000000</v>
+        <v>21030000000</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Charter Communications Inc</t>
+          <t>Super Micro Computer Inc</t>
         </is>
       </c>
       <c r="L168" t="n">
-        <v>18190000000</v>
+        <v>17890000000</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Super Micro Computer Inc</t>
+          <t>Charter Communications Inc</t>
         </is>
       </c>
       <c r="L169" t="n">
-        <v>17890000000</v>
+        <v>17720000000</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>GRAB</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Grab Holdings Limited</t>
+          <t>Circle Internet Group Inc</t>
         </is>
       </c>
       <c r="L170" t="n">
-        <v>16150000000</v>
+        <v>15710000000</v>
       </c>
     </row>
     <row r="171">
@@ -3051,22 +3051,22 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>16150000000</v>
+        <v>15580000000</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>CRCL</t>
+          <t>GRAB</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Circle Internet Group Inc</t>
+          <t>Grab Holdings Limited</t>
         </is>
       </c>
       <c r="L172" t="n">
-        <v>15660000000</v>
+        <v>15580000000</v>
       </c>
     </row>
     <row r="173">
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>14510000000</v>
+        <v>14670000000</v>
       </c>
     </row>
     <row r="174">
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>13910000000</v>
+        <v>13770000000</v>
       </c>
     </row>
     <row r="175">
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>12660000000</v>
+        <v>12670000000</v>
       </c>
     </row>
     <row r="176">
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>12620000000</v>
+        <v>12430000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>10950000000</v>
+        <v>10550000000</v>
       </c>
     </row>
     <row r="178">
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>9530000000</v>
+        <v>9370000000</v>
       </c>
     </row>
     <row r="179">
@@ -3171,67 +3171,67 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>8630000000</v>
+        <v>8770000000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>MBLY</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Applied Digital Corp</t>
+          <t>Mobileye Global Inc</t>
         </is>
       </c>
       <c r="L180" t="n">
-        <v>8240000000</v>
+        <v>8500000000</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>MBLY</t>
+          <t>HIMS</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Mobileye Global Inc</t>
+          <t>Hims &amp; Hers Health Inc</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>8210000000</v>
+        <v>8140000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>OKLO</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Oklo Inc</t>
+          <t>Applied Digital Corp</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>7970000000</v>
+        <v>8140000000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>HIMS</t>
+          <t>OKLO</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Hims &amp; Hers Health Inc</t>
+          <t>Oklo Inc</t>
         </is>
       </c>
       <c r="L183" t="n">
-        <v>7960000000</v>
+        <v>8050000000</v>
       </c>
     </row>
     <row r="184">
@@ -3246,7 +3246,7 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>7630000000</v>
+        <v>7700000000</v>
       </c>
     </row>
     <row r="185">
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>7360000000</v>
+        <v>7280000000</v>
       </c>
     </row>
     <row r="186">
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>7180000000</v>
+        <v>7260000000</v>
       </c>
     </row>
     <row r="187">
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>6360000000</v>
+        <v>6830000000</v>
       </c>
     </row>
     <row r="188">
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>5430000000</v>
+        <v>5390000000</v>
       </c>
     </row>
     <row r="189">
@@ -3321,7 +3321,7 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>5110000000</v>
+        <v>5350000000</v>
       </c>
     </row>
     <row r="190">
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>4880000000</v>
+        <v>4870000000</v>
       </c>
     </row>
     <row r="191">
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>4650000000</v>
+        <v>4640000000</v>
       </c>
     </row>
     <row r="192">
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>3640000000</v>
+        <v>3850000000</v>
       </c>
     </row>
     <row r="193">
@@ -3381,37 +3381,37 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3130000000</v>
+        <v>3270000000</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>LEU</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Centrus Energy Corp</t>
+          <t>NuScale Power Corp</t>
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3070000000</v>
+        <v>3140000000</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>LEU</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>NuScale Power Corp</t>
+          <t>Centrus Energy Corp</t>
         </is>
       </c>
       <c r="L195" t="n">
-        <v>3050000000</v>
+        <v>3140000000</v>
       </c>
     </row>
     <row r="196">
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>3010000000</v>
+        <v>3040000000</v>
       </c>
     </row>
     <row r="197">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2790000000</v>
+        <v>2880000000</v>
       </c>
     </row>
     <row r="198">
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2740000000</v>
+        <v>2700000000</v>
       </c>
     </row>
     <row r="199">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>2620000000</v>
+        <v>2580000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1800000000</v>
+        <v>1880000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1740000000</v>
+        <v>1670000000</v>
       </c>
     </row>
     <row r="202">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>938540000</v>
+        <v>944790000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>823010000</v>
+        <v>892790000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>577900000</v>
+        <v>591750000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4624460000000</v>
+        <v>4810110000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5125560000000</v>
+        <v>5142500000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4362800000000</v>
+        <v>4522170000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2859430000000</v>
+        <v>2938910000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2662280000000</v>
+        <v>2742630000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2180340000000</v>
+        <v>2175620000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1851220000000</v>
+        <v>1875820000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1678000000000</v>
+        <v>1729450000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,52 +681,52 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1487940000000</v>
+        <v>1481480000000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Micron Technology Inc</t>
+          <t>Lilly(Eli) &amp; Co</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1110330000000</v>
+        <v>1089250000000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>BRK-B</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lilly(Eli) &amp; Co</t>
+          <t>Berkshire Hathaway Inc</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1085390000000</v>
+        <v>1053480000000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BRK-B</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Inc</t>
+          <t>Micron Technology Inc</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1059000000000</v>
+        <v>1021290000000</v>
       </c>
     </row>
     <row r="17">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>918780000000</v>
+        <v>929550000000</v>
       </c>
     </row>
     <row r="18">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>904830000000</v>
+        <v>895520000000</v>
       </c>
     </row>
     <row r="19">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>893780000000</v>
+        <v>862820000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>684370000000</v>
+        <v>699640000000</v>
       </c>
     </row>
     <row r="21">
@@ -801,37 +801,37 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>670790000000</v>
+        <v>669130000000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>ExxonMobil Holdings Corp</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>611070000000</v>
+        <v>598920000000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ExxonMobil Holdings Corp</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>601320000000</v>
+        <v>594630000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>475390000000</v>
+        <v>472900000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>472960000000</v>
+        <v>460040000000</v>
       </c>
     </row>
     <row r="26">
@@ -876,22 +876,22 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>461500000000</v>
+        <v>440530000000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Lam Research Corp</t>
+          <t>Bank Of America Corp</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>432820000000</v>
+        <v>437080000000</v>
       </c>
     </row>
     <row r="28">
@@ -906,37 +906,37 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>432480000000</v>
+        <v>431290000000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Bank Of America Corp</t>
+          <t>Caterpillar Inc</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>430200000000</v>
+        <v>421160000000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Caterpillar Inc</t>
+          <t>Lam Research Corp</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>429930000000</v>
+        <v>419480000000</v>
       </c>
     </row>
     <row r="31">
@@ -951,52 +951,52 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>408780000000</v>
+        <v>406470000000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Unitedhealth Group Inc</t>
+          <t>Oracle Corp</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>386130000000</v>
+        <v>381630000000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Unitedhealth Group Inc</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>369060000000</v>
+        <v>380080000000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Oracle Corp</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>368530000000</v>
+        <v>375970000000</v>
       </c>
     </row>
     <row r="35">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>361990000000</v>
+        <v>361670000000</v>
       </c>
     </row>
     <row r="36">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>359100000000</v>
+        <v>360490000000</v>
       </c>
     </row>
     <row r="37">
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>357450000000</v>
+        <v>354740000000</v>
       </c>
     </row>
     <row r="38">
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>340160000000</v>
+        <v>344750000000</v>
       </c>
     </row>
     <row r="39">
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>336770000000</v>
+        <v>340460000000</v>
       </c>
     </row>
     <row r="40">
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>336310000000</v>
+        <v>339870000000</v>
       </c>
     </row>
     <row r="41">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>320570000000</v>
+        <v>320660000000</v>
       </c>
     </row>
     <row r="42">
@@ -1116,22 +1116,22 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>309620000000</v>
+        <v>310250000000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>KLA Corp</t>
+          <t>Merck &amp; Co Inc</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>300930000000</v>
+        <v>305300000000</v>
       </c>
     </row>
     <row r="44">
@@ -1146,82 +1146,82 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>299160000000</v>
+        <v>294740000000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Merck &amp; Co Inc</t>
+          <t>KLA Corp</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>298310000000</v>
+        <v>293260000000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>296610000000</v>
+        <v>288530000000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>287610000000</v>
+        <v>283570000000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>Alibaba Group Holding Ltd ADR</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>286460000000</v>
+        <v>282110000000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>Philip Morris International Inc</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>278080000000</v>
+        <v>281910000000</v>
       </c>
     </row>
     <row r="50">
@@ -1236,52 +1236,52 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>275240000000</v>
+        <v>276050000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Philip Morris International Inc</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>274230000000</v>
+        <v>274110000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Alibaba Group Holding Ltd ADR</t>
+          <t>Wells Fargo &amp; Co</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>269240000000</v>
+        <v>267800000000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Co</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>261000000000</v>
+        <v>267530000000</v>
       </c>
     </row>
     <row r="54">
@@ -1296,52 +1296,52 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>260440000000</v>
+        <v>263800000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>Astrazeneca plc</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>260320000000</v>
+        <v>261120000000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Astrazeneca plc</t>
+          <t>American Express Co</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>255120000000</v>
+        <v>244570000000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>American Express Co</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>242270000000</v>
+        <v>239160000000</v>
       </c>
     </row>
     <row r="58">
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>241730000000</v>
+        <v>237850000000</v>
       </c>
     </row>
     <row r="59">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>235340000000</v>
+        <v>235980000000</v>
       </c>
     </row>
     <row r="60">
@@ -1386,7 +1386,7 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>228550000000</v>
+        <v>231320000000</v>
       </c>
     </row>
     <row r="61">
@@ -1401,97 +1401,97 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>214580000000</v>
+        <v>210550000000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>International Business Machines Corp</t>
+          <t>T-Mobile US Inc</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>204020000000</v>
+        <v>203040000000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>T-Mobile US Inc</t>
+          <t>Thermo Fisher Scientific Inc</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>202510000000</v>
+        <v>198930000000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc</t>
+          <t>International Business Machines Corp</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>198470000000</v>
+        <v>198500000000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>AMGEN Inc</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>194170000000</v>
+        <v>193390000000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>AMGEN Inc</t>
+          <t>McDonald's Corp</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>191730000000</v>
+        <v>188250000000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>McDonald's Corp</t>
+          <t>Toyota Motor Corp ADR</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>191080000000</v>
+        <v>188250000000</v>
       </c>
     </row>
     <row r="68">
@@ -1506,277 +1506,277 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>187720000000</v>
+        <v>187590000000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Toyota Motor Corp ADR</t>
+          <t>NextEra Energy Inc</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>187510000000</v>
+        <v>185830000000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NextEra Energy Inc</t>
+          <t>PepsiCo Inc</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>186750000000</v>
+        <v>184810000000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PepsiCo Inc</t>
+          <t>Sap SE ADR</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>184870000000</v>
+        <v>182030000000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Sap SE ADR</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>180750000000</v>
+        <v>178900000000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Verizon Communications Inc</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>180170000000</v>
+        <v>178840000000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc</t>
+          <t>Charles Schwab Corp</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>177340000000</v>
+        <v>178770000000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Charles Schwab Corp</t>
+          <t>Blackrock Inc</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>175830000000</v>
+        <v>177790000000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Boeing Co</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>171150000000</v>
+        <v>177110000000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Blackrock Inc</t>
+          <t>Boeing Co</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>166740000000</v>
+        <v>171940000000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Walt Disney Co</t>
+          <t>Novo Nordisk ADR</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>166480000000</v>
+        <v>169780000000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Novo Nordisk ADR</t>
+          <t>Walt Disney Co</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>164780000000</v>
+        <v>168700000000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Shopify Inc</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>163090000000</v>
+        <v>163510000000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Corning Inc</t>
+          <t>Shopify Inc</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>161490000000</v>
+        <v>160320000000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>Deere &amp; Co</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>161450000000</v>
+        <v>159120000000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Deere &amp; Co</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>157750000000</v>
+        <v>155490000000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Blackstone Inc</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>154950000000</v>
+        <v>155190000000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Blackstone Inc</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>152150000000</v>
+        <v>152090000000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>Corning Inc</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>150830000000</v>
+        <v>150100000000</v>
       </c>
     </row>
     <row r="87">
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>147860000000</v>
+        <v>148900000000</v>
       </c>
     </row>
     <row r="88">
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>146730000000</v>
+        <v>147930000000</v>
       </c>
     </row>
     <row r="89">
@@ -1821,187 +1821,187 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>140880000000</v>
+        <v>142110000000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Salesforce Inc</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>137230000000</v>
+        <v>141650000000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Intuitive Surgical Inc</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>135650000000</v>
+        <v>137760000000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>Salesforce Inc</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>135490000000</v>
+        <v>136770000000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Intuitive Surgical Inc</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>134400000000</v>
+        <v>136540000000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Chubb Limited</t>
+          <t>S&amp;P Global Inc</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>134280000000</v>
+        <v>131570000000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Progressive Corp</t>
+          <t>Chubb Limited</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>132400000000</v>
+        <v>130880000000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>S&amp;P Global Inc</t>
+          <t>PDD Holdings Inc ADR</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>129910000000</v>
+        <v>122040000000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Starbucks Corp</t>
+          <t>Progressive Corp</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>121000000000</v>
+        <v>119920000000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PDD Holdings Inc ADR</t>
+          <t>Bristol-Myers Squibb Co</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>119440000000</v>
+        <v>119910000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corp</t>
+          <t>Starbucks Corp</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>118740000000</v>
+        <v>119790000000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Altria Group Inc</t>
+          <t>Lockheed Martin Corp</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>117160000000</v>
+        <v>118620000000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>Altria Group Inc</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>116610000000</v>
+        <v>117760000000</v>
       </c>
     </row>
     <row r="102">
@@ -2016,22 +2016,22 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>116450000000</v>
+        <v>117560000000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Co</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>116300000000</v>
+        <v>116990000000</v>
       </c>
     </row>
     <row r="104">
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>101510000000</v>
+        <v>103010000000</v>
       </c>
     </row>
     <row r="105">
@@ -2061,33 +2061,33 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>100950000000</v>
+        <v>100850000000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>Spotify Technology SA</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>100060000000</v>
+        <v>99800000000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Spotify Technology SA</t>
+          <t>Automatic Data Processing Inc</t>
         </is>
       </c>
       <c r="L107" t="n">
@@ -2097,31 +2097,31 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>98510000000</v>
+        <v>98150000000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>96800000000</v>
+        <v>96960000000</v>
       </c>
     </row>
     <row r="110">
@@ -2136,37 +2136,37 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>96620000000</v>
+        <v>96000000000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>Snowflake Inc</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>96370000000</v>
+        <v>94230000000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Snowflake Inc</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>95640000000</v>
+        <v>94140000000</v>
       </c>
     </row>
     <row r="113">
@@ -2181,172 +2181,172 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>95000000000</v>
+        <v>93440000000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Elevance Health Inc</t>
+          <t>Airbnb Inc</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>92680000000</v>
+        <v>89430000000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Airbnb Inc</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>88320000000</v>
+        <v>89260000000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>MMC</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>Marsh</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>87760000000</v>
+        <v>84900000000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>MMC</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Marsh</t>
+          <t>Elevance Health Inc</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>85780000000</v>
+        <v>84760000000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>HCA Healthcare Inc</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>82340000000</v>
+        <v>84040000000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>3M Co</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>81670000000</v>
+        <v>83850000000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>HCA Healthcare Inc</t>
+          <t>3M Co</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>80660000000</v>
+        <v>83730000000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Cigna Group</t>
+          <t>Intercontinental Exchange Inc</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>80250000000</v>
+        <v>79080000000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange Inc</t>
+          <t>Cigna Group</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>77820000000</v>
+        <v>78780000000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Intuit Inc</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>77260000000</v>
+        <v>78360000000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Intuit Inc</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>75920000000</v>
+        <v>76510000000</v>
       </c>
     </row>
     <row r="125">
@@ -2361,7 +2361,7 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>75090000000</v>
+        <v>74600000000</v>
       </c>
     </row>
     <row r="126">
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>72840000000</v>
+        <v>73190000000</v>
       </c>
     </row>
     <row r="127">
@@ -2391,37 +2391,37 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>71080000000</v>
+        <v>71090000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>General Motors Company</t>
+          <t>Apollo Global Management Inc</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>69310000000</v>
+        <v>70240000000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Apollo Global Management Inc</t>
+          <t>General Motors Company</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>69140000000</v>
+        <v>70010000000</v>
       </c>
     </row>
     <row r="130">
@@ -2436,7 +2436,7 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>68790000000</v>
+        <v>69660000000</v>
       </c>
     </row>
     <row r="131">
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>67580000000</v>
+        <v>67050000000</v>
       </c>
     </row>
     <row r="132">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>65160000000</v>
+        <v>66320000000</v>
       </c>
     </row>
     <row r="133">
@@ -2481,52 +2481,52 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>63470000000</v>
+        <v>63340000000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Astera Labs Inc</t>
+          <t>Sea Ltd ADR</t>
         </is>
       </c>
       <c r="L134" t="n">
-        <v>62010000000</v>
+        <v>63140000000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Sea Ltd ADR</t>
+          <t>Target Corp</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>61960000000</v>
+        <v>62810000000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Target Corp</t>
+          <t>Astera Labs Inc</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>60860000000</v>
+        <v>60100000000</v>
       </c>
     </row>
     <row r="137">
@@ -2541,37 +2541,37 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>55550000000</v>
+        <v>56500000000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Occidental Petroleum Corp</t>
+          <t>Vistra Corp</t>
         </is>
       </c>
       <c r="L138" t="n">
-        <v>54280000000</v>
+        <v>54030000000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Vistra Corp</t>
+          <t>Occidental Petroleum Corp</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>53420000000</v>
+        <v>53480000000</v>
       </c>
     </row>
     <row r="140">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>51870000000</v>
+        <v>50250000000</v>
       </c>
     </row>
     <row r="141">
@@ -2601,52 +2601,52 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>48840000000</v>
+        <v>50210000000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Block Inc</t>
+          <t>PayPal Holdings Inc</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>47610000000</v>
+        <v>48970000000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Rocket Lab Corp</t>
+          <t>Block Inc</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>47140000000</v>
+        <v>48690000000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>Rocket Lab Corp</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>46730000000</v>
+        <v>45580000000</v>
       </c>
     </row>
     <row r="145">
@@ -2661,22 +2661,22 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>44510000000</v>
+        <v>45260000000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>43610000000</v>
+        <v>44420000000</v>
       </c>
     </row>
     <row r="147">
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>43450000000</v>
+        <v>44090000000</v>
       </c>
     </row>
     <row r="148">
@@ -2706,22 +2706,22 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>42550000000</v>
+        <v>44050000000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>PayPal Holdings Inc</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>41790000000</v>
+        <v>42070000000</v>
       </c>
     </row>
     <row r="150">
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>39130000000</v>
+        <v>38120000000</v>
       </c>
     </row>
     <row r="151">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>36300000000</v>
+        <v>36420000000</v>
       </c>
     </row>
     <row r="152">
@@ -2766,7 +2766,7 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>34990000000</v>
+        <v>35520000000</v>
       </c>
     </row>
     <row r="153">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>34530000000</v>
+        <v>35030000000</v>
       </c>
     </row>
     <row r="154">
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>34200000000</v>
+        <v>34160000000</v>
       </c>
     </row>
     <row r="155">
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>33060000000</v>
+        <v>32110000000</v>
       </c>
     </row>
     <row r="156">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>31050000000</v>
+        <v>31250000000</v>
       </c>
     </row>
     <row r="157">
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>29250000000</v>
+        <v>29780000000</v>
       </c>
     </row>
     <row r="158">
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>28930000000</v>
+        <v>28320000000</v>
       </c>
     </row>
     <row r="159">
@@ -2871,37 +2871,37 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>28280000000</v>
+        <v>27360000000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>ZM</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>Zoom Communications Inc</t>
         </is>
       </c>
       <c r="L160" t="n">
-        <v>26760000000</v>
+        <v>27150000000</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ZM</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Zoom Communications Inc</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="L161" t="n">
-        <v>26730000000</v>
+        <v>27090000000</v>
       </c>
     </row>
     <row r="162">
@@ -2916,52 +2916,52 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>26420000000</v>
+        <v>26850000000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Zscaler Inc</t>
+          <t>First Solar Inc</t>
         </is>
       </c>
       <c r="L163" t="n">
-        <v>24590000000</v>
+        <v>24050000000</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>SoFi Technologies Inc</t>
+          <t>Zscaler Inc</t>
         </is>
       </c>
       <c r="L164" t="n">
-        <v>23790000000</v>
+        <v>23960000000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>First Solar Inc</t>
+          <t>SoFi Technologies Inc</t>
         </is>
       </c>
       <c r="L165" t="n">
-        <v>23700000000</v>
+        <v>22920000000</v>
       </c>
     </row>
     <row r="166">
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>22420000000</v>
+        <v>22450000000</v>
       </c>
     </row>
     <row r="167">
@@ -2991,37 +2991,37 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>21030000000</v>
+        <v>21260000000</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Super Micro Computer Inc</t>
+          <t>Charter Communications Inc</t>
         </is>
       </c>
       <c r="L168" t="n">
-        <v>17890000000</v>
+        <v>18180000000</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Charter Communications Inc</t>
+          <t>Super Micro Computer Inc</t>
         </is>
       </c>
       <c r="L169" t="n">
-        <v>17720000000</v>
+        <v>17390000000</v>
       </c>
     </row>
     <row r="170">
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>15710000000</v>
+        <v>16330000000</v>
       </c>
     </row>
     <row r="171">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>15580000000</v>
+        <v>15660000000</v>
       </c>
     </row>
     <row r="172">
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>15580000000</v>
+        <v>15660000000</v>
       </c>
     </row>
     <row r="173">
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>14670000000</v>
+        <v>14000000000</v>
       </c>
     </row>
     <row r="174">
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>13770000000</v>
+        <v>13660000000</v>
       </c>
     </row>
     <row r="175">
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>12670000000</v>
+        <v>13260000000</v>
       </c>
     </row>
     <row r="176">
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>12430000000</v>
+        <v>12480000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>10550000000</v>
+        <v>10520000000</v>
       </c>
     </row>
     <row r="178">
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>9370000000</v>
+        <v>9230000000</v>
       </c>
     </row>
     <row r="179">
@@ -3171,97 +3171,97 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>8770000000</v>
+        <v>9050000000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>MBLY</t>
+          <t>HIMS</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Mobileye Global Inc</t>
+          <t>Hims &amp; Hers Health Inc</t>
         </is>
       </c>
       <c r="L180" t="n">
-        <v>8500000000</v>
+        <v>8600000000</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>HIMS</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Hims &amp; Hers Health Inc</t>
+          <t>Applied Digital Corp</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>8140000000</v>
+        <v>8300000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>OKLO</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Applied Digital Corp</t>
+          <t>Oklo Inc</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>8140000000</v>
+        <v>7950000000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>OKLO</t>
+          <t>MBLY</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Oklo Inc</t>
+          <t>Mobileye Global Inc</t>
         </is>
       </c>
       <c r="L183" t="n">
-        <v>8050000000</v>
+        <v>7940000000</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Celsius Holdings Inc</t>
+          <t>Zillow Group Inc</t>
         </is>
       </c>
       <c r="L184" t="n">
-        <v>7700000000</v>
+        <v>7740000000</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Zillow Group Inc</t>
+          <t>Celsius Holdings Inc</t>
         </is>
       </c>
       <c r="L185" t="n">
-        <v>7280000000</v>
+        <v>7720000000</v>
       </c>
     </row>
     <row r="186">
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>7260000000</v>
+        <v>7150000000</v>
       </c>
     </row>
     <row r="187">
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>6830000000</v>
+        <v>6710000000</v>
       </c>
     </row>
     <row r="188">
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>5390000000</v>
+        <v>5070000000</v>
       </c>
     </row>
     <row r="189">
@@ -3321,7 +3321,7 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>5350000000</v>
+        <v>5070000000</v>
       </c>
     </row>
     <row r="190">
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>4870000000</v>
+        <v>4950000000</v>
       </c>
     </row>
     <row r="191">
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>4640000000</v>
+        <v>4690000000</v>
       </c>
     </row>
     <row r="192">
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>3850000000</v>
+        <v>3740000000</v>
       </c>
     </row>
     <row r="193">
@@ -3381,37 +3381,37 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3270000000</v>
+        <v>3130000000</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>LEU</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>NuScale Power Corp</t>
+          <t>Centrus Energy Corp</t>
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3140000000</v>
+        <v>3080000000</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>LEU</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Centrus Energy Corp</t>
+          <t>NuScale Power Corp</t>
         </is>
       </c>
       <c r="L195" t="n">
-        <v>3140000000</v>
+        <v>3060000000</v>
       </c>
     </row>
     <row r="196">
@@ -3426,37 +3426,37 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>3040000000</v>
+        <v>3020000000</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>FLNC</t>
+          <t>PENN</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Fluence Energy Inc</t>
+          <t>PENN Entertainment Inc</t>
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2880000000</v>
+        <v>2830000000</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>PENN</t>
+          <t>FLNC</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>PENN Entertainment Inc</t>
+          <t>Fluence Energy Inc</t>
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2700000000</v>
+        <v>2830000000</v>
       </c>
     </row>
     <row r="199">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>2580000000</v>
+        <v>2610000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1880000000</v>
+        <v>1810000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1670000000</v>
+        <v>1750000000</v>
       </c>
     </row>
     <row r="202">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>944790000</v>
+        <v>930730000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>892790000</v>
+        <v>885140000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>591750000</v>
+        <v>576640000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4810110000000</v>
+        <v>4894710000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5142500000000</v>
+        <v>5019080000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4522170000000</v>
+        <v>4311940000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2938910000000</v>
+        <v>2979550000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2742630000000</v>
+        <v>2688090000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2175620000000</v>
+        <v>2125110000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1875820000000</v>
+        <v>1781480000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1729450000000</v>
+        <v>1686880000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1481480000000</v>
+        <v>1468710000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1089250000000</v>
+        <v>1101060000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1053480000000</v>
+        <v>1063920000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1021290000000</v>
+        <v>963600000000</v>
       </c>
     </row>
     <row r="17">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>929550000000</v>
+        <v>919470000000</v>
       </c>
     </row>
     <row r="18">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>895520000000</v>
+        <v>914780000000</v>
       </c>
     </row>
     <row r="19">
@@ -771,37 +771,37 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>862820000000</v>
+        <v>816830000000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ASML Holding NV</t>
+          <t>Visa Inc</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>699640000000</v>
+        <v>687970000000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Visa Inc</t>
+          <t>ASML Holding NV</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>669130000000</v>
+        <v>687920000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>598920000000</v>
+        <v>604880000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>594630000000</v>
+        <v>601730000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,37 +846,37 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>472900000000</v>
+        <v>487330000000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Applied Materials Inc</t>
+          <t>Abbvie Inc</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>460040000000</v>
+        <v>449450000000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cisco Systems Inc</t>
+          <t>Applied Materials Inc</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>440530000000</v>
+        <v>445360000000</v>
       </c>
     </row>
     <row r="27">
@@ -891,187 +891,187 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>437080000000</v>
+        <v>436370000000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Abbvie Inc</t>
+          <t>Cisco Systems Inc</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>431290000000</v>
+        <v>432220000000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Caterpillar Inc</t>
+          <t>Costco Wholesale Corp</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>421160000000</v>
+        <v>419340000000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Lam Research Corp</t>
+          <t>Caterpillar Inc</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>419480000000</v>
+        <v>404060000000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Costco Wholesale Corp</t>
+          <t>Lam Research Corp</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>406470000000</v>
+        <v>401380000000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Oracle Corp</t>
+          <t>Unitedhealth Group Inc</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>381630000000</v>
+        <v>384490000000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Unitedhealth Group Inc</t>
+          <t>Chevron Corp</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>380080000000</v>
+        <v>366180000000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Coca-Cola Co</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>375970000000</v>
+        <v>365370000000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Chevron Corp</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>361670000000</v>
+        <v>360710000000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Oracle Corp</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>360490000000</v>
+        <v>357780000000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Coca-Cola Co</t>
+          <t>Procter &amp; Gamble Co</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>354740000000</v>
+        <v>352780000000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble Co</t>
+          <t>Home Depot Inc</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>344750000000</v>
+        <v>347020000000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Home Depot Inc</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>340460000000</v>
+        <v>344430000000</v>
       </c>
     </row>
     <row r="40">
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>339870000000</v>
+        <v>323170000000</v>
       </c>
     </row>
     <row r="41">
@@ -1101,187 +1101,187 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>320660000000</v>
+        <v>322290000000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Netflix Inc</t>
+          <t>Merck &amp; Co Inc</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>310250000000</v>
+        <v>315220000000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Merck &amp; Co Inc</t>
+          <t>Netflix Inc</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>305300000000</v>
+        <v>313070000000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>Philip Morris International Inc</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>294740000000</v>
+        <v>295880000000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>KLA Corp</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>293260000000</v>
+        <v>288500000000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>KLA Corp</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>288530000000</v>
+        <v>286560000000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>Alibaba Group Holding Ltd ADR</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>283570000000</v>
+        <v>281630000000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>NVS</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Alibaba Group Holding Ltd ADR</t>
+          <t>Novartis AG ADR</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>282110000000</v>
+        <v>279580000000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Philip Morris International Inc</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>281910000000</v>
+        <v>278780000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NVS</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Novartis AG ADR</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>276050000000</v>
+        <v>278450000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>Wells Fargo &amp; Co</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>274110000000</v>
+        <v>269510000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Co</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>267800000000</v>
+        <v>265040000000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>Astrazeneca plc</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>267530000000</v>
+        <v>262550000000</v>
       </c>
     </row>
     <row r="54">
@@ -1296,22 +1296,22 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>263800000000</v>
+        <v>261740000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Astrazeneca plc</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>261120000000</v>
+        <v>253720000000</v>
       </c>
     </row>
     <row r="56">
@@ -1326,127 +1326,127 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>244570000000</v>
+        <v>246710000000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>Linde Plc</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>239160000000</v>
+        <v>240890000000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Linde Plc</t>
+          <t>Shell Plc ADR</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>237850000000</v>
+        <v>237210000000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Shell Plc ADR</t>
+          <t>Citigroup Inc</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>235980000000</v>
+        <v>225870000000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Citigroup Inc</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>231320000000</v>
+        <v>208970000000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>T-Mobile US Inc</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>210550000000</v>
+        <v>208700000000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>T-Mobile US Inc</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>203040000000</v>
+        <v>207480000000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc</t>
+          <t>International Business Machines Corp</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>198930000000</v>
+        <v>205880000000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>International Business Machines Corp</t>
+          <t>Thermo Fisher Scientific Inc</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>198500000000</v>
+        <v>201860000000</v>
       </c>
     </row>
     <row r="65">
@@ -1461,7 +1461,7 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>193390000000</v>
+        <v>200540000000</v>
       </c>
     </row>
     <row r="66">
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>188250000000</v>
+        <v>194290000000</v>
       </c>
     </row>
     <row r="67">
@@ -1491,202 +1491,202 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>188250000000</v>
+        <v>191270000000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>PepsiCo Inc</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>187590000000</v>
+        <v>190310000000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NextEra Energy Inc</t>
+          <t>Sap SE ADR</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>185830000000</v>
+        <v>188720000000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PepsiCo Inc</t>
+          <t>NextEra Energy Inc</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>184810000000</v>
+        <v>186350000000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Sap SE ADR</t>
+          <t>Verizon Communications Inc</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>182030000000</v>
+        <v>183220000000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>178900000000</v>
+        <v>179820000000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc</t>
+          <t>Charles Schwab Corp</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>178840000000</v>
+        <v>178780000000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Charles Schwab Corp</t>
+          <t>Blackrock Inc</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>178770000000</v>
+        <v>176760000000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Blackrock Inc</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>177790000000</v>
+        <v>175510000000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>Walt Disney Co</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>177110000000</v>
+        <v>173150000000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Boeing Co</t>
+          <t>Novo Nordisk ADR</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>171940000000</v>
+        <v>172870000000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Novo Nordisk ADR</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>169780000000</v>
+        <v>172140000000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Walt Disney Co</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>168700000000</v>
+        <v>169230000000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>Boeing Co</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>163510000000</v>
+        <v>168960000000</v>
       </c>
     </row>
     <row r="81">
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>160320000000</v>
+        <v>162280000000</v>
       </c>
     </row>
     <row r="82">
@@ -1716,22 +1716,22 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>159120000000</v>
+        <v>161680000000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>155490000000</v>
+        <v>160900000000</v>
       </c>
     </row>
     <row r="84">
@@ -1746,97 +1746,97 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>155190000000</v>
+        <v>157540000000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>AT&amp;T Inc</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>152090000000</v>
+        <v>152720000000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Corning Inc</t>
+          <t>Uber Technologies Inc</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>150100000000</v>
+        <v>150720000000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>148900000000</v>
+        <v>145960000000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Uber Technologies Inc</t>
+          <t>Danaher Corp</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>147930000000</v>
+        <v>145100000000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Danaher Corp</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>142110000000</v>
+        <v>143050000000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>141650000000</v>
+        <v>142860000000</v>
       </c>
     </row>
     <row r="91">
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>137760000000</v>
+        <v>142490000000</v>
       </c>
     </row>
     <row r="92">
@@ -1866,22 +1866,22 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>136770000000</v>
+        <v>141420000000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Corning Inc</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>136540000000</v>
+        <v>136320000000</v>
       </c>
     </row>
     <row r="94">
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>131570000000</v>
+        <v>135380000000</v>
       </c>
     </row>
     <row r="95">
@@ -1911,112 +1911,112 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>130880000000</v>
+        <v>133310000000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PDD Holdings Inc ADR</t>
+          <t>Bristol-Myers Squibb Co</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>122040000000</v>
+        <v>123570000000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Progressive Corp</t>
+          <t>Starbucks Corp</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>119920000000</v>
+        <v>123510000000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Co</t>
+          <t>PDD Holdings Inc ADR</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>119910000000</v>
+        <v>123380000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Starbucks Corp</t>
+          <t>Altria Group Inc</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>119790000000</v>
+        <v>121950000000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corp</t>
+          <t>Lowe's Cos. Inc</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>118620000000</v>
+        <v>121200000000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Altria Group Inc</t>
+          <t>Progressive Corp</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>117760000000</v>
+        <v>120260000000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Lowe's Cos. Inc</t>
+          <t>Lockheed Martin Corp</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>117560000000</v>
+        <v>118400000000</v>
       </c>
     </row>
     <row r="103">
@@ -2031,7 +2031,7 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>116990000000</v>
+        <v>112970000000</v>
       </c>
     </row>
     <row r="104">
@@ -2046,202 +2046,202 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>103010000000</v>
+        <v>106960000000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Equinix Inc</t>
+          <t>Automatic Data Processing Inc</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>100850000000</v>
+        <v>102560000000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Spotify Technology SA</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>99800000000</v>
+        <v>99710000000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc</t>
+          <t>United Parcel Service Inc</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>98920000000</v>
+        <v>99600000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>Equinix Inc</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>98150000000</v>
+        <v>99530000000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>Spotify Technology SA</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>96960000000</v>
+        <v>97890000000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>United Parcel Service Inc</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>96000000000</v>
+        <v>96760000000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Snowflake Inc</t>
+          <t>MercadoLibre Inc</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>94230000000</v>
+        <v>94170000000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>Snowflake Inc</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>94140000000</v>
+        <v>93590000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>MercadoLibre Inc</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>93440000000</v>
+        <v>93540000000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Airbnb Inc</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>89430000000</v>
+        <v>93380000000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>Airbnb Inc</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>89260000000</v>
+        <v>89080000000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MMC</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Marsh</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>84900000000</v>
+        <v>88490000000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>MMC</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Elevance Health Inc</t>
+          <t>Marsh</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>84760000000</v>
+        <v>87760000000</v>
       </c>
     </row>
     <row r="118">
@@ -2256,67 +2256,67 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>84040000000</v>
+        <v>85570000000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>3M Co</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>83850000000</v>
+        <v>84370000000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>3M Co</t>
+          <t>Elevance Health Inc</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>83730000000</v>
+        <v>80970000000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange Inc</t>
+          <t>Intuit Inc</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>79080000000</v>
+        <v>80640000000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Cigna Group</t>
+          <t>Intercontinental Exchange Inc</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>78780000000</v>
+        <v>80170000000</v>
       </c>
     </row>
     <row r="123">
@@ -2331,67 +2331,67 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>78360000000</v>
+        <v>78840000000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Intuit Inc</t>
+          <t>Colgate-Palmolive Co</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>76510000000</v>
+        <v>75270000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp</t>
+          <t>Cigna Group</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>74600000000</v>
+        <v>75080000000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive Co</t>
+          <t>Northrop Grumman Corp</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>73190000000</v>
+        <v>73670000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>SLB Ltd</t>
+          <t>Regeneron Pharmaceuticals Inc</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>71090000000</v>
+        <v>71180000000</v>
       </c>
     </row>
     <row r="128">
@@ -2406,67 +2406,67 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>70240000000</v>
+        <v>71110000000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>General Motors Company</t>
+          <t>SLB Ltd</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>70010000000</v>
+        <v>70390000000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals Inc</t>
+          <t>General Motors Company</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>69660000000</v>
+        <v>70080000000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>NU</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Nu Holdings Ltd</t>
+          <t>Ferrari NV</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>67050000000</v>
+        <v>67530000000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Ferrari NV</t>
+          <t>Nu Holdings Ltd</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>66320000000</v>
+        <v>66610000000</v>
       </c>
     </row>
     <row r="133">
@@ -2481,97 +2481,97 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>63340000000</v>
+        <v>66000000000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Sea Ltd ADR</t>
+          <t>Target Corp</t>
         </is>
       </c>
       <c r="L134" t="n">
-        <v>63140000000</v>
+        <v>63680000000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Target Corp</t>
+          <t>Sea Ltd ADR</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>62810000000</v>
+        <v>60220000000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Astera Labs Inc</t>
+          <t>Ford Motor Co</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>60100000000</v>
+        <v>56540000000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Ford Motor Co</t>
+          <t>Astera Labs Inc</t>
         </is>
       </c>
       <c r="L137" t="n">
-        <v>56500000000</v>
+        <v>54810000000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Vistra Corp</t>
+          <t>Occidental Petroleum Corp</t>
         </is>
       </c>
       <c r="L138" t="n">
-        <v>54030000000</v>
+        <v>53360000000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Occidental Petroleum Corp</t>
+          <t>Vistra Corp</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>53480000000</v>
+        <v>51440000000</v>
       </c>
     </row>
     <row r="140">
@@ -2586,127 +2586,127 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>50250000000</v>
+        <v>50580000000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>PayPal Holdings Inc</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>50210000000</v>
+        <v>50040000000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>PayPal Holdings Inc</t>
+          <t>Block Inc</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>48970000000</v>
+        <v>48520000000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Block Inc</t>
+          <t>MSCI Inc</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>48690000000</v>
+        <v>46390000000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Rocket Lab Corp</t>
+          <t>Autodesk Inc</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>45580000000</v>
+        <v>45800000000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MSCI Inc</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>45260000000</v>
+        <v>43870000000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>44420000000</v>
+        <v>43230000000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Autodesk Inc</t>
+          <t>Coinbase Global Inc</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>44090000000</v>
+        <v>42280000000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Coinbase Global Inc</t>
+          <t>Rocket Lab Corp</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>44050000000</v>
+        <v>40290000000</v>
       </c>
     </row>
     <row r="149">
@@ -2721,67 +2721,67 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>42070000000</v>
+        <v>39780000000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>RDDT</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Reddit Inc</t>
+          <t>Carnival Corp Ltd</t>
         </is>
       </c>
       <c r="L150" t="n">
-        <v>38120000000</v>
+        <v>36790000000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Carnival Corp Ltd</t>
+          <t>JD.com Inc ADR</t>
         </is>
       </c>
       <c r="L151" t="n">
-        <v>36420000000</v>
+        <v>36010000000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>JD</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>JD.com Inc ADR</t>
+          <t>Workday Inc</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>35520000000</v>
+        <v>35920000000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>RDDT</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Workday Inc</t>
+          <t>Reddit Inc</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>35030000000</v>
+        <v>35660000000</v>
       </c>
     </row>
     <row r="154">
@@ -2796,37 +2796,37 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>34160000000</v>
+        <v>32950000000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Twilio Inc</t>
+          <t>Zoetis Inc</t>
         </is>
       </c>
       <c r="L155" t="n">
-        <v>32110000000</v>
+        <v>32240000000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Zoetis Inc</t>
+          <t>Twilio Inc</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>31250000000</v>
+        <v>31370000000</v>
       </c>
     </row>
     <row r="157">
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>29780000000</v>
+        <v>29970000000</v>
       </c>
     </row>
     <row r="158">
@@ -2856,22 +2856,22 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>28320000000</v>
+        <v>28780000000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>AFRM</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Affirm Holdings Inc</t>
+          <t>Fiserv Inc</t>
         </is>
       </c>
       <c r="L159" t="n">
-        <v>27360000000</v>
+        <v>27580000000</v>
       </c>
     </row>
     <row r="160">
@@ -2886,67 +2886,67 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>27150000000</v>
+        <v>27250000000</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>AFRM</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>Affirm Holdings Inc</t>
         </is>
       </c>
       <c r="L161" t="n">
-        <v>27090000000</v>
+        <v>26740000000</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Fiserv Inc</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="L162" t="n">
-        <v>26850000000</v>
+        <v>25060000000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>First Solar Inc</t>
+          <t>Zscaler Inc</t>
         </is>
       </c>
       <c r="L163" t="n">
-        <v>24050000000</v>
+        <v>23680000000</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Zscaler Inc</t>
+          <t>First Solar Inc</t>
         </is>
       </c>
       <c r="L164" t="n">
-        <v>23960000000</v>
+        <v>22770000000</v>
       </c>
     </row>
     <row r="165">
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>22920000000</v>
+        <v>22220000000</v>
       </c>
     </row>
     <row r="166">
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>22450000000</v>
+        <v>22090000000</v>
       </c>
     </row>
     <row r="167">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>21260000000</v>
+        <v>21330000000</v>
       </c>
     </row>
     <row r="168">
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>18180000000</v>
+        <v>18470000000</v>
       </c>
     </row>
     <row r="169">
@@ -3021,22 +3021,22 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>17390000000</v>
+        <v>15960000000</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>CRCL</t>
+          <t>GRAB</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Circle Internet Group Inc</t>
+          <t>Grab Holdings Limited</t>
         </is>
       </c>
       <c r="L170" t="n">
-        <v>16330000000</v>
+        <v>15290000000</v>
       </c>
     </row>
     <row r="171">
@@ -3051,22 +3051,22 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>15660000000</v>
+        <v>15290000000</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>GRAB</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Grab Holdings Limited</t>
+          <t>Circle Internet Group Inc</t>
         </is>
       </c>
       <c r="L172" t="n">
-        <v>15660000000</v>
+        <v>15070000000</v>
       </c>
     </row>
     <row r="173">
@@ -3081,22 +3081,22 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>14000000000</v>
+        <v>13100000000</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>TXRH</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>IREN Ltd</t>
+          <t>Texas Roadhouse Inc</t>
         </is>
       </c>
       <c r="L174" t="n">
-        <v>13660000000</v>
+        <v>12980000000</v>
       </c>
     </row>
     <row r="175">
@@ -3111,22 +3111,22 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>13260000000</v>
+        <v>12930000000</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>TXRH</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Texas Roadhouse Inc</t>
+          <t>IREN Ltd</t>
         </is>
       </c>
       <c r="L176" t="n">
-        <v>12480000000</v>
+        <v>12430000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,37 +3141,37 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>10520000000</v>
+        <v>10770000000</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>OSCR</t>
+          <t>PRMB</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Oscar Health Inc</t>
+          <t>Primo Brands Corp</t>
         </is>
       </c>
       <c r="L178" t="n">
-        <v>9230000000</v>
+        <v>9210000000</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>PRMB</t>
+          <t>OSCR</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Primo Brands Corp</t>
+          <t>Oscar Health Inc</t>
         </is>
       </c>
       <c r="L179" t="n">
-        <v>9050000000</v>
+        <v>8700000000</v>
       </c>
     </row>
     <row r="180">
@@ -3186,97 +3186,97 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>8600000000</v>
+        <v>7800000000</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Applied Digital Corp</t>
+          <t>Zillow Group Inc</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>8300000000</v>
+        <v>7790000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>OKLO</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Oklo Inc</t>
+          <t>Celsius Holdings Inc</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>7950000000</v>
+        <v>7660000000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>MBLY</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Mobileye Global Inc</t>
+          <t>Applied Digital Corp</t>
         </is>
       </c>
       <c r="L183" t="n">
-        <v>7940000000</v>
+        <v>7560000000</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Zillow Group Inc</t>
+          <t>AeroVironment Inc</t>
         </is>
       </c>
       <c r="L184" t="n">
-        <v>7740000000</v>
+        <v>7560000000</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>MBLY</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Celsius Holdings Inc</t>
+          <t>Mobileye Global Inc</t>
         </is>
       </c>
       <c r="L185" t="n">
-        <v>7720000000</v>
+        <v>7550000000</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>OKLO</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>AeroVironment Inc</t>
+          <t>Oklo Inc</t>
         </is>
       </c>
       <c r="L186" t="n">
-        <v>7150000000</v>
+        <v>7260000000</v>
       </c>
     </row>
     <row r="187">
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>6710000000</v>
+        <v>6730000000</v>
       </c>
     </row>
     <row r="188">
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>5070000000</v>
+        <v>4960000000</v>
       </c>
     </row>
     <row r="189">
@@ -3321,7 +3321,7 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>5070000000</v>
+        <v>4690000000</v>
       </c>
     </row>
     <row r="190">
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>4950000000</v>
+        <v>4680000000</v>
       </c>
     </row>
     <row r="191">
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>4690000000</v>
+        <v>4350000000</v>
       </c>
     </row>
     <row r="192">
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>3740000000</v>
+        <v>3520000000</v>
       </c>
     </row>
     <row r="193">
@@ -3381,67 +3381,67 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3130000000</v>
+        <v>3180000000</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>LEU</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Centrus Energy Corp</t>
+          <t>Upstart Holdings Inc</t>
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3080000000</v>
+        <v>2960000000</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>LEU</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>NuScale Power Corp</t>
+          <t>Centrus Energy Corp</t>
         </is>
       </c>
       <c r="L195" t="n">
-        <v>3060000000</v>
+        <v>2890000000</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>PENN</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Upstart Holdings Inc</t>
+          <t>PENN Entertainment Inc</t>
         </is>
       </c>
       <c r="L196" t="n">
-        <v>3020000000</v>
+        <v>2850000000</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>PENN</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>PENN Entertainment Inc</t>
+          <t>NuScale Power Corp</t>
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2830000000</v>
+        <v>2790000000</v>
       </c>
     </row>
     <row r="198">
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2830000000</v>
+        <v>2660000000</v>
       </c>
     </row>
     <row r="199">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>2610000000</v>
+        <v>2630000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1810000000</v>
+        <v>1720000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1750000000</v>
+        <v>1710000000</v>
       </c>
     </row>
     <row r="202">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1420000000</v>
+        <v>1390000000</v>
       </c>
     </row>
     <row r="203">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>930730000</v>
+        <v>843750000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>885140000</v>
+        <v>795290000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>576640000</v>
+        <v>496690000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4894710000000</v>
+        <v>4901760000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5019080000000</v>
+        <v>4908000000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4311940000000</v>
+        <v>4218030000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2979550000000</v>
+        <v>2925470000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2688090000000</v>
+        <v>2659480000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2125110000000</v>
+        <v>2066140000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1781480000000</v>
+        <v>1764230000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1686880000000</v>
+        <v>1639850000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1468710000000</v>
+        <v>1430330000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1101060000000</v>
+        <v>1110420000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1063920000000</v>
+        <v>1058230000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>963600000000</v>
+        <v>958800000000</v>
       </c>
     </row>
     <row r="17">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>919470000000</v>
+        <v>913980000000</v>
       </c>
     </row>
     <row r="18">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>914780000000</v>
+        <v>909130000000</v>
       </c>
     </row>
     <row r="19">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>816830000000</v>
+        <v>808390000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>687970000000</v>
+        <v>675570000000</v>
       </c>
     </row>
     <row r="21">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>687920000000</v>
+        <v>673550000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>604880000000</v>
+        <v>610730000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>601730000000</v>
+        <v>609120000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>487330000000</v>
+        <v>480320000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,22 +861,22 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>449450000000</v>
+        <v>449630000000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Applied Materials Inc</t>
+          <t>Cisco Systems Inc</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>445360000000</v>
+        <v>441200000000</v>
       </c>
     </row>
     <row r="27">
@@ -891,22 +891,22 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>436370000000</v>
+        <v>434810000000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cisco Systems Inc</t>
+          <t>Applied Materials Inc</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>432220000000</v>
+        <v>420530000000</v>
       </c>
     </row>
     <row r="29">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>419340000000</v>
+        <v>417260000000</v>
       </c>
     </row>
     <row r="30">
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>404060000000</v>
+        <v>405490000000</v>
       </c>
     </row>
     <row r="31">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>401380000000</v>
+        <v>391800000000</v>
       </c>
     </row>
     <row r="32">
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>384490000000</v>
+        <v>386950000000</v>
       </c>
     </row>
     <row r="33">
@@ -981,22 +981,22 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>366180000000</v>
+        <v>373190000000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Coca-Cola Co</t>
+          <t>Oracle Corp</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>365370000000</v>
+        <v>364120000000</v>
       </c>
     </row>
     <row r="35">
@@ -1011,22 +1011,22 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>360710000000</v>
+        <v>363950000000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Oracle Corp</t>
+          <t>Coca-Cola Co</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>357780000000</v>
+        <v>350910000000</v>
       </c>
     </row>
     <row r="37">
@@ -1041,157 +1041,157 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>352780000000</v>
+        <v>349240000000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Home Depot Inc</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>347020000000</v>
+        <v>339900000000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Home Depot Inc</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>344430000000</v>
+        <v>337890000000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Goldman Sachs Group Inc</t>
+          <t>Palantir Technologies Inc</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>323170000000</v>
+        <v>317360000000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc</t>
+          <t>Merck &amp; Co Inc</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>322290000000</v>
+        <v>314900000000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Merck &amp; Co Inc</t>
+          <t>Goldman Sachs Group Inc</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>315220000000</v>
+        <v>314250000000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Netflix Inc</t>
+          <t>Philip Morris International Inc</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>313070000000</v>
+        <v>300770000000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Philip Morris International Inc</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>295880000000</v>
+        <v>292320000000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>Netflix Inc</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>288500000000</v>
+        <v>290330000000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>KLA Corp</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>286560000000</v>
+        <v>284290000000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Alibaba Group Holding Ltd ADR</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>281630000000</v>
+        <v>284260000000</v>
       </c>
     </row>
     <row r="48">
@@ -1206,37 +1206,37 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>279580000000</v>
+        <v>281470000000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>KLA Corp</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>278780000000</v>
+        <v>277910000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>Alibaba Group Holding Ltd ADR</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>278450000000</v>
+        <v>275590000000</v>
       </c>
     </row>
     <row r="51">
@@ -1251,52 +1251,52 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>269510000000</v>
+        <v>267800000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>Astrazeneca plc</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>265040000000</v>
+        <v>261940000000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Astrazeneca plc</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>262550000000</v>
+        <v>260600000000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>261740000000</v>
+        <v>258480000000</v>
       </c>
     </row>
     <row r="55">
@@ -1311,52 +1311,52 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>253720000000</v>
+        <v>256940000000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>American Express Co</t>
+          <t>Shell Plc ADR</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>246710000000</v>
+        <v>243460000000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Linde Plc</t>
+          <t>American Express Co</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>240890000000</v>
+        <v>242460000000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Shell Plc ADR</t>
+          <t>Linde Plc</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>237210000000</v>
+        <v>237420000000</v>
       </c>
     </row>
     <row r="59">
@@ -1371,52 +1371,52 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>225870000000</v>
+        <v>221840000000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>T-Mobile US Inc</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>208970000000</v>
+        <v>208250000000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>T-Mobile US Inc</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>208700000000</v>
+        <v>206790000000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>207480000000</v>
+        <v>200630000000</v>
       </c>
     </row>
     <row r="63">
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>205880000000</v>
+        <v>199890000000</v>
       </c>
     </row>
     <row r="64">
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>201860000000</v>
+        <v>197880000000</v>
       </c>
     </row>
     <row r="65">
@@ -1461,7 +1461,7 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>200540000000</v>
+        <v>197690000000</v>
       </c>
     </row>
     <row r="66">
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>194290000000</v>
+        <v>190210000000</v>
       </c>
     </row>
     <row r="67">
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>191270000000</v>
+        <v>188990000000</v>
       </c>
     </row>
     <row r="68">
@@ -1506,7 +1506,7 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>190310000000</v>
+        <v>187150000000</v>
       </c>
     </row>
     <row r="69">
@@ -1521,7 +1521,7 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>188720000000</v>
+        <v>185690000000</v>
       </c>
     </row>
     <row r="70">
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>186350000000</v>
+        <v>185200000000</v>
       </c>
     </row>
     <row r="71">
@@ -1551,157 +1551,157 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>183220000000</v>
+        <v>182010000000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>179820000000</v>
+        <v>181240000000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Charles Schwab Corp</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>178780000000</v>
+        <v>181060000000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Blackrock Inc</t>
+          <t>Charles Schwab Corp</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>176760000000</v>
+        <v>176630000000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>175510000000</v>
+        <v>175370000000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Walt Disney Co</t>
+          <t>Blackrock Inc</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>173150000000</v>
+        <v>174340000000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Novo Nordisk ADR</t>
+          <t>Walt Disney Co</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>172870000000</v>
+        <v>169610000000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Novo Nordisk ADR</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>172140000000</v>
+        <v>168970000000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>Boeing Co</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>169230000000</v>
+        <v>168720000000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Boeing Co</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>168960000000</v>
+        <v>166720000000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Shopify Inc</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>162280000000</v>
+        <v>164490000000</v>
       </c>
     </row>
     <row r="82">
@@ -1716,22 +1716,22 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>161680000000</v>
+        <v>161220000000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>Shopify Inc</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>160900000000</v>
+        <v>160340000000</v>
       </c>
     </row>
     <row r="84">
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>157540000000</v>
+        <v>155020000000</v>
       </c>
     </row>
     <row r="85">
@@ -1761,7 +1761,7 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>152720000000</v>
+        <v>151540000000</v>
       </c>
     </row>
     <row r="86">
@@ -1776,247 +1776,247 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>150720000000</v>
+        <v>147500000000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>Danaher Corp</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>145960000000</v>
+        <v>144260000000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Danaher Corp</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>145100000000</v>
+        <v>142620000000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>143050000000</v>
+        <v>142600000000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>142860000000</v>
+        <v>140780000000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Intuitive Surgical Inc</t>
+          <t>Salesforce Inc</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>142490000000</v>
+        <v>139860000000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Salesforce Inc</t>
+          <t>Chubb Limited</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>141420000000</v>
+        <v>136590000000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Corning Inc</t>
+          <t>S&amp;P Global Inc</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>136320000000</v>
+        <v>133450000000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>S&amp;P Global Inc</t>
+          <t>Corning Inc</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>135380000000</v>
+        <v>133060000000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Chubb Limited</t>
+          <t>Bristol-Myers Squibb Co</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>133310000000</v>
+        <v>124040000000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Co</t>
+          <t>Altria Group Inc</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>123570000000</v>
+        <v>123920000000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Starbucks Corp</t>
+          <t>Intuitive Surgical Inc</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>123510000000</v>
+        <v>122330000000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PDD Holdings Inc ADR</t>
+          <t>Progressive Corp</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>123380000000</v>
+        <v>121510000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Altria Group Inc</t>
+          <t>Starbucks Corp</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>121950000000</v>
+        <v>120230000000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Lowe's Cos. Inc</t>
+          <t>PDD Holdings Inc ADR</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>121200000000</v>
+        <v>119760000000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Progressive Corp</t>
+          <t>Lockheed Martin Corp</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>120260000000</v>
+        <v>117300000000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corp</t>
+          <t>Lowe's Cos. Inc</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>118400000000</v>
+        <v>117040000000</v>
       </c>
     </row>
     <row r="103">
@@ -2031,7 +2031,7 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>112970000000</v>
+        <v>111220000000</v>
       </c>
     </row>
     <row r="104">
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>106960000000</v>
+        <v>106500000000</v>
       </c>
     </row>
     <row r="105">
@@ -2061,22 +2061,22 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>102560000000</v>
+        <v>102040000000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>Equinix Inc</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>99710000000</v>
+        <v>100600000000</v>
       </c>
     </row>
     <row r="107">
@@ -2091,67 +2091,67 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>99600000000</v>
+        <v>100060000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Equinix Inc</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>99530000000</v>
+        <v>98600000000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Spotify Technology SA</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>97890000000</v>
+        <v>98360000000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>Spotify Technology SA</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>96760000000</v>
+        <v>98320000000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>MercadoLibre Inc</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>94170000000</v>
+        <v>94310000000</v>
       </c>
     </row>
     <row r="112">
@@ -2166,37 +2166,37 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>93590000000</v>
+        <v>93200000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>93540000000</v>
+        <v>92080000000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>MercadoLibre Inc</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>93380000000</v>
+        <v>91960000000</v>
       </c>
     </row>
     <row r="115">
@@ -2211,7 +2211,7 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>89080000000</v>
+        <v>87980000000</v>
       </c>
     </row>
     <row r="116">
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>88490000000</v>
+        <v>87860000000</v>
       </c>
     </row>
     <row r="117">
@@ -2241,37 +2241,37 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>87760000000</v>
+        <v>87770000000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>HCA Healthcare Inc</t>
+          <t>3M Co</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>85570000000</v>
+        <v>83370000000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>3M Co</t>
+          <t>HCA Healthcare Inc</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>84370000000</v>
+        <v>82340000000</v>
       </c>
     </row>
     <row r="120">
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>80970000000</v>
+        <v>80920000000</v>
       </c>
     </row>
     <row r="121">
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>80640000000</v>
+        <v>79620000000</v>
       </c>
     </row>
     <row r="122">
@@ -2316,7 +2316,7 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>80170000000</v>
+        <v>78970000000</v>
       </c>
     </row>
     <row r="123">
@@ -2331,37 +2331,37 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>78840000000</v>
+        <v>76960000000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive Co</t>
+          <t>Cigna Group</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>75270000000</v>
+        <v>74450000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Cigna Group</t>
+          <t>Colgate-Palmolive Co</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>75080000000</v>
+        <v>74400000000</v>
       </c>
     </row>
     <row r="126">
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>73670000000</v>
+        <v>74080000000</v>
       </c>
     </row>
     <row r="127">
@@ -2391,37 +2391,37 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>71180000000</v>
+        <v>70940000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Apollo Global Management Inc</t>
+          <t>SLB Ltd</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>71110000000</v>
+        <v>70250000000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SLB Ltd</t>
+          <t>Apollo Global Management Inc</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>70390000000</v>
+        <v>69450000000</v>
       </c>
     </row>
     <row r="130">
@@ -2436,7 +2436,7 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>70080000000</v>
+        <v>68590000000</v>
       </c>
     </row>
     <row r="131">
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>67530000000</v>
+        <v>66510000000</v>
       </c>
     </row>
     <row r="132">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>66610000000</v>
+        <v>65650000000</v>
       </c>
     </row>
     <row r="133">
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>66000000000</v>
+        <v>64900000000</v>
       </c>
     </row>
     <row r="134">
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>63680000000</v>
+        <v>63410000000</v>
       </c>
     </row>
     <row r="135">
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>60220000000</v>
+        <v>58990000000</v>
       </c>
     </row>
     <row r="136">
@@ -2526,82 +2526,82 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>56540000000</v>
+        <v>56700000000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Astera Labs Inc</t>
+          <t>Occidental Petroleum Corp</t>
         </is>
       </c>
       <c r="L137" t="n">
-        <v>54810000000</v>
+        <v>54570000000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Occidental Petroleum Corp</t>
+          <t>Vistra Corp</t>
         </is>
       </c>
       <c r="L138" t="n">
-        <v>53360000000</v>
+        <v>52410000000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Vistra Corp</t>
+          <t>Astera Labs Inc</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>51440000000</v>
+        <v>52040000000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences Corp</t>
+          <t>PayPal Holdings Inc</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>50580000000</v>
+        <v>49890000000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>PayPal Holdings Inc</t>
+          <t>Edwards Lifesciences Corp</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>50040000000</v>
+        <v>49360000000</v>
       </c>
     </row>
     <row r="142">
@@ -2616,67 +2616,67 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>48520000000</v>
+        <v>47580000000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MSCI Inc</t>
+          <t>Autodesk Inc</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>46390000000</v>
+        <v>46070000000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Autodesk Inc</t>
+          <t>MSCI Inc</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>45800000000</v>
+        <v>45770000000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>43870000000</v>
+        <v>44720000000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>43230000000</v>
+        <v>44180000000</v>
       </c>
     </row>
     <row r="147">
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>42280000000</v>
+        <v>41390000000</v>
       </c>
     </row>
     <row r="148">
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>40290000000</v>
+        <v>40450000000</v>
       </c>
     </row>
     <row r="149">
@@ -2721,7 +2721,7 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>39780000000</v>
+        <v>39940000000</v>
       </c>
     </row>
     <row r="150">
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>36790000000</v>
+        <v>36170000000</v>
       </c>
     </row>
     <row r="151">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>36010000000</v>
+        <v>35930000000</v>
       </c>
     </row>
     <row r="152">
@@ -2766,7 +2766,7 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>35920000000</v>
+        <v>35760000000</v>
       </c>
     </row>
     <row r="153">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>35660000000</v>
+        <v>34880000000</v>
       </c>
     </row>
     <row r="154">
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>32950000000</v>
+        <v>33240000000</v>
       </c>
     </row>
     <row r="155">
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>32240000000</v>
+        <v>32100000000</v>
       </c>
     </row>
     <row r="156">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>31370000000</v>
+        <v>31380000000</v>
       </c>
     </row>
     <row r="157">
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>29970000000</v>
+        <v>29710000000</v>
       </c>
     </row>
     <row r="158">
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>28780000000</v>
+        <v>28240000000</v>
       </c>
     </row>
     <row r="159">
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>27580000000</v>
+        <v>27000000000</v>
       </c>
     </row>
     <row r="160">
@@ -2886,7 +2886,7 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>27250000000</v>
+        <v>26720000000</v>
       </c>
     </row>
     <row r="161">
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>26740000000</v>
+        <v>25480000000</v>
       </c>
     </row>
     <row r="162">
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>25060000000</v>
+        <v>24530000000</v>
       </c>
     </row>
     <row r="163">
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>23680000000</v>
+        <v>24250000000</v>
       </c>
     </row>
     <row r="164">
@@ -2946,37 +2946,37 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>22770000000</v>
+        <v>22780000000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>DKNG</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>SoFi Technologies Inc</t>
+          <t>DraftKings Inc</t>
         </is>
       </c>
       <c r="L165" t="n">
-        <v>22220000000</v>
+        <v>22180000000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>DKNG</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>DraftKings Inc</t>
+          <t>SoFi Technologies Inc</t>
         </is>
       </c>
       <c r="L166" t="n">
-        <v>22090000000</v>
+        <v>22170000000</v>
       </c>
     </row>
     <row r="167">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>21330000000</v>
+        <v>21430000000</v>
       </c>
     </row>
     <row r="168">
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>18470000000</v>
+        <v>18190000000</v>
       </c>
     </row>
     <row r="169">
@@ -3021,22 +3021,22 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>15960000000</v>
+        <v>15640000000</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>GRAB</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Grab Holdings Limited</t>
+          <t>Circle Internet Group Inc</t>
         </is>
       </c>
       <c r="L170" t="n">
-        <v>15290000000</v>
+        <v>15030000000</v>
       </c>
     </row>
     <row r="171">
@@ -3051,48 +3051,48 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>15290000000</v>
+        <v>14630000000</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>CRCL</t>
+          <t>GRAB</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Circle Internet Group Inc</t>
+          <t>Grab Holdings Limited</t>
         </is>
       </c>
       <c r="L172" t="n">
-        <v>15070000000</v>
+        <v>14630000000</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>PINS</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>IonQ Inc</t>
+          <t>Pinterest Inc</t>
         </is>
       </c>
       <c r="L173" t="n">
-        <v>13100000000</v>
+        <v>13000000000</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>TXRH</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Texas Roadhouse Inc</t>
+          <t>IonQ Inc</t>
         </is>
       </c>
       <c r="L174" t="n">
@@ -3102,16 +3102,16 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>PINS</t>
+          <t>TXRH</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Pinterest Inc</t>
+          <t>Texas Roadhouse Inc</t>
         </is>
       </c>
       <c r="L175" t="n">
-        <v>12930000000</v>
+        <v>12950000000</v>
       </c>
     </row>
     <row r="176">
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>12430000000</v>
+        <v>12000000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>10770000000</v>
+        <v>11260000000</v>
       </c>
     </row>
     <row r="178">
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>9210000000</v>
+        <v>9010000000</v>
       </c>
     </row>
     <row r="179">
@@ -3171,22 +3171,22 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>8700000000</v>
+        <v>8770000000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>HIMS</t>
+          <t>MBLY</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Hims &amp; Hers Health Inc</t>
+          <t>Mobileye Global Inc</t>
         </is>
       </c>
       <c r="L180" t="n">
-        <v>7800000000</v>
+        <v>7760000000</v>
       </c>
     </row>
     <row r="181">
@@ -3201,67 +3201,67 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>7790000000</v>
+        <v>7750000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>HIMS</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Celsius Holdings Inc</t>
+          <t>Hims &amp; Hers Health Inc</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>7660000000</v>
+        <v>7600000000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Applied Digital Corp</t>
+          <t>Celsius Holdings Inc</t>
         </is>
       </c>
       <c r="L183" t="n">
-        <v>7560000000</v>
+        <v>7410000000</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>AeroVironment Inc</t>
+          <t>Applied Digital Corp</t>
         </is>
       </c>
       <c r="L184" t="n">
-        <v>7560000000</v>
+        <v>7370000000</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>MBLY</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Mobileye Global Inc</t>
+          <t>AeroVironment Inc</t>
         </is>
       </c>
       <c r="L185" t="n">
-        <v>7550000000</v>
+        <v>7200000000</v>
       </c>
     </row>
     <row r="186">
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>7260000000</v>
+        <v>7150000000</v>
       </c>
     </row>
     <row r="187">
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>6730000000</v>
+        <v>6710000000</v>
       </c>
     </row>
     <row r="188">
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>4960000000</v>
+        <v>5160000000</v>
       </c>
     </row>
     <row r="189">
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>4680000000</v>
+        <v>4610000000</v>
       </c>
     </row>
     <row r="191">
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>4350000000</v>
+        <v>4080000000</v>
       </c>
     </row>
     <row r="192">
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>3520000000</v>
+        <v>3460000000</v>
       </c>
     </row>
     <row r="193">
@@ -3381,67 +3381,67 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3180000000</v>
+        <v>3240000000</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>LEU</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Upstart Holdings Inc</t>
+          <t>Centrus Energy Corp</t>
         </is>
       </c>
       <c r="L194" t="n">
-        <v>2960000000</v>
+        <v>3070000000</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>LEU</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Centrus Energy Corp</t>
+          <t>NuScale Power Corp</t>
         </is>
       </c>
       <c r="L195" t="n">
-        <v>2890000000</v>
+        <v>2820000000</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>PENN</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>PENN Entertainment Inc</t>
+          <t>Upstart Holdings Inc</t>
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2850000000</v>
+        <v>2820000000</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>PENN</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>NuScale Power Corp</t>
+          <t>PENN Entertainment Inc</t>
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2790000000</v>
+        <v>2750000000</v>
       </c>
     </row>
     <row r="198">
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2660000000</v>
+        <v>2590000000</v>
       </c>
     </row>
     <row r="199">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>2630000000</v>
+        <v>2560000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1720000000</v>
+        <v>1760000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1710000000</v>
+        <v>1700000000</v>
       </c>
     </row>
     <row r="202">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1390000000</v>
+        <v>1370000000</v>
       </c>
     </row>
     <row r="203">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>843750000</v>
+        <v>834900000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>795290000</v>
+        <v>809150000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>496690000</v>
+        <v>487880000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4218030000000</v>
+        <v>4218130000000</v>
       </c>
     </row>
     <row r="8">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1058230000000</v>
+        <v>1058640000000</v>
       </c>
     </row>
     <row r="16">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>363950000000</v>
+        <v>361930000000</v>
       </c>
     </row>
     <row r="36">
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>3460000000</v>
+        <v>3720000000</v>
       </c>
     </row>
     <row r="193">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4901760000000</v>
+        <v>4796740000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4908000000000</v>
+        <v>4919380000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4218130000000</v>
+        <v>4282110000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2925470000000</v>
+        <v>2988390000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2659480000000</v>
+        <v>2689170000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2066140000000</v>
+        <v>2086520000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1764230000000</v>
+        <v>1799130000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1639850000000</v>
+        <v>1639440000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1430330000000</v>
+        <v>1388000000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1110420000000</v>
+        <v>1080080000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1058640000000</v>
+        <v>1059370000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>958800000000</v>
+        <v>977440000000</v>
       </c>
     </row>
     <row r="17">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>913980000000</v>
+        <v>908010000000</v>
       </c>
     </row>
     <row r="18">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>909130000000</v>
+        <v>892900000000</v>
       </c>
     </row>
     <row r="19">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>808390000000</v>
+        <v>821120000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>675570000000</v>
+        <v>679360000000</v>
       </c>
     </row>
     <row r="21">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>673550000000</v>
+        <v>670250000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>610730000000</v>
+        <v>614870000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>609120000000</v>
+        <v>598960000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>480320000000</v>
+        <v>483710000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>449630000000</v>
+        <v>447670000000</v>
       </c>
     </row>
     <row r="26">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>441200000000</v>
+        <v>436320000000</v>
       </c>
     </row>
     <row r="27">
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>434810000000</v>
+        <v>428780000000</v>
       </c>
     </row>
     <row r="28">
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>420530000000</v>
+        <v>417380000000</v>
       </c>
     </row>
     <row r="29">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>417260000000</v>
+        <v>415010000000</v>
       </c>
     </row>
     <row r="30">
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>405490000000</v>
+        <v>398130000000</v>
       </c>
     </row>
     <row r="31">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>391800000000</v>
+        <v>383630000000</v>
       </c>
     </row>
     <row r="32">
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>386950000000</v>
+        <v>382830000000</v>
       </c>
     </row>
     <row r="33">
@@ -981,52 +981,52 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>373190000000</v>
+        <v>377830000000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Oracle Corp</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>364120000000</v>
+        <v>354120000000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Coca-Cola Co</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>361930000000</v>
+        <v>353320000000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Coca-Cola Co</t>
+          <t>Oracle Corp</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>350910000000</v>
+        <v>349630000000</v>
       </c>
     </row>
     <row r="37">
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>349240000000</v>
+        <v>347260000000</v>
       </c>
     </row>
     <row r="38">
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>339900000000</v>
+        <v>332710000000</v>
       </c>
     </row>
     <row r="39">
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>337890000000</v>
+        <v>332080000000</v>
       </c>
     </row>
     <row r="40">
@@ -1086,37 +1086,37 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>317360000000</v>
+        <v>323280000000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Merck &amp; Co Inc</t>
+          <t>Goldman Sachs Group Inc</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>314900000000</v>
+        <v>311240000000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Goldman Sachs Group Inc</t>
+          <t>Merck &amp; Co Inc</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>314250000000</v>
+        <v>307250000000</v>
       </c>
     </row>
     <row r="43">
@@ -1131,37 +1131,37 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>300770000000</v>
+        <v>300370000000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>292320000000</v>
+        <v>290000000000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Netflix Inc</t>
+          <t>Alibaba Group Holding Ltd ADR</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>290330000000</v>
+        <v>288460000000</v>
       </c>
     </row>
     <row r="46">
@@ -1176,67 +1176,67 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>284290000000</v>
+        <v>286870000000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>Netflix Inc</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>284260000000</v>
+        <v>284650000000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>NVS</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Novartis AG ADR</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>281470000000</v>
+        <v>284160000000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>NVS</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>KLA Corp</t>
+          <t>Novartis AG ADR</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>277910000000</v>
+        <v>273780000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Alibaba Group Holding Ltd ADR</t>
+          <t>KLA Corp</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>275590000000</v>
+        <v>271180000000</v>
       </c>
     </row>
     <row r="51">
@@ -1251,52 +1251,52 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>267800000000</v>
+        <v>264190000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Astrazeneca plc</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>261940000000</v>
+        <v>261850000000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>260600000000</v>
+        <v>258530000000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>Astrazeneca plc</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>258480000000</v>
+        <v>255150000000</v>
       </c>
     </row>
     <row r="55">
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>256940000000</v>
+        <v>247570000000</v>
       </c>
     </row>
     <row r="56">
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>243460000000</v>
+        <v>240330000000</v>
       </c>
     </row>
     <row r="57">
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>242460000000</v>
+        <v>240130000000</v>
       </c>
     </row>
     <row r="58">
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>237420000000</v>
+        <v>236870000000</v>
       </c>
     </row>
     <row r="59">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>221840000000</v>
+        <v>220740000000</v>
       </c>
     </row>
     <row r="60">
@@ -1386,37 +1386,37 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>208250000000</v>
+        <v>211720000000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>206790000000</v>
+        <v>205990000000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>200630000000</v>
+        <v>202110000000</v>
       </c>
     </row>
     <row r="63">
@@ -1431,37 +1431,37 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>199890000000</v>
+        <v>200200000000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc</t>
+          <t>AMGEN Inc</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>197880000000</v>
+        <v>196550000000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>AMGEN Inc</t>
+          <t>Thermo Fisher Scientific Inc</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>197690000000</v>
+        <v>195560000000</v>
       </c>
     </row>
     <row r="66">
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>190210000000</v>
+        <v>190160000000</v>
       </c>
     </row>
     <row r="67">
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>188990000000</v>
+        <v>189960000000</v>
       </c>
     </row>
     <row r="68">
@@ -1506,7 +1506,7 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>187150000000</v>
+        <v>184890000000</v>
       </c>
     </row>
     <row r="69">
@@ -1521,7 +1521,7 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>185690000000</v>
+        <v>184880000000</v>
       </c>
     </row>
     <row r="70">
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>185200000000</v>
+        <v>183530000000</v>
       </c>
     </row>
     <row r="71">
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>182010000000</v>
+        <v>181640000000</v>
       </c>
     </row>
     <row r="72">
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>181240000000</v>
+        <v>179920000000</v>
       </c>
     </row>
     <row r="73">
@@ -1581,7 +1581,7 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>181060000000</v>
+        <v>179520000000</v>
       </c>
     </row>
     <row r="74">
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>176630000000</v>
+        <v>178330000000</v>
       </c>
     </row>
     <row r="75">
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>175370000000</v>
+        <v>177070000000</v>
       </c>
     </row>
     <row r="76">
@@ -1626,52 +1626,52 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>174340000000</v>
+        <v>171400000000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Walt Disney Co</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>169610000000</v>
+        <v>168000000000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Novo Nordisk ADR</t>
+          <t>Walt Disney Co</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>168970000000</v>
+        <v>167420000000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Boeing Co</t>
+          <t>Novo Nordisk ADR</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>168720000000</v>
+        <v>166590000000</v>
       </c>
     </row>
     <row r="80">
@@ -1686,82 +1686,82 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>166720000000</v>
+        <v>165390000000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>Boeing Co</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>164490000000</v>
+        <v>165130000000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Deere &amp; Co</t>
+          <t>Shopify Inc</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>161220000000</v>
+        <v>161530000000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Shopify Inc</t>
+          <t>Deere &amp; Co</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>160340000000</v>
+        <v>158180000000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Blackstone Inc</t>
+          <t>AT&amp;T Inc</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>155020000000</v>
+        <v>152520000000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc</t>
+          <t>Blackstone Inc</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>151540000000</v>
+        <v>150990000000</v>
       </c>
     </row>
     <row r="86">
@@ -1776,82 +1776,82 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>147500000000</v>
+        <v>146910000000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Danaher Corp</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>144260000000</v>
+        <v>142640000000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>Danaher Corp</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>142620000000</v>
+        <v>142340000000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Salesforce Inc</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>142600000000</v>
+        <v>142330000000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>140780000000</v>
+        <v>140410000000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Salesforce Inc</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>139860000000</v>
+        <v>139050000000</v>
       </c>
     </row>
     <row r="92">
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>136590000000</v>
+        <v>136730000000</v>
       </c>
     </row>
     <row r="93">
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>133450000000</v>
+        <v>132710000000</v>
       </c>
     </row>
     <row r="94">
@@ -1896,22 +1896,22 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>133060000000</v>
+        <v>131760000000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Co</t>
+          <t>Intuitive Surgical Inc</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>124040000000</v>
+        <v>125080000000</v>
       </c>
     </row>
     <row r="96">
@@ -1926,67 +1926,67 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>123920000000</v>
+        <v>124670000000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Intuitive Surgical Inc</t>
+          <t>Progressive Corp</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>122330000000</v>
+        <v>124010000000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Progressive Corp</t>
+          <t>Bristol-Myers Squibb Co</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>121510000000</v>
+        <v>122850000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Starbucks Corp</t>
+          <t>PDD Holdings Inc ADR</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>120230000000</v>
+        <v>122480000000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PDD Holdings Inc ADR</t>
+          <t>Starbucks Corp</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>119760000000</v>
+        <v>119450000000</v>
       </c>
     </row>
     <row r="101">
@@ -2001,7 +2001,7 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>117300000000</v>
+        <v>117480000000</v>
       </c>
     </row>
     <row r="102">
@@ -2016,7 +2016,7 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>117040000000</v>
+        <v>114780000000</v>
       </c>
     </row>
     <row r="103">
@@ -2031,7 +2031,7 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>111220000000</v>
+        <v>112030000000</v>
       </c>
     </row>
     <row r="104">
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>106500000000</v>
+        <v>106610000000</v>
       </c>
     </row>
     <row r="105">
@@ -2061,127 +2061,127 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>102040000000</v>
+        <v>102030000000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Equinix Inc</t>
+          <t>Spotify Technology SA</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>100600000000</v>
+        <v>101230000000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>United Parcel Service Inc</t>
+          <t>Equinix Inc</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>100060000000</v>
+        <v>100330000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>98600000000</v>
+        <v>98360000000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>98360000000</v>
+        <v>96740000000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Spotify Technology SA</t>
+          <t>United Parcel Service Inc</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>98320000000</v>
+        <v>96180000000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>Snowflake Inc</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>94310000000</v>
+        <v>95090000000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Snowflake Inc</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>93200000000</v>
+        <v>93690000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>92080000000</v>
+        <v>93310000000</v>
       </c>
     </row>
     <row r="114">
@@ -2196,52 +2196,52 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>91960000000</v>
+        <v>92900000000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Airbnb Inc</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>87980000000</v>
+        <v>88570000000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>MMC</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>Marsh</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>87860000000</v>
+        <v>87730000000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>MMC</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Marsh</t>
+          <t>Airbnb Inc</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>87770000000</v>
+        <v>87360000000</v>
       </c>
     </row>
     <row r="118">
@@ -2256,37 +2256,37 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>83370000000</v>
+        <v>82990000000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>HCA Healthcare Inc</t>
+          <t>Elevance Health Inc</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>82340000000</v>
+        <v>82890000000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Elevance Health Inc</t>
+          <t>HCA Healthcare Inc</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>80920000000</v>
+        <v>82170000000</v>
       </c>
     </row>
     <row r="121">
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>79620000000</v>
+        <v>80370000000</v>
       </c>
     </row>
     <row r="122">
@@ -2316,7 +2316,7 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>78970000000</v>
+        <v>80060000000</v>
       </c>
     </row>
     <row r="123">
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>76960000000</v>
+        <v>76750000000</v>
       </c>
     </row>
     <row r="124">
@@ -2346,37 +2346,37 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>74450000000</v>
+        <v>75110000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive Co</t>
+          <t>Northrop Grumman Corp</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>74400000000</v>
+        <v>74420000000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp</t>
+          <t>Colgate-Palmolive Co</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>74080000000</v>
+        <v>73560000000</v>
       </c>
     </row>
     <row r="127">
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>70940000000</v>
+        <v>70470000000</v>
       </c>
     </row>
     <row r="128">
@@ -2406,67 +2406,67 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>70250000000</v>
+        <v>69360000000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Apollo Global Management Inc</t>
+          <t>General Motors Company</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>69450000000</v>
+        <v>68350000000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>General Motors Company</t>
+          <t>Apollo Global Management Inc</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>68590000000</v>
+        <v>68170000000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Ferrari NV</t>
+          <t>Nu Holdings Ltd</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>66510000000</v>
+        <v>67580000000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>NU</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Nu Holdings Ltd</t>
+          <t>Ferrari NV</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>65650000000</v>
+        <v>65580000000</v>
       </c>
     </row>
     <row r="133">
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>64900000000</v>
+        <v>64470000000</v>
       </c>
     </row>
     <row r="134">
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>63410000000</v>
+        <v>63400000000</v>
       </c>
     </row>
     <row r="135">
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>58990000000</v>
+        <v>59920000000</v>
       </c>
     </row>
     <row r="136">
@@ -2526,7 +2526,7 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>56700000000</v>
+        <v>55750000000</v>
       </c>
     </row>
     <row r="137">
@@ -2541,7 +2541,7 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>54570000000</v>
+        <v>54890000000</v>
       </c>
     </row>
     <row r="138">
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>52410000000</v>
+        <v>53270000000</v>
       </c>
     </row>
     <row r="139">
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>52040000000</v>
+        <v>52980000000</v>
       </c>
     </row>
     <row r="140">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>49890000000</v>
+        <v>50120000000</v>
       </c>
     </row>
     <row r="141">
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>49360000000</v>
+        <v>48940000000</v>
       </c>
     </row>
     <row r="142">
@@ -2616,7 +2616,7 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>47580000000</v>
+        <v>47190000000</v>
       </c>
     </row>
     <row r="143">
@@ -2631,37 +2631,37 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>46070000000</v>
+        <v>45960000000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MSCI Inc</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>45770000000</v>
+        <v>45960000000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>MSCI Inc</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>44720000000</v>
+        <v>45510000000</v>
       </c>
     </row>
     <row r="146">
@@ -2676,7 +2676,7 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>44180000000</v>
+        <v>42500000000</v>
       </c>
     </row>
     <row r="147">
@@ -2691,82 +2691,82 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>41390000000</v>
+        <v>42270000000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Rocket Lab Corp</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>40450000000</v>
+        <v>39860000000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Rocket Lab Corp</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>39940000000</v>
+        <v>39320000000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Carnival Corp Ltd</t>
+          <t>JD.com Inc ADR</t>
         </is>
       </c>
       <c r="L150" t="n">
-        <v>36170000000</v>
+        <v>37120000000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>JD</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>JD.com Inc ADR</t>
+          <t>Workday Inc</t>
         </is>
       </c>
       <c r="L151" t="n">
-        <v>35930000000</v>
+        <v>36360000000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Workday Inc</t>
+          <t>Carnival Corp Ltd</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>35760000000</v>
+        <v>35670000000</v>
       </c>
     </row>
     <row r="153">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>34880000000</v>
+        <v>34970000000</v>
       </c>
     </row>
     <row r="154">
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>33240000000</v>
+        <v>34280000000</v>
       </c>
     </row>
     <row r="155">
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>32100000000</v>
+        <v>31950000000</v>
       </c>
     </row>
     <row r="156">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>31380000000</v>
+        <v>31150000000</v>
       </c>
     </row>
     <row r="157">
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>29710000000</v>
+        <v>30260000000</v>
       </c>
     </row>
     <row r="158">
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>28240000000</v>
+        <v>27940000000</v>
       </c>
     </row>
     <row r="159">
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>27000000000</v>
+        <v>27560000000</v>
       </c>
     </row>
     <row r="160">
@@ -2886,7 +2886,7 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>26720000000</v>
+        <v>26660000000</v>
       </c>
     </row>
     <row r="161">
@@ -2901,37 +2901,37 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>25480000000</v>
+        <v>25220000000</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>Zscaler Inc</t>
         </is>
       </c>
       <c r="L162" t="n">
-        <v>24530000000</v>
+        <v>24230000000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Zscaler Inc</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="L163" t="n">
-        <v>24250000000</v>
+        <v>23600000000</v>
       </c>
     </row>
     <row r="164">
@@ -2946,37 +2946,37 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>22780000000</v>
+        <v>22060000000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>DKNG</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>DraftKings Inc</t>
+          <t>SoFi Technologies Inc</t>
         </is>
       </c>
       <c r="L165" t="n">
-        <v>22180000000</v>
+        <v>21820000000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>DKNG</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>SoFi Technologies Inc</t>
+          <t>DraftKings Inc</t>
         </is>
       </c>
       <c r="L166" t="n">
-        <v>22170000000</v>
+        <v>21620000000</v>
       </c>
     </row>
     <row r="167">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>21430000000</v>
+        <v>21380000000</v>
       </c>
     </row>
     <row r="168">
@@ -3006,37 +3006,37 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>18190000000</v>
+        <v>17890000000</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Super Micro Computer Inc</t>
+          <t>Circle Internet Group Inc</t>
         </is>
       </c>
       <c r="L169" t="n">
-        <v>15640000000</v>
+        <v>16270000000</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>CRCL</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Circle Internet Group Inc</t>
+          <t>Super Micro Computer Inc</t>
         </is>
       </c>
       <c r="L170" t="n">
-        <v>15030000000</v>
+        <v>15410000000</v>
       </c>
     </row>
     <row r="171">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>14630000000</v>
+        <v>14840000000</v>
       </c>
     </row>
     <row r="172">
@@ -3066,67 +3066,67 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>14630000000</v>
+        <v>14840000000</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>PINS</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Pinterest Inc</t>
+          <t>IREN Ltd</t>
         </is>
       </c>
       <c r="L173" t="n">
-        <v>13000000000</v>
+        <v>14350000000</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>TXRH</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>IonQ Inc</t>
+          <t>Texas Roadhouse Inc</t>
         </is>
       </c>
       <c r="L174" t="n">
-        <v>12980000000</v>
+        <v>12900000000</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>TXRH</t>
+          <t>PINS</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Texas Roadhouse Inc</t>
+          <t>Pinterest Inc</t>
         </is>
       </c>
       <c r="L175" t="n">
-        <v>12950000000</v>
+        <v>12780000000</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>IREN Ltd</t>
+          <t>IonQ Inc</t>
         </is>
       </c>
       <c r="L176" t="n">
-        <v>12000000000</v>
+        <v>12780000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,142 +3141,142 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>11260000000</v>
+        <v>10920000000</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>PRMB</t>
+          <t>OSCR</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Primo Brands Corp</t>
+          <t>Oscar Health Inc</t>
         </is>
       </c>
       <c r="L178" t="n">
-        <v>9010000000</v>
+        <v>8920000000</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>OSCR</t>
+          <t>PRMB</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Oscar Health Inc</t>
+          <t>Primo Brands Corp</t>
         </is>
       </c>
       <c r="L179" t="n">
-        <v>8770000000</v>
+        <v>8820000000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>MBLY</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Mobileye Global Inc</t>
+          <t>Applied Digital Corp</t>
         </is>
       </c>
       <c r="L180" t="n">
-        <v>7760000000</v>
+        <v>7960000000</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>HIMS</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Zillow Group Inc</t>
+          <t>Hims &amp; Hers Health Inc</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>7750000000</v>
+        <v>7570000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>HIMS</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Hims &amp; Hers Health Inc</t>
+          <t>Zillow Group Inc</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>7600000000</v>
+        <v>7550000000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>MBLY</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Celsius Holdings Inc</t>
+          <t>Mobileye Global Inc</t>
         </is>
       </c>
       <c r="L183" t="n">
-        <v>7410000000</v>
+        <v>7540000000</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Applied Digital Corp</t>
+          <t>Celsius Holdings Inc</t>
         </is>
       </c>
       <c r="L184" t="n">
-        <v>7370000000</v>
+        <v>7520000000</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>OKLO</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>AeroVironment Inc</t>
+          <t>Oklo Inc</t>
         </is>
       </c>
       <c r="L185" t="n">
-        <v>7200000000</v>
+        <v>7220000000</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>OKLO</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Oklo Inc</t>
+          <t>AeroVironment Inc</t>
         </is>
       </c>
       <c r="L186" t="n">
-        <v>7150000000</v>
+        <v>7220000000</v>
       </c>
     </row>
     <row r="187">
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>6710000000</v>
+        <v>6670000000</v>
       </c>
     </row>
     <row r="188">
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>5160000000</v>
+        <v>5180000000</v>
       </c>
     </row>
     <row r="189">
@@ -3321,7 +3321,7 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>4690000000</v>
+        <v>4740000000</v>
       </c>
     </row>
     <row r="190">
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>4610000000</v>
+        <v>4530000000</v>
       </c>
     </row>
     <row r="191">
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>4080000000</v>
+        <v>4450000000</v>
       </c>
     </row>
     <row r="192">
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>3720000000</v>
+        <v>3910000000</v>
       </c>
     </row>
     <row r="193">
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3240000000</v>
+        <v>3200000000</v>
       </c>
     </row>
     <row r="194">
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3070000000</v>
+        <v>3080000000</v>
       </c>
     </row>
     <row r="195">
@@ -3411,37 +3411,37 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>2820000000</v>
+        <v>2910000000</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>PENN</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Upstart Holdings Inc</t>
+          <t>PENN Entertainment Inc</t>
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2820000000</v>
+        <v>2840000000</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>PENN</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>PENN Entertainment Inc</t>
+          <t>Upstart Holdings Inc</t>
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2750000000</v>
+        <v>2760000000</v>
       </c>
     </row>
     <row r="198">
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2590000000</v>
+        <v>2630000000</v>
       </c>
     </row>
     <row r="199">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>2560000000</v>
+        <v>2540000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1760000000</v>
+        <v>1790000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1700000000</v>
+        <v>1740000000</v>
       </c>
     </row>
     <row r="202">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1370000000</v>
+        <v>1340000000</v>
       </c>
     </row>
     <row r="203">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>834900000</v>
+        <v>854690000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>809150000</v>
+        <v>830660000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>487880000</v>
+        <v>489770000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4796740000000</v>
+        <v>4813630000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4919380000000</v>
+        <v>5016420000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4282110000000</v>
+        <v>4218720000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2988390000000</v>
+        <v>2954660000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2689170000000</v>
+        <v>2662920000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2086520000000</v>
+        <v>2202230000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1799130000000</v>
+        <v>1838800000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1639440000000</v>
+        <v>1634260000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1388000000000</v>
+        <v>1423160000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,37 +696,37 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1080080000000</v>
+        <v>1106930000000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BRK-B</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Inc</t>
+          <t>Micron Technology Inc</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1059370000000</v>
+        <v>1096440000000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>BRK-B</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Micron Technology Inc</t>
+          <t>Berkshire Hathaway Inc</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>977440000000</v>
+        <v>1055760000000</v>
       </c>
     </row>
     <row r="17">
@@ -741,67 +741,67 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>908010000000</v>
+        <v>925050000000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Walmart Inc</t>
+          <t>Advanced Micro Devices Inc</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>892900000000</v>
+        <v>887750000000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices Inc</t>
+          <t>Walmart Inc</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>821120000000</v>
+        <v>878490000000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Visa Inc</t>
+          <t>ASML Holding NV</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>679360000000</v>
+        <v>694340000000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ASML Holding NV</t>
+          <t>Visa Inc</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>670250000000</v>
+        <v>670410000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>614870000000</v>
+        <v>628760000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>598960000000</v>
+        <v>603270000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>483710000000</v>
+        <v>475630000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,52 +861,52 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>447670000000</v>
+        <v>452480000000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cisco Systems Inc</t>
+          <t>Applied Materials Inc</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>436320000000</v>
+        <v>448230000000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Bank Of America Corp</t>
+          <t>Cisco Systems Inc</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>428780000000</v>
+        <v>442150000000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Applied Materials Inc</t>
+          <t>Bank Of America Corp</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>417380000000</v>
+        <v>434450000000</v>
       </c>
     </row>
     <row r="29">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>415010000000</v>
+        <v>412090000000</v>
       </c>
     </row>
     <row r="30">
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>398130000000</v>
+        <v>409950000000</v>
       </c>
     </row>
     <row r="31">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>383630000000</v>
+        <v>402680000000</v>
       </c>
     </row>
     <row r="32">
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>382830000000</v>
+        <v>396270000000</v>
       </c>
     </row>
     <row r="33">
@@ -981,52 +981,52 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>377830000000</v>
+        <v>380530000000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Oracle Corp</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>354120000000</v>
+        <v>365960000000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Coca-Cola Co</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>353320000000</v>
+        <v>353500000000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Oracle Corp</t>
+          <t>Coca-Cola Co</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>349630000000</v>
+        <v>352670000000</v>
       </c>
     </row>
     <row r="37">
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>347260000000</v>
+        <v>344870000000</v>
       </c>
     </row>
     <row r="38">
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>332710000000</v>
+        <v>341320000000</v>
       </c>
     </row>
     <row r="39">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>332080000000</v>
+        <v>330640000000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc</t>
+          <t>Goldman Sachs Group Inc</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>323280000000</v>
+        <v>320250000000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Goldman Sachs Group Inc</t>
+          <t>Palantir Technologies Inc</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>311240000000</v>
+        <v>318030000000</v>
       </c>
     </row>
     <row r="42">
@@ -1116,97 +1116,97 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>307250000000</v>
+        <v>311840000000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Philip Morris International Inc</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>300370000000</v>
+        <v>308270000000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>Philip Morris International Inc</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>290000000000</v>
+        <v>293070000000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Alibaba Group Holding Ltd ADR</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>288460000000</v>
+        <v>289900000000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>Netflix Inc</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>286870000000</v>
+        <v>285940000000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Netflix Inc</t>
+          <t>KLA Corp</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>284650000000</v>
+        <v>284190000000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>Alibaba Group Holding Ltd ADR</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>284160000000</v>
+        <v>282780000000</v>
       </c>
     </row>
     <row r="49">
@@ -1221,22 +1221,22 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>273780000000</v>
+        <v>281670000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>KLA Corp</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>271180000000</v>
+        <v>278850000000</v>
       </c>
     </row>
     <row r="51">
@@ -1251,67 +1251,67 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>264190000000</v>
+        <v>268500000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>261850000000</v>
+        <v>265110000000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>Astrazeneca plc</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>258530000000</v>
+        <v>262620000000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Astrazeneca plc</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>255150000000</v>
+        <v>262000000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>247570000000</v>
+        <v>260810000000</v>
       </c>
     </row>
     <row r="56">
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>240330000000</v>
+        <v>243120000000</v>
       </c>
     </row>
     <row r="57">
@@ -1341,112 +1341,112 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>240130000000</v>
+        <v>239350000000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Linde Plc</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>236870000000</v>
+        <v>235370000000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Citigroup Inc</t>
+          <t>Linde Plc</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>220740000000</v>
+        <v>233630000000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>T-Mobile US Inc</t>
+          <t>Citigroup Inc</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>211720000000</v>
+        <v>227810000000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>T-Mobile US Inc</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>205990000000</v>
+        <v>206450000000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>International Business Machines Corp</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>202110000000</v>
+        <v>197850000000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>International Business Machines Corp</t>
+          <t>AMGEN Inc</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>200200000000</v>
+        <v>197660000000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AMGEN Inc</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>196550000000</v>
+        <v>194640000000</v>
       </c>
     </row>
     <row r="65">
@@ -1461,187 +1461,187 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>195560000000</v>
+        <v>194530000000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>McDonald's Corp</t>
+          <t>Toyota Motor Corp ADR</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>190160000000</v>
+        <v>191890000000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Toyota Motor Corp ADR</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>189960000000</v>
+        <v>189020000000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PepsiCo Inc</t>
+          <t>McDonald's Corp</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>184890000000</v>
+        <v>187510000000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Sap SE ADR</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>184880000000</v>
+        <v>186000000000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NextEra Energy Inc</t>
+          <t>PepsiCo Inc</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>183530000000</v>
+        <v>184260000000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc</t>
+          <t>NextEra Energy Inc</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>181640000000</v>
+        <v>183390000000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>179920000000</v>
+        <v>182870000000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>Verizon Communications Inc</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>179520000000</v>
+        <v>182810000000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Charles Schwab Corp</t>
+          <t>Sap SE ADR</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>178330000000</v>
+        <v>180200000000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Charles Schwab Corp</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>177070000000</v>
+        <v>173840000000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Blackrock Inc</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>171400000000</v>
+        <v>173610000000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>Blackrock Inc</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>168000000000</v>
+        <v>168820000000</v>
       </c>
     </row>
     <row r="78">
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>167420000000</v>
+        <v>166950000000</v>
       </c>
     </row>
     <row r="79">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>166590000000</v>
+        <v>165820000000</v>
       </c>
     </row>
     <row r="80">
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>165390000000</v>
+        <v>161750000000</v>
       </c>
     </row>
     <row r="81">
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>165130000000</v>
+        <v>161440000000</v>
       </c>
     </row>
     <row r="82">
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>161530000000</v>
+        <v>159650000000</v>
       </c>
     </row>
     <row r="83">
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>158180000000</v>
+        <v>158420000000</v>
       </c>
     </row>
     <row r="84">
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>152520000000</v>
+        <v>154670000000</v>
       </c>
     </row>
     <row r="85">
@@ -1761,7 +1761,7 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>150990000000</v>
+        <v>151650000000</v>
       </c>
     </row>
     <row r="86">
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>146910000000</v>
+        <v>145650000000</v>
       </c>
     </row>
     <row r="87">
@@ -1791,52 +1791,52 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>142640000000</v>
+        <v>144010000000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Danaher Corp</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>142340000000</v>
+        <v>142750000000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Salesforce Inc</t>
+          <t>Corning Inc</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>142330000000</v>
+        <v>139780000000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Salesforce Inc</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>140410000000</v>
+        <v>139280000000</v>
       </c>
     </row>
     <row r="91">
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>139050000000</v>
+        <v>139010000000</v>
       </c>
     </row>
     <row r="92">
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>136730000000</v>
+        <v>137610000000</v>
       </c>
     </row>
     <row r="93">
@@ -1881,97 +1881,97 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>132710000000</v>
+        <v>127650000000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Corning Inc</t>
+          <t>Danaher Corp</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>131760000000</v>
+        <v>126700000000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Intuitive Surgical Inc</t>
+          <t>Bristol-Myers Squibb Co</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>125080000000</v>
+        <v>124420000000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Altria Group Inc</t>
+          <t>Intuitive Surgical Inc</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>124670000000</v>
+        <v>123980000000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Progressive Corp</t>
+          <t>Altria Group Inc</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>124010000000</v>
+        <v>121890000000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Co</t>
+          <t>PDD Holdings Inc ADR</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>122850000000</v>
+        <v>120750000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PDD Holdings Inc ADR</t>
+          <t>Progressive Corp</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>122480000000</v>
+        <v>120310000000</v>
       </c>
     </row>
     <row r="100">
@@ -1986,52 +1986,52 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>119450000000</v>
+        <v>119040000000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corp</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>117480000000</v>
+        <v>116960000000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Lowe's Cos. Inc</t>
+          <t>Lockheed Martin Corp</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>114780000000</v>
+        <v>116920000000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>Lowe's Cos. Inc</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>112030000000</v>
+        <v>114110000000</v>
       </c>
     </row>
     <row r="104">
@@ -2046,97 +2046,97 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>106610000000</v>
+        <v>105410000000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc</t>
+          <t>Spotify Technology SA</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>102030000000</v>
+        <v>101470000000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Spotify Technology SA</t>
+          <t>Equinix Inc</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>101230000000</v>
+        <v>101370000000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Equinix Inc</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>100330000000</v>
+        <v>99240000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>United Parcel Service Inc</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>98360000000</v>
+        <v>98890000000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>Automatic Data Processing Inc</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>96740000000</v>
+        <v>98420000000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>United Parcel Service Inc</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>96180000000</v>
+        <v>96700000000</v>
       </c>
     </row>
     <row r="111">
@@ -2151,67 +2151,67 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>95090000000</v>
+        <v>94180000000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>MercadoLibre Inc</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>93690000000</v>
+        <v>92400000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>93310000000</v>
+        <v>90700000000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>MercadoLibre Inc</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>92900000000</v>
+        <v>90300000000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>3M Co</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>88570000000</v>
+        <v>89060000000</v>
       </c>
     </row>
     <row r="116">
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>87730000000</v>
+        <v>87490000000</v>
       </c>
     </row>
     <row r="117">
@@ -2241,22 +2241,22 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>87360000000</v>
+        <v>86850000000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>3M Co</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>82990000000</v>
+        <v>86200000000</v>
       </c>
     </row>
     <row r="119">
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>82890000000</v>
+        <v>85330000000</v>
       </c>
     </row>
     <row r="120">
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>82170000000</v>
+        <v>82770000000</v>
       </c>
     </row>
     <row r="121">
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>80370000000</v>
+        <v>79300000000</v>
       </c>
     </row>
     <row r="122">
@@ -2316,7 +2316,7 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>80060000000</v>
+        <v>78420000000</v>
       </c>
     </row>
     <row r="123">
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>76750000000</v>
+        <v>77210000000</v>
       </c>
     </row>
     <row r="124">
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>75110000000</v>
+        <v>76840000000</v>
       </c>
     </row>
     <row r="125">
@@ -2361,7 +2361,7 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>74420000000</v>
+        <v>72760000000</v>
       </c>
     </row>
     <row r="126">
@@ -2376,82 +2376,82 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>73560000000</v>
+        <v>72420000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals Inc</t>
+          <t>General Motors Company</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>70470000000</v>
+        <v>71700000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SLB Ltd</t>
+          <t>Regeneron Pharmaceuticals Inc</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>69360000000</v>
+        <v>70790000000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>General Motors Company</t>
+          <t>SLB Ltd</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>68350000000</v>
+        <v>69650000000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Apollo Global Management Inc</t>
+          <t>Nu Holdings Ltd</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>68170000000</v>
+        <v>69510000000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>NU</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Nu Holdings Ltd</t>
+          <t>Apollo Global Management Inc</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>67580000000</v>
+        <v>68260000000</v>
       </c>
     </row>
     <row r="132">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>65580000000</v>
+        <v>65300000000</v>
       </c>
     </row>
     <row r="133">
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>64470000000</v>
+        <v>63730000000</v>
       </c>
     </row>
     <row r="134">
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>63400000000</v>
+        <v>62900000000</v>
       </c>
     </row>
     <row r="135">
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>59920000000</v>
+        <v>60250000000</v>
       </c>
     </row>
     <row r="136">
@@ -2526,7 +2526,7 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>55750000000</v>
+        <v>56860000000</v>
       </c>
     </row>
     <row r="137">
@@ -2541,187 +2541,187 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>54890000000</v>
+        <v>56200000000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Vistra Corp</t>
+          <t>Astera Labs Inc</t>
         </is>
       </c>
       <c r="L138" t="n">
-        <v>53270000000</v>
+        <v>54810000000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Astera Labs Inc</t>
+          <t>Vistra Corp</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>52980000000</v>
+        <v>54730000000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>PayPal Holdings Inc</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>50120000000</v>
+        <v>54590000000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences Corp</t>
+          <t>PayPal Holdings Inc</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>48940000000</v>
+        <v>49270000000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Block Inc</t>
+          <t>Edwards Lifesciences Corp</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>47190000000</v>
+        <v>48680000000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Autodesk Inc</t>
+          <t>Block Inc</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>45960000000</v>
+        <v>47840000000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Coinbase Global Inc</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>45960000000</v>
+        <v>46330000000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MSCI Inc</t>
+          <t>Autodesk Inc</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>45510000000</v>
+        <v>44550000000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>42500000000</v>
+        <v>43420000000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Coinbase Global Inc</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>42270000000</v>
+        <v>42740000000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Rocket Lab Corp</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>39860000000</v>
+        <v>41350000000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Rocket Lab Corp</t>
+          <t>MSCI Inc</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>39320000000</v>
+        <v>40890000000</v>
       </c>
     </row>
     <row r="150">
@@ -2736,67 +2736,67 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>37120000000</v>
+        <v>36920000000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Workday Inc</t>
+          <t>Carnival Corp Ltd</t>
         </is>
       </c>
       <c r="L151" t="n">
-        <v>36360000000</v>
+        <v>35830000000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>RDDT</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Carnival Corp Ltd</t>
+          <t>Reddit Inc</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>35670000000</v>
+        <v>35780000000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>RDDT</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Reddit Inc</t>
+          <t>Strategy Inc</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>34970000000</v>
+        <v>35730000000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Strategy Inc</t>
+          <t>Workday Inc</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>34280000000</v>
+        <v>34870000000</v>
       </c>
     </row>
     <row r="155">
@@ -2811,37 +2811,37 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>31950000000</v>
+        <v>31590000000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Twilio Inc</t>
+          <t>Estee Lauder Cos. Inc</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>31150000000</v>
+        <v>29800000000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Estee Lauder Cos. Inc</t>
+          <t>Twilio Inc</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>30260000000</v>
+        <v>29780000000</v>
       </c>
     </row>
     <row r="158">
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>27940000000</v>
+        <v>29130000000</v>
       </c>
     </row>
     <row r="159">
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>27560000000</v>
+        <v>26990000000</v>
       </c>
     </row>
     <row r="160">
@@ -2886,7 +2886,7 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>26660000000</v>
+        <v>26320000000</v>
       </c>
     </row>
     <row r="161">
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>25220000000</v>
+        <v>25020000000</v>
       </c>
     </row>
     <row r="162">
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>24230000000</v>
+        <v>24050000000</v>
       </c>
     </row>
     <row r="163">
@@ -2931,67 +2931,67 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>23600000000</v>
+        <v>23670000000</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>First Solar Inc</t>
+          <t>SoFi Technologies Inc</t>
         </is>
       </c>
       <c r="L164" t="n">
-        <v>22060000000</v>
+        <v>22630000000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>SoFi Technologies Inc</t>
+          <t>First Solar Inc</t>
         </is>
       </c>
       <c r="L165" t="n">
-        <v>21820000000</v>
+        <v>22140000000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>DKNG</t>
+          <t>ROKU</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>DraftKings Inc</t>
+          <t>Roku Inc</t>
         </is>
       </c>
       <c r="L166" t="n">
-        <v>21620000000</v>
+        <v>21400000000</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ROKU</t>
+          <t>DKNG</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Roku Inc</t>
+          <t>DraftKings Inc</t>
         </is>
       </c>
       <c r="L167" t="n">
-        <v>21380000000</v>
+        <v>21210000000</v>
       </c>
     </row>
     <row r="168">
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>17890000000</v>
+        <v>17700000000</v>
       </c>
     </row>
     <row r="169">
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>16270000000</v>
+        <v>17670000000</v>
       </c>
     </row>
     <row r="170">
@@ -3036,22 +3036,22 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>15410000000</v>
+        <v>16500000000</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>GRAB</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Grab Holdings Limited</t>
+          <t>IREN Ltd</t>
         </is>
       </c>
       <c r="L171" t="n">
-        <v>14840000000</v>
+        <v>14730000000</v>
       </c>
     </row>
     <row r="172">
@@ -3066,18 +3066,18 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>14840000000</v>
+        <v>14350000000</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>GRAB</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>IREN Ltd</t>
+          <t>Grab Holdings Limited</t>
         </is>
       </c>
       <c r="L173" t="n">
@@ -3087,16 +3087,16 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>TXRH</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Texas Roadhouse Inc</t>
+          <t>IonQ Inc</t>
         </is>
       </c>
       <c r="L174" t="n">
-        <v>12900000000</v>
+        <v>13250000000</v>
       </c>
     </row>
     <row r="175">
@@ -3111,22 +3111,22 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>12780000000</v>
+        <v>12790000000</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>TXRH</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>IonQ Inc</t>
+          <t>Texas Roadhouse Inc</t>
         </is>
       </c>
       <c r="L176" t="n">
-        <v>12780000000</v>
+        <v>12770000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>10920000000</v>
+        <v>10900000000</v>
       </c>
     </row>
     <row r="178">
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>8920000000</v>
+        <v>9280000000</v>
       </c>
     </row>
     <row r="179">
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>8820000000</v>
+        <v>8600000000</v>
       </c>
     </row>
     <row r="180">
@@ -3186,37 +3186,37 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>7960000000</v>
+        <v>8590000000</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>HIMS</t>
+          <t>OKLO</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Hims &amp; Hers Health Inc</t>
+          <t>Oklo Inc</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>7570000000</v>
+        <v>7680000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>HIMS</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Zillow Group Inc</t>
+          <t>Hims &amp; Hers Health Inc</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>7550000000</v>
+        <v>7580000000</v>
       </c>
     </row>
     <row r="183">
@@ -3231,52 +3231,52 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>7540000000</v>
+        <v>7570000000</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Celsius Holdings Inc</t>
+          <t>AeroVironment Inc</t>
         </is>
       </c>
       <c r="L184" t="n">
-        <v>7520000000</v>
+        <v>7530000000</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>OKLO</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Oklo Inc</t>
+          <t>Zillow Group Inc</t>
         </is>
       </c>
       <c r="L185" t="n">
-        <v>7220000000</v>
+        <v>7280000000</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>AeroVironment Inc</t>
+          <t>Celsius Holdings Inc</t>
         </is>
       </c>
       <c r="L186" t="n">
-        <v>7220000000</v>
+        <v>7160000000</v>
       </c>
     </row>
     <row r="187">
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>6670000000</v>
+        <v>6450000000</v>
       </c>
     </row>
     <row r="188">
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>5180000000</v>
+        <v>5270000000</v>
       </c>
     </row>
     <row r="189">
@@ -3321,37 +3321,37 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>4740000000</v>
+        <v>5080000000</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>CRSP</t>
+          <t>MARA</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>CRISPR Therapeutics AG</t>
+          <t>MARA Holdings Inc</t>
         </is>
       </c>
       <c r="L190" t="n">
-        <v>4530000000</v>
+        <v>4670000000</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>MARA</t>
+          <t>CRSP</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>MARA Holdings Inc</t>
+          <t>CRISPR Therapeutics AG</t>
         </is>
       </c>
       <c r="L191" t="n">
-        <v>4450000000</v>
+        <v>4640000000</v>
       </c>
     </row>
     <row r="192">
@@ -3366,37 +3366,37 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>3910000000</v>
+        <v>4360000000</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>FSLY</t>
+          <t>LEU</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Fastly Inc</t>
+          <t>Centrus Energy Corp</t>
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3200000000</v>
+        <v>3370000000</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>LEU</t>
+          <t>FSLY</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Centrus Energy Corp</t>
+          <t>Fastly Inc</t>
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3080000000</v>
+        <v>3240000000</v>
       </c>
     </row>
     <row r="195">
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>2910000000</v>
+        <v>3180000000</v>
       </c>
     </row>
     <row r="196">
@@ -3432,31 +3432,31 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>FLNC</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Upstart Holdings Inc</t>
+          <t>Fluence Energy Inc</t>
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2760000000</v>
+        <v>2820000000</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>FLNC</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Fluence Energy Inc</t>
+          <t>Upstart Holdings Inc</t>
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2630000000</v>
+        <v>2800000000</v>
       </c>
     </row>
     <row r="199">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>2540000000</v>
+        <v>2570000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1790000000</v>
+        <v>1850000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1740000000</v>
+        <v>1750000000</v>
       </c>
     </row>
     <row r="202">
@@ -3522,31 +3522,31 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>NNE</t>
+          <t>UMAC</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Nano Nuclear Energy Inc</t>
+          <t>Unusual Machines Inc</t>
         </is>
       </c>
       <c r="L203" t="n">
-        <v>854690000</v>
+        <v>933420000</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>UMAC</t>
+          <t>NNE</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Unusual Machines Inc</t>
+          <t>Nano Nuclear Energy Inc</t>
         </is>
       </c>
       <c r="L204" t="n">
-        <v>830660000</v>
+        <v>901040000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>489770000</v>
+        <v>536340000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4813630000000</v>
+        <v>4786460000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5016420000000</v>
+        <v>5131850000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4218720000000</v>
+        <v>4168870000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2954660000000</v>
+        <v>2899620000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2662920000000</v>
+        <v>2633880000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2202230000000</v>
+        <v>2184600000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1838800000000</v>
+        <v>1887860000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1634260000000</v>
+        <v>1592020000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1423160000000</v>
+        <v>1404680000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1106930000000</v>
+        <v>1095250000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1096440000000</v>
+        <v>1083630000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1055760000000</v>
+        <v>1055060000000</v>
       </c>
     </row>
     <row r="17">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>925050000000</v>
+        <v>933030000000</v>
       </c>
     </row>
     <row r="18">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>887750000000</v>
+        <v>900630000000</v>
       </c>
     </row>
     <row r="19">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>878490000000</v>
+        <v>870060000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>694340000000</v>
+        <v>694470000000</v>
       </c>
     </row>
     <row r="21">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>670410000000</v>
+        <v>665890000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>628760000000</v>
+        <v>640110000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>603270000000</v>
+        <v>615360000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>475630000000</v>
+        <v>470050000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,37 +861,37 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>452480000000</v>
+        <v>447530000000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Applied Materials Inc</t>
+          <t>Cisco Systems Inc</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>448230000000</v>
+        <v>442270000000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cisco Systems Inc</t>
+          <t>Applied Materials Inc</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>442150000000</v>
+        <v>439790000000</v>
       </c>
     </row>
     <row r="28">
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>434450000000</v>
+        <v>437290000000</v>
       </c>
     </row>
     <row r="29">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>412090000000</v>
+        <v>411240000000</v>
       </c>
     </row>
     <row r="30">
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>409950000000</v>
+        <v>409650000000</v>
       </c>
     </row>
     <row r="31">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>402680000000</v>
+        <v>399290000000</v>
       </c>
     </row>
     <row r="32">
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>396270000000</v>
+        <v>391690000000</v>
       </c>
     </row>
     <row r="33">
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>380530000000</v>
+        <v>384340000000</v>
       </c>
     </row>
     <row r="34">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>365960000000</v>
+        <v>362480000000</v>
       </c>
     </row>
     <row r="35">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>353500000000</v>
+        <v>354010000000</v>
       </c>
     </row>
     <row r="36">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>352670000000</v>
+        <v>353660000000</v>
       </c>
     </row>
     <row r="37">
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>344870000000</v>
+        <v>347260000000</v>
       </c>
     </row>
     <row r="38">
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>341320000000</v>
+        <v>344640000000</v>
       </c>
     </row>
     <row r="39">
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>330640000000</v>
+        <v>330490000000</v>
       </c>
     </row>
     <row r="40">
@@ -1086,37 +1086,37 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>320250000000</v>
+        <v>323980000000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc</t>
+          <t>Merck &amp; Co Inc</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>318030000000</v>
+        <v>314830000000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Merck &amp; Co Inc</t>
+          <t>Philip Morris International Inc</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>311840000000</v>
+        <v>302830000000</v>
       </c>
     </row>
     <row r="43">
@@ -1131,37 +1131,37 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>308270000000</v>
+        <v>301540000000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Philip Morris International Inc</t>
+          <t>Palantir Technologies Inc</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>293070000000</v>
+        <v>298630000000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>289900000000</v>
+        <v>286410000000</v>
       </c>
     </row>
     <row r="46">
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>285940000000</v>
+        <v>285350000000</v>
       </c>
     </row>
     <row r="47">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>284190000000</v>
+        <v>280440000000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>NVS</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Alibaba Group Holding Ltd ADR</t>
+          <t>Novartis AG ADR</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>282780000000</v>
+        <v>280220000000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>NVS</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Novartis AG ADR</t>
+          <t>Alibaba Group Holding Ltd ADR</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>281670000000</v>
+        <v>279400000000</v>
       </c>
     </row>
     <row r="50">
@@ -1236,67 +1236,67 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>278850000000</v>
+        <v>273250000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Co</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>268500000000</v>
+        <v>267740000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>265110000000</v>
+        <v>264700000000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Astrazeneca plc</t>
+          <t>Wells Fargo &amp; Co</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>262620000000</v>
+        <v>264460000000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>Astrazeneca plc</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>262000000000</v>
+        <v>263230000000</v>
       </c>
     </row>
     <row r="55">
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>260810000000</v>
+        <v>262440000000</v>
       </c>
     </row>
     <row r="56">
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>243120000000</v>
+        <v>244710000000</v>
       </c>
     </row>
     <row r="57">
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>239350000000</v>
+        <v>237950000000</v>
       </c>
     </row>
     <row r="58">
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>235370000000</v>
+        <v>236840000000</v>
       </c>
     </row>
     <row r="59">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>233630000000</v>
+        <v>235310000000</v>
       </c>
     </row>
     <row r="60">
@@ -1386,7 +1386,7 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>227810000000</v>
+        <v>226800000000</v>
       </c>
     </row>
     <row r="61">
@@ -1401,157 +1401,157 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>206450000000</v>
+        <v>206640000000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>International Business Machines Corp</t>
+          <t>AMGEN Inc</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>197850000000</v>
+        <v>197560000000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AMGEN Inc</t>
+          <t>Thermo Fisher Scientific Inc</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>197660000000</v>
+        <v>195640000000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>International Business Machines Corp</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>194640000000</v>
+        <v>193400000000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>194530000000</v>
+        <v>191870000000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Toyota Motor Corp ADR</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>191890000000</v>
+        <v>191860000000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>Toyota Motor Corp ADR</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>189020000000</v>
+        <v>191470000000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>McDonald's Corp</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>187510000000</v>
+        <v>189070000000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>McDonald's Corp</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>186000000000</v>
+        <v>187270000000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PepsiCo Inc</t>
+          <t>NextEra Energy Inc</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>184260000000</v>
+        <v>186470000000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NextEra Energy Inc</t>
+          <t>PepsiCo Inc</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>183390000000</v>
+        <v>185150000000</v>
       </c>
     </row>
     <row r="72">
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>182870000000</v>
+        <v>185110000000</v>
       </c>
     </row>
     <row r="73">
@@ -1581,52 +1581,52 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>182810000000</v>
+        <v>184940000000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Sap SE ADR</t>
+          <t>Charles Schwab Corp</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>180200000000</v>
+        <v>175300000000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Charles Schwab Corp</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>173840000000</v>
+        <v>175170000000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Sap SE ADR</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>173610000000</v>
+        <v>173670000000</v>
       </c>
     </row>
     <row r="77">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>168820000000</v>
+        <v>171810000000</v>
       </c>
     </row>
     <row r="78">
@@ -1656,97 +1656,97 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>166950000000</v>
+        <v>166480000000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Novo Nordisk ADR</t>
+          <t>Boeing Co</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>165820000000</v>
+        <v>164480000000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>Deere &amp; Co</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>161750000000</v>
+        <v>163940000000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Boeing Co</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>161440000000</v>
+        <v>161830000000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Shopify Inc</t>
+          <t>Novo Nordisk ADR</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>159650000000</v>
+        <v>161820000000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Deere &amp; Co</t>
+          <t>AT&amp;T Inc</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>158420000000</v>
+        <v>160090000000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc</t>
+          <t>Shopify Inc</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>154670000000</v>
+        <v>153670000000</v>
       </c>
     </row>
     <row r="85">
@@ -1761,7 +1761,7 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>151650000000</v>
+        <v>150030000000</v>
       </c>
     </row>
     <row r="86">
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>145650000000</v>
+        <v>143160000000</v>
       </c>
     </row>
     <row r="87">
@@ -1791,37 +1791,37 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>144010000000</v>
+        <v>138570000000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>142750000000</v>
+        <v>137820000000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Corning Inc</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>139780000000</v>
+        <v>137760000000</v>
       </c>
     </row>
     <row r="90">
@@ -1836,37 +1836,37 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>139280000000</v>
+        <v>133500000000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>Chubb Limited</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>139010000000</v>
+        <v>133130000000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Chubb Limited</t>
+          <t>Corning Inc</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>137610000000</v>
+        <v>132590000000</v>
       </c>
     </row>
     <row r="93">
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>127650000000</v>
+        <v>127000000000</v>
       </c>
     </row>
     <row r="94">
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>126700000000</v>
+        <v>126790000000</v>
       </c>
     </row>
     <row r="95">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>124420000000</v>
+        <v>124080000000</v>
       </c>
     </row>
     <row r="96">
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>123980000000</v>
+        <v>120660000000</v>
       </c>
     </row>
     <row r="97">
@@ -1941,82 +1941,82 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>121890000000</v>
+        <v>120520000000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PDD Holdings Inc ADR</t>
+          <t>Progressive Corp</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>120750000000</v>
+        <v>119520000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Progressive Corp</t>
+          <t>PDD Holdings Inc ADR</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>120310000000</v>
+        <v>118980000000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Starbucks Corp</t>
+          <t>Lockheed Martin Corp</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>119040000000</v>
+        <v>118590000000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>Starbucks Corp</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>116960000000</v>
+        <v>118510000000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corp</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>116920000000</v>
+        <v>115680000000</v>
       </c>
     </row>
     <row r="103">
@@ -2031,7 +2031,7 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>114110000000</v>
+        <v>114580000000</v>
       </c>
     </row>
     <row r="104">
@@ -2046,67 +2046,67 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>105410000000</v>
+        <v>104820000000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Spotify Technology SA</t>
+          <t>Equinix Inc</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>101470000000</v>
+        <v>101460000000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Equinix Inc</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>101370000000</v>
+        <v>100430000000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>United Parcel Service Inc</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>99240000000</v>
+        <v>98460000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>United Parcel Service Inc</t>
+          <t>Spotify Technology SA</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>98890000000</v>
+        <v>97540000000</v>
       </c>
     </row>
     <row r="109">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>98420000000</v>
+        <v>97180000000</v>
       </c>
     </row>
     <row r="110">
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>96700000000</v>
+        <v>95520000000</v>
       </c>
     </row>
     <row r="111">
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>94180000000</v>
+        <v>92820000000</v>
       </c>
     </row>
     <row r="112">
@@ -2166,97 +2166,97 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>92400000000</v>
+        <v>91210000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>3M Co</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>90700000000</v>
+        <v>89060000000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>90300000000</v>
+        <v>87480000000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>3M Co</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>89060000000</v>
+        <v>86800000000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MMC</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Marsh</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>87490000000</v>
+        <v>85730000000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>MMC</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Airbnb Inc</t>
+          <t>Marsh</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>86850000000</v>
+        <v>84790000000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>Airbnb Inc</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>86200000000</v>
+        <v>84410000000</v>
       </c>
     </row>
     <row r="119">
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>85330000000</v>
+        <v>84380000000</v>
       </c>
     </row>
     <row r="120">
@@ -2286,37 +2286,37 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>82770000000</v>
+        <v>82500000000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Intuit Inc</t>
+          <t>Intercontinental Exchange Inc</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>79300000000</v>
+        <v>80600000000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange Inc</t>
+          <t>Intuit Inc</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>78420000000</v>
+        <v>77810000000</v>
       </c>
     </row>
     <row r="123">
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>77210000000</v>
+        <v>76660000000</v>
       </c>
     </row>
     <row r="124">
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>76840000000</v>
+        <v>75350000000</v>
       </c>
     </row>
     <row r="125">
@@ -2361,97 +2361,97 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>72760000000</v>
+        <v>74610000000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive Co</t>
+          <t>General Motors Company</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>72420000000</v>
+        <v>74050000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>General Motors Company</t>
+          <t>Colgate-Palmolive Co</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>71700000000</v>
+        <v>73320000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals Inc</t>
+          <t>SLB Ltd</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>70790000000</v>
+        <v>71270000000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SLB Ltd</t>
+          <t>Nu Holdings Ltd</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>69650000000</v>
+        <v>70090000000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>NU</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Nu Holdings Ltd</t>
+          <t>Apollo Global Management Inc</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>69510000000</v>
+        <v>68630000000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Apollo Global Management Inc</t>
+          <t>Regeneron Pharmaceuticals Inc</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>68260000000</v>
+        <v>68270000000</v>
       </c>
     </row>
     <row r="132">
@@ -2466,37 +2466,37 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>65300000000</v>
+        <v>65590000000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Nike Inc</t>
+          <t>Target Corp</t>
         </is>
       </c>
       <c r="L133" t="n">
-        <v>63730000000</v>
+        <v>62640000000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Target Corp</t>
+          <t>Nike Inc</t>
         </is>
       </c>
       <c r="L134" t="n">
-        <v>62900000000</v>
+        <v>62620000000</v>
       </c>
     </row>
     <row r="135">
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>60250000000</v>
+        <v>59460000000</v>
       </c>
     </row>
     <row r="136">
@@ -2526,7 +2526,7 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>56860000000</v>
+        <v>57460000000</v>
       </c>
     </row>
     <row r="137">
@@ -2541,7 +2541,7 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>56200000000</v>
+        <v>57190000000</v>
       </c>
     </row>
     <row r="138">
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>54810000000</v>
+        <v>56720000000</v>
       </c>
     </row>
     <row r="139">
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>54730000000</v>
+        <v>56220000000</v>
       </c>
     </row>
     <row r="140">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>54590000000</v>
+        <v>54900000000</v>
       </c>
     </row>
     <row r="141">
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>49270000000</v>
+        <v>48970000000</v>
       </c>
     </row>
     <row r="142">
@@ -2616,7 +2616,7 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>48680000000</v>
+        <v>48580000000</v>
       </c>
     </row>
     <row r="143">
@@ -2631,97 +2631,97 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>47840000000</v>
+        <v>46100000000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Coinbase Global Inc</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>46330000000</v>
+        <v>45090000000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Autodesk Inc</t>
+          <t>Coinbase Global Inc</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>44550000000</v>
+        <v>43770000000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Autodesk Inc</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>43420000000</v>
+        <v>42940000000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>Rocket Lab Corp</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>42740000000</v>
+        <v>41720000000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Rocket Lab Corp</t>
+          <t>MSCI Inc</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>41350000000</v>
+        <v>41570000000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>MSCI Inc</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>40890000000</v>
+        <v>41300000000</v>
       </c>
     </row>
     <row r="150">
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>36920000000</v>
+        <v>36580000000</v>
       </c>
     </row>
     <row r="151">
@@ -2751,37 +2751,37 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>35830000000</v>
+        <v>35750000000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>RDDT</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Reddit Inc</t>
+          <t>Strategy Inc</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>35780000000</v>
+        <v>35050000000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>RDDT</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Strategy Inc</t>
+          <t>Reddit Inc</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>35730000000</v>
+        <v>32800000000</v>
       </c>
     </row>
     <row r="154">
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>34870000000</v>
+        <v>32710000000</v>
       </c>
     </row>
     <row r="155">
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>31590000000</v>
+        <v>31100000000</v>
       </c>
     </row>
     <row r="156">
@@ -2826,37 +2826,37 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>29800000000</v>
+        <v>29900000000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Twilio Inc</t>
+          <t>Illumina Inc</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>29780000000</v>
+        <v>28880000000</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Illumina Inc</t>
+          <t>Twilio Inc</t>
         </is>
       </c>
       <c r="L158" t="n">
-        <v>29130000000</v>
+        <v>27830000000</v>
       </c>
     </row>
     <row r="159">
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>26990000000</v>
+        <v>26780000000</v>
       </c>
     </row>
     <row r="160">
@@ -2886,7 +2886,7 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>26320000000</v>
+        <v>25160000000</v>
       </c>
     </row>
     <row r="161">
@@ -2901,67 +2901,67 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>25020000000</v>
+        <v>24750000000</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Zscaler Inc</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="L162" t="n">
-        <v>24050000000</v>
+        <v>23040000000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>Zscaler Inc</t>
         </is>
       </c>
       <c r="L163" t="n">
-        <v>23670000000</v>
+        <v>23000000000</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>SoFi Technologies Inc</t>
+          <t>First Solar Inc</t>
         </is>
       </c>
       <c r="L164" t="n">
-        <v>22630000000</v>
+        <v>22440000000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>First Solar Inc</t>
+          <t>SoFi Technologies Inc</t>
         </is>
       </c>
       <c r="L165" t="n">
-        <v>22140000000</v>
+        <v>21900000000</v>
       </c>
     </row>
     <row r="166">
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>21400000000</v>
+        <v>21220000000</v>
       </c>
     </row>
     <row r="167">
@@ -2991,52 +2991,52 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>21210000000</v>
+        <v>20300000000</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Charter Communications Inc</t>
+          <t>Super Micro Computer Inc</t>
         </is>
       </c>
       <c r="L168" t="n">
-        <v>17700000000</v>
+        <v>19770000000</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>CRCL</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Circle Internet Group Inc</t>
+          <t>Charter Communications Inc</t>
         </is>
       </c>
       <c r="L169" t="n">
-        <v>17670000000</v>
+        <v>17900000000</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Super Micro Computer Inc</t>
+          <t>Circle Internet Group Inc</t>
         </is>
       </c>
       <c r="L170" t="n">
-        <v>16500000000</v>
+        <v>16450000000</v>
       </c>
     </row>
     <row r="171">
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>14350000000</v>
+        <v>13730000000</v>
       </c>
     </row>
     <row r="173">
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>14350000000</v>
+        <v>13730000000</v>
       </c>
     </row>
     <row r="174">
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>13250000000</v>
+        <v>12940000000</v>
       </c>
     </row>
     <row r="175">
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>12790000000</v>
+        <v>12630000000</v>
       </c>
     </row>
     <row r="176">
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>12770000000</v>
+        <v>12580000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>10900000000</v>
+        <v>10700000000</v>
       </c>
     </row>
     <row r="178">
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>9280000000</v>
+        <v>8890000000</v>
       </c>
     </row>
     <row r="179">
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>8600000000</v>
+        <v>8610000000</v>
       </c>
     </row>
     <row r="180">
@@ -3186,7 +3186,7 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>8590000000</v>
+        <v>8600000000</v>
       </c>
     </row>
     <row r="181">
@@ -3201,22 +3201,22 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>7680000000</v>
+        <v>7740000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>HIMS</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Hims &amp; Hers Health Inc</t>
+          <t>AeroVironment Inc</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>7580000000</v>
+        <v>7610000000</v>
       </c>
     </row>
     <row r="183">
@@ -3231,33 +3231,33 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>7570000000</v>
+        <v>7390000000</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>HIMS</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>AeroVironment Inc</t>
+          <t>Hims &amp; Hers Health Inc</t>
         </is>
       </c>
       <c r="L184" t="n">
-        <v>7530000000</v>
+        <v>7330000000</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Zillow Group Inc</t>
+          <t>Celsius Holdings Inc</t>
         </is>
       </c>
       <c r="L185" t="n">
@@ -3267,16 +3267,16 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Celsius Holdings Inc</t>
+          <t>Zillow Group Inc</t>
         </is>
       </c>
       <c r="L186" t="n">
-        <v>7160000000</v>
+        <v>7170000000</v>
       </c>
     </row>
     <row r="187">
@@ -3291,37 +3291,37 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>6450000000</v>
+        <v>6250000000</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>LMND</t>
+          <t>RGTI</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Lemonade Inc</t>
+          <t>Rigetti Computing Inc</t>
         </is>
       </c>
       <c r="L188" t="n">
-        <v>5270000000</v>
+        <v>5060000000</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>RGTI</t>
+          <t>LMND</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Rigetti Computing Inc</t>
+          <t>Lemonade Inc</t>
         </is>
       </c>
       <c r="L189" t="n">
-        <v>5080000000</v>
+        <v>4870000000</v>
       </c>
     </row>
     <row r="190">
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>4670000000</v>
+        <v>4730000000</v>
       </c>
     </row>
     <row r="191">
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>4640000000</v>
+        <v>4560000000</v>
       </c>
     </row>
     <row r="192">
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>4360000000</v>
+        <v>4560000000</v>
       </c>
     </row>
     <row r="193">
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3370000000</v>
+        <v>3430000000</v>
       </c>
     </row>
     <row r="194">
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3240000000</v>
+        <v>3200000000</v>
       </c>
     </row>
     <row r="195">
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>3180000000</v>
+        <v>3170000000</v>
       </c>
     </row>
     <row r="196">
@@ -3426,37 +3426,37 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2840000000</v>
+        <v>2800000000</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>FLNC</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Fluence Energy Inc</t>
+          <t>Upstart Holdings Inc</t>
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2820000000</v>
+        <v>2740000000</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>FLNC</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Upstart Holdings Inc</t>
+          <t>Fluence Energy Inc</t>
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2800000000</v>
+        <v>2700000000</v>
       </c>
     </row>
     <row r="199">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>2570000000</v>
+        <v>2460000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1850000000</v>
+        <v>1780000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1750000000</v>
+        <v>1610000000</v>
       </c>
     </row>
     <row r="202">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1340000000</v>
+        <v>1270000000</v>
       </c>
     </row>
     <row r="203">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>933420000</v>
+        <v>940110000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>901040000</v>
+        <v>902080000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>536340000</v>
+        <v>513690000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4786460000000</v>
+        <v>4724340000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5131850000000</v>
+        <v>5051990000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4168870000000</v>
+        <v>3876700000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2899620000000</v>
+        <v>2834540000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2633880000000</v>
+        <v>2513510000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2184600000000</v>
+        <v>2155400000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1887860000000</v>
+        <v>1867210000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1592020000000</v>
+        <v>1538540000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,37 +681,37 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1404680000000</v>
+        <v>1200670000000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lilly(Eli) &amp; Co</t>
+          <t>Micron Technology Inc</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1095250000000</v>
+        <v>1118340000000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Micron Technology Inc</t>
+          <t>Lilly(Eli) &amp; Co</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1083630000000</v>
+        <v>1116780000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1055060000000</v>
+        <v>1058010000000</v>
       </c>
     </row>
     <row r="17">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>933030000000</v>
+        <v>937560000000</v>
       </c>
     </row>
     <row r="18">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>900630000000</v>
+        <v>880020000000</v>
       </c>
     </row>
     <row r="19">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>870060000000</v>
+        <v>862660000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>694470000000</v>
+        <v>694910000000</v>
       </c>
     </row>
     <row r="21">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>665890000000</v>
+        <v>662460000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>640110000000</v>
+        <v>650220000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>615360000000</v>
+        <v>624120000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>470050000000</v>
+        <v>468560000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,37 +861,37 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>447530000000</v>
+        <v>453920000000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cisco Systems Inc</t>
+          <t>Applied Materials Inc</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>442270000000</v>
+        <v>446840000000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Applied Materials Inc</t>
+          <t>Cisco Systems Inc</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>439790000000</v>
+        <v>444440000000</v>
       </c>
     </row>
     <row r="28">
@@ -906,37 +906,37 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>437290000000</v>
+        <v>434880000000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Costco Wholesale Corp</t>
+          <t>Caterpillar Inc</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>411240000000</v>
+        <v>412060000000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Caterpillar Inc</t>
+          <t>Costco Wholesale Corp</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>409650000000</v>
+        <v>410690000000</v>
       </c>
     </row>
     <row r="31">
@@ -951,82 +951,82 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>399290000000</v>
+        <v>399910000000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Unitedhealth Group Inc</t>
+          <t>Chevron Corp</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>391690000000</v>
+        <v>387210000000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Chevron Corp</t>
+          <t>Unitedhealth Group Inc</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>384340000000</v>
+        <v>384650000000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Oracle Corp</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>362480000000</v>
+        <v>362110000000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Coca-Cola Co</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>354010000000</v>
+        <v>349230000000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Coca-Cola Co</t>
+          <t>Oracle Corp</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>353660000000</v>
+        <v>345770000000</v>
       </c>
     </row>
     <row r="37">
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>347260000000</v>
+        <v>342230000000</v>
       </c>
     </row>
     <row r="38">
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>344640000000</v>
+        <v>339400000000</v>
       </c>
     </row>
     <row r="39">
@@ -1071,67 +1071,67 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>330490000000</v>
+        <v>323770000000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Goldman Sachs Group Inc</t>
+          <t>Merck &amp; Co Inc</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>323980000000</v>
+        <v>322260000000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Merck &amp; Co Inc</t>
+          <t>Goldman Sachs Group Inc</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>314830000000</v>
+        <v>317050000000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Philip Morris International Inc</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>302830000000</v>
+        <v>301150000000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>Philip Morris International Inc</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>301540000000</v>
+        <v>297870000000</v>
       </c>
     </row>
     <row r="44">
@@ -1146,37 +1146,37 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>298630000000</v>
+        <v>295760000000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>Netflix Inc</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>286410000000</v>
+        <v>286850000000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>NVS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Netflix Inc</t>
+          <t>Novartis AG ADR</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>285350000000</v>
+        <v>285820000000</v>
       </c>
     </row>
     <row r="47">
@@ -1191,82 +1191,82 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>280440000000</v>
+        <v>285720000000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>NVS</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Novartis AG ADR</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>280220000000</v>
+        <v>284820000000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Alibaba Group Holding Ltd ADR</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>279400000000</v>
+        <v>281670000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>273250000000</v>
+        <v>277100000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>Alibaba Group Holding Ltd ADR</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>267740000000</v>
+        <v>273410000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>264700000000</v>
+        <v>265390000000</v>
       </c>
     </row>
     <row r="53">
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>264460000000</v>
+        <v>263760000000</v>
       </c>
     </row>
     <row r="54">
@@ -1296,22 +1296,22 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>263230000000</v>
+        <v>260960000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>262440000000</v>
+        <v>259370000000</v>
       </c>
     </row>
     <row r="56">
@@ -1326,52 +1326,52 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>244710000000</v>
+        <v>245210000000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>American Express Co</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>237950000000</v>
+        <v>238470000000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>Linde Plc</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>236840000000</v>
+        <v>234220000000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Linde Plc</t>
+          <t>American Express Co</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>235310000000</v>
+        <v>232560000000</v>
       </c>
     </row>
     <row r="60">
@@ -1386,22 +1386,22 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>226800000000</v>
+        <v>226160000000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>T-Mobile US Inc</t>
+          <t>Thermo Fisher Scientific Inc</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>206640000000</v>
+        <v>212690000000</v>
       </c>
     </row>
     <row r="62">
@@ -1416,97 +1416,97 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>197560000000</v>
+        <v>200500000000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc</t>
+          <t>International Business Machines Corp</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>195640000000</v>
+        <v>194230000000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>International Business Machines Corp</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>193400000000</v>
+        <v>192440000000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>191870000000</v>
+        <v>192010000000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>Toyota Motor Corp ADR</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>191860000000</v>
+        <v>188120000000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Toyota Motor Corp ADR</t>
+          <t>NextEra Energy Inc</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>191470000000</v>
+        <v>187270000000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>189070000000</v>
+        <v>186770000000</v>
       </c>
     </row>
     <row r="69">
@@ -1521,22 +1521,22 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>187270000000</v>
+        <v>186720000000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NextEra Energy Inc</t>
+          <t>T-Mobile US Inc</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>186470000000</v>
+        <v>184430000000</v>
       </c>
     </row>
     <row r="71">
@@ -1551,37 +1551,37 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>185150000000</v>
+        <v>184190000000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>Verizon Communications Inc</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>185110000000</v>
+        <v>182970000000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>184940000000</v>
+        <v>180350000000</v>
       </c>
     </row>
     <row r="74">
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>175300000000</v>
+        <v>176710000000</v>
       </c>
     </row>
     <row r="75">
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>175170000000</v>
+        <v>175490000000</v>
       </c>
     </row>
     <row r="76">
@@ -1626,7 +1626,7 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>173670000000</v>
+        <v>170910000000</v>
       </c>
     </row>
     <row r="77">
@@ -1641,82 +1641,82 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>171810000000</v>
+        <v>168640000000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Walt Disney Co</t>
+          <t>Boeing Co</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>166480000000</v>
+        <v>164940000000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Boeing Co</t>
+          <t>Deere &amp; Co</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>164480000000</v>
+        <v>164670000000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Deere &amp; Co</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>163940000000</v>
+        <v>162470000000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>Novo Nordisk ADR</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>161830000000</v>
+        <v>161790000000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Novo Nordisk ADR</t>
+          <t>Walt Disney Co</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>161820000000</v>
+        <v>161200000000</v>
       </c>
     </row>
     <row r="83">
@@ -1731,37 +1731,37 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>160090000000</v>
+        <v>159530000000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Shopify Inc</t>
+          <t>Blackstone Inc</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>153670000000</v>
+        <v>152080000000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Blackstone Inc</t>
+          <t>Shopify Inc</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>150030000000</v>
+        <v>145340000000</v>
       </c>
     </row>
     <row r="86">
@@ -1776,127 +1776,127 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>143160000000</v>
+        <v>140270000000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>138570000000</v>
+        <v>138160000000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>Chubb Limited</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>137820000000</v>
+        <v>137010000000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Danaher Corp</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>137760000000</v>
+        <v>135320000000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Salesforce Inc</t>
+          <t>Corning Inc</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>133500000000</v>
+        <v>134310000000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Chubb Limited</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>133130000000</v>
+        <v>133990000000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Corning Inc</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>132590000000</v>
+        <v>133920000000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>S&amp;P Global Inc</t>
+          <t>Lockheed Martin Corp</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>127000000000</v>
+        <v>131100000000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Danaher Corp</t>
+          <t>Salesforce Inc</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>126790000000</v>
+        <v>128530000000</v>
       </c>
     </row>
     <row r="95">
@@ -1911,52 +1911,52 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>124080000000</v>
+        <v>125610000000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Intuitive Surgical Inc</t>
+          <t>S&amp;P Global Inc</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>120660000000</v>
+        <v>124320000000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Altria Group Inc</t>
+          <t>Progressive Corp</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>120520000000</v>
+        <v>121000000000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Progressive Corp</t>
+          <t>Altria Group Inc</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>119520000000</v>
+        <v>120370000000</v>
       </c>
     </row>
     <row r="99">
@@ -1971,37 +1971,37 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>118980000000</v>
+        <v>118570000000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corp</t>
+          <t>Starbucks Corp</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>118590000000</v>
+        <v>117630000000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Starbucks Corp</t>
+          <t>Intuitive Surgical Inc</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>118510000000</v>
+        <v>117300000000</v>
       </c>
     </row>
     <row r="102">
@@ -2016,7 +2016,7 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>115680000000</v>
+        <v>116780000000</v>
       </c>
     </row>
     <row r="103">
@@ -2031,7 +2031,7 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>114580000000</v>
+        <v>113220000000</v>
       </c>
     </row>
     <row r="104">
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>104820000000</v>
+        <v>104980000000</v>
       </c>
     </row>
     <row r="105">
@@ -2061,7 +2061,7 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>101460000000</v>
+        <v>101930000000</v>
       </c>
     </row>
     <row r="106">
@@ -2076,52 +2076,52 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>100430000000</v>
+        <v>98650000000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>United Parcel Service Inc</t>
+          <t>Automatic Data Processing Inc</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>98460000000</v>
+        <v>97090000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Spotify Technology SA</t>
+          <t>United Parcel Service Inc</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>97540000000</v>
+        <v>96990000000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc</t>
+          <t>Spotify Technology SA</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>97180000000</v>
+        <v>96480000000</v>
       </c>
     </row>
     <row r="110">
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>95520000000</v>
+        <v>93160000000</v>
       </c>
     </row>
     <row r="111">
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>92820000000</v>
+        <v>91890000000</v>
       </c>
     </row>
     <row r="112">
@@ -2166,7 +2166,7 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>91210000000</v>
+        <v>91190000000</v>
       </c>
     </row>
     <row r="113">
@@ -2181,7 +2181,7 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>89060000000</v>
+        <v>87460000000</v>
       </c>
     </row>
     <row r="114">
@@ -2196,37 +2196,37 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>87480000000</v>
+        <v>86990000000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>86800000000</v>
+        <v>84900000000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>85730000000</v>
+        <v>84340000000</v>
       </c>
     </row>
     <row r="117">
@@ -2241,52 +2241,52 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>84790000000</v>
+        <v>84180000000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Airbnb Inc</t>
+          <t>HCA Healthcare Inc</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>84410000000</v>
+        <v>83520000000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Elevance Health Inc</t>
+          <t>Airbnb Inc</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>84380000000</v>
+        <v>82910000000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>HCA Healthcare Inc</t>
+          <t>Elevance Health Inc</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>82500000000</v>
+        <v>82260000000</v>
       </c>
     </row>
     <row r="121">
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>80600000000</v>
+        <v>80990000000</v>
       </c>
     </row>
     <row r="122">
@@ -2316,7 +2316,7 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>77810000000</v>
+        <v>77010000000</v>
       </c>
     </row>
     <row r="123">
@@ -2331,67 +2331,67 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>76660000000</v>
+        <v>76010000000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Cigna Group</t>
+          <t>Northrop Grumman Corp</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>75350000000</v>
+        <v>75790000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp</t>
+          <t>Cigna Group</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>74610000000</v>
+        <v>75730000000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>General Motors Company</t>
+          <t>Colgate-Palmolive Co</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>74050000000</v>
+        <v>72080000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive Co</t>
+          <t>General Motors Company</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>73320000000</v>
+        <v>70780000000</v>
       </c>
     </row>
     <row r="128">
@@ -2406,37 +2406,37 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>71270000000</v>
+        <v>70600000000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>NU</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Nu Holdings Ltd</t>
+          <t>Apollo Global Management Inc</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>70090000000</v>
+        <v>68610000000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Apollo Global Management Inc</t>
+          <t>Nu Holdings Ltd</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>68630000000</v>
+        <v>68540000000</v>
       </c>
     </row>
     <row r="131">
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>68270000000</v>
+        <v>68350000000</v>
       </c>
     </row>
     <row r="132">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>65590000000</v>
+        <v>63440000000</v>
       </c>
     </row>
     <row r="133">
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>62640000000</v>
+        <v>61080000000</v>
       </c>
     </row>
     <row r="134">
@@ -2496,82 +2496,82 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>62620000000</v>
+        <v>60810000000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Sea Ltd ADR</t>
+          <t>Occidental Petroleum Corp</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>59460000000</v>
+        <v>57290000000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Ford Motor Co</t>
+          <t>Vistra Corp</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>57460000000</v>
+        <v>56980000000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Occidental Petroleum Corp</t>
+          <t>Sea Ltd ADR</t>
         </is>
       </c>
       <c r="L137" t="n">
-        <v>57190000000</v>
+        <v>56410000000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Astera Labs Inc</t>
+          <t>Ford Motor Co</t>
         </is>
       </c>
       <c r="L138" t="n">
-        <v>56720000000</v>
+        <v>56380000000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Vistra Corp</t>
+          <t>Astera Labs Inc</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>56220000000</v>
+        <v>56050000000</v>
       </c>
     </row>
     <row r="140">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>54900000000</v>
+        <v>55610000000</v>
       </c>
     </row>
     <row r="141">
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>48970000000</v>
+        <v>49400000000</v>
       </c>
     </row>
     <row r="142">
@@ -2616,7 +2616,7 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>48580000000</v>
+        <v>48260000000</v>
       </c>
     </row>
     <row r="143">
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>46100000000</v>
+        <v>45530000000</v>
       </c>
     </row>
     <row r="144">
@@ -2646,37 +2646,37 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>45090000000</v>
+        <v>44250000000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Coinbase Global Inc</t>
+          <t>Autodesk Inc</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>43770000000</v>
+        <v>43310000000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Autodesk Inc</t>
+          <t>Coinbase Global Inc</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>42940000000</v>
+        <v>42460000000</v>
       </c>
     </row>
     <row r="147">
@@ -2691,37 +2691,37 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>41720000000</v>
+        <v>41870000000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>MSCI Inc</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>41570000000</v>
+        <v>41060000000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>MSCI Inc</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>41300000000</v>
+        <v>40170000000</v>
       </c>
     </row>
     <row r="150">
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>36580000000</v>
+        <v>36500000000</v>
       </c>
     </row>
     <row r="151">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>35750000000</v>
+        <v>34610000000</v>
       </c>
     </row>
     <row r="152">
@@ -2766,7 +2766,7 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>35050000000</v>
+        <v>32810000000</v>
       </c>
     </row>
     <row r="153">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>32800000000</v>
+        <v>32490000000</v>
       </c>
     </row>
     <row r="154">
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>32710000000</v>
+        <v>31580000000</v>
       </c>
     </row>
     <row r="155">
@@ -2811,37 +2811,37 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>31100000000</v>
+        <v>31260000000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Estee Lauder Cos. Inc</t>
+          <t>Illumina Inc</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>29900000000</v>
+        <v>29780000000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Illumina Inc</t>
+          <t>Estee Lauder Cos. Inc</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>28880000000</v>
+        <v>28910000000</v>
       </c>
     </row>
     <row r="158">
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>27830000000</v>
+        <v>28090000000</v>
       </c>
     </row>
     <row r="159">
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>26780000000</v>
+        <v>26650000000</v>
       </c>
     </row>
     <row r="160">
@@ -2886,7 +2886,7 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>25160000000</v>
+        <v>24660000000</v>
       </c>
     </row>
     <row r="161">
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>24750000000</v>
+        <v>23850000000</v>
       </c>
     </row>
     <row r="162">
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>23040000000</v>
+        <v>22620000000</v>
       </c>
     </row>
     <row r="163">
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>23000000000</v>
+        <v>22590000000</v>
       </c>
     </row>
     <row r="164">
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>22440000000</v>
+        <v>22130000000</v>
       </c>
     </row>
     <row r="165">
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>21900000000</v>
+        <v>21360000000</v>
       </c>
     </row>
     <row r="166">
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>21220000000</v>
+        <v>21020000000</v>
       </c>
     </row>
     <row r="167">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>20300000000</v>
+        <v>20280000000</v>
       </c>
     </row>
     <row r="168">
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>19770000000</v>
+        <v>20180000000</v>
       </c>
     </row>
     <row r="169">
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>17900000000</v>
+        <v>17520000000</v>
       </c>
     </row>
     <row r="170">
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>16450000000</v>
+        <v>15460000000</v>
       </c>
     </row>
     <row r="171">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>14730000000</v>
+        <v>14480000000</v>
       </c>
     </row>
     <row r="172">
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>13730000000</v>
+        <v>13530000000</v>
       </c>
     </row>
     <row r="173">
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>13730000000</v>
+        <v>13530000000</v>
       </c>
     </row>
     <row r="174">
@@ -3096,37 +3096,37 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>12940000000</v>
+        <v>12720000000</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>PINS</t>
+          <t>TXRH</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Pinterest Inc</t>
+          <t>Texas Roadhouse Inc</t>
         </is>
       </c>
       <c r="L175" t="n">
-        <v>12630000000</v>
+        <v>12550000000</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>TXRH</t>
+          <t>PINS</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Texas Roadhouse Inc</t>
+          <t>Pinterest Inc</t>
         </is>
       </c>
       <c r="L176" t="n">
-        <v>12580000000</v>
+        <v>12260000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>10700000000</v>
+        <v>10540000000</v>
       </c>
     </row>
     <row r="178">
@@ -3156,127 +3156,127 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>8890000000</v>
+        <v>8720000000</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>PRMB</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Primo Brands Corp</t>
+          <t>Applied Digital Corp</t>
         </is>
       </c>
       <c r="L179" t="n">
-        <v>8610000000</v>
+        <v>8540000000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>PRMB</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Applied Digital Corp</t>
+          <t>Primo Brands Corp</t>
         </is>
       </c>
       <c r="L180" t="n">
-        <v>8600000000</v>
+        <v>8270000000</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>OKLO</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Oklo Inc</t>
+          <t>AeroVironment Inc</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>7740000000</v>
+        <v>8030000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>OKLO</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>AeroVironment Inc</t>
+          <t>Oklo Inc</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>7610000000</v>
+        <v>7660000000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>MBLY</t>
+          <t>HIMS</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Mobileye Global Inc</t>
+          <t>Hims &amp; Hers Health Inc</t>
         </is>
       </c>
       <c r="L183" t="n">
-        <v>7390000000</v>
+        <v>7580000000</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>HIMS</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Hims &amp; Hers Health Inc</t>
+          <t>Celsius Holdings Inc</t>
         </is>
       </c>
       <c r="L184" t="n">
-        <v>7330000000</v>
+        <v>6950000000</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Celsius Holdings Inc</t>
+          <t>Zillow Group Inc</t>
         </is>
       </c>
       <c r="L185" t="n">
-        <v>7280000000</v>
+        <v>6770000000</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>MBLY</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Zillow Group Inc</t>
+          <t>Mobileye Global Inc</t>
         </is>
       </c>
       <c r="L186" t="n">
-        <v>7170000000</v>
+        <v>6290000000</v>
       </c>
     </row>
     <row r="187">
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>6250000000</v>
+        <v>5960000000</v>
       </c>
     </row>
     <row r="188">
@@ -3306,18 +3306,18 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>5060000000</v>
+        <v>4940000000</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>LMND</t>
+          <t>MARA</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Lemonade Inc</t>
+          <t>MARA Holdings Inc</t>
         </is>
       </c>
       <c r="L189" t="n">
@@ -3327,16 +3327,16 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>MARA</t>
+          <t>LMND</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>MARA Holdings Inc</t>
+          <t>Lemonade Inc</t>
         </is>
       </c>
       <c r="L190" t="n">
-        <v>4730000000</v>
+        <v>4660000000</v>
       </c>
     </row>
     <row r="191">
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>4560000000</v>
+        <v>4580000000</v>
       </c>
     </row>
     <row r="192">
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>4560000000</v>
+        <v>4520000000</v>
       </c>
     </row>
     <row r="193">
@@ -3381,37 +3381,37 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3430000000</v>
+        <v>3360000000</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>FSLY</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Fastly Inc</t>
+          <t>NuScale Power Corp</t>
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3200000000</v>
+        <v>3220000000</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>FSLY</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>NuScale Power Corp</t>
+          <t>Fastly Inc</t>
         </is>
       </c>
       <c r="L195" t="n">
-        <v>3170000000</v>
+        <v>3040000000</v>
       </c>
     </row>
     <row r="196">
@@ -3426,37 +3426,37 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2800000000</v>
+        <v>2710000000</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>FLNC</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Upstart Holdings Inc</t>
+          <t>Fluence Energy Inc</t>
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2740000000</v>
+        <v>2660000000</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>FLNC</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Fluence Energy Inc</t>
+          <t>Upstart Holdings Inc</t>
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2700000000</v>
+        <v>2640000000</v>
       </c>
     </row>
     <row r="199">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1780000000</v>
+        <v>1770000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1610000000</v>
+        <v>1560000000</v>
       </c>
     </row>
     <row r="202">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>940110000</v>
+        <v>1030000000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>902080000</v>
+        <v>879160000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>513690000</v>
+        <v>508650000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4724340000000</v>
+        <v>4891180000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5051990000000</v>
+        <v>5005530000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3876700000000</v>
+        <v>3880100000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2834540000000</v>
+        <v>2835430000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2513510000000</v>
+        <v>2496830000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2155400000000</v>
+        <v>2092280000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1867210000000</v>
+        <v>1817020000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1538540000000</v>
+        <v>1510840000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,37 +681,37 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1200670000000</v>
+        <v>1175650000000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Micron Technology Inc</t>
+          <t>Lilly(Eli) &amp; Co</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1118340000000</v>
+        <v>1126350000000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lilly(Eli) &amp; Co</t>
+          <t>Micron Technology Inc</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1116780000000</v>
+        <v>1040110000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1058010000000</v>
+        <v>960900000000</v>
       </c>
     </row>
     <row r="17">
@@ -741,37 +741,37 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>937560000000</v>
+        <v>946430000000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices Inc</t>
+          <t>Walmart Inc</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>880020000000</v>
+        <v>871170000000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Walmart Inc</t>
+          <t>Advanced Micro Devices Inc</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>862660000000</v>
+        <v>851090000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>694910000000</v>
+        <v>677220000000</v>
       </c>
     </row>
     <row r="21">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>662460000000</v>
+        <v>670260000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>650220000000</v>
+        <v>650430000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>624120000000</v>
+        <v>634060000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>468560000000</v>
+        <v>476830000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,127 +861,127 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>453920000000</v>
+        <v>458240000000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Applied Materials Inc</t>
+          <t>Cisco Systems Inc</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>446840000000</v>
+        <v>449990000000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cisco Systems Inc</t>
+          <t>Bank Of America Corp</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>444440000000</v>
+        <v>440340000000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Bank Of America Corp</t>
+          <t>Applied Materials Inc</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>434880000000</v>
+        <v>425760000000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Caterpillar Inc</t>
+          <t>Costco Wholesale Corp</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>412060000000</v>
+        <v>414670000000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Costco Wholesale Corp</t>
+          <t>Caterpillar Inc</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>410690000000</v>
+        <v>409380000000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Lam Research Corp</t>
+          <t>Chevron Corp</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>399910000000</v>
+        <v>387940000000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Chevron Corp</t>
+          <t>Unitedhealth Group Inc</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>387210000000</v>
+        <v>382090000000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Unitedhealth Group Inc</t>
+          <t>Lam Research Corp</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>384650000000</v>
+        <v>381690000000</v>
       </c>
     </row>
     <row r="34">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>362110000000</v>
+        <v>367020000000</v>
       </c>
     </row>
     <row r="35">
@@ -1011,67 +1011,67 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>349230000000</v>
+        <v>353880000000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Oracle Corp</t>
+          <t>Procter &amp; Gamble Co</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>345770000000</v>
+        <v>343260000000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble Co</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>342230000000</v>
+        <v>338300000000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Home Depot Inc</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>339400000000</v>
+        <v>332020000000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Home Depot Inc</t>
+          <t>Oracle Corp</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>323770000000</v>
+        <v>331230000000</v>
       </c>
     </row>
     <row r="40">
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>322260000000</v>
+        <v>323720000000</v>
       </c>
     </row>
     <row r="41">
@@ -1101,67 +1101,67 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>317050000000</v>
+        <v>313070000000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>Philip Morris International Inc</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>301150000000</v>
+        <v>300800000000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Philip Morris International Inc</t>
+          <t>Palantir Technologies Inc</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>297870000000</v>
+        <v>294680000000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc</t>
+          <t>Netflix Inc</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>295760000000</v>
+        <v>291850000000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Netflix Inc</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>286850000000</v>
+        <v>286560000000</v>
       </c>
     </row>
     <row r="46">
@@ -1176,52 +1176,52 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>285820000000</v>
+        <v>283750000000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>KLA Corp</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>285720000000</v>
+        <v>283620000000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>284820000000</v>
+        <v>276650000000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>KLA Corp</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>281670000000</v>
+        <v>275000000000</v>
       </c>
     </row>
     <row r="50">
@@ -1236,7 +1236,7 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>277100000000</v>
+        <v>270260000000</v>
       </c>
     </row>
     <row r="51">
@@ -1251,37 +1251,37 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>273410000000</v>
+        <v>268810000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>Wells Fargo &amp; Co</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>265390000000</v>
+        <v>264120000000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Co</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>263760000000</v>
+        <v>263890000000</v>
       </c>
     </row>
     <row r="54">
@@ -1296,7 +1296,7 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>260960000000</v>
+        <v>262500000000</v>
       </c>
     </row>
     <row r="55">
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>259370000000</v>
+        <v>254440000000</v>
       </c>
     </row>
     <row r="56">
@@ -1326,37 +1326,37 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>245210000000</v>
+        <v>246410000000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>Linde Plc</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>238470000000</v>
+        <v>236980000000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Linde Plc</t>
+          <t>Citigroup Inc</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>234220000000</v>
+        <v>226690000000</v>
       </c>
     </row>
     <row r="59">
@@ -1371,22 +1371,22 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>232560000000</v>
+        <v>222550000000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Citigroup Inc</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>226160000000</v>
+        <v>212740000000</v>
       </c>
     </row>
     <row r="61">
@@ -1401,7 +1401,7 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>212690000000</v>
+        <v>211180000000</v>
       </c>
     </row>
     <row r="62">
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>200500000000</v>
+        <v>202950000000</v>
       </c>
     </row>
     <row r="63">
@@ -1431,202 +1431,202 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>194230000000</v>
+        <v>201310000000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>T-Mobile US Inc</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>192440000000</v>
+        <v>194890000000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Verizon Communications Inc</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>192010000000</v>
+        <v>193660000000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Toyota Motor Corp ADR</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>188120000000</v>
+        <v>193280000000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NextEra Energy Inc</t>
+          <t>Toyota Motor Corp ADR</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>187270000000</v>
+        <v>188780000000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>McDonald's Corp</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>186770000000</v>
+        <v>188110000000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>McDonald's Corp</t>
+          <t>NextEra Energy Inc</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>186720000000</v>
+        <v>187250000000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>T-Mobile US Inc</t>
+          <t>Sap SE ADR</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>184430000000</v>
+        <v>186810000000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PepsiCo Inc</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>184190000000</v>
+        <v>186630000000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc</t>
+          <t>PepsiCo Inc</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>182970000000</v>
+        <v>186500000000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>180350000000</v>
+        <v>179510000000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Charles Schwab Corp</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>176710000000</v>
+        <v>179170000000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Charles Schwab Corp</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>175490000000</v>
+        <v>177340000000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Sap SE ADR</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>170910000000</v>
+        <v>175990000000</v>
       </c>
     </row>
     <row r="77">
@@ -1641,97 +1641,97 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>168640000000</v>
+        <v>171650000000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Boeing Co</t>
+          <t>Deere &amp; Co</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>164940000000</v>
+        <v>169560000000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Deere &amp; Co</t>
+          <t>AT&amp;T Inc</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>164670000000</v>
+        <v>165350000000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>Boeing Co</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>162470000000</v>
+        <v>165170000000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Novo Nordisk ADR</t>
+          <t>Walt Disney Co</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>161790000000</v>
+        <v>164710000000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Walt Disney Co</t>
+          <t>Novo Nordisk ADR</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>161200000000</v>
+        <v>163770000000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>159530000000</v>
+        <v>160550000000</v>
       </c>
     </row>
     <row r="84">
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>152080000000</v>
+        <v>160430000000</v>
       </c>
     </row>
     <row r="85">
@@ -1761,52 +1761,52 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>145340000000</v>
+        <v>147610000000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Uber Technologies Inc</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>140270000000</v>
+        <v>140550000000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Chubb Limited</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>138160000000</v>
+        <v>139530000000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Chubb Limited</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>137010000000</v>
+        <v>137510000000</v>
       </c>
     </row>
     <row r="89">
@@ -1821,112 +1821,112 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>135320000000</v>
+        <v>134620000000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Corning Inc</t>
+          <t>Lockheed Martin Corp</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>134310000000</v>
+        <v>134330000000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>Uber Technologies Inc</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>133990000000</v>
+        <v>134230000000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>Salesforce Inc</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>133920000000</v>
+        <v>134040000000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corp</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>131100000000</v>
+        <v>131680000000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Salesforce Inc</t>
+          <t>Bristol-Myers Squibb Co</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>128530000000</v>
+        <v>126790000000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Co</t>
+          <t>S&amp;P Global Inc</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>125610000000</v>
+        <v>126210000000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>S&amp;P Global Inc</t>
+          <t>Corning Inc</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>124320000000</v>
+        <v>126210000000</v>
       </c>
     </row>
     <row r="97">
@@ -1941,7 +1941,7 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>121000000000</v>
+        <v>124950000000</v>
       </c>
     </row>
     <row r="98">
@@ -1956,22 +1956,22 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>120370000000</v>
+        <v>121890000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PDD Holdings Inc ADR</t>
+          <t>Intuitive Surgical Inc</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>118570000000</v>
+        <v>119230000000</v>
       </c>
     </row>
     <row r="100">
@@ -1986,142 +1986,142 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>117630000000</v>
+        <v>117670000000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Intuitive Surgical Inc</t>
+          <t>PDD Holdings Inc ADR</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>117300000000</v>
+        <v>117660000000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>Lowe's Cos. Inc</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>116780000000</v>
+        <v>116430000000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Lowe's Cos. Inc</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>113220000000</v>
+        <v>111530000000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Medtronic Plc</t>
+          <t>Equinix Inc</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>104980000000</v>
+        <v>106930000000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Equinix Inc</t>
+          <t>Medtronic Plc</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>101930000000</v>
+        <v>106510000000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>Automatic Data Processing Inc</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>98650000000</v>
+        <v>99970000000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>97090000000</v>
+        <v>99650000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>United Parcel Service Inc</t>
+          <t>Spotify Technology SA</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>96990000000</v>
+        <v>99370000000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Spotify Technology SA</t>
+          <t>United Parcel Service Inc</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>96480000000</v>
+        <v>97570000000</v>
       </c>
     </row>
     <row r="110">
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>93160000000</v>
+        <v>93100000000</v>
       </c>
     </row>
     <row r="111">
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>91890000000</v>
+        <v>92910000000</v>
       </c>
     </row>
     <row r="112">
@@ -2166,67 +2166,67 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>91190000000</v>
+        <v>91330000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>3M Co</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>87460000000</v>
+        <v>89950000000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>86990000000</v>
+        <v>89480000000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>3M Co</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>84900000000</v>
+        <v>89020000000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>84340000000</v>
+        <v>87870000000</v>
       </c>
     </row>
     <row r="117">
@@ -2241,67 +2241,67 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>84180000000</v>
+        <v>86250000000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>HCA Healthcare Inc</t>
+          <t>Airbnb Inc</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>83520000000</v>
+        <v>85040000000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Airbnb Inc</t>
+          <t>HCA Healthcare Inc</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>82910000000</v>
+        <v>84780000000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Elevance Health Inc</t>
+          <t>Intercontinental Exchange Inc</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>82260000000</v>
+        <v>82450000000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange Inc</t>
+          <t>Elevance Health Inc</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>80990000000</v>
+        <v>81910000000</v>
       </c>
     </row>
     <row r="122">
@@ -2316,7 +2316,7 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>77010000000</v>
+        <v>81060000000</v>
       </c>
     </row>
     <row r="123">
@@ -2331,82 +2331,82 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>76010000000</v>
+        <v>78730000000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp</t>
+          <t>SLB Ltd</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>75790000000</v>
+        <v>78370000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Cigna Group</t>
+          <t>Northrop Grumman Corp</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>75730000000</v>
+        <v>77030000000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive Co</t>
+          <t>Cigna Group</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>72080000000</v>
+        <v>76600000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>General Motors Company</t>
+          <t>Colgate-Palmolive Co</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>70780000000</v>
+        <v>72620000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SLB Ltd</t>
+          <t>General Motors Company</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>70600000000</v>
+        <v>72510000000</v>
       </c>
     </row>
     <row r="129">
@@ -2421,37 +2421,37 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>68610000000</v>
+        <v>70690000000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>NU</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Nu Holdings Ltd</t>
+          <t>Regeneron Pharmaceuticals Inc</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>68540000000</v>
+        <v>68780000000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals Inc</t>
+          <t>Nu Holdings Ltd</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>68350000000</v>
+        <v>68060000000</v>
       </c>
     </row>
     <row r="132">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>63440000000</v>
+        <v>63570000000</v>
       </c>
     </row>
     <row r="133">
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>61080000000</v>
+        <v>62120000000</v>
       </c>
     </row>
     <row r="134">
@@ -2496,37 +2496,37 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>60810000000</v>
+        <v>61860000000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Occidental Petroleum Corp</t>
+          <t>Ford Motor Co</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>57290000000</v>
+        <v>57260000000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Vistra Corp</t>
+          <t>Occidental Petroleum Corp</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>56980000000</v>
+        <v>56990000000</v>
       </c>
     </row>
     <row r="137">
@@ -2541,22 +2541,22 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>56410000000</v>
+        <v>56700000000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Ford Motor Co</t>
+          <t>Vistra Corp</t>
         </is>
       </c>
       <c r="L138" t="n">
-        <v>56380000000</v>
+        <v>55090000000</v>
       </c>
     </row>
     <row r="139">
@@ -2571,52 +2571,52 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>56050000000</v>
+        <v>49980000000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>PayPal Holdings Inc</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>55610000000</v>
+        <v>49530000000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>PayPal Holdings Inc</t>
+          <t>Edwards Lifesciences Corp</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>49400000000</v>
+        <v>47580000000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences Corp</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>48260000000</v>
+        <v>47250000000</v>
       </c>
     </row>
     <row r="143">
@@ -2631,97 +2631,97 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>45530000000</v>
+        <v>45920000000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Autodesk Inc</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>44250000000</v>
+        <v>44260000000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Autodesk Inc</t>
+          <t>Coinbase Global Inc</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>43310000000</v>
+        <v>41700000000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Coinbase Global Inc</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>42460000000</v>
+        <v>40780000000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Rocket Lab Corp</t>
+          <t>MSCI Inc</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>41870000000</v>
+        <v>40040000000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>41060000000</v>
+        <v>39220000000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>MSCI Inc</t>
+          <t>Rocket Lab Corp</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>40170000000</v>
+        <v>38230000000</v>
       </c>
     </row>
     <row r="150">
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>36500000000</v>
+        <v>36630000000</v>
       </c>
     </row>
     <row r="151">
@@ -2751,22 +2751,22 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>34610000000</v>
+        <v>36060000000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Strategy Inc</t>
+          <t>Workday Inc</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>32810000000</v>
+        <v>33430000000</v>
       </c>
     </row>
     <row r="153">
@@ -2781,22 +2781,22 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>32490000000</v>
+        <v>32480000000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Workday Inc</t>
+          <t>Strategy Inc</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>31580000000</v>
+        <v>32130000000</v>
       </c>
     </row>
     <row r="155">
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>31260000000</v>
+        <v>31590000000</v>
       </c>
     </row>
     <row r="156">
@@ -2826,37 +2826,37 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>29780000000</v>
+        <v>29370000000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Estee Lauder Cos. Inc</t>
+          <t>Twilio Inc</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>28910000000</v>
+        <v>29060000000</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Twilio Inc</t>
+          <t>Estee Lauder Cos. Inc</t>
         </is>
       </c>
       <c r="L158" t="n">
-        <v>28090000000</v>
+        <v>29050000000</v>
       </c>
     </row>
     <row r="159">
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>26650000000</v>
+        <v>27210000000</v>
       </c>
     </row>
     <row r="160">
@@ -2886,7 +2886,7 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>24660000000</v>
+        <v>25800000000</v>
       </c>
     </row>
     <row r="161">
@@ -2901,52 +2901,52 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>23850000000</v>
+        <v>23520000000</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>Zscaler Inc</t>
         </is>
       </c>
       <c r="L162" t="n">
-        <v>22620000000</v>
+        <v>23010000000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Zscaler Inc</t>
+          <t>First Solar Inc</t>
         </is>
       </c>
       <c r="L163" t="n">
-        <v>22590000000</v>
+        <v>21790000000</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>First Solar Inc</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="L164" t="n">
-        <v>22130000000</v>
+        <v>21450000000</v>
       </c>
     </row>
     <row r="165">
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>21360000000</v>
+        <v>21110000000</v>
       </c>
     </row>
     <row r="166">
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>21020000000</v>
+        <v>21060000000</v>
       </c>
     </row>
     <row r="167">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>20280000000</v>
+        <v>20460000000</v>
       </c>
     </row>
     <row r="168">
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>20180000000</v>
+        <v>19470000000</v>
       </c>
     </row>
     <row r="169">
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>17520000000</v>
+        <v>17080000000</v>
       </c>
     </row>
     <row r="170">
@@ -3036,22 +3036,22 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>15460000000</v>
+        <v>15500000000</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>GRAB</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>IREN Ltd</t>
+          <t>Grab Holdings Limited</t>
         </is>
       </c>
       <c r="L171" t="n">
-        <v>14480000000</v>
+        <v>13570000000</v>
       </c>
     </row>
     <row r="172">
@@ -3066,63 +3066,63 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>13530000000</v>
+        <v>13570000000</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>GRAB</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Grab Holdings Limited</t>
+          <t>IREN Ltd</t>
         </is>
       </c>
       <c r="L173" t="n">
-        <v>13530000000</v>
+        <v>13230000000</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>TXRH</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>IonQ Inc</t>
+          <t>Texas Roadhouse Inc</t>
         </is>
       </c>
       <c r="L174" t="n">
-        <v>12720000000</v>
+        <v>12700000000</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>TXRH</t>
+          <t>PINS</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Texas Roadhouse Inc</t>
+          <t>Pinterest Inc</t>
         </is>
       </c>
       <c r="L175" t="n">
-        <v>12550000000</v>
+        <v>12400000000</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>PINS</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Pinterest Inc</t>
+          <t>IonQ Inc</t>
         </is>
       </c>
       <c r="L176" t="n">
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>10540000000</v>
+        <v>10550000000</v>
       </c>
     </row>
     <row r="178">
@@ -3156,37 +3156,37 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>8720000000</v>
+        <v>8500000000</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>PRMB</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Applied Digital Corp</t>
+          <t>Primo Brands Corp</t>
         </is>
       </c>
       <c r="L179" t="n">
-        <v>8540000000</v>
+        <v>8240000000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>PRMB</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Primo Brands Corp</t>
+          <t>Applied Digital Corp</t>
         </is>
       </c>
       <c r="L180" t="n">
-        <v>8270000000</v>
+        <v>7770000000</v>
       </c>
     </row>
     <row r="181">
@@ -3201,37 +3201,37 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>8030000000</v>
+        <v>7570000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>OKLO</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Oklo Inc</t>
+          <t>Zillow Group Inc</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>7660000000</v>
+        <v>7040000000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>HIMS</t>
+          <t>OKLO</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Hims &amp; Hers Health Inc</t>
+          <t>Oklo Inc</t>
         </is>
       </c>
       <c r="L183" t="n">
-        <v>7580000000</v>
+        <v>7000000000</v>
       </c>
     </row>
     <row r="184">
@@ -3246,37 +3246,37 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>6950000000</v>
+        <v>6930000000</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>MBLY</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Zillow Group Inc</t>
+          <t>Mobileye Global Inc</t>
         </is>
       </c>
       <c r="L185" t="n">
-        <v>6770000000</v>
+        <v>6780000000</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>MBLY</t>
+          <t>HIMS</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Mobileye Global Inc</t>
+          <t>Hims &amp; Hers Health Inc</t>
         </is>
       </c>
       <c r="L186" t="n">
-        <v>6290000000</v>
+        <v>6500000000</v>
       </c>
     </row>
     <row r="187">
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>5960000000</v>
+        <v>6220000000</v>
       </c>
     </row>
     <row r="188">
@@ -3306,37 +3306,37 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>4940000000</v>
+        <v>4700000000</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>MARA</t>
+          <t>LMND</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>MARA Holdings Inc</t>
+          <t>Lemonade Inc</t>
         </is>
       </c>
       <c r="L189" t="n">
-        <v>4870000000</v>
+        <v>4620000000</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>LMND</t>
+          <t>MARA</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Lemonade Inc</t>
+          <t>MARA Holdings Inc</t>
         </is>
       </c>
       <c r="L190" t="n">
-        <v>4660000000</v>
+        <v>4620000000</v>
       </c>
     </row>
     <row r="191">
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>4580000000</v>
+        <v>4490000000</v>
       </c>
     </row>
     <row r="192">
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>4520000000</v>
+        <v>4440000000</v>
       </c>
     </row>
     <row r="193">
@@ -3381,37 +3381,37 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3360000000</v>
+        <v>3220000000</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>FSLY</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>NuScale Power Corp</t>
+          <t>Fastly Inc</t>
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3220000000</v>
+        <v>3170000000</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>FSLY</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Fastly Inc</t>
+          <t>NuScale Power Corp</t>
         </is>
       </c>
       <c r="L195" t="n">
-        <v>3040000000</v>
+        <v>2960000000</v>
       </c>
     </row>
     <row r="196">
@@ -3426,52 +3426,52 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2710000000</v>
+        <v>2740000000</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>FLNC</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Fluence Energy Inc</t>
+          <t>Upstart Holdings Inc</t>
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2660000000</v>
+        <v>2580000000</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>TMDX</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Upstart Holdings Inc</t>
+          <t>Transmedics Group Inc</t>
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2640000000</v>
+        <v>2500000000</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>TMDX</t>
+          <t>FLNC</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Transmedics Group Inc</t>
+          <t>Fluence Energy Inc</t>
         </is>
       </c>
       <c r="L199" t="n">
-        <v>2460000000</v>
+        <v>2480000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1770000000</v>
+        <v>1680000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1560000000</v>
+        <v>1580000000</v>
       </c>
     </row>
     <row r="202">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>1030000000</v>
+        <v>925290000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>879160000</v>
+        <v>811980000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>508650000</v>
+        <v>487250000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3880100000000</v>
+        <v>3888810000000</v>
       </c>
     </row>
     <row r="8">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1175650000000</v>
+        <v>1236330000000</v>
       </c>
     </row>
     <row r="14">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>960900000000</v>
+        <v>962040000000</v>
       </c>
     </row>
     <row r="17">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>634060000000</v>
+        <v>634770000000</v>
       </c>
     </row>
     <row r="24">
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>286560000000</v>
+        <v>286790000000</v>
       </c>
     </row>
     <row r="46">
@@ -1431,37 +1431,37 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>201310000000</v>
+        <v>201800000000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>T-Mobile US Inc</t>
+          <t>Verizon Communications Inc</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>194890000000</v>
+        <v>193660000000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc</t>
+          <t>T-Mobile US Inc</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>193660000000</v>
+        <v>193180000000</v>
       </c>
     </row>
     <row r="66">
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>193280000000</v>
+        <v>193060000000</v>
       </c>
     </row>
     <row r="67">
@@ -1722,31 +1722,31 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>Blackstone Inc</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>160550000000</v>
+        <v>161700000000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Blackstone Inc</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>160430000000</v>
+        <v>160550000000</v>
       </c>
     </row>
     <row r="85">
@@ -1836,7 +1836,7 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>134330000000</v>
+        <v>134460000000</v>
       </c>
     </row>
     <row r="91">
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>99650000000</v>
+        <v>99670000000</v>
       </c>
     </row>
     <row r="108">
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>7040000000</v>
+        <v>7030000000</v>
       </c>
     </row>
     <row r="183">
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>6780000000</v>
+        <v>6840000000</v>
       </c>
     </row>
     <row r="186">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4891180000000</v>
+        <v>4948320000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5005530000000</v>
+        <v>4755540000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3888810000000</v>
+        <v>3998410000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2835430000000</v>
+        <v>2890400000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2496830000000</v>
+        <v>2489090000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2092280000000</v>
+        <v>2069870000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1817020000000</v>
+        <v>1823200000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1510840000000</v>
+        <v>1507490000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1236330000000</v>
+        <v>1221280000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1126350000000</v>
+        <v>1127760000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1040110000000</v>
+        <v>1016680000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>962040000000</v>
+        <v>966410000000</v>
       </c>
     </row>
     <row r="17">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>946430000000</v>
+        <v>954440000000</v>
       </c>
     </row>
     <row r="18">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>871170000000</v>
+        <v>889240000000</v>
       </c>
     </row>
     <row r="19">
@@ -771,67 +771,67 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>851090000000</v>
+        <v>807070000000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ASML Holding NV</t>
+          <t>Visa Inc</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>677220000000</v>
+        <v>683050000000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Visa Inc</t>
+          <t>ExxonMobil Holdings Corp</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>670260000000</v>
+        <v>641440000000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ExxonMobil Holdings Corp</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>650430000000</v>
+        <v>640910000000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>ASML Holding NV</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>634770000000</v>
+        <v>637970000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>476830000000</v>
+        <v>487480000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>458240000000</v>
+        <v>453910000000</v>
       </c>
     </row>
     <row r="26">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>449990000000</v>
+        <v>451570000000</v>
       </c>
     </row>
     <row r="27">
@@ -891,37 +891,37 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>440340000000</v>
+        <v>440910000000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Applied Materials Inc</t>
+          <t>Costco Wholesale Corp</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>425760000000</v>
+        <v>422010000000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Costco Wholesale Corp</t>
+          <t>Applied Materials Inc</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>414670000000</v>
+        <v>410390000000</v>
       </c>
     </row>
     <row r="30">
@@ -936,67 +936,67 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>409380000000</v>
+        <v>402270000000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Chevron Corp</t>
+          <t>Unitedhealth Group Inc</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>387940000000</v>
+        <v>379280000000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Unitedhealth Group Inc</t>
+          <t>Chevron Corp</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>382090000000</v>
+        <v>378400000000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Lam Research Corp</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>381690000000</v>
+        <v>375190000000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Lam Research Corp</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>367020000000</v>
+        <v>364680000000</v>
       </c>
     </row>
     <row r="35">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>353880000000</v>
+        <v>361710000000</v>
       </c>
     </row>
     <row r="36">
@@ -1026,52 +1026,52 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>343260000000</v>
+        <v>346100000000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Oracle Corp</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>338300000000</v>
+        <v>345370000000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Home Depot Inc</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>332020000000</v>
+        <v>338420000000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Oracle Corp</t>
+          <t>Home Depot Inc</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>331230000000</v>
+        <v>335120000000</v>
       </c>
     </row>
     <row r="40">
@@ -1086,82 +1086,82 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>323720000000</v>
+        <v>322950000000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Goldman Sachs Group Inc</t>
+          <t>Palantir Technologies Inc</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>313070000000</v>
+        <v>315320000000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Philip Morris International Inc</t>
+          <t>Goldman Sachs Group Inc</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>300800000000</v>
+        <v>309240000000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc</t>
+          <t>Philip Morris International Inc</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>294680000000</v>
+        <v>304950000000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Netflix Inc</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>291850000000</v>
+        <v>294380000000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Netflix Inc</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>286790000000</v>
+        <v>293140000000</v>
       </c>
     </row>
     <row r="46">
@@ -1176,127 +1176,127 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>283750000000</v>
+        <v>285770000000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>283620000000</v>
+        <v>283380000000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>276650000000</v>
+        <v>276760000000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>KLA Corp</t>
+          <t>Alibaba Group Holding Ltd ADR</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>275000000000</v>
+        <v>275660000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>Wells Fargo &amp; Co</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>270260000000</v>
+        <v>267060000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Alibaba Group Holding Ltd ADR</t>
+          <t>KLA Corp</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>268810000000</v>
+        <v>265640000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Co</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>264120000000</v>
+        <v>265420000000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>Astrazeneca plc</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>263890000000</v>
+        <v>263090000000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Astrazeneca plc</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>262500000000</v>
+        <v>258620000000</v>
       </c>
     </row>
     <row r="55">
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>254440000000</v>
+        <v>254290000000</v>
       </c>
     </row>
     <row r="56">
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>246410000000</v>
+        <v>240810000000</v>
       </c>
     </row>
     <row r="57">
@@ -1341,67 +1341,67 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>236980000000</v>
+        <v>234550000000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Citigroup Inc</t>
+          <t>American Express Co</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>226690000000</v>
+        <v>228850000000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>American Express Co</t>
+          <t>Citigroup Inc</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>222550000000</v>
+        <v>228250000000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>Thermo Fisher Scientific Inc</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>212740000000</v>
+        <v>207930000000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc</t>
+          <t>International Business Machines Corp</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>211180000000</v>
+        <v>203760000000</v>
       </c>
     </row>
     <row r="62">
@@ -1416,22 +1416,22 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>202950000000</v>
+        <v>203070000000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>International Business Machines Corp</t>
+          <t>Sap SE ADR</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>201800000000</v>
+        <v>199660000000</v>
       </c>
     </row>
     <row r="64">
@@ -1446,127 +1446,127 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>193660000000</v>
+        <v>197590000000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>T-Mobile US Inc</t>
+          <t>Toyota Motor Corp ADR</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>193180000000</v>
+        <v>193820000000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>McDonald's Corp</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>193060000000</v>
+        <v>192310000000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Toyota Motor Corp ADR</t>
+          <t>PepsiCo Inc</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>188780000000</v>
+        <v>190800000000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>McDonald's Corp</t>
+          <t>T-Mobile US Inc</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>188110000000</v>
+        <v>190090000000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NextEra Energy Inc</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>187250000000</v>
+        <v>189290000000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Sap SE ADR</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>186810000000</v>
+        <v>187190000000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>NextEra Energy Inc</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>186630000000</v>
+        <v>185260000000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PepsiCo Inc</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>186500000000</v>
+        <v>183400000000</v>
       </c>
     </row>
     <row r="73">
@@ -1581,67 +1581,67 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>179510000000</v>
+        <v>182000000000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>Charles Schwab Corp</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>179170000000</v>
+        <v>181180000000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Charles Schwab Corp</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>177340000000</v>
+        <v>179220000000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>Blackrock Inc</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>175990000000</v>
+        <v>172710000000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Blackrock Inc</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>171650000000</v>
+        <v>171620000000</v>
       </c>
     </row>
     <row r="78">
@@ -1656,67 +1656,67 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>169560000000</v>
+        <v>168720000000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc</t>
+          <t>Walt Disney Co</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>165350000000</v>
+        <v>167830000000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Boeing Co</t>
+          <t>AT&amp;T Inc</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>165170000000</v>
+        <v>167340000000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Walt Disney Co</t>
+          <t>Novo Nordisk ADR</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>164710000000</v>
+        <v>166790000000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Novo Nordisk ADR</t>
+          <t>Boeing Co</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>163770000000</v>
+        <v>166730000000</v>
       </c>
     </row>
     <row r="83">
@@ -1731,292 +1731,292 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>161700000000</v>
+        <v>164930000000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>Shopify Inc</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>160550000000</v>
+        <v>164650000000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Shopify Inc</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>147610000000</v>
+        <v>162050000000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>140550000000</v>
+        <v>144740000000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Chubb Limited</t>
+          <t>Salesforce Inc</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>139530000000</v>
+        <v>142180000000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>137510000000</v>
+        <v>140200000000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Danaher Corp</t>
+          <t>Chubb Limited</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>134620000000</v>
+        <v>139210000000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corp</t>
+          <t>Uber Technologies Inc</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>134460000000</v>
+        <v>138790000000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Uber Technologies Inc</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>134230000000</v>
+        <v>138650000000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Salesforce Inc</t>
+          <t>Danaher Corp</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>134040000000</v>
+        <v>138140000000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>Lockheed Martin Corp</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>131680000000</v>
+        <v>133860000000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Co</t>
+          <t>S&amp;P Global Inc</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>126790000000</v>
+        <v>130190000000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>S&amp;P Global Inc</t>
+          <t>Bristol-Myers Squibb Co</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>126210000000</v>
+        <v>127750000000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Corning Inc</t>
+          <t>Progressive Corp</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>126210000000</v>
+        <v>126080000000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Progressive Corp</t>
+          <t>Intuitive Surgical Inc</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>124950000000</v>
+        <v>126060000000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Altria Group Inc</t>
+          <t>Corning Inc</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>121890000000</v>
+        <v>123380000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Intuitive Surgical Inc</t>
+          <t>Altria Group Inc</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>119230000000</v>
+        <v>121720000000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Starbucks Corp</t>
+          <t>PDD Holdings Inc ADR</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>117670000000</v>
+        <v>120780000000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PDD Holdings Inc ADR</t>
+          <t>Lowe's Cos. Inc</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>117660000000</v>
+        <v>118620000000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Lowe's Cos. Inc</t>
+          <t>Starbucks Corp</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>116430000000</v>
+        <v>118130000000</v>
       </c>
     </row>
     <row r="103">
@@ -2031,37 +2031,37 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>111530000000</v>
+        <v>110470000000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Equinix Inc</t>
+          <t>Medtronic Plc</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>106930000000</v>
+        <v>107810000000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Medtronic Plc</t>
+          <t>Equinix Inc</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>106510000000</v>
+        <v>103240000000</v>
       </c>
     </row>
     <row r="106">
@@ -2076,37 +2076,37 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>99970000000</v>
+        <v>101920000000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>Spotify Technology SA</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>99670000000</v>
+        <v>101850000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Spotify Technology SA</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>99370000000</v>
+        <v>98920000000</v>
       </c>
     </row>
     <row r="109">
@@ -2121,52 +2121,52 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>97570000000</v>
+        <v>96010000000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>Snowflake Inc</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>93100000000</v>
+        <v>94590000000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Snowflake Inc</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>92910000000</v>
+        <v>94510000000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>MercadoLibre Inc</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>91330000000</v>
+        <v>94320000000</v>
       </c>
     </row>
     <row r="113">
@@ -2181,22 +2181,22 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>89950000000</v>
+        <v>94280000000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>MercadoLibre Inc</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>89480000000</v>
+        <v>92260000000</v>
       </c>
     </row>
     <row r="115">
@@ -2211,7 +2211,7 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>89020000000</v>
+        <v>91920000000</v>
       </c>
     </row>
     <row r="116">
@@ -2226,37 +2226,37 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>87870000000</v>
+        <v>89650000000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>MMC</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Marsh</t>
+          <t>Airbnb Inc</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>86250000000</v>
+        <v>88510000000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>MMC</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Airbnb Inc</t>
+          <t>Marsh</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>85040000000</v>
+        <v>87480000000</v>
       </c>
     </row>
     <row r="119">
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>84780000000</v>
+        <v>86430000000</v>
       </c>
     </row>
     <row r="120">
@@ -2286,37 +2286,37 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>82450000000</v>
+        <v>84110000000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Elevance Health Inc</t>
+          <t>Intuit Inc</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>81910000000</v>
+        <v>83130000000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Intuit Inc</t>
+          <t>Elevance Health Inc</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>81060000000</v>
+        <v>82050000000</v>
       </c>
     </row>
     <row r="123">
@@ -2331,37 +2331,37 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>78730000000</v>
+        <v>81810000000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>SLB Ltd</t>
+          <t>Northrop Grumman Corp</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>78370000000</v>
+        <v>77790000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp</t>
+          <t>SLB Ltd</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>77030000000</v>
+        <v>77040000000</v>
       </c>
     </row>
     <row r="126">
@@ -2376,37 +2376,37 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>76600000000</v>
+        <v>76980000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive Co</t>
+          <t>General Motors Company</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>72620000000</v>
+        <v>76370000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>General Motors Company</t>
+          <t>Colgate-Palmolive Co</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>72510000000</v>
+        <v>73600000000</v>
       </c>
     </row>
     <row r="129">
@@ -2421,37 +2421,37 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>70690000000</v>
+        <v>71630000000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals Inc</t>
+          <t>Nu Holdings Ltd</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>68780000000</v>
+        <v>70190000000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>NU</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Nu Holdings Ltd</t>
+          <t>Regeneron Pharmaceuticals Inc</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>68060000000</v>
+        <v>69950000000</v>
       </c>
     </row>
     <row r="132">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>63570000000</v>
+        <v>67080000000</v>
       </c>
     </row>
     <row r="133">
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>62120000000</v>
+        <v>63740000000</v>
       </c>
     </row>
     <row r="134">
@@ -2496,52 +2496,52 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>61860000000</v>
+        <v>62510000000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Ford Motor Co</t>
+          <t>Sea Ltd ADR</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>57260000000</v>
+        <v>59180000000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Occidental Petroleum Corp</t>
+          <t>Ford Motor Co</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>56990000000</v>
+        <v>58500000000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Sea Ltd ADR</t>
+          <t>Occidental Petroleum Corp</t>
         </is>
       </c>
       <c r="L137" t="n">
-        <v>56700000000</v>
+        <v>54640000000</v>
       </c>
     </row>
     <row r="138">
@@ -2556,97 +2556,97 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>55090000000</v>
+        <v>52960000000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Astera Labs Inc</t>
+          <t>PayPal Holdings Inc</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>49980000000</v>
+        <v>49460000000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>PayPal Holdings Inc</t>
+          <t>Astera Labs Inc</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>49530000000</v>
+        <v>48430000000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences Corp</t>
+          <t>Block Inc</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>47580000000</v>
+        <v>48350000000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Edwards Lifesciences Corp</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>47250000000</v>
+        <v>47810000000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Block Inc</t>
+          <t>Autodesk Inc</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>45920000000</v>
+        <v>47670000000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Autodesk Inc</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>44260000000</v>
+        <v>47280000000</v>
       </c>
     </row>
     <row r="145">
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>41700000000</v>
+        <v>44130000000</v>
       </c>
     </row>
     <row r="146">
@@ -2676,7 +2676,7 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>40780000000</v>
+        <v>42590000000</v>
       </c>
     </row>
     <row r="147">
@@ -2691,37 +2691,37 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>40040000000</v>
+        <v>41510000000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Rocket Lab Corp</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>39220000000</v>
+        <v>40040000000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Rocket Lab Corp</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>38230000000</v>
+        <v>38620000000</v>
       </c>
     </row>
     <row r="150">
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>36630000000</v>
+        <v>37550000000</v>
       </c>
     </row>
     <row r="151">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>36060000000</v>
+        <v>37140000000</v>
       </c>
     </row>
     <row r="152">
@@ -2766,37 +2766,37 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>33430000000</v>
+        <v>36440000000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>RDDT</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Reddit Inc</t>
+          <t>Strategy Inc</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>32480000000</v>
+        <v>34570000000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>RDDT</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Strategy Inc</t>
+          <t>Reddit Inc</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>32130000000</v>
+        <v>34500000000</v>
       </c>
     </row>
     <row r="155">
@@ -2811,22 +2811,22 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>31590000000</v>
+        <v>32250000000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Illumina Inc</t>
+          <t>Estee Lauder Cos. Inc</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>29370000000</v>
+        <v>30100000000</v>
       </c>
     </row>
     <row r="157">
@@ -2841,22 +2841,22 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>29060000000</v>
+        <v>29520000000</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Estee Lauder Cos. Inc</t>
+          <t>Illumina Inc</t>
         </is>
       </c>
       <c r="L158" t="n">
-        <v>29050000000</v>
+        <v>28670000000</v>
       </c>
     </row>
     <row r="159">
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>27210000000</v>
+        <v>27890000000</v>
       </c>
     </row>
     <row r="160">
@@ -2886,7 +2886,7 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>25800000000</v>
+        <v>26750000000</v>
       </c>
     </row>
     <row r="161">
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>23520000000</v>
+        <v>24460000000</v>
       </c>
     </row>
     <row r="162">
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>23010000000</v>
+        <v>23820000000</v>
       </c>
     </row>
     <row r="163">
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>21790000000</v>
+        <v>22120000000</v>
       </c>
     </row>
     <row r="164">
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>21450000000</v>
+        <v>22070000000</v>
       </c>
     </row>
     <row r="165">
@@ -2961,37 +2961,37 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>21110000000</v>
+        <v>21650000000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ROKU</t>
+          <t>DKNG</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Roku Inc</t>
+          <t>DraftKings Inc</t>
         </is>
       </c>
       <c r="L166" t="n">
-        <v>21060000000</v>
+        <v>21440000000</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>DKNG</t>
+          <t>ROKU</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>DraftKings Inc</t>
+          <t>Roku Inc</t>
         </is>
       </c>
       <c r="L167" t="n">
-        <v>20460000000</v>
+        <v>21200000000</v>
       </c>
     </row>
     <row r="168">
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>19470000000</v>
+        <v>19280000000</v>
       </c>
     </row>
     <row r="169">
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>17080000000</v>
+        <v>18090000000</v>
       </c>
     </row>
     <row r="170">
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>15500000000</v>
+        <v>16320000000</v>
       </c>
     </row>
     <row r="171">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>13570000000</v>
+        <v>13730000000</v>
       </c>
     </row>
     <row r="172">
@@ -3066,22 +3066,22 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>13570000000</v>
+        <v>13730000000</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>IREN Ltd</t>
+          <t>IonQ Inc</t>
         </is>
       </c>
       <c r="L173" t="n">
-        <v>13230000000</v>
+        <v>13410000000</v>
       </c>
     </row>
     <row r="174">
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>12700000000</v>
+        <v>13210000000</v>
       </c>
     </row>
     <row r="175">
@@ -3111,22 +3111,22 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>12400000000</v>
+        <v>13160000000</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>IonQ Inc</t>
+          <t>IREN Ltd</t>
         </is>
       </c>
       <c r="L176" t="n">
-        <v>12260000000</v>
+        <v>12950000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>10550000000</v>
+        <v>10830000000</v>
       </c>
     </row>
     <row r="178">
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>8500000000</v>
+        <v>8540000000</v>
       </c>
     </row>
     <row r="179">
@@ -3171,112 +3171,112 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>8240000000</v>
+        <v>8290000000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Applied Digital Corp</t>
+          <t>AeroVironment Inc</t>
         </is>
       </c>
       <c r="L180" t="n">
-        <v>7770000000</v>
+        <v>7810000000</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>AeroVironment Inc</t>
+          <t>Applied Digital Corp</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>7570000000</v>
+        <v>7540000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Zillow Group Inc</t>
+          <t>Celsius Holdings Inc</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>7030000000</v>
+        <v>7360000000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>OKLO</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Oklo Inc</t>
+          <t>Zillow Group Inc</t>
         </is>
       </c>
       <c r="L183" t="n">
-        <v>7000000000</v>
+        <v>7320000000</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>OKLO</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Celsius Holdings Inc</t>
+          <t>Oklo Inc</t>
         </is>
       </c>
       <c r="L184" t="n">
-        <v>6930000000</v>
+        <v>7270000000</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>MBLY</t>
+          <t>HIMS</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Mobileye Global Inc</t>
+          <t>Hims &amp; Hers Health Inc</t>
         </is>
       </c>
       <c r="L185" t="n">
-        <v>6840000000</v>
+        <v>7000000000</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>HIMS</t>
+          <t>MBLY</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Hims &amp; Hers Health Inc</t>
+          <t>Mobileye Global Inc</t>
         </is>
       </c>
       <c r="L186" t="n">
-        <v>6500000000</v>
+        <v>6810000000</v>
       </c>
     </row>
     <row r="187">
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>4700000000</v>
+        <v>5200000000</v>
       </c>
     </row>
     <row r="189">
@@ -3321,22 +3321,22 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>4620000000</v>
+        <v>4760000000</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>MARA</t>
+          <t>ONDS</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>MARA Holdings Inc</t>
+          <t>Ondas Inc</t>
         </is>
       </c>
       <c r="L190" t="n">
-        <v>4620000000</v>
+        <v>4570000000</v>
       </c>
     </row>
     <row r="191">
@@ -3351,22 +3351,22 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>4490000000</v>
+        <v>4510000000</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ONDS</t>
+          <t>MARA</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Ondas Inc</t>
+          <t>MARA Holdings Inc</t>
         </is>
       </c>
       <c r="L192" t="n">
-        <v>4440000000</v>
+        <v>4490000000</v>
       </c>
     </row>
     <row r="193">
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3220000000</v>
+        <v>3460000000</v>
       </c>
     </row>
     <row r="194">
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3170000000</v>
+        <v>3140000000</v>
       </c>
     </row>
     <row r="195">
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>2960000000</v>
+        <v>3120000000</v>
       </c>
     </row>
     <row r="196">
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2740000000</v>
+        <v>2830000000</v>
       </c>
     </row>
     <row r="197">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2580000000</v>
+        <v>2630000000</v>
       </c>
     </row>
     <row r="198">
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2500000000</v>
+        <v>2570000000</v>
       </c>
     </row>
     <row r="199">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>2480000000</v>
+        <v>2490000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1680000000</v>
+        <v>1800000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1580000000</v>
+        <v>1610000000</v>
       </c>
     </row>
     <row r="202">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1270000000</v>
+        <v>1370000000</v>
       </c>
     </row>
     <row r="203">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>925290000</v>
+        <v>984550000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>811980000</v>
+        <v>874480000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>487250000</v>
+        <v>509910000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4948320000000</v>
+        <v>4994880000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4755540000000</v>
+        <v>4767640000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3998410000000</v>
+        <v>4067630000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2890400000000</v>
+        <v>2921970000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2489090000000</v>
+        <v>2483390000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2069870000000</v>
+        <v>2034710000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1823200000000</v>
+        <v>1812210000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1507490000000</v>
+        <v>1506330000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1221280000000</v>
+        <v>1214250000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,52 +696,52 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1127760000000</v>
+        <v>1149550000000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>BRK-B</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Micron Technology Inc</t>
+          <t>Berkshire Hathaway Inc</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1016680000000</v>
+        <v>994610000000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BRK-B</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Inc</t>
+          <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>966410000000</v>
+        <v>957420000000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co</t>
+          <t>Micron Technology Inc</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>954440000000</v>
+        <v>926700000000</v>
       </c>
     </row>
     <row r="18">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>889240000000</v>
+        <v>900060000000</v>
       </c>
     </row>
     <row r="19">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>807070000000</v>
+        <v>741300000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,37 +786,37 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>683050000000</v>
+        <v>690700000000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ExxonMobil Holdings Corp</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>641440000000</v>
+        <v>642790000000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>ExxonMobil Holdings Corp</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>640910000000</v>
+        <v>634270000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>637970000000</v>
+        <v>610100000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>487480000000</v>
+        <v>497240000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>453910000000</v>
+        <v>465020000000</v>
       </c>
     </row>
     <row r="26">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>451570000000</v>
+        <v>455550000000</v>
       </c>
     </row>
     <row r="27">
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>440910000000</v>
+        <v>444390000000</v>
       </c>
     </row>
     <row r="28">
@@ -906,22 +906,22 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>422010000000</v>
+        <v>428660000000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Applied Materials Inc</t>
+          <t>Unitedhealth Group Inc</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>410390000000</v>
+        <v>389400000000</v>
       </c>
     </row>
     <row r="30">
@@ -936,37 +936,37 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>402270000000</v>
+        <v>387330000000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Unitedhealth Group Inc</t>
+          <t>Coca-Cola Co</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>379280000000</v>
+        <v>379780000000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Chevron Corp</t>
+          <t>Applied Materials Inc</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>378400000000</v>
+        <v>378290000000</v>
       </c>
     </row>
     <row r="33">
@@ -981,97 +981,97 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>375190000000</v>
+        <v>377250000000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Lam Research Corp</t>
+          <t>Chevron Corp</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>364680000000</v>
+        <v>373580000000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Coca-Cola Co</t>
+          <t>Procter &amp; Gamble Co</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>361710000000</v>
+        <v>346680000000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble Co</t>
+          <t>Oracle Corp</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>346100000000</v>
+        <v>345540000000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Oracle Corp</t>
+          <t>Home Depot Inc</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>345370000000</v>
+        <v>343480000000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Lam Research Corp</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>338420000000</v>
+        <v>337170000000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Home Depot Inc</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>335120000000</v>
+        <v>333720000000</v>
       </c>
     </row>
     <row r="40">
@@ -1086,22 +1086,22 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>322950000000</v>
+        <v>325570000000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc</t>
+          <t>Philip Morris International Inc</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>315320000000</v>
+        <v>311990000000</v>
       </c>
     </row>
     <row r="42">
@@ -1116,52 +1116,52 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>309240000000</v>
+        <v>304840000000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Philip Morris International Inc</t>
+          <t>Netflix Inc</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>304950000000</v>
+        <v>301430000000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Palantir Technologies Inc</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>294380000000</v>
+        <v>296140000000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Netflix Inc</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>293140000000</v>
+        <v>294590000000</v>
       </c>
     </row>
     <row r="46">
@@ -1176,142 +1176,142 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>285770000000</v>
+        <v>292610000000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>Alibaba Group Holding Ltd ADR</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>283380000000</v>
+        <v>276120000000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>Astrazeneca plc</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>276760000000</v>
+        <v>267490000000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Alibaba Group Holding Ltd ADR</t>
+          <t>Wells Fargo &amp; Co</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>275660000000</v>
+        <v>265840000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Co</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>267060000000</v>
+        <v>260400000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>KLA Corp</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>265640000000</v>
+        <v>259990000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>265420000000</v>
+        <v>254190000000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Astrazeneca plc</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>263090000000</v>
+        <v>253030000000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>258620000000</v>
+        <v>251250000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>KLA Corp</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>254290000000</v>
+        <v>249240000000</v>
       </c>
     </row>
     <row r="56">
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>240810000000</v>
+        <v>240330000000</v>
       </c>
     </row>
     <row r="57">
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>234550000000</v>
+        <v>236470000000</v>
       </c>
     </row>
     <row r="58">
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>228850000000</v>
+        <v>227330000000</v>
       </c>
     </row>
     <row r="59">
@@ -1371,37 +1371,37 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>228250000000</v>
+        <v>227170000000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc</t>
+          <t>International Business Machines Corp</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>207930000000</v>
+        <v>214380000000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>International Business Machines Corp</t>
+          <t>Thermo Fisher Scientific Inc</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>203760000000</v>
+        <v>214210000000</v>
       </c>
     </row>
     <row r="62">
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>203070000000</v>
+        <v>212160000000</v>
       </c>
     </row>
     <row r="63">
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>199660000000</v>
+        <v>206800000000</v>
       </c>
     </row>
     <row r="64">
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>197590000000</v>
+        <v>201220000000</v>
       </c>
     </row>
     <row r="65">
@@ -1461,22 +1461,22 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>193820000000</v>
+        <v>198230000000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>McDonald's Corp</t>
+          <t>T-Mobile US Inc</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>192310000000</v>
+        <v>195640000000</v>
       </c>
     </row>
     <row r="67">
@@ -1491,52 +1491,52 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>190800000000</v>
+        <v>194990000000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>T-Mobile US Inc</t>
+          <t>McDonald's Corp</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>190090000000</v>
+        <v>193980000000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>189290000000</v>
+        <v>187230000000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>187190000000</v>
+        <v>186840000000</v>
       </c>
     </row>
     <row r="71">
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>185260000000</v>
+        <v>186200000000</v>
       </c>
     </row>
     <row r="72">
@@ -1566,157 +1566,157 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>183400000000</v>
+        <v>185120000000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Charles Schwab Corp</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>182000000000</v>
+        <v>184300000000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Charles Schwab Corp</t>
+          <t>Blackrock Inc</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>181180000000</v>
+        <v>178460000000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>Boeing Co</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>179220000000</v>
+        <v>174660000000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Blackrock Inc</t>
+          <t>Deere &amp; Co</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>172710000000</v>
+        <v>172720000000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>Walt Disney Co</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>171620000000</v>
+        <v>171720000000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Deere &amp; Co</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>168720000000</v>
+        <v>171680000000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Walt Disney Co</t>
+          <t>Novo Nordisk ADR</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>167830000000</v>
+        <v>171120000000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc</t>
+          <t>Shopify Inc</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>167340000000</v>
+        <v>169060000000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Novo Nordisk ADR</t>
+          <t>AT&amp;T Inc</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>166790000000</v>
+        <v>168980000000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Boeing Co</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>166730000000</v>
+        <v>166770000000</v>
       </c>
     </row>
     <row r="83">
@@ -1731,37 +1731,37 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>164930000000</v>
+        <v>166550000000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Shopify Inc</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>164650000000</v>
+        <v>162320000000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>162050000000</v>
+        <v>159760000000</v>
       </c>
     </row>
     <row r="86">
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>144740000000</v>
+        <v>154440000000</v>
       </c>
     </row>
     <row r="87">
@@ -1791,22 +1791,22 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>142180000000</v>
+        <v>148650000000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Uber Technologies Inc</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>140200000000</v>
+        <v>144000000000</v>
       </c>
     </row>
     <row r="89">
@@ -1821,37 +1821,37 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>139210000000</v>
+        <v>140990000000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Uber Technologies Inc</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>138790000000</v>
+        <v>140500000000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>138650000000</v>
+        <v>140060000000</v>
       </c>
     </row>
     <row r="92">
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>138140000000</v>
+        <v>139930000000</v>
       </c>
     </row>
     <row r="93">
@@ -1881,97 +1881,97 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>133860000000</v>
+        <v>134160000000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>S&amp;P Global Inc</t>
+          <t>Bristol-Myers Squibb Co</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>130190000000</v>
+        <v>129880000000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Co</t>
+          <t>Progressive Corp</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>127750000000</v>
+        <v>128270000000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Progressive Corp</t>
+          <t>Intuitive Surgical Inc</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>126080000000</v>
+        <v>127820000000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Intuitive Surgical Inc</t>
+          <t>S&amp;P Global Inc</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>126060000000</v>
+        <v>125610000000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Corning Inc</t>
+          <t>Altria Group Inc</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>123380000000</v>
+        <v>124940000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Altria Group Inc</t>
+          <t>Lowe's Cos. Inc</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>121720000000</v>
+        <v>122370000000</v>
       </c>
     </row>
     <row r="100">
@@ -1986,412 +1986,412 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>120780000000</v>
+        <v>122000000000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Lowe's Cos. Inc</t>
+          <t>Starbucks Corp</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>118620000000</v>
+        <v>117500000000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Starbucks Corp</t>
+          <t>Medtronic Plc</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>118130000000</v>
+        <v>111210000000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>Corning Inc</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>110470000000</v>
+        <v>108450000000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Medtronic Plc</t>
+          <t>Automatic Data Processing Inc</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>107810000000</v>
+        <v>105600000000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Equinix Inc</t>
+          <t>Spotify Technology SA</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>103240000000</v>
+        <v>105320000000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>101920000000</v>
+        <v>103540000000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Spotify Technology SA</t>
+          <t>Equinix Inc</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>101850000000</v>
+        <v>102060000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>98920000000</v>
+        <v>100760000000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>United Parcel Service Inc</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>96010000000</v>
+        <v>100380000000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Snowflake Inc</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>94590000000</v>
+        <v>99050000000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>MercadoLibre Inc</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>94510000000</v>
+        <v>94420000000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>3M Co</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>94320000000</v>
+        <v>94110000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>94280000000</v>
+        <v>93790000000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>MercadoLibre Inc</t>
+          <t>Snowflake Inc</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>92260000000</v>
+        <v>93710000000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>3M Co</t>
+          <t>HCA Healthcare Inc</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>91920000000</v>
+        <v>92770000000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>Airbnb Inc</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>89650000000</v>
+        <v>92280000000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>MMC</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Airbnb Inc</t>
+          <t>Marsh</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>88510000000</v>
+        <v>91720000000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>MMC</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Marsh</t>
+          <t>United Parcel Service Inc</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>87480000000</v>
+        <v>89700000000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>HCA Healthcare Inc</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>86430000000</v>
+        <v>89300000000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange Inc</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>84110000000</v>
+        <v>86490000000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Intuit Inc</t>
+          <t>Intercontinental Exchange Inc</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>83130000000</v>
+        <v>86370000000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Elevance Health Inc</t>
+          <t>Intuit Inc</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>82050000000</v>
+        <v>85610000000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Elevance Health Inc</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>81810000000</v>
+        <v>83650000000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp</t>
+          <t>Cigna Group</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>77790000000</v>
+        <v>79640000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>SLB Ltd</t>
+          <t>General Motors Company</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>77040000000</v>
+        <v>79230000000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Cigna Group</t>
+          <t>Northrop Grumman Corp</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>76980000000</v>
+        <v>78020000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>General Motors Company</t>
+          <t>SLB Ltd</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>76370000000</v>
+        <v>74720000000</v>
       </c>
     </row>
     <row r="128">
@@ -2406,52 +2406,52 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>73600000000</v>
+        <v>74200000000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Apollo Global Management Inc</t>
+          <t>Regeneron Pharmaceuticals Inc</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>71630000000</v>
+        <v>72880000000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>NU</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Nu Holdings Ltd</t>
+          <t>Apollo Global Management Inc</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>70190000000</v>
+        <v>71890000000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals Inc</t>
+          <t>Nu Holdings Ltd</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>69950000000</v>
+        <v>70910000000</v>
       </c>
     </row>
     <row r="132">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>67080000000</v>
+        <v>68860000000</v>
       </c>
     </row>
     <row r="133">
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>63740000000</v>
+        <v>65490000000</v>
       </c>
     </row>
     <row r="134">
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>62510000000</v>
+        <v>63860000000</v>
       </c>
     </row>
     <row r="135">
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>59180000000</v>
+        <v>60900000000</v>
       </c>
     </row>
     <row r="136">
@@ -2526,7 +2526,7 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>58500000000</v>
+        <v>59610000000</v>
       </c>
     </row>
     <row r="137">
@@ -2541,52 +2541,52 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>54640000000</v>
+        <v>53640000000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Vistra Corp</t>
+          <t>PayPal Holdings Inc</t>
         </is>
       </c>
       <c r="L138" t="n">
-        <v>52960000000</v>
+        <v>51440000000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>PayPal Holdings Inc</t>
+          <t>Vistra Corp</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>49460000000</v>
+        <v>50120000000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Astera Labs Inc</t>
+          <t>Autodesk Inc</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>48430000000</v>
+        <v>50090000000</v>
       </c>
     </row>
     <row r="141">
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>48350000000</v>
+        <v>49460000000</v>
       </c>
     </row>
     <row r="142">
@@ -2616,67 +2616,67 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>47810000000</v>
+        <v>48180000000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Autodesk Inc</t>
+          <t>Astera Labs Inc</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>47670000000</v>
+        <v>44610000000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Coinbase Global Inc</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>47280000000</v>
+        <v>44240000000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Coinbase Global Inc</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>44130000000</v>
+        <v>42980000000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>42590000000</v>
+        <v>42700000000</v>
       </c>
     </row>
     <row r="147">
@@ -2691,37 +2691,37 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>41510000000</v>
+        <v>42120000000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Rocket Lab Corp</t>
+          <t>Workday Inc</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>40040000000</v>
+        <v>39440000000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Carnival Corp Ltd</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>38620000000</v>
+        <v>38670000000</v>
       </c>
     </row>
     <row r="150">
@@ -2736,67 +2736,67 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>37550000000</v>
+        <v>38570000000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Carnival Corp Ltd</t>
+          <t>Rocket Lab Corp</t>
         </is>
       </c>
       <c r="L151" t="n">
-        <v>37140000000</v>
+        <v>38220000000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Workday Inc</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>36440000000</v>
+        <v>36720000000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>RDDT</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Strategy Inc</t>
+          <t>Reddit Inc</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>34570000000</v>
+        <v>34350000000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>RDDT</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Reddit Inc</t>
+          <t>Strategy Inc</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>34500000000</v>
+        <v>33700000000</v>
       </c>
     </row>
     <row r="155">
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>32250000000</v>
+        <v>32490000000</v>
       </c>
     </row>
     <row r="156">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>30100000000</v>
+        <v>30660000000</v>
       </c>
     </row>
     <row r="157">
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>29520000000</v>
+        <v>29490000000</v>
       </c>
     </row>
     <row r="158">
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>28670000000</v>
+        <v>29200000000</v>
       </c>
     </row>
     <row r="159">
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>27890000000</v>
+        <v>28910000000</v>
       </c>
     </row>
     <row r="160">
@@ -2886,97 +2886,97 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>26750000000</v>
+        <v>26820000000</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>AFRM</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Affirm Holdings Inc</t>
+          <t>Zscaler Inc</t>
         </is>
       </c>
       <c r="L161" t="n">
-        <v>24460000000</v>
+        <v>24520000000</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>AFRM</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Zscaler Inc</t>
+          <t>Affirm Holdings Inc</t>
         </is>
       </c>
       <c r="L162" t="n">
-        <v>23820000000</v>
+        <v>24250000000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>First Solar Inc</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="L163" t="n">
-        <v>22120000000</v>
+        <v>22140000000</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>DKNG</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>DraftKings Inc</t>
         </is>
       </c>
       <c r="L164" t="n">
-        <v>22070000000</v>
+        <v>21890000000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>SoFi Technologies Inc</t>
+          <t>First Solar Inc</t>
         </is>
       </c>
       <c r="L165" t="n">
-        <v>21650000000</v>
+        <v>21770000000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>DKNG</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>DraftKings Inc</t>
+          <t>SoFi Technologies Inc</t>
         </is>
       </c>
       <c r="L166" t="n">
-        <v>21440000000</v>
+        <v>21470000000</v>
       </c>
     </row>
     <row r="167">
@@ -2991,37 +2991,37 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>21200000000</v>
+        <v>21350000000</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Super Micro Computer Inc</t>
+          <t>Charter Communications Inc</t>
         </is>
       </c>
       <c r="L168" t="n">
-        <v>19280000000</v>
+        <v>18730000000</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Charter Communications Inc</t>
+          <t>Super Micro Computer Inc</t>
         </is>
       </c>
       <c r="L169" t="n">
-        <v>18090000000</v>
+        <v>18400000000</v>
       </c>
     </row>
     <row r="170">
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>16320000000</v>
+        <v>15990000000</v>
       </c>
     </row>
     <row r="171">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>13730000000</v>
+        <v>14140000000</v>
       </c>
     </row>
     <row r="172">
@@ -3066,22 +3066,22 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>13730000000</v>
+        <v>14140000000</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>PINS</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>IonQ Inc</t>
+          <t>Pinterest Inc</t>
         </is>
       </c>
       <c r="L173" t="n">
-        <v>13410000000</v>
+        <v>13650000000</v>
       </c>
     </row>
     <row r="174">
@@ -3096,22 +3096,22 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>13210000000</v>
+        <v>13460000000</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>PINS</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Pinterest Inc</t>
+          <t>IonQ Inc</t>
         </is>
       </c>
       <c r="L175" t="n">
-        <v>13160000000</v>
+        <v>12650000000</v>
       </c>
     </row>
     <row r="176">
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>12950000000</v>
+        <v>12110000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>10830000000</v>
+        <v>10660000000</v>
       </c>
     </row>
     <row r="178">
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>8540000000</v>
+        <v>9470000000</v>
       </c>
     </row>
     <row r="179">
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>8290000000</v>
+        <v>8540000000</v>
       </c>
     </row>
     <row r="180">
@@ -3186,97 +3186,97 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>7810000000</v>
+        <v>7910000000</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Applied Digital Corp</t>
+          <t>Zillow Group Inc</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>7540000000</v>
+        <v>7700000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Celsius Holdings Inc</t>
+          <t>Applied Digital Corp</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>7360000000</v>
+        <v>7610000000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Zillow Group Inc</t>
+          <t>Celsius Holdings Inc</t>
         </is>
       </c>
       <c r="L183" t="n">
-        <v>7320000000</v>
+        <v>7530000000</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>OKLO</t>
+          <t>MBLY</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Oklo Inc</t>
+          <t>Mobileye Global Inc</t>
         </is>
       </c>
       <c r="L184" t="n">
-        <v>7270000000</v>
+        <v>7170000000</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>HIMS</t>
+          <t>OKLO</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Hims &amp; Hers Health Inc</t>
+          <t>Oklo Inc</t>
         </is>
       </c>
       <c r="L185" t="n">
-        <v>7000000000</v>
+        <v>6890000000</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>MBLY</t>
+          <t>HIMS</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Mobileye Global Inc</t>
+          <t>Hims &amp; Hers Health Inc</t>
         </is>
       </c>
       <c r="L186" t="n">
-        <v>6810000000</v>
+        <v>6790000000</v>
       </c>
     </row>
     <row r="187">
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>6220000000</v>
+        <v>6290000000</v>
       </c>
     </row>
     <row r="188">
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>5200000000</v>
+        <v>4830000000</v>
       </c>
     </row>
     <row r="189">
@@ -3321,37 +3321,37 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>4760000000</v>
+        <v>4770000000</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ONDS</t>
+          <t>CRSP</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Ondas Inc</t>
+          <t>CRISPR Therapeutics AG</t>
         </is>
       </c>
       <c r="L190" t="n">
-        <v>4570000000</v>
+        <v>4590000000</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>CRSP</t>
+          <t>ONDS</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>CRISPR Therapeutics AG</t>
+          <t>Ondas Inc</t>
         </is>
       </c>
       <c r="L191" t="n">
-        <v>4510000000</v>
+        <v>4480000000</v>
       </c>
     </row>
     <row r="192">
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>4490000000</v>
+        <v>4340000000</v>
       </c>
     </row>
     <row r="193">
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3460000000</v>
+        <v>3340000000</v>
       </c>
     </row>
     <row r="194">
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3140000000</v>
+        <v>3260000000</v>
       </c>
     </row>
     <row r="195">
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>3120000000</v>
+        <v>3000000000</v>
       </c>
     </row>
     <row r="196">
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2830000000</v>
+        <v>2820000000</v>
       </c>
     </row>
     <row r="197">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2630000000</v>
+        <v>2660000000</v>
       </c>
     </row>
     <row r="198">
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2570000000</v>
+        <v>2640000000</v>
       </c>
     </row>
     <row r="199">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>2490000000</v>
+        <v>2330000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1800000000</v>
+        <v>1740000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1610000000</v>
+        <v>1690000000</v>
       </c>
     </row>
     <row r="202">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1370000000</v>
+        <v>1380000000</v>
       </c>
     </row>
     <row r="203">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>984550000</v>
+        <v>952050000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>874480000</v>
+        <v>836460000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>509910000</v>
+        <v>475290000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4994880000000</v>
+        <v>4967120000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4767640000000</v>
+        <v>4598240000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4067630000000</v>
+        <v>4113860000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2921970000000</v>
+        <v>2901100000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2483390000000</v>
+        <v>2438100000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2034710000000</v>
+        <v>1943220000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1812210000000</v>
+        <v>1761830000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1506330000000</v>
+        <v>1486530000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1214250000000</v>
+        <v>1178230000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1149550000000</v>
+        <v>1139530000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>994610000000</v>
+        <v>988070000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,37 +726,37 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>957420000000</v>
+        <v>923650000000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Micron Technology Inc</t>
+          <t>Walmart Inc</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>926700000000</v>
+        <v>908970000000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Walmart Inc</t>
+          <t>Micron Technology Inc</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>900060000000</v>
+        <v>834620000000</v>
       </c>
     </row>
     <row r="19">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>741300000000</v>
+        <v>700440000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,37 +786,37 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>690700000000</v>
+        <v>694730000000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>ExxonMobil Holdings Corp</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>642790000000</v>
+        <v>649640000000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ExxonMobil Holdings Corp</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>634270000000</v>
+        <v>639900000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>610100000000</v>
+        <v>597670000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>497240000000</v>
+        <v>497740000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>465020000000</v>
+        <v>465200000000</v>
       </c>
     </row>
     <row r="26">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>455550000000</v>
+        <v>443330000000</v>
       </c>
     </row>
     <row r="27">
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>444390000000</v>
+        <v>433390000000</v>
       </c>
     </row>
     <row r="28">
@@ -906,97 +906,97 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>428660000000</v>
+        <v>431960000000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Unitedhealth Group Inc</t>
+          <t>Coca-Cola Co</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>389400000000</v>
+        <v>383270000000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Caterpillar Inc</t>
+          <t>Chevron Corp</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>387330000000</v>
+        <v>382110000000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Coca-Cola Co</t>
+          <t>Unitedhealth Group Inc</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>379780000000</v>
+        <v>381940000000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Applied Materials Inc</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>378290000000</v>
+        <v>363800000000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Caterpillar Inc</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>377250000000</v>
+        <v>360550000000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Chevron Corp</t>
+          <t>Applied Materials Inc</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>373580000000</v>
+        <v>346520000000</v>
       </c>
     </row>
     <row r="35">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>346680000000</v>
+        <v>340210000000</v>
       </c>
     </row>
     <row r="36">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>345540000000</v>
+        <v>339150000000</v>
       </c>
     </row>
     <row r="37">
@@ -1041,22 +1041,22 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>343480000000</v>
+        <v>337290000000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Lam Research Corp</t>
+          <t>Merck &amp; Co Inc</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>337170000000</v>
+        <v>321970000000</v>
       </c>
     </row>
     <row r="39">
@@ -1071,22 +1071,22 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>333720000000</v>
+        <v>320390000000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Merck &amp; Co Inc</t>
+          <t>Lam Research Corp</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>325570000000</v>
+        <v>315580000000</v>
       </c>
     </row>
     <row r="41">
@@ -1101,52 +1101,52 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>311990000000</v>
+        <v>309290000000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Goldman Sachs Group Inc</t>
+          <t>Netflix Inc</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>304840000000</v>
+        <v>306590000000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Netflix Inc</t>
+          <t>Palantir Technologies Inc</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>301430000000</v>
+        <v>294870000000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>NVS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc</t>
+          <t>Novartis AG ADR</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>296140000000</v>
+        <v>290750000000</v>
       </c>
     </row>
     <row r="45">
@@ -1161,22 +1161,22 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>294590000000</v>
+        <v>290100000000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NVS</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Novartis AG ADR</t>
+          <t>Goldman Sachs Group Inc</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>292610000000</v>
+        <v>289330000000</v>
       </c>
     </row>
     <row r="47">
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>276120000000</v>
+        <v>275730000000</v>
       </c>
     </row>
     <row r="48">
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>267490000000</v>
+        <v>268770000000</v>
       </c>
     </row>
     <row r="49">
@@ -1221,142 +1221,142 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>265840000000</v>
+        <v>256660000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>260400000000</v>
+        <v>256030000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>259990000000</v>
+        <v>247760000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>Shell Plc ADR</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>254190000000</v>
+        <v>246300000000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>253030000000</v>
+        <v>239770000000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>251250000000</v>
+        <v>239630000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>KLA Corp</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>249240000000</v>
+        <v>239280000000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Shell Plc ADR</t>
+          <t>Linde Plc</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>240330000000</v>
+        <v>236470000000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Linde Plc</t>
+          <t>American Express Co</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>236470000000</v>
+        <v>223870000000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>American Express Co</t>
+          <t>KLA Corp</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>227330000000</v>
+        <v>222310000000</v>
       </c>
     </row>
     <row r="59">
@@ -1371,22 +1371,22 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>227170000000</v>
+        <v>218020000000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>International Business Machines Corp</t>
+          <t>Sap SE ADR</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>214380000000</v>
+        <v>214670000000</v>
       </c>
     </row>
     <row r="61">
@@ -1401,127 +1401,127 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>214210000000</v>
+        <v>214220000000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AMGEN Inc</t>
+          <t>International Business Machines Corp</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>212160000000</v>
+        <v>213340000000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Sap SE ADR</t>
+          <t>AMGEN Inc</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>206800000000</v>
+        <v>209210000000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc</t>
+          <t>Toyota Motor Corp ADR</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>201220000000</v>
+        <v>205190000000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Toyota Motor Corp ADR</t>
+          <t>Verizon Communications Inc</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>198230000000</v>
+        <v>197170000000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>T-Mobile US Inc</t>
+          <t>PepsiCo Inc</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>195640000000</v>
+        <v>195860000000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PepsiCo Inc</t>
+          <t>T-Mobile US Inc</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>194990000000</v>
+        <v>194710000000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>McDonald's Corp</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>193980000000</v>
+        <v>192950000000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>McDonald's Corp</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>187230000000</v>
+        <v>192920000000</v>
       </c>
     </row>
     <row r="70">
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>186840000000</v>
+        <v>188120000000</v>
       </c>
     </row>
     <row r="71">
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>186200000000</v>
+        <v>184510000000</v>
       </c>
     </row>
     <row r="72">
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>185120000000</v>
+        <v>182660000000</v>
       </c>
     </row>
     <row r="73">
@@ -1581,7 +1581,7 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>184300000000</v>
+        <v>181690000000</v>
       </c>
     </row>
     <row r="74">
@@ -1596,127 +1596,127 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>178460000000</v>
+        <v>175480000000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Boeing Co</t>
+          <t>Novo Nordisk ADR</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>174660000000</v>
+        <v>173200000000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Deere &amp; Co</t>
+          <t>Walt Disney Co</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>172720000000</v>
+        <v>171010000000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Walt Disney Co</t>
+          <t>Boeing Co</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>171720000000</v>
+        <v>168700000000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>Shopify Inc</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>171680000000</v>
+        <v>167620000000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Novo Nordisk ADR</t>
+          <t>Deere &amp; Co</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>171120000000</v>
+        <v>164920000000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Shopify Inc</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>169060000000</v>
+        <v>164790000000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>168980000000</v>
+        <v>164090000000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>AT&amp;T Inc</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>166770000000</v>
+        <v>164050000000</v>
       </c>
     </row>
     <row r="83">
@@ -1731,67 +1731,67 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>166550000000</v>
+        <v>160950000000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>162320000000</v>
+        <v>159260000000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>159760000000</v>
+        <v>155980000000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>Salesforce Inc</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>154440000000</v>
+        <v>154280000000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Salesforce Inc</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>148650000000</v>
+        <v>150440000000</v>
       </c>
     </row>
     <row r="88">
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>144000000000</v>
+        <v>144930000000</v>
       </c>
     </row>
     <row r="89">
@@ -1821,52 +1821,52 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>140990000000</v>
+        <v>140370000000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>140500000000</v>
+        <v>138490000000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Danaher Corp</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>140060000000</v>
+        <v>138130000000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Danaher Corp</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>139930000000</v>
+        <v>134190000000</v>
       </c>
     </row>
     <row r="93">
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>134160000000</v>
+        <v>131370000000</v>
       </c>
     </row>
     <row r="94">
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>129880000000</v>
+        <v>128850000000</v>
       </c>
     </row>
     <row r="95">
@@ -1911,82 +1911,82 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>128270000000</v>
+        <v>128550000000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Intuitive Surgical Inc</t>
+          <t>PDD Holdings Inc ADR</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>127820000000</v>
+        <v>125710000000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>S&amp;P Global Inc</t>
+          <t>Altria Group Inc</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>125610000000</v>
+        <v>125110000000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Altria Group Inc</t>
+          <t>Intuitive Surgical Inc</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>124940000000</v>
+        <v>124740000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Lowe's Cos. Inc</t>
+          <t>S&amp;P Global Inc</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>122370000000</v>
+        <v>124210000000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PDD Holdings Inc ADR</t>
+          <t>Lowe's Cos. Inc</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>122000000000</v>
+        <v>120930000000</v>
       </c>
     </row>
     <row r="101">
@@ -2001,7 +2001,7 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>117500000000</v>
+        <v>118690000000</v>
       </c>
     </row>
     <row r="102">
@@ -2016,307 +2016,307 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>111210000000</v>
+        <v>112060000000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Corning Inc</t>
+          <t>Automatic Data Processing Inc</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>108450000000</v>
+        <v>109280000000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc</t>
+          <t>Spotify Technology SA</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>105600000000</v>
+        <v>107880000000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Spotify Technology SA</t>
+          <t>Corning Inc</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>105320000000</v>
+        <v>106760000000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>103540000000</v>
+        <v>105970000000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Equinix Inc</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>102060000000</v>
+        <v>104710000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>Equinix Inc</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>100760000000</v>
+        <v>99420000000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>Snowflake Inc</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>100380000000</v>
+        <v>98050000000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>99050000000</v>
+        <v>97870000000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>MercadoLibre Inc</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>94420000000</v>
+        <v>96020000000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>3M Co</t>
+          <t>MercadoLibre Inc</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>94110000000</v>
+        <v>94460000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>MMC</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>Marsh</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>93790000000</v>
+        <v>94290000000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Snowflake Inc</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>93710000000</v>
+        <v>94040000000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>HCA Healthcare Inc</t>
+          <t>Airbnb Inc</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>92770000000</v>
+        <v>92220000000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Airbnb Inc</t>
+          <t>3M Co</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>92280000000</v>
+        <v>91770000000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>MMC</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Marsh</t>
+          <t>Intuit Inc</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>91720000000</v>
+        <v>91120000000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>United Parcel Service Inc</t>
+          <t>HCA Healthcare Inc</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>89700000000</v>
+        <v>90550000000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>United Parcel Service Inc</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>89300000000</v>
+        <v>88880000000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Intercontinental Exchange Inc</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>86490000000</v>
+        <v>87250000000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange Inc</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>86370000000</v>
+        <v>86780000000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Intuit Inc</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>85610000000</v>
+        <v>85670000000</v>
       </c>
     </row>
     <row r="123">
@@ -2331,37 +2331,37 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>83650000000</v>
+        <v>81540000000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Cigna Group</t>
+          <t>General Motors Company</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>79640000000</v>
+        <v>78440000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>General Motors Company</t>
+          <t>Cigna Group</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>79230000000</v>
+        <v>78430000000</v>
       </c>
     </row>
     <row r="126">
@@ -2376,37 +2376,37 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>78020000000</v>
+        <v>76010000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>SLB Ltd</t>
+          <t>Colgate-Palmolive Co</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>74720000000</v>
+        <v>74810000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive Co</t>
+          <t>SLB Ltd</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>74200000000</v>
+        <v>73200000000</v>
       </c>
     </row>
     <row r="129">
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>72880000000</v>
+        <v>72910000000</v>
       </c>
     </row>
     <row r="130">
@@ -2436,37 +2436,37 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>71890000000</v>
+        <v>69050000000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>NU</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Nu Holdings Ltd</t>
+          <t>Ferrari NV</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>70910000000</v>
+        <v>68080000000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Ferrari NV</t>
+          <t>Nu Holdings Ltd</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>68860000000</v>
+        <v>67820000000</v>
       </c>
     </row>
     <row r="133">
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>65490000000</v>
+        <v>66270000000</v>
       </c>
     </row>
     <row r="134">
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>63860000000</v>
+        <v>64120000000</v>
       </c>
     </row>
     <row r="135">
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>60900000000</v>
+        <v>61440000000</v>
       </c>
     </row>
     <row r="136">
@@ -2526,7 +2526,7 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>59610000000</v>
+        <v>60890000000</v>
       </c>
     </row>
     <row r="137">
@@ -2541,52 +2541,52 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>53640000000</v>
+        <v>55730000000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>PayPal Holdings Inc</t>
+          <t>Autodesk Inc</t>
         </is>
       </c>
       <c r="L138" t="n">
-        <v>51440000000</v>
+        <v>51750000000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Vistra Corp</t>
+          <t>PayPal Holdings Inc</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>50120000000</v>
+        <v>51470000000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Autodesk Inc</t>
+          <t>Edwards Lifesciences Corp</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>50090000000</v>
+        <v>49380000000</v>
       </c>
     </row>
     <row r="141">
@@ -2601,112 +2601,112 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>49460000000</v>
+        <v>48910000000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences Corp</t>
+          <t>Vistra Corp</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>48180000000</v>
+        <v>48150000000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Astera Labs Inc</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>44610000000</v>
+        <v>43920000000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Coinbase Global Inc</t>
+          <t>Astera Labs Inc</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>44240000000</v>
+        <v>42810000000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>MSCI Inc</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>42980000000</v>
+        <v>42380000000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Coinbase Global Inc</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>42700000000</v>
+        <v>42180000000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MSCI Inc</t>
+          <t>Workday Inc</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>42120000000</v>
+        <v>41500000000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Workday Inc</t>
+          <t>JD.com Inc ADR</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>39440000000</v>
+        <v>39060000000</v>
       </c>
     </row>
     <row r="149">
@@ -2721,22 +2721,22 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>38670000000</v>
+        <v>38090000000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>JD</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>JD.com Inc ADR</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L150" t="n">
-        <v>38570000000</v>
+        <v>37300000000</v>
       </c>
     </row>
     <row r="151">
@@ -2751,37 +2751,37 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>38220000000</v>
+        <v>35050000000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>RDDT</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Reddit Inc</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>36720000000</v>
+        <v>34260000000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>RDDT</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Reddit Inc</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>34350000000</v>
+        <v>33180000000</v>
       </c>
     </row>
     <row r="154">
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>33700000000</v>
+        <v>32710000000</v>
       </c>
     </row>
     <row r="155">
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>32490000000</v>
+        <v>32670000000</v>
       </c>
     </row>
     <row r="156">
@@ -2826,22 +2826,22 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>30660000000</v>
+        <v>30440000000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Twilio Inc</t>
+          <t>Fiserv Inc</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>29490000000</v>
+        <v>29660000000</v>
       </c>
     </row>
     <row r="158">
@@ -2856,22 +2856,22 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>29200000000</v>
+        <v>29480000000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Fiserv Inc</t>
+          <t>Twilio Inc</t>
         </is>
       </c>
       <c r="L159" t="n">
-        <v>28910000000</v>
+        <v>28570000000</v>
       </c>
     </row>
     <row r="160">
@@ -2886,7 +2886,7 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>26820000000</v>
+        <v>27100000000</v>
       </c>
     </row>
     <row r="161">
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>24520000000</v>
+        <v>24870000000</v>
       </c>
     </row>
     <row r="162">
@@ -2916,82 +2916,82 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>24250000000</v>
+        <v>23480000000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>DKNG</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>DraftKings Inc</t>
         </is>
       </c>
       <c r="L163" t="n">
-        <v>22140000000</v>
+        <v>21830000000</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>DKNG</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>DraftKings Inc</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="L164" t="n">
-        <v>21890000000</v>
+        <v>21620000000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>ROKU</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>First Solar Inc</t>
+          <t>Roku Inc</t>
         </is>
       </c>
       <c r="L165" t="n">
-        <v>21770000000</v>
+        <v>21560000000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>SoFi Technologies Inc</t>
+          <t>First Solar Inc</t>
         </is>
       </c>
       <c r="L166" t="n">
-        <v>21470000000</v>
+        <v>21410000000</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ROKU</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Roku Inc</t>
+          <t>SoFi Technologies Inc</t>
         </is>
       </c>
       <c r="L167" t="n">
-        <v>21350000000</v>
+        <v>19560000000</v>
       </c>
     </row>
     <row r="168">
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>18730000000</v>
+        <v>19430000000</v>
       </c>
     </row>
     <row r="169">
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>18400000000</v>
+        <v>16620000000</v>
       </c>
     </row>
     <row r="170">
@@ -3036,22 +3036,22 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>15990000000</v>
+        <v>15250000000</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>GRAB</t>
+          <t>TXRH</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Grab Holdings Limited</t>
+          <t>Texas Roadhouse Inc</t>
         </is>
       </c>
       <c r="L171" t="n">
-        <v>14140000000</v>
+        <v>13750000000</v>
       </c>
     </row>
     <row r="172">
@@ -3066,37 +3066,37 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>14140000000</v>
+        <v>13730000000</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>PINS</t>
+          <t>GRAB</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Pinterest Inc</t>
+          <t>Grab Holdings Limited</t>
         </is>
       </c>
       <c r="L173" t="n">
-        <v>13650000000</v>
+        <v>13730000000</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>TXRH</t>
+          <t>PINS</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Texas Roadhouse Inc</t>
+          <t>Pinterest Inc</t>
         </is>
       </c>
       <c r="L174" t="n">
-        <v>13460000000</v>
+        <v>13690000000</v>
       </c>
     </row>
     <row r="175">
@@ -3111,37 +3111,37 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>12650000000</v>
+        <v>11940000000</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>BROS</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>IREN Ltd</t>
+          <t>Dutch Bros Inc</t>
         </is>
       </c>
       <c r="L176" t="n">
-        <v>12110000000</v>
+        <v>10650000000</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>BROS</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Dutch Bros Inc</t>
+          <t>IREN Ltd</t>
         </is>
       </c>
       <c r="L177" t="n">
-        <v>10660000000</v>
+        <v>10460000000</v>
       </c>
     </row>
     <row r="178">
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>9470000000</v>
+        <v>9220000000</v>
       </c>
     </row>
     <row r="179">
@@ -3171,82 +3171,82 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>8540000000</v>
+        <v>8350000000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>AeroVironment Inc</t>
+          <t>Zillow Group Inc</t>
         </is>
       </c>
       <c r="L180" t="n">
-        <v>7910000000</v>
+        <v>7790000000</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Zillow Group Inc</t>
+          <t>Celsius Holdings Inc</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>7700000000</v>
+        <v>7380000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Applied Digital Corp</t>
+          <t>AeroVironment Inc</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>7610000000</v>
+        <v>7190000000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>MBLY</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Celsius Holdings Inc</t>
+          <t>Mobileye Global Inc</t>
         </is>
       </c>
       <c r="L183" t="n">
-        <v>7530000000</v>
+        <v>6810000000</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>MBLY</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Mobileye Global Inc</t>
+          <t>Applied Digital Corp</t>
         </is>
       </c>
       <c r="L184" t="n">
-        <v>7170000000</v>
+        <v>6640000000</v>
       </c>
     </row>
     <row r="185">
@@ -3261,202 +3261,202 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>6890000000</v>
+        <v>6410000000</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>HIMS</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Hims &amp; Hers Health Inc</t>
+          <t>SentinelOne Inc</t>
         </is>
       </c>
       <c r="L186" t="n">
-        <v>6790000000</v>
+        <v>6350000000</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>HIMS</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>SentinelOne Inc</t>
+          <t>Hims &amp; Hers Health Inc</t>
         </is>
       </c>
       <c r="L187" t="n">
-        <v>6290000000</v>
+        <v>5790000000</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>RGTI</t>
+          <t>CRSP</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Rigetti Computing Inc</t>
+          <t>CRISPR Therapeutics AG</t>
         </is>
       </c>
       <c r="L188" t="n">
-        <v>4830000000</v>
+        <v>4590000000</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>LMND</t>
+          <t>RGTI</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Lemonade Inc</t>
+          <t>Rigetti Computing Inc</t>
         </is>
       </c>
       <c r="L189" t="n">
-        <v>4770000000</v>
+        <v>4390000000</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>CRSP</t>
+          <t>ONDS</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>CRISPR Therapeutics AG</t>
+          <t>Ondas Inc</t>
         </is>
       </c>
       <c r="L190" t="n">
-        <v>4590000000</v>
+        <v>3870000000</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ONDS</t>
+          <t>MARA</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Ondas Inc</t>
+          <t>MARA Holdings Inc</t>
         </is>
       </c>
       <c r="L191" t="n">
-        <v>4480000000</v>
+        <v>3830000000</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>MARA</t>
+          <t>LMND</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>MARA Holdings Inc</t>
+          <t>Lemonade Inc</t>
         </is>
       </c>
       <c r="L192" t="n">
-        <v>4340000000</v>
+        <v>3640000000</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>LEU</t>
+          <t>FSLY</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Centrus Energy Corp</t>
+          <t>Fastly Inc</t>
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3340000000</v>
+        <v>3240000000</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>FSLY</t>
+          <t>LEU</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Fastly Inc</t>
+          <t>Centrus Energy Corp</t>
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3260000000</v>
+        <v>3140000000</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>PENN</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>NuScale Power Corp</t>
+          <t>PENN Entertainment Inc</t>
         </is>
       </c>
       <c r="L195" t="n">
-        <v>3000000000</v>
+        <v>2840000000</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>PENN</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>PENN Entertainment Inc</t>
+          <t>NuScale Power Corp</t>
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2820000000</v>
+        <v>2770000000</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>TMDX</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Upstart Holdings Inc</t>
+          <t>Transmedics Group Inc</t>
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2660000000</v>
+        <v>2700000000</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>TMDX</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Transmedics Group Inc</t>
+          <t>Upstart Holdings Inc</t>
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2640000000</v>
+        <v>2550000000</v>
       </c>
     </row>
     <row r="199">
@@ -3471,37 +3471,37 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>2330000000</v>
+        <v>2190000000</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>QUBT</t>
+          <t>TDOC</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Quantum Computing Inc</t>
+          <t>Teladoc Health Inc</t>
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1740000000</v>
+        <v>1660000000</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>TDOC</t>
+          <t>QUBT</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Teladoc Health Inc</t>
+          <t>Quantum Computing Inc</t>
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1690000000</v>
+        <v>1650000000</v>
       </c>
     </row>
     <row r="202">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>952050000</v>
+        <v>824920000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>836460000</v>
+        <v>775000000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>475290000</v>
+        <v>445700000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4967120000000</v>
+        <v>4897210000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4598240000000</v>
+        <v>4719970000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4113860000000</v>
+        <v>4087230000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2901100000000</v>
+        <v>3350970000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2438100000000</v>
+        <v>2533300000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1943220000000</v>
+        <v>2091760000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1761830000000</v>
+        <v>1845180000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1486530000000</v>
+        <v>1368290000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1178230000000</v>
+        <v>1219820000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1139530000000</v>
+        <v>1087680000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,52 +711,52 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>988070000000</v>
+        <v>989060000000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co</t>
+          <t>Micron Technology Inc</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>923650000000</v>
+        <v>987830000000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Walmart Inc</t>
+          <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>908970000000</v>
+        <v>940110000000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Micron Technology Inc</t>
+          <t>Walmart Inc</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>834620000000</v>
+        <v>884140000000</v>
       </c>
     </row>
     <row r="19">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>700440000000</v>
+        <v>791480000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>694730000000</v>
+        <v>665240000000</v>
       </c>
     </row>
     <row r="21">
@@ -801,37 +801,37 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>649640000000</v>
+        <v>650560000000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>ASML Holding NV</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>639900000000</v>
+        <v>636500000000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ASML Holding NV</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>597670000000</v>
+        <v>616500000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>497740000000</v>
+        <v>510140000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>465200000000</v>
+        <v>454790000000</v>
       </c>
     </row>
     <row r="26">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>443330000000</v>
+        <v>447590000000</v>
       </c>
     </row>
     <row r="27">
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>433390000000</v>
+        <v>438070000000</v>
       </c>
     </row>
     <row r="28">
@@ -906,22 +906,22 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>431960000000</v>
+        <v>423150000000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Coca-Cola Co</t>
+          <t>Applied Materials Inc</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>383270000000</v>
+        <v>398380000000</v>
       </c>
     </row>
     <row r="30">
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>382110000000</v>
+        <v>383000000000</v>
       </c>
     </row>
     <row r="31">
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>381940000000</v>
+        <v>382760000000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Coca-Cola Co</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>363800000000</v>
+        <v>380730000000</v>
       </c>
     </row>
     <row r="33">
@@ -981,37 +981,37 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>360550000000</v>
+        <v>372720000000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Applied Materials Inc</t>
+          <t>Lam Research Corp</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>346520000000</v>
+        <v>372320000000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble Co</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>340210000000</v>
+        <v>368380000000</v>
       </c>
     </row>
     <row r="36">
@@ -1026,37 +1026,37 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>339150000000</v>
+        <v>367430000000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Home Depot Inc</t>
+          <t>Procter &amp; Gamble Co</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>337290000000</v>
+        <v>335230000000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Merck &amp; Co Inc</t>
+          <t>Home Depot Inc</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>321970000000</v>
+        <v>332390000000</v>
       </c>
     </row>
     <row r="39">
@@ -1071,112 +1071,112 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>320390000000</v>
+        <v>331320000000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Lam Research Corp</t>
+          <t>Merck &amp; Co Inc</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>315580000000</v>
+        <v>320560000000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Philip Morris International Inc</t>
+          <t>Netflix Inc</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>309290000000</v>
+        <v>304680000000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Netflix Inc</t>
+          <t>Goldman Sachs Group Inc</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>306590000000</v>
+        <v>302340000000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc</t>
+          <t>Philip Morris International Inc</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>294870000000</v>
+        <v>299250000000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>NVS</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Novartis AG ADR</t>
+          <t>Palantir Technologies Inc</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>290750000000</v>
+        <v>293100000000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>NVS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Novartis AG ADR</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>290100000000</v>
+        <v>290030000000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Goldman Sachs Group Inc</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>289330000000</v>
+        <v>288930000000</v>
       </c>
     </row>
     <row r="47">
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>275730000000</v>
+        <v>278830000000</v>
       </c>
     </row>
     <row r="48">
@@ -1206,157 +1206,157 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>268770000000</v>
+        <v>265730000000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Co</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>256660000000</v>
+        <v>265430000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>256030000000</v>
+        <v>262430000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>247760000000</v>
+        <v>261530000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Shell Plc ADR</t>
+          <t>Wells Fargo &amp; Co</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>246300000000</v>
+        <v>261430000000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>239770000000</v>
+        <v>257000000000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>239630000000</v>
+        <v>254580000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>Shell Plc ADR</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>239280000000</v>
+        <v>252350000000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Linde Plc</t>
+          <t>KLA Corp</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>236470000000</v>
+        <v>235560000000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>American Express Co</t>
+          <t>Linde Plc</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>223870000000</v>
+        <v>235300000000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>KLA Corp</t>
+          <t>American Express Co</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>222310000000</v>
+        <v>227930000000</v>
       </c>
     </row>
     <row r="59">
@@ -1371,37 +1371,37 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>218020000000</v>
+        <v>226920000000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sap SE ADR</t>
+          <t>Thermo Fisher Scientific Inc</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>214670000000</v>
+        <v>214340000000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc</t>
+          <t>AMGEN Inc</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>214220000000</v>
+        <v>209210000000</v>
       </c>
     </row>
     <row r="62">
@@ -1416,22 +1416,22 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>213340000000</v>
+        <v>208910000000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AMGEN Inc</t>
+          <t>Sap SE ADR</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>209210000000</v>
+        <v>208770000000</v>
       </c>
     </row>
     <row r="64">
@@ -1446,187 +1446,187 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>205190000000</v>
+        <v>203710000000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>197170000000</v>
+        <v>193570000000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PepsiCo Inc</t>
+          <t>Verizon Communications Inc</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>195860000000</v>
+        <v>192540000000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>T-Mobile US Inc</t>
+          <t>PepsiCo Inc</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>194710000000</v>
+        <v>191360000000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>McDonald's Corp</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>192950000000</v>
+        <v>190730000000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>McDonald's Corp</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>192920000000</v>
+        <v>189550000000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>188120000000</v>
+        <v>188600000000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NextEra Energy Inc</t>
+          <t>T-Mobile US Inc</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>184510000000</v>
+        <v>185940000000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>182660000000</v>
+        <v>183730000000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Charles Schwab Corp</t>
+          <t>NextEra Energy Inc</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>181690000000</v>
+        <v>183400000000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Blackrock Inc</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>175480000000</v>
+        <v>182750000000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Novo Nordisk ADR</t>
+          <t>Charles Schwab Corp</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>173200000000</v>
+        <v>181440000000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Walt Disney Co</t>
+          <t>Blackrock Inc</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>171010000000</v>
+        <v>178600000000</v>
       </c>
     </row>
     <row r="77">
@@ -1641,37 +1641,37 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>168700000000</v>
+        <v>174590000000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Shopify Inc</t>
+          <t>Novo Nordisk ADR</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>167620000000</v>
+        <v>173310000000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Deere &amp; Co</t>
+          <t>Walt Disney Co</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>164920000000</v>
+        <v>166980000000</v>
       </c>
     </row>
     <row r="80">
@@ -1686,37 +1686,37 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>164790000000</v>
+        <v>162990000000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>Deere &amp; Co</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>164090000000</v>
+        <v>161820000000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>164050000000</v>
+        <v>159790000000</v>
       </c>
     </row>
     <row r="83">
@@ -1731,67 +1731,67 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>160950000000</v>
+        <v>159300000000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>AT&amp;T Inc</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>159260000000</v>
+        <v>159040000000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>Shopify Inc</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>155980000000</v>
+        <v>158830000000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Salesforce Inc</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>154280000000</v>
+        <v>149740000000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>Salesforce Inc</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>150440000000</v>
+        <v>148000000000</v>
       </c>
     </row>
     <row r="88">
@@ -1806,67 +1806,67 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>144930000000</v>
+        <v>143250000000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Chubb Limited</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>140370000000</v>
+        <v>139180000000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Danaher Corp</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>138490000000</v>
+        <v>137900000000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Danaher Corp</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>138130000000</v>
+        <v>135680000000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>Chubb Limited</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>134190000000</v>
+        <v>135090000000</v>
       </c>
     </row>
     <row r="93">
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>131370000000</v>
+        <v>132500000000</v>
       </c>
     </row>
     <row r="94">
@@ -1896,82 +1896,82 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>128850000000</v>
+        <v>132450000000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Progressive Corp</t>
+          <t>Intuitive Surgical Inc</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>128550000000</v>
+        <v>124700000000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PDD Holdings Inc ADR</t>
+          <t>Progressive Corp</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>125710000000</v>
+        <v>124630000000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Altria Group Inc</t>
+          <t>PDD Holdings Inc ADR</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>125110000000</v>
+        <v>124460000000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Intuitive Surgical Inc</t>
+          <t>S&amp;P Global Inc</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>124740000000</v>
+        <v>122340000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>S&amp;P Global Inc</t>
+          <t>Starbucks Corp</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>124210000000</v>
+        <v>120640000000</v>
       </c>
     </row>
     <row r="100">
@@ -1986,52 +1986,52 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>120930000000</v>
+        <v>117790000000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Starbucks Corp</t>
+          <t>Corning Inc</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>118690000000</v>
+        <v>116380000000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Medtronic Plc</t>
+          <t>Altria Group Inc</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>112060000000</v>
+        <v>113450000000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc</t>
+          <t>Medtronic Plc</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>109280000000</v>
+        <v>109710000000</v>
       </c>
     </row>
     <row r="104">
@@ -2046,172 +2046,172 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>107880000000</v>
+        <v>107600000000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Corning Inc</t>
+          <t>Automatic Data Processing Inc</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>106760000000</v>
+        <v>105480000000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>Snowflake Inc</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>105970000000</v>
+        <v>103320000000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>Equinix Inc</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>104710000000</v>
+        <v>103310000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Equinix Inc</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>99420000000</v>
+        <v>100640000000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Snowflake Inc</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>98050000000</v>
+        <v>99920000000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>97870000000</v>
+        <v>98540000000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>96020000000</v>
+        <v>98000000000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>MercadoLibre Inc</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>94460000000</v>
+        <v>95600000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MMC</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Marsh</t>
+          <t>MercadoLibre Inc</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>94290000000</v>
+        <v>95600000000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>Airbnb Inc</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>94040000000</v>
+        <v>91660000000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>MMC</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Airbnb Inc</t>
+          <t>Marsh</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>92220000000</v>
+        <v>91390000000</v>
       </c>
     </row>
     <row r="116">
@@ -2226,97 +2226,97 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>91770000000</v>
+        <v>90800000000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Intuit Inc</t>
+          <t>United Parcel Service Inc</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>91120000000</v>
+        <v>89480000000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>HCA Healthcare Inc</t>
+          <t>Intercontinental Exchange Inc</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>90550000000</v>
+        <v>88370000000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>United Parcel Service Inc</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>88880000000</v>
+        <v>87380000000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange Inc</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>87250000000</v>
+        <v>86340000000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Intuit Inc</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>86780000000</v>
+        <v>86300000000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>HCA Healthcare Inc</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>85670000000</v>
+        <v>85690000000</v>
       </c>
     </row>
     <row r="123">
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>81540000000</v>
+        <v>81630000000</v>
       </c>
     </row>
     <row r="124">
@@ -2346,127 +2346,127 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>78440000000</v>
+        <v>77570000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Cigna Group</t>
+          <t>Regeneron Pharmaceuticals Inc</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>78430000000</v>
+        <v>77410000000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp</t>
+          <t>Cigna Group</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>76010000000</v>
+        <v>76100000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive Co</t>
+          <t>Northrop Grumman Corp</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>74810000000</v>
+        <v>75980000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SLB Ltd</t>
+          <t>Colgate-Palmolive Co</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>73200000000</v>
+        <v>73300000000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals Inc</t>
+          <t>SLB Ltd</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>72910000000</v>
+        <v>73120000000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Apollo Global Management Inc</t>
+          <t>Ferrari NV</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>69050000000</v>
+        <v>70200000000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Ferrari NV</t>
+          <t>Nu Holdings Ltd</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>68080000000</v>
+        <v>69990000000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>NU</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Nu Holdings Ltd</t>
+          <t>Apollo Global Management Inc</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>67820000000</v>
+        <v>69330000000</v>
       </c>
     </row>
     <row r="133">
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>66270000000</v>
+        <v>65640000000</v>
       </c>
     </row>
     <row r="134">
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>64120000000</v>
+        <v>62740000000</v>
       </c>
     </row>
     <row r="135">
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>61440000000</v>
+        <v>60230000000</v>
       </c>
     </row>
     <row r="136">
@@ -2526,7 +2526,7 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>60890000000</v>
+        <v>59210000000</v>
       </c>
     </row>
     <row r="137">
@@ -2541,22 +2541,22 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>55730000000</v>
+        <v>55650000000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Autodesk Inc</t>
+          <t>Astera Labs Inc</t>
         </is>
       </c>
       <c r="L138" t="n">
-        <v>51750000000</v>
+        <v>51370000000</v>
       </c>
     </row>
     <row r="139">
@@ -2571,52 +2571,52 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>51470000000</v>
+        <v>50850000000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences Corp</t>
+          <t>Vistra Corp</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>49380000000</v>
+        <v>50110000000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Block Inc</t>
+          <t>Edwards Lifesciences Corp</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>48910000000</v>
+        <v>50050000000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Vistra Corp</t>
+          <t>Autodesk Inc</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>48150000000</v>
+        <v>49580000000</v>
       </c>
     </row>
     <row r="143">
@@ -2631,37 +2631,37 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>43920000000</v>
+        <v>49410000000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Astera Labs Inc</t>
+          <t>Block Inc</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>42810000000</v>
+        <v>49160000000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MSCI Inc</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>42380000000</v>
+        <v>47420000000</v>
       </c>
     </row>
     <row r="146">
@@ -2676,67 +2676,67 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>42180000000</v>
+        <v>43100000000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Workday Inc</t>
+          <t>MSCI Inc</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>41500000000</v>
+        <v>41860000000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>JD</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>JD.com Inc ADR</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>39060000000</v>
+        <v>40320000000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Carnival Corp Ltd</t>
+          <t>JD.com Inc ADR</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>38090000000</v>
+        <v>39200000000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Workday Inc</t>
         </is>
       </c>
       <c r="L150" t="n">
-        <v>37300000000</v>
+        <v>39050000000</v>
       </c>
     </row>
     <row r="151">
@@ -2751,37 +2751,37 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>35050000000</v>
+        <v>38690000000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>RDDT</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Reddit Inc</t>
+          <t>Carnival Corp Ltd</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>34260000000</v>
+        <v>38040000000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>RDDT</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Reddit Inc</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>33180000000</v>
+        <v>34270000000</v>
       </c>
     </row>
     <row r="154">
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>32710000000</v>
+        <v>34250000000</v>
       </c>
     </row>
     <row r="155">
@@ -2811,67 +2811,67 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>32670000000</v>
+        <v>31870000000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Estee Lauder Cos. Inc</t>
+          <t>Illumina Inc</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>30440000000</v>
+        <v>31030000000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Fiserv Inc</t>
+          <t>Estee Lauder Cos. Inc</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>29660000000</v>
+        <v>30710000000</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Illumina Inc</t>
+          <t>Twilio Inc</t>
         </is>
       </c>
       <c r="L158" t="n">
-        <v>29480000000</v>
+        <v>28980000000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Twilio Inc</t>
+          <t>Fiserv Inc</t>
         </is>
       </c>
       <c r="L159" t="n">
-        <v>28570000000</v>
+        <v>28830000000</v>
       </c>
     </row>
     <row r="160">
@@ -2886,67 +2886,67 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>27100000000</v>
+        <v>27070000000</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>AFRM</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Zscaler Inc</t>
+          <t>Affirm Holdings Inc</t>
         </is>
       </c>
       <c r="L161" t="n">
-        <v>24870000000</v>
+        <v>24530000000</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>AFRM</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Affirm Holdings Inc</t>
+          <t>Zscaler Inc</t>
         </is>
       </c>
       <c r="L162" t="n">
-        <v>23480000000</v>
+        <v>24000000000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>DKNG</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>DraftKings Inc</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="L163" t="n">
-        <v>21830000000</v>
+        <v>22980000000</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>First Solar Inc</t>
         </is>
       </c>
       <c r="L164" t="n">
-        <v>21620000000</v>
+        <v>22140000000</v>
       </c>
     </row>
     <row r="165">
@@ -2961,37 +2961,37 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>21560000000</v>
+        <v>21520000000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>First Solar Inc</t>
+          <t>SoFi Technologies Inc</t>
         </is>
       </c>
       <c r="L166" t="n">
-        <v>21410000000</v>
+        <v>21130000000</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>DKNG</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>SoFi Technologies Inc</t>
+          <t>DraftKings Inc</t>
         </is>
       </c>
       <c r="L167" t="n">
-        <v>19560000000</v>
+        <v>21090000000</v>
       </c>
     </row>
     <row r="168">
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>19430000000</v>
+        <v>19000000000</v>
       </c>
     </row>
     <row r="169">
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>16620000000</v>
+        <v>17940000000</v>
       </c>
     </row>
     <row r="170">
@@ -3036,22 +3036,22 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>15250000000</v>
+        <v>15970000000</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>TXRH</t>
+          <t>GRAB</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Texas Roadhouse Inc</t>
+          <t>Grab Holdings Limited</t>
         </is>
       </c>
       <c r="L171" t="n">
-        <v>13750000000</v>
+        <v>13940000000</v>
       </c>
     </row>
     <row r="172">
@@ -3066,22 +3066,22 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>13730000000</v>
+        <v>13940000000</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>GRAB</t>
+          <t>TXRH</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Grab Holdings Limited</t>
+          <t>Texas Roadhouse Inc</t>
         </is>
       </c>
       <c r="L173" t="n">
-        <v>13730000000</v>
+        <v>13690000000</v>
       </c>
     </row>
     <row r="174">
@@ -3096,52 +3096,52 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>13690000000</v>
+        <v>13680000000</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>IonQ Inc</t>
+          <t>IREN Ltd</t>
         </is>
       </c>
       <c r="L175" t="n">
-        <v>11940000000</v>
+        <v>13650000000</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>BROS</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Dutch Bros Inc</t>
+          <t>IonQ Inc</t>
         </is>
       </c>
       <c r="L176" t="n">
-        <v>10650000000</v>
+        <v>13350000000</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>BROS</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>IREN Ltd</t>
+          <t>Dutch Bros Inc</t>
         </is>
       </c>
       <c r="L177" t="n">
-        <v>10460000000</v>
+        <v>10780000000</v>
       </c>
     </row>
     <row r="178">
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>9220000000</v>
+        <v>9420000000</v>
       </c>
     </row>
     <row r="179">
@@ -3171,97 +3171,97 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>8350000000</v>
+        <v>8260000000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Zillow Group Inc</t>
+          <t>Applied Digital Corp</t>
         </is>
       </c>
       <c r="L180" t="n">
-        <v>7790000000</v>
+        <v>7990000000</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Celsius Holdings Inc</t>
+          <t>Zillow Group Inc</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>7380000000</v>
+        <v>7730000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>AeroVironment Inc</t>
+          <t>Celsius Holdings Inc</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>7190000000</v>
+        <v>7500000000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>MBLY</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Mobileye Global Inc</t>
+          <t>AeroVironment Inc</t>
         </is>
       </c>
       <c r="L183" t="n">
-        <v>6810000000</v>
+        <v>7420000000</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>OKLO</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Applied Digital Corp</t>
+          <t>Oklo Inc</t>
         </is>
       </c>
       <c r="L184" t="n">
-        <v>6640000000</v>
+        <v>7150000000</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>OKLO</t>
+          <t>MBLY</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Oklo Inc</t>
+          <t>Mobileye Global Inc</t>
         </is>
       </c>
       <c r="L185" t="n">
-        <v>6410000000</v>
+        <v>6720000000</v>
       </c>
     </row>
     <row r="186">
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>6350000000</v>
+        <v>6310000000</v>
       </c>
     </row>
     <row r="187">
@@ -3291,67 +3291,67 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>5790000000</v>
+        <v>6260000000</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>CRSP</t>
+          <t>RGTI</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>CRISPR Therapeutics AG</t>
+          <t>Rigetti Computing Inc</t>
         </is>
       </c>
       <c r="L188" t="n">
-        <v>4590000000</v>
+        <v>4940000000</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>RGTI</t>
+          <t>CRSP</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Rigetti Computing Inc</t>
+          <t>CRISPR Therapeutics AG</t>
         </is>
       </c>
       <c r="L189" t="n">
-        <v>4390000000</v>
+        <v>4670000000</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ONDS</t>
+          <t>MARA</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Ondas Inc</t>
+          <t>MARA Holdings Inc</t>
         </is>
       </c>
       <c r="L190" t="n">
-        <v>3870000000</v>
+        <v>4510000000</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>MARA</t>
+          <t>ONDS</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>MARA Holdings Inc</t>
+          <t>Ondas Inc</t>
         </is>
       </c>
       <c r="L191" t="n">
-        <v>3830000000</v>
+        <v>4320000000</v>
       </c>
     </row>
     <row r="192">
@@ -3366,67 +3366,67 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>3640000000</v>
+        <v>3730000000</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>FSLY</t>
+          <t>LEU</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Fastly Inc</t>
+          <t>Centrus Energy Corp</t>
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3240000000</v>
+        <v>3480000000</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>LEU</t>
+          <t>FSLY</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Centrus Energy Corp</t>
+          <t>Fastly Inc</t>
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3140000000</v>
+        <v>3370000000</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>PENN</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>PENN Entertainment Inc</t>
+          <t>NuScale Power Corp</t>
         </is>
       </c>
       <c r="L195" t="n">
-        <v>2840000000</v>
+        <v>3140000000</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>PENN</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>NuScale Power Corp</t>
+          <t>PENN Entertainment Inc</t>
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2770000000</v>
+        <v>2750000000</v>
       </c>
     </row>
     <row r="197">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2700000000</v>
+        <v>2630000000</v>
       </c>
     </row>
     <row r="198">
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2550000000</v>
+        <v>2590000000</v>
       </c>
     </row>
     <row r="199">
@@ -3471,52 +3471,52 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>2190000000</v>
+        <v>2480000000</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>TDOC</t>
+          <t>QUBT</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Teladoc Health Inc</t>
+          <t>Quantum Computing Inc</t>
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1660000000</v>
+        <v>1810000000</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>QUBT</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Quantum Computing Inc</t>
+          <t>C3.ai Inc</t>
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1650000000</v>
+        <v>1410000000</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>TDOC</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>C3.ai Inc</t>
+          <t>Teladoc Health Inc</t>
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1380000000</v>
+        <v>1190000000</v>
       </c>
     </row>
     <row r="203">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>824920000</v>
+        <v>980250000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>775000000</v>
+        <v>895690000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>445700000</v>
+        <v>501100000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4897210000000</v>
+        <v>4537070000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4719970000000</v>
+        <v>4858150000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4087230000000</v>
+        <v>4361690000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3350970000000</v>
+        <v>3450800000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2533300000000</v>
+        <v>2921420000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2091760000000</v>
+        <v>2096630000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1845180000000</v>
+        <v>1852030000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1368290000000</v>
+        <v>1412960000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1219820000000</v>
+        <v>1229140000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1087680000000</v>
+        <v>1081910000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,37 +711,37 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>989060000000</v>
+        <v>993200000000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Micron Technology Inc</t>
+          <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>987830000000</v>
+        <v>942630000000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co</t>
+          <t>Micron Technology Inc</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>940110000000</v>
+        <v>929520000000</v>
       </c>
     </row>
     <row r="18">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>884140000000</v>
+        <v>884940000000</v>
       </c>
     </row>
     <row r="19">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>791480000000</v>
+        <v>776410000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>665240000000</v>
+        <v>651420000000</v>
       </c>
     </row>
     <row r="21">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>650560000000</v>
+        <v>644210000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>636500000000</v>
+        <v>627850000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>616500000000</v>
+        <v>617780000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,37 +846,37 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>510140000000</v>
+        <v>506640000000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Abbvie Inc</t>
+          <t>Cisco Systems Inc</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>454790000000</v>
+        <v>457170000000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cisco Systems Inc</t>
+          <t>Abbvie Inc</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>447590000000</v>
+        <v>443360000000</v>
       </c>
     </row>
     <row r="27">
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>438070000000</v>
+        <v>439630000000</v>
       </c>
     </row>
     <row r="28">
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>423150000000</v>
+        <v>422140000000</v>
       </c>
     </row>
     <row r="29">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>398380000000</v>
+        <v>403070000000</v>
       </c>
     </row>
     <row r="30">
@@ -936,37 +936,37 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>383000000000</v>
+        <v>392010000000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Unitedhealth Group Inc</t>
+          <t>Coca-Cola Co</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>382760000000</v>
+        <v>376860000000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Coca-Cola Co</t>
+          <t>Unitedhealth Group Inc</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>380730000000</v>
+        <v>376340000000</v>
       </c>
     </row>
     <row r="33">
@@ -981,22 +981,22 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>372720000000</v>
+        <v>375330000000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Lam Research Corp</t>
+          <t>Oracle Corp</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>372320000000</v>
+        <v>374090000000</v>
       </c>
     </row>
     <row r="35">
@@ -1011,22 +1011,22 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>368380000000</v>
+        <v>373600000000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Oracle Corp</t>
+          <t>Lam Research Corp</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>367430000000</v>
+        <v>366440000000</v>
       </c>
     </row>
     <row r="37">
@@ -1041,37 +1041,37 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>335230000000</v>
+        <v>336460000000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Home Depot Inc</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>332390000000</v>
+        <v>331890000000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Home Depot Inc</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>331320000000</v>
+        <v>331000000000</v>
       </c>
     </row>
     <row r="40">
@@ -1086,37 +1086,37 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>320560000000</v>
+        <v>321570000000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Netflix Inc</t>
+          <t>Goldman Sachs Group Inc</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>304680000000</v>
+        <v>300430000000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Goldman Sachs Group Inc</t>
+          <t>Netflix Inc</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>302340000000</v>
+        <v>298600000000</v>
       </c>
     </row>
     <row r="43">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>299250000000</v>
+        <v>297410000000</v>
       </c>
     </row>
     <row r="44">
@@ -1146,22 +1146,22 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>293100000000</v>
+        <v>295010000000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NVS</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Novartis AG ADR</t>
+          <t>Alibaba Group Holding Ltd ADR</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>290030000000</v>
+        <v>293040000000</v>
       </c>
     </row>
     <row r="46">
@@ -1176,82 +1176,82 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>288930000000</v>
+        <v>290060000000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>NVS</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Alibaba Group Holding Ltd ADR</t>
+          <t>Novartis AG ADR</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>278830000000</v>
+        <v>285840000000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Astrazeneca plc</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>265730000000</v>
+        <v>270440000000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>265430000000</v>
+        <v>263750000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>Astrazeneca plc</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>262430000000</v>
+        <v>263090000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>261530000000</v>
+        <v>262790000000</v>
       </c>
     </row>
     <row r="52">
@@ -1266,52 +1266,52 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>261430000000</v>
+        <v>261420000000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>Shell Plc ADR</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>257000000000</v>
+        <v>256450000000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>254580000000</v>
+        <v>255990000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Shell Plc ADR</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>252350000000</v>
+        <v>251820000000</v>
       </c>
     </row>
     <row r="56">
@@ -1326,22 +1326,22 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>235560000000</v>
+        <v>238810000000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Linde Plc</t>
+          <t>Citigroup Inc</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>235300000000</v>
+        <v>227140000000</v>
       </c>
     </row>
     <row r="58">
@@ -1356,22 +1356,22 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>227930000000</v>
+        <v>227070000000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Citigroup Inc</t>
+          <t>Linde Plc</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>226920000000</v>
+        <v>221300000000</v>
       </c>
     </row>
     <row r="60">
@@ -1386,22 +1386,22 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>214340000000</v>
+        <v>213420000000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>AMGEN Inc</t>
+          <t>Sap SE ADR</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>209210000000</v>
+        <v>211930000000</v>
       </c>
     </row>
     <row r="62">
@@ -1416,22 +1416,22 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>208910000000</v>
+        <v>210710000000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Sap SE ADR</t>
+          <t>AMGEN Inc</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>208770000000</v>
+        <v>207870000000</v>
       </c>
     </row>
     <row r="64">
@@ -1446,52 +1446,52 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>203710000000</v>
+        <v>201090000000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Verizon Communications Inc</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>193570000000</v>
+        <v>195460000000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>192540000000</v>
+        <v>195420000000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PepsiCo Inc</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>191360000000</v>
+        <v>194340000000</v>
       </c>
     </row>
     <row r="68">
@@ -1506,37 +1506,37 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>190730000000</v>
+        <v>192290000000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>PepsiCo Inc</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>189550000000</v>
+        <v>190480000000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>188600000000</v>
+        <v>187800000000</v>
       </c>
     </row>
     <row r="71">
@@ -1551,67 +1551,67 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>185940000000</v>
+        <v>185260000000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>Charles Schwab Corp</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>183730000000</v>
+        <v>183030000000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>NextEra Energy Inc</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>183400000000</v>
+        <v>182900000000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>NextEra Energy Inc</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>182750000000</v>
+        <v>181310000000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Charles Schwab Corp</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>181440000000</v>
+        <v>179900000000</v>
       </c>
     </row>
     <row r="76">
@@ -1626,7 +1626,7 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>178600000000</v>
+        <v>177300000000</v>
       </c>
     </row>
     <row r="77">
@@ -1641,112 +1641,112 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>174590000000</v>
+        <v>170830000000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Novo Nordisk ADR</t>
+          <t>Walt Disney Co</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>173310000000</v>
+        <v>167040000000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Walt Disney Co</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>166980000000</v>
+        <v>161660000000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>Deere &amp; Co</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>162990000000</v>
+        <v>159980000000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Deere &amp; Co</t>
+          <t>AT&amp;T Inc</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>161820000000</v>
+        <v>159320000000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>Blackstone Inc</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>159790000000</v>
+        <v>158900000000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Blackstone Inc</t>
+          <t>Novo Nordisk ADR</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>159300000000</v>
+        <v>158090000000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>159040000000</v>
+        <v>154990000000</v>
       </c>
     </row>
     <row r="85">
@@ -1761,37 +1761,37 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>158830000000</v>
+        <v>152020000000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>Salesforce Inc</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>149740000000</v>
+        <v>150710000000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Salesforce Inc</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>148000000000</v>
+        <v>149470000000</v>
       </c>
     </row>
     <row r="88">
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>143250000000</v>
+        <v>143220000000</v>
       </c>
     </row>
     <row r="89">
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>139180000000</v>
+        <v>137780000000</v>
       </c>
     </row>
     <row r="90">
@@ -1836,112 +1836,112 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>137900000000</v>
+        <v>137070000000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>Chubb Limited</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>135680000000</v>
+        <v>135290000000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Chubb Limited</t>
+          <t>Lockheed Martin Corp</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>135090000000</v>
+        <v>134490000000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corp</t>
+          <t>Bristol-Myers Squibb Co</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>132500000000</v>
+        <v>133370000000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Co</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>132450000000</v>
+        <v>133000000000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Intuitive Surgical Inc</t>
+          <t>PDD Holdings Inc ADR</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>124700000000</v>
+        <v>126060000000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Progressive Corp</t>
+          <t>Intuitive Surgical Inc</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>124630000000</v>
+        <v>124820000000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PDD Holdings Inc ADR</t>
+          <t>Progressive Corp</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>124460000000</v>
+        <v>123540000000</v>
       </c>
     </row>
     <row r="98">
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>122340000000</v>
+        <v>121440000000</v>
       </c>
     </row>
     <row r="99">
@@ -1971,37 +1971,37 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>120640000000</v>
+        <v>119990000000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Lowe's Cos. Inc</t>
+          <t>Corning Inc</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>117790000000</v>
+        <v>119090000000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Corning Inc</t>
+          <t>Lowe's Cos. Inc</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>116380000000</v>
+        <v>116520000000</v>
       </c>
     </row>
     <row r="102">
@@ -2016,7 +2016,7 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>113450000000</v>
+        <v>114100000000</v>
       </c>
     </row>
     <row r="103">
@@ -2031,37 +2031,37 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>109710000000</v>
+        <v>109300000000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Spotify Technology SA</t>
+          <t>Automatic Data Processing Inc</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>107600000000</v>
+        <v>106510000000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc</t>
+          <t>Spotify Technology SA</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>105480000000</v>
+        <v>102930000000</v>
       </c>
     </row>
     <row r="106">
@@ -2076,67 +2076,67 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>103320000000</v>
+        <v>101650000000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Equinix Inc</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>103310000000</v>
+        <v>101530000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>Equinix Inc</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>100640000000</v>
+        <v>100570000000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>99920000000</v>
+        <v>99540000000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>98540000000</v>
+        <v>99070000000</v>
       </c>
     </row>
     <row r="111">
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>98000000000</v>
+        <v>98170000000</v>
       </c>
     </row>
     <row r="112">
@@ -2166,7 +2166,7 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>95600000000</v>
+        <v>95390000000</v>
       </c>
     </row>
     <row r="113">
@@ -2181,37 +2181,37 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>95600000000</v>
+        <v>95210000000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Airbnb Inc</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>91660000000</v>
+        <v>93000000000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MMC</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Marsh</t>
+          <t>Airbnb Inc</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>91390000000</v>
+        <v>91320000000</v>
       </c>
     </row>
     <row r="116">
@@ -2226,97 +2226,97 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>90800000000</v>
+        <v>90910000000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>MMC</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>United Parcel Service Inc</t>
+          <t>Marsh</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>89480000000</v>
+        <v>90520000000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange Inc</t>
+          <t>United Parcel Service Inc</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>88370000000</v>
+        <v>88590000000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>HCA Healthcare Inc</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>87380000000</v>
+        <v>87160000000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Intuit Inc</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>86340000000</v>
+        <v>86460000000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Intuit Inc</t>
+          <t>Intercontinental Exchange Inc</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>86300000000</v>
+        <v>85600000000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>HCA Healthcare Inc</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>85690000000</v>
+        <v>85370000000</v>
       </c>
     </row>
     <row r="123">
@@ -2331,142 +2331,142 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>81630000000</v>
+        <v>81510000000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>General Motors Company</t>
+          <t>Regeneron Pharmaceuticals Inc</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>77570000000</v>
+        <v>79940000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals Inc</t>
+          <t>General Motors Company</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>77410000000</v>
+        <v>77970000000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Cigna Group</t>
+          <t>Northrop Grumman Corp</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>76100000000</v>
+        <v>77070000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp</t>
+          <t>SLB Ltd</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>75980000000</v>
+        <v>74140000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive Co</t>
+          <t>Cigna Group</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>73300000000</v>
+        <v>73820000000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SLB Ltd</t>
+          <t>Colgate-Palmolive Co</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>73120000000</v>
+        <v>73060000000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Ferrari NV</t>
+          <t>Apollo Global Management Inc</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>70200000000</v>
+        <v>72400000000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>NU</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Nu Holdings Ltd</t>
+          <t>Ferrari NV</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>69990000000</v>
+        <v>69290000000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Apollo Global Management Inc</t>
+          <t>Nu Holdings Ltd</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>69330000000</v>
+        <v>69220000000</v>
       </c>
     </row>
     <row r="133">
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>65640000000</v>
+        <v>65630000000</v>
       </c>
     </row>
     <row r="134">
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>62740000000</v>
+        <v>61880000000</v>
       </c>
     </row>
     <row r="135">
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>60230000000</v>
+        <v>60520000000</v>
       </c>
     </row>
     <row r="136">
@@ -2526,7 +2526,7 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>59210000000</v>
+        <v>58540000000</v>
       </c>
     </row>
     <row r="137">
@@ -2541,7 +2541,7 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>55650000000</v>
+        <v>56760000000</v>
       </c>
     </row>
     <row r="138">
@@ -2556,202 +2556,202 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>51370000000</v>
+        <v>53350000000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>PayPal Holdings Inc</t>
+          <t>Vistra Corp</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>50850000000</v>
+        <v>49970000000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Vistra Corp</t>
+          <t>Edwards Lifesciences Corp</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>50110000000</v>
+        <v>49560000000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences Corp</t>
+          <t>Autodesk Inc</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>50050000000</v>
+        <v>49420000000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Autodesk Inc</t>
+          <t>PayPal Holdings Inc</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>49580000000</v>
+        <v>48940000000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>Block Inc</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>49410000000</v>
+        <v>48350000000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Block Inc</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>49160000000</v>
+        <v>47920000000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>47420000000</v>
+        <v>47740000000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Coinbase Global Inc</t>
+          <t>MSCI Inc</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>43100000000</v>
+        <v>41600000000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MSCI Inc</t>
+          <t>JD.com Inc ADR</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>41860000000</v>
+        <v>40050000000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Workday Inc</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>40320000000</v>
+        <v>39600000000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>JD</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>JD.com Inc ADR</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>39200000000</v>
+        <v>39160000000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Workday Inc</t>
+          <t>Rocket Lab Corp</t>
         </is>
       </c>
       <c r="L150" t="n">
-        <v>39050000000</v>
+        <v>38850000000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Rocket Lab Corp</t>
+          <t>Coinbase Global Inc</t>
         </is>
       </c>
       <c r="L151" t="n">
-        <v>38690000000</v>
+        <v>38530000000</v>
       </c>
     </row>
     <row r="152">
@@ -2766,187 +2766,187 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>38040000000</v>
+        <v>38090000000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>RDDT</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Reddit Inc</t>
+          <t>Strategy Inc</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>34270000000</v>
+        <v>32690000000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Strategy Inc</t>
+          <t>Zoetis Inc</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>34250000000</v>
+        <v>32400000000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Zoetis Inc</t>
+          <t>Illumina Inc</t>
         </is>
       </c>
       <c r="L155" t="n">
-        <v>31870000000</v>
+        <v>31030000000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Illumina Inc</t>
+          <t>Estee Lauder Cos. Inc</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>31030000000</v>
+        <v>30350000000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Estee Lauder Cos. Inc</t>
+          <t>Twilio Inc</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>30710000000</v>
+        <v>29950000000</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Twilio Inc</t>
+          <t>Fiserv Inc</t>
         </is>
       </c>
       <c r="L158" t="n">
-        <v>28980000000</v>
+        <v>28760000000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>ZM</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Fiserv Inc</t>
+          <t>Zoom Communications Inc</t>
         </is>
       </c>
       <c r="L159" t="n">
-        <v>28830000000</v>
+        <v>28170000000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ZM</t>
+          <t>RDDT</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Zoom Communications Inc</t>
+          <t>Reddit Inc</t>
         </is>
       </c>
       <c r="L160" t="n">
-        <v>27070000000</v>
+        <v>27080000000</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>AFRM</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Affirm Holdings Inc</t>
+          <t>Zscaler Inc</t>
         </is>
       </c>
       <c r="L161" t="n">
-        <v>24530000000</v>
+        <v>24450000000</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>AFRM</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Zscaler Inc</t>
+          <t>Affirm Holdings Inc</t>
         </is>
       </c>
       <c r="L162" t="n">
-        <v>24000000000</v>
+        <v>23950000000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>First Solar Inc</t>
         </is>
       </c>
       <c r="L163" t="n">
-        <v>22980000000</v>
+        <v>22680000000</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>First Solar Inc</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="L164" t="n">
-        <v>22140000000</v>
+        <v>21750000000</v>
       </c>
     </row>
     <row r="165">
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>21520000000</v>
+        <v>21510000000</v>
       </c>
     </row>
     <row r="166">
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>21130000000</v>
+        <v>20920000000</v>
       </c>
     </row>
     <row r="167">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>21090000000</v>
+        <v>20880000000</v>
       </c>
     </row>
     <row r="168">
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>19000000000</v>
+        <v>19400000000</v>
       </c>
     </row>
     <row r="169">
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>17940000000</v>
+        <v>18370000000</v>
       </c>
     </row>
     <row r="170">
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>15970000000</v>
+        <v>15560000000</v>
       </c>
     </row>
     <row r="171">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>13940000000</v>
+        <v>14350000000</v>
       </c>
     </row>
     <row r="172">
@@ -3066,67 +3066,67 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>13940000000</v>
+        <v>14350000000</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>TXRH</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Texas Roadhouse Inc</t>
+          <t>IonQ Inc</t>
         </is>
       </c>
       <c r="L173" t="n">
-        <v>13690000000</v>
+        <v>13600000000</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>PINS</t>
+          <t>TXRH</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Pinterest Inc</t>
+          <t>Texas Roadhouse Inc</t>
         </is>
       </c>
       <c r="L174" t="n">
-        <v>13680000000</v>
+        <v>13500000000</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>PINS</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>IREN Ltd</t>
+          <t>Pinterest Inc</t>
         </is>
       </c>
       <c r="L175" t="n">
-        <v>13650000000</v>
+        <v>13450000000</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>IonQ Inc</t>
+          <t>IREN Ltd</t>
         </is>
       </c>
       <c r="L176" t="n">
-        <v>13350000000</v>
+        <v>13130000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>10780000000</v>
+        <v>10850000000</v>
       </c>
     </row>
     <row r="178">
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>9420000000</v>
+        <v>9410000000</v>
       </c>
     </row>
     <row r="179">
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>8260000000</v>
+        <v>8240000000</v>
       </c>
     </row>
     <row r="180">
@@ -3186,7 +3186,7 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>7990000000</v>
+        <v>7980000000</v>
       </c>
     </row>
     <row r="181">
@@ -3201,37 +3201,37 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>7730000000</v>
+        <v>7810000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Celsius Holdings Inc</t>
+          <t>AeroVironment Inc</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>7500000000</v>
+        <v>7560000000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>AeroVironment Inc</t>
+          <t>Celsius Holdings Inc</t>
         </is>
       </c>
       <c r="L183" t="n">
-        <v>7420000000</v>
+        <v>7470000000</v>
       </c>
     </row>
     <row r="184">
@@ -3246,7 +3246,7 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>7150000000</v>
+        <v>6760000000</v>
       </c>
     </row>
     <row r="185">
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>6720000000</v>
+        <v>6750000000</v>
       </c>
     </row>
     <row r="186">
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>6310000000</v>
+        <v>6530000000</v>
       </c>
     </row>
     <row r="187">
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>6260000000</v>
+        <v>6430000000</v>
       </c>
     </row>
     <row r="188">
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>4940000000</v>
+        <v>4970000000</v>
       </c>
     </row>
     <row r="189">
@@ -3321,7 +3321,7 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>4670000000</v>
+        <v>4630000000</v>
       </c>
     </row>
     <row r="190">
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>4510000000</v>
+        <v>4320000000</v>
       </c>
     </row>
     <row r="191">
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>4320000000</v>
+        <v>4270000000</v>
       </c>
     </row>
     <row r="192">
@@ -3366,37 +3366,37 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>3730000000</v>
+        <v>3710000000</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>LEU</t>
+          <t>FSLY</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Centrus Energy Corp</t>
+          <t>Fastly Inc</t>
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3480000000</v>
+        <v>3550000000</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>FSLY</t>
+          <t>LEU</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Fastly Inc</t>
+          <t>Centrus Energy Corp</t>
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3370000000</v>
+        <v>3480000000</v>
       </c>
     </row>
     <row r="195">
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>3140000000</v>
+        <v>3080000000</v>
       </c>
     </row>
     <row r="196">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2630000000</v>
+        <v>2640000000</v>
       </c>
     </row>
     <row r="198">
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2590000000</v>
+        <v>2630000000</v>
       </c>
     </row>
     <row r="199">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>2480000000</v>
+        <v>2570000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1810000000</v>
+        <v>1830000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1410000000</v>
+        <v>1430000000</v>
       </c>
     </row>
     <row r="202">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1190000000</v>
+        <v>1210000000</v>
       </c>
     </row>
     <row r="203">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>980250000</v>
+        <v>1010000000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>895690000</v>
+        <v>854340000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>501100000</v>
+        <v>503620000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4361690000000</v>
+        <v>4358340000000</v>
       </c>
     </row>
     <row r="8">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1412960000000</v>
+        <v>1418010000000</v>
       </c>
     </row>
     <row r="13">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>993200000000</v>
+        <v>992600000000</v>
       </c>
     </row>
     <row r="16">
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>137780000000</v>
+        <v>137670000000</v>
       </c>
     </row>
     <row r="90">
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>133370000000</v>
+        <v>133410000000</v>
       </c>
     </row>
     <row r="94">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>119990000000</v>
+        <v>119980000000</v>
       </c>
     </row>
     <row r="100">
@@ -2016,7 +2016,7 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>114100000000</v>
+        <v>114090000000</v>
       </c>
     </row>
     <row r="103">
@@ -2382,16 +2382,16 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>SLB Ltd</t>
+          <t>Apollo Global Management Inc</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>74140000000</v>
+        <v>74240000000</v>
       </c>
     </row>
     <row r="128">
@@ -2406,37 +2406,37 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>73820000000</v>
+        <v>73740000000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive Co</t>
+          <t>SLB Ltd</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>73060000000</v>
+        <v>73600000000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Apollo Global Management Inc</t>
+          <t>Colgate-Palmolive Co</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>72400000000</v>
+        <v>73060000000</v>
       </c>
     </row>
     <row r="131">
@@ -3201,7 +3201,7 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>7810000000</v>
+        <v>7820000000</v>
       </c>
     </row>
     <row r="182">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1210000000</v>
+        <v>1220000000</v>
       </c>
     </row>
     <row r="203">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>503620000</v>
+        <v>503610000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -1095,11 +1095,6 @@
           <t>GS</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Goldman Sachs Group Inc</t>
-        </is>
-      </c>
       <c r="L41" t="n">
         <v>300430000000</v>
       </c>

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4537070000000</v>
+        <v>4456440000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4858150000000</v>
+        <v>5000690000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4358340000000</v>
+        <v>4551670000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3450800000000</v>
+        <v>3621070000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2921420000000</v>
+        <v>3055230000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2096630000000</v>
+        <v>2106280000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1852030000000</v>
+        <v>1866070000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1418010000000</v>
+        <v>1503420000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1229140000000</v>
+        <v>1272070000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1081910000000</v>
+        <v>1056030000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>992600000000</v>
+        <v>995710000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>942630000000</v>
+        <v>944900000000</v>
       </c>
     </row>
     <row r="17">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>929520000000</v>
+        <v>936830000000</v>
       </c>
     </row>
     <row r="18">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>884940000000</v>
+        <v>881040000000</v>
       </c>
     </row>
     <row r="19">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>776410000000</v>
+        <v>790250000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>651420000000</v>
+        <v>672910000000</v>
       </c>
     </row>
     <row r="21">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>644210000000</v>
+        <v>642640000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>627850000000</v>
+        <v>633060000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>617780000000</v>
+        <v>613100000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>506640000000</v>
+        <v>504760000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,37 +861,37 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>457170000000</v>
+        <v>456650000000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Abbvie Inc</t>
+          <t>Bank Of America Corp</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>443360000000</v>
+        <v>443390000000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Bank Of America Corp</t>
+          <t>Abbvie Inc</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>439630000000</v>
+        <v>433040000000</v>
       </c>
     </row>
     <row r="28">
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>422140000000</v>
+        <v>423110000000</v>
       </c>
     </row>
     <row r="29">
@@ -921,52 +921,52 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>403070000000</v>
+        <v>411440000000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Chevron Corp</t>
+          <t>Oracle Corp</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>392010000000</v>
+        <v>408590000000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Coca-Cola Co</t>
+          <t>Chevron Corp</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>376860000000</v>
+        <v>384740000000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Unitedhealth Group Inc</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>376340000000</v>
+        <v>382790000000</v>
       </c>
     </row>
     <row r="33">
@@ -981,37 +981,37 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>375330000000</v>
+        <v>382340000000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Oracle Corp</t>
+          <t>Unitedhealth Group Inc</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>374090000000</v>
+        <v>377210000000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Coca-Cola Co</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>373600000000</v>
+        <v>373720000000</v>
       </c>
     </row>
     <row r="36">
@@ -1026,52 +1026,52 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>366440000000</v>
+        <v>368430000000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble Co</t>
+          <t>Home Depot Inc</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>336460000000</v>
+        <v>339040000000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Procter &amp; Gamble Co</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>331890000000</v>
+        <v>337580000000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Home Depot Inc</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>331000000000</v>
+        <v>333170000000</v>
       </c>
     </row>
     <row r="40">
@@ -1086,47 +1086,47 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>321570000000</v>
+        <v>315570000000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Netflix Inc</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>300430000000</v>
+        <v>305340000000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Netflix Inc</t>
+          <t>Alibaba Group Holding Ltd ADR</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>298600000000</v>
+        <v>305150000000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Philip Morris International Inc</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>297410000000</v>
+        <v>302990000000</v>
       </c>
     </row>
     <row r="44">
@@ -1141,22 +1141,22 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>295010000000</v>
+        <v>301220000000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Alibaba Group Holding Ltd ADR</t>
+          <t>Philip Morris International Inc</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>293040000000</v>
+        <v>292100000000</v>
       </c>
     </row>
     <row r="46">
@@ -1171,97 +1171,97 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>290060000000</v>
+        <v>291990000000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NVS</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Novartis AG ADR</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>285840000000</v>
+        <v>282910000000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>NVS</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>Novartis AG ADR</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>270440000000</v>
+        <v>281300000000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>263750000000</v>
+        <v>278130000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Astrazeneca plc</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>263090000000</v>
+        <v>268130000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>Wells Fargo &amp; Co</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>262790000000</v>
+        <v>265780000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Co</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>261420000000</v>
+        <v>255320000000</v>
       </c>
     </row>
     <row r="53">
@@ -1276,37 +1276,37 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>256450000000</v>
+        <v>253940000000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>255990000000</v>
+        <v>245700000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>Astrazeneca plc</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>251820000000</v>
+        <v>244990000000</v>
       </c>
     </row>
     <row r="56">
@@ -1321,37 +1321,37 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>238810000000</v>
+        <v>238720000000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Citigroup Inc</t>
+          <t>American Express Co</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>227140000000</v>
+        <v>232790000000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>American Express Co</t>
+          <t>Citigroup Inc</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>227070000000</v>
+        <v>229060000000</v>
       </c>
     </row>
     <row r="59">
@@ -1366,37 +1366,37 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>221300000000</v>
+        <v>222260000000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc</t>
+          <t>Sap SE ADR</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>213420000000</v>
+        <v>218890000000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Sap SE ADR</t>
+          <t>Thermo Fisher Scientific Inc</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>211930000000</v>
+        <v>213320000000</v>
       </c>
     </row>
     <row r="62">
@@ -1411,97 +1411,97 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>210710000000</v>
+        <v>213210000000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AMGEN Inc</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>207870000000</v>
+        <v>206240000000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Toyota Motor Corp ADR</t>
+          <t>AMGEN Inc</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>201090000000</v>
+        <v>204480000000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc</t>
+          <t>Toyota Motor Corp ADR</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>195460000000</v>
+        <v>198090000000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Verizon Communications Inc</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>195420000000</v>
+        <v>197750000000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>194340000000</v>
+        <v>193950000000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>McDonald's Corp</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>192290000000</v>
+        <v>190740000000</v>
       </c>
     </row>
     <row r="69">
@@ -1516,127 +1516,127 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>190480000000</v>
+        <v>190580000000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>T-Mobile US Inc</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>187800000000</v>
+        <v>189960000000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>T-Mobile US Inc</t>
+          <t>McDonald's Corp</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>185260000000</v>
+        <v>188450000000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Charles Schwab Corp</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>183030000000</v>
+        <v>185360000000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Boeing Co</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>182900000000</v>
+        <v>184540000000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NextEra Energy Inc</t>
+          <t>Charles Schwab Corp</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>181310000000</v>
+        <v>184120000000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>Blackrock Inc</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>179900000000</v>
+        <v>183190000000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Blackrock Inc</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>177300000000</v>
+        <v>181720000000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Boeing Co</t>
+          <t>NextEra Energy Inc</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>170830000000</v>
+        <v>180540000000</v>
       </c>
     </row>
     <row r="78">
@@ -1651,22 +1651,22 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>167040000000</v>
+        <v>170420000000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>Blackstone Inc</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>161660000000</v>
+        <v>167520000000</v>
       </c>
     </row>
     <row r="80">
@@ -1681,97 +1681,97 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>159980000000</v>
+        <v>163330000000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>159320000000</v>
+        <v>162830000000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Blackstone Inc</t>
+          <t>AT&amp;T Inc</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>158900000000</v>
+        <v>161650000000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Novo Nordisk ADR</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>158090000000</v>
+        <v>159150000000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>Novo Nordisk ADR</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>154990000000</v>
+        <v>158130000000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Shopify Inc</t>
+          <t>Salesforce Inc</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>152020000000</v>
+        <v>152290000000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Salesforce Inc</t>
+          <t>Shopify Inc</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>150710000000</v>
+        <v>151840000000</v>
       </c>
     </row>
     <row r="87">
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>149470000000</v>
+        <v>149330000000</v>
       </c>
     </row>
     <row r="88">
@@ -1801,52 +1801,52 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>143220000000</v>
+        <v>145770000000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Danaher Corp</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>137670000000</v>
+        <v>138840000000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Danaher Corp</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>137070000000</v>
+        <v>137230000000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Chubb Limited</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>135290000000</v>
+        <v>136450000000</v>
       </c>
     </row>
     <row r="92">
@@ -1861,142 +1861,142 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>134490000000</v>
+        <v>135310000000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Co</t>
+          <t>Chubb Limited</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>133410000000</v>
+        <v>134350000000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>Bristol-Myers Squibb Co</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>133000000000</v>
+        <v>133740000000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PDD Holdings Inc ADR</t>
+          <t>Intuitive Surgical Inc</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>126060000000</v>
+        <v>132620000000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Intuitive Surgical Inc</t>
+          <t>PDD Holdings Inc ADR</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>124820000000</v>
+        <v>128320000000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Progressive Corp</t>
+          <t>Corning Inc</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>123540000000</v>
+        <v>126310000000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>S&amp;P Global Inc</t>
+          <t>Progressive Corp</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>121440000000</v>
+        <v>122980000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Starbucks Corp</t>
+          <t>S&amp;P Global Inc</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>119980000000</v>
+        <v>122710000000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Corning Inc</t>
+          <t>Lowe's Cos. Inc</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>119090000000</v>
+        <v>118900000000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Lowe's Cos. Inc</t>
+          <t>Starbucks Corp</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>116520000000</v>
+        <v>117840000000</v>
       </c>
     </row>
     <row r="102">
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>114090000000</v>
+        <v>113980000000</v>
       </c>
     </row>
     <row r="103">
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>109300000000</v>
+        <v>110950000000</v>
       </c>
     </row>
     <row r="104">
@@ -2041,37 +2041,37 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>106510000000</v>
+        <v>107840000000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Spotify Technology SA</t>
+          <t>Snowflake Inc</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>102930000000</v>
+        <v>106590000000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Snowflake Inc</t>
+          <t>Equinix Inc</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>101650000000</v>
+        <v>101770000000</v>
       </c>
     </row>
     <row r="107">
@@ -2086,127 +2086,127 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>101530000000</v>
+        <v>101440000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Equinix Inc</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>100570000000</v>
+        <v>101270000000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>99540000000</v>
+        <v>100410000000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>Spotify Technology SA</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>99070000000</v>
+        <v>100130000000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>98170000000</v>
+        <v>99910000000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>95390000000</v>
+        <v>99620000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>MercadoLibre Inc</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>95210000000</v>
+        <v>97390000000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>MercadoLibre Inc</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>93000000000</v>
+        <v>96260000000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>MMC</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Airbnb Inc</t>
+          <t>Marsh</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>91320000000</v>
+        <v>92030000000</v>
       </c>
     </row>
     <row r="116">
@@ -2221,37 +2221,37 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>90910000000</v>
+        <v>91400000000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>MMC</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Marsh</t>
+          <t>United Parcel Service Inc</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>90520000000</v>
+        <v>90840000000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>United Parcel Service Inc</t>
+          <t>Airbnb Inc</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>88590000000</v>
+        <v>90790000000</v>
       </c>
     </row>
     <row r="119">
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>87160000000</v>
+        <v>88030000000</v>
       </c>
     </row>
     <row r="120">
@@ -2281,37 +2281,37 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>86460000000</v>
+        <v>87090000000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange Inc</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>85600000000</v>
+        <v>86900000000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Intercontinental Exchange Inc</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>85370000000</v>
+        <v>85220000000</v>
       </c>
     </row>
     <row r="123">
@@ -2326,7 +2326,7 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>81510000000</v>
+        <v>83010000000</v>
       </c>
     </row>
     <row r="124">
@@ -2341,37 +2341,37 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>79940000000</v>
+        <v>78150000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>General Motors Company</t>
+          <t>Northrop Grumman Corp</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>77970000000</v>
+        <v>77920000000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp</t>
+          <t>General Motors Company</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>77070000000</v>
+        <v>76930000000</v>
       </c>
     </row>
     <row r="127">
@@ -2386,7 +2386,7 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>74240000000</v>
+        <v>76500000000</v>
       </c>
     </row>
     <row r="128">
@@ -2401,7 +2401,7 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>73740000000</v>
+        <v>74530000000</v>
       </c>
     </row>
     <row r="129">
@@ -2416,7 +2416,7 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>73600000000</v>
+        <v>73180000000</v>
       </c>
     </row>
     <row r="130">
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>73060000000</v>
+        <v>71920000000</v>
       </c>
     </row>
     <row r="131">
@@ -2446,7 +2446,7 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>69290000000</v>
+        <v>70590000000</v>
       </c>
     </row>
     <row r="132">
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>69220000000</v>
+        <v>69750000000</v>
       </c>
     </row>
     <row r="133">
@@ -2476,7 +2476,7 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>65630000000</v>
+        <v>67830000000</v>
       </c>
     </row>
     <row r="134">
@@ -2491,7 +2491,7 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>61880000000</v>
+        <v>63260000000</v>
       </c>
     </row>
     <row r="135">
@@ -2506,7 +2506,7 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>60520000000</v>
+        <v>63020000000</v>
       </c>
     </row>
     <row r="136">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>58540000000</v>
+        <v>57540000000</v>
       </c>
     </row>
     <row r="137">
@@ -2536,7 +2536,7 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>56760000000</v>
+        <v>55170000000</v>
       </c>
     </row>
     <row r="138">
@@ -2551,97 +2551,97 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>53350000000</v>
+        <v>55030000000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Vistra Corp</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>49970000000</v>
+        <v>53500000000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences Corp</t>
+          <t>Vistra Corp</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>49560000000</v>
+        <v>52580000000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Autodesk Inc</t>
+          <t>Edwards Lifesciences Corp</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>49420000000</v>
+        <v>51140000000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>PayPal Holdings Inc</t>
+          <t>Autodesk Inc</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>48940000000</v>
+        <v>49520000000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Block Inc</t>
+          <t>PayPal Holdings Inc</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>48350000000</v>
+        <v>49510000000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Block Inc</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>47920000000</v>
+        <v>48860000000</v>
       </c>
     </row>
     <row r="145">
@@ -2656,112 +2656,112 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>47740000000</v>
+        <v>48050000000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MSCI Inc</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>41600000000</v>
+        <v>46790000000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>JD</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>JD.com Inc ADR</t>
+          <t>Rocket Lab Corp</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>40050000000</v>
+        <v>42130000000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Workday Inc</t>
+          <t>MSCI Inc</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>39600000000</v>
+        <v>41760000000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Workday Inc</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>39160000000</v>
+        <v>40770000000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Rocket Lab Corp</t>
+          <t>JD.com Inc ADR</t>
         </is>
       </c>
       <c r="L150" t="n">
-        <v>38850000000</v>
+        <v>40060000000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Coinbase Global Inc</t>
+          <t>Carnival Corp Ltd</t>
         </is>
       </c>
       <c r="L151" t="n">
-        <v>38530000000</v>
+        <v>39360000000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Carnival Corp Ltd</t>
+          <t>Coinbase Global Inc</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>38090000000</v>
+        <v>38600000000</v>
       </c>
     </row>
     <row r="153">
@@ -2776,7 +2776,7 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>32690000000</v>
+        <v>33240000000</v>
       </c>
     </row>
     <row r="154">
@@ -2791,37 +2791,37 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>32400000000</v>
+        <v>32320000000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Illumina Inc</t>
+          <t>Estee Lauder Cos. Inc</t>
         </is>
       </c>
       <c r="L155" t="n">
-        <v>31030000000</v>
+        <v>30640000000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Estee Lauder Cos. Inc</t>
+          <t>Illumina Inc</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>30350000000</v>
+        <v>29980000000</v>
       </c>
     </row>
     <row r="157">
@@ -2836,142 +2836,142 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>29950000000</v>
+        <v>29840000000</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>RDDT</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Fiserv Inc</t>
+          <t>Reddit Inc</t>
         </is>
       </c>
       <c r="L158" t="n">
-        <v>28760000000</v>
+        <v>29780000000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ZM</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Zoom Communications Inc</t>
+          <t>Fiserv Inc</t>
         </is>
       </c>
       <c r="L159" t="n">
-        <v>28170000000</v>
+        <v>28980000000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>RDDT</t>
+          <t>ZM</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Reddit Inc</t>
+          <t>Zoom Communications Inc</t>
         </is>
       </c>
       <c r="L160" t="n">
-        <v>27080000000</v>
+        <v>28810000000</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>AFRM</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Zscaler Inc</t>
+          <t>Affirm Holdings Inc</t>
         </is>
       </c>
       <c r="L161" t="n">
-        <v>24450000000</v>
+        <v>25330000000</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>AFRM</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Affirm Holdings Inc</t>
+          <t>First Solar Inc</t>
         </is>
       </c>
       <c r="L162" t="n">
-        <v>23950000000</v>
+        <v>25010000000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>First Solar Inc</t>
+          <t>Zscaler Inc</t>
         </is>
       </c>
       <c r="L163" t="n">
-        <v>22680000000</v>
+        <v>24980000000</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>SoFi Technologies Inc</t>
         </is>
       </c>
       <c r="L164" t="n">
-        <v>21750000000</v>
+        <v>23130000000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ROKU</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Roku Inc</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="L165" t="n">
-        <v>21510000000</v>
+        <v>21880000000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>ROKU</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>SoFi Technologies Inc</t>
+          <t>Roku Inc</t>
         </is>
       </c>
       <c r="L166" t="n">
-        <v>20920000000</v>
+        <v>21630000000</v>
       </c>
     </row>
     <row r="167">
@@ -2986,7 +2986,7 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>20880000000</v>
+        <v>20890000000</v>
       </c>
     </row>
     <row r="168">
@@ -3001,7 +3001,7 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>19400000000</v>
+        <v>19280000000</v>
       </c>
     </row>
     <row r="169">
@@ -3016,22 +3016,22 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>18370000000</v>
+        <v>18530000000</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>CRCL</t>
+          <t>GRAB</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Circle Internet Group Inc</t>
+          <t>Grab Holdings Limited</t>
         </is>
       </c>
       <c r="L170" t="n">
-        <v>15560000000</v>
+        <v>15040000000</v>
       </c>
     </row>
     <row r="171">
@@ -3046,22 +3046,22 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>14350000000</v>
+        <v>15040000000</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>GRAB</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Grab Holdings Limited</t>
+          <t>Circle Internet Group Inc</t>
         </is>
       </c>
       <c r="L172" t="n">
-        <v>14350000000</v>
+        <v>15000000000</v>
       </c>
     </row>
     <row r="173">
@@ -3076,52 +3076,52 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>13600000000</v>
+        <v>14500000000</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>TXRH</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Texas Roadhouse Inc</t>
+          <t>IREN Ltd</t>
         </is>
       </c>
       <c r="L174" t="n">
-        <v>13500000000</v>
+        <v>14190000000</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>PINS</t>
+          <t>TXRH</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Pinterest Inc</t>
+          <t>Texas Roadhouse Inc</t>
         </is>
       </c>
       <c r="L175" t="n">
-        <v>13450000000</v>
+        <v>13850000000</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>PINS</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>IREN Ltd</t>
+          <t>Pinterest Inc</t>
         </is>
       </c>
       <c r="L176" t="n">
-        <v>13130000000</v>
+        <v>13530000000</v>
       </c>
     </row>
     <row r="177">
@@ -3136,7 +3136,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>10850000000</v>
+        <v>10710000000</v>
       </c>
     </row>
     <row r="178">
@@ -3151,37 +3151,37 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>9410000000</v>
+        <v>9270000000</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>PRMB</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Primo Brands Corp</t>
+          <t>Applied Digital Corp</t>
         </is>
       </c>
       <c r="L179" t="n">
-        <v>8240000000</v>
+        <v>8600000000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>PRMB</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Applied Digital Corp</t>
+          <t>Primo Brands Corp</t>
         </is>
       </c>
       <c r="L180" t="n">
-        <v>7980000000</v>
+        <v>8100000000</v>
       </c>
     </row>
     <row r="181">
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>7820000000</v>
+        <v>8060000000</v>
       </c>
     </row>
     <row r="182">
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>7560000000</v>
+        <v>8060000000</v>
       </c>
     </row>
     <row r="183">
@@ -3226,7 +3226,7 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>7470000000</v>
+        <v>7220000000</v>
       </c>
     </row>
     <row r="184">
@@ -3241,52 +3241,52 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>6760000000</v>
+        <v>7170000000</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>MBLY</t>
+          <t>HIMS</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Mobileye Global Inc</t>
+          <t>Hims &amp; Hers Health Inc</t>
         </is>
       </c>
       <c r="L185" t="n">
-        <v>6750000000</v>
+        <v>7130000000</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>MBLY</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>SentinelOne Inc</t>
+          <t>Mobileye Global Inc</t>
         </is>
       </c>
       <c r="L186" t="n">
-        <v>6530000000</v>
+        <v>6870000000</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>HIMS</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Hims &amp; Hers Health Inc</t>
+          <t>SentinelOne Inc</t>
         </is>
       </c>
       <c r="L187" t="n">
-        <v>6430000000</v>
+        <v>6870000000</v>
       </c>
     </row>
     <row r="188">
@@ -3301,7 +3301,7 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>4970000000</v>
+        <v>5330000000</v>
       </c>
     </row>
     <row r="189">
@@ -3316,37 +3316,37 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>4630000000</v>
+        <v>4780000000</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>MARA</t>
+          <t>ONDS</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>MARA Holdings Inc</t>
+          <t>Ondas Inc</t>
         </is>
       </c>
       <c r="L190" t="n">
-        <v>4320000000</v>
+        <v>4770000000</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ONDS</t>
+          <t>MARA</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Ondas Inc</t>
+          <t>MARA Holdings Inc</t>
         </is>
       </c>
       <c r="L191" t="n">
-        <v>4270000000</v>
+        <v>4480000000</v>
       </c>
     </row>
     <row r="192">
@@ -3361,37 +3361,37 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>3710000000</v>
+        <v>4080000000</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>FSLY</t>
+          <t>LEU</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Fastly Inc</t>
+          <t>Centrus Energy Corp</t>
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3550000000</v>
+        <v>3630000000</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>LEU</t>
+          <t>FSLY</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Centrus Energy Corp</t>
+          <t>Fastly Inc</t>
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3480000000</v>
+        <v>3600000000</v>
       </c>
     </row>
     <row r="195">
@@ -3406,67 +3406,67 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>3080000000</v>
+        <v>3290000000</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>PENN</t>
+          <t>TMDX</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>PENN Entertainment Inc</t>
+          <t>Transmedics Group Inc</t>
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2750000000</v>
+        <v>2820000000</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>TMDX</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Transmedics Group Inc</t>
+          <t>Upstart Holdings Inc</t>
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2640000000</v>
+        <v>2820000000</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>FLNC</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Upstart Holdings Inc</t>
+          <t>Fluence Energy Inc</t>
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2630000000</v>
+        <v>2680000000</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>FLNC</t>
+          <t>PENN</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Fluence Energy Inc</t>
+          <t>PENN Entertainment Inc</t>
         </is>
       </c>
       <c r="L199" t="n">
-        <v>2570000000</v>
+        <v>2670000000</v>
       </c>
     </row>
     <row r="200">
@@ -3481,7 +3481,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1830000000</v>
+        <v>1970000000</v>
       </c>
     </row>
     <row r="201">
@@ -3496,7 +3496,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1430000000</v>
+        <v>1510000000</v>
       </c>
     </row>
     <row r="202">
@@ -3511,7 +3511,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1220000000</v>
+        <v>1210000000</v>
       </c>
     </row>
     <row r="203">
@@ -3526,7 +3526,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>1010000000</v>
+        <v>1100000000</v>
       </c>
     </row>
     <row r="204">
@@ -3541,7 +3541,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>854340000</v>
+        <v>944020000</v>
       </c>
     </row>
     <row r="205">
@@ -3556,7 +3556,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>503610000</v>
+        <v>521240000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4456440000000</v>
+        <v>4515150000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5000690000000</v>
+        <v>5128950000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4551670000000</v>
+        <v>4597560000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3621070000000</v>
+        <v>3659380000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3055230000000</v>
+        <v>2992340000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2106280000000</v>
+        <v>2163640000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1866070000000</v>
+        <v>1989430000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1503420000000</v>
+        <v>1497780000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1272070000000</v>
+        <v>1292880000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,52 +696,52 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1056030000000</v>
+        <v>1050680000000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BRK-B</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Inc</t>
+          <t>Micron Technology Inc</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>995710000000</v>
+        <v>1008180000000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>BRK-B</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co</t>
+          <t>Berkshire Hathaway Inc</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>944900000000</v>
+        <v>1003240000000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Micron Technology Inc</t>
+          <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>936830000000</v>
+        <v>957980000000</v>
       </c>
     </row>
     <row r="18">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>881040000000</v>
+        <v>887720000000</v>
       </c>
     </row>
     <row r="19">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>790250000000</v>
+        <v>845600000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,37 +786,37 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>672910000000</v>
+        <v>690040000000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ExxonMobil Holdings Corp</t>
+          <t>ASML Holding NV</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>642640000000</v>
+        <v>659800000000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ASML Holding NV</t>
+          <t>ExxonMobil Holdings Corp</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>633060000000</v>
+        <v>638080000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>613100000000</v>
+        <v>614360000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>504760000000</v>
+        <v>504870000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>456650000000</v>
+        <v>479830000000</v>
       </c>
     </row>
     <row r="26">
@@ -876,52 +876,52 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>443390000000</v>
+        <v>439840000000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Abbvie Inc</t>
+          <t>Applied Materials Inc</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>433040000000</v>
+        <v>433990000000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Costco Wholesale Corp</t>
+          <t>Abbvie Inc</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>423110000000</v>
+        <v>430740000000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Applied Materials Inc</t>
+          <t>Costco Wholesale Corp</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>411440000000</v>
+        <v>420350000000</v>
       </c>
     </row>
     <row r="30">
@@ -936,242 +936,242 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>408590000000</v>
+        <v>419800000000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Chevron Corp</t>
+          <t>Caterpillar Inc</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>384740000000</v>
+        <v>403770000000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Lam Research Corp</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>382790000000</v>
+        <v>397360000000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Caterpillar Inc</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>382340000000</v>
+        <v>391450000000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Unitedhealth Group Inc</t>
+          <t>Palantir Technologies Inc</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>377210000000</v>
+        <v>389950000000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Coca-Cola Co</t>
+          <t>Chevron Corp</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>373720000000</v>
+        <v>379200000000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Lam Research Corp</t>
+          <t>Coca-Cola Co</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>368430000000</v>
+        <v>372430000000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Home Depot Inc</t>
+          <t>Unitedhealth Group Inc</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>339040000000</v>
+        <v>370110000000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble Co</t>
+          <t>Home Depot Inc</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>337580000000</v>
+        <v>347240000000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Procter &amp; Gamble Co</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>333170000000</v>
+        <v>344660000000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Merck &amp; Co Inc</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>315570000000</v>
+        <v>342330000000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Netflix Inc</t>
+          <t>Merck &amp; Co Inc</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>305340000000</v>
+        <v>316140000000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BABA</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Alibaba Group Holding Ltd ADR</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>305150000000</v>
+        <v>310640000000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>BABA</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Alibaba Group Holding Ltd ADR</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>302990000000</v>
+        <v>309200000000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc</t>
+          <t>Netflix Inc</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>301220000000</v>
+        <v>306340000000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Philip Morris International Inc</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>292100000000</v>
+        <v>302920000000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>291990000000</v>
+        <v>299640000000</v>
       </c>
     </row>
     <row r="47">
@@ -1186,247 +1186,247 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>282910000000</v>
+        <v>298570000000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>NVS</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Novartis AG ADR</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>281300000000</v>
+        <v>293720000000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>Philip Morris International Inc</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>278130000000</v>
+        <v>291320000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>NVS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>Novartis AG ADR</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>268130000000</v>
+        <v>280570000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Co</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>265780000000</v>
+        <v>271270000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>Wells Fargo &amp; Co</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>255320000000</v>
+        <v>267290000000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Shell Plc ADR</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>253940000000</v>
+        <v>259020000000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>KLA Corp</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>245700000000</v>
+        <v>255310000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Astrazeneca plc</t>
+          <t>Shell Plc ADR</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>244990000000</v>
+        <v>250480000000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>KLA Corp</t>
+          <t>Astrazeneca plc</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>238720000000</v>
+        <v>241350000000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>American Express Co</t>
+          <t>Citigroup Inc</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>232790000000</v>
+        <v>234720000000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Citigroup Inc</t>
+          <t>American Express Co</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>229060000000</v>
+        <v>234140000000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Linde Plc</t>
+          <t>Sap SE ADR</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>222260000000</v>
+        <v>225630000000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sap SE ADR</t>
+          <t>Linde Plc</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>218890000000</v>
+        <v>223410000000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc</t>
+          <t>International Business Machines Corp</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>213320000000</v>
+        <v>221540000000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>International Business Machines Corp</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>213210000000</v>
+        <v>215080000000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>206240000000</v>
+        <v>211420000000</v>
       </c>
     </row>
     <row r="64">
@@ -1441,127 +1441,127 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>204480000000</v>
+        <v>210500000000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Toyota Motor Corp ADR</t>
+          <t>Thermo Fisher Scientific Inc</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>198090000000</v>
+        <v>208810000000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc</t>
+          <t>Toyota Motor Corp ADR</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>197750000000</v>
+        <v>201290000000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Verizon Communications Inc</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>193950000000</v>
+        <v>194780000000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>McDonald's Corp</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>190740000000</v>
+        <v>190660000000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PepsiCo Inc</t>
+          <t>T-Mobile US Inc</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>190580000000</v>
+        <v>190090000000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>T-Mobile US Inc</t>
+          <t>PepsiCo Inc</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>189960000000</v>
+        <v>189860000000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>McDonald's Corp</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>188450000000</v>
+        <v>189480000000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>185360000000</v>
+        <v>189080000000</v>
       </c>
     </row>
     <row r="73">
@@ -1576,7 +1576,7 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>184540000000</v>
+        <v>187440000000</v>
       </c>
     </row>
     <row r="74">
@@ -1591,7 +1591,7 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>184120000000</v>
+        <v>184960000000</v>
       </c>
     </row>
     <row r="75">
@@ -1606,22 +1606,22 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>183190000000</v>
+        <v>183920000000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>181720000000</v>
+        <v>182490000000</v>
       </c>
     </row>
     <row r="77">
@@ -1636,22 +1636,22 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>180540000000</v>
+        <v>181900000000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Walt Disney Co</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>170420000000</v>
+        <v>170800000000</v>
       </c>
     </row>
     <row r="79">
@@ -1666,22 +1666,22 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>167520000000</v>
+        <v>170650000000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Deere &amp; Co</t>
+          <t>Walt Disney Co</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>163330000000</v>
+        <v>170490000000</v>
       </c>
     </row>
     <row r="81">
@@ -1696,52 +1696,52 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>162830000000</v>
+        <v>167920000000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc</t>
+          <t>Deere &amp; Co</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>161650000000</v>
+        <v>166650000000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>AT&amp;T Inc</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>159150000000</v>
+        <v>160210000000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Novo Nordisk ADR</t>
+          <t>Shopify Inc</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>158130000000</v>
+        <v>160000000000</v>
       </c>
     </row>
     <row r="85">
@@ -1756,37 +1756,37 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>152290000000</v>
+        <v>156420000000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Shopify Inc</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>151840000000</v>
+        <v>150540000000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>Novo Nordisk ADR</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>149330000000</v>
+        <v>148690000000</v>
       </c>
     </row>
     <row r="88">
@@ -1801,52 +1801,52 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>145770000000</v>
+        <v>146540000000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Danaher Corp</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>138840000000</v>
+        <v>140990000000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Corning Inc</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>137230000000</v>
+        <v>137730000000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>Danaher Corp</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>136450000000</v>
+        <v>136930000000</v>
       </c>
     </row>
     <row r="92">
@@ -1861,82 +1861,82 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>135310000000</v>
+        <v>136010000000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Chubb Limited</t>
+          <t>Bristol-Myers Squibb Co</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>134350000000</v>
+        <v>134590000000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Co</t>
+          <t>Chubb Limited</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>133740000000</v>
+        <v>134370000000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Intuitive Surgical Inc</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>132620000000</v>
+        <v>132380000000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PDD Holdings Inc ADR</t>
+          <t>Intuitive Surgical Inc</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>128320000000</v>
+        <v>130100000000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Corning Inc</t>
+          <t>PDD Holdings Inc ADR</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>126310000000</v>
+        <v>129570000000</v>
       </c>
     </row>
     <row r="98">
@@ -1951,37 +1951,37 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>122980000000</v>
+        <v>123150000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>S&amp;P Global Inc</t>
+          <t>Lowe's Cos. Inc</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>122710000000</v>
+        <v>122280000000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Lowe's Cos. Inc</t>
+          <t>S&amp;P Global Inc</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>118900000000</v>
+        <v>121610000000</v>
       </c>
     </row>
     <row r="101">
@@ -1996,7 +1996,7 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>117840000000</v>
+        <v>119670000000</v>
       </c>
     </row>
     <row r="102">
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>113980000000</v>
+        <v>113660000000</v>
       </c>
     </row>
     <row r="103">
@@ -2026,52 +2026,52 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>110950000000</v>
+        <v>110340000000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc</t>
+          <t>Snowflake Inc</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>107840000000</v>
+        <v>109790000000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Snowflake Inc</t>
+          <t>Automatic Data Processing Inc</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>106590000000</v>
+        <v>108180000000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Equinix Inc</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>101770000000</v>
+        <v>107010000000</v>
       </c>
     </row>
     <row r="107">
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>101440000000</v>
+        <v>104290000000</v>
       </c>
     </row>
     <row r="108">
@@ -2101,37 +2101,37 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>101270000000</v>
+        <v>103920000000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>Equinix Inc</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>100410000000</v>
+        <v>103760000000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Spotify Technology SA</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>100130000000</v>
+        <v>102570000000</v>
       </c>
     </row>
     <row r="111">
@@ -2146,7 +2146,7 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>99910000000</v>
+        <v>102350000000</v>
       </c>
     </row>
     <row r="112">
@@ -2161,22 +2161,22 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>99620000000</v>
+        <v>100070000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>Spotify Technology SA</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>97390000000</v>
+        <v>98450000000</v>
       </c>
     </row>
     <row r="114">
@@ -2191,52 +2191,52 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>96260000000</v>
+        <v>95740000000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MMC</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Marsh</t>
+          <t>3M Co</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>92030000000</v>
+        <v>93580000000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>3M Co</t>
+          <t>United Parcel Service Inc</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>91400000000</v>
+        <v>92740000000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>MMC</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>United Parcel Service Inc</t>
+          <t>Marsh</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>90840000000</v>
+        <v>91360000000</v>
       </c>
     </row>
     <row r="118">
@@ -2251,52 +2251,52 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>90790000000</v>
+        <v>90360000000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>HCA Healthcare Inc</t>
+          <t>Intuit Inc</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>88030000000</v>
+        <v>88520000000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Intuit Inc</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>87090000000</v>
+        <v>87360000000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>HCA Healthcare Inc</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>86900000000</v>
+        <v>86760000000</v>
       </c>
     </row>
     <row r="122">
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>85220000000</v>
+        <v>83760000000</v>
       </c>
     </row>
     <row r="123">
@@ -2326,22 +2326,22 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>83010000000</v>
+        <v>81980000000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals Inc</t>
+          <t>Apollo Global Management Inc</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>78150000000</v>
+        <v>78740000000</v>
       </c>
     </row>
     <row r="125">
@@ -2356,82 +2356,82 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>77920000000</v>
+        <v>78350000000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>General Motors Company</t>
+          <t>Regeneron Pharmaceuticals Inc</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>76930000000</v>
+        <v>78300000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Apollo Global Management Inc</t>
+          <t>General Motors Company</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>76500000000</v>
+        <v>77490000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Cigna Group</t>
+          <t>SLB Ltd</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>74530000000</v>
+        <v>75410000000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SLB Ltd</t>
+          <t>Colgate-Palmolive Co</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>73180000000</v>
+        <v>73760000000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive Co</t>
+          <t>Cigna Group</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>71920000000</v>
+        <v>72420000000</v>
       </c>
     </row>
     <row r="131">
@@ -2446,7 +2446,7 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>70590000000</v>
+        <v>70860000000</v>
       </c>
     </row>
     <row r="132">
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>69750000000</v>
+        <v>69220000000</v>
       </c>
     </row>
     <row r="133">
@@ -2476,142 +2476,142 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>67830000000</v>
+        <v>67270000000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Nike Inc</t>
+          <t>Sea Ltd ADR</t>
         </is>
       </c>
       <c r="L134" t="n">
-        <v>63260000000</v>
+        <v>63180000000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Sea Ltd ADR</t>
+          <t>Astera Labs Inc</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>63020000000</v>
+        <v>61990000000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Ford Motor Co</t>
+          <t>Nike Inc</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>57540000000</v>
+        <v>61610000000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Occidental Petroleum Corp</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L137" t="n">
-        <v>55170000000</v>
+        <v>56810000000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Astera Labs Inc</t>
+          <t>Ford Motor Co</t>
         </is>
       </c>
       <c r="L138" t="n">
-        <v>55030000000</v>
+        <v>56790000000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Occidental Petroleum Corp</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>53500000000</v>
+        <v>54790000000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Vistra Corp</t>
+          <t>Edwards Lifesciences Corp</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>52580000000</v>
+        <v>51590000000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences Corp</t>
+          <t>Block Inc</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>51140000000</v>
+        <v>50380000000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Autodesk Inc</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>49520000000</v>
+        <v>50140000000</v>
       </c>
     </row>
     <row r="143">
@@ -2626,127 +2626,127 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>49510000000</v>
+        <v>50080000000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Block Inc</t>
+          <t>Autodesk Inc</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>48860000000</v>
+        <v>50050000000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>Vistra Corp</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>48050000000</v>
+        <v>48290000000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Rocket Lab Corp</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>46790000000</v>
+        <v>44550000000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Rocket Lab Corp</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>42130000000</v>
+        <v>42800000000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>MSCI Inc</t>
+          <t>Workday Inc</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>41760000000</v>
+        <v>42310000000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Workday Inc</t>
+          <t>MSCI Inc</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>40770000000</v>
+        <v>41550000000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>JD</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>JD.com Inc ADR</t>
+          <t>Carnival Corp Ltd</t>
         </is>
       </c>
       <c r="L150" t="n">
-        <v>40060000000</v>
+        <v>40530000000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Carnival Corp Ltd</t>
+          <t>JD.com Inc ADR</t>
         </is>
       </c>
       <c r="L151" t="n">
-        <v>39360000000</v>
+        <v>40000000000</v>
       </c>
     </row>
     <row r="152">
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>38600000000</v>
+        <v>39710000000</v>
       </c>
     </row>
     <row r="153">
@@ -2776,7 +2776,7 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>33240000000</v>
+        <v>34220000000</v>
       </c>
     </row>
     <row r="154">
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>32320000000</v>
+        <v>31880000000</v>
       </c>
     </row>
     <row r="155">
@@ -2806,52 +2806,52 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>30640000000</v>
+        <v>31470000000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>RDDT</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Illumina Inc</t>
+          <t>Reddit Inc</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>29980000000</v>
+        <v>30810000000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Twilio Inc</t>
+          <t>Illumina Inc</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>29840000000</v>
+        <v>30650000000</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>RDDT</t>
+          <t>ZM</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Reddit Inc</t>
+          <t>Zoom Communications Inc</t>
         </is>
       </c>
       <c r="L158" t="n">
-        <v>29780000000</v>
+        <v>29940000000</v>
       </c>
     </row>
     <row r="159">
@@ -2866,37 +2866,37 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>28980000000</v>
+        <v>29740000000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ZM</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Zoom Communications Inc</t>
+          <t>Twilio Inc</t>
         </is>
       </c>
       <c r="L160" t="n">
-        <v>28810000000</v>
+        <v>29450000000</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>AFRM</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Affirm Holdings Inc</t>
+          <t>Zscaler Inc</t>
         </is>
       </c>
       <c r="L161" t="n">
-        <v>25330000000</v>
+        <v>26390000000</v>
       </c>
     </row>
     <row r="162">
@@ -2911,22 +2911,22 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>25010000000</v>
+        <v>26180000000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>AFRM</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Zscaler Inc</t>
+          <t>Affirm Holdings Inc</t>
         </is>
       </c>
       <c r="L163" t="n">
-        <v>24980000000</v>
+        <v>26160000000</v>
       </c>
     </row>
     <row r="164">
@@ -2941,7 +2941,7 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>23130000000</v>
+        <v>23990000000</v>
       </c>
     </row>
     <row r="165">
@@ -2956,7 +2956,7 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>21880000000</v>
+        <v>22750000000</v>
       </c>
     </row>
     <row r="166">
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>21630000000</v>
+        <v>21860000000</v>
       </c>
     </row>
     <row r="167">
@@ -2986,97 +2986,97 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>20890000000</v>
+        <v>20990000000</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Charter Communications Inc</t>
+          <t>Super Micro Computer Inc</t>
         </is>
       </c>
       <c r="L168" t="n">
-        <v>19280000000</v>
+        <v>20500000000</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Super Micro Computer Inc</t>
+          <t>Charter Communications Inc</t>
         </is>
       </c>
       <c r="L169" t="n">
-        <v>18530000000</v>
+        <v>20480000000</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>GRAB</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Grab Holdings Limited</t>
+          <t>IonQ Inc</t>
         </is>
       </c>
       <c r="L170" t="n">
-        <v>15040000000</v>
+        <v>16580000000</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>GRAB</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Grab Holdings Limited</t>
+          <t>Circle Internet Group Inc</t>
         </is>
       </c>
       <c r="L171" t="n">
-        <v>15040000000</v>
+        <v>15720000000</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>CRCL</t>
+          <t>GRAB</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Circle Internet Group Inc</t>
+          <t>Grab Holdings Limited</t>
         </is>
       </c>
       <c r="L172" t="n">
-        <v>15000000000</v>
+        <v>15250000000</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>GRAB</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>IonQ Inc</t>
+          <t>Grab Holdings Limited</t>
         </is>
       </c>
       <c r="L173" t="n">
-        <v>14500000000</v>
+        <v>15250000000</v>
       </c>
     </row>
     <row r="174">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>14190000000</v>
+        <v>14580000000</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>TXRH</t>
+          <t>PINS</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Texas Roadhouse Inc</t>
+          <t>Pinterest Inc</t>
         </is>
       </c>
       <c r="L175" t="n">
-        <v>13850000000</v>
+        <v>14330000000</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>PINS</t>
+          <t>TXRH</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Pinterest Inc</t>
+          <t>Texas Roadhouse Inc</t>
         </is>
       </c>
       <c r="L176" t="n">
-        <v>13530000000</v>
+        <v>13690000000</v>
       </c>
     </row>
     <row r="177">
@@ -3136,7 +3136,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>10710000000</v>
+        <v>10560000000</v>
       </c>
     </row>
     <row r="178">
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>9270000000</v>
+        <v>9160000000</v>
       </c>
     </row>
     <row r="179">
@@ -3166,52 +3166,52 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>8600000000</v>
+        <v>9110000000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>PRMB</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Primo Brands Corp</t>
+          <t>AeroVironment Inc</t>
         </is>
       </c>
       <c r="L180" t="n">
-        <v>8100000000</v>
+        <v>8550000000</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>PRMB</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Zillow Group Inc</t>
+          <t>Primo Brands Corp</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>8060000000</v>
+        <v>8450000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>AeroVironment Inc</t>
+          <t>Zillow Group Inc</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>8060000000</v>
+        <v>8330000000</v>
       </c>
     </row>
     <row r="183">
@@ -3226,7 +3226,7 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>7220000000</v>
+        <v>7550000000</v>
       </c>
     </row>
     <row r="184">
@@ -3241,7 +3241,7 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>7170000000</v>
+        <v>7540000000</v>
       </c>
     </row>
     <row r="185">
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>7130000000</v>
+        <v>7440000000</v>
       </c>
     </row>
     <row r="186">
@@ -3271,7 +3271,7 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>6870000000</v>
+        <v>7350000000</v>
       </c>
     </row>
     <row r="187">
@@ -3286,7 +3286,7 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>6870000000</v>
+        <v>7190000000</v>
       </c>
     </row>
     <row r="188">
@@ -3301,7 +3301,7 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>5330000000</v>
+        <v>5800000000</v>
       </c>
     </row>
     <row r="189">
@@ -3316,7 +3316,7 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>4780000000</v>
+        <v>5120000000</v>
       </c>
     </row>
     <row r="190">
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>4770000000</v>
+        <v>5050000000</v>
       </c>
     </row>
     <row r="191">
@@ -3361,37 +3361,37 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>4080000000</v>
+        <v>4160000000</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>LEU</t>
+          <t>FSLY</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Centrus Energy Corp</t>
+          <t>Fastly Inc</t>
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3630000000</v>
+        <v>3900000000</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>FSLY</t>
+          <t>LEU</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Fastly Inc</t>
+          <t>Centrus Energy Corp</t>
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3600000000</v>
+        <v>3720000000</v>
       </c>
     </row>
     <row r="195">
@@ -3406,52 +3406,52 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>3290000000</v>
+        <v>3470000000</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>TMDX</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Transmedics Group Inc</t>
+          <t>Upstart Holdings Inc</t>
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2820000000</v>
+        <v>2900000000</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>FLNC</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Upstart Holdings Inc</t>
+          <t>Fluence Energy Inc</t>
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2820000000</v>
+        <v>2890000000</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>FLNC</t>
+          <t>TMDX</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Fluence Energy Inc</t>
+          <t>Transmedics Group Inc</t>
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2680000000</v>
+        <v>2790000000</v>
       </c>
     </row>
     <row r="199">
@@ -3466,7 +3466,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>2670000000</v>
+        <v>2680000000</v>
       </c>
     </row>
     <row r="200">
@@ -3481,7 +3481,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1970000000</v>
+        <v>2080000000</v>
       </c>
     </row>
     <row r="201">
@@ -3496,37 +3496,37 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1510000000</v>
+        <v>1560000000</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>TDOC</t>
+          <t>UMAC</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Teladoc Health Inc</t>
+          <t>Unusual Machines Inc</t>
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1210000000</v>
+        <v>1270000000</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>UMAC</t>
+          <t>TDOC</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Unusual Machines Inc</t>
+          <t>Teladoc Health Inc</t>
         </is>
       </c>
       <c r="L203" t="n">
-        <v>1100000000</v>
+        <v>1220000000</v>
       </c>
     </row>
     <row r="204">
@@ -3541,7 +3541,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>944020000</v>
+        <v>975690000</v>
       </c>
     </row>
     <row r="205">
@@ -3556,7 +3556,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>521240000</v>
+        <v>540130000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4515150000000</v>
+        <v>4538790000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5128950000000</v>
+        <v>5305120000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4597560000000</v>
+        <v>4419180000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3659380000000</v>
+        <v>3619660000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2992340000000</v>
+        <v>2940890000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2163640000000</v>
+        <v>2147200000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1989430000000</v>
+        <v>1990000000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1497780000000</v>
+        <v>1499900000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1292880000000</v>
+        <v>1269980000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1050680000000</v>
+        <v>1101710000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1008180000000</v>
+        <v>1008760000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1003240000000</v>
+        <v>1006380000000</v>
       </c>
     </row>
     <row r="17">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>957980000000</v>
+        <v>962590000000</v>
       </c>
     </row>
     <row r="18">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>887720000000</v>
+        <v>894010000000</v>
       </c>
     </row>
     <row r="19">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>845600000000</v>
+        <v>786030000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>690040000000</v>
+        <v>688080000000</v>
       </c>
     </row>
     <row r="21">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>659800000000</v>
+        <v>646820000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>638080000000</v>
+        <v>623490000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>614360000000</v>
+        <v>620770000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>504870000000</v>
+        <v>504320000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>479830000000</v>
+        <v>478880000000</v>
       </c>
     </row>
     <row r="26">
@@ -876,37 +876,37 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>439840000000</v>
+        <v>442290000000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Applied Materials Inc</t>
+          <t>Abbvie Inc</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>433990000000</v>
+        <v>435060000000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Abbvie Inc</t>
+          <t>Applied Materials Inc</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>430740000000</v>
+        <v>424160000000</v>
       </c>
     </row>
     <row r="29">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>420350000000</v>
+        <v>417750000000</v>
       </c>
     </row>
     <row r="30">
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>419800000000</v>
+        <v>415910000000</v>
       </c>
     </row>
     <row r="31">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>403770000000</v>
+        <v>401250000000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Lam Research Corp</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>397360000000</v>
+        <v>395540000000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Lam Research Corp</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>391450000000</v>
+        <v>384450000000</v>
       </c>
     </row>
     <row r="34">
@@ -996,22 +996,22 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>389950000000</v>
+        <v>379990000000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Chevron Corp</t>
+          <t>Unitedhealth Group Inc</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>379200000000</v>
+        <v>374840000000</v>
       </c>
     </row>
     <row r="36">
@@ -1026,22 +1026,22 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>372430000000</v>
+        <v>373590000000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Unitedhealth Group Inc</t>
+          <t>Chevron Corp</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>370110000000</v>
+        <v>371250000000</v>
       </c>
     </row>
     <row r="38">
@@ -1056,37 +1056,37 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>347240000000</v>
+        <v>352120000000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble Co</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>344660000000</v>
+        <v>344270000000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Procter &amp; Gamble Co</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>342330000000</v>
+        <v>341840000000</v>
       </c>
     </row>
     <row r="41">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>316140000000</v>
+        <v>316950000000</v>
       </c>
     </row>
     <row r="42">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>310640000000</v>
+        <v>312820000000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Alibaba Group Holding Ltd ADR</t>
+          <t>Netflix Inc</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>309200000000</v>
+        <v>308960000000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Netflix Inc</t>
+          <t>Alibaba Group Holding Ltd ADR</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>306340000000</v>
+        <v>308090000000</v>
       </c>
     </row>
     <row r="45">
@@ -1156,22 +1156,22 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>302920000000</v>
+        <v>299960000000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>299640000000</v>
+        <v>299620000000</v>
       </c>
     </row>
     <row r="47">
@@ -1186,37 +1186,37 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>298570000000</v>
+        <v>295570000000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Philip Morris International Inc</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>293720000000</v>
+        <v>294470000000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Philip Morris International Inc</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>291320000000</v>
+        <v>293250000000</v>
       </c>
     </row>
     <row r="50">
@@ -1231,7 +1231,7 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>280570000000</v>
+        <v>282710000000</v>
       </c>
     </row>
     <row r="51">
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>271270000000</v>
+        <v>271120000000</v>
       </c>
     </row>
     <row r="52">
@@ -1261,7 +1261,7 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>267290000000</v>
+        <v>269650000000</v>
       </c>
     </row>
     <row r="53">
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>259020000000</v>
+        <v>253630000000</v>
       </c>
     </row>
     <row r="54">
@@ -1291,37 +1291,37 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>255310000000</v>
+        <v>251850000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Shell Plc ADR</t>
+          <t>Astrazeneca plc</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>250480000000</v>
+        <v>250470000000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Astrazeneca plc</t>
+          <t>Shell Plc ADR</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>241350000000</v>
+        <v>244680000000</v>
       </c>
     </row>
     <row r="57">
@@ -1336,7 +1336,7 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>234720000000</v>
+        <v>236040000000</v>
       </c>
     </row>
     <row r="58">
@@ -1351,7 +1351,7 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>234140000000</v>
+        <v>235680000000</v>
       </c>
     </row>
     <row r="59">
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>225630000000</v>
+        <v>227760000000</v>
       </c>
     </row>
     <row r="60">
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>223410000000</v>
+        <v>226360000000</v>
       </c>
     </row>
     <row r="61">
@@ -1396,67 +1396,67 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>221540000000</v>
+        <v>222270000000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>AMGEN Inc</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>215080000000</v>
+        <v>220110000000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>211420000000</v>
+        <v>213690000000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AMGEN Inc</t>
+          <t>Thermo Fisher Scientific Inc</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>210500000000</v>
+        <v>213650000000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>208810000000</v>
+        <v>200000000000</v>
       </c>
     </row>
     <row r="66">
@@ -1471,52 +1471,52 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>201290000000</v>
+        <v>197800000000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc</t>
+          <t>McDonald's Corp</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>194780000000</v>
+        <v>194680000000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>McDonald's Corp</t>
+          <t>Verizon Communications Inc</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>190660000000</v>
+        <v>193070000000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>T-Mobile US Inc</t>
+          <t>Boeing Co</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>190090000000</v>
+        <v>189840000000</v>
       </c>
     </row>
     <row r="70">
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>189860000000</v>
+        <v>189420000000</v>
       </c>
     </row>
     <row r="71">
@@ -1546,52 +1546,52 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>189480000000</v>
+        <v>188480000000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>Charles Schwab Corp</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>189080000000</v>
+        <v>187860000000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Boeing Co</t>
+          <t>Shopify Inc</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>187440000000</v>
+        <v>187170000000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Charles Schwab Corp</t>
+          <t>T-Mobile US Inc</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>184960000000</v>
+        <v>186070000000</v>
       </c>
     </row>
     <row r="75">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>183920000000</v>
+        <v>184320000000</v>
       </c>
     </row>
     <row r="76">
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>182490000000</v>
+        <v>182920000000</v>
       </c>
     </row>
     <row r="77">
@@ -1636,67 +1636,67 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>181900000000</v>
+        <v>179210000000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>170800000000</v>
+        <v>178950000000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Blackstone Inc</t>
+          <t>Walt Disney Co</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>170650000000</v>
+        <v>176710000000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Walt Disney Co</t>
+          <t>Blackstone Inc</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>170490000000</v>
+        <v>169200000000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>167920000000</v>
+        <v>165440000000</v>
       </c>
     </row>
     <row r="82">
@@ -1711,37 +1711,37 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>166650000000</v>
+        <v>165200000000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>160210000000</v>
+        <v>163590000000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Shopify Inc</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>160000000000</v>
+        <v>160420000000</v>
       </c>
     </row>
     <row r="85">
@@ -1756,22 +1756,22 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>156420000000</v>
+        <v>158050000000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>AT&amp;T Inc</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>150540000000</v>
+        <v>158020000000</v>
       </c>
     </row>
     <row r="87">
@@ -1786,22 +1786,22 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>148690000000</v>
+        <v>149530000000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Uber Technologies Inc</t>
+          <t>Danaher Corp</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>146540000000</v>
+        <v>140360000000</v>
       </c>
     </row>
     <row r="89">
@@ -1816,112 +1816,112 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>140990000000</v>
+        <v>140360000000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Corning Inc</t>
+          <t>Uber Technologies Inc</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>137730000000</v>
+        <v>138790000000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Danaher Corp</t>
+          <t>Chubb Limited</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>136930000000</v>
+        <v>136010000000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corp</t>
+          <t>Corning Inc</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>136010000000</v>
+        <v>134980000000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Co</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>134590000000</v>
+        <v>134010000000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Chubb Limited</t>
+          <t>Lockheed Martin Corp</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>134370000000</v>
+        <v>133300000000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Intuitive Surgical Inc</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>132380000000</v>
+        <v>132550000000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Intuitive Surgical Inc</t>
+          <t>Bristol-Myers Squibb Co</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>130100000000</v>
+        <v>129980000000</v>
       </c>
     </row>
     <row r="97">
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>129570000000</v>
+        <v>129440000000</v>
       </c>
     </row>
     <row r="98">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>123150000000</v>
+        <v>123690000000</v>
       </c>
     </row>
     <row r="99">
@@ -1966,7 +1966,7 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>122280000000</v>
+        <v>123320000000</v>
       </c>
     </row>
     <row r="100">
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>121610000000</v>
+        <v>120880000000</v>
       </c>
     </row>
     <row r="101">
@@ -1996,7 +1996,7 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>119670000000</v>
+        <v>120840000000</v>
       </c>
     </row>
     <row r="102">
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>113660000000</v>
+        <v>114280000000</v>
       </c>
     </row>
     <row r="103">
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>110340000000</v>
+        <v>110070000000</v>
       </c>
     </row>
     <row r="104">
@@ -2041,7 +2041,7 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>109790000000</v>
+        <v>109820000000</v>
       </c>
     </row>
     <row r="105">
@@ -2056,22 +2056,22 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>108180000000</v>
+        <v>107960000000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>107010000000</v>
+        <v>107000000000</v>
       </c>
     </row>
     <row r="107">
@@ -2086,67 +2086,67 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>104290000000</v>
+        <v>104480000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>Equinix Inc</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>103920000000</v>
+        <v>104220000000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Equinix Inc</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>103760000000</v>
+        <v>104040000000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>102570000000</v>
+        <v>103080000000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>102350000000</v>
+        <v>100800000000</v>
       </c>
     </row>
     <row r="112">
@@ -2161,7 +2161,7 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>100070000000</v>
+        <v>100040000000</v>
       </c>
     </row>
     <row r="113">
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>98450000000</v>
+        <v>99280000000</v>
       </c>
     </row>
     <row r="114">
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>95740000000</v>
+        <v>97470000000</v>
       </c>
     </row>
     <row r="115">
@@ -2206,52 +2206,52 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>93580000000</v>
+        <v>93900000000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>United Parcel Service Inc</t>
+          <t>Airbnb Inc</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>92740000000</v>
+        <v>91910000000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>MMC</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Marsh</t>
+          <t>United Parcel Service Inc</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>91360000000</v>
+        <v>91550000000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>MMC</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Airbnb Inc</t>
+          <t>Marsh</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>90360000000</v>
+        <v>91370000000</v>
       </c>
     </row>
     <row r="119">
@@ -2266,187 +2266,187 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>88520000000</v>
+        <v>89700000000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>HCA Healthcare Inc</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>87360000000</v>
+        <v>88690000000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>HCA Healthcare Inc</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>86760000000</v>
+        <v>87810000000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange Inc</t>
+          <t>Elevance Health Inc</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>83760000000</v>
+        <v>84850000000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Elevance Health Inc</t>
+          <t>Intercontinental Exchange Inc</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>81980000000</v>
+        <v>84120000000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Apollo Global Management Inc</t>
+          <t>Northrop Grumman Corp</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>78740000000</v>
+        <v>79200000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp</t>
+          <t>Regeneron Pharmaceuticals Inc</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>78350000000</v>
+        <v>79130000000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals Inc</t>
+          <t>General Motors Company</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>78300000000</v>
+        <v>78230000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>General Motors Company</t>
+          <t>Apollo Global Management Inc</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>77490000000</v>
+        <v>76690000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SLB Ltd</t>
+          <t>Colgate-Palmolive Co</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>75410000000</v>
+        <v>74360000000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive Co</t>
+          <t>SLB Ltd</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>73760000000</v>
+        <v>74070000000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Cigna Group</t>
+          <t>Ferrari NV</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>72420000000</v>
+        <v>71560000000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Ferrari NV</t>
+          <t>Cigna Group</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>70860000000</v>
+        <v>71480000000</v>
       </c>
     </row>
     <row r="132">
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>69220000000</v>
+        <v>69950000000</v>
       </c>
     </row>
     <row r="133">
@@ -2476,7 +2476,7 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>67270000000</v>
+        <v>67080000000</v>
       </c>
     </row>
     <row r="134">
@@ -2491,37 +2491,37 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>63180000000</v>
+        <v>65150000000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Astera Labs Inc</t>
+          <t>Nike Inc</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>61990000000</v>
+        <v>62970000000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Nike Inc</t>
+          <t>Ford Motor Co</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>61610000000</v>
+        <v>56350000000</v>
       </c>
     </row>
     <row r="137">
@@ -2536,22 +2536,22 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>56810000000</v>
+        <v>55110000000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Ford Motor Co</t>
+          <t>Astera Labs Inc</t>
         </is>
       </c>
       <c r="L138" t="n">
-        <v>56790000000</v>
+        <v>54580000000</v>
       </c>
     </row>
     <row r="139">
@@ -2566,7 +2566,7 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>54790000000</v>
+        <v>53520000000</v>
       </c>
     </row>
     <row r="140">
@@ -2581,37 +2581,37 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>51590000000</v>
+        <v>51230000000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Block Inc</t>
+          <t>Autodesk Inc</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>50380000000</v>
+        <v>50650000000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Block Inc</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>50140000000</v>
+        <v>50110000000</v>
       </c>
     </row>
     <row r="143">
@@ -2626,22 +2626,22 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>50080000000</v>
+        <v>49560000000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Autodesk Inc</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>50050000000</v>
+        <v>49040000000</v>
       </c>
     </row>
     <row r="145">
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>48290000000</v>
+        <v>47400000000</v>
       </c>
     </row>
     <row r="146">
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>44550000000</v>
+        <v>44760000000</v>
       </c>
     </row>
     <row r="147">
@@ -2686,7 +2686,7 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>42800000000</v>
+        <v>43660000000</v>
       </c>
     </row>
     <row r="148">
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>42310000000</v>
+        <v>42150000000</v>
       </c>
     </row>
     <row r="149">
@@ -2716,7 +2716,7 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>41550000000</v>
+        <v>41570000000</v>
       </c>
     </row>
     <row r="150">
@@ -2731,37 +2731,37 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>40530000000</v>
+        <v>40640000000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>JD</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>JD.com Inc ADR</t>
+          <t>Coinbase Global Inc</t>
         </is>
       </c>
       <c r="L151" t="n">
-        <v>40000000000</v>
+        <v>39490000000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Coinbase Global Inc</t>
+          <t>JD.com Inc ADR</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>39710000000</v>
+        <v>39480000000</v>
       </c>
     </row>
     <row r="153">
@@ -2776,67 +2776,67 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>34220000000</v>
+        <v>37800000000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Zoetis Inc</t>
+          <t>Estee Lauder Cos. Inc</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>31880000000</v>
+        <v>31460000000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Estee Lauder Cos. Inc</t>
+          <t>Zoetis Inc</t>
         </is>
       </c>
       <c r="L155" t="n">
-        <v>31470000000</v>
+        <v>31190000000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>RDDT</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Reddit Inc</t>
+          <t>Illumina Inc</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>30810000000</v>
+        <v>30180000000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>RDDT</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Illumina Inc</t>
+          <t>Reddit Inc</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>30650000000</v>
+        <v>29900000000</v>
       </c>
     </row>
     <row r="158">
@@ -2851,82 +2851,82 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>29940000000</v>
+        <v>29510000000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Fiserv Inc</t>
+          <t>Twilio Inc</t>
         </is>
       </c>
       <c r="L159" t="n">
-        <v>29740000000</v>
+        <v>29330000000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Twilio Inc</t>
+          <t>Fiserv Inc</t>
         </is>
       </c>
       <c r="L160" t="n">
-        <v>29450000000</v>
+        <v>28850000000</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>AFRM</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Zscaler Inc</t>
+          <t>Affirm Holdings Inc</t>
         </is>
       </c>
       <c r="L161" t="n">
-        <v>26390000000</v>
+        <v>26280000000</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>First Solar Inc</t>
+          <t>Zscaler Inc</t>
         </is>
       </c>
       <c r="L162" t="n">
-        <v>26180000000</v>
+        <v>26140000000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>AFRM</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Affirm Holdings Inc</t>
+          <t>First Solar Inc</t>
         </is>
       </c>
       <c r="L163" t="n">
-        <v>26160000000</v>
+        <v>25450000000</v>
       </c>
     </row>
     <row r="164">
@@ -2941,7 +2941,7 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>23990000000</v>
+        <v>23410000000</v>
       </c>
     </row>
     <row r="165">
@@ -2956,7 +2956,7 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>22750000000</v>
+        <v>22460000000</v>
       </c>
     </row>
     <row r="166">
@@ -2971,22 +2971,22 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>21860000000</v>
+        <v>21800000000</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>DKNG</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>DraftKings Inc</t>
+          <t>Charter Communications Inc</t>
         </is>
       </c>
       <c r="L167" t="n">
-        <v>20990000000</v>
+        <v>20490000000</v>
       </c>
     </row>
     <row r="168">
@@ -3001,22 +3001,22 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>20500000000</v>
+        <v>19610000000</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>DKNG</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Charter Communications Inc</t>
+          <t>DraftKings Inc</t>
         </is>
       </c>
       <c r="L169" t="n">
-        <v>20480000000</v>
+        <v>19350000000</v>
       </c>
     </row>
     <row r="170">
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>16580000000</v>
+        <v>15860000000</v>
       </c>
     </row>
     <row r="171">
@@ -3046,7 +3046,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>15720000000</v>
+        <v>15730000000</v>
       </c>
     </row>
     <row r="172">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>14580000000</v>
+        <v>13880000000</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>PINS</t>
+          <t>TXRH</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Pinterest Inc</t>
+          <t>Texas Roadhouse Inc</t>
         </is>
       </c>
       <c r="L175" t="n">
-        <v>14330000000</v>
+        <v>13700000000</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>TXRH</t>
+          <t>PINS</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Texas Roadhouse Inc</t>
+          <t>Pinterest Inc</t>
         </is>
       </c>
       <c r="L176" t="n">
-        <v>13690000000</v>
+        <v>13090000000</v>
       </c>
     </row>
     <row r="177">
@@ -3136,67 +3136,67 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>10560000000</v>
+        <v>10820000000</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>OSCR</t>
+          <t>PRMB</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Oscar Health Inc</t>
+          <t>Primo Brands Corp</t>
         </is>
       </c>
       <c r="L178" t="n">
-        <v>9160000000</v>
+        <v>9190000000</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>OSCR</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Applied Digital Corp</t>
+          <t>Oscar Health Inc</t>
         </is>
       </c>
       <c r="L179" t="n">
-        <v>9110000000</v>
+        <v>9080000000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>AeroVironment Inc</t>
+          <t>Applied Digital Corp</t>
         </is>
       </c>
       <c r="L180" t="n">
-        <v>8550000000</v>
+        <v>8710000000</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>PRMB</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Primo Brands Corp</t>
+          <t>AeroVironment Inc</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>8450000000</v>
+        <v>8510000000</v>
       </c>
     </row>
     <row r="182">
@@ -3211,37 +3211,37 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>8330000000</v>
+        <v>8290000000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>OKLO</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Celsius Holdings Inc</t>
+          <t>Oklo Inc</t>
         </is>
       </c>
       <c r="L183" t="n">
-        <v>7550000000</v>
+        <v>7480000000</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>OKLO</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Oklo Inc</t>
+          <t>Celsius Holdings Inc</t>
         </is>
       </c>
       <c r="L184" t="n">
-        <v>7540000000</v>
+        <v>7450000000</v>
       </c>
     </row>
     <row r="185">
@@ -3256,37 +3256,37 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>7440000000</v>
+        <v>7330000000</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>MBLY</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Mobileye Global Inc</t>
+          <t>SentinelOne Inc</t>
         </is>
       </c>
       <c r="L186" t="n">
-        <v>7350000000</v>
+        <v>7200000000</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>MBLY</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>SentinelOne Inc</t>
+          <t>Mobileye Global Inc</t>
         </is>
       </c>
       <c r="L187" t="n">
-        <v>7190000000</v>
+        <v>7180000000</v>
       </c>
     </row>
     <row r="188">
@@ -3301,7 +3301,7 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>5800000000</v>
+        <v>5580000000</v>
       </c>
     </row>
     <row r="189">
@@ -3316,7 +3316,7 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>5120000000</v>
+        <v>5070000000</v>
       </c>
     </row>
     <row r="190">
@@ -3346,37 +3346,37 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>4480000000</v>
+        <v>4290000000</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>LMND</t>
+          <t>FSLY</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Lemonade Inc</t>
+          <t>Fastly Inc</t>
         </is>
       </c>
       <c r="L192" t="n">
-        <v>4160000000</v>
+        <v>4070000000</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>FSLY</t>
+          <t>LMND</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Fastly Inc</t>
+          <t>Lemonade Inc</t>
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3900000000</v>
+        <v>4000000000</v>
       </c>
 